--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-31.xlsx
@@ -655,7 +655,7 @@
     <t>Melgar</t>
   </si>
   <si>
-    <t>2026-08-29 01:01:41</t>
+    <t>2026-08-29 03:32:28</t>
   </si>
 </sst>
 </file>
@@ -1255,7 +1255,7 @@
         <v>1.61</v>
       </c>
       <c r="H2">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="I2">
         <v>6.8</v>
@@ -1273,7 +1273,7 @@
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="O2">
         <v>1.24</v>
@@ -1282,13 +1282,13 @@
         <v>2.04</v>
       </c>
       <c r="Q2">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="R2">
         <v>1.42</v>
       </c>
       <c r="S2">
-        <v>2.76</v>
+        <v>2.64</v>
       </c>
       <c r="T2">
         <v>1.01</v>
@@ -1300,7 +1300,7 @@
         <v>1.17</v>
       </c>
       <c r="W2">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1506,7 +1506,7 @@
         <v>6.4</v>
       </c>
       <c r="K3">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1575,7 +1575,7 @@
         <v>14</v>
       </c>
       <c r="AH3">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AI3">
         <v>1000</v>
@@ -1584,7 +1584,7 @@
         <v>15.5</v>
       </c>
       <c r="AK3">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AL3">
         <v>1000</v>
@@ -1599,58 +1599,58 @@
         <v>1000</v>
       </c>
       <c r="AP3">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="AQ3">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="AR3">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="AS3">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="AT3">
-        <v>1.92</v>
+        <v>2.26</v>
       </c>
       <c r="AU3">
-        <v>1.96</v>
+        <v>2.3</v>
       </c>
       <c r="AV3">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="AW3">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="AX3">
-        <v>1.85</v>
+        <v>7.8</v>
       </c>
       <c r="AY3">
-        <v>1.86</v>
+        <v>2.16</v>
       </c>
       <c r="AZ3">
-        <v>2.14</v>
+        <v>2.44</v>
       </c>
       <c r="BA3">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="BB3">
-        <v>1.88</v>
+        <v>2.2</v>
       </c>
       <c r="BC3">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="BD3">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="BE3">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="BF3">
-        <v>1.44</v>
+        <v>1.62</v>
       </c>
       <c r="BG3">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1978,7 +1978,7 @@
         <v>2.24</v>
       </c>
       <c r="G5">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="H5">
         <v>3.6</v>
@@ -1987,10 +1987,10 @@
         <v>4.4</v>
       </c>
       <c r="J5">
-        <v>2.72</v>
+        <v>2.62</v>
       </c>
       <c r="K5">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -2005,7 +2005,7 @@
         <v>1.01</v>
       </c>
       <c r="P5">
-        <v>1.5</v>
+        <v>1.55</v>
       </c>
       <c r="Q5">
         <v>2.52</v>
@@ -2017,16 +2017,16 @@
         <v>4.9</v>
       </c>
       <c r="T5">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="U5">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="V5">
         <v>1.29</v>
       </c>
       <c r="W5">
-        <v>1.68</v>
+        <v>1.64</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -2220,7 +2220,7 @@
         <v>1.99</v>
       </c>
       <c r="G6">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="H6">
         <v>4.1</v>
@@ -2268,7 +2268,7 @@
         <v>1.23</v>
       </c>
       <c r="W6">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2459,22 +2459,22 @@
         <v>177</v>
       </c>
       <c r="F7">
-        <v>1.44</v>
+        <v>1.5</v>
       </c>
       <c r="G7">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H7">
         <v>6.2</v>
       </c>
       <c r="I7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="J7">
         <v>4.6</v>
       </c>
       <c r="K7">
-        <v>7</v>
+        <v>5.9</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2483,19 +2483,19 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>1.52</v>
+        <v>2.4</v>
       </c>
       <c r="O7">
         <v>1.15</v>
       </c>
       <c r="P7">
-        <v>1.52</v>
+        <v>2.4</v>
       </c>
       <c r="Q7">
         <v>1.46</v>
       </c>
       <c r="R7">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="S7">
         <v>2.14</v>
@@ -2510,7 +2510,7 @@
         <v>1.13</v>
       </c>
       <c r="W7">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -3672,7 +3672,7 @@
         <v>2.04</v>
       </c>
       <c r="G12">
-        <v>2.78</v>
+        <v>2.48</v>
       </c>
       <c r="H12">
         <v>2.92</v>
@@ -3944,7 +3944,7 @@
         <v>1.79</v>
       </c>
       <c r="Q13">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -4153,7 +4153,7 @@
         <v>184</v>
       </c>
       <c r="F14">
-        <v>1.43</v>
+        <v>1.38</v>
       </c>
       <c r="G14">
         <v>1.54</v>
@@ -4195,13 +4195,13 @@
         <v>2.5</v>
       </c>
       <c r="T14">
-        <v>1.67</v>
+        <v>1.01</v>
       </c>
       <c r="U14">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="V14">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="W14">
         <v>2.84</v>
@@ -4398,7 +4398,7 @@
         <v>5.7</v>
       </c>
       <c r="G15">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="H15">
         <v>1.62</v>
@@ -4407,7 +4407,7 @@
         <v>1.68</v>
       </c>
       <c r="J15">
-        <v>4</v>
+        <v>3.85</v>
       </c>
       <c r="K15">
         <v>4.8</v>
@@ -4425,22 +4425,22 @@
         <v>1.28</v>
       </c>
       <c r="P15">
-        <v>1.93</v>
+        <v>1.88</v>
       </c>
       <c r="Q15">
-        <v>1.72</v>
+        <v>1.84</v>
       </c>
       <c r="R15">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="S15">
         <v>3.05</v>
       </c>
       <c r="T15">
-        <v>1.86</v>
+        <v>1.04</v>
       </c>
       <c r="U15">
-        <v>1.81</v>
+        <v>1.01</v>
       </c>
       <c r="V15">
         <v>2.46</v>
@@ -4449,172 +4449,172 @@
         <v>1.17</v>
       </c>
       <c r="X15">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Y15">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="Z15">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AA15">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="AB15">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AC15">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AD15">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AE15">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AF15">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AG15">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AH15">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="AI15">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AJ15">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AK15">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AL15">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AM15">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AN15">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AO15">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AP15">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ15">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR15">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AS15">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU15">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AV15">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW15">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AX15">
-        <v>3.95</v>
+        <v>1.01</v>
       </c>
       <c r="AY15">
-        <v>3.65</v>
+        <v>1.01</v>
       </c>
       <c r="AZ15">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BA15">
-        <v>3.85</v>
+        <v>1.01</v>
       </c>
       <c r="BB15">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BC15">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BD15">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BE15">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF15">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BG15">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BH15">
-        <v>4.2</v>
+        <v>1000</v>
       </c>
       <c r="BI15">
-        <v>2.84</v>
+        <v>1.01</v>
       </c>
       <c r="BJ15">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="BK15">
-        <v>3.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL15">
         <v>1000</v>
       </c>
       <c r="BM15">
-        <v>4.5</v>
+        <v>1.01</v>
       </c>
       <c r="BN15">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BO15">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BP15">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="BQ15">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BR15">
         <v>1000</v>
       </c>
       <c r="BS15">
-        <v>4.3</v>
+        <v>1.01</v>
       </c>
       <c r="BT15">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BU15">
-        <v>3.3</v>
+        <v>1.01</v>
       </c>
       <c r="BV15">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BW15">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="BX15">
-        <v>32</v>
+        <v>1000</v>
       </c>
       <c r="BY15">
-        <v>4</v>
+        <v>1.01</v>
       </c>
       <c r="BZ15">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="CA15">
-        <v>3.9</v>
+        <v>1.01</v>
       </c>
       <c r="CB15" t="s">
         <v>213</v>
@@ -4664,10 +4664,10 @@
         <v>3.5</v>
       </c>
       <c r="O16">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P16">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="Q16">
         <v>2.1</v>
@@ -4760,7 +4760,7 @@
         <v>20</v>
       </c>
       <c r="AU16">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AV16">
         <v>9.6</v>
@@ -5366,7 +5366,7 @@
         <v>1.94</v>
       </c>
       <c r="G19">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="H19">
         <v>3.5</v>
@@ -5378,7 +5378,7 @@
         <v>4.1</v>
       </c>
       <c r="K19">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -5620,7 +5620,7 @@
         <v>4.7</v>
       </c>
       <c r="K20">
-        <v>50</v>
+        <v>6.6</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -5635,7 +5635,7 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>1.25</v>
+        <v>2.08</v>
       </c>
       <c r="Q20">
         <v>1.53</v>
@@ -5847,22 +5847,22 @@
         <v>191</v>
       </c>
       <c r="F21">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="G21">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="H21">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="I21">
-        <v>7.4</v>
+        <v>5.6</v>
       </c>
       <c r="J21">
-        <v>3.45</v>
+        <v>3.65</v>
       </c>
       <c r="K21">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -7060,20 +7060,20 @@
         <v>2.92</v>
       </c>
       <c r="G26">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="H26">
         <v>2.58</v>
       </c>
       <c r="I26">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="J26">
+        <v>3.55</v>
+      </c>
+      <c r="K26">
         <v>3.6</v>
       </c>
-      <c r="K26">
-        <v>3.7</v>
-      </c>
       <c r="L26">
         <v>0</v>
       </c>
@@ -7087,10 +7087,10 @@
         <v>0</v>
       </c>
       <c r="P26">
-        <v>1.83</v>
+        <v>1.89</v>
       </c>
       <c r="Q26">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="R26">
         <v>0</v>
@@ -7314,7 +7314,7 @@
         <v>3.1</v>
       </c>
       <c r="K27">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -7344,7 +7344,7 @@
         <v>2.5</v>
       </c>
       <c r="U27">
-        <v>1.63</v>
+        <v>1.62</v>
       </c>
       <c r="V27">
         <v>0</v>
@@ -7371,7 +7371,7 @@
         <v>7.4</v>
       </c>
       <c r="AD27">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AE27">
         <v>110</v>
@@ -7392,7 +7392,7 @@
         <v>38</v>
       </c>
       <c r="AK27">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AL27">
         <v>100</v>
@@ -7449,19 +7449,19 @@
         <v>32</v>
       </c>
       <c r="BD27">
+        <v>12</v>
+      </c>
+      <c r="BE27">
+        <v>13.5</v>
+      </c>
+      <c r="BF27">
         <v>36</v>
       </c>
-      <c r="BE27">
+      <c r="BG27">
         <v>13</v>
       </c>
-      <c r="BF27">
-        <v>23</v>
-      </c>
-      <c r="BG27">
-        <v>12.5</v>
-      </c>
       <c r="BH27">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="BI27">
         <v>1.01</v>
@@ -8515,7 +8515,7 @@
         <v>1.48</v>
       </c>
       <c r="H32">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="I32">
         <v>10.5</v>
@@ -8763,7 +8763,7 @@
         <v>2.22</v>
       </c>
       <c r="J33">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K33">
         <v>4.1</v>
@@ -8999,7 +8999,7 @@
         <v>5.1</v>
       </c>
       <c r="H34">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="I34">
         <v>1.93</v>
@@ -9265,7 +9265,7 @@
         <v>1.33</v>
       </c>
       <c r="P35">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q35">
         <v>2.02</v>
@@ -9292,7 +9292,7 @@
         <v>15</v>
       </c>
       <c r="Y35">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Z35">
         <v>36</v>
@@ -9313,7 +9313,7 @@
         <v>60</v>
       </c>
       <c r="AF35">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG35">
         <v>10.5</v>
@@ -9331,13 +9331,13 @@
         <v>21</v>
       </c>
       <c r="AL35">
-        <v>44</v>
+        <v>38</v>
       </c>
       <c r="AM35">
         <v>110</v>
       </c>
       <c r="AN35">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AO35">
         <v>75</v>
@@ -9352,7 +9352,7 @@
         <v>19.5</v>
       </c>
       <c r="AS35">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AT35">
         <v>8.4</v>
@@ -9388,7 +9388,7 @@
         <v>23</v>
       </c>
       <c r="BE35">
-        <v>11.5</v>
+        <v>38</v>
       </c>
       <c r="BF35">
         <v>12.5</v>
@@ -9501,7 +9501,7 @@
         <v>1.06</v>
       </c>
       <c r="N36">
-        <v>3.55</v>
+        <v>2.66</v>
       </c>
       <c r="O36">
         <v>1.3</v>
@@ -9725,13 +9725,13 @@
         <v>7.2</v>
       </c>
       <c r="H37">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="I37">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="J37">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="K37">
         <v>4.6</v>
@@ -9755,7 +9755,7 @@
         <v>1.89</v>
       </c>
       <c r="R37">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S37">
         <v>3.3</v>
@@ -9776,7 +9776,7 @@
         <v>17</v>
       </c>
       <c r="Y37">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z37">
         <v>9</v>
@@ -9797,19 +9797,19 @@
         <v>16.5</v>
       </c>
       <c r="AF37">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AG37">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AH37">
         <v>24</v>
       </c>
       <c r="AI37">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AJ37">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AK37">
         <v>130</v>
@@ -9821,7 +9821,7 @@
         <v>130</v>
       </c>
       <c r="AN37">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AO37">
         <v>8.6</v>
@@ -9842,7 +9842,7 @@
         <v>20</v>
       </c>
       <c r="AU37">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV37">
         <v>9</v>
@@ -9854,22 +9854,22 @@
         <v>48</v>
       </c>
       <c r="AY37">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ37">
         <v>21</v>
       </c>
       <c r="BA37">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB37">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="BC37">
-        <v>38</v>
+        <v>55</v>
       </c>
       <c r="BD37">
-        <v>38</v>
+        <v>60</v>
       </c>
       <c r="BE37">
         <v>42</v>
@@ -9884,7 +9884,7 @@
         <v>1000</v>
       </c>
       <c r="BI37">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ37">
         <v>1000</v>
@@ -9961,22 +9961,22 @@
         <v>208</v>
       </c>
       <c r="F38">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="G38">
-        <v>2.16</v>
+        <v>2.12</v>
       </c>
       <c r="H38">
         <v>3.15</v>
       </c>
       <c r="I38">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="J38">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K38">
-        <v>5.1</v>
+        <v>5.6</v>
       </c>
       <c r="L38">
         <v>0</v>
@@ -9991,10 +9991,10 @@
         <v>0</v>
       </c>
       <c r="P38">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="Q38">
-        <v>1.29</v>
+        <v>1.26</v>
       </c>
       <c r="R38">
         <v>0</v>
@@ -10203,16 +10203,16 @@
         <v>209</v>
       </c>
       <c r="F39">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="G39">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="H39">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="I39">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="J39">
         <v>3.6</v>
@@ -10236,7 +10236,7 @@
         <v>1.25</v>
       </c>
       <c r="Q39">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="R39">
         <v>0</v>
@@ -10245,10 +10245,10 @@
         <v>0</v>
       </c>
       <c r="T39">
-        <v>1.04</v>
+        <v>1.73</v>
       </c>
       <c r="U39">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="V39">
         <v>0</v>
@@ -10257,7 +10257,7 @@
         <v>0</v>
       </c>
       <c r="X39">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y39">
         <v>19.5</v>
@@ -10269,7 +10269,7 @@
         <v>150</v>
       </c>
       <c r="AB39">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC39">
         <v>9.800000000000001</v>
@@ -10281,7 +10281,7 @@
         <v>85</v>
       </c>
       <c r="AF39">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG39">
         <v>12</v>
@@ -10293,7 +10293,7 @@
         <v>90</v>
       </c>
       <c r="AJ39">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK39">
         <v>24</v>
@@ -10317,22 +10317,22 @@
         <v>14.5</v>
       </c>
       <c r="AR39">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="AS39">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="AT39">
         <v>7.2</v>
       </c>
       <c r="AU39">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AV39">
         <v>18</v>
       </c>
       <c r="AW39">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AX39">
         <v>9.800000000000001</v>
@@ -10344,7 +10344,7 @@
         <v>17.5</v>
       </c>
       <c r="BA39">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="BB39">
         <v>17.5</v>
@@ -10353,16 +10353,16 @@
         <v>18</v>
       </c>
       <c r="BD39">
-        <v>4.5</v>
+        <v>4.7</v>
       </c>
       <c r="BE39">
-        <v>4.9</v>
+        <v>5.1</v>
       </c>
       <c r="BF39">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BG39">
-        <v>4.8</v>
+        <v>5.1</v>
       </c>
       <c r="BH39">
         <v>0</v>
@@ -10478,7 +10478,7 @@
         <v>1.25</v>
       </c>
       <c r="Q40">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="R40">
         <v>0</v>
@@ -10693,16 +10693,16 @@
         <v>1.19</v>
       </c>
       <c r="H41">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="I41">
         <v>21</v>
       </c>
       <c r="J41">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="K41">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="L41">
         <v>0</v>
@@ -10711,13 +10711,13 @@
         <v>1.02</v>
       </c>
       <c r="N41">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="O41">
         <v>1.13</v>
       </c>
       <c r="P41">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="Q41">
         <v>1.38</v>
@@ -10789,7 +10789,7 @@
         <v>180</v>
       </c>
       <c r="AN41">
-        <v>2.96</v>
+        <v>2.94</v>
       </c>
       <c r="AO41">
         <v>350</v>
@@ -10804,7 +10804,7 @@
         <v>16.5</v>
       </c>
       <c r="AS41">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="AT41">
         <v>11.5</v>
@@ -10828,7 +10828,7 @@
         <v>24</v>
       </c>
       <c r="BA41">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BB41">
         <v>8.4</v>
@@ -10840,7 +10840,7 @@
         <v>23</v>
       </c>
       <c r="BE41">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BF41">
         <v>2.76</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-31.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="326" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="219">
   <si>
     <t>League</t>
   </si>
@@ -274,18 +274,21 @@
     <t>Kazakhstan Premier League</t>
   </si>
   <si>
+    <t>Latvian Virsliga</t>
+  </si>
+  <si>
     <t>Romanian Liga II</t>
   </si>
   <si>
-    <t>Latvian Virsliga</t>
-  </si>
-  <si>
     <t>Ukrainian Premier League</t>
   </si>
   <si>
     <t>Lithuanian A Lyga</t>
   </si>
   <si>
+    <t>Armenian Premier League</t>
+  </si>
+  <si>
     <t>Bulgarian A League</t>
   </si>
   <si>
@@ -298,12 +301,12 @@
     <t>Italian Serie A</t>
   </si>
   <si>
+    <t>Swedish Superettan</t>
+  </si>
+  <si>
     <t>Swedish Division 1</t>
   </si>
   <si>
-    <t>Swedish Superettan</t>
-  </si>
-  <si>
     <t>Swedish Allsvenskan</t>
   </si>
   <si>
@@ -430,18 +433,21 @@
     <t>Elimai FC</t>
   </si>
   <si>
+    <t>Liepajas Metalurgs</t>
+  </si>
+  <si>
     <t>ACS Fotbal Club Bacau</t>
   </si>
   <si>
-    <t>Liepajas Metalurgs</t>
-  </si>
-  <si>
     <t>FC Bukovyna</t>
   </si>
   <si>
     <t>FC Dziugas</t>
   </si>
   <si>
+    <t>FC Pyunik</t>
+  </si>
+  <si>
     <t>Dunav Ruse</t>
   </si>
   <si>
@@ -454,12 +460,12 @@
     <t>Lecce</t>
   </si>
   <si>
+    <t>Sundsvall</t>
+  </si>
+  <si>
     <t>Hammarby TFF</t>
   </si>
   <si>
-    <t>Sundsvall</t>
-  </si>
-  <si>
     <t>Sirius</t>
   </si>
   <si>
@@ -499,12 +505,12 @@
     <t>Racing Club (Uru)</t>
   </si>
   <si>
+    <t>Amed Sportif Faaliyetler</t>
+  </si>
+  <si>
     <t>Besiktas</t>
   </si>
   <si>
-    <t>Amed Sportif Faaliyetler</t>
-  </si>
-  <si>
     <t>Dijon</t>
   </si>
   <si>
@@ -526,6 +532,9 @@
     <t>Benfica</t>
   </si>
   <si>
+    <t>Celta Vigo B</t>
+  </si>
+  <si>
     <t>Barcelona</t>
   </si>
   <si>
@@ -553,18 +562,21 @@
     <t>Kairat Almaty</t>
   </si>
   <si>
+    <t>FK Riga</t>
+  </si>
+  <si>
     <t>CSM Slatina</t>
   </si>
   <si>
-    <t>FK Riga</t>
-  </si>
-  <si>
     <t>Dynamo Kiev</t>
   </si>
   <si>
     <t>Hegelmann Litauen</t>
   </si>
   <si>
+    <t>Ararat Armenia</t>
+  </si>
+  <si>
     <t>Lokomotiv Sofia</t>
   </si>
   <si>
@@ -577,12 +589,12 @@
     <t>Roma</t>
   </si>
   <si>
+    <t>Norrby IF</t>
+  </si>
+  <si>
     <t>Karlbergs BK</t>
   </si>
   <si>
-    <t>Norrby IF</t>
-  </si>
-  <si>
     <t>Malmo FF</t>
   </si>
   <si>
@@ -622,12 +634,12 @@
     <t>Albion FC</t>
   </si>
   <si>
+    <t>Trabzonspor</t>
+  </si>
+  <si>
     <t>Corum Belediyespor</t>
   </si>
   <si>
-    <t>Trabzonspor</t>
-  </si>
-  <si>
     <t>St Etienne</t>
   </si>
   <si>
@@ -649,13 +661,16 @@
     <t>Estoril Praia</t>
   </si>
   <si>
+    <t>CD Castellon</t>
+  </si>
+  <si>
     <t>Rayo Vallecano</t>
   </si>
   <si>
     <t>Melgar</t>
   </si>
   <si>
-    <t>2026-08-29 03:32:28</t>
+    <t>2026-08-29 06:03:47</t>
   </si>
 </sst>
 </file>
@@ -987,7 +1002,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB42"/>
+  <dimension ref="A1:CB44"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1237,16 +1252,16 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D2" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="E2" t="s">
-        <v>172</v>
+        <v>175</v>
       </c>
       <c r="F2">
         <v>1.57</v>
@@ -1273,7 +1288,7 @@
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>2.66</v>
+        <v>2.48</v>
       </c>
       <c r="O2">
         <v>1.24</v>
@@ -1282,13 +1297,13 @@
         <v>2.04</v>
       </c>
       <c r="Q2">
-        <v>1.71</v>
+        <v>1.51</v>
       </c>
       <c r="R2">
         <v>1.42</v>
       </c>
       <c r="S2">
-        <v>2.64</v>
+        <v>2.76</v>
       </c>
       <c r="T2">
         <v>1.01</v>
@@ -1471,7 +1486,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1479,34 +1494,34 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D3" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="E3" t="s">
-        <v>173</v>
+        <v>176</v>
       </c>
       <c r="F3">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="G3">
         <v>1.33</v>
       </c>
       <c r="H3">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="I3">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="J3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="K3">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1518,7 +1533,7 @@
         <v>7</v>
       </c>
       <c r="O3">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="P3">
         <v>3.05</v>
@@ -1530,7 +1545,7 @@
         <v>1.82</v>
       </c>
       <c r="S3">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="T3">
         <v>1.75</v>
@@ -1539,10 +1554,10 @@
         <v>2.1</v>
       </c>
       <c r="V3">
-        <v>1.09</v>
+        <v>1.08</v>
       </c>
       <c r="W3">
-        <v>3.9</v>
+        <v>3.8</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -1713,7 +1728,7 @@
         <v>0</v>
       </c>
       <c r="CB3" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1721,16 +1736,16 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="D4" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="E4" t="s">
-        <v>174</v>
+        <v>177</v>
       </c>
       <c r="F4">
         <v>1.93</v>
@@ -1748,7 +1763,7 @@
         <v>2.9</v>
       </c>
       <c r="K4">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1955,7 +1970,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1963,22 +1978,22 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C5" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D5" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E5" t="s">
-        <v>175</v>
+        <v>178</v>
       </c>
       <c r="F5">
         <v>2.24</v>
       </c>
       <c r="G5">
-        <v>2.56</v>
+        <v>2.48</v>
       </c>
       <c r="H5">
         <v>3.6</v>
@@ -1987,7 +2002,7 @@
         <v>4.4</v>
       </c>
       <c r="J5">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="K5">
         <v>3.55</v>
@@ -1999,13 +2014,13 @@
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>2.52</v>
+        <v>2.6</v>
       </c>
       <c r="O5">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="P5">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="Q5">
         <v>2.52</v>
@@ -2023,10 +2038,10 @@
         <v>1.71</v>
       </c>
       <c r="V5">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="W5">
-        <v>1.64</v>
+        <v>1.67</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -2098,7 +2113,7 @@
         <v>1.01</v>
       </c>
       <c r="AU5">
-        <v>6.2</v>
+        <v>5.9</v>
       </c>
       <c r="AV5">
         <v>1.01</v>
@@ -2113,7 +2128,7 @@
         <v>1.01</v>
       </c>
       <c r="AZ5">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BA5">
         <v>1.01</v>
@@ -2197,7 +2212,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2205,22 +2220,22 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C6" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D6" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E6" t="s">
-        <v>176</v>
+        <v>179</v>
       </c>
       <c r="F6">
         <v>1.99</v>
       </c>
       <c r="G6">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="H6">
         <v>4.1</v>
@@ -2268,7 +2283,7 @@
         <v>1.23</v>
       </c>
       <c r="W6">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2439,7 +2454,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2447,19 +2462,19 @@
         <v>81</v>
       </c>
       <c r="B7" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D7" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E7" t="s">
-        <v>177</v>
+        <v>180</v>
       </c>
       <c r="F7">
-        <v>1.5</v>
+        <v>1.41</v>
       </c>
       <c r="G7">
         <v>1.59</v>
@@ -2474,7 +2489,7 @@
         <v>4.6</v>
       </c>
       <c r="K7">
-        <v>5.9</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L7">
         <v>1.01</v>
@@ -2483,19 +2498,19 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="O7">
         <v>1.15</v>
       </c>
       <c r="P7">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="Q7">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R7">
-        <v>1.54</v>
+        <v>1.51</v>
       </c>
       <c r="S7">
         <v>2.14</v>
@@ -2504,7 +2519,7 @@
         <v>1.01</v>
       </c>
       <c r="U7">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="V7">
         <v>1.13</v>
@@ -2681,7 +2696,7 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2689,16 +2704,16 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C8" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D8" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E8" t="s">
-        <v>178</v>
+        <v>181</v>
       </c>
       <c r="F8">
         <v>1.04</v>
@@ -2716,7 +2731,7 @@
         <v>1.04</v>
       </c>
       <c r="K8">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="L8">
         <v>0</v>
@@ -2923,7 +2938,7 @@
         <v>0</v>
       </c>
       <c r="CB8" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="9" spans="1:80">
@@ -2931,16 +2946,16 @@
         <v>86</v>
       </c>
       <c r="B9" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C9" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D9" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="E9" t="s">
-        <v>179</v>
+        <v>182</v>
       </c>
       <c r="F9">
         <v>1.04</v>
@@ -2958,7 +2973,7 @@
         <v>1.04</v>
       </c>
       <c r="K9">
-        <v>1000</v>
+        <v>310</v>
       </c>
       <c r="L9">
         <v>0</v>
@@ -2973,7 +2988,7 @@
         <v>0</v>
       </c>
       <c r="P9">
-        <v>1.24</v>
+        <v>1.04</v>
       </c>
       <c r="Q9">
         <v>1.01</v>
@@ -3165,7 +3180,7 @@
         <v>0</v>
       </c>
       <c r="CB9" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="10" spans="1:80">
@@ -3173,16 +3188,16 @@
         <v>87</v>
       </c>
       <c r="B10" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C10" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D10" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="E10" t="s">
-        <v>180</v>
+        <v>183</v>
       </c>
       <c r="F10">
         <v>1.04</v>
@@ -3200,7 +3215,7 @@
         <v>1.04</v>
       </c>
       <c r="K10">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="L10">
         <v>0</v>
@@ -3215,7 +3230,7 @@
         <v>0</v>
       </c>
       <c r="P10">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="Q10">
         <v>1.01</v>
@@ -3407,7 +3422,7 @@
         <v>0</v>
       </c>
       <c r="CB10" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="11" spans="1:80">
@@ -3415,16 +3430,16 @@
         <v>88</v>
       </c>
       <c r="B11" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C11" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="D11" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="E11" t="s">
-        <v>181</v>
+        <v>184</v>
       </c>
       <c r="F11">
         <v>1.04</v>
@@ -3442,7 +3457,7 @@
         <v>1.04</v>
       </c>
       <c r="K11">
-        <v>1000</v>
+        <v>410</v>
       </c>
       <c r="L11">
         <v>0</v>
@@ -3649,7 +3664,7 @@
         <v>0</v>
       </c>
       <c r="CB11" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="12" spans="1:80">
@@ -3657,31 +3672,31 @@
         <v>89</v>
       </c>
       <c r="B12" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C12" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="D12" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="E12" t="s">
-        <v>182</v>
+        <v>185</v>
       </c>
       <c r="F12">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="G12">
-        <v>2.48</v>
+        <v>2.74</v>
       </c>
       <c r="H12">
-        <v>2.92</v>
+        <v>2.96</v>
       </c>
       <c r="I12">
         <v>4.5</v>
       </c>
       <c r="J12">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="K12">
         <v>6</v>
@@ -3699,10 +3714,10 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="Q12">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -3891,7 +3906,7 @@
         <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="13" spans="1:80">
@@ -3899,34 +3914,34 @@
         <v>90</v>
       </c>
       <c r="B13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C13" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="D13" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="E13" t="s">
-        <v>183</v>
+        <v>186</v>
       </c>
       <c r="F13">
-        <v>3.45</v>
+        <v>1.01</v>
       </c>
       <c r="G13">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="H13">
-        <v>1.93</v>
+        <v>1.01</v>
       </c>
       <c r="I13">
-        <v>2.6</v>
+        <v>1000</v>
       </c>
       <c r="J13">
-        <v>2.98</v>
+        <v>1.01</v>
       </c>
       <c r="K13">
-        <v>5.3</v>
+        <v>1000</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -3941,10 +3956,10 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>1.79</v>
+        <v>1.07</v>
       </c>
       <c r="Q13">
-        <v>2.04</v>
+        <v>1.01</v>
       </c>
       <c r="R13">
         <v>0</v>
@@ -4133,7 +4148,7 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="14" spans="1:80">
@@ -4141,241 +4156,241 @@
         <v>91</v>
       </c>
       <c r="B14" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C14" t="s">
         <v>120</v>
       </c>
       <c r="D14" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="E14" t="s">
-        <v>184</v>
+        <v>187</v>
       </c>
       <c r="F14">
-        <v>1.38</v>
+        <v>3.45</v>
       </c>
       <c r="G14">
-        <v>1.54</v>
+        <v>5.2</v>
       </c>
       <c r="H14">
-        <v>4.3</v>
+        <v>1.93</v>
       </c>
       <c r="I14">
-        <v>17</v>
+        <v>2.6</v>
       </c>
       <c r="J14">
-        <v>4.5</v>
+        <v>2.98</v>
       </c>
       <c r="K14">
-        <v>950</v>
+        <v>5.3</v>
       </c>
       <c r="L14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N14">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O14">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="P14">
-        <v>2.24</v>
+        <v>1.79</v>
       </c>
       <c r="Q14">
-        <v>1.6</v>
+        <v>2.04</v>
       </c>
       <c r="R14">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="S14">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V14">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W14">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="X14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ14">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA14">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="15" spans="1:80">
@@ -4383,70 +4398,70 @@
         <v>92</v>
       </c>
       <c r="B15" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C15" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D15" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="E15" t="s">
-        <v>185</v>
+        <v>188</v>
       </c>
       <c r="F15">
-        <v>5.7</v>
+        <v>1.38</v>
       </c>
       <c r="G15">
-        <v>7</v>
+        <v>1.54</v>
       </c>
       <c r="H15">
-        <v>1.62</v>
+        <v>3.7</v>
       </c>
       <c r="I15">
-        <v>1.68</v>
+        <v>17</v>
       </c>
       <c r="J15">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="K15">
-        <v>4.8</v>
+        <v>950</v>
       </c>
       <c r="L15">
         <v>1.01</v>
       </c>
       <c r="M15">
+        <v>1.01</v>
+      </c>
+      <c r="N15">
+        <v>2.24</v>
+      </c>
+      <c r="O15">
+        <v>1.2</v>
+      </c>
+      <c r="P15">
+        <v>2.24</v>
+      </c>
+      <c r="Q15">
+        <v>1.6</v>
+      </c>
+      <c r="R15">
+        <v>1.49</v>
+      </c>
+      <c r="S15">
+        <v>2.5</v>
+      </c>
+      <c r="T15">
+        <v>1.01</v>
+      </c>
+      <c r="U15">
+        <v>1.01</v>
+      </c>
+      <c r="V15">
         <v>1.06</v>
       </c>
-      <c r="N15">
-        <v>3.7</v>
-      </c>
-      <c r="O15">
-        <v>1.28</v>
-      </c>
-      <c r="P15">
-        <v>1.88</v>
-      </c>
-      <c r="Q15">
-        <v>1.84</v>
-      </c>
-      <c r="R15">
-        <v>1.32</v>
-      </c>
-      <c r="S15">
-        <v>3.05</v>
-      </c>
-      <c r="T15">
-        <v>1.04</v>
-      </c>
-      <c r="U15">
-        <v>1.01</v>
-      </c>
-      <c r="V15">
-        <v>2.46</v>
-      </c>
       <c r="W15">
-        <v>1.17</v>
+        <v>2.84</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4617,7 +4632,7 @@
         <v>1.01</v>
       </c>
       <c r="CB15" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="16" spans="1:80">
@@ -4625,178 +4640,178 @@
         <v>93</v>
       </c>
       <c r="B16" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C16" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="D16" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="E16" t="s">
-        <v>186</v>
+        <v>189</v>
       </c>
       <c r="F16">
-        <v>8.6</v>
+        <v>5.7</v>
       </c>
       <c r="G16">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="H16">
-        <v>1.51</v>
+        <v>1.62</v>
       </c>
       <c r="I16">
-        <v>1.52</v>
+        <v>1.67</v>
       </c>
       <c r="J16">
-        <v>4.3</v>
+        <v>3.9</v>
       </c>
       <c r="K16">
-        <v>4.5</v>
+        <v>4.8</v>
       </c>
       <c r="L16">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M16">
-        <v>1.08</v>
+        <v>1.04</v>
       </c>
       <c r="N16">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="O16">
-        <v>1.36</v>
+        <v>1.28</v>
       </c>
       <c r="P16">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="Q16">
-        <v>2.1</v>
+        <v>1.84</v>
       </c>
       <c r="R16">
         <v>1.32</v>
       </c>
       <c r="S16">
-        <v>3.9</v>
+        <v>3.05</v>
       </c>
       <c r="T16">
-        <v>2.3</v>
+        <v>1.87</v>
       </c>
       <c r="U16">
-        <v>1.74</v>
+        <v>1.88</v>
       </c>
       <c r="V16">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="W16">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X16">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="Y16">
-        <v>7</v>
+        <v>1000</v>
       </c>
       <c r="Z16">
-        <v>7.8</v>
+        <v>1000</v>
       </c>
       <c r="AA16">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AB16">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AC16">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="AD16">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AE16">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="AF16">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AG16">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AH16">
-        <v>30</v>
+        <v>1000</v>
       </c>
       <c r="AI16">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AJ16">
-        <v>420</v>
+        <v>1000</v>
       </c>
       <c r="AK16">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AL16">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AM16">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AN16">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="AO16">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AP16">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AQ16">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR16">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="AS16">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AT16">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AU16">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AV16">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AW16">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="AX16">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="AY16">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AZ16">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA16">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BB16">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BC16">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BD16">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BE16">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BF16">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BG16">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH16">
         <v>1000</v>
@@ -4859,7 +4874,7 @@
         <v>1.01</v>
       </c>
       <c r="CB16" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="17" spans="1:80">
@@ -4867,64 +4882,64 @@
         <v>94</v>
       </c>
       <c r="B17" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C17" t="s">
         <v>121</v>
       </c>
       <c r="D17" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="E17" t="s">
-        <v>187</v>
+        <v>190</v>
       </c>
       <c r="F17">
-        <v>1.44</v>
+        <v>8.6</v>
       </c>
       <c r="G17">
-        <v>1.61</v>
+        <v>9</v>
       </c>
       <c r="H17">
-        <v>2.62</v>
+        <v>1.51</v>
       </c>
       <c r="I17">
-        <v>1000</v>
+        <v>1.52</v>
       </c>
       <c r="J17">
-        <v>2.62</v>
+        <v>4.4</v>
       </c>
       <c r="K17">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N17">
-        <v>0</v>
+        <v>3.6</v>
       </c>
       <c r="O17">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P17">
-        <v>2.5</v>
+        <v>1.85</v>
       </c>
       <c r="Q17">
-        <v>1.47</v>
+        <v>2.1</v>
       </c>
       <c r="R17">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S17">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="T17">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U17">
-        <v>0</v>
+        <v>1.74</v>
       </c>
       <c r="V17">
         <v>0</v>
@@ -4933,175 +4948,175 @@
         <v>0</v>
       </c>
       <c r="X17">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="Y17">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z17">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA17">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AB17">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AC17">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD17">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AE17">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AF17">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AG17">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AH17">
-        <v>0</v>
+        <v>30</v>
       </c>
       <c r="AI17">
-        <v>0</v>
+        <v>55</v>
       </c>
       <c r="AJ17">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="AK17">
-        <v>0</v>
+        <v>200</v>
       </c>
       <c r="AL17">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AM17">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="AN17">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="AO17">
-        <v>0</v>
+        <v>9.4</v>
       </c>
       <c r="AP17">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ17">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AR17">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AS17">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AT17">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AU17">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AV17">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AW17">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AX17">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AY17">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AZ17">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BA17">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BB17">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BC17">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BD17">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BE17">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="BF17">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="BG17">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BH17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ17">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA17">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB17" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="18" spans="1:80">
@@ -5109,16 +5124,16 @@
         <v>95</v>
       </c>
       <c r="B18" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C18" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D18" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="E18" t="s">
-        <v>188</v>
+        <v>191</v>
       </c>
       <c r="F18">
         <v>3.15</v>
@@ -5343,7 +5358,7 @@
         <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="19" spans="1:80">
@@ -5351,34 +5366,34 @@
         <v>96</v>
       </c>
       <c r="B19" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C19" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D19" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="E19" t="s">
-        <v>189</v>
+        <v>192</v>
       </c>
       <c r="F19">
-        <v>1.94</v>
+        <v>1.44</v>
       </c>
       <c r="G19">
-        <v>2.04</v>
+        <v>1.61</v>
       </c>
       <c r="H19">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="I19">
-        <v>3.95</v>
+        <v>1000</v>
       </c>
       <c r="J19">
-        <v>4.1</v>
+        <v>2.62</v>
       </c>
       <c r="K19">
-        <v>4.5</v>
+        <v>8.6</v>
       </c>
       <c r="L19">
         <v>0</v>
@@ -5393,10 +5408,10 @@
         <v>0</v>
       </c>
       <c r="P19">
-        <v>1.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q19">
-        <v>1.03</v>
+        <v>1.45</v>
       </c>
       <c r="R19">
         <v>0</v>
@@ -5585,42 +5600,42 @@
         <v>0</v>
       </c>
       <c r="CB19" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B20" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C20" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D20" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="E20" t="s">
-        <v>190</v>
+        <v>193</v>
       </c>
       <c r="F20">
-        <v>1.5</v>
+        <v>1.94</v>
       </c>
       <c r="G20">
-        <v>1.6</v>
+        <v>2.04</v>
       </c>
       <c r="H20">
-        <v>5.3</v>
+        <v>3.5</v>
       </c>
       <c r="I20">
-        <v>75</v>
+        <v>3.95</v>
       </c>
       <c r="J20">
-        <v>4.7</v>
+        <v>4.1</v>
       </c>
       <c r="K20">
-        <v>6.6</v>
+        <v>4.5</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -5635,10 +5650,10 @@
         <v>0</v>
       </c>
       <c r="P20">
-        <v>2.08</v>
+        <v>1.25</v>
       </c>
       <c r="Q20">
-        <v>1.53</v>
+        <v>1.03</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -5827,7 +5842,7 @@
         <v>0</v>
       </c>
       <c r="CB20" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="21" spans="1:80">
@@ -5835,34 +5850,34 @@
         <v>97</v>
       </c>
       <c r="B21" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C21" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D21" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="E21" t="s">
-        <v>191</v>
+        <v>194</v>
       </c>
       <c r="F21">
-        <v>1.8</v>
+        <v>1.5</v>
       </c>
       <c r="G21">
-        <v>1.9</v>
+        <v>1.6</v>
       </c>
       <c r="H21">
-        <v>5</v>
+        <v>5.3</v>
       </c>
       <c r="I21">
-        <v>5.6</v>
+        <v>75</v>
       </c>
       <c r="J21">
-        <v>3.65</v>
+        <v>4.7</v>
       </c>
       <c r="K21">
-        <v>3.85</v>
+        <v>6.2</v>
       </c>
       <c r="L21">
         <v>0</v>
@@ -5877,10 +5892,10 @@
         <v>0</v>
       </c>
       <c r="P21">
-        <v>1.25</v>
+        <v>2.08</v>
       </c>
       <c r="Q21">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="R21">
         <v>0</v>
@@ -6069,7 +6084,7 @@
         <v>0</v>
       </c>
       <c r="CB21" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="22" spans="1:80">
@@ -6077,34 +6092,34 @@
         <v>98</v>
       </c>
       <c r="B22" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C22" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D22" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="E22" t="s">
-        <v>192</v>
+        <v>195</v>
       </c>
       <c r="F22">
-        <v>1.39</v>
+        <v>1.79</v>
       </c>
       <c r="G22">
-        <v>1.4</v>
+        <v>1.9</v>
       </c>
       <c r="H22">
-        <v>7.4</v>
+        <v>5</v>
       </c>
       <c r="I22">
-        <v>8.800000000000001</v>
+        <v>5.6</v>
       </c>
       <c r="J22">
-        <v>5.2</v>
+        <v>3.65</v>
       </c>
       <c r="K22">
-        <v>6.2</v>
+        <v>3.9</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -6119,10 +6134,10 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>2.7</v>
+        <v>1.25</v>
       </c>
       <c r="Q22">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -6311,7 +6326,7 @@
         <v>0</v>
       </c>
       <c r="CB22" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="23" spans="1:80">
@@ -6319,34 +6334,34 @@
         <v>99</v>
       </c>
       <c r="B23" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C23" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D23" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="E23" t="s">
-        <v>193</v>
+        <v>196</v>
       </c>
       <c r="F23">
-        <v>1.14</v>
+        <v>1.38</v>
       </c>
       <c r="G23">
-        <v>1.25</v>
+        <v>1.4</v>
       </c>
       <c r="H23">
-        <v>12</v>
+        <v>7.2</v>
       </c>
       <c r="I23">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="J23">
-        <v>6.4</v>
+        <v>5.2</v>
       </c>
       <c r="K23">
-        <v>26</v>
+        <v>6.2</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6361,10 +6376,10 @@
         <v>0</v>
       </c>
       <c r="P23">
-        <v>2.6</v>
+        <v>2.7</v>
       </c>
       <c r="Q23">
-        <v>1.32</v>
+        <v>1.46</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -6553,42 +6568,42 @@
         <v>0</v>
       </c>
       <c r="CB23" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>96</v>
+        <v>100</v>
       </c>
       <c r="B24" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C24" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D24" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="E24" t="s">
-        <v>194</v>
+        <v>197</v>
       </c>
       <c r="F24">
-        <v>1.55</v>
+        <v>1.14</v>
       </c>
       <c r="G24">
-        <v>1.69</v>
+        <v>1.25</v>
       </c>
       <c r="H24">
-        <v>4.6</v>
+        <v>12</v>
       </c>
       <c r="I24">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="J24">
-        <v>3.85</v>
+        <v>6.4</v>
       </c>
       <c r="K24">
-        <v>4.7</v>
+        <v>26</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -6603,10 +6618,10 @@
         <v>0</v>
       </c>
       <c r="P24">
-        <v>2.24</v>
+        <v>2.6</v>
       </c>
       <c r="Q24">
-        <v>1.6</v>
+        <v>1.32</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -6795,240 +6810,240 @@
         <v>0</v>
       </c>
       <c r="CB24" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="B25" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C25" t="s">
         <v>122</v>
       </c>
       <c r="D25" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="E25" t="s">
-        <v>195</v>
+        <v>198</v>
       </c>
       <c r="F25">
+        <v>1.55</v>
+      </c>
+      <c r="G25">
         <v>1.69</v>
       </c>
-      <c r="G25">
-        <v>1.87</v>
-      </c>
       <c r="H25">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="I25">
-        <v>5.7</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>3.45</v>
+        <v>3.95</v>
       </c>
       <c r="K25">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="L25">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M25">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N25">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O25">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="P25">
-        <v>2.6</v>
+        <v>2.24</v>
       </c>
       <c r="Q25">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="R25">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S25">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T25">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U25">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V25">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="W25">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="X25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP25">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ25">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR25">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS25">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT25">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU25">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV25">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW25">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX25">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY25">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ25">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA25">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB25">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC25">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD25">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE25">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF25">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG25">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI25">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK25">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM25">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO25">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ25">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS25">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU25">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW25">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX25">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY25">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ25">
         <v>0</v>
@@ -7037,7 +7052,7 @@
         <v>0</v>
       </c>
       <c r="CB25" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="26" spans="1:80">
@@ -7045,232 +7060,232 @@
         <v>101</v>
       </c>
       <c r="B26" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C26" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D26" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="E26" t="s">
-        <v>196</v>
+        <v>199</v>
       </c>
       <c r="F26">
-        <v>2.92</v>
+        <v>1.69</v>
       </c>
       <c r="G26">
-        <v>3</v>
+        <v>1.87</v>
       </c>
       <c r="H26">
-        <v>2.58</v>
+        <v>4.1</v>
       </c>
       <c r="I26">
-        <v>2.66</v>
+        <v>5.7</v>
       </c>
       <c r="J26">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="K26">
-        <v>3.6</v>
+        <v>6.2</v>
       </c>
       <c r="L26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N26">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O26">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P26">
-        <v>1.89</v>
+        <v>2.6</v>
       </c>
       <c r="Q26">
-        <v>2.04</v>
+        <v>1.44</v>
       </c>
       <c r="R26">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S26">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V26">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W26">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="X26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX26">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY26">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ26">
         <v>0</v>
@@ -7279,7 +7294,7 @@
         <v>0</v>
       </c>
       <c r="CB26" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27" spans="1:80">
@@ -7287,64 +7302,64 @@
         <v>102</v>
       </c>
       <c r="B27" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C27" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D27" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="E27" t="s">
-        <v>197</v>
+        <v>200</v>
       </c>
       <c r="F27">
-        <v>2.24</v>
+        <v>2.92</v>
       </c>
       <c r="G27">
-        <v>2.28</v>
+        <v>3.05</v>
       </c>
       <c r="H27">
-        <v>4.1</v>
+        <v>2.52</v>
       </c>
       <c r="I27">
-        <v>4.3</v>
+        <v>2.66</v>
       </c>
       <c r="J27">
-        <v>3.1</v>
+        <v>3.55</v>
       </c>
       <c r="K27">
-        <v>3.2</v>
+        <v>3.6</v>
       </c>
       <c r="L27">
         <v>0</v>
       </c>
       <c r="M27">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="N27">
-        <v>2.34</v>
+        <v>0</v>
       </c>
       <c r="O27">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="P27">
-        <v>1.44</v>
+        <v>1.91</v>
       </c>
       <c r="Q27">
-        <v>3.2</v>
+        <v>1.87</v>
       </c>
       <c r="R27">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="S27">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="T27">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U27">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V27">
         <v>0</v>
@@ -7353,175 +7368,175 @@
         <v>0</v>
       </c>
       <c r="X27">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="Y27">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="Z27">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AA27">
-        <v>150</v>
+        <v>0</v>
       </c>
       <c r="AB27">
-        <v>6.2</v>
+        <v>0</v>
       </c>
       <c r="AC27">
-        <v>7.4</v>
+        <v>0</v>
       </c>
       <c r="AD27">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AE27">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AF27">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AG27">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AH27">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AI27">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AJ27">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AK27">
-        <v>42</v>
+        <v>0</v>
       </c>
       <c r="AL27">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AM27">
-        <v>340</v>
+        <v>0</v>
       </c>
       <c r="AN27">
-        <v>50</v>
+        <v>0</v>
       </c>
       <c r="AO27">
-        <v>170</v>
+        <v>0</v>
       </c>
       <c r="AP27">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AQ27">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AR27">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AS27">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="AT27">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AU27">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AV27">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AW27">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AX27">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="AY27">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AZ27">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="BA27">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BB27">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="BC27">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BD27">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BE27">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BF27">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="BG27">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="BH27">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="BI27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ27">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA27">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB27" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="28" spans="1:80">
@@ -7529,64 +7544,64 @@
         <v>103</v>
       </c>
       <c r="B28" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C28" t="s">
         <v>123</v>
       </c>
       <c r="D28" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="E28" t="s">
-        <v>198</v>
+        <v>201</v>
       </c>
       <c r="F28">
-        <v>1.45</v>
+        <v>2.24</v>
       </c>
       <c r="G28">
-        <v>1.81</v>
+        <v>2.26</v>
       </c>
       <c r="H28">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I28">
-        <v>15.5</v>
+        <v>4.3</v>
       </c>
       <c r="J28">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="K28">
-        <v>14</v>
+        <v>3.2</v>
       </c>
       <c r="L28">
         <v>0</v>
       </c>
       <c r="M28">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="N28">
-        <v>0</v>
+        <v>2.34</v>
       </c>
       <c r="O28">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="P28">
-        <v>3</v>
+        <v>1.44</v>
       </c>
       <c r="Q28">
-        <v>1.24</v>
+        <v>3.2</v>
       </c>
       <c r="R28">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="S28">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="T28">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="U28">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="V28">
         <v>0</v>
@@ -7595,210 +7610,210 @@
         <v>0</v>
       </c>
       <c r="X28">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="Y28">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="Z28">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="AA28">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AB28">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="AC28">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AD28">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AE28">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AF28">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AG28">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="AH28">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AI28">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AJ28">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AK28">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AL28">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="AM28">
-        <v>0</v>
+        <v>340</v>
       </c>
       <c r="AN28">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="AO28">
-        <v>0</v>
+        <v>170</v>
       </c>
       <c r="AP28">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AQ28">
-        <v>0</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AR28">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="AS28">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AT28">
-        <v>0</v>
+        <v>5.7</v>
       </c>
       <c r="AU28">
-        <v>0</v>
+        <v>6.8</v>
       </c>
       <c r="AV28">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AW28">
-        <v>0</v>
+        <v>34</v>
       </c>
       <c r="AX28">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AY28">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AZ28">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="BA28">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BB28">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="BC28">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BD28">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="BE28">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="BF28">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="BG28">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BH28">
-        <v>0</v>
+        <v>2.56</v>
       </c>
       <c r="BI28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ28">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA28">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB28" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="29" spans="1:80">
       <c r="A29" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B29" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C29" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D29" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="E29" t="s">
-        <v>199</v>
+        <v>202</v>
       </c>
       <c r="F29">
-        <v>1.53</v>
+        <v>1.45</v>
       </c>
       <c r="G29">
-        <v>1.73</v>
+        <v>1.81</v>
       </c>
       <c r="H29">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="I29">
-        <v>8.199999999999999</v>
+        <v>15.5</v>
       </c>
       <c r="J29">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="K29">
-        <v>8.4</v>
+        <v>14</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -7816,7 +7831,7 @@
         <v>3</v>
       </c>
       <c r="Q29">
-        <v>1.35</v>
+        <v>1.24</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -8005,42 +8020,42 @@
         <v>0</v>
       </c>
       <c r="CB29" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="30" spans="1:80">
       <c r="A30" t="s">
-        <v>90</v>
+        <v>104</v>
       </c>
       <c r="B30" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C30" t="s">
         <v>124</v>
       </c>
       <c r="D30" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="E30" t="s">
-        <v>200</v>
+        <v>203</v>
       </c>
       <c r="F30">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="G30">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="H30">
-        <v>6.2</v>
+        <v>4.4</v>
       </c>
       <c r="I30">
-        <v>36</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J30">
-        <v>3.6</v>
+        <v>4.5</v>
       </c>
       <c r="K30">
-        <v>7</v>
+        <v>8.4</v>
       </c>
       <c r="L30">
         <v>0</v>
@@ -8055,10 +8070,10 @@
         <v>0</v>
       </c>
       <c r="P30">
-        <v>1.54</v>
+        <v>3</v>
       </c>
       <c r="Q30">
-        <v>2.12</v>
+        <v>1.35</v>
       </c>
       <c r="R30">
         <v>0</v>
@@ -8247,249 +8262,249 @@
         <v>0</v>
       </c>
       <c r="CB30" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="31" spans="1:80">
       <c r="A31" t="s">
-        <v>104</v>
+        <v>91</v>
       </c>
       <c r="B31" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C31" t="s">
         <v>125</v>
       </c>
       <c r="D31" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E31" t="s">
-        <v>201</v>
+        <v>204</v>
       </c>
       <c r="F31">
-        <v>1.86</v>
+        <v>1.44</v>
       </c>
       <c r="G31">
-        <v>2.02</v>
+        <v>1.77</v>
       </c>
       <c r="H31">
-        <v>4.6</v>
+        <v>6.2</v>
       </c>
       <c r="I31">
-        <v>5.4</v>
+        <v>36</v>
       </c>
       <c r="J31">
-        <v>3.4</v>
+        <v>3.6</v>
       </c>
       <c r="K31">
-        <v>3.8</v>
+        <v>7</v>
       </c>
       <c r="L31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M31">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="N31">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="O31">
-        <v>1.42</v>
+        <v>0</v>
       </c>
       <c r="P31">
-        <v>1.67</v>
+        <v>1.54</v>
       </c>
       <c r="Q31">
-        <v>2.24</v>
+        <v>2.12</v>
       </c>
       <c r="R31">
-        <v>1.24</v>
+        <v>0</v>
       </c>
       <c r="S31">
-        <v>4.3</v>
+        <v>0</v>
       </c>
       <c r="T31">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="U31">
-        <v>1.83</v>
+        <v>0</v>
       </c>
       <c r="V31">
-        <v>1.23</v>
+        <v>0</v>
       </c>
       <c r="W31">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="X31">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="Y31">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="Z31">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AA31">
-        <v>160</v>
+        <v>0</v>
       </c>
       <c r="AB31">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AC31">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AD31">
-        <v>25</v>
+        <v>0</v>
       </c>
       <c r="AE31">
-        <v>95</v>
+        <v>0</v>
       </c>
       <c r="AF31">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AG31">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AH31">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AI31">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AJ31">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AK31">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AL31">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AM31">
-        <v>190</v>
+        <v>0</v>
       </c>
       <c r="AN31">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="AO31">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AP31">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AQ31">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AR31">
-        <v>26</v>
+        <v>0</v>
       </c>
       <c r="AS31">
-        <v>90</v>
+        <v>0</v>
       </c>
       <c r="AT31">
-        <v>5.5</v>
+        <v>0</v>
       </c>
       <c r="AU31">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="AV31">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AW31">
-        <v>55</v>
+        <v>0</v>
       </c>
       <c r="AX31">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AY31">
-        <v>7.8</v>
+        <v>0</v>
       </c>
       <c r="AZ31">
-        <v>16</v>
+        <v>0</v>
       </c>
       <c r="BA31">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="BB31">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BC31">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BD31">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="BE31">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="BF31">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="BG31">
-        <v>80</v>
+        <v>0</v>
       </c>
       <c r="BH31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ31">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA31">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB31" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="32" spans="1:80">
@@ -8497,264 +8512,264 @@
         <v>105</v>
       </c>
       <c r="B32" t="s">
+        <v>111</v>
+      </c>
+      <c r="C32" t="s">
+        <v>126</v>
+      </c>
+      <c r="D32" t="s">
+        <v>162</v>
+      </c>
+      <c r="E32" t="s">
+        <v>205</v>
+      </c>
+      <c r="F32">
+        <v>1.86</v>
+      </c>
+      <c r="G32">
+        <v>2.02</v>
+      </c>
+      <c r="H32">
+        <v>4.6</v>
+      </c>
+      <c r="I32">
+        <v>5.4</v>
+      </c>
+      <c r="J32">
+        <v>3.4</v>
+      </c>
+      <c r="K32">
+        <v>3.7</v>
+      </c>
+      <c r="L32">
+        <v>1.01</v>
+      </c>
+      <c r="M32">
+        <v>1.06</v>
+      </c>
+      <c r="N32">
+        <v>2.8</v>
+      </c>
+      <c r="O32">
+        <v>1.41</v>
+      </c>
+      <c r="P32">
+        <v>1.64</v>
+      </c>
+      <c r="Q32">
+        <v>2.22</v>
+      </c>
+      <c r="R32">
+        <v>1.14</v>
+      </c>
+      <c r="S32">
+        <v>2.58</v>
+      </c>
+      <c r="T32">
+        <v>2</v>
+      </c>
+      <c r="U32">
+        <v>1.83</v>
+      </c>
+      <c r="V32">
+        <v>1.23</v>
+      </c>
+      <c r="W32">
+        <v>1.98</v>
+      </c>
+      <c r="X32">
+        <v>13</v>
+      </c>
+      <c r="Y32">
+        <v>17.5</v>
+      </c>
+      <c r="Z32">
+        <v>46</v>
+      </c>
+      <c r="AA32">
+        <v>160</v>
+      </c>
+      <c r="AB32">
+        <v>8.6</v>
+      </c>
+      <c r="AC32">
+        <v>9.6</v>
+      </c>
+      <c r="AD32">
+        <v>25</v>
+      </c>
+      <c r="AE32">
+        <v>95</v>
+      </c>
+      <c r="AF32">
+        <v>13</v>
+      </c>
+      <c r="AG32">
+        <v>13</v>
+      </c>
+      <c r="AH32">
+        <v>27</v>
+      </c>
+      <c r="AI32">
         <v>110</v>
       </c>
-      <c r="C32" t="s">
-        <v>125</v>
-      </c>
-      <c r="D32" t="s">
-        <v>161</v>
-      </c>
-      <c r="E32" t="s">
-        <v>202</v>
-      </c>
-      <c r="F32">
-        <v>1.44</v>
-      </c>
-      <c r="G32">
-        <v>1.48</v>
-      </c>
-      <c r="H32">
+      <c r="AJ32">
+        <v>28</v>
+      </c>
+      <c r="AK32">
+        <v>29</v>
+      </c>
+      <c r="AL32">
+        <v>60</v>
+      </c>
+      <c r="AM32">
+        <v>190</v>
+      </c>
+      <c r="AN32">
+        <v>22</v>
+      </c>
+      <c r="AO32">
+        <v>140</v>
+      </c>
+      <c r="AP32">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AQ32">
+        <v>10.5</v>
+      </c>
+      <c r="AR32">
+        <v>26</v>
+      </c>
+      <c r="AS32">
+        <v>90</v>
+      </c>
+      <c r="AT32">
+        <v>5.5</v>
+      </c>
+      <c r="AU32">
+        <v>6</v>
+      </c>
+      <c r="AV32">
+        <v>14.5</v>
+      </c>
+      <c r="AW32">
+        <v>55</v>
+      </c>
+      <c r="AX32">
         <v>8</v>
       </c>
-      <c r="I32">
-        <v>10.5</v>
-      </c>
-      <c r="J32">
-        <v>4.8</v>
-      </c>
-      <c r="K32">
-        <v>5.1</v>
-      </c>
-      <c r="L32">
-        <v>0</v>
-      </c>
-      <c r="M32">
-        <v>0</v>
-      </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
-      <c r="O32">
-        <v>0</v>
-      </c>
-      <c r="P32">
-        <v>1.25</v>
-      </c>
-      <c r="Q32">
-        <v>1.01</v>
-      </c>
-      <c r="R32">
-        <v>0</v>
-      </c>
-      <c r="S32">
-        <v>0</v>
-      </c>
-      <c r="T32">
-        <v>0</v>
-      </c>
-      <c r="U32">
-        <v>0</v>
-      </c>
-      <c r="V32">
-        <v>0</v>
-      </c>
-      <c r="W32">
-        <v>0</v>
-      </c>
-      <c r="X32">
-        <v>0</v>
-      </c>
-      <c r="Y32">
-        <v>0</v>
-      </c>
-      <c r="Z32">
-        <v>0</v>
-      </c>
-      <c r="AA32">
-        <v>0</v>
-      </c>
-      <c r="AB32">
-        <v>0</v>
-      </c>
-      <c r="AC32">
-        <v>0</v>
-      </c>
-      <c r="AD32">
-        <v>0</v>
-      </c>
-      <c r="AE32">
-        <v>0</v>
-      </c>
-      <c r="AF32">
-        <v>0</v>
-      </c>
-      <c r="AG32">
-        <v>0</v>
-      </c>
-      <c r="AH32">
-        <v>0</v>
-      </c>
-      <c r="AI32">
-        <v>0</v>
-      </c>
-      <c r="AJ32">
-        <v>0</v>
-      </c>
-      <c r="AK32">
-        <v>0</v>
-      </c>
-      <c r="AL32">
-        <v>0</v>
-      </c>
-      <c r="AM32">
-        <v>0</v>
-      </c>
-      <c r="AN32">
-        <v>0</v>
-      </c>
-      <c r="AO32">
-        <v>0</v>
-      </c>
-      <c r="AP32">
-        <v>0</v>
-      </c>
-      <c r="AQ32">
-        <v>0</v>
-      </c>
-      <c r="AR32">
-        <v>0</v>
-      </c>
-      <c r="AS32">
-        <v>0</v>
-      </c>
-      <c r="AT32">
-        <v>0</v>
-      </c>
-      <c r="AU32">
-        <v>0</v>
-      </c>
-      <c r="AV32">
-        <v>0</v>
-      </c>
-      <c r="AW32">
-        <v>0</v>
-      </c>
-      <c r="AX32">
-        <v>0</v>
-      </c>
       <c r="AY32">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AZ32">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="BA32">
-        <v>0</v>
+        <v>60</v>
       </c>
       <c r="BB32">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="BC32">
-        <v>0</v>
+        <v>17</v>
       </c>
       <c r="BD32">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="BE32">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="BF32">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="BG32">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="BH32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ32">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA32">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB32" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="33" spans="1:80">
       <c r="A33" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B33" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C33" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="D33" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="E33" t="s">
-        <v>203</v>
+        <v>206</v>
       </c>
       <c r="F33">
         <v>3.55</v>
       </c>
       <c r="G33">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="H33">
         <v>2.12</v>
@@ -8763,7 +8778,7 @@
         <v>2.22</v>
       </c>
       <c r="J33">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K33">
         <v>4.1</v>
@@ -8973,7 +8988,7 @@
         <v>0</v>
       </c>
       <c r="CB33" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="34" spans="1:80">
@@ -8981,35 +8996,35 @@
         <v>106</v>
       </c>
       <c r="B34" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C34" t="s">
         <v>126</v>
       </c>
       <c r="D34" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="E34" t="s">
-        <v>204</v>
+        <v>207</v>
       </c>
       <c r="F34">
-        <v>4.5</v>
+        <v>1.45</v>
       </c>
       <c r="G34">
+        <v>1.49</v>
+      </c>
+      <c r="H34">
+        <v>8</v>
+      </c>
+      <c r="I34">
+        <v>10</v>
+      </c>
+      <c r="J34">
+        <v>4.8</v>
+      </c>
+      <c r="K34">
         <v>5.1</v>
       </c>
-      <c r="H34">
-        <v>1.86</v>
-      </c>
-      <c r="I34">
-        <v>1.93</v>
-      </c>
-      <c r="J34">
-        <v>3.65</v>
-      </c>
-      <c r="K34">
-        <v>3.95</v>
-      </c>
       <c r="L34">
         <v>0</v>
       </c>
@@ -9023,10 +9038,10 @@
         <v>0</v>
       </c>
       <c r="P34">
-        <v>1.84</v>
+        <v>1.25</v>
       </c>
       <c r="Q34">
-        <v>1.01</v>
+        <v>1.8</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -9215,72 +9230,72 @@
         <v>0</v>
       </c>
       <c r="CB34" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="35" spans="1:80">
       <c r="A35" t="s">
-        <v>93</v>
+        <v>107</v>
       </c>
       <c r="B35" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C35" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="D35" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="E35" t="s">
-        <v>205</v>
+        <v>208</v>
       </c>
       <c r="F35">
-        <v>1.97</v>
+        <v>4.5</v>
       </c>
       <c r="G35">
-        <v>1.99</v>
+        <v>5.1</v>
       </c>
       <c r="H35">
-        <v>4.2</v>
+        <v>1.86</v>
       </c>
       <c r="I35">
-        <v>4.5</v>
+        <v>1.93</v>
       </c>
       <c r="J35">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K35">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L35">
         <v>0</v>
       </c>
       <c r="M35">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="N35">
-        <v>3.8</v>
+        <v>0</v>
       </c>
       <c r="O35">
-        <v>1.33</v>
+        <v>0</v>
       </c>
       <c r="P35">
-        <v>1.95</v>
+        <v>1.84</v>
       </c>
       <c r="Q35">
-        <v>2.02</v>
+        <v>1.01</v>
       </c>
       <c r="R35">
-        <v>1.37</v>
+        <v>0</v>
       </c>
       <c r="S35">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="T35">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="U35">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="V35">
         <v>0</v>
@@ -9289,354 +9304,354 @@
         <v>0</v>
       </c>
       <c r="X35">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="Y35">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="Z35">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AA35">
-        <v>120</v>
+        <v>0</v>
       </c>
       <c r="AB35">
-        <v>9.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AC35">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AD35">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="AE35">
-        <v>60</v>
+        <v>0</v>
       </c>
       <c r="AF35">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AG35">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AH35">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AI35">
-        <v>65</v>
+        <v>0</v>
       </c>
       <c r="AJ35">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AK35">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AL35">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AM35">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="AN35">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="AO35">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="AP35">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AQ35">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AR35">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="AS35">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AT35">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="AU35">
-        <v>7.6</v>
+        <v>0</v>
       </c>
       <c r="AV35">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AW35">
-        <v>28</v>
+        <v>0</v>
       </c>
       <c r="AX35">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AY35">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AZ35">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BA35">
-        <v>30</v>
+        <v>0</v>
       </c>
       <c r="BB35">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="BC35">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BD35">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BE35">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="BF35">
-        <v>12.5</v>
+        <v>0</v>
       </c>
       <c r="BG35">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="BH35">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI35">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ35">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK35">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL35">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM35">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN35">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO35">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP35">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ35">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR35">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS35">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT35">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU35">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV35">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW35">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX35">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY35">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ35">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA35">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB35" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="36" spans="1:80">
       <c r="A36" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="B36" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C36" t="s">
         <v>127</v>
       </c>
       <c r="D36" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="E36" t="s">
-        <v>206</v>
+        <v>209</v>
       </c>
       <c r="F36">
-        <v>5.3</v>
+        <v>1.98</v>
       </c>
       <c r="G36">
-        <v>9.800000000000001</v>
+        <v>2.02</v>
       </c>
       <c r="H36">
-        <v>1.52</v>
+        <v>4.2</v>
       </c>
       <c r="I36">
-        <v>1.91</v>
+        <v>4.4</v>
       </c>
       <c r="J36">
-        <v>3.25</v>
+        <v>3.75</v>
       </c>
       <c r="K36">
-        <v>6.4</v>
+        <v>3.85</v>
       </c>
       <c r="L36">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M36">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N36">
-        <v>2.66</v>
+        <v>3.8</v>
       </c>
       <c r="O36">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="P36">
-        <v>1.74</v>
+        <v>1.95</v>
       </c>
       <c r="Q36">
-        <v>1.86</v>
+        <v>2.02</v>
       </c>
       <c r="R36">
-        <v>1.27</v>
+        <v>1.37</v>
       </c>
       <c r="S36">
-        <v>2.92</v>
+        <v>3.5</v>
       </c>
       <c r="T36">
-        <v>1.01</v>
+        <v>1.85</v>
       </c>
       <c r="U36">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="V36">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="W36">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X36">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Y36">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Z36">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA36">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AB36">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC36">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD36">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE36">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AF36">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG36">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AH36">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI36">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ36">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK36">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AL36">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM36">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN36">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AO36">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AP36">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AQ36">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AR36">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AS36">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AT36">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AU36">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AV36">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AW36">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="AX36">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AY36">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ36">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BA36">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BB36">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BC36">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BD36">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BE36">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BF36">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BG36">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BH36">
         <v>1000</v>
@@ -9699,192 +9714,192 @@
         <v>1.01</v>
       </c>
       <c r="CB36" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="37" spans="1:80">
       <c r="A37" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="B37" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C37" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D37" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="E37" t="s">
-        <v>207</v>
+        <v>210</v>
       </c>
       <c r="F37">
-        <v>7</v>
+        <v>5.3</v>
       </c>
       <c r="G37">
-        <v>7.2</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H37">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="I37">
-        <v>1.58</v>
+        <v>1.91</v>
       </c>
       <c r="J37">
-        <v>4.4</v>
+        <v>3.25</v>
       </c>
       <c r="K37">
-        <v>4.6</v>
+        <v>6.4</v>
       </c>
       <c r="L37">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M37">
         <v>1.06</v>
       </c>
       <c r="N37">
-        <v>4.2</v>
+        <v>3.55</v>
       </c>
       <c r="O37">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P37">
-        <v>2.08</v>
+        <v>1.74</v>
       </c>
       <c r="Q37">
-        <v>1.89</v>
+        <v>1.86</v>
       </c>
       <c r="R37">
-        <v>1.42</v>
+        <v>1.27</v>
       </c>
       <c r="S37">
-        <v>3.3</v>
+        <v>2.92</v>
       </c>
       <c r="T37">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="U37">
-        <v>1.95</v>
+        <v>1.01</v>
       </c>
       <c r="V37">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="W37">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X37">
-        <v>17</v>
+        <v>1000</v>
       </c>
       <c r="Y37">
-        <v>8.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="Z37">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="AA37">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AB37">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AC37">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD37">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AE37">
-        <v>16.5</v>
+        <v>1000</v>
       </c>
       <c r="AF37">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AG37">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AH37">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI37">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AJ37">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AK37">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AL37">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AM37">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AN37">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AO37">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AP37">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ37">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AR37">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AS37">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT37">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="AU37">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AV37">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AW37">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="AX37">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="AY37">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AZ37">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BA37">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BB37">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BC37">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BD37">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="BE37">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BF37">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BG37">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="BH37">
         <v>1000</v>
       </c>
       <c r="BI37">
-        <v>3.05</v>
+        <v>1.01</v>
       </c>
       <c r="BJ37">
         <v>1000</v>
@@ -9941,7 +9956,7 @@
         <v>1.01</v>
       </c>
       <c r="CB37" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="38" spans="1:80">
@@ -9949,64 +9964,64 @@
         <v>108</v>
       </c>
       <c r="B38" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C38" t="s">
         <v>128</v>
       </c>
       <c r="D38" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="E38" t="s">
-        <v>208</v>
+        <v>211</v>
       </c>
       <c r="F38">
-        <v>1.99</v>
+        <v>6.8</v>
       </c>
       <c r="G38">
-        <v>2.12</v>
+        <v>7</v>
       </c>
       <c r="H38">
-        <v>3.15</v>
+        <v>1.58</v>
       </c>
       <c r="I38">
-        <v>3.45</v>
+        <v>1.59</v>
       </c>
       <c r="J38">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="K38">
-        <v>5.6</v>
+        <v>4.5</v>
       </c>
       <c r="L38">
         <v>0</v>
       </c>
       <c r="M38">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="N38">
-        <v>0</v>
+        <v>4.2</v>
       </c>
       <c r="O38">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P38">
-        <v>3.85</v>
+        <v>2.1</v>
       </c>
       <c r="Q38">
-        <v>1.26</v>
+        <v>1.89</v>
       </c>
       <c r="R38">
-        <v>0</v>
+        <v>1.42</v>
       </c>
       <c r="S38">
-        <v>0</v>
+        <v>3.3</v>
       </c>
       <c r="T38">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="U38">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V38">
         <v>0</v>
@@ -10015,175 +10030,175 @@
         <v>0</v>
       </c>
       <c r="X38">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y38">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z38">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AA38">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AB38">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC38">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD38">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE38">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AF38">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG38">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AH38">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI38">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ38">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AK38">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AL38">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM38">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN38">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AO38">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AP38">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AQ38">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AR38">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AS38">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AT38">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AU38">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AV38">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW38">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AX38">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="AY38">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AZ38">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BA38">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BB38">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BC38">
-        <v>1.01</v>
+        <v>55</v>
       </c>
       <c r="BD38">
-        <v>1.01</v>
+        <v>60</v>
       </c>
       <c r="BE38">
-        <v>1.01</v>
+        <v>80</v>
       </c>
       <c r="BF38">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BG38">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BH38">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ38">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL38">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN38">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP38">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR38">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT38">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV38">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX38">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ38">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB38" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="39" spans="1:80">
@@ -10191,34 +10206,34 @@
         <v>109</v>
       </c>
       <c r="B39" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C39" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D39" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="E39" t="s">
-        <v>209</v>
+        <v>212</v>
       </c>
       <c r="F39">
-        <v>1.83</v>
+        <v>1.99</v>
       </c>
       <c r="G39">
-        <v>1.88</v>
+        <v>2.12</v>
       </c>
       <c r="H39">
-        <v>5</v>
+        <v>3.15</v>
       </c>
       <c r="I39">
-        <v>5.4</v>
+        <v>3.4</v>
       </c>
       <c r="J39">
-        <v>3.6</v>
+        <v>4.6</v>
       </c>
       <c r="K39">
-        <v>3.95</v>
+        <v>5.6</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -10233,10 +10248,10 @@
         <v>0</v>
       </c>
       <c r="P39">
-        <v>1.25</v>
+        <v>3.85</v>
       </c>
       <c r="Q39">
-        <v>1.94</v>
+        <v>1.26</v>
       </c>
       <c r="R39">
         <v>0</v>
@@ -10245,10 +10260,10 @@
         <v>0</v>
       </c>
       <c r="T39">
-        <v>1.73</v>
+        <v>1.01</v>
       </c>
       <c r="U39">
-        <v>1.89</v>
+        <v>1.01</v>
       </c>
       <c r="V39">
         <v>0</v>
@@ -10257,112 +10272,112 @@
         <v>0</v>
       </c>
       <c r="X39">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="Y39">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="Z39">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AA39">
-        <v>150</v>
+        <v>1000</v>
       </c>
       <c r="AB39">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC39">
-        <v>9.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AD39">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AE39">
-        <v>85</v>
+        <v>1000</v>
       </c>
       <c r="AF39">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="AG39">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AH39">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AI39">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AJ39">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK39">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AL39">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AM39">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AN39">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="AO39">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AP39">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="AQ39">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR39">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="AS39">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="AT39">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU39">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV39">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AW39">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="AX39">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AY39">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ39">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA39">
-        <v>5</v>
+        <v>1.01</v>
       </c>
       <c r="BB39">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC39">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BD39">
-        <v>4.7</v>
+        <v>1.01</v>
       </c>
       <c r="BE39">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BF39">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG39">
-        <v>5.1</v>
+        <v>1.01</v>
       </c>
       <c r="BH39">
         <v>0</v>
@@ -10425,42 +10440,42 @@
         <v>0</v>
       </c>
       <c r="CB39" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="40" spans="1:80">
       <c r="A40" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B40" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C40" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D40" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="E40" t="s">
-        <v>210</v>
+        <v>213</v>
       </c>
       <c r="F40">
-        <v>1.14</v>
+        <v>1.83</v>
       </c>
       <c r="G40">
-        <v>1.21</v>
+        <v>1.89</v>
       </c>
       <c r="H40">
-        <v>14</v>
+        <v>5</v>
       </c>
       <c r="I40">
-        <v>1000</v>
+        <v>5.4</v>
       </c>
       <c r="J40">
-        <v>5.7</v>
+        <v>3.6</v>
       </c>
       <c r="K40">
-        <v>19.5</v>
+        <v>3.95</v>
       </c>
       <c r="L40">
         <v>0</v>
@@ -10478,7 +10493,7 @@
         <v>1.25</v>
       </c>
       <c r="Q40">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="R40">
         <v>0</v>
@@ -10487,10 +10502,10 @@
         <v>0</v>
       </c>
       <c r="T40">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="U40">
-        <v>0</v>
+        <v>1.89</v>
       </c>
       <c r="V40">
         <v>0</v>
@@ -10499,112 +10514,112 @@
         <v>0</v>
       </c>
       <c r="X40">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="Y40">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="Z40">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="AA40">
-        <v>0</v>
+        <v>150</v>
       </c>
       <c r="AB40">
-        <v>0</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AC40">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AD40">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AE40">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AF40">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AG40">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AH40">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI40">
-        <v>0</v>
+        <v>90</v>
       </c>
       <c r="AJ40">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AK40">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AL40">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AM40">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN40">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AO40">
-        <v>0</v>
+        <v>110</v>
       </c>
       <c r="AP40">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ40">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AR40">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="AS40">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="AT40">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AU40">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AV40">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AW40">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="AX40">
-        <v>0</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AY40">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ40">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BA40">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BB40">
-        <v>0</v>
+        <v>17.5</v>
       </c>
       <c r="BC40">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="BD40">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="BE40">
-        <v>0</v>
+        <v>5.2</v>
       </c>
       <c r="BF40">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="BG40">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="BH40">
         <v>0</v>
@@ -10667,72 +10682,72 @@
         <v>0</v>
       </c>
       <c r="CB40" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="41" spans="1:80">
       <c r="A41" t="s">
-        <v>102</v>
+        <v>110</v>
       </c>
       <c r="B41" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C41" t="s">
         <v>129</v>
       </c>
       <c r="D41" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E41" t="s">
-        <v>211</v>
+        <v>214</v>
       </c>
       <c r="F41">
-        <v>1.18</v>
+        <v>1.14</v>
       </c>
       <c r="G41">
-        <v>1.19</v>
+        <v>1.21</v>
       </c>
       <c r="H41">
-        <v>18.5</v>
+        <v>14</v>
       </c>
       <c r="I41">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="J41">
-        <v>9.4</v>
+        <v>5.7</v>
       </c>
       <c r="K41">
-        <v>9.800000000000001</v>
+        <v>19.5</v>
       </c>
       <c r="L41">
         <v>0</v>
       </c>
       <c r="M41">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N41">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="O41">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="P41">
-        <v>3.45</v>
+        <v>1.25</v>
       </c>
       <c r="Q41">
-        <v>1.38</v>
+        <v>1.01</v>
       </c>
       <c r="R41">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S41">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="T41">
-        <v>2.06</v>
+        <v>0</v>
       </c>
       <c r="U41">
-        <v>1.86</v>
+        <v>0</v>
       </c>
       <c r="V41">
         <v>0</v>
@@ -10741,417 +10756,901 @@
         <v>0</v>
       </c>
       <c r="X41">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="Y41">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="Z41">
-        <v>230</v>
+        <v>0</v>
       </c>
       <c r="AA41">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB41">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AC41">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="AD41">
-        <v>70</v>
+        <v>0</v>
       </c>
       <c r="AE41">
-        <v>330</v>
+        <v>0</v>
       </c>
       <c r="AF41">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AG41">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="AH41">
-        <v>40</v>
+        <v>0</v>
       </c>
       <c r="AI41">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ41">
-        <v>9.6</v>
+        <v>0</v>
       </c>
       <c r="AK41">
-        <v>13.5</v>
+        <v>0</v>
       </c>
       <c r="AL41">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AM41">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c r="AN41">
-        <v>2.94</v>
+        <v>0</v>
       </c>
       <c r="AO41">
-        <v>350</v>
+        <v>0</v>
       </c>
       <c r="AP41">
-        <v>34</v>
+        <v>0</v>
       </c>
       <c r="AQ41">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AR41">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AS41">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AT41">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AU41">
-        <v>20</v>
+        <v>0</v>
       </c>
       <c r="AV41">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AW41">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AX41">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AY41">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AZ41">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="BA41">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="BB41">
-        <v>8.4</v>
+        <v>0</v>
       </c>
       <c r="BC41">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="BD41">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BE41">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="BF41">
-        <v>2.76</v>
+        <v>0</v>
       </c>
       <c r="BG41">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="BH41">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI41">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ41">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK41">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL41">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM41">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN41">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO41">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP41">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ41">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR41">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS41">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT41">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU41">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV41">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW41">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX41">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY41">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ41">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA41">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB41" t="s">
-        <v>213</v>
+        <v>218</v>
       </c>
     </row>
     <row r="42" spans="1:80">
       <c r="A42" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="B42" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C42" t="s">
         <v>130</v>
       </c>
       <c r="D42" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="E42" t="s">
-        <v>212</v>
+        <v>215</v>
       </c>
       <c r="F42">
+        <v>4.1</v>
+      </c>
+      <c r="G42">
+        <v>5.4</v>
+      </c>
+      <c r="H42">
+        <v>1.28</v>
+      </c>
+      <c r="I42">
+        <v>1.96</v>
+      </c>
+      <c r="J42">
+        <v>3.3</v>
+      </c>
+      <c r="K42">
+        <v>4.6</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>0</v>
+      </c>
+      <c r="N42">
+        <v>0</v>
+      </c>
+      <c r="O42">
+        <v>0</v>
+      </c>
+      <c r="P42">
+        <v>2.08</v>
+      </c>
+      <c r="Q42">
+        <v>1.5</v>
+      </c>
+      <c r="R42">
+        <v>0</v>
+      </c>
+      <c r="S42">
+        <v>0</v>
+      </c>
+      <c r="T42">
+        <v>1.64</v>
+      </c>
+      <c r="U42">
+        <v>1.01</v>
+      </c>
+      <c r="V42">
+        <v>0</v>
+      </c>
+      <c r="W42">
+        <v>0</v>
+      </c>
+      <c r="X42">
+        <v>1000</v>
+      </c>
+      <c r="Y42">
+        <v>1000</v>
+      </c>
+      <c r="Z42">
+        <v>1000</v>
+      </c>
+      <c r="AA42">
+        <v>1000</v>
+      </c>
+      <c r="AB42">
+        <v>1000</v>
+      </c>
+      <c r="AC42">
+        <v>1000</v>
+      </c>
+      <c r="AD42">
+        <v>1000</v>
+      </c>
+      <c r="AE42">
+        <v>1000</v>
+      </c>
+      <c r="AF42">
+        <v>1000</v>
+      </c>
+      <c r="AG42">
+        <v>1000</v>
+      </c>
+      <c r="AH42">
+        <v>1000</v>
+      </c>
+      <c r="AI42">
+        <v>1000</v>
+      </c>
+      <c r="AJ42">
+        <v>1000</v>
+      </c>
+      <c r="AK42">
+        <v>1000</v>
+      </c>
+      <c r="AL42">
+        <v>1000</v>
+      </c>
+      <c r="AM42">
+        <v>1000</v>
+      </c>
+      <c r="AN42">
+        <v>1000</v>
+      </c>
+      <c r="AO42">
+        <v>1000</v>
+      </c>
+      <c r="AP42">
+        <v>15</v>
+      </c>
+      <c r="AQ42">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR42">
+        <v>9.4</v>
+      </c>
+      <c r="AS42">
+        <v>17</v>
+      </c>
+      <c r="AT42">
+        <v>14</v>
+      </c>
+      <c r="AU42">
+        <v>7.4</v>
+      </c>
+      <c r="AV42">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW42">
+        <v>15</v>
+      </c>
+      <c r="AX42">
+        <v>25</v>
+      </c>
+      <c r="AY42">
+        <v>13.5</v>
+      </c>
+      <c r="AZ42">
+        <v>13.5</v>
+      </c>
+      <c r="BA42">
+        <v>24</v>
+      </c>
+      <c r="BB42">
+        <v>60</v>
+      </c>
+      <c r="BC42">
+        <v>38</v>
+      </c>
+      <c r="BD42">
+        <v>38</v>
+      </c>
+      <c r="BE42">
+        <v>48</v>
+      </c>
+      <c r="BF42">
+        <v>1.01</v>
+      </c>
+      <c r="BG42">
+        <v>1.01</v>
+      </c>
+      <c r="BH42">
+        <v>0</v>
+      </c>
+      <c r="BI42">
+        <v>0</v>
+      </c>
+      <c r="BJ42">
+        <v>0</v>
+      </c>
+      <c r="BK42">
+        <v>0</v>
+      </c>
+      <c r="BL42">
+        <v>0</v>
+      </c>
+      <c r="BM42">
+        <v>0</v>
+      </c>
+      <c r="BN42">
+        <v>0</v>
+      </c>
+      <c r="BO42">
+        <v>0</v>
+      </c>
+      <c r="BP42">
+        <v>0</v>
+      </c>
+      <c r="BQ42">
+        <v>0</v>
+      </c>
+      <c r="BR42">
+        <v>0</v>
+      </c>
+      <c r="BS42">
+        <v>0</v>
+      </c>
+      <c r="BT42">
+        <v>0</v>
+      </c>
+      <c r="BU42">
+        <v>0</v>
+      </c>
+      <c r="BV42">
+        <v>0</v>
+      </c>
+      <c r="BW42">
+        <v>0</v>
+      </c>
+      <c r="BX42">
+        <v>0</v>
+      </c>
+      <c r="BY42">
+        <v>0</v>
+      </c>
+      <c r="BZ42">
+        <v>0</v>
+      </c>
+      <c r="CA42">
+        <v>0</v>
+      </c>
+      <c r="CB42" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="43" spans="1:80">
+      <c r="A43" t="s">
+        <v>103</v>
+      </c>
+      <c r="B43" t="s">
+        <v>111</v>
+      </c>
+      <c r="C43" t="s">
+        <v>130</v>
+      </c>
+      <c r="D43" t="s">
+        <v>173</v>
+      </c>
+      <c r="E43" t="s">
+        <v>216</v>
+      </c>
+      <c r="F43">
+        <v>1.17</v>
+      </c>
+      <c r="G43">
+        <v>1.18</v>
+      </c>
+      <c r="H43">
+        <v>19.5</v>
+      </c>
+      <c r="I43">
+        <v>21</v>
+      </c>
+      <c r="J43">
+        <v>9.4</v>
+      </c>
+      <c r="K43">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="L43">
+        <v>0</v>
+      </c>
+      <c r="M43">
+        <v>1.02</v>
+      </c>
+      <c r="N43">
+        <v>8</v>
+      </c>
+      <c r="O43">
+        <v>1.13</v>
+      </c>
+      <c r="P43">
+        <v>3.45</v>
+      </c>
+      <c r="Q43">
+        <v>1.38</v>
+      </c>
+      <c r="R43">
+        <v>2</v>
+      </c>
+      <c r="S43">
+        <v>1.94</v>
+      </c>
+      <c r="T43">
+        <v>2.06</v>
+      </c>
+      <c r="U43">
+        <v>1.86</v>
+      </c>
+      <c r="V43">
+        <v>0</v>
+      </c>
+      <c r="W43">
+        <v>0</v>
+      </c>
+      <c r="X43">
+        <v>42</v>
+      </c>
+      <c r="Y43">
+        <v>75</v>
+      </c>
+      <c r="Z43">
+        <v>230</v>
+      </c>
+      <c r="AA43">
+        <v>1000</v>
+      </c>
+      <c r="AB43">
+        <v>13.5</v>
+      </c>
+      <c r="AC43">
+        <v>23</v>
+      </c>
+      <c r="AD43">
+        <v>70</v>
+      </c>
+      <c r="AE43">
+        <v>330</v>
+      </c>
+      <c r="AF43">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AG43">
+        <v>13</v>
+      </c>
+      <c r="AH43">
+        <v>40</v>
+      </c>
+      <c r="AI43">
+        <v>1000</v>
+      </c>
+      <c r="AJ43">
+        <v>9.6</v>
+      </c>
+      <c r="AK43">
+        <v>13.5</v>
+      </c>
+      <c r="AL43">
+        <v>38</v>
+      </c>
+      <c r="AM43">
+        <v>180</v>
+      </c>
+      <c r="AN43">
+        <v>2.96</v>
+      </c>
+      <c r="AO43">
+        <v>350</v>
+      </c>
+      <c r="AP43">
+        <v>25</v>
+      </c>
+      <c r="AQ43">
+        <v>34</v>
+      </c>
+      <c r="AR43">
+        <v>48</v>
+      </c>
+      <c r="AS43">
+        <v>18</v>
+      </c>
+      <c r="AT43">
+        <v>11.5</v>
+      </c>
+      <c r="AU43">
+        <v>20</v>
+      </c>
+      <c r="AV43">
+        <v>34</v>
+      </c>
+      <c r="AW43">
+        <v>50</v>
+      </c>
+      <c r="AX43">
+        <v>8.6</v>
+      </c>
+      <c r="AY43">
+        <v>11.5</v>
+      </c>
+      <c r="AZ43">
+        <v>24</v>
+      </c>
+      <c r="BA43">
+        <v>48</v>
+      </c>
+      <c r="BB43">
+        <v>8.4</v>
+      </c>
+      <c r="BC43">
+        <v>11.5</v>
+      </c>
+      <c r="BD43">
+        <v>23</v>
+      </c>
+      <c r="BE43">
+        <v>46</v>
+      </c>
+      <c r="BF43">
+        <v>2.72</v>
+      </c>
+      <c r="BG43">
+        <v>17</v>
+      </c>
+      <c r="BH43">
+        <v>1000</v>
+      </c>
+      <c r="BI43">
+        <v>1.01</v>
+      </c>
+      <c r="BJ43">
+        <v>1000</v>
+      </c>
+      <c r="BK43">
+        <v>1.01</v>
+      </c>
+      <c r="BL43">
+        <v>1000</v>
+      </c>
+      <c r="BM43">
+        <v>1.01</v>
+      </c>
+      <c r="BN43">
+        <v>1000</v>
+      </c>
+      <c r="BO43">
+        <v>1.01</v>
+      </c>
+      <c r="BP43">
+        <v>1000</v>
+      </c>
+      <c r="BQ43">
+        <v>1.01</v>
+      </c>
+      <c r="BR43">
+        <v>1000</v>
+      </c>
+      <c r="BS43">
+        <v>1.01</v>
+      </c>
+      <c r="BT43">
+        <v>1000</v>
+      </c>
+      <c r="BU43">
+        <v>1.01</v>
+      </c>
+      <c r="BV43">
+        <v>1000</v>
+      </c>
+      <c r="BW43">
+        <v>1.01</v>
+      </c>
+      <c r="BX43">
+        <v>1000</v>
+      </c>
+      <c r="BY43">
+        <v>1.01</v>
+      </c>
+      <c r="BZ43">
+        <v>1000</v>
+      </c>
+      <c r="CA43">
+        <v>1.01</v>
+      </c>
+      <c r="CB43" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="44" spans="1:80">
+      <c r="A44" t="s">
+        <v>82</v>
+      </c>
+      <c r="B44" t="s">
+        <v>111</v>
+      </c>
+      <c r="C44" t="s">
+        <v>131</v>
+      </c>
+      <c r="D44" t="s">
+        <v>174</v>
+      </c>
+      <c r="E44" t="s">
+        <v>217</v>
+      </c>
+      <c r="F44">
         <v>2.66</v>
       </c>
-      <c r="G42">
+      <c r="G44">
         <v>3.75</v>
       </c>
-      <c r="H42">
+      <c r="H44">
         <v>2.66</v>
       </c>
-      <c r="I42">
+      <c r="I44">
         <v>3.75</v>
       </c>
-      <c r="J42">
+      <c r="J44">
         <v>2.5</v>
       </c>
-      <c r="K42">
+      <c r="K44">
         <v>3.45</v>
       </c>
-      <c r="L42">
-        <v>1.01</v>
-      </c>
-      <c r="M42">
+      <c r="L44">
+        <v>1.01</v>
+      </c>
+      <c r="M44">
         <v>1.1</v>
       </c>
-      <c r="N42">
+      <c r="N44">
         <v>2.46</v>
       </c>
-      <c r="O42">
+      <c r="O44">
         <v>1.42</v>
       </c>
-      <c r="P42">
+      <c r="P44">
         <v>1.5</v>
       </c>
-      <c r="Q42">
+      <c r="Q44">
         <v>2.24</v>
       </c>
-      <c r="R42">
+      <c r="R44">
         <v>1.18</v>
       </c>
-      <c r="S42">
+      <c r="S44">
         <v>3.85</v>
       </c>
-      <c r="T42">
-        <v>1.01</v>
-      </c>
-      <c r="U42">
-        <v>1.01</v>
-      </c>
-      <c r="V42">
+      <c r="T44">
+        <v>1.01</v>
+      </c>
+      <c r="U44">
+        <v>1.01</v>
+      </c>
+      <c r="V44">
         <v>1.36</v>
       </c>
-      <c r="W42">
+      <c r="W44">
         <v>1.36</v>
       </c>
-      <c r="X42">
-        <v>1000</v>
-      </c>
-      <c r="Y42">
-        <v>1000</v>
-      </c>
-      <c r="Z42">
-        <v>1000</v>
-      </c>
-      <c r="AA42">
-        <v>1000</v>
-      </c>
-      <c r="AB42">
-        <v>1000</v>
-      </c>
-      <c r="AC42">
-        <v>1000</v>
-      </c>
-      <c r="AD42">
-        <v>1000</v>
-      </c>
-      <c r="AE42">
-        <v>1000</v>
-      </c>
-      <c r="AF42">
-        <v>1000</v>
-      </c>
-      <c r="AG42">
-        <v>1000</v>
-      </c>
-      <c r="AH42">
-        <v>1000</v>
-      </c>
-      <c r="AI42">
-        <v>1000</v>
-      </c>
-      <c r="AJ42">
-        <v>1000</v>
-      </c>
-      <c r="AK42">
-        <v>1000</v>
-      </c>
-      <c r="AL42">
-        <v>1000</v>
-      </c>
-      <c r="AM42">
-        <v>1000</v>
-      </c>
-      <c r="AN42">
-        <v>1000</v>
-      </c>
-      <c r="AO42">
-        <v>1000</v>
-      </c>
-      <c r="AP42">
-        <v>1.01</v>
-      </c>
-      <c r="AQ42">
-        <v>1.01</v>
-      </c>
-      <c r="AR42">
-        <v>1.01</v>
-      </c>
-      <c r="AS42">
-        <v>1.01</v>
-      </c>
-      <c r="AT42">
-        <v>1.01</v>
-      </c>
-      <c r="AU42">
-        <v>1.01</v>
-      </c>
-      <c r="AV42">
-        <v>1.01</v>
-      </c>
-      <c r="AW42">
-        <v>1.01</v>
-      </c>
-      <c r="AX42">
-        <v>1.01</v>
-      </c>
-      <c r="AY42">
-        <v>1.01</v>
-      </c>
-      <c r="AZ42">
-        <v>1.01</v>
-      </c>
-      <c r="BA42">
-        <v>1.01</v>
-      </c>
-      <c r="BB42">
-        <v>1.01</v>
-      </c>
-      <c r="BC42">
-        <v>1.01</v>
-      </c>
-      <c r="BD42">
-        <v>1.01</v>
-      </c>
-      <c r="BE42">
-        <v>1.01</v>
-      </c>
-      <c r="BF42">
-        <v>1.01</v>
-      </c>
-      <c r="BG42">
-        <v>1.01</v>
-      </c>
-      <c r="BH42">
-        <v>1000</v>
-      </c>
-      <c r="BI42">
-        <v>1.01</v>
-      </c>
-      <c r="BJ42">
-        <v>1000</v>
-      </c>
-      <c r="BK42">
-        <v>1.01</v>
-      </c>
-      <c r="BL42">
-        <v>1000</v>
-      </c>
-      <c r="BM42">
-        <v>1.01</v>
-      </c>
-      <c r="BN42">
-        <v>1000</v>
-      </c>
-      <c r="BO42">
-        <v>1.01</v>
-      </c>
-      <c r="BP42">
-        <v>1000</v>
-      </c>
-      <c r="BQ42">
-        <v>1.01</v>
-      </c>
-      <c r="BR42">
-        <v>1000</v>
-      </c>
-      <c r="BS42">
-        <v>1.01</v>
-      </c>
-      <c r="BT42">
-        <v>1000</v>
-      </c>
-      <c r="BU42">
-        <v>1.01</v>
-      </c>
-      <c r="BV42">
-        <v>1000</v>
-      </c>
-      <c r="BW42">
-        <v>1.01</v>
-      </c>
-      <c r="BX42">
-        <v>1000</v>
-      </c>
-      <c r="BY42">
-        <v>1.01</v>
-      </c>
-      <c r="BZ42">
-        <v>0</v>
-      </c>
-      <c r="CA42">
-        <v>0</v>
-      </c>
-      <c r="CB42" t="s">
-        <v>213</v>
+      <c r="X44">
+        <v>1000</v>
+      </c>
+      <c r="Y44">
+        <v>1000</v>
+      </c>
+      <c r="Z44">
+        <v>1000</v>
+      </c>
+      <c r="AA44">
+        <v>1000</v>
+      </c>
+      <c r="AB44">
+        <v>1000</v>
+      </c>
+      <c r="AC44">
+        <v>1000</v>
+      </c>
+      <c r="AD44">
+        <v>1000</v>
+      </c>
+      <c r="AE44">
+        <v>1000</v>
+      </c>
+      <c r="AF44">
+        <v>1000</v>
+      </c>
+      <c r="AG44">
+        <v>1000</v>
+      </c>
+      <c r="AH44">
+        <v>1000</v>
+      </c>
+      <c r="AI44">
+        <v>1000</v>
+      </c>
+      <c r="AJ44">
+        <v>1000</v>
+      </c>
+      <c r="AK44">
+        <v>1000</v>
+      </c>
+      <c r="AL44">
+        <v>1000</v>
+      </c>
+      <c r="AM44">
+        <v>1000</v>
+      </c>
+      <c r="AN44">
+        <v>1000</v>
+      </c>
+      <c r="AO44">
+        <v>1000</v>
+      </c>
+      <c r="AP44">
+        <v>1.01</v>
+      </c>
+      <c r="AQ44">
+        <v>1.01</v>
+      </c>
+      <c r="AR44">
+        <v>1.01</v>
+      </c>
+      <c r="AS44">
+        <v>1.01</v>
+      </c>
+      <c r="AT44">
+        <v>1.01</v>
+      </c>
+      <c r="AU44">
+        <v>1.01</v>
+      </c>
+      <c r="AV44">
+        <v>1.01</v>
+      </c>
+      <c r="AW44">
+        <v>1.01</v>
+      </c>
+      <c r="AX44">
+        <v>1.01</v>
+      </c>
+      <c r="AY44">
+        <v>1.01</v>
+      </c>
+      <c r="AZ44">
+        <v>1.01</v>
+      </c>
+      <c r="BA44">
+        <v>1.01</v>
+      </c>
+      <c r="BB44">
+        <v>1.01</v>
+      </c>
+      <c r="BC44">
+        <v>1.01</v>
+      </c>
+      <c r="BD44">
+        <v>1.01</v>
+      </c>
+      <c r="BE44">
+        <v>1.01</v>
+      </c>
+      <c r="BF44">
+        <v>1.01</v>
+      </c>
+      <c r="BG44">
+        <v>1.01</v>
+      </c>
+      <c r="BH44">
+        <v>1000</v>
+      </c>
+      <c r="BI44">
+        <v>1.01</v>
+      </c>
+      <c r="BJ44">
+        <v>1000</v>
+      </c>
+      <c r="BK44">
+        <v>1.01</v>
+      </c>
+      <c r="BL44">
+        <v>1000</v>
+      </c>
+      <c r="BM44">
+        <v>1.01</v>
+      </c>
+      <c r="BN44">
+        <v>1000</v>
+      </c>
+      <c r="BO44">
+        <v>1.01</v>
+      </c>
+      <c r="BP44">
+        <v>1000</v>
+      </c>
+      <c r="BQ44">
+        <v>1.01</v>
+      </c>
+      <c r="BR44">
+        <v>1000</v>
+      </c>
+      <c r="BS44">
+        <v>1.01</v>
+      </c>
+      <c r="BT44">
+        <v>1000</v>
+      </c>
+      <c r="BU44">
+        <v>1.01</v>
+      </c>
+      <c r="BV44">
+        <v>1000</v>
+      </c>
+      <c r="BW44">
+        <v>1.01</v>
+      </c>
+      <c r="BX44">
+        <v>1000</v>
+      </c>
+      <c r="BY44">
+        <v>1.01</v>
+      </c>
+      <c r="BZ44">
+        <v>0</v>
+      </c>
+      <c r="CA44">
+        <v>0</v>
+      </c>
+      <c r="CB44" t="s">
+        <v>218</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-31.xlsx
@@ -670,7 +670,7 @@
     <t>Melgar</t>
   </si>
   <si>
-    <t>2026-08-29 06:03:47</t>
+    <t>2026-08-29 08:34:44</t>
   </si>
 </sst>
 </file>
@@ -1270,16 +1270,16 @@
         <v>1.61</v>
       </c>
       <c r="H2">
-        <v>5.7</v>
+        <v>2.72</v>
       </c>
       <c r="I2">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="J2">
-        <v>4.2</v>
+        <v>3.9</v>
       </c>
       <c r="K2">
-        <v>4.8</v>
+        <v>950</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -1297,7 +1297,7 @@
         <v>2.04</v>
       </c>
       <c r="Q2">
-        <v>1.51</v>
+        <v>1.64</v>
       </c>
       <c r="R2">
         <v>1.42</v>
@@ -1312,10 +1312,10 @@
         <v>1.01</v>
       </c>
       <c r="V2">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="W2">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1506,22 +1506,22 @@
         <v>176</v>
       </c>
       <c r="F3">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="G3">
         <v>1.33</v>
       </c>
       <c r="H3">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I3">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="J3">
         <v>6.2</v>
       </c>
       <c r="K3">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1533,7 +1533,7 @@
         <v>7</v>
       </c>
       <c r="O3">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="P3">
         <v>3.05</v>
@@ -1554,10 +1554,10 @@
         <v>2.1</v>
       </c>
       <c r="V3">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="W3">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -1769,7 +1769,7 @@
         <v>1.01</v>
       </c>
       <c r="M4">
-        <v>1.04</v>
+        <v>1.01</v>
       </c>
       <c r="N4">
         <v>2.76</v>
@@ -1999,13 +1999,13 @@
         <v>3.6</v>
       </c>
       <c r="I5">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J5">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="K5">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -2014,13 +2014,13 @@
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>2.6</v>
+        <v>2.52</v>
       </c>
       <c r="O5">
         <v>1.02</v>
       </c>
       <c r="P5">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="Q5">
         <v>2.52</v>
@@ -2498,7 +2498,7 @@
         <v>1.01</v>
       </c>
       <c r="N7">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="O7">
         <v>1.15</v>
@@ -2585,7 +2585,7 @@
         <v>20</v>
       </c>
       <c r="AQ7">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="AR7">
         <v>36</v>
@@ -2609,22 +2609,22 @@
         <v>8.800000000000001</v>
       </c>
       <c r="AY7">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AZ7">
-        <v>15.5</v>
+        <v>14.5</v>
       </c>
       <c r="BA7">
         <v>40</v>
       </c>
       <c r="BB7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BC7">
         <v>10</v>
       </c>
       <c r="BD7">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BE7">
         <v>40</v>
@@ -3926,19 +3926,19 @@
         <v>186</v>
       </c>
       <c r="F13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="G13">
         <v>1000</v>
       </c>
       <c r="H13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="I13">
         <v>1000</v>
       </c>
       <c r="J13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="K13">
         <v>1000</v>
@@ -4168,22 +4168,22 @@
         <v>187</v>
       </c>
       <c r="F14">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="G14">
         <v>5.2</v>
       </c>
       <c r="H14">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="I14">
         <v>2.6</v>
       </c>
       <c r="J14">
-        <v>2.98</v>
+        <v>3.05</v>
       </c>
       <c r="K14">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -4198,10 +4198,10 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>1.79</v>
+        <v>1.69</v>
       </c>
       <c r="Q14">
-        <v>2.04</v>
+        <v>1.85</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4416,7 +4416,7 @@
         <v>1.54</v>
       </c>
       <c r="H15">
-        <v>3.7</v>
+        <v>1.04</v>
       </c>
       <c r="I15">
         <v>17</v>
@@ -4682,13 +4682,13 @@
         <v>1.28</v>
       </c>
       <c r="P16">
-        <v>1.88</v>
+        <v>1.93</v>
       </c>
       <c r="Q16">
         <v>1.84</v>
       </c>
       <c r="R16">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="S16">
         <v>3.05</v>
@@ -4906,7 +4906,7 @@
         <v>1.52</v>
       </c>
       <c r="J17">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="K17">
         <v>4.5</v>
@@ -4918,7 +4918,7 @@
         <v>1.08</v>
       </c>
       <c r="N17">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="O17">
         <v>1.36</v>
@@ -4933,13 +4933,13 @@
         <v>1.32</v>
       </c>
       <c r="S17">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T17">
         <v>2.3</v>
       </c>
       <c r="U17">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="V17">
         <v>0</v>
@@ -4948,109 +4948,109 @@
         <v>0</v>
       </c>
       <c r="X17">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="Y17">
-        <v>7</v>
+        <v>9.4</v>
       </c>
       <c r="Z17">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AA17">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="AB17">
         <v>24</v>
       </c>
       <c r="AC17">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="AD17">
         <v>10.5</v>
       </c>
       <c r="AE17">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AF17">
-        <v>90</v>
+        <v>1000</v>
       </c>
       <c r="AG17">
-        <v>34</v>
+        <v>46</v>
       </c>
       <c r="AH17">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AI17">
-        <v>55</v>
+        <v>280</v>
       </c>
       <c r="AJ17">
-        <v>420</v>
+        <v>1000</v>
       </c>
       <c r="AK17">
-        <v>200</v>
+        <v>1000</v>
       </c>
       <c r="AL17">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AM17">
-        <v>250</v>
+        <v>1000</v>
       </c>
       <c r="AN17">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="AO17">
-        <v>9.4</v>
+        <v>15</v>
       </c>
       <c r="AP17">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AQ17">
         <v>6.4</v>
       </c>
       <c r="AR17">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="AS17">
         <v>11</v>
       </c>
       <c r="AT17">
-        <v>20</v>
+        <v>16.5</v>
       </c>
       <c r="AU17">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV17">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AW17">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AX17">
-        <v>32</v>
+        <v>6.6</v>
       </c>
       <c r="AY17">
         <v>21</v>
       </c>
       <c r="AZ17">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BA17">
-        <v>28</v>
+        <v>10.5</v>
       </c>
       <c r="BB17">
-        <v>15</v>
+        <v>5.4</v>
       </c>
       <c r="BC17">
-        <v>15</v>
+        <v>6.4</v>
       </c>
       <c r="BD17">
-        <v>15</v>
+        <v>6.4</v>
       </c>
       <c r="BE17">
-        <v>14.5</v>
+        <v>6.4</v>
       </c>
       <c r="BF17">
-        <v>15</v>
+        <v>5.4</v>
       </c>
       <c r="BG17">
         <v>8.6</v>
@@ -5620,22 +5620,22 @@
         <v>193</v>
       </c>
       <c r="F20">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="G20">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="H20">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="I20">
-        <v>3.95</v>
+        <v>4.4</v>
       </c>
       <c r="J20">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="K20">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="L20">
         <v>0</v>
@@ -5653,7 +5653,7 @@
         <v>1.25</v>
       </c>
       <c r="Q20">
-        <v>1.03</v>
+        <v>1.51</v>
       </c>
       <c r="R20">
         <v>0</v>
@@ -6104,22 +6104,22 @@
         <v>195</v>
       </c>
       <c r="F22">
-        <v>1.79</v>
+        <v>1.37</v>
       </c>
       <c r="G22">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="H22">
-        <v>5</v>
+        <v>4.6</v>
       </c>
       <c r="I22">
-        <v>5.6</v>
+        <v>60</v>
       </c>
       <c r="J22">
-        <v>3.65</v>
+        <v>3.55</v>
       </c>
       <c r="K22">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -6137,7 +6137,7 @@
         <v>1.25</v>
       </c>
       <c r="Q22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -6346,22 +6346,22 @@
         <v>196</v>
       </c>
       <c r="F23">
-        <v>1.38</v>
+        <v>1.09</v>
       </c>
       <c r="G23">
-        <v>1.4</v>
+        <v>1.49</v>
       </c>
       <c r="H23">
-        <v>7.2</v>
+        <v>1.1</v>
       </c>
       <c r="I23">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="J23">
-        <v>5.2</v>
+        <v>4.7</v>
       </c>
       <c r="K23">
-        <v>6.2</v>
+        <v>950</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6830,7 +6830,7 @@
         <v>198</v>
       </c>
       <c r="F25">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="G25">
         <v>1.69</v>
@@ -6839,7 +6839,7 @@
         <v>4.6</v>
       </c>
       <c r="I25">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="J25">
         <v>3.95</v>
@@ -7317,10 +7317,10 @@
         <v>2.92</v>
       </c>
       <c r="G27">
-        <v>3.05</v>
+        <v>3.65</v>
       </c>
       <c r="H27">
-        <v>2.52</v>
+        <v>2.24</v>
       </c>
       <c r="I27">
         <v>2.66</v>
@@ -7344,7 +7344,7 @@
         <v>0</v>
       </c>
       <c r="P27">
-        <v>1.91</v>
+        <v>1.24</v>
       </c>
       <c r="Q27">
         <v>1.87</v>
@@ -7559,7 +7559,7 @@
         <v>2.24</v>
       </c>
       <c r="G28">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H28">
         <v>4.1</v>
@@ -7580,10 +7580,10 @@
         <v>1.15</v>
       </c>
       <c r="N28">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="O28">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="P28">
         <v>1.44</v>
@@ -7601,7 +7601,7 @@
         <v>2.5</v>
       </c>
       <c r="U28">
-        <v>1.59</v>
+        <v>1.62</v>
       </c>
       <c r="V28">
         <v>0</v>
@@ -7610,40 +7610,40 @@
         <v>0</v>
       </c>
       <c r="X28">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="Y28">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Z28">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA28">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB28">
-        <v>6.2</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC28">
-        <v>7.4</v>
+        <v>10.5</v>
       </c>
       <c r="AD28">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="AE28">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AF28">
-        <v>11.5</v>
+        <v>21</v>
       </c>
       <c r="AG28">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="AH28">
         <v>38</v>
       </c>
       <c r="AI28">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AJ28">
         <v>38</v>
@@ -7652,70 +7652,70 @@
         <v>44</v>
       </c>
       <c r="AL28">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AM28">
-        <v>340</v>
+        <v>1000</v>
       </c>
       <c r="AN28">
         <v>48</v>
       </c>
       <c r="AO28">
-        <v>170</v>
+        <v>1000</v>
       </c>
       <c r="AP28">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ28">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AR28">
         <v>17.5</v>
       </c>
       <c r="AS28">
-        <v>12</v>
+        <v>5.9</v>
       </c>
       <c r="AT28">
         <v>5.7</v>
       </c>
       <c r="AU28">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AV28">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AW28">
-        <v>34</v>
+        <v>5.8</v>
       </c>
       <c r="AX28">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="AY28">
         <v>12</v>
       </c>
       <c r="AZ28">
-        <v>21</v>
+        <v>5.3</v>
       </c>
       <c r="BA28">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="BB28">
-        <v>20</v>
+        <v>5.3</v>
       </c>
       <c r="BC28">
-        <v>32</v>
+        <v>5.4</v>
       </c>
       <c r="BD28">
-        <v>12</v>
+        <v>6</v>
       </c>
       <c r="BE28">
         <v>110</v>
       </c>
       <c r="BF28">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="BG28">
-        <v>12.5</v>
+        <v>6</v>
       </c>
       <c r="BH28">
         <v>2.56</v>
@@ -8282,22 +8282,22 @@
         <v>204</v>
       </c>
       <c r="F31">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="G31">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="H31">
+        <v>6.6</v>
+      </c>
+      <c r="I31">
+        <v>21</v>
+      </c>
+      <c r="J31">
+        <v>2.28</v>
+      </c>
+      <c r="K31">
         <v>6.2</v>
-      </c>
-      <c r="I31">
-        <v>36</v>
-      </c>
-      <c r="J31">
-        <v>3.6</v>
-      </c>
-      <c r="K31">
-        <v>7</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -8315,7 +8315,7 @@
         <v>1.54</v>
       </c>
       <c r="Q31">
-        <v>2.12</v>
+        <v>1.01</v>
       </c>
       <c r="R31">
         <v>0</v>
@@ -8527,10 +8527,10 @@
         <v>1.86</v>
       </c>
       <c r="G32">
-        <v>2.02</v>
+        <v>2.08</v>
       </c>
       <c r="H32">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="I32">
         <v>5.4</v>
@@ -8563,127 +8563,127 @@
         <v>1.14</v>
       </c>
       <c r="S32">
-        <v>2.58</v>
+        <v>4</v>
       </c>
       <c r="T32">
-        <v>2</v>
+        <v>1.01</v>
       </c>
       <c r="U32">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="V32">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W32">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="X32">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="Y32">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="Z32">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="AA32">
-        <v>160</v>
+        <v>1000</v>
       </c>
       <c r="AB32">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AC32">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AD32">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="AE32">
-        <v>95</v>
+        <v>1000</v>
       </c>
       <c r="AF32">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AG32">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH32">
-        <v>27</v>
+        <v>1000</v>
       </c>
       <c r="AI32">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AJ32">
-        <v>28</v>
+        <v>1000</v>
       </c>
       <c r="AK32">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="AL32">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AM32">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AN32">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AO32">
-        <v>140</v>
+        <v>1000</v>
       </c>
       <c r="AP32">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AQ32">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR32">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="AS32">
-        <v>90</v>
+        <v>1.01</v>
       </c>
       <c r="AT32">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU32">
-        <v>6</v>
+        <v>1.01</v>
       </c>
       <c r="AV32">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW32">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="AX32">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AY32">
-        <v>7.8</v>
+        <v>1.01</v>
       </c>
       <c r="AZ32">
-        <v>16</v>
+        <v>1.01</v>
       </c>
       <c r="BA32">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="BB32">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC32">
-        <v>17</v>
+        <v>1.01</v>
       </c>
       <c r="BD32">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BE32">
-        <v>110</v>
+        <v>1.01</v>
       </c>
       <c r="BF32">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG32">
-        <v>80</v>
+        <v>1.01</v>
       </c>
       <c r="BH32">
         <v>1000</v>
@@ -8766,22 +8766,22 @@
         <v>206</v>
       </c>
       <c r="F33">
-        <v>3.55</v>
+        <v>3.45</v>
       </c>
       <c r="G33">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="H33">
         <v>2.12</v>
       </c>
       <c r="I33">
-        <v>2.22</v>
+        <v>2.28</v>
       </c>
       <c r="J33">
-        <v>3.7</v>
+        <v>1.95</v>
       </c>
       <c r="K33">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -9041,7 +9041,7 @@
         <v>1.25</v>
       </c>
       <c r="Q34">
-        <v>1.8</v>
+        <v>1.01</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -9250,13 +9250,13 @@
         <v>208</v>
       </c>
       <c r="F35">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="G35">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="H35">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="I35">
         <v>1.93</v>
@@ -9265,7 +9265,7 @@
         <v>3.65</v>
       </c>
       <c r="K35">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -9280,10 +9280,10 @@
         <v>0</v>
       </c>
       <c r="P35">
-        <v>1.84</v>
+        <v>1.85</v>
       </c>
       <c r="Q35">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -9495,7 +9495,7 @@
         <v>1.98</v>
       </c>
       <c r="G36">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="H36">
         <v>4.2</v>
@@ -9522,7 +9522,7 @@
         <v>1.33</v>
       </c>
       <c r="P36">
-        <v>1.95</v>
+        <v>1.92</v>
       </c>
       <c r="Q36">
         <v>2.02</v>
@@ -9531,7 +9531,7 @@
         <v>1.37</v>
       </c>
       <c r="S36">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="T36">
         <v>1.85</v>
@@ -9549,22 +9549,22 @@
         <v>15</v>
       </c>
       <c r="Y36">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="Z36">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AA36">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AB36">
         <v>9.199999999999999</v>
       </c>
       <c r="AC36">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD36">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE36">
         <v>60</v>
@@ -9585,10 +9585,10 @@
         <v>23</v>
       </c>
       <c r="AK36">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AL36">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AM36">
         <v>110</v>
@@ -9597,7 +9597,7 @@
         <v>14.5</v>
       </c>
       <c r="AO36">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AP36">
         <v>13</v>
@@ -9609,13 +9609,13 @@
         <v>19.5</v>
       </c>
       <c r="AS36">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AT36">
         <v>8.4</v>
       </c>
       <c r="AU36">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AV36">
         <v>15.5</v>
@@ -9639,13 +9639,13 @@
         <v>19</v>
       </c>
       <c r="BC36">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BD36">
         <v>23</v>
       </c>
       <c r="BE36">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="BF36">
         <v>12.5</v>
@@ -9740,7 +9740,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="H37">
-        <v>1.52</v>
+        <v>1.56</v>
       </c>
       <c r="I37">
         <v>1.91</v>
@@ -9749,13 +9749,13 @@
         <v>3.25</v>
       </c>
       <c r="K37">
-        <v>6.4</v>
+        <v>5.8</v>
       </c>
       <c r="L37">
         <v>1.01</v>
       </c>
       <c r="M37">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N37">
         <v>3.55</v>
@@ -9982,7 +9982,7 @@
         <v>7</v>
       </c>
       <c r="H38">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="I38">
         <v>1.59</v>
@@ -10018,10 +10018,10 @@
         <v>3.3</v>
       </c>
       <c r="T38">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U38">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="V38">
         <v>0</v>
@@ -10030,7 +10030,7 @@
         <v>0</v>
       </c>
       <c r="X38">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="Y38">
         <v>8.199999999999999</v>
@@ -10048,13 +10048,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD38">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AE38">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="AF38">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="AG38">
         <v>27</v>
@@ -10063,7 +10063,7 @@
         <v>24</v>
       </c>
       <c r="AI38">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AJ38">
         <v>260</v>
@@ -10090,7 +10090,7 @@
         <v>7.8</v>
       </c>
       <c r="AR38">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS38">
         <v>12.5</v>
@@ -10102,7 +10102,7 @@
         <v>9.4</v>
       </c>
       <c r="AV38">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW38">
         <v>15.5</v>
@@ -10117,19 +10117,19 @@
         <v>21</v>
       </c>
       <c r="BA38">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="BB38">
-        <v>21</v>
+        <v>50</v>
       </c>
       <c r="BC38">
-        <v>55</v>
+        <v>40</v>
       </c>
       <c r="BD38">
         <v>60</v>
       </c>
       <c r="BE38">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="BF38">
         <v>40</v>
@@ -10218,22 +10218,22 @@
         <v>212</v>
       </c>
       <c r="F39">
-        <v>1.99</v>
+        <v>1.96</v>
       </c>
       <c r="G39">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="H39">
         <v>3.15</v>
       </c>
       <c r="I39">
-        <v>3.4</v>
+        <v>3.85</v>
       </c>
       <c r="J39">
-        <v>4.6</v>
+        <v>4.2</v>
       </c>
       <c r="K39">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -10248,10 +10248,10 @@
         <v>0</v>
       </c>
       <c r="P39">
-        <v>3.85</v>
+        <v>3.55</v>
       </c>
       <c r="Q39">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="R39">
         <v>0</v>
@@ -10460,7 +10460,7 @@
         <v>213</v>
       </c>
       <c r="F40">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="G40">
         <v>1.89</v>
@@ -10469,7 +10469,7 @@
         <v>5</v>
       </c>
       <c r="I40">
-        <v>5.4</v>
+        <v>5.8</v>
       </c>
       <c r="J40">
         <v>3.6</v>
@@ -10705,7 +10705,7 @@
         <v>1.14</v>
       </c>
       <c r="G41">
-        <v>1.21</v>
+        <v>1.19</v>
       </c>
       <c r="H41">
         <v>14</v>
@@ -10714,7 +10714,7 @@
         <v>1000</v>
       </c>
       <c r="J41">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="K41">
         <v>19.5</v>
@@ -10947,19 +10947,19 @@
         <v>4.1</v>
       </c>
       <c r="G42">
-        <v>5.4</v>
+        <v>5.2</v>
       </c>
       <c r="H42">
-        <v>1.28</v>
+        <v>1.75</v>
       </c>
       <c r="I42">
         <v>1.96</v>
       </c>
       <c r="J42">
-        <v>3.3</v>
+        <v>3.85</v>
       </c>
       <c r="K42">
-        <v>4.6</v>
+        <v>5.5</v>
       </c>
       <c r="L42">
         <v>0</v>
@@ -10974,7 +10974,7 @@
         <v>0</v>
       </c>
       <c r="P42">
-        <v>2.08</v>
+        <v>2.16</v>
       </c>
       <c r="Q42">
         <v>1.5</v>
@@ -10989,7 +10989,7 @@
         <v>1.64</v>
       </c>
       <c r="U42">
-        <v>1.01</v>
+        <v>2.22</v>
       </c>
       <c r="V42">
         <v>0</v>
@@ -11195,13 +11195,13 @@
         <v>19.5</v>
       </c>
       <c r="I43">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J43">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="K43">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="L43">
         <v>0</v>
@@ -11210,16 +11210,16 @@
         <v>1.02</v>
       </c>
       <c r="N43">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O43">
         <v>1.13</v>
       </c>
       <c r="P43">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="Q43">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="R43">
         <v>2</v>
@@ -11228,10 +11228,10 @@
         <v>1.94</v>
       </c>
       <c r="T43">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="U43">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="V43">
         <v>0</v>
@@ -11240,13 +11240,13 @@
         <v>0</v>
       </c>
       <c r="X43">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="Y43">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="Z43">
-        <v>230</v>
+        <v>1000</v>
       </c>
       <c r="AA43">
         <v>1000</v>
@@ -11255,46 +11255,46 @@
         <v>13.5</v>
       </c>
       <c r="AC43">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AD43">
         <v>70</v>
       </c>
       <c r="AE43">
-        <v>330</v>
+        <v>360</v>
       </c>
       <c r="AF43">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AG43">
         <v>13</v>
       </c>
       <c r="AH43">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="AI43">
         <v>1000</v>
       </c>
       <c r="AJ43">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AK43">
         <v>13.5</v>
       </c>
       <c r="AL43">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM43">
-        <v>180</v>
+        <v>1000</v>
       </c>
       <c r="AN43">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="AO43">
-        <v>350</v>
+        <v>380</v>
       </c>
       <c r="AP43">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AQ43">
         <v>34</v>
@@ -11303,19 +11303,19 @@
         <v>48</v>
       </c>
       <c r="AS43">
-        <v>18</v>
+        <v>16.5</v>
       </c>
       <c r="AT43">
         <v>11.5</v>
       </c>
       <c r="AU43">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV43">
         <v>34</v>
       </c>
       <c r="AW43">
-        <v>50</v>
+        <v>19</v>
       </c>
       <c r="AX43">
         <v>8.6</v>
@@ -11324,10 +11324,10 @@
         <v>11.5</v>
       </c>
       <c r="AZ43">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="BA43">
-        <v>48</v>
+        <v>16.5</v>
       </c>
       <c r="BB43">
         <v>8.4</v>
@@ -11336,16 +11336,16 @@
         <v>11.5</v>
       </c>
       <c r="BD43">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="BE43">
         <v>46</v>
       </c>
       <c r="BF43">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="BG43">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BH43">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-31.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="338" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="362" uniqueCount="229">
   <si>
     <t>League</t>
   </si>
@@ -271,15 +271,18 @@
     <t>Colombian Primera A</t>
   </si>
   <si>
+    <t>Welsh Premiership</t>
+  </si>
+  <si>
     <t>Kazakhstan Premier League</t>
   </si>
   <si>
+    <t>Romanian Liga II</t>
+  </si>
+  <si>
     <t>Latvian Virsliga</t>
   </si>
   <si>
-    <t>Romanian Liga II</t>
-  </si>
-  <si>
     <t>Ukrainian Premier League</t>
   </si>
   <si>
@@ -364,6 +367,9 @@
     <t>02:10:00</t>
   </si>
   <si>
+    <t>13:30:00</t>
+  </si>
+  <si>
     <t>14:00:00</t>
   </si>
   <si>
@@ -430,15 +436,27 @@
     <t>Monterrey</t>
   </si>
   <si>
+    <t>Ammanford AFC</t>
+  </si>
+  <si>
+    <t>Airbus UK Broughton</t>
+  </si>
+  <si>
+    <t>Flint Town United</t>
+  </si>
+  <si>
+    <t>Briton Ferry Llansawel</t>
+  </si>
+  <si>
     <t>Elimai FC</t>
   </si>
   <si>
+    <t>ACS Fotbal Club Bacau</t>
+  </si>
+  <si>
     <t>Liepajas Metalurgs</t>
   </si>
   <si>
-    <t>ACS Fotbal Club Bacau</t>
-  </si>
-  <si>
     <t>FC Bukovyna</t>
   </si>
   <si>
@@ -466,10 +484,13 @@
     <t>Hammarby TFF</t>
   </si>
   <si>
+    <t>Djurgardens</t>
+  </si>
+  <si>
     <t>Sirius</t>
   </si>
   <si>
-    <t>Djurgardens</t>
+    <t>GAIS</t>
   </si>
   <si>
     <t>Burgos</t>
@@ -481,9 +502,6 @@
     <t>Omonia</t>
   </si>
   <si>
-    <t>GAIS</t>
-  </si>
-  <si>
     <t>Maccabi Tel Aviv</t>
   </si>
   <si>
@@ -532,12 +550,12 @@
     <t>Benfica</t>
   </si>
   <si>
+    <t>Barcelona</t>
+  </si>
+  <si>
     <t>Celta Vigo B</t>
   </si>
   <si>
-    <t>Barcelona</t>
-  </si>
-  <si>
     <t>Atletico Grau</t>
   </si>
   <si>
@@ -559,15 +577,27 @@
     <t>Atletico San Luis</t>
   </si>
   <si>
+    <t>Cardiff Metropolitan</t>
+  </si>
+  <si>
+    <t>Holywell Town</t>
+  </si>
+  <si>
+    <t>Connahs Quay</t>
+  </si>
+  <si>
+    <t>Barry Town Utd</t>
+  </si>
+  <si>
     <t>Kairat Almaty</t>
   </si>
   <si>
+    <t>CSM Slatina</t>
+  </si>
+  <si>
     <t>FK Riga</t>
   </si>
   <si>
-    <t>CSM Slatina</t>
-  </si>
-  <si>
     <t>Dynamo Kiev</t>
   </si>
   <si>
@@ -595,10 +625,13 @@
     <t>Karlbergs BK</t>
   </si>
   <si>
+    <t>Mjallby</t>
+  </si>
+  <si>
     <t>Malmo FF</t>
   </si>
   <si>
-    <t>Mjallby</t>
+    <t>Brommapojkarna</t>
   </si>
   <si>
     <t>Sociedad B</t>
@@ -610,9 +643,6 @@
     <t>Omonia FC Aradippou</t>
   </si>
   <si>
-    <t>Brommapojkarna</t>
-  </si>
-  <si>
     <t>Maccabi Haifa</t>
   </si>
   <si>
@@ -661,16 +691,16 @@
     <t>Estoril Praia</t>
   </si>
   <si>
+    <t>Rayo Vallecano</t>
+  </si>
+  <si>
     <t>CD Castellon</t>
   </si>
   <si>
-    <t>Rayo Vallecano</t>
-  </si>
-  <si>
     <t>Melgar</t>
   </si>
   <si>
-    <t>2026-08-29 08:34:44</t>
+    <t>2026-08-29 11:03:29</t>
   </si>
 </sst>
 </file>
@@ -1002,7 +1032,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:CB44"/>
+  <dimension ref="A1:CB48"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:80">
@@ -1252,34 +1282,34 @@
         <v>80</v>
       </c>
       <c r="B2" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C2" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D2" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E2" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="F2">
         <v>1.57</v>
       </c>
       <c r="G2">
-        <v>1.61</v>
+        <v>1.69</v>
       </c>
       <c r="H2">
-        <v>2.72</v>
+        <v>5.6</v>
       </c>
       <c r="I2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J2">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="K2">
-        <v>950</v>
+        <v>4.8</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -1288,7 +1318,7 @@
         <v>1.01</v>
       </c>
       <c r="N2">
-        <v>2.48</v>
+        <v>4.1</v>
       </c>
       <c r="O2">
         <v>1.24</v>
@@ -1297,10 +1327,10 @@
         <v>2.04</v>
       </c>
       <c r="Q2">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="R2">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="S2">
         <v>2.76</v>
@@ -1312,10 +1342,10 @@
         <v>1.01</v>
       </c>
       <c r="V2">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W2">
-        <v>2.38</v>
+        <v>2.44</v>
       </c>
       <c r="X2">
         <v>1000</v>
@@ -1486,7 +1516,7 @@
         <v>1.01</v>
       </c>
       <c r="CB2" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="3" spans="1:80">
@@ -1494,16 +1524,16 @@
         <v>81</v>
       </c>
       <c r="B3" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C3" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D3" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="E3" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="F3">
         <v>1.3</v>
@@ -1512,16 +1542,16 @@
         <v>1.33</v>
       </c>
       <c r="H3">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="I3">
         <v>12</v>
       </c>
       <c r="J3">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="K3">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1533,7 +1563,7 @@
         <v>7</v>
       </c>
       <c r="O3">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="P3">
         <v>3.05</v>
@@ -1557,7 +1587,7 @@
         <v>1.09</v>
       </c>
       <c r="W3">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="X3">
         <v>1000</v>
@@ -1662,7 +1692,7 @@
         <v>2.56</v>
       </c>
       <c r="BF3">
-        <v>1.62</v>
+        <v>2.74</v>
       </c>
       <c r="BG3">
         <v>2.56</v>
@@ -1728,7 +1758,7 @@
         <v>0</v>
       </c>
       <c r="CB3" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="4" spans="1:80">
@@ -1736,19 +1766,19 @@
         <v>82</v>
       </c>
       <c r="B4" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C4" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="D4" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="E4" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="F4">
-        <v>1.93</v>
+        <v>1.94</v>
       </c>
       <c r="G4">
         <v>2.42</v>
@@ -1970,7 +2000,7 @@
         <v>1.01</v>
       </c>
       <c r="CB4" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="5" spans="1:80">
@@ -1978,16 +2008,16 @@
         <v>83</v>
       </c>
       <c r="B5" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C5" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="D5" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="E5" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="F5">
         <v>2.24</v>
@@ -2005,7 +2035,7 @@
         <v>3</v>
       </c>
       <c r="K5">
-        <v>3.35</v>
+        <v>3.55</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -2014,7 +2044,7 @@
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>2.52</v>
+        <v>2.58</v>
       </c>
       <c r="O5">
         <v>1.02</v>
@@ -2113,7 +2143,7 @@
         <v>1.01</v>
       </c>
       <c r="AU5">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AV5">
         <v>1.01</v>
@@ -2128,7 +2158,7 @@
         <v>1.01</v>
       </c>
       <c r="AZ5">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BA5">
         <v>1.01</v>
@@ -2212,7 +2242,7 @@
         <v>1.01</v>
       </c>
       <c r="CB5" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="6" spans="1:80">
@@ -2220,22 +2250,22 @@
         <v>84</v>
       </c>
       <c r="B6" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C6" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="D6" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="E6" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="F6">
         <v>1.99</v>
       </c>
       <c r="G6">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H6">
         <v>4.1</v>
@@ -2283,7 +2313,7 @@
         <v>1.23</v>
       </c>
       <c r="W6">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="X6">
         <v>1000</v>
@@ -2340,28 +2370,28 @@
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ6">
         <v>9</v>
       </c>
       <c r="AR6">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AS6">
         <v>40</v>
       </c>
       <c r="AT6">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="AU6">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="AV6">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AW6">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AX6">
         <v>8.800000000000001</v>
@@ -2376,7 +2406,7 @@
         <v>40</v>
       </c>
       <c r="BB6">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC6">
         <v>19.5</v>
@@ -2454,7 +2484,7 @@
         <v>1.01</v>
       </c>
       <c r="CB6" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="7" spans="1:80">
@@ -2462,16 +2492,16 @@
         <v>81</v>
       </c>
       <c r="B7" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C7" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="D7" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="E7" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="F7">
         <v>1.41</v>
@@ -2483,10 +2513,10 @@
         <v>6.2</v>
       </c>
       <c r="I7">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="J7">
-        <v>4.6</v>
+        <v>3.85</v>
       </c>
       <c r="K7">
         <v>8.199999999999999</v>
@@ -2525,7 +2555,7 @@
         <v>1.13</v>
       </c>
       <c r="W7">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="X7">
         <v>1000</v>
@@ -2696,7 +2726,7 @@
         <v>0</v>
       </c>
       <c r="CB7" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8" spans="1:80">
@@ -2704,258 +2734,258 @@
         <v>85</v>
       </c>
       <c r="B8" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C8" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="D8" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="E8" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="F8">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="G8">
         <v>1000</v>
       </c>
       <c r="H8">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="I8">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J8">
-        <v>1.04</v>
+        <v>1.09</v>
       </c>
       <c r="K8">
-        <v>280</v>
+        <v>300</v>
       </c>
       <c r="L8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N8">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="P8">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="Q8">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="R8">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S8">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="T8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ8">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA8">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB8" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9" spans="1:80">
       <c r="A9" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="B9" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C9" t="s">
         <v>117</v>
       </c>
       <c r="D9" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="E9" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="F9">
         <v>1.04</v>
@@ -2973,733 +3003,733 @@
         <v>1.04</v>
       </c>
       <c r="K9">
-        <v>310</v>
+        <v>240</v>
       </c>
       <c r="L9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N9">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O9">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="P9">
-        <v>1.04</v>
+        <v>1.24</v>
       </c>
       <c r="Q9">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="R9">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="S9">
-        <v>0</v>
+        <v>1.12</v>
       </c>
       <c r="T9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ9">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA9">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB9" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="10" spans="1:80">
       <c r="A10" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="B10" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C10" t="s">
         <v>117</v>
       </c>
       <c r="D10" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="E10" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="F10">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="G10">
         <v>1000</v>
       </c>
       <c r="H10">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="I10">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J10">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K10">
-        <v>210</v>
+        <v>410</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P10">
         <v>1.24</v>
       </c>
       <c r="Q10">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ10">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA10">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB10" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="11" spans="1:80">
       <c r="A11" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="B11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C11" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D11" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="E11" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="F11">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="G11">
         <v>1000</v>
       </c>
       <c r="H11">
-        <v>1.35</v>
+        <v>1.08</v>
       </c>
       <c r="I11">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J11">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K11">
-        <v>410</v>
+        <v>230</v>
       </c>
       <c r="L11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N11">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="O11">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="P11">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="Q11">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="R11">
-        <v>0</v>
+        <v>1.18</v>
       </c>
       <c r="S11">
-        <v>0</v>
+        <v>1.24</v>
       </c>
       <c r="T11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="W11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="X11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA11">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="12" spans="1:80">
       <c r="A12" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="B12" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C12" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="E12" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="F12">
-        <v>2.02</v>
+        <v>1.04</v>
       </c>
       <c r="G12">
-        <v>2.74</v>
+        <v>1000</v>
       </c>
       <c r="H12">
-        <v>2.96</v>
+        <v>1.04</v>
       </c>
       <c r="I12">
-        <v>4.5</v>
+        <v>1000</v>
       </c>
       <c r="J12">
-        <v>3.1</v>
+        <v>1.04</v>
       </c>
       <c r="K12">
-        <v>6</v>
+        <v>280</v>
       </c>
       <c r="L12">
         <v>0</v>
@@ -3714,10 +3744,10 @@
         <v>0</v>
       </c>
       <c r="P12">
-        <v>1.72</v>
+        <v>1.1</v>
       </c>
       <c r="Q12">
-        <v>1.83</v>
+        <v>1.01</v>
       </c>
       <c r="R12">
         <v>0</v>
@@ -3906,24 +3936,24 @@
         <v>0</v>
       </c>
       <c r="CB12" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="13" spans="1:80">
       <c r="A13" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="B13" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C13" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D13" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="E13" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="F13">
         <v>1.04</v>
@@ -3941,7 +3971,7 @@
         <v>1.04</v>
       </c>
       <c r="K13">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="L13">
         <v>0</v>
@@ -3956,7 +3986,7 @@
         <v>0</v>
       </c>
       <c r="P13">
-        <v>1.07</v>
+        <v>1.24</v>
       </c>
       <c r="Q13">
         <v>1.01</v>
@@ -4148,42 +4178,42 @@
         <v>0</v>
       </c>
       <c r="CB13" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="14" spans="1:80">
       <c r="A14" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="B14" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C14" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D14" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="E14" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="F14">
-        <v>3.35</v>
+        <v>1.04</v>
       </c>
       <c r="G14">
-        <v>5.2</v>
+        <v>1000</v>
       </c>
       <c r="H14">
-        <v>1.94</v>
+        <v>1.04</v>
       </c>
       <c r="I14">
-        <v>2.6</v>
+        <v>1000</v>
       </c>
       <c r="J14">
-        <v>3.05</v>
+        <v>1.04</v>
       </c>
       <c r="K14">
-        <v>5.4</v>
+        <v>310</v>
       </c>
       <c r="L14">
         <v>0</v>
@@ -4198,10 +4228,10 @@
         <v>0</v>
       </c>
       <c r="P14">
-        <v>1.69</v>
+        <v>1.04</v>
       </c>
       <c r="Q14">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="R14">
         <v>0</v>
@@ -4390,556 +4420,556 @@
         <v>0</v>
       </c>
       <c r="CB14" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="15" spans="1:80">
       <c r="A15" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="B15" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C15" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D15" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="E15" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="F15">
-        <v>1.38</v>
+        <v>1.04</v>
       </c>
       <c r="G15">
-        <v>1.54</v>
+        <v>1000</v>
       </c>
       <c r="H15">
+        <v>1.35</v>
+      </c>
+      <c r="I15">
+        <v>1000</v>
+      </c>
+      <c r="J15">
         <v>1.04</v>
       </c>
-      <c r="I15">
-        <v>17</v>
-      </c>
-      <c r="J15">
-        <v>4.5</v>
-      </c>
       <c r="K15">
-        <v>950</v>
+        <v>410</v>
       </c>
       <c r="L15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N15">
-        <v>2.24</v>
+        <v>0</v>
       </c>
       <c r="O15">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="P15">
-        <v>2.24</v>
+        <v>1.07</v>
       </c>
       <c r="Q15">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="R15">
-        <v>1.49</v>
+        <v>0</v>
       </c>
       <c r="S15">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="T15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V15">
-        <v>1.06</v>
+        <v>0</v>
       </c>
       <c r="W15">
-        <v>2.84</v>
+        <v>0</v>
       </c>
       <c r="X15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ15">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA15">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB15" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="16" spans="1:80">
       <c r="A16" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="B16" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C16" t="s">
         <v>121</v>
       </c>
       <c r="D16" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="E16" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="F16">
-        <v>5.7</v>
+        <v>2.02</v>
       </c>
       <c r="G16">
-        <v>7</v>
+        <v>2.74</v>
       </c>
       <c r="H16">
-        <v>1.62</v>
+        <v>2.96</v>
       </c>
       <c r="I16">
-        <v>1.67</v>
+        <v>4.5</v>
       </c>
       <c r="J16">
-        <v>3.9</v>
+        <v>3.1</v>
       </c>
       <c r="K16">
-        <v>4.8</v>
+        <v>6</v>
       </c>
       <c r="L16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M16">
-        <v>1.04</v>
+        <v>0</v>
       </c>
       <c r="N16">
-        <v>3.7</v>
+        <v>0</v>
       </c>
       <c r="O16">
-        <v>1.28</v>
+        <v>0</v>
       </c>
       <c r="P16">
-        <v>1.93</v>
+        <v>1.72</v>
       </c>
       <c r="Q16">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="R16">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S16">
-        <v>3.05</v>
+        <v>0</v>
       </c>
       <c r="T16">
-        <v>1.87</v>
+        <v>0</v>
       </c>
       <c r="U16">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="V16">
-        <v>2.48</v>
+        <v>0</v>
       </c>
       <c r="W16">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ16">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA16">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB16" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="17" spans="1:80">
       <c r="A17" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="B17" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C17" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="D17" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="E17" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="F17">
-        <v>8.6</v>
+        <v>1.04</v>
       </c>
       <c r="G17">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="H17">
-        <v>1.51</v>
+        <v>1.04</v>
       </c>
       <c r="I17">
-        <v>1.52</v>
+        <v>1000</v>
       </c>
       <c r="J17">
-        <v>4.3</v>
+        <v>1.04</v>
       </c>
       <c r="K17">
-        <v>4.5</v>
+        <v>300</v>
       </c>
       <c r="L17">
         <v>0</v>
       </c>
       <c r="M17">
-        <v>1.08</v>
+        <v>0</v>
       </c>
       <c r="N17">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O17">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="P17">
-        <v>1.85</v>
+        <v>1.07</v>
       </c>
       <c r="Q17">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="R17">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="S17">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="T17">
-        <v>2.3</v>
+        <v>0</v>
       </c>
       <c r="U17">
-        <v>1.72</v>
+        <v>0</v>
       </c>
       <c r="V17">
         <v>0</v>
@@ -4948,210 +4978,210 @@
         <v>0</v>
       </c>
       <c r="X17">
-        <v>14.5</v>
+        <v>0</v>
       </c>
       <c r="Y17">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="Z17">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="AA17">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AB17">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="AC17">
-        <v>17</v>
+        <v>0</v>
       </c>
       <c r="AD17">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AE17">
-        <v>19</v>
+        <v>0</v>
       </c>
       <c r="AF17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG17">
-        <v>46</v>
+        <v>0</v>
       </c>
       <c r="AH17">
-        <v>36</v>
+        <v>0</v>
       </c>
       <c r="AI17">
-        <v>280</v>
+        <v>0</v>
       </c>
       <c r="AJ17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO17">
-        <v>15</v>
+        <v>0</v>
       </c>
       <c r="AP17">
-        <v>11.5</v>
+        <v>0</v>
       </c>
       <c r="AQ17">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="AR17">
-        <v>6.8</v>
+        <v>0</v>
       </c>
       <c r="AS17">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="AT17">
-        <v>16.5</v>
+        <v>0</v>
       </c>
       <c r="AU17">
-        <v>8.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="AV17">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AW17">
-        <v>15.5</v>
+        <v>0</v>
       </c>
       <c r="AX17">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AY17">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AZ17">
-        <v>19.5</v>
+        <v>0</v>
       </c>
       <c r="BA17">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="BB17">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BC17">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BD17">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BE17">
-        <v>6.4</v>
+        <v>0</v>
       </c>
       <c r="BF17">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BG17">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="BH17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI17">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK17">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM17">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO17">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ17">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS17">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU17">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW17">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY17">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ17">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA17">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB17" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="18" spans="1:80">
       <c r="A18" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="B18" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C18" t="s">
         <v>122</v>
       </c>
       <c r="D18" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="E18" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="F18">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="G18">
-        <v>3.9</v>
+        <v>5.2</v>
       </c>
       <c r="H18">
-        <v>2.22</v>
+        <v>1.94</v>
       </c>
       <c r="I18">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="J18">
-        <v>3.4</v>
+        <v>3.05</v>
       </c>
       <c r="K18">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="L18">
         <v>0</v>
@@ -5166,10 +5196,10 @@
         <v>0</v>
       </c>
       <c r="P18">
-        <v>1.91</v>
+        <v>1.76</v>
       </c>
       <c r="Q18">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="R18">
         <v>0</v>
@@ -5358,556 +5388,556 @@
         <v>0</v>
       </c>
       <c r="CB18" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="19" spans="1:80">
       <c r="A19" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="B19" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C19" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D19" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="E19" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="F19">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="G19">
-        <v>1.61</v>
+        <v>1.54</v>
       </c>
       <c r="H19">
-        <v>5.3</v>
+        <v>1.04</v>
       </c>
       <c r="I19">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="J19">
-        <v>2.62</v>
+        <v>4.5</v>
       </c>
       <c r="K19">
-        <v>8.6</v>
+        <v>950</v>
       </c>
       <c r="L19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N19">
-        <v>0</v>
+        <v>2.24</v>
       </c>
       <c r="O19">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="P19">
+        <v>2.24</v>
+      </c>
+      <c r="Q19">
+        <v>1.6</v>
+      </c>
+      <c r="R19">
+        <v>1.49</v>
+      </c>
+      <c r="S19">
         <v>2.5</v>
       </c>
-      <c r="Q19">
-        <v>1.45</v>
-      </c>
-      <c r="R19">
-        <v>0</v>
-      </c>
-      <c r="S19">
-        <v>0</v>
-      </c>
       <c r="T19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V19">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W19">
-        <v>0</v>
+        <v>2.84</v>
       </c>
       <c r="X19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ19">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA19">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB19" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="20" spans="1:80">
       <c r="A20" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="B20" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C20" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D20" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="E20" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="F20">
+        <v>5.7</v>
+      </c>
+      <c r="G20">
+        <v>7</v>
+      </c>
+      <c r="H20">
+        <v>1.62</v>
+      </c>
+      <c r="I20">
+        <v>1.67</v>
+      </c>
+      <c r="J20">
+        <v>3.9</v>
+      </c>
+      <c r="K20">
+        <v>4.5</v>
+      </c>
+      <c r="L20">
+        <v>1.01</v>
+      </c>
+      <c r="M20">
+        <v>1.04</v>
+      </c>
+      <c r="N20">
+        <v>3.7</v>
+      </c>
+      <c r="O20">
+        <v>1.28</v>
+      </c>
+      <c r="P20">
         <v>1.93</v>
       </c>
-      <c r="G20">
-        <v>2.12</v>
-      </c>
-      <c r="H20">
-        <v>3.4</v>
-      </c>
-      <c r="I20">
-        <v>4.4</v>
-      </c>
-      <c r="J20">
-        <v>4</v>
-      </c>
-      <c r="K20">
-        <v>5.4</v>
-      </c>
-      <c r="L20">
-        <v>0</v>
-      </c>
-      <c r="M20">
-        <v>0</v>
-      </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
-      <c r="O20">
-        <v>0</v>
-      </c>
-      <c r="P20">
-        <v>1.25</v>
-      </c>
       <c r="Q20">
-        <v>1.51</v>
+        <v>1.84</v>
       </c>
       <c r="R20">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="S20">
-        <v>0</v>
+        <v>3.05</v>
       </c>
       <c r="T20">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U20">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="V20">
-        <v>0</v>
+        <v>2.48</v>
       </c>
       <c r="W20">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="X20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ20">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA20">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB20" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="21" spans="1:80">
       <c r="A21" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="B21" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C21" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="D21" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="E21" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="F21">
-        <v>1.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="G21">
-        <v>1.6</v>
+        <v>9</v>
       </c>
       <c r="H21">
-        <v>5.3</v>
+        <v>1.51</v>
       </c>
       <c r="I21">
-        <v>75</v>
+        <v>1.52</v>
       </c>
       <c r="J21">
-        <v>4.7</v>
+        <v>4.3</v>
       </c>
       <c r="K21">
-        <v>6.2</v>
+        <v>4.5</v>
       </c>
       <c r="L21">
         <v>0</v>
       </c>
       <c r="M21">
-        <v>0</v>
+        <v>1.08</v>
       </c>
       <c r="N21">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O21">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="P21">
-        <v>2.08</v>
+        <v>1.86</v>
       </c>
       <c r="Q21">
-        <v>1.53</v>
+        <v>2.1</v>
       </c>
       <c r="R21">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="S21">
-        <v>0</v>
+        <v>3.85</v>
       </c>
       <c r="T21">
-        <v>0</v>
+        <v>2.3</v>
       </c>
       <c r="U21">
-        <v>0</v>
+        <v>1.73</v>
       </c>
       <c r="V21">
         <v>0</v>
@@ -5916,210 +5946,210 @@
         <v>0</v>
       </c>
       <c r="X21">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="Y21">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="Z21">
-        <v>0</v>
+        <v>7.8</v>
       </c>
       <c r="AA21">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AB21">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AC21">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AD21">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="AE21">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="AF21">
-        <v>0</v>
+        <v>95</v>
       </c>
       <c r="AG21">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="AH21">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AI21">
-        <v>0</v>
+        <v>65</v>
       </c>
       <c r="AJ21">
-        <v>0</v>
+        <v>420</v>
       </c>
       <c r="AK21">
-        <v>0</v>
+        <v>210</v>
       </c>
       <c r="AL21">
-        <v>0</v>
+        <v>180</v>
       </c>
       <c r="AM21">
-        <v>0</v>
+        <v>250</v>
       </c>
       <c r="AN21">
-        <v>0</v>
+        <v>350</v>
       </c>
       <c r="AO21">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AP21">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AQ21">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AR21">
-        <v>0</v>
+        <v>7.2</v>
       </c>
       <c r="AS21">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="AT21">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="AU21">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AV21">
-        <v>0</v>
+        <v>9.6</v>
       </c>
       <c r="AW21">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AX21">
-        <v>0</v>
+        <v>32</v>
       </c>
       <c r="AY21">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="AZ21">
-        <v>0</v>
+        <v>19.5</v>
       </c>
       <c r="BA21">
-        <v>0</v>
+        <v>28</v>
       </c>
       <c r="BB21">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BC21">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BD21">
-        <v>0</v>
+        <v>13</v>
       </c>
       <c r="BE21">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BF21">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="BG21">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="BH21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ21">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA21">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB21" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="22" spans="1:80">
       <c r="A22" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="B22" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C22" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D22" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="E22" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="F22">
-        <v>1.37</v>
+        <v>1.69</v>
       </c>
       <c r="G22">
-        <v>1.96</v>
+        <v>3.9</v>
       </c>
       <c r="H22">
-        <v>4.6</v>
+        <v>1.36</v>
       </c>
       <c r="I22">
-        <v>60</v>
+        <v>2.5</v>
       </c>
       <c r="J22">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K22">
-        <v>3.95</v>
+        <v>950</v>
       </c>
       <c r="L22">
         <v>0</v>
@@ -6134,10 +6164,10 @@
         <v>0</v>
       </c>
       <c r="P22">
-        <v>1.25</v>
+        <v>1.95</v>
       </c>
       <c r="Q22">
-        <v>1.02</v>
+        <v>1.9</v>
       </c>
       <c r="R22">
         <v>0</v>
@@ -6326,42 +6356,42 @@
         <v>0</v>
       </c>
       <c r="CB22" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="23" spans="1:80">
       <c r="A23" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="B23" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C23" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D23" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="E23" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="F23">
-        <v>1.09</v>
+        <v>1.04</v>
       </c>
       <c r="G23">
-        <v>1.49</v>
+        <v>1000</v>
       </c>
       <c r="H23">
-        <v>1.1</v>
+        <v>1.04</v>
       </c>
       <c r="I23">
         <v>1000</v>
       </c>
       <c r="J23">
-        <v>4.7</v>
+        <v>1.06</v>
       </c>
       <c r="K23">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L23">
         <v>0</v>
@@ -6376,10 +6406,10 @@
         <v>0</v>
       </c>
       <c r="P23">
-        <v>2.7</v>
+        <v>2.56</v>
       </c>
       <c r="Q23">
-        <v>1.46</v>
+        <v>1.45</v>
       </c>
       <c r="R23">
         <v>0</v>
@@ -6568,42 +6598,42 @@
         <v>0</v>
       </c>
       <c r="CB23" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="24" spans="1:80">
       <c r="A24" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="B24" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C24" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D24" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="E24" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
       <c r="F24">
-        <v>1.14</v>
+        <v>1.52</v>
       </c>
       <c r="G24">
-        <v>1.25</v>
+        <v>1.6</v>
       </c>
       <c r="H24">
-        <v>12</v>
+        <v>5.4</v>
       </c>
       <c r="I24">
-        <v>1000</v>
+        <v>6.6</v>
       </c>
       <c r="J24">
-        <v>6.4</v>
+        <v>4.7</v>
       </c>
       <c r="K24">
-        <v>26</v>
+        <v>5.2</v>
       </c>
       <c r="L24">
         <v>0</v>
@@ -6618,10 +6648,10 @@
         <v>0</v>
       </c>
       <c r="P24">
-        <v>2.6</v>
+        <v>2.08</v>
       </c>
       <c r="Q24">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="R24">
         <v>0</v>
@@ -6810,42 +6840,42 @@
         <v>0</v>
       </c>
       <c r="CB24" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="25" spans="1:80">
       <c r="A25" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B25" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C25" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D25" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="E25" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="F25">
-        <v>1.56</v>
+        <v>1.08</v>
       </c>
       <c r="G25">
-        <v>1.69</v>
+        <v>2.08</v>
       </c>
       <c r="H25">
-        <v>4.6</v>
+        <v>2</v>
       </c>
       <c r="I25">
-        <v>8</v>
+        <v>42</v>
       </c>
       <c r="J25">
-        <v>3.95</v>
+        <v>2</v>
       </c>
       <c r="K25">
-        <v>4.7</v>
+        <v>950</v>
       </c>
       <c r="L25">
         <v>0</v>
@@ -6860,10 +6890,10 @@
         <v>0</v>
       </c>
       <c r="P25">
-        <v>2.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q25">
-        <v>1.6</v>
+        <v>1.03</v>
       </c>
       <c r="R25">
         <v>0</v>
@@ -7052,240 +7082,240 @@
         <v>0</v>
       </c>
       <c r="CB25" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="26" spans="1:80">
       <c r="A26" t="s">
-        <v>101</v>
+        <v>98</v>
       </c>
       <c r="B26" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C26" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D26" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="E26" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="F26">
+        <v>1.56</v>
+      </c>
+      <c r="G26">
         <v>1.69</v>
       </c>
-      <c r="G26">
-        <v>1.87</v>
-      </c>
       <c r="H26">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="I26">
-        <v>5.7</v>
+        <v>10.5</v>
       </c>
       <c r="J26">
-        <v>3.45</v>
+        <v>3.85</v>
       </c>
       <c r="K26">
-        <v>6.2</v>
+        <v>4.7</v>
       </c>
       <c r="L26">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M26">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="N26">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="O26">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="P26">
-        <v>2.6</v>
+        <v>2.24</v>
       </c>
       <c r="Q26">
-        <v>1.44</v>
+        <v>1.6</v>
       </c>
       <c r="R26">
-        <v>1.68</v>
+        <v>0</v>
       </c>
       <c r="S26">
-        <v>2.12</v>
+        <v>0</v>
       </c>
       <c r="T26">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U26">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V26">
-        <v>1.21</v>
+        <v>0</v>
       </c>
       <c r="W26">
-        <v>2.14</v>
+        <v>0</v>
       </c>
       <c r="X26">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y26">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z26">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA26">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB26">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC26">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD26">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE26">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF26">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG26">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH26">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI26">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ26">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK26">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL26">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM26">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN26">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO26">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP26">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ26">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR26">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS26">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT26">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU26">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV26">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW26">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX26">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY26">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ26">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA26">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB26">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC26">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD26">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE26">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF26">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG26">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH26">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI26">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ26">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK26">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL26">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM26">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN26">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO26">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP26">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ26">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR26">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS26">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT26">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU26">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV26">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW26">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX26">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY26">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ26">
         <v>0</v>
@@ -7294,42 +7324,42 @@
         <v>0</v>
       </c>
       <c r="CB26" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="27" spans="1:80">
       <c r="A27" t="s">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="B27" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C27" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D27" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="E27" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
       <c r="F27">
-        <v>2.92</v>
+        <v>1.74</v>
       </c>
       <c r="G27">
-        <v>3.65</v>
+        <v>1.94</v>
       </c>
       <c r="H27">
-        <v>2.24</v>
+        <v>4.8</v>
       </c>
       <c r="I27">
-        <v>2.66</v>
+        <v>60</v>
       </c>
       <c r="J27">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K27">
-        <v>3.6</v>
+        <v>3.9</v>
       </c>
       <c r="L27">
         <v>0</v>
@@ -7344,10 +7374,10 @@
         <v>0</v>
       </c>
       <c r="P27">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="Q27">
-        <v>1.87</v>
+        <v>1.02</v>
       </c>
       <c r="R27">
         <v>0</v>
@@ -7536,72 +7566,72 @@
         <v>0</v>
       </c>
       <c r="CB27" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="28" spans="1:80">
       <c r="A28" t="s">
-        <v>103</v>
+        <v>100</v>
       </c>
       <c r="B28" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C28" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="D28" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="E28" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="F28">
-        <v>2.24</v>
+        <v>1.38</v>
       </c>
       <c r="G28">
-        <v>2.28</v>
+        <v>1.46</v>
       </c>
       <c r="H28">
-        <v>4.1</v>
+        <v>7.4</v>
       </c>
       <c r="I28">
-        <v>4.3</v>
+        <v>9</v>
       </c>
       <c r="J28">
-        <v>3.1</v>
+        <v>5.2</v>
       </c>
       <c r="K28">
-        <v>3.2</v>
+        <v>6.2</v>
       </c>
       <c r="L28">
         <v>0</v>
       </c>
       <c r="M28">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="N28">
-        <v>2.32</v>
+        <v>0</v>
       </c>
       <c r="O28">
-        <v>1.69</v>
+        <v>0</v>
       </c>
       <c r="P28">
-        <v>1.44</v>
+        <v>2.7</v>
       </c>
       <c r="Q28">
-        <v>3.2</v>
+        <v>1.46</v>
       </c>
       <c r="R28">
-        <v>1.15</v>
+        <v>0</v>
       </c>
       <c r="S28">
-        <v>7.2</v>
+        <v>0</v>
       </c>
       <c r="T28">
-        <v>2.5</v>
+        <v>0</v>
       </c>
       <c r="U28">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V28">
         <v>0</v>
@@ -7610,210 +7640,210 @@
         <v>0</v>
       </c>
       <c r="X28">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="Y28">
-        <v>9.800000000000001</v>
+        <v>0</v>
       </c>
       <c r="Z28">
-        <v>29</v>
+        <v>0</v>
       </c>
       <c r="AA28">
-        <v>140</v>
+        <v>0</v>
       </c>
       <c r="AB28">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="AC28">
-        <v>10.5</v>
+        <v>0</v>
       </c>
       <c r="AD28">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="AE28">
-        <v>100</v>
+        <v>0</v>
       </c>
       <c r="AF28">
-        <v>21</v>
+        <v>0</v>
       </c>
       <c r="AG28">
-        <v>32</v>
+        <v>0</v>
       </c>
       <c r="AH28">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AI28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ28">
-        <v>38</v>
+        <v>0</v>
       </c>
       <c r="AK28">
-        <v>44</v>
+        <v>0</v>
       </c>
       <c r="AL28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN28">
-        <v>48</v>
+        <v>0</v>
       </c>
       <c r="AO28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP28">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AQ28">
-        <v>8.6</v>
+        <v>0</v>
       </c>
       <c r="AR28">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AS28">
-        <v>5.9</v>
+        <v>0</v>
       </c>
       <c r="AT28">
-        <v>5.7</v>
+        <v>0</v>
       </c>
       <c r="AU28">
-        <v>6.6</v>
+        <v>0</v>
       </c>
       <c r="AV28">
-        <v>17.5</v>
+        <v>0</v>
       </c>
       <c r="AW28">
-        <v>5.8</v>
+        <v>0</v>
       </c>
       <c r="AX28">
-        <v>9.4</v>
+        <v>0</v>
       </c>
       <c r="AY28">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="AZ28">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BA28">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BB28">
-        <v>5.3</v>
+        <v>0</v>
       </c>
       <c r="BC28">
-        <v>5.4</v>
+        <v>0</v>
       </c>
       <c r="BD28">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BE28">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="BF28">
-        <v>23</v>
+        <v>0</v>
       </c>
       <c r="BG28">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="BH28">
-        <v>2.56</v>
+        <v>0</v>
       </c>
       <c r="BI28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ28">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA28">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB28" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="29" spans="1:80">
       <c r="A29" t="s">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="B29" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C29" t="s">
         <v>124</v>
       </c>
       <c r="D29" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="E29" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="F29">
-        <v>1.45</v>
+        <v>1.14</v>
       </c>
       <c r="G29">
-        <v>1.81</v>
+        <v>1.25</v>
       </c>
       <c r="H29">
-        <v>4.2</v>
+        <v>12</v>
       </c>
       <c r="I29">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="J29">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="K29">
-        <v>14</v>
+        <v>26</v>
       </c>
       <c r="L29">
         <v>0</v>
@@ -7828,10 +7858,10 @@
         <v>0</v>
       </c>
       <c r="P29">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="Q29">
-        <v>1.24</v>
+        <v>1.32</v>
       </c>
       <c r="R29">
         <v>0</v>
@@ -8020,240 +8050,240 @@
         <v>0</v>
       </c>
       <c r="CB29" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="30" spans="1:80">
       <c r="A30" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="B30" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C30" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="D30" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="E30" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="F30">
-        <v>1.53</v>
+        <v>1.69</v>
       </c>
       <c r="G30">
-        <v>1.73</v>
+        <v>1.87</v>
       </c>
       <c r="H30">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="I30">
-        <v>8.199999999999999</v>
+        <v>5.7</v>
       </c>
       <c r="J30">
-        <v>4.5</v>
+        <v>3.45</v>
       </c>
       <c r="K30">
-        <v>8.4</v>
+        <v>6.2</v>
       </c>
       <c r="L30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N30">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="O30">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="P30">
-        <v>3</v>
+        <v>2.6</v>
       </c>
       <c r="Q30">
-        <v>1.35</v>
+        <v>1.44</v>
       </c>
       <c r="R30">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="S30">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="T30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V30">
-        <v>0</v>
+        <v>1.21</v>
       </c>
       <c r="W30">
-        <v>0</v>
+        <v>2.14</v>
       </c>
       <c r="X30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX30">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY30">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ30">
         <v>0</v>
@@ -8262,42 +8292,42 @@
         <v>0</v>
       </c>
       <c r="CB30" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="31" spans="1:80">
       <c r="A31" t="s">
-        <v>91</v>
+        <v>103</v>
       </c>
       <c r="B31" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C31" t="s">
         <v>125</v>
       </c>
       <c r="D31" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="E31" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="F31">
-        <v>1.46</v>
+        <v>2.92</v>
       </c>
       <c r="G31">
-        <v>1.72</v>
+        <v>3.05</v>
       </c>
       <c r="H31">
-        <v>6.6</v>
+        <v>2.52</v>
       </c>
       <c r="I31">
-        <v>21</v>
+        <v>2.72</v>
       </c>
       <c r="J31">
-        <v>2.28</v>
+        <v>3.45</v>
       </c>
       <c r="K31">
-        <v>6.2</v>
+        <v>3.6</v>
       </c>
       <c r="L31">
         <v>0</v>
@@ -8312,7 +8342,7 @@
         <v>0</v>
       </c>
       <c r="P31">
-        <v>1.54</v>
+        <v>1.88</v>
       </c>
       <c r="Q31">
         <v>1.01</v>
@@ -8504,189 +8534,189 @@
         <v>0</v>
       </c>
       <c r="CB31" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="32" spans="1:80">
       <c r="A32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="B32" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C32" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D32" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="E32" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="F32">
-        <v>1.86</v>
+        <v>2.24</v>
       </c>
       <c r="G32">
-        <v>2.08</v>
+        <v>2.28</v>
       </c>
       <c r="H32">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I32">
-        <v>5.4</v>
+        <v>4.3</v>
       </c>
       <c r="J32">
-        <v>3.4</v>
+        <v>3.1</v>
       </c>
       <c r="K32">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="L32">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M32">
-        <v>1.06</v>
+        <v>1.15</v>
       </c>
       <c r="N32">
-        <v>2.8</v>
+        <v>2.36</v>
       </c>
       <c r="O32">
-        <v>1.41</v>
+        <v>1.66</v>
       </c>
       <c r="P32">
-        <v>1.64</v>
+        <v>1.44</v>
       </c>
       <c r="Q32">
-        <v>2.22</v>
+        <v>3.2</v>
       </c>
       <c r="R32">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="S32">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="T32">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="U32">
-        <v>1.01</v>
+        <v>1.62</v>
       </c>
       <c r="V32">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="W32">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="X32">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="Y32">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="Z32">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA32">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB32">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="AC32">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="AD32">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AE32">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AF32">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AG32">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH32">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AI32">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AJ32">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AK32">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL32">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AM32">
-        <v>1000</v>
+        <v>390</v>
       </c>
       <c r="AN32">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO32">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AP32">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AQ32">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AR32">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AS32">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AT32">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AU32">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AV32">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AW32">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AX32">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AY32">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AZ32">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BA32">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BB32">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BC32">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BD32">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BE32">
-        <v>1.01</v>
+        <v>110</v>
       </c>
       <c r="BF32">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BG32">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BH32">
-        <v>1000</v>
+        <v>2.56</v>
       </c>
       <c r="BI32">
         <v>1.01</v>
@@ -8746,42 +8776,42 @@
         <v>1.01</v>
       </c>
       <c r="CB32" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="33" spans="1:80">
       <c r="A33" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B33" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C33" t="s">
         <v>126</v>
       </c>
       <c r="D33" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="E33" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="F33">
-        <v>3.45</v>
+        <v>1.45</v>
       </c>
       <c r="G33">
-        <v>4.7</v>
+        <v>1.8</v>
       </c>
       <c r="H33">
-        <v>2.12</v>
+        <v>4.2</v>
       </c>
       <c r="I33">
-        <v>2.28</v>
+        <v>15.5</v>
       </c>
       <c r="J33">
-        <v>1.95</v>
+        <v>4.1</v>
       </c>
       <c r="K33">
-        <v>4.2</v>
+        <v>14</v>
       </c>
       <c r="L33">
         <v>0</v>
@@ -8796,10 +8826,10 @@
         <v>0</v>
       </c>
       <c r="P33">
-        <v>1.25</v>
+        <v>3</v>
       </c>
       <c r="Q33">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="R33">
         <v>0</v>
@@ -8988,42 +9018,42 @@
         <v>0</v>
       </c>
       <c r="CB33" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="34" spans="1:80">
       <c r="A34" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B34" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C34" t="s">
         <v>126</v>
       </c>
       <c r="D34" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="E34" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="F34">
-        <v>1.45</v>
+        <v>1.53</v>
       </c>
       <c r="G34">
-        <v>1.49</v>
+        <v>1.73</v>
       </c>
       <c r="H34">
-        <v>8</v>
+        <v>4.4</v>
       </c>
       <c r="I34">
-        <v>10</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="J34">
-        <v>4.8</v>
+        <v>4.5</v>
       </c>
       <c r="K34">
-        <v>5.1</v>
+        <v>8.4</v>
       </c>
       <c r="L34">
         <v>0</v>
@@ -9038,10 +9068,10 @@
         <v>0</v>
       </c>
       <c r="P34">
-        <v>1.25</v>
+        <v>3</v>
       </c>
       <c r="Q34">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="R34">
         <v>0</v>
@@ -9230,42 +9260,42 @@
         <v>0</v>
       </c>
       <c r="CB34" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="35" spans="1:80">
       <c r="A35" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="B35" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C35" t="s">
         <v>127</v>
       </c>
       <c r="D35" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="E35" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="F35">
-        <v>4.3</v>
+        <v>1.46</v>
       </c>
       <c r="G35">
-        <v>5.4</v>
+        <v>1.77</v>
       </c>
       <c r="H35">
-        <v>1.83</v>
+        <v>6.6</v>
       </c>
       <c r="I35">
-        <v>1.93</v>
+        <v>1000</v>
       </c>
       <c r="J35">
-        <v>3.65</v>
+        <v>2.28</v>
       </c>
       <c r="K35">
-        <v>3.95</v>
+        <v>6.2</v>
       </c>
       <c r="L35">
         <v>0</v>
@@ -9280,10 +9310,10 @@
         <v>0</v>
       </c>
       <c r="P35">
-        <v>1.85</v>
+        <v>1.54</v>
       </c>
       <c r="Q35">
-        <v>1.98</v>
+        <v>2.12</v>
       </c>
       <c r="R35">
         <v>0</v>
@@ -9472,186 +9502,186 @@
         <v>0</v>
       </c>
       <c r="CB35" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="36" spans="1:80">
       <c r="A36" t="s">
-        <v>94</v>
+        <v>106</v>
       </c>
       <c r="B36" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C36" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="D36" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="E36" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="F36">
-        <v>1.98</v>
+        <v>1.87</v>
       </c>
       <c r="G36">
-        <v>2</v>
+        <v>2.18</v>
       </c>
       <c r="H36">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="I36">
-        <v>4.4</v>
+        <v>5.4</v>
       </c>
       <c r="J36">
-        <v>3.75</v>
+        <v>2.8</v>
       </c>
       <c r="K36">
-        <v>3.85</v>
+        <v>3.7</v>
       </c>
       <c r="L36">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M36">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N36">
-        <v>3.8</v>
+        <v>2.34</v>
       </c>
       <c r="O36">
-        <v>1.33</v>
+        <v>1.41</v>
       </c>
       <c r="P36">
-        <v>1.92</v>
+        <v>1.26</v>
       </c>
       <c r="Q36">
-        <v>2.02</v>
+        <v>1.68</v>
       </c>
       <c r="R36">
-        <v>1.37</v>
+        <v>1.14</v>
       </c>
       <c r="S36">
-        <v>3.55</v>
+        <v>4</v>
       </c>
       <c r="T36">
-        <v>1.85</v>
+        <v>1.01</v>
       </c>
       <c r="U36">
-        <v>2.1</v>
+        <v>1.01</v>
       </c>
       <c r="V36">
-        <v>0</v>
+        <v>1.22</v>
       </c>
       <c r="W36">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="X36">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="Y36">
-        <v>16</v>
+        <v>1000</v>
       </c>
       <c r="Z36">
-        <v>34</v>
+        <v>1000</v>
       </c>
       <c r="AA36">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="AB36">
-        <v>9.199999999999999</v>
+        <v>1000</v>
       </c>
       <c r="AC36">
-        <v>8.6</v>
+        <v>1000</v>
       </c>
       <c r="AD36">
-        <v>17.5</v>
+        <v>1000</v>
       </c>
       <c r="AE36">
-        <v>60</v>
+        <v>1000</v>
       </c>
       <c r="AF36">
-        <v>12</v>
+        <v>1000</v>
       </c>
       <c r="AG36">
-        <v>10.5</v>
+        <v>1000</v>
       </c>
       <c r="AH36">
-        <v>19.5</v>
+        <v>1000</v>
       </c>
       <c r="AI36">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="AJ36">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AK36">
-        <v>22</v>
+        <v>1000</v>
       </c>
       <c r="AL36">
-        <v>40</v>
+        <v>1000</v>
       </c>
       <c r="AM36">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="AN36">
-        <v>14.5</v>
+        <v>1000</v>
       </c>
       <c r="AO36">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AP36">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="AQ36">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR36">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="AS36">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT36">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU36">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AV36">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW36">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="AX36">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AY36">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="AZ36">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BA36">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BB36">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BC36">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BD36">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BE36">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BF36">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG36">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BH36">
         <v>1000</v>
@@ -9714,428 +9744,428 @@
         <v>1.01</v>
       </c>
       <c r="CB36" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="37" spans="1:80">
       <c r="A37" t="s">
-        <v>92</v>
+        <v>107</v>
       </c>
       <c r="B37" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C37" t="s">
         <v>128</v>
       </c>
       <c r="D37" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="E37" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="F37">
-        <v>5.3</v>
+        <v>3.55</v>
       </c>
       <c r="G37">
-        <v>9.800000000000001</v>
+        <v>3.85</v>
       </c>
       <c r="H37">
-        <v>1.56</v>
+        <v>2.12</v>
       </c>
       <c r="I37">
-        <v>1.91</v>
+        <v>2.2</v>
       </c>
       <c r="J37">
-        <v>3.25</v>
+        <v>3.7</v>
       </c>
       <c r="K37">
-        <v>5.8</v>
+        <v>4.1</v>
       </c>
       <c r="L37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="M37">
-        <v>1.05</v>
+        <v>0</v>
       </c>
       <c r="N37">
-        <v>3.55</v>
+        <v>0</v>
       </c>
       <c r="O37">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="P37">
-        <v>1.74</v>
+        <v>1.25</v>
       </c>
       <c r="Q37">
-        <v>1.86</v>
+        <v>1.71</v>
       </c>
       <c r="R37">
-        <v>1.27</v>
+        <v>0</v>
       </c>
       <c r="S37">
-        <v>2.92</v>
+        <v>0</v>
       </c>
       <c r="T37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V37">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="W37">
-        <v>1.11</v>
+        <v>0</v>
       </c>
       <c r="X37">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y37">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z37">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA37">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB37">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC37">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD37">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE37">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF37">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG37">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH37">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI37">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ37">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK37">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL37">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM37">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN37">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO37">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH37">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ37">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL37">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN37">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP37">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR37">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT37">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV37">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX37">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ37">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA37">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB37" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="38" spans="1:80">
       <c r="A38" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B38" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C38" t="s">
         <v>128</v>
       </c>
       <c r="D38" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="E38" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="F38">
-        <v>6.8</v>
+        <v>1.45</v>
       </c>
       <c r="G38">
-        <v>7</v>
+        <v>1.49</v>
       </c>
       <c r="H38">
-        <v>1.57</v>
+        <v>8</v>
       </c>
       <c r="I38">
-        <v>1.59</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="J38">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="K38">
-        <v>4.5</v>
+        <v>5.4</v>
       </c>
       <c r="L38">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M38">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N38">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="O38">
         <v>1.29</v>
       </c>
       <c r="P38">
-        <v>2.1</v>
+        <v>2.04</v>
       </c>
       <c r="Q38">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="R38">
-        <v>1.42</v>
+        <v>1.39</v>
       </c>
       <c r="S38">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="T38">
-        <v>1.99</v>
+        <v>1.85</v>
       </c>
       <c r="U38">
-        <v>1.97</v>
+        <v>1.84</v>
       </c>
       <c r="V38">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="W38">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="X38">
-        <v>17.5</v>
+        <v>22</v>
       </c>
       <c r="Y38">
-        <v>8.199999999999999</v>
+        <v>32</v>
       </c>
       <c r="Z38">
+        <v>75</v>
+      </c>
+      <c r="AA38">
+        <v>350</v>
+      </c>
+      <c r="AB38">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC38">
+        <v>11.5</v>
+      </c>
+      <c r="AD38">
+        <v>32</v>
+      </c>
+      <c r="AE38">
+        <v>170</v>
+      </c>
+      <c r="AF38">
+        <v>8.6</v>
+      </c>
+      <c r="AG38">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AH38">
+        <v>34</v>
+      </c>
+      <c r="AI38">
+        <v>150</v>
+      </c>
+      <c r="AJ38">
+        <v>16</v>
+      </c>
+      <c r="AK38">
+        <v>19.5</v>
+      </c>
+      <c r="AL38">
+        <v>46</v>
+      </c>
+      <c r="AM38">
+        <v>200</v>
+      </c>
+      <c r="AN38">
+        <v>7.8</v>
+      </c>
+      <c r="AO38">
+        <v>230</v>
+      </c>
+      <c r="AP38">
+        <v>5.2</v>
+      </c>
+      <c r="AQ38">
+        <v>5.6</v>
+      </c>
+      <c r="AR38">
+        <v>6.2</v>
+      </c>
+      <c r="AS38">
+        <v>6.6</v>
+      </c>
+      <c r="AT38">
+        <v>7</v>
+      </c>
+      <c r="AU38">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AV38">
+        <v>5.6</v>
+      </c>
+      <c r="AW38">
+        <v>6.4</v>
+      </c>
+      <c r="AX38">
+        <v>7.6</v>
+      </c>
+      <c r="AY38">
         <v>8.800000000000001</v>
       </c>
-      <c r="AA38">
-        <v>13.5</v>
-      </c>
-      <c r="AB38">
-        <v>23</v>
-      </c>
-      <c r="AC38">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AD38">
-        <v>9.6</v>
-      </c>
-      <c r="AE38">
-        <v>17</v>
-      </c>
-      <c r="AF38">
-        <v>70</v>
-      </c>
-      <c r="AG38">
-        <v>27</v>
-      </c>
-      <c r="AH38">
-        <v>24</v>
-      </c>
-      <c r="AI38">
-        <v>40</v>
-      </c>
-      <c r="AJ38">
-        <v>260</v>
-      </c>
-      <c r="AK38">
-        <v>130</v>
-      </c>
-      <c r="AL38">
-        <v>120</v>
-      </c>
-      <c r="AM38">
-        <v>100</v>
-      </c>
-      <c r="AN38">
-        <v>170</v>
-      </c>
-      <c r="AO38">
-        <v>8.6</v>
-      </c>
-      <c r="AP38">
-        <v>16</v>
-      </c>
-      <c r="AQ38">
-        <v>7.8</v>
-      </c>
-      <c r="AR38">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AS38">
-        <v>12.5</v>
-      </c>
-      <c r="AT38">
-        <v>20</v>
-      </c>
-      <c r="AU38">
-        <v>9.4</v>
-      </c>
-      <c r="AV38">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AW38">
-        <v>15.5</v>
-      </c>
-      <c r="AX38">
-        <v>48</v>
-      </c>
-      <c r="AY38">
-        <v>23</v>
-      </c>
       <c r="AZ38">
-        <v>21</v>
+        <v>5.6</v>
       </c>
       <c r="BA38">
-        <v>30</v>
+        <v>6.4</v>
       </c>
       <c r="BB38">
-        <v>50</v>
+        <v>11.5</v>
       </c>
       <c r="BC38">
-        <v>40</v>
+        <v>14</v>
       </c>
       <c r="BD38">
-        <v>60</v>
+        <v>5.9</v>
       </c>
       <c r="BE38">
-        <v>70</v>
+        <v>6.4</v>
       </c>
       <c r="BF38">
-        <v>40</v>
+        <v>5.9</v>
       </c>
       <c r="BG38">
-        <v>7.8</v>
+        <v>6.6</v>
       </c>
       <c r="BH38">
         <v>1000</v>
@@ -10198,42 +10228,42 @@
         <v>1.01</v>
       </c>
       <c r="CB38" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="39" spans="1:80">
       <c r="A39" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B39" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C39" t="s">
         <v>129</v>
       </c>
       <c r="D39" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="E39" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="F39">
-        <v>1.96</v>
+        <v>4.5</v>
       </c>
       <c r="G39">
-        <v>2.16</v>
+        <v>5</v>
       </c>
       <c r="H39">
-        <v>3.15</v>
+        <v>1.86</v>
       </c>
       <c r="I39">
-        <v>3.85</v>
+        <v>1.93</v>
       </c>
       <c r="J39">
-        <v>4.2</v>
+        <v>3.65</v>
       </c>
       <c r="K39">
-        <v>5.8</v>
+        <v>3.95</v>
       </c>
       <c r="L39">
         <v>0</v>
@@ -10248,7 +10278,7 @@
         <v>0</v>
       </c>
       <c r="P39">
-        <v>3.55</v>
+        <v>1.25</v>
       </c>
       <c r="Q39">
         <v>1.01</v>
@@ -10260,10 +10290,10 @@
         <v>0</v>
       </c>
       <c r="T39">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="U39">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="V39">
         <v>0</v>
@@ -10272,112 +10302,112 @@
         <v>0</v>
       </c>
       <c r="X39">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Y39">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="Z39">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AA39">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AB39">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AC39">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AD39">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AE39">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AF39">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AG39">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AH39">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AI39">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AJ39">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AK39">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AL39">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AM39">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AN39">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AO39">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="AP39">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AQ39">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AR39">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AS39">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AT39">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AU39">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AV39">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AW39">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AX39">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AY39">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="AZ39">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BA39">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BB39">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BC39">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BD39">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BE39">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BF39">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BG39">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BH39">
         <v>0</v>
@@ -10440,72 +10470,72 @@
         <v>0</v>
       </c>
       <c r="CB39" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="40" spans="1:80">
       <c r="A40" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="B40" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C40" t="s">
         <v>129</v>
       </c>
       <c r="D40" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="E40" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="F40">
-        <v>1.81</v>
+        <v>1.99</v>
       </c>
       <c r="G40">
-        <v>1.89</v>
+        <v>2.02</v>
       </c>
       <c r="H40">
-        <v>5</v>
+        <v>4.2</v>
       </c>
       <c r="I40">
-        <v>5.8</v>
+        <v>4.4</v>
       </c>
       <c r="J40">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K40">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L40">
         <v>0</v>
       </c>
       <c r="M40">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N40">
-        <v>0</v>
+        <v>3.8</v>
       </c>
       <c r="O40">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="P40">
-        <v>1.25</v>
+        <v>1.94</v>
       </c>
       <c r="Q40">
-        <v>1.94</v>
+        <v>2.02</v>
       </c>
       <c r="R40">
-        <v>0</v>
+        <v>1.37</v>
       </c>
       <c r="S40">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T40">
-        <v>1.73</v>
+        <v>1.86</v>
       </c>
       <c r="U40">
-        <v>1.89</v>
+        <v>2.1</v>
       </c>
       <c r="V40">
         <v>0</v>
@@ -10514,483 +10544,483 @@
         <v>0</v>
       </c>
       <c r="X40">
+        <v>15</v>
+      </c>
+      <c r="Y40">
         <v>15.5</v>
       </c>
-      <c r="Y40">
-        <v>19.5</v>
-      </c>
       <c r="Z40">
-        <v>46</v>
+        <v>34</v>
       </c>
       <c r="AA40">
-        <v>150</v>
+        <v>100</v>
       </c>
       <c r="AB40">
         <v>9.199999999999999</v>
       </c>
       <c r="AC40">
-        <v>9.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD40">
-        <v>24</v>
+        <v>17.5</v>
       </c>
       <c r="AE40">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="AF40">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AG40">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH40">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="AI40">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="AJ40">
         <v>23</v>
       </c>
       <c r="AK40">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL40">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM40">
-        <v>140</v>
+        <v>110</v>
       </c>
       <c r="AN40">
+        <v>14.5</v>
+      </c>
+      <c r="AO40">
+        <v>65</v>
+      </c>
+      <c r="AP40">
+        <v>13</v>
+      </c>
+      <c r="AQ40">
+        <v>13.5</v>
+      </c>
+      <c r="AR40">
+        <v>19.5</v>
+      </c>
+      <c r="AS40">
+        <v>12</v>
+      </c>
+      <c r="AT40">
+        <v>8.4</v>
+      </c>
+      <c r="AU40">
+        <v>7.4</v>
+      </c>
+      <c r="AV40">
         <v>15.5</v>
       </c>
-      <c r="AO40">
-        <v>110</v>
-      </c>
-      <c r="AP40">
-        <v>12</v>
-      </c>
-      <c r="AQ40">
-        <v>14.5</v>
-      </c>
-      <c r="AR40">
-        <v>4.8</v>
-      </c>
-      <c r="AS40">
-        <v>5.2</v>
-      </c>
-      <c r="AT40">
-        <v>7.2</v>
-      </c>
-      <c r="AU40">
-        <v>7.6</v>
-      </c>
-      <c r="AV40">
-        <v>18</v>
-      </c>
       <c r="AW40">
-        <v>5</v>
+        <v>28</v>
       </c>
       <c r="AX40">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AY40">
-        <v>9</v>
+        <v>9.6</v>
       </c>
       <c r="AZ40">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA40">
-        <v>5.1</v>
+        <v>30</v>
       </c>
       <c r="BB40">
-        <v>17.5</v>
+        <v>19</v>
       </c>
       <c r="BC40">
         <v>18</v>
       </c>
       <c r="BD40">
-        <v>4.8</v>
+        <v>24</v>
       </c>
       <c r="BE40">
-        <v>5.2</v>
+        <v>12</v>
       </c>
       <c r="BF40">
-        <v>11.5</v>
+        <v>12.5</v>
       </c>
       <c r="BG40">
-        <v>5.1</v>
+        <v>29</v>
       </c>
       <c r="BH40">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ40">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL40">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN40">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP40">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR40">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT40">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV40">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX40">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ40">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA40">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB40" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="41" spans="1:80">
       <c r="A41" t="s">
-        <v>110</v>
+        <v>93</v>
       </c>
       <c r="B41" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C41" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="D41" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="E41" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="F41">
-        <v>1.14</v>
+        <v>5.3</v>
       </c>
       <c r="G41">
-        <v>1.19</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H41">
-        <v>14</v>
+        <v>1.56</v>
       </c>
       <c r="I41">
-        <v>1000</v>
+        <v>1.91</v>
       </c>
       <c r="J41">
-        <v>6.2</v>
+        <v>3.25</v>
       </c>
       <c r="K41">
-        <v>19.5</v>
+        <v>5.8</v>
       </c>
       <c r="L41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M41">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="N41">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="O41">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="P41">
-        <v>1.25</v>
+        <v>1.74</v>
       </c>
       <c r="Q41">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="R41">
-        <v>0</v>
+        <v>1.27</v>
       </c>
       <c r="S41">
-        <v>0</v>
+        <v>2.92</v>
       </c>
       <c r="T41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="U41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="V41">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="W41">
-        <v>0</v>
+        <v>1.11</v>
       </c>
       <c r="X41">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y41">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Z41">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA41">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB41">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC41">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD41">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AE41">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF41">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AG41">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH41">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI41">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ41">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AK41">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AL41">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM41">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN41">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AO41">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AQ41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AR41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AS41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AT41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AU41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AV41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AW41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AX41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AY41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="AZ41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BA41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BB41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BC41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BD41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BE41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BF41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BG41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BH41">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ41">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL41">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN41">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP41">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR41">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT41">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV41">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX41">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ41">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA41">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB41" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="42" spans="1:80">
       <c r="A42" t="s">
-        <v>98</v>
+        <v>109</v>
       </c>
       <c r="B42" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C42" t="s">
         <v>130</v>
       </c>
       <c r="D42" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="E42" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="F42">
-        <v>4.1</v>
+        <v>7</v>
       </c>
       <c r="G42">
-        <v>5.2</v>
+        <v>7.2</v>
       </c>
       <c r="H42">
-        <v>1.75</v>
+        <v>1.57</v>
       </c>
       <c r="I42">
+        <v>1.59</v>
+      </c>
+      <c r="J42">
+        <v>4.4</v>
+      </c>
+      <c r="K42">
+        <v>4.5</v>
+      </c>
+      <c r="L42">
+        <v>0</v>
+      </c>
+      <c r="M42">
+        <v>1.06</v>
+      </c>
+      <c r="N42">
+        <v>4.2</v>
+      </c>
+      <c r="O42">
+        <v>1.29</v>
+      </c>
+      <c r="P42">
+        <v>2.1</v>
+      </c>
+      <c r="Q42">
+        <v>1.88</v>
+      </c>
+      <c r="R42">
+        <v>1.41</v>
+      </c>
+      <c r="S42">
+        <v>3.3</v>
+      </c>
+      <c r="T42">
+        <v>1.98</v>
+      </c>
+      <c r="U42">
         <v>1.96</v>
       </c>
-      <c r="J42">
-        <v>3.85</v>
-      </c>
-      <c r="K42">
-        <v>5.5</v>
-      </c>
-      <c r="L42">
-        <v>0</v>
-      </c>
-      <c r="M42">
-        <v>0</v>
-      </c>
-      <c r="N42">
-        <v>0</v>
-      </c>
-      <c r="O42">
-        <v>0</v>
-      </c>
-      <c r="P42">
-        <v>2.16</v>
-      </c>
-      <c r="Q42">
-        <v>1.5</v>
-      </c>
-      <c r="R42">
-        <v>0</v>
-      </c>
-      <c r="S42">
-        <v>0</v>
-      </c>
-      <c r="T42">
-        <v>1.64</v>
-      </c>
-      <c r="U42">
-        <v>2.22</v>
-      </c>
       <c r="V42">
         <v>0</v>
       </c>
@@ -10998,240 +11028,240 @@
         <v>0</v>
       </c>
       <c r="X42">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y42">
-        <v>1000</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="Z42">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AA42">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AB42">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AC42">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD42">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AE42">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AF42">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AG42">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AH42">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AI42">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ42">
-        <v>1000</v>
+        <v>260</v>
       </c>
       <c r="AK42">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AL42">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AM42">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN42">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AO42">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AP42">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AQ42">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="AR42">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AS42">
+        <v>12.5</v>
+      </c>
+      <c r="AT42">
+        <v>20</v>
+      </c>
+      <c r="AU42">
         <v>9.4</v>
       </c>
-      <c r="AS42">
-        <v>17</v>
-      </c>
-      <c r="AT42">
-        <v>14</v>
-      </c>
-      <c r="AU42">
-        <v>7.4</v>
-      </c>
       <c r="AV42">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AW42">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="AX42">
-        <v>25</v>
+        <v>48</v>
       </c>
       <c r="AY42">
-        <v>13.5</v>
+        <v>23</v>
       </c>
       <c r="AZ42">
-        <v>13.5</v>
+        <v>21</v>
       </c>
       <c r="BA42">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="BB42">
+        <v>50</v>
+      </c>
+      <c r="BC42">
+        <v>40</v>
+      </c>
+      <c r="BD42">
         <v>60</v>
       </c>
-      <c r="BC42">
-        <v>38</v>
-      </c>
-      <c r="BD42">
-        <v>38</v>
-      </c>
       <c r="BE42">
-        <v>48</v>
+        <v>90</v>
       </c>
       <c r="BF42">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BG42">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BH42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ42">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA42">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB42" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="43" spans="1:80">
       <c r="A43" t="s">
-        <v>103</v>
+        <v>110</v>
       </c>
       <c r="B43" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C43" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="D43" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="E43" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="F43">
-        <v>1.17</v>
+        <v>1.96</v>
       </c>
       <c r="G43">
-        <v>1.18</v>
+        <v>2.16</v>
       </c>
       <c r="H43">
-        <v>19.5</v>
+        <v>3.15</v>
       </c>
       <c r="I43">
-        <v>22</v>
+        <v>3.85</v>
       </c>
       <c r="J43">
-        <v>10</v>
+        <v>4.2</v>
       </c>
       <c r="K43">
-        <v>10.5</v>
+        <v>5.8</v>
       </c>
       <c r="L43">
         <v>0</v>
       </c>
       <c r="M43">
-        <v>1.02</v>
+        <v>0</v>
       </c>
       <c r="N43">
-        <v>8.199999999999999</v>
+        <v>0</v>
       </c>
       <c r="O43">
-        <v>1.13</v>
+        <v>0</v>
       </c>
       <c r="P43">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="Q43">
-        <v>1.37</v>
+        <v>1.26</v>
       </c>
       <c r="R43">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="S43">
-        <v>1.94</v>
+        <v>0</v>
       </c>
       <c r="T43">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="U43">
-        <v>1.87</v>
+        <v>1.01</v>
       </c>
       <c r="V43">
         <v>0</v>
@@ -11240,10 +11270,10 @@
         <v>0</v>
       </c>
       <c r="X43">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="Y43">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="Z43">
         <v>1000</v>
@@ -11252,405 +11282,1373 @@
         <v>1000</v>
       </c>
       <c r="AB43">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AC43">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="AD43">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AE43">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="AF43">
-        <v>9.6</v>
+        <v>1000</v>
       </c>
       <c r="AG43">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="AH43">
-        <v>44</v>
+        <v>1000</v>
       </c>
       <c r="AI43">
         <v>1000</v>
       </c>
       <c r="AJ43">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="AK43">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="AL43">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AM43">
         <v>1000</v>
       </c>
       <c r="AN43">
-        <v>2.92</v>
+        <v>1000</v>
       </c>
       <c r="AO43">
-        <v>380</v>
+        <v>1000</v>
       </c>
       <c r="AP43">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="AQ43">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AR43">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="AS43">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT43">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU43">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AV43">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AW43">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="AX43">
-        <v>8.6</v>
+        <v>1.01</v>
       </c>
       <c r="AY43">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="AZ43">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BA43">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BB43">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BC43">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD43">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="BE43">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BF43">
-        <v>2.76</v>
+        <v>1.01</v>
       </c>
       <c r="BG43">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH43">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BI43">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BJ43">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BK43">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BL43">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BM43">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BN43">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BO43">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BP43">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BQ43">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BR43">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BS43">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BT43">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BU43">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BV43">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BW43">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BX43">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="BY43">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="BZ43">
-        <v>1000</v>
+        <v>0</v>
       </c>
       <c r="CA43">
-        <v>1.01</v>
+        <v>0</v>
       </c>
       <c r="CB43" t="s">
-        <v>218</v>
+        <v>228</v>
       </c>
     </row>
     <row r="44" spans="1:80">
       <c r="A44" t="s">
-        <v>82</v>
+        <v>111</v>
       </c>
       <c r="B44" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C44" t="s">
         <v>131</v>
       </c>
       <c r="D44" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="E44" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="F44">
+        <v>1.81</v>
+      </c>
+      <c r="G44">
+        <v>1.89</v>
+      </c>
+      <c r="H44">
+        <v>5</v>
+      </c>
+      <c r="I44">
+        <v>5.6</v>
+      </c>
+      <c r="J44">
+        <v>3.6</v>
+      </c>
+      <c r="K44">
+        <v>3.95</v>
+      </c>
+      <c r="L44">
+        <v>0</v>
+      </c>
+      <c r="M44">
+        <v>0</v>
+      </c>
+      <c r="N44">
+        <v>0</v>
+      </c>
+      <c r="O44">
+        <v>0</v>
+      </c>
+      <c r="P44">
+        <v>1.25</v>
+      </c>
+      <c r="Q44">
+        <v>1.94</v>
+      </c>
+      <c r="R44">
+        <v>0</v>
+      </c>
+      <c r="S44">
+        <v>0</v>
+      </c>
+      <c r="T44">
+        <v>1.73</v>
+      </c>
+      <c r="U44">
+        <v>1.89</v>
+      </c>
+      <c r="V44">
+        <v>0</v>
+      </c>
+      <c r="W44">
+        <v>0</v>
+      </c>
+      <c r="X44">
+        <v>15.5</v>
+      </c>
+      <c r="Y44">
+        <v>19.5</v>
+      </c>
+      <c r="Z44">
+        <v>46</v>
+      </c>
+      <c r="AA44">
+        <v>150</v>
+      </c>
+      <c r="AB44">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AC44">
+        <v>9.6</v>
+      </c>
+      <c r="AD44">
+        <v>24</v>
+      </c>
+      <c r="AE44">
+        <v>85</v>
+      </c>
+      <c r="AF44">
+        <v>12.5</v>
+      </c>
+      <c r="AG44">
+        <v>12</v>
+      </c>
+      <c r="AH44">
+        <v>24</v>
+      </c>
+      <c r="AI44">
+        <v>90</v>
+      </c>
+      <c r="AJ44">
+        <v>23</v>
+      </c>
+      <c r="AK44">
+        <v>24</v>
+      </c>
+      <c r="AL44">
+        <v>44</v>
+      </c>
+      <c r="AM44">
+        <v>140</v>
+      </c>
+      <c r="AN44">
+        <v>15.5</v>
+      </c>
+      <c r="AO44">
+        <v>110</v>
+      </c>
+      <c r="AP44">
+        <v>12</v>
+      </c>
+      <c r="AQ44">
+        <v>14.5</v>
+      </c>
+      <c r="AR44">
+        <v>4.8</v>
+      </c>
+      <c r="AS44">
+        <v>5.2</v>
+      </c>
+      <c r="AT44">
+        <v>7.2</v>
+      </c>
+      <c r="AU44">
+        <v>7.6</v>
+      </c>
+      <c r="AV44">
+        <v>18</v>
+      </c>
+      <c r="AW44">
+        <v>5</v>
+      </c>
+      <c r="AX44">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AY44">
+        <v>9</v>
+      </c>
+      <c r="AZ44">
+        <v>17.5</v>
+      </c>
+      <c r="BA44">
+        <v>5.1</v>
+      </c>
+      <c r="BB44">
+        <v>17.5</v>
+      </c>
+      <c r="BC44">
+        <v>18</v>
+      </c>
+      <c r="BD44">
+        <v>4.8</v>
+      </c>
+      <c r="BE44">
+        <v>5.2</v>
+      </c>
+      <c r="BF44">
+        <v>11.5</v>
+      </c>
+      <c r="BG44">
+        <v>5.1</v>
+      </c>
+      <c r="BH44">
+        <v>0</v>
+      </c>
+      <c r="BI44">
+        <v>0</v>
+      </c>
+      <c r="BJ44">
+        <v>0</v>
+      </c>
+      <c r="BK44">
+        <v>0</v>
+      </c>
+      <c r="BL44">
+        <v>0</v>
+      </c>
+      <c r="BM44">
+        <v>0</v>
+      </c>
+      <c r="BN44">
+        <v>0</v>
+      </c>
+      <c r="BO44">
+        <v>0</v>
+      </c>
+      <c r="BP44">
+        <v>0</v>
+      </c>
+      <c r="BQ44">
+        <v>0</v>
+      </c>
+      <c r="BR44">
+        <v>0</v>
+      </c>
+      <c r="BS44">
+        <v>0</v>
+      </c>
+      <c r="BT44">
+        <v>0</v>
+      </c>
+      <c r="BU44">
+        <v>0</v>
+      </c>
+      <c r="BV44">
+        <v>0</v>
+      </c>
+      <c r="BW44">
+        <v>0</v>
+      </c>
+      <c r="BX44">
+        <v>0</v>
+      </c>
+      <c r="BY44">
+        <v>0</v>
+      </c>
+      <c r="BZ44">
+        <v>0</v>
+      </c>
+      <c r="CA44">
+        <v>0</v>
+      </c>
+      <c r="CB44" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="45" spans="1:80">
+      <c r="A45" t="s">
+        <v>111</v>
+      </c>
+      <c r="B45" t="s">
+        <v>112</v>
+      </c>
+      <c r="C45" t="s">
+        <v>131</v>
+      </c>
+      <c r="D45" t="s">
+        <v>177</v>
+      </c>
+      <c r="E45" t="s">
+        <v>224</v>
+      </c>
+      <c r="F45">
+        <v>1.18</v>
+      </c>
+      <c r="G45">
+        <v>1.19</v>
+      </c>
+      <c r="H45">
+        <v>18</v>
+      </c>
+      <c r="I45">
+        <v>22</v>
+      </c>
+      <c r="J45">
+        <v>8.6</v>
+      </c>
+      <c r="K45">
+        <v>9.6</v>
+      </c>
+      <c r="L45">
+        <v>0</v>
+      </c>
+      <c r="M45">
+        <v>0</v>
+      </c>
+      <c r="N45">
+        <v>0</v>
+      </c>
+      <c r="O45">
+        <v>0</v>
+      </c>
+      <c r="P45">
+        <v>3</v>
+      </c>
+      <c r="Q45">
+        <v>1.35</v>
+      </c>
+      <c r="R45">
+        <v>0</v>
+      </c>
+      <c r="S45">
+        <v>0</v>
+      </c>
+      <c r="T45">
+        <v>0</v>
+      </c>
+      <c r="U45">
+        <v>0</v>
+      </c>
+      <c r="V45">
+        <v>0</v>
+      </c>
+      <c r="W45">
+        <v>0</v>
+      </c>
+      <c r="X45">
+        <v>0</v>
+      </c>
+      <c r="Y45">
+        <v>0</v>
+      </c>
+      <c r="Z45">
+        <v>0</v>
+      </c>
+      <c r="AA45">
+        <v>0</v>
+      </c>
+      <c r="AB45">
+        <v>0</v>
+      </c>
+      <c r="AC45">
+        <v>0</v>
+      </c>
+      <c r="AD45">
+        <v>0</v>
+      </c>
+      <c r="AE45">
+        <v>0</v>
+      </c>
+      <c r="AF45">
+        <v>0</v>
+      </c>
+      <c r="AG45">
+        <v>0</v>
+      </c>
+      <c r="AH45">
+        <v>0</v>
+      </c>
+      <c r="AI45">
+        <v>0</v>
+      </c>
+      <c r="AJ45">
+        <v>0</v>
+      </c>
+      <c r="AK45">
+        <v>0</v>
+      </c>
+      <c r="AL45">
+        <v>0</v>
+      </c>
+      <c r="AM45">
+        <v>0</v>
+      </c>
+      <c r="AN45">
+        <v>0</v>
+      </c>
+      <c r="AO45">
+        <v>0</v>
+      </c>
+      <c r="AP45">
+        <v>0</v>
+      </c>
+      <c r="AQ45">
+        <v>0</v>
+      </c>
+      <c r="AR45">
+        <v>0</v>
+      </c>
+      <c r="AS45">
+        <v>0</v>
+      </c>
+      <c r="AT45">
+        <v>0</v>
+      </c>
+      <c r="AU45">
+        <v>0</v>
+      </c>
+      <c r="AV45">
+        <v>0</v>
+      </c>
+      <c r="AW45">
+        <v>0</v>
+      </c>
+      <c r="AX45">
+        <v>0</v>
+      </c>
+      <c r="AY45">
+        <v>0</v>
+      </c>
+      <c r="AZ45">
+        <v>0</v>
+      </c>
+      <c r="BA45">
+        <v>0</v>
+      </c>
+      <c r="BB45">
+        <v>0</v>
+      </c>
+      <c r="BC45">
+        <v>0</v>
+      </c>
+      <c r="BD45">
+        <v>0</v>
+      </c>
+      <c r="BE45">
+        <v>0</v>
+      </c>
+      <c r="BF45">
+        <v>0</v>
+      </c>
+      <c r="BG45">
+        <v>0</v>
+      </c>
+      <c r="BH45">
+        <v>0</v>
+      </c>
+      <c r="BI45">
+        <v>0</v>
+      </c>
+      <c r="BJ45">
+        <v>0</v>
+      </c>
+      <c r="BK45">
+        <v>0</v>
+      </c>
+      <c r="BL45">
+        <v>0</v>
+      </c>
+      <c r="BM45">
+        <v>0</v>
+      </c>
+      <c r="BN45">
+        <v>0</v>
+      </c>
+      <c r="BO45">
+        <v>0</v>
+      </c>
+      <c r="BP45">
+        <v>0</v>
+      </c>
+      <c r="BQ45">
+        <v>0</v>
+      </c>
+      <c r="BR45">
+        <v>0</v>
+      </c>
+      <c r="BS45">
+        <v>0</v>
+      </c>
+      <c r="BT45">
+        <v>0</v>
+      </c>
+      <c r="BU45">
+        <v>0</v>
+      </c>
+      <c r="BV45">
+        <v>0</v>
+      </c>
+      <c r="BW45">
+        <v>0</v>
+      </c>
+      <c r="BX45">
+        <v>0</v>
+      </c>
+      <c r="BY45">
+        <v>0</v>
+      </c>
+      <c r="BZ45">
+        <v>0</v>
+      </c>
+      <c r="CA45">
+        <v>0</v>
+      </c>
+      <c r="CB45" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="46" spans="1:80">
+      <c r="A46" t="s">
+        <v>104</v>
+      </c>
+      <c r="B46" t="s">
+        <v>112</v>
+      </c>
+      <c r="C46" t="s">
+        <v>132</v>
+      </c>
+      <c r="D46" t="s">
+        <v>178</v>
+      </c>
+      <c r="E46" t="s">
+        <v>225</v>
+      </c>
+      <c r="F46">
+        <v>1.17</v>
+      </c>
+      <c r="G46">
+        <v>1.18</v>
+      </c>
+      <c r="H46">
+        <v>19.5</v>
+      </c>
+      <c r="I46">
+        <v>21</v>
+      </c>
+      <c r="J46">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="K46">
+        <v>10.5</v>
+      </c>
+      <c r="L46">
+        <v>0</v>
+      </c>
+      <c r="M46">
+        <v>1.02</v>
+      </c>
+      <c r="N46">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="O46">
+        <v>1.13</v>
+      </c>
+      <c r="P46">
+        <v>3.5</v>
+      </c>
+      <c r="Q46">
+        <v>1.37</v>
+      </c>
+      <c r="R46">
+        <v>2.02</v>
+      </c>
+      <c r="S46">
+        <v>1.94</v>
+      </c>
+      <c r="T46">
+        <v>2.08</v>
+      </c>
+      <c r="U46">
+        <v>1.86</v>
+      </c>
+      <c r="V46">
+        <v>0</v>
+      </c>
+      <c r="W46">
+        <v>0</v>
+      </c>
+      <c r="X46">
+        <v>44</v>
+      </c>
+      <c r="Y46">
+        <v>80</v>
+      </c>
+      <c r="Z46">
+        <v>1000</v>
+      </c>
+      <c r="AA46">
+        <v>1000</v>
+      </c>
+      <c r="AB46">
+        <v>13.5</v>
+      </c>
+      <c r="AC46">
+        <v>24</v>
+      </c>
+      <c r="AD46">
+        <v>70</v>
+      </c>
+      <c r="AE46">
+        <v>360</v>
+      </c>
+      <c r="AF46">
+        <v>9.6</v>
+      </c>
+      <c r="AG46">
+        <v>13</v>
+      </c>
+      <c r="AH46">
+        <v>44</v>
+      </c>
+      <c r="AI46">
+        <v>1000</v>
+      </c>
+      <c r="AJ46">
+        <v>9.4</v>
+      </c>
+      <c r="AK46">
+        <v>13.5</v>
+      </c>
+      <c r="AL46">
+        <v>36</v>
+      </c>
+      <c r="AM46">
+        <v>1000</v>
+      </c>
+      <c r="AN46">
+        <v>2.9</v>
+      </c>
+      <c r="AO46">
+        <v>380</v>
+      </c>
+      <c r="AP46">
+        <v>27</v>
+      </c>
+      <c r="AQ46">
+        <v>34</v>
+      </c>
+      <c r="AR46">
+        <v>48</v>
+      </c>
+      <c r="AS46">
+        <v>19</v>
+      </c>
+      <c r="AT46">
+        <v>12</v>
+      </c>
+      <c r="AU46">
+        <v>21</v>
+      </c>
+      <c r="AV46">
+        <v>34</v>
+      </c>
+      <c r="AW46">
+        <v>50</v>
+      </c>
+      <c r="AX46">
+        <v>8.6</v>
+      </c>
+      <c r="AY46">
+        <v>11.5</v>
+      </c>
+      <c r="AZ46">
+        <v>26</v>
+      </c>
+      <c r="BA46">
+        <v>46</v>
+      </c>
+      <c r="BB46">
+        <v>8.4</v>
+      </c>
+      <c r="BC46">
+        <v>11.5</v>
+      </c>
+      <c r="BD46">
+        <v>25</v>
+      </c>
+      <c r="BE46">
+        <v>46</v>
+      </c>
+      <c r="BF46">
+        <v>2.76</v>
+      </c>
+      <c r="BG46">
+        <v>55</v>
+      </c>
+      <c r="BH46">
+        <v>1000</v>
+      </c>
+      <c r="BI46">
+        <v>1.01</v>
+      </c>
+      <c r="BJ46">
+        <v>1000</v>
+      </c>
+      <c r="BK46">
+        <v>1.01</v>
+      </c>
+      <c r="BL46">
+        <v>1000</v>
+      </c>
+      <c r="BM46">
+        <v>1.01</v>
+      </c>
+      <c r="BN46">
+        <v>1000</v>
+      </c>
+      <c r="BO46">
+        <v>1.01</v>
+      </c>
+      <c r="BP46">
+        <v>1000</v>
+      </c>
+      <c r="BQ46">
+        <v>1.01</v>
+      </c>
+      <c r="BR46">
+        <v>1000</v>
+      </c>
+      <c r="BS46">
+        <v>1.01</v>
+      </c>
+      <c r="BT46">
+        <v>1000</v>
+      </c>
+      <c r="BU46">
+        <v>1.01</v>
+      </c>
+      <c r="BV46">
+        <v>1000</v>
+      </c>
+      <c r="BW46">
+        <v>1.01</v>
+      </c>
+      <c r="BX46">
+        <v>1000</v>
+      </c>
+      <c r="BY46">
+        <v>1.01</v>
+      </c>
+      <c r="BZ46">
+        <v>1000</v>
+      </c>
+      <c r="CA46">
+        <v>1.01</v>
+      </c>
+      <c r="CB46" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="47" spans="1:80">
+      <c r="A47" t="s">
+        <v>99</v>
+      </c>
+      <c r="B47" t="s">
+        <v>112</v>
+      </c>
+      <c r="C47" t="s">
+        <v>132</v>
+      </c>
+      <c r="D47" t="s">
+        <v>179</v>
+      </c>
+      <c r="E47" t="s">
+        <v>226</v>
+      </c>
+      <c r="F47">
+        <v>4.2</v>
+      </c>
+      <c r="G47">
+        <v>5.3</v>
+      </c>
+      <c r="H47">
+        <v>1.82</v>
+      </c>
+      <c r="I47">
+        <v>1.95</v>
+      </c>
+      <c r="J47">
+        <v>3.85</v>
+      </c>
+      <c r="K47">
+        <v>4.3</v>
+      </c>
+      <c r="L47">
+        <v>0</v>
+      </c>
+      <c r="M47">
+        <v>0</v>
+      </c>
+      <c r="N47">
+        <v>0</v>
+      </c>
+      <c r="O47">
+        <v>0</v>
+      </c>
+      <c r="P47">
+        <v>2.16</v>
+      </c>
+      <c r="Q47">
+        <v>1.5</v>
+      </c>
+      <c r="R47">
+        <v>0</v>
+      </c>
+      <c r="S47">
+        <v>0</v>
+      </c>
+      <c r="T47">
+        <v>1.64</v>
+      </c>
+      <c r="U47">
+        <v>2.22</v>
+      </c>
+      <c r="V47">
+        <v>0</v>
+      </c>
+      <c r="W47">
+        <v>0</v>
+      </c>
+      <c r="X47">
+        <v>1000</v>
+      </c>
+      <c r="Y47">
+        <v>1000</v>
+      </c>
+      <c r="Z47">
+        <v>1000</v>
+      </c>
+      <c r="AA47">
+        <v>1000</v>
+      </c>
+      <c r="AB47">
+        <v>1000</v>
+      </c>
+      <c r="AC47">
+        <v>1000</v>
+      </c>
+      <c r="AD47">
+        <v>1000</v>
+      </c>
+      <c r="AE47">
+        <v>1000</v>
+      </c>
+      <c r="AF47">
+        <v>1000</v>
+      </c>
+      <c r="AG47">
+        <v>1000</v>
+      </c>
+      <c r="AH47">
+        <v>1000</v>
+      </c>
+      <c r="AI47">
+        <v>1000</v>
+      </c>
+      <c r="AJ47">
+        <v>1000</v>
+      </c>
+      <c r="AK47">
+        <v>1000</v>
+      </c>
+      <c r="AL47">
+        <v>1000</v>
+      </c>
+      <c r="AM47">
+        <v>1000</v>
+      </c>
+      <c r="AN47">
+        <v>1000</v>
+      </c>
+      <c r="AO47">
+        <v>1000</v>
+      </c>
+      <c r="AP47">
+        <v>15</v>
+      </c>
+      <c r="AQ47">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AR47">
+        <v>9.4</v>
+      </c>
+      <c r="AS47">
+        <v>17</v>
+      </c>
+      <c r="AT47">
+        <v>14</v>
+      </c>
+      <c r="AU47">
+        <v>7.4</v>
+      </c>
+      <c r="AV47">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW47">
+        <v>15</v>
+      </c>
+      <c r="AX47">
+        <v>25</v>
+      </c>
+      <c r="AY47">
+        <v>13.5</v>
+      </c>
+      <c r="AZ47">
+        <v>13.5</v>
+      </c>
+      <c r="BA47">
+        <v>24</v>
+      </c>
+      <c r="BB47">
+        <v>60</v>
+      </c>
+      <c r="BC47">
+        <v>38</v>
+      </c>
+      <c r="BD47">
+        <v>38</v>
+      </c>
+      <c r="BE47">
+        <v>48</v>
+      </c>
+      <c r="BF47">
+        <v>1.01</v>
+      </c>
+      <c r="BG47">
+        <v>1.01</v>
+      </c>
+      <c r="BH47">
+        <v>0</v>
+      </c>
+      <c r="BI47">
+        <v>0</v>
+      </c>
+      <c r="BJ47">
+        <v>0</v>
+      </c>
+      <c r="BK47">
+        <v>0</v>
+      </c>
+      <c r="BL47">
+        <v>0</v>
+      </c>
+      <c r="BM47">
+        <v>0</v>
+      </c>
+      <c r="BN47">
+        <v>0</v>
+      </c>
+      <c r="BO47">
+        <v>0</v>
+      </c>
+      <c r="BP47">
+        <v>0</v>
+      </c>
+      <c r="BQ47">
+        <v>0</v>
+      </c>
+      <c r="BR47">
+        <v>0</v>
+      </c>
+      <c r="BS47">
+        <v>0</v>
+      </c>
+      <c r="BT47">
+        <v>0</v>
+      </c>
+      <c r="BU47">
+        <v>0</v>
+      </c>
+      <c r="BV47">
+        <v>0</v>
+      </c>
+      <c r="BW47">
+        <v>0</v>
+      </c>
+      <c r="BX47">
+        <v>0</v>
+      </c>
+      <c r="BY47">
+        <v>0</v>
+      </c>
+      <c r="BZ47">
+        <v>0</v>
+      </c>
+      <c r="CA47">
+        <v>0</v>
+      </c>
+      <c r="CB47" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="48" spans="1:80">
+      <c r="A48" t="s">
+        <v>82</v>
+      </c>
+      <c r="B48" t="s">
+        <v>112</v>
+      </c>
+      <c r="C48" t="s">
+        <v>133</v>
+      </c>
+      <c r="D48" t="s">
+        <v>180</v>
+      </c>
+      <c r="E48" t="s">
+        <v>227</v>
+      </c>
+      <c r="F48">
         <v>2.66</v>
       </c>
-      <c r="G44">
+      <c r="G48">
         <v>3.75</v>
       </c>
-      <c r="H44">
+      <c r="H48">
         <v>2.66</v>
       </c>
-      <c r="I44">
+      <c r="I48">
         <v>3.75</v>
       </c>
-      <c r="J44">
+      <c r="J48">
         <v>2.5</v>
       </c>
-      <c r="K44">
+      <c r="K48">
         <v>3.45</v>
       </c>
-      <c r="L44">
-        <v>1.01</v>
-      </c>
-      <c r="M44">
+      <c r="L48">
+        <v>1.01</v>
+      </c>
+      <c r="M48">
         <v>1.1</v>
       </c>
-      <c r="N44">
+      <c r="N48">
         <v>2.46</v>
       </c>
-      <c r="O44">
+      <c r="O48">
         <v>1.42</v>
       </c>
-      <c r="P44">
+      <c r="P48">
         <v>1.5</v>
       </c>
-      <c r="Q44">
+      <c r="Q48">
         <v>2.24</v>
       </c>
-      <c r="R44">
+      <c r="R48">
         <v>1.18</v>
       </c>
-      <c r="S44">
+      <c r="S48">
         <v>3.85</v>
       </c>
-      <c r="T44">
-        <v>1.01</v>
-      </c>
-      <c r="U44">
-        <v>1.01</v>
-      </c>
-      <c r="V44">
+      <c r="T48">
+        <v>1.01</v>
+      </c>
+      <c r="U48">
+        <v>1.01</v>
+      </c>
+      <c r="V48">
         <v>1.36</v>
       </c>
-      <c r="W44">
+      <c r="W48">
         <v>1.36</v>
       </c>
-      <c r="X44">
-        <v>1000</v>
-      </c>
-      <c r="Y44">
-        <v>1000</v>
-      </c>
-      <c r="Z44">
-        <v>1000</v>
-      </c>
-      <c r="AA44">
-        <v>1000</v>
-      </c>
-      <c r="AB44">
-        <v>1000</v>
-      </c>
-      <c r="AC44">
-        <v>1000</v>
-      </c>
-      <c r="AD44">
-        <v>1000</v>
-      </c>
-      <c r="AE44">
-        <v>1000</v>
-      </c>
-      <c r="AF44">
-        <v>1000</v>
-      </c>
-      <c r="AG44">
-        <v>1000</v>
-      </c>
-      <c r="AH44">
-        <v>1000</v>
-      </c>
-      <c r="AI44">
-        <v>1000</v>
-      </c>
-      <c r="AJ44">
-        <v>1000</v>
-      </c>
-      <c r="AK44">
-        <v>1000</v>
-      </c>
-      <c r="AL44">
-        <v>1000</v>
-      </c>
-      <c r="AM44">
-        <v>1000</v>
-      </c>
-      <c r="AN44">
-        <v>1000</v>
-      </c>
-      <c r="AO44">
-        <v>1000</v>
-      </c>
-      <c r="AP44">
-        <v>1.01</v>
-      </c>
-      <c r="AQ44">
-        <v>1.01</v>
-      </c>
-      <c r="AR44">
-        <v>1.01</v>
-      </c>
-      <c r="AS44">
-        <v>1.01</v>
-      </c>
-      <c r="AT44">
-        <v>1.01</v>
-      </c>
-      <c r="AU44">
-        <v>1.01</v>
-      </c>
-      <c r="AV44">
-        <v>1.01</v>
-      </c>
-      <c r="AW44">
-        <v>1.01</v>
-      </c>
-      <c r="AX44">
-        <v>1.01</v>
-      </c>
-      <c r="AY44">
-        <v>1.01</v>
-      </c>
-      <c r="AZ44">
-        <v>1.01</v>
-      </c>
-      <c r="BA44">
-        <v>1.01</v>
-      </c>
-      <c r="BB44">
-        <v>1.01</v>
-      </c>
-      <c r="BC44">
-        <v>1.01</v>
-      </c>
-      <c r="BD44">
-        <v>1.01</v>
-      </c>
-      <c r="BE44">
-        <v>1.01</v>
-      </c>
-      <c r="BF44">
-        <v>1.01</v>
-      </c>
-      <c r="BG44">
-        <v>1.01</v>
-      </c>
-      <c r="BH44">
-        <v>1000</v>
-      </c>
-      <c r="BI44">
-        <v>1.01</v>
-      </c>
-      <c r="BJ44">
-        <v>1000</v>
-      </c>
-      <c r="BK44">
-        <v>1.01</v>
-      </c>
-      <c r="BL44">
-        <v>1000</v>
-      </c>
-      <c r="BM44">
-        <v>1.01</v>
-      </c>
-      <c r="BN44">
-        <v>1000</v>
-      </c>
-      <c r="BO44">
-        <v>1.01</v>
-      </c>
-      <c r="BP44">
-        <v>1000</v>
-      </c>
-      <c r="BQ44">
-        <v>1.01</v>
-      </c>
-      <c r="BR44">
-        <v>1000</v>
-      </c>
-      <c r="BS44">
-        <v>1.01</v>
-      </c>
-      <c r="BT44">
-        <v>1000</v>
-      </c>
-      <c r="BU44">
-        <v>1.01</v>
-      </c>
-      <c r="BV44">
-        <v>1000</v>
-      </c>
-      <c r="BW44">
-        <v>1.01</v>
-      </c>
-      <c r="BX44">
-        <v>1000</v>
-      </c>
-      <c r="BY44">
-        <v>1.01</v>
-      </c>
-      <c r="BZ44">
-        <v>0</v>
-      </c>
-      <c r="CA44">
-        <v>0</v>
-      </c>
-      <c r="CB44" t="s">
-        <v>218</v>
+      <c r="X48">
+        <v>1000</v>
+      </c>
+      <c r="Y48">
+        <v>1000</v>
+      </c>
+      <c r="Z48">
+        <v>1000</v>
+      </c>
+      <c r="AA48">
+        <v>1000</v>
+      </c>
+      <c r="AB48">
+        <v>1000</v>
+      </c>
+      <c r="AC48">
+        <v>1000</v>
+      </c>
+      <c r="AD48">
+        <v>1000</v>
+      </c>
+      <c r="AE48">
+        <v>1000</v>
+      </c>
+      <c r="AF48">
+        <v>1000</v>
+      </c>
+      <c r="AG48">
+        <v>1000</v>
+      </c>
+      <c r="AH48">
+        <v>1000</v>
+      </c>
+      <c r="AI48">
+        <v>1000</v>
+      </c>
+      <c r="AJ48">
+        <v>1000</v>
+      </c>
+      <c r="AK48">
+        <v>1000</v>
+      </c>
+      <c r="AL48">
+        <v>1000</v>
+      </c>
+      <c r="AM48">
+        <v>1000</v>
+      </c>
+      <c r="AN48">
+        <v>1000</v>
+      </c>
+      <c r="AO48">
+        <v>1000</v>
+      </c>
+      <c r="AP48">
+        <v>1.01</v>
+      </c>
+      <c r="AQ48">
+        <v>1.01</v>
+      </c>
+      <c r="AR48">
+        <v>1.01</v>
+      </c>
+      <c r="AS48">
+        <v>1.01</v>
+      </c>
+      <c r="AT48">
+        <v>1.01</v>
+      </c>
+      <c r="AU48">
+        <v>1.01</v>
+      </c>
+      <c r="AV48">
+        <v>1.01</v>
+      </c>
+      <c r="AW48">
+        <v>1.01</v>
+      </c>
+      <c r="AX48">
+        <v>1.01</v>
+      </c>
+      <c r="AY48">
+        <v>1.01</v>
+      </c>
+      <c r="AZ48">
+        <v>1.01</v>
+      </c>
+      <c r="BA48">
+        <v>1.01</v>
+      </c>
+      <c r="BB48">
+        <v>1.01</v>
+      </c>
+      <c r="BC48">
+        <v>1.01</v>
+      </c>
+      <c r="BD48">
+        <v>1.01</v>
+      </c>
+      <c r="BE48">
+        <v>1.01</v>
+      </c>
+      <c r="BF48">
+        <v>1.01</v>
+      </c>
+      <c r="BG48">
+        <v>1.01</v>
+      </c>
+      <c r="BH48">
+        <v>1000</v>
+      </c>
+      <c r="BI48">
+        <v>1.01</v>
+      </c>
+      <c r="BJ48">
+        <v>1000</v>
+      </c>
+      <c r="BK48">
+        <v>1.01</v>
+      </c>
+      <c r="BL48">
+        <v>1000</v>
+      </c>
+      <c r="BM48">
+        <v>1.01</v>
+      </c>
+      <c r="BN48">
+        <v>1000</v>
+      </c>
+      <c r="BO48">
+        <v>1.01</v>
+      </c>
+      <c r="BP48">
+        <v>1000</v>
+      </c>
+      <c r="BQ48">
+        <v>1.01</v>
+      </c>
+      <c r="BR48">
+        <v>1000</v>
+      </c>
+      <c r="BS48">
+        <v>1.01</v>
+      </c>
+      <c r="BT48">
+        <v>1000</v>
+      </c>
+      <c r="BU48">
+        <v>1.01</v>
+      </c>
+      <c r="BV48">
+        <v>1000</v>
+      </c>
+      <c r="BW48">
+        <v>1.01</v>
+      </c>
+      <c r="BX48">
+        <v>1000</v>
+      </c>
+      <c r="BY48">
+        <v>1.01</v>
+      </c>
+      <c r="BZ48">
+        <v>0</v>
+      </c>
+      <c r="CA48">
+        <v>0</v>
+      </c>
+      <c r="CB48" t="s">
+        <v>228</v>
       </c>
     </row>
   </sheetData>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-31.xlsx
@@ -826,7 +826,7 @@
     <t>Melgar</t>
   </si>
   <si>
-    <t>2026-08-29 15:54:25</t>
+    <t>2026-08-29 18:16:44</t>
   </si>
 </sst>
 </file>
@@ -1459,7 +1459,7 @@
         <v>1.44</v>
       </c>
       <c r="S2">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="T2">
         <v>1.82</v>
@@ -1821,7 +1821,7 @@
         <v>2.86</v>
       </c>
       <c r="BG3">
-        <v>18</v>
+        <v>2.58</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1904,22 +1904,22 @@
         <v>206</v>
       </c>
       <c r="F4">
-        <v>2</v>
+        <v>2.06</v>
       </c>
       <c r="G4">
-        <v>110</v>
+        <v>2.42</v>
       </c>
       <c r="H4">
-        <v>1.1</v>
+        <v>2.84</v>
       </c>
       <c r="I4">
-        <v>6.6</v>
+        <v>4.7</v>
       </c>
       <c r="J4">
-        <v>2.96</v>
+        <v>2.98</v>
       </c>
       <c r="K4">
-        <v>7.4</v>
+        <v>6</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -1928,22 +1928,22 @@
         <v>1.01</v>
       </c>
       <c r="N4">
-        <v>1.25</v>
+        <v>2.78</v>
       </c>
       <c r="O4">
         <v>1.23</v>
       </c>
       <c r="P4">
-        <v>1.25</v>
+        <v>1.88</v>
       </c>
       <c r="Q4">
-        <v>1.24</v>
+        <v>1.61</v>
       </c>
       <c r="R4">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="S4">
-        <v>1.24</v>
+        <v>2.52</v>
       </c>
       <c r="T4">
         <v>1.01</v>
@@ -1952,10 +1952,10 @@
         <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.17</v>
+        <v>1.27</v>
       </c>
       <c r="W4">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -2146,10 +2146,10 @@
         <v>207</v>
       </c>
       <c r="F5">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G5">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="H5">
         <v>3.65</v>
@@ -2158,10 +2158,10 @@
         <v>4.2</v>
       </c>
       <c r="J5">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="K5">
-        <v>3.3</v>
+        <v>3.55</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -2176,28 +2176,28 @@
         <v>1.02</v>
       </c>
       <c r="P5">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q5">
-        <v>2.18</v>
+        <v>2.56</v>
       </c>
       <c r="R5">
-        <v>1.12</v>
+        <v>1.19</v>
       </c>
       <c r="S5">
-        <v>2.06</v>
+        <v>5</v>
       </c>
       <c r="T5">
         <v>1.01</v>
       </c>
       <c r="U5">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="V5">
         <v>1.34</v>
       </c>
       <c r="W5">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="X5">
         <v>1000</v>
@@ -2269,7 +2269,7 @@
         <v>1.01</v>
       </c>
       <c r="AU5">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV5">
         <v>1.01</v>
@@ -2284,7 +2284,7 @@
         <v>1.01</v>
       </c>
       <c r="AZ5">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BA5">
         <v>1.01</v>
@@ -2299,7 +2299,7 @@
         <v>1.01</v>
       </c>
       <c r="BE5">
-        <v>100</v>
+        <v>1.01</v>
       </c>
       <c r="BF5">
         <v>1.01</v>
@@ -2388,7 +2388,7 @@
         <v>208</v>
       </c>
       <c r="F6">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="G6">
         <v>2.22</v>
@@ -2400,10 +2400,10 @@
         <v>5.2</v>
       </c>
       <c r="J6">
-        <v>2.82</v>
+        <v>3.1</v>
       </c>
       <c r="K6">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -2412,22 +2412,22 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>2.28</v>
+        <v>2.62</v>
       </c>
       <c r="O6">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="P6">
-        <v>1.47</v>
+        <v>1.57</v>
       </c>
       <c r="Q6">
-        <v>2.28</v>
+        <v>2.46</v>
       </c>
       <c r="R6">
         <v>1.13</v>
       </c>
       <c r="S6">
-        <v>2.28</v>
+        <v>4.5</v>
       </c>
       <c r="T6">
         <v>1.01</v>
@@ -2436,7 +2436,7 @@
         <v>1.01</v>
       </c>
       <c r="V6">
-        <v>1.23</v>
+        <v>1.24</v>
       </c>
       <c r="W6">
         <v>1.83</v>
@@ -2448,22 +2448,22 @@
         <v>1000</v>
       </c>
       <c r="Z6">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AA6">
         <v>1000</v>
       </c>
       <c r="AB6">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AC6">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD6">
         <v>1000</v>
       </c>
       <c r="AE6">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF6">
         <v>1000</v>
@@ -2478,10 +2478,10 @@
         <v>1000</v>
       </c>
       <c r="AJ6">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK6">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AL6">
         <v>1000</v>
@@ -2490,64 +2490,64 @@
         <v>1000</v>
       </c>
       <c r="AN6">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AO6">
         <v>1000</v>
       </c>
       <c r="AP6">
-        <v>8.4</v>
+        <v>1.5</v>
       </c>
       <c r="AQ6">
-        <v>9</v>
+        <v>1.5</v>
       </c>
       <c r="AR6">
+        <v>1.45</v>
+      </c>
+      <c r="AS6">
+        <v>1.5</v>
+      </c>
+      <c r="AT6">
+        <v>1.28</v>
+      </c>
+      <c r="AU6">
+        <v>1.3</v>
+      </c>
+      <c r="AV6">
+        <v>1.5</v>
+      </c>
+      <c r="AW6">
+        <v>1.48</v>
+      </c>
+      <c r="AX6">
+        <v>1.5</v>
+      </c>
+      <c r="AY6">
+        <v>1.5</v>
+      </c>
+      <c r="AZ6">
+        <v>1.5</v>
+      </c>
+      <c r="BA6">
+        <v>1.5</v>
+      </c>
+      <c r="BB6">
         <v>19</v>
       </c>
-      <c r="AS6">
-        <v>40</v>
-      </c>
-      <c r="AT6">
-        <v>5.7</v>
-      </c>
-      <c r="AU6">
-        <v>5.9</v>
-      </c>
-      <c r="AV6">
-        <v>14.5</v>
-      </c>
-      <c r="AW6">
-        <v>40</v>
-      </c>
-      <c r="AX6">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY6">
-        <v>9</v>
-      </c>
-      <c r="AZ6">
-        <v>18.5</v>
-      </c>
-      <c r="BA6">
-        <v>40</v>
-      </c>
-      <c r="BB6">
-        <v>18</v>
-      </c>
       <c r="BC6">
-        <v>19.5</v>
+        <v>1.45</v>
       </c>
       <c r="BD6">
-        <v>40</v>
+        <v>1.5</v>
       </c>
       <c r="BE6">
-        <v>40</v>
+        <v>1.5</v>
       </c>
       <c r="BF6">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BG6">
-        <v>1.01</v>
+        <v>1.5</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2639,7 +2639,7 @@
         <v>6.2</v>
       </c>
       <c r="I7">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="J7">
         <v>4.6</v>
@@ -2651,13 +2651,13 @@
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.03</v>
+        <v>1.02</v>
       </c>
       <c r="N7">
         <v>5.3</v>
       </c>
       <c r="O7">
-        <v>1.17</v>
+        <v>1.19</v>
       </c>
       <c r="P7">
         <v>2.5</v>
@@ -2789,7 +2789,7 @@
         <v>4.3</v>
       </c>
       <c r="BG7">
-        <v>2.14</v>
+        <v>18</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -3138,13 +3138,13 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="O9">
         <v>1.12</v>
       </c>
       <c r="P9">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Q9">
         <v>1.12</v>
@@ -3380,13 +3380,13 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="O10">
         <v>1.24</v>
       </c>
       <c r="P10">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="Q10">
         <v>1.25</v>
@@ -3843,13 +3843,13 @@
         <v>1.04</v>
       </c>
       <c r="G12">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H12">
         <v>1.04</v>
       </c>
       <c r="I12">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J12">
         <v>1.04</v>
@@ -4082,22 +4082,22 @@
         <v>215</v>
       </c>
       <c r="F13">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="G13">
-        <v>1.88</v>
+        <v>1.77</v>
       </c>
       <c r="H13">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="I13">
-        <v>8.4</v>
+        <v>6.4</v>
       </c>
       <c r="J13">
-        <v>4.1</v>
+        <v>4.4</v>
       </c>
       <c r="K13">
-        <v>5.1</v>
+        <v>7</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -4106,13 +4106,13 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="O13">
         <v>1.17</v>
       </c>
       <c r="P13">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="Q13">
         <v>1.5</v>
@@ -4130,10 +4130,10 @@
         <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.15</v>
+        <v>1.19</v>
       </c>
       <c r="W13">
-        <v>2.14</v>
+        <v>2.3</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -4324,22 +4324,22 @@
         <v>216</v>
       </c>
       <c r="F14">
-        <v>1.04</v>
+        <v>2.62</v>
       </c>
       <c r="G14">
-        <v>110</v>
+        <v>3.2</v>
       </c>
       <c r="H14">
-        <v>1.04</v>
+        <v>2.56</v>
       </c>
       <c r="I14">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="J14">
-        <v>1.06</v>
+        <v>2.74</v>
       </c>
       <c r="K14">
-        <v>1000</v>
+        <v>4.4</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -4348,22 +4348,22 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>1.12</v>
+        <v>2.32</v>
       </c>
       <c r="O14">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="P14">
-        <v>1.12</v>
+        <v>1.92</v>
       </c>
       <c r="Q14">
-        <v>1.27</v>
+        <v>1.83</v>
       </c>
       <c r="R14">
-        <v>1.08</v>
+        <v>1.35</v>
       </c>
       <c r="S14">
-        <v>1.27</v>
+        <v>3</v>
       </c>
       <c r="T14">
         <v>1.01</v>
@@ -4372,10 +4372,10 @@
         <v>1.01</v>
       </c>
       <c r="V14">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="W14">
-        <v>1.02</v>
+        <v>1.46</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4566,22 +4566,22 @@
         <v>217</v>
       </c>
       <c r="F15">
-        <v>1.04</v>
+        <v>2.38</v>
       </c>
       <c r="G15">
-        <v>1000</v>
+        <v>2.84</v>
       </c>
       <c r="H15">
-        <v>1.04</v>
+        <v>2.56</v>
       </c>
       <c r="I15">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="J15">
-        <v>1.04</v>
+        <v>3.65</v>
       </c>
       <c r="K15">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4590,22 +4590,22 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>1.13</v>
+        <v>2.3</v>
       </c>
       <c r="O15">
         <v>1.19</v>
       </c>
       <c r="P15">
-        <v>1.13</v>
+        <v>2.3</v>
       </c>
       <c r="Q15">
-        <v>1.19</v>
+        <v>1.54</v>
       </c>
       <c r="R15">
-        <v>1.08</v>
+        <v>1.53</v>
       </c>
       <c r="S15">
-        <v>1.19</v>
+        <v>2.32</v>
       </c>
       <c r="T15">
         <v>1.01</v>
@@ -4614,10 +4614,10 @@
         <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.01</v>
+        <v>1.48</v>
       </c>
       <c r="W15">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4811,16 +4811,16 @@
         <v>2.28</v>
       </c>
       <c r="G16">
-        <v>2.68</v>
+        <v>2.66</v>
       </c>
       <c r="H16">
-        <v>2.7</v>
+        <v>2.88</v>
       </c>
       <c r="I16">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="J16">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="K16">
         <v>4.1</v>
@@ -4838,10 +4838,10 @@
         <v>1.24</v>
       </c>
       <c r="P16">
-        <v>1.96</v>
+        <v>2.08</v>
       </c>
       <c r="Q16">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R16">
         <v>1.45</v>
@@ -5053,25 +5053,25 @@
         <v>1.64</v>
       </c>
       <c r="G17">
-        <v>2.98</v>
+        <v>1.95</v>
       </c>
       <c r="H17">
-        <v>2.46</v>
+        <v>3.85</v>
       </c>
       <c r="I17">
-        <v>110</v>
+        <v>6.4</v>
       </c>
       <c r="J17">
-        <v>1.58</v>
+        <v>3.95</v>
       </c>
       <c r="K17">
-        <v>270</v>
+        <v>7.8</v>
       </c>
       <c r="L17">
         <v>1.01</v>
       </c>
       <c r="M17">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N17">
         <v>2.04</v>
@@ -5083,25 +5083,25 @@
         <v>2.04</v>
       </c>
       <c r="Q17">
-        <v>1.21</v>
+        <v>1.58</v>
       </c>
       <c r="R17">
-        <v>1.08</v>
+        <v>1.4</v>
       </c>
       <c r="S17">
-        <v>1.21</v>
+        <v>2.42</v>
       </c>
       <c r="T17">
         <v>1.01</v>
       </c>
       <c r="U17">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V17">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="W17">
-        <v>1.56</v>
+        <v>2.04</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -5292,10 +5292,10 @@
         <v>220</v>
       </c>
       <c r="F18">
-        <v>3.95</v>
+        <v>4.1</v>
       </c>
       <c r="G18">
-        <v>5.9</v>
+        <v>5.5</v>
       </c>
       <c r="H18">
         <v>1.67</v>
@@ -5304,7 +5304,7 @@
         <v>1.84</v>
       </c>
       <c r="J18">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="K18">
         <v>5.1</v>
@@ -5322,10 +5322,10 @@
         <v>1.17</v>
       </c>
       <c r="P18">
-        <v>2.36</v>
+        <v>2.52</v>
       </c>
       <c r="Q18">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="R18">
         <v>1.64</v>
@@ -5337,13 +5337,13 @@
         <v>1.48</v>
       </c>
       <c r="U18">
-        <v>2.22</v>
+        <v>2.4</v>
       </c>
       <c r="V18">
         <v>2.18</v>
       </c>
       <c r="W18">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="X18">
         <v>34</v>
@@ -5534,22 +5534,22 @@
         <v>221</v>
       </c>
       <c r="F19">
-        <v>1.04</v>
+        <v>1.54</v>
       </c>
       <c r="G19">
-        <v>1000</v>
+        <v>1.75</v>
       </c>
       <c r="H19">
-        <v>1.04</v>
+        <v>4.2</v>
       </c>
       <c r="I19">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="J19">
-        <v>1.06</v>
+        <v>3.85</v>
       </c>
       <c r="K19">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="L19">
         <v>1.01</v>
@@ -5558,22 +5558,22 @@
         <v>1.01</v>
       </c>
       <c r="N19">
-        <v>1.21</v>
+        <v>2.26</v>
       </c>
       <c r="O19">
-        <v>1.17</v>
+        <v>1.16</v>
       </c>
       <c r="P19">
-        <v>1.21</v>
+        <v>2.26</v>
       </c>
       <c r="Q19">
-        <v>1.17</v>
+        <v>1.44</v>
       </c>
       <c r="R19">
-        <v>1.08</v>
+        <v>1.51</v>
       </c>
       <c r="S19">
-        <v>1.17</v>
+        <v>2.1</v>
       </c>
       <c r="T19">
         <v>1.01</v>
@@ -5582,10 +5582,10 @@
         <v>1.01</v>
       </c>
       <c r="V19">
-        <v>1.01</v>
+        <v>1.15</v>
       </c>
       <c r="W19">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="X19">
         <v>1000</v>
@@ -5776,7 +5776,7 @@
         <v>222</v>
       </c>
       <c r="F20">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G20">
         <v>2.58</v>
@@ -5788,7 +5788,7 @@
         <v>3.25</v>
       </c>
       <c r="J20">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K20">
         <v>4.1</v>
@@ -5800,7 +5800,7 @@
         <v>1.01</v>
       </c>
       <c r="N20">
-        <v>2.04</v>
+        <v>2.4</v>
       </c>
       <c r="O20">
         <v>1.23</v>
@@ -5812,16 +5812,16 @@
         <v>1.55</v>
       </c>
       <c r="R20">
-        <v>1.29</v>
+        <v>1.41</v>
       </c>
       <c r="S20">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="T20">
         <v>1.01</v>
       </c>
       <c r="U20">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="V20">
         <v>1.44</v>
@@ -6018,7 +6018,7 @@
         <v>223</v>
       </c>
       <c r="F21">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="G21">
         <v>3.7</v>
@@ -6033,10 +6033,10 @@
         <v>3.4</v>
       </c>
       <c r="K21">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L21">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M21">
         <v>1.01</v>
@@ -6048,16 +6048,16 @@
         <v>1.01</v>
       </c>
       <c r="P21">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="Q21">
         <v>1.8</v>
       </c>
       <c r="R21">
-        <v>1.13</v>
+        <v>1.32</v>
       </c>
       <c r="S21">
-        <v>2.02</v>
+        <v>2.92</v>
       </c>
       <c r="T21">
         <v>1.01</v>
@@ -6260,10 +6260,10 @@
         <v>224</v>
       </c>
       <c r="F22">
-        <v>1.97</v>
+        <v>1.95</v>
       </c>
       <c r="G22">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="H22">
         <v>3.75</v>
@@ -6293,7 +6293,7 @@
         <v>2.16</v>
       </c>
       <c r="Q22">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R22">
         <v>1.46</v>
@@ -6305,13 +6305,13 @@
         <v>1.67</v>
       </c>
       <c r="U22">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="V22">
         <v>1.31</v>
       </c>
       <c r="W22">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X22">
         <v>19</v>
@@ -6416,10 +6416,10 @@
         <v>55</v>
       </c>
       <c r="BF22">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG22">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -6502,16 +6502,16 @@
         <v>225</v>
       </c>
       <c r="F23">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="G23">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H23">
         <v>1.23</v>
       </c>
       <c r="I23">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J23">
         <v>1.08</v>
@@ -6550,10 +6550,10 @@
         <v>1.01</v>
       </c>
       <c r="V23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X23">
         <v>1000</v>
@@ -6747,13 +6747,13 @@
         <v>1.04</v>
       </c>
       <c r="G24">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H24">
         <v>1.04</v>
       </c>
       <c r="I24">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J24">
         <v>1.04</v>
@@ -6771,7 +6771,7 @@
         <v>1.26</v>
       </c>
       <c r="O24">
-        <v>1.02</v>
+        <v>1.41</v>
       </c>
       <c r="P24">
         <v>1.25</v>
@@ -6792,10 +6792,10 @@
         <v>1.01</v>
       </c>
       <c r="V24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W24">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -6989,13 +6989,13 @@
         <v>1.04</v>
       </c>
       <c r="G25">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H25">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="I25">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J25">
         <v>1.04</v>
@@ -7034,10 +7034,10 @@
         <v>1.01</v>
       </c>
       <c r="V25">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W25">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X25">
         <v>1000</v>
@@ -7228,22 +7228,22 @@
         <v>228</v>
       </c>
       <c r="F26">
-        <v>1.09</v>
+        <v>2.02</v>
       </c>
       <c r="G26">
-        <v>110</v>
+        <v>2.62</v>
       </c>
       <c r="H26">
-        <v>1.1</v>
+        <v>3.05</v>
       </c>
       <c r="I26">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="J26">
-        <v>1.08</v>
+        <v>3.35</v>
       </c>
       <c r="K26">
-        <v>100</v>
+        <v>5.6</v>
       </c>
       <c r="L26">
         <v>1.01</v>
@@ -7252,22 +7252,22 @@
         <v>1.01</v>
       </c>
       <c r="N26">
+        <v>2.94</v>
+      </c>
+      <c r="O26">
+        <v>1.33</v>
+      </c>
+      <c r="P26">
+        <v>1.72</v>
+      </c>
+      <c r="Q26">
+        <v>1.96</v>
+      </c>
+      <c r="R26">
         <v>1.25</v>
       </c>
-      <c r="O26">
-        <v>1.01</v>
-      </c>
-      <c r="P26">
-        <v>1.24</v>
-      </c>
-      <c r="Q26">
-        <v>1.35</v>
-      </c>
-      <c r="R26">
-        <v>1.18</v>
-      </c>
       <c r="S26">
-        <v>1.36</v>
+        <v>2.7</v>
       </c>
       <c r="T26">
         <v>1.01</v>
@@ -7276,10 +7276,10 @@
         <v>1.01</v>
       </c>
       <c r="V26">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="W26">
-        <v>1.01</v>
+        <v>1.61</v>
       </c>
       <c r="X26">
         <v>1000</v>
@@ -7494,13 +7494,13 @@
         <v>1.05</v>
       </c>
       <c r="N27">
-        <v>2.06</v>
+        <v>2.7</v>
       </c>
       <c r="O27">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="P27">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="Q27">
         <v>1.76</v>
@@ -7509,13 +7509,13 @@
         <v>1.44</v>
       </c>
       <c r="S27">
-        <v>2.48</v>
+        <v>2.88</v>
       </c>
       <c r="T27">
-        <v>1.63</v>
+        <v>1.01</v>
       </c>
       <c r="U27">
-        <v>2.24</v>
+        <v>1.01</v>
       </c>
       <c r="V27">
         <v>1.36</v>
@@ -7718,13 +7718,13 @@
         <v>2.48</v>
       </c>
       <c r="H28">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="I28">
         <v>3.35</v>
       </c>
       <c r="J28">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="K28">
         <v>4</v>
@@ -7736,7 +7736,7 @@
         <v>1.01</v>
       </c>
       <c r="N28">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="O28">
         <v>1.24</v>
@@ -7748,16 +7748,16 @@
         <v>1.77</v>
       </c>
       <c r="R28">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S28">
-        <v>2.38</v>
+        <v>2.86</v>
       </c>
       <c r="T28">
-        <v>1.62</v>
+        <v>1.01</v>
       </c>
       <c r="U28">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="V28">
         <v>1.42</v>
@@ -7954,22 +7954,22 @@
         <v>231</v>
       </c>
       <c r="F29">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="G29">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H29">
-        <v>3.2</v>
+        <v>3.55</v>
       </c>
       <c r="I29">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="J29">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="K29">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L29">
         <v>1.01</v>
@@ -7978,25 +7978,25 @@
         <v>1.01</v>
       </c>
       <c r="N29">
-        <v>2.14</v>
+        <v>2.96</v>
       </c>
       <c r="O29">
         <v>1.21</v>
       </c>
       <c r="P29">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="Q29">
-        <v>1.65</v>
+        <v>1.72</v>
       </c>
       <c r="R29">
-        <v>1.41</v>
+        <v>1.44</v>
       </c>
       <c r="S29">
-        <v>1.65</v>
+        <v>2.66</v>
       </c>
       <c r="T29">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="U29">
         <v>2.3</v>
@@ -8196,13 +8196,13 @@
         <v>232</v>
       </c>
       <c r="F30">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="G30">
         <v>4.1</v>
       </c>
       <c r="H30">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="I30">
         <v>1.93</v>
@@ -8211,7 +8211,7 @@
         <v>4.2</v>
       </c>
       <c r="K30">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L30">
         <v>1.01</v>
@@ -8223,37 +8223,37 @@
         <v>5.4</v>
       </c>
       <c r="O30">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P30">
-        <v>2.4</v>
+        <v>2.44</v>
       </c>
       <c r="Q30">
-        <v>1.53</v>
+        <v>1.58</v>
       </c>
       <c r="R30">
-        <v>1.56</v>
+        <v>1.6</v>
       </c>
       <c r="S30">
-        <v>2.36</v>
+        <v>2.46</v>
       </c>
       <c r="T30">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="U30">
-        <v>2.3</v>
+        <v>2.5</v>
       </c>
       <c r="V30">
         <v>2.06</v>
       </c>
       <c r="W30">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="X30">
         <v>28</v>
       </c>
       <c r="Y30">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z30">
         <v>14.5</v>
@@ -8262,10 +8262,10 @@
         <v>23</v>
       </c>
       <c r="AB30">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC30">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AD30">
         <v>11</v>
@@ -8277,7 +8277,7 @@
         <v>38</v>
       </c>
       <c r="AG30">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AH30">
         <v>18.5</v>
@@ -8286,7 +8286,7 @@
         <v>29</v>
       </c>
       <c r="AJ30">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AK30">
         <v>44</v>
@@ -8298,7 +8298,7 @@
         <v>70</v>
       </c>
       <c r="AN30">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AO30">
         <v>9.199999999999999</v>
@@ -8307,25 +8307,25 @@
         <v>18</v>
       </c>
       <c r="AQ30">
+        <v>11.5</v>
+      </c>
+      <c r="AR30">
         <v>11</v>
-      </c>
-      <c r="AR30">
-        <v>11.5</v>
       </c>
       <c r="AS30">
         <v>19.5</v>
       </c>
       <c r="AT30">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AU30">
-        <v>8.6</v>
+        <v>8</v>
       </c>
       <c r="AV30">
         <v>9.6</v>
       </c>
       <c r="AW30">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AX30">
         <v>26</v>
@@ -8340,7 +8340,7 @@
         <v>19</v>
       </c>
       <c r="BB30">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BC30">
         <v>28</v>
@@ -8349,7 +8349,7 @@
         <v>30</v>
       </c>
       <c r="BE30">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="BF30">
         <v>21</v>
@@ -8441,7 +8441,7 @@
         <v>2.4</v>
       </c>
       <c r="G31">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="H31">
         <v>3.05</v>
@@ -8450,19 +8450,19 @@
         <v>3.35</v>
       </c>
       <c r="J31">
-        <v>3.35</v>
+        <v>3.25</v>
       </c>
       <c r="K31">
         <v>3.7</v>
       </c>
       <c r="L31">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M31">
         <v>1.01</v>
       </c>
       <c r="N31">
-        <v>2.2</v>
+        <v>3.25</v>
       </c>
       <c r="O31">
         <v>1.31</v>
@@ -8471,13 +8471,13 @@
         <v>1.86</v>
       </c>
       <c r="Q31">
-        <v>1.9</v>
+        <v>1.96</v>
       </c>
       <c r="R31">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="S31">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="T31">
         <v>1.71</v>
@@ -8489,7 +8489,7 @@
         <v>1.42</v>
       </c>
       <c r="W31">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="X31">
         <v>1000</v>
@@ -8683,13 +8683,13 @@
         <v>1.04</v>
       </c>
       <c r="G32">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H32">
         <v>1.04</v>
       </c>
       <c r="I32">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J32">
         <v>1.04</v>
@@ -8704,19 +8704,19 @@
         <v>1.01</v>
       </c>
       <c r="N32">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="O32">
-        <v>1.36</v>
+        <v>1.02</v>
       </c>
       <c r="P32">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="Q32">
         <v>1.38</v>
       </c>
       <c r="R32">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="S32">
         <v>1.38</v>
@@ -8925,19 +8925,19 @@
         <v>1.85</v>
       </c>
       <c r="G33">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="H33">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="I33">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="J33">
-        <v>3.75</v>
+        <v>4</v>
       </c>
       <c r="K33">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="L33">
         <v>1.01</v>
@@ -8958,16 +8958,16 @@
         <v>1.59</v>
       </c>
       <c r="R33">
-        <v>1.47</v>
+        <v>1.5</v>
       </c>
       <c r="S33">
-        <v>2.04</v>
+        <v>2.22</v>
       </c>
       <c r="T33">
-        <v>1.46</v>
+        <v>1.01</v>
       </c>
       <c r="U33">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="V33">
         <v>1.29</v>
@@ -9176,40 +9176,40 @@
         <v>2.34</v>
       </c>
       <c r="J34">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="K34">
         <v>3.8</v>
       </c>
       <c r="L34">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M34">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N34">
         <v>3.25</v>
       </c>
       <c r="O34">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="P34">
         <v>1.78</v>
       </c>
       <c r="Q34">
-        <v>2.04</v>
+        <v>2</v>
       </c>
       <c r="R34">
-        <v>1.26</v>
+        <v>1.3</v>
       </c>
       <c r="S34">
         <v>3.6</v>
       </c>
       <c r="T34">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="U34">
-        <v>1.01</v>
+        <v>1.9</v>
       </c>
       <c r="V34">
         <v>1.74</v>
@@ -9218,58 +9218,58 @@
         <v>1.31</v>
       </c>
       <c r="X34">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Y34">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="Z34">
-        <v>18.5</v>
+        <v>14</v>
       </c>
       <c r="AA34">
-        <v>40</v>
+        <v>30</v>
       </c>
       <c r="AB34">
-        <v>17.5</v>
+        <v>14</v>
       </c>
       <c r="AC34">
-        <v>10.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD34">
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="AE34">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="AF34">
-        <v>38</v>
+        <v>28</v>
       </c>
       <c r="AG34">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="AH34">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="AI34">
+        <v>44</v>
+      </c>
+      <c r="AJ34">
+        <v>85</v>
+      </c>
+      <c r="AK34">
         <v>55</v>
       </c>
-      <c r="AJ34">
-        <v>100</v>
-      </c>
-      <c r="AK34">
-        <v>70</v>
-      </c>
       <c r="AL34">
-        <v>85</v>
+        <v>65</v>
       </c>
       <c r="AM34">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN34">
-        <v>75</v>
+        <v>60</v>
       </c>
       <c r="AO34">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="AP34">
         <v>9.800000000000001</v>
@@ -9287,7 +9287,7 @@
         <v>10</v>
       </c>
       <c r="AU34">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="AV34">
         <v>8.6</v>
@@ -9317,7 +9317,7 @@
         <v>44</v>
       </c>
       <c r="BE34">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="BF34">
         <v>40</v>
@@ -9406,22 +9406,22 @@
         <v>237</v>
       </c>
       <c r="F35">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="G35">
-        <v>1.64</v>
+        <v>1.54</v>
       </c>
       <c r="H35">
-        <v>5.1</v>
+        <v>3.65</v>
       </c>
       <c r="I35">
-        <v>130</v>
+        <v>13.5</v>
       </c>
       <c r="J35">
-        <v>1.03</v>
+        <v>4.5</v>
       </c>
       <c r="K35">
-        <v>5.3</v>
+        <v>950</v>
       </c>
       <c r="L35">
         <v>1.01</v>
@@ -9430,22 +9430,22 @@
         <v>1.01</v>
       </c>
       <c r="N35">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="O35">
         <v>1.19</v>
       </c>
       <c r="P35">
-        <v>2.12</v>
+        <v>2.24</v>
       </c>
       <c r="Q35">
-        <v>1.28</v>
+        <v>1.61</v>
       </c>
       <c r="R35">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S35">
-        <v>2.38</v>
+        <v>2.52</v>
       </c>
       <c r="T35">
         <v>1.01</v>
@@ -9454,10 +9454,10 @@
         <v>1.01</v>
       </c>
       <c r="V35">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="W35">
-        <v>2.56</v>
+        <v>2.84</v>
       </c>
       <c r="X35">
         <v>1000</v>
@@ -9654,13 +9654,13 @@
         <v>6.2</v>
       </c>
       <c r="H36">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="I36">
         <v>1.69</v>
       </c>
       <c r="J36">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K36">
         <v>4.3</v>
@@ -9669,31 +9669,31 @@
         <v>1.01</v>
       </c>
       <c r="M36">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="N36">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="O36">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P36">
-        <v>1.92</v>
+        <v>1.95</v>
       </c>
       <c r="Q36">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R36">
-        <v>1.18</v>
+        <v>1.37</v>
       </c>
       <c r="S36">
-        <v>2.1</v>
+        <v>3.2</v>
       </c>
       <c r="T36">
-        <v>1.04</v>
+        <v>1.84</v>
       </c>
       <c r="U36">
-        <v>1.87</v>
+        <v>1.98</v>
       </c>
       <c r="V36">
         <v>2.44</v>
@@ -9702,46 +9702,46 @@
         <v>1.19</v>
       </c>
       <c r="X36">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="Y36">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Z36">
         <v>10.5</v>
       </c>
-      <c r="Z36">
-        <v>11.5</v>
-      </c>
       <c r="AA36">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="AB36">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="AC36">
+        <v>9.4</v>
+      </c>
+      <c r="AD36">
         <v>10.5</v>
       </c>
-      <c r="AD36">
-        <v>11.5</v>
-      </c>
       <c r="AE36">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AF36">
         <v>55</v>
       </c>
       <c r="AG36">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AH36">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="AI36">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AJ36">
         <v>190</v>
       </c>
       <c r="AK36">
-        <v>100</v>
+        <v>85</v>
       </c>
       <c r="AL36">
         <v>110</v>
@@ -9750,64 +9750,64 @@
         <v>160</v>
       </c>
       <c r="AN36">
-        <v>130</v>
+        <v>100</v>
       </c>
       <c r="AO36">
+        <v>13</v>
+      </c>
+      <c r="AP36">
         <v>13.5</v>
       </c>
-      <c r="AP36">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AQ36">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AR36">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AS36">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AT36">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU36">
-        <v>7.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AV36">
         <v>8.6</v>
       </c>
       <c r="AW36">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AX36">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AY36">
-        <v>17.5</v>
+        <v>19.5</v>
       </c>
       <c r="AZ36">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA36">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BB36">
-        <v>4.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BC36">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="BD36">
-        <v>4.6</v>
+        <v>10</v>
       </c>
       <c r="BE36">
-        <v>4.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF36">
-        <v>4.6</v>
+        <v>10.5</v>
       </c>
       <c r="BG36">
-        <v>7.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH36">
         <v>1000</v>
@@ -9893,7 +9893,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="G37">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="H37">
         <v>1.51</v>
@@ -9908,28 +9908,28 @@
         <v>4.5</v>
       </c>
       <c r="L37">
-        <v>1.41</v>
+        <v>1.45</v>
       </c>
       <c r="M37">
         <v>1.08</v>
       </c>
       <c r="N37">
-        <v>3.55</v>
+        <v>3.65</v>
       </c>
       <c r="O37">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="P37">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="Q37">
         <v>2.08</v>
       </c>
       <c r="R37">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="S37">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="T37">
         <v>2.28</v>
@@ -9980,10 +9980,10 @@
         <v>55</v>
       </c>
       <c r="AJ37">
-        <v>390</v>
+        <v>380</v>
       </c>
       <c r="AK37">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AL37">
         <v>160</v>
@@ -9992,19 +9992,19 @@
         <v>240</v>
       </c>
       <c r="AN37">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="AO37">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AP37">
         <v>12</v>
       </c>
       <c r="AQ37">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR37">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="AS37">
         <v>11.5</v>
@@ -10025,7 +10025,7 @@
         <v>32</v>
       </c>
       <c r="AY37">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AZ37">
         <v>27</v>
@@ -10034,19 +10034,19 @@
         <v>42</v>
       </c>
       <c r="BB37">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="BC37">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BD37">
+        <v>20</v>
+      </c>
+      <c r="BE37">
         <v>21</v>
       </c>
-      <c r="BE37">
-        <v>17.5</v>
-      </c>
       <c r="BF37">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BG37">
         <v>8.6</v>
@@ -10061,55 +10061,55 @@
         <v>1000</v>
       </c>
       <c r="BK37">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="BL37">
         <v>1000</v>
       </c>
       <c r="BM37">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BN37">
         <v>1000</v>
       </c>
       <c r="BO37">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="BP37">
         <v>1000</v>
       </c>
       <c r="BQ37">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BR37">
         <v>1000</v>
       </c>
       <c r="BS37">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT37">
         <v>1000</v>
       </c>
       <c r="BU37">
-        <v>2.68</v>
+        <v>1.01</v>
       </c>
       <c r="BV37">
         <v>1000</v>
       </c>
       <c r="BW37">
-        <v>5.2</v>
+        <v>1.01</v>
       </c>
       <c r="BX37">
         <v>1000</v>
       </c>
       <c r="BY37">
-        <v>12.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ37">
         <v>1000</v>
       </c>
       <c r="CA37">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="CB37" t="s">
         <v>270</v>
@@ -10132,22 +10132,22 @@
         <v>240</v>
       </c>
       <c r="F38">
-        <v>1.04</v>
+        <v>1.14</v>
       </c>
       <c r="G38">
-        <v>110</v>
+        <v>1.32</v>
       </c>
       <c r="H38">
-        <v>1.06</v>
+        <v>12</v>
       </c>
       <c r="I38">
-        <v>1000</v>
+        <v>660</v>
       </c>
       <c r="J38">
-        <v>1.06</v>
+        <v>6.2</v>
       </c>
       <c r="K38">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="L38">
         <v>1.01</v>
@@ -10156,22 +10156,22 @@
         <v>1.01</v>
       </c>
       <c r="N38">
-        <v>1.26</v>
+        <v>2.66</v>
       </c>
       <c r="O38">
         <v>1.11</v>
       </c>
       <c r="P38">
-        <v>1.25</v>
+        <v>2.66</v>
       </c>
       <c r="Q38">
-        <v>1.11</v>
+        <v>1.33</v>
       </c>
       <c r="R38">
-        <v>1.18</v>
+        <v>1.58</v>
       </c>
       <c r="S38">
-        <v>1.01</v>
+        <v>1.7</v>
       </c>
       <c r="T38">
         <v>1.01</v>
@@ -10183,7 +10183,7 @@
         <v>1.01</v>
       </c>
       <c r="W38">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="X38">
         <v>1000</v>
@@ -10389,10 +10389,10 @@
         <v>3.45</v>
       </c>
       <c r="K39">
-        <v>3.7</v>
+        <v>4</v>
       </c>
       <c r="L39">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="M39">
         <v>1.07</v>
@@ -10619,19 +10619,19 @@
         <v>3.75</v>
       </c>
       <c r="G40">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="H40">
         <v>1.97</v>
       </c>
       <c r="I40">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="J40">
-        <v>3.1</v>
+        <v>2.8</v>
       </c>
       <c r="K40">
-        <v>3.55</v>
+        <v>4.4</v>
       </c>
       <c r="L40">
         <v>1.01</v>
@@ -10640,10 +10640,10 @@
         <v>1.07</v>
       </c>
       <c r="N40">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="O40">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="P40">
         <v>1.51</v>
@@ -10655,7 +10655,7 @@
         <v>1.18</v>
       </c>
       <c r="S40">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="T40">
         <v>1.01</v>
@@ -10664,7 +10664,7 @@
         <v>1.01</v>
       </c>
       <c r="V40">
-        <v>1.73</v>
+        <v>1.71</v>
       </c>
       <c r="W40">
         <v>1.2</v>
@@ -10858,28 +10858,28 @@
         <v>243</v>
       </c>
       <c r="F41">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G41">
-        <v>1.93</v>
+        <v>1.81</v>
       </c>
       <c r="H41">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="I41">
-        <v>8.4</v>
+        <v>7.4</v>
       </c>
       <c r="J41">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K41">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="L41">
-        <v>1.01</v>
+        <v>1.36</v>
       </c>
       <c r="M41">
-        <v>1.08</v>
+        <v>1.06</v>
       </c>
       <c r="N41">
         <v>1.01</v>
@@ -10888,16 +10888,16 @@
         <v>1.35</v>
       </c>
       <c r="P41">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="Q41">
-        <v>2.16</v>
+        <v>1.58</v>
       </c>
       <c r="R41">
-        <v>1.12</v>
+        <v>1.28</v>
       </c>
       <c r="S41">
-        <v>2.16</v>
+        <v>4.1</v>
       </c>
       <c r="T41">
         <v>1.01</v>
@@ -10909,7 +10909,7 @@
         <v>1.16</v>
       </c>
       <c r="W41">
-        <v>2.08</v>
+        <v>2.22</v>
       </c>
       <c r="X41">
         <v>1000</v>
@@ -11100,10 +11100,10 @@
         <v>244</v>
       </c>
       <c r="F42">
-        <v>1.73</v>
+        <v>1.76</v>
       </c>
       <c r="G42">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="H42">
         <v>5.6</v>
@@ -11115,13 +11115,13 @@
         <v>3.75</v>
       </c>
       <c r="K42">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L42">
         <v>1.01</v>
       </c>
       <c r="M42">
-        <v>1.05</v>
+        <v>1.09</v>
       </c>
       <c r="N42">
         <v>3.15</v>
@@ -11133,7 +11133,7 @@
         <v>1.74</v>
       </c>
       <c r="Q42">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="R42">
         <v>1.28</v>
@@ -11145,40 +11145,40 @@
         <v>2.04</v>
       </c>
       <c r="U42">
-        <v>1.8</v>
+        <v>1.85</v>
       </c>
       <c r="V42">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W42">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="X42">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="Y42">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="Z42">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AA42">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="AB42">
         <v>7</v>
       </c>
       <c r="AC42">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD42">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AE42">
-        <v>120</v>
+        <v>95</v>
       </c>
       <c r="AF42">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG42">
         <v>10</v>
@@ -11199,13 +11199,13 @@
         <v>44</v>
       </c>
       <c r="AM42">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AN42">
         <v>14.5</v>
       </c>
       <c r="AO42">
-        <v>170</v>
+        <v>140</v>
       </c>
       <c r="AP42">
         <v>11</v>
@@ -11214,13 +11214,13 @@
         <v>15</v>
       </c>
       <c r="AR42">
-        <v>38</v>
+        <v>13</v>
       </c>
       <c r="AS42">
-        <v>4.7</v>
+        <v>15.5</v>
       </c>
       <c r="AT42">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AU42">
         <v>7.8</v>
@@ -11229,37 +11229,37 @@
         <v>20</v>
       </c>
       <c r="AW42">
-        <v>4.7</v>
+        <v>14.5</v>
       </c>
       <c r="AX42">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY42">
         <v>9.199999999999999</v>
       </c>
       <c r="AZ42">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BA42">
-        <v>4.7</v>
+        <v>15</v>
       </c>
       <c r="BB42">
         <v>16.5</v>
       </c>
       <c r="BC42">
-        <v>7.4</v>
+        <v>18.5</v>
       </c>
       <c r="BD42">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="BE42">
-        <v>4.7</v>
+        <v>15.5</v>
       </c>
       <c r="BF42">
         <v>12.5</v>
       </c>
       <c r="BG42">
-        <v>4.7</v>
+        <v>15</v>
       </c>
       <c r="BH42">
         <v>1000</v>
@@ -11342,22 +11342,22 @@
         <v>245</v>
       </c>
       <c r="F43">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="G43">
-        <v>1.69</v>
+        <v>1.76</v>
       </c>
       <c r="H43">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I43">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J43">
-        <v>3.7</v>
+        <v>4.2</v>
       </c>
       <c r="K43">
-        <v>4.9</v>
+        <v>4.5</v>
       </c>
       <c r="L43">
         <v>1.01</v>
@@ -11366,7 +11366,7 @@
         <v>1.02</v>
       </c>
       <c r="N43">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="O43">
         <v>1.21</v>
@@ -11375,25 +11375,25 @@
         <v>2.16</v>
       </c>
       <c r="Q43">
-        <v>1.64</v>
+        <v>1.68</v>
       </c>
       <c r="R43">
-        <v>1.43</v>
+        <v>1.44</v>
       </c>
       <c r="S43">
-        <v>2.22</v>
+        <v>2.68</v>
       </c>
       <c r="T43">
-        <v>1.01</v>
+        <v>1.65</v>
       </c>
       <c r="U43">
         <v>1.01</v>
       </c>
       <c r="V43">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="W43">
-        <v>2.44</v>
+        <v>2.32</v>
       </c>
       <c r="X43">
         <v>1000</v>
@@ -11465,7 +11465,7 @@
         <v>1.06</v>
       </c>
       <c r="AU43">
-        <v>1.06</v>
+        <v>5.8</v>
       </c>
       <c r="AV43">
         <v>1.06</v>
@@ -11584,19 +11584,19 @@
         <v>246</v>
       </c>
       <c r="F44">
-        <v>1.94</v>
+        <v>1.95</v>
       </c>
       <c r="G44">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="H44">
-        <v>3.45</v>
+        <v>3.6</v>
       </c>
       <c r="I44">
+        <v>4</v>
+      </c>
+      <c r="J44">
         <v>4.1</v>
-      </c>
-      <c r="J44">
-        <v>4</v>
       </c>
       <c r="K44">
         <v>4.7</v>
@@ -11608,142 +11608,142 @@
         <v>1.01</v>
       </c>
       <c r="N44">
-        <v>2.42</v>
+        <v>5.7</v>
       </c>
       <c r="O44">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="P44">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="Q44">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="R44">
-        <v>1.26</v>
+        <v>1.64</v>
       </c>
       <c r="S44">
-        <v>1.8</v>
+        <v>2.32</v>
       </c>
       <c r="T44">
-        <v>1.01</v>
+        <v>1.53</v>
       </c>
       <c r="U44">
-        <v>1.01</v>
+        <v>2.56</v>
       </c>
       <c r="V44">
         <v>1.33</v>
       </c>
       <c r="W44">
-        <v>1.94</v>
+        <v>1.96</v>
       </c>
       <c r="X44">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="Y44">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Z44">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA44">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB44">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="AC44">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AD44">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AE44">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF44">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AG44">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH44">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AI44">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AJ44">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AK44">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL44">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AM44">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN44">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO44">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AP44">
+        <v>4.8</v>
+      </c>
+      <c r="AQ44">
+        <v>17.5</v>
+      </c>
+      <c r="AR44">
+        <v>4.9</v>
+      </c>
+      <c r="AS44">
+        <v>5.3</v>
+      </c>
+      <c r="AT44">
+        <v>12</v>
+      </c>
+      <c r="AU44">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AV44">
+        <v>13.5</v>
+      </c>
+      <c r="AW44">
+        <v>5.1</v>
+      </c>
+      <c r="AX44">
+        <v>13</v>
+      </c>
+      <c r="AY44">
+        <v>9.4</v>
+      </c>
+      <c r="AZ44">
+        <v>13</v>
+      </c>
+      <c r="BA44">
+        <v>5.1</v>
+      </c>
+      <c r="BB44">
         <v>20</v>
       </c>
-      <c r="AQ44">
-        <v>16</v>
-      </c>
-      <c r="AR44">
-        <v>22</v>
-      </c>
-      <c r="AS44">
-        <v>40</v>
-      </c>
-      <c r="AT44">
-        <v>10</v>
-      </c>
-      <c r="AU44">
-        <v>8.4</v>
-      </c>
-      <c r="AV44">
-        <v>11.5</v>
-      </c>
-      <c r="AW44">
-        <v>25</v>
-      </c>
-      <c r="AX44">
-        <v>11</v>
-      </c>
-      <c r="AY44">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AZ44">
-        <v>10.5</v>
-      </c>
-      <c r="BA44">
-        <v>25</v>
-      </c>
-      <c r="BB44">
-        <v>19</v>
-      </c>
       <c r="BC44">
-        <v>13.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD44">
+        <v>4.8</v>
+      </c>
+      <c r="BE44">
+        <v>5.3</v>
+      </c>
+      <c r="BF44">
+        <v>6.6</v>
+      </c>
+      <c r="BG44">
         <v>18</v>
-      </c>
-      <c r="BE44">
-        <v>34</v>
-      </c>
-      <c r="BF44">
-        <v>1.01</v>
-      </c>
-      <c r="BG44">
-        <v>1.01</v>
       </c>
       <c r="BH44">
         <v>1000</v>
@@ -11826,64 +11826,64 @@
         <v>247</v>
       </c>
       <c r="F45">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="G45">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="H45">
+        <v>5.4</v>
+      </c>
+      <c r="I45">
+        <v>6.6</v>
+      </c>
+      <c r="J45">
+        <v>4.7</v>
+      </c>
+      <c r="K45">
+        <v>5.1</v>
+      </c>
+      <c r="L45">
+        <v>1.01</v>
+      </c>
+      <c r="M45">
+        <v>1.01</v>
+      </c>
+      <c r="N45">
         <v>5.5</v>
       </c>
-      <c r="I45">
-        <v>7.8</v>
-      </c>
-      <c r="J45">
-        <v>4.4</v>
-      </c>
-      <c r="K45">
-        <v>5.2</v>
-      </c>
-      <c r="L45">
-        <v>1.01</v>
-      </c>
-      <c r="M45">
-        <v>1.01</v>
-      </c>
-      <c r="N45">
-        <v>6</v>
-      </c>
       <c r="O45">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="P45">
-        <v>2.46</v>
+        <v>2.54</v>
       </c>
       <c r="Q45">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="R45">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="S45">
-        <v>2.26</v>
+        <v>2.36</v>
       </c>
       <c r="T45">
-        <v>1.6</v>
+        <v>1.65</v>
       </c>
       <c r="U45">
         <v>1.01</v>
       </c>
       <c r="V45">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W45">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="X45">
         <v>1000</v>
       </c>
       <c r="Y45">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="Z45">
         <v>1000</v>
@@ -11901,7 +11901,7 @@
         <v>1000</v>
       </c>
       <c r="AE45">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="AF45">
         <v>1000</v>
@@ -11916,16 +11916,16 @@
         <v>1000</v>
       </c>
       <c r="AJ45">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AK45">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AL45">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AM45">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN45">
         <v>8.4</v>
@@ -11934,58 +11934,58 @@
         <v>1000</v>
       </c>
       <c r="AP45">
-        <v>1.13</v>
+        <v>1.43</v>
       </c>
       <c r="AQ45">
-        <v>1.13</v>
+        <v>1.37</v>
       </c>
       <c r="AR45">
-        <v>1.13</v>
+        <v>1.43</v>
       </c>
       <c r="AS45">
-        <v>1.13</v>
+        <v>1.43</v>
       </c>
       <c r="AT45">
-        <v>1.13</v>
+        <v>1.43</v>
       </c>
       <c r="AU45">
-        <v>1.13</v>
+        <v>1.43</v>
       </c>
       <c r="AV45">
-        <v>1.13</v>
+        <v>18</v>
       </c>
       <c r="AW45">
-        <v>1.13</v>
+        <v>1.41</v>
       </c>
       <c r="AX45">
-        <v>1.13</v>
+        <v>1.43</v>
       </c>
       <c r="AY45">
-        <v>1.13</v>
+        <v>8.4</v>
       </c>
       <c r="AZ45">
-        <v>1.13</v>
+        <v>1.43</v>
       </c>
       <c r="BA45">
-        <v>1.13</v>
+        <v>1.43</v>
       </c>
       <c r="BB45">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="BC45">
-        <v>1.13</v>
+        <v>1.33</v>
       </c>
       <c r="BD45">
-        <v>1.13</v>
+        <v>1.37</v>
       </c>
       <c r="BE45">
-        <v>1.13</v>
+        <v>1.41</v>
       </c>
       <c r="BF45">
-        <v>5.1</v>
+        <v>5.4</v>
       </c>
       <c r="BG45">
-        <v>1.13</v>
+        <v>1.43</v>
       </c>
       <c r="BH45">
         <v>1000</v>
@@ -12068,19 +12068,19 @@
         <v>248</v>
       </c>
       <c r="F46">
-        <v>1.14</v>
+        <v>1.44</v>
       </c>
       <c r="G46">
-        <v>1000</v>
+        <v>1.61</v>
       </c>
       <c r="H46">
-        <v>1.14</v>
+        <v>2.7</v>
       </c>
       <c r="I46">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="J46">
-        <v>1.06</v>
+        <v>2.7</v>
       </c>
       <c r="K46">
         <v>110</v>
@@ -12092,34 +12092,34 @@
         <v>1.01</v>
       </c>
       <c r="N46">
-        <v>1.25</v>
+        <v>2.56</v>
       </c>
       <c r="O46">
         <v>1.01</v>
       </c>
       <c r="P46">
-        <v>1.25</v>
+        <v>2.56</v>
       </c>
       <c r="Q46">
+        <v>1.45</v>
+      </c>
+      <c r="R46">
+        <v>1.63</v>
+      </c>
+      <c r="S46">
+        <v>2.16</v>
+      </c>
+      <c r="T46">
+        <v>1.01</v>
+      </c>
+      <c r="U46">
+        <v>1.01</v>
+      </c>
+      <c r="V46">
         <v>1.02</v>
       </c>
-      <c r="R46">
-        <v>1.24</v>
-      </c>
-      <c r="S46">
-        <v>1.02</v>
-      </c>
-      <c r="T46">
-        <v>1.01</v>
-      </c>
-      <c r="U46">
-        <v>1.01</v>
-      </c>
-      <c r="V46">
-        <v>1.01</v>
-      </c>
       <c r="W46">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="X46">
         <v>1000</v>
@@ -12310,10 +12310,10 @@
         <v>249</v>
       </c>
       <c r="F47">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="G47">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="H47">
         <v>7.4</v>
@@ -12325,7 +12325,7 @@
         <v>5.3</v>
       </c>
       <c r="K47">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="L47">
         <v>1.01</v>
@@ -12334,7 +12334,7 @@
         <v>1.01</v>
       </c>
       <c r="N47">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="O47">
         <v>1.15</v>
@@ -12343,22 +12343,22 @@
         <v>2.8</v>
       </c>
       <c r="Q47">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="R47">
         <v>1.72</v>
       </c>
       <c r="S47">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T47">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="U47">
         <v>2.18</v>
       </c>
       <c r="V47">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W47">
         <v>3.1</v>
@@ -12388,7 +12388,7 @@
         <v>110</v>
       </c>
       <c r="AF47">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AG47">
         <v>12.5</v>
@@ -12418,13 +12418,13 @@
         <v>100</v>
       </c>
       <c r="AP47">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AQ47">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AR47">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AS47">
         <v>5.4</v>
@@ -12436,10 +12436,10 @@
         <v>11</v>
       </c>
       <c r="AV47">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="AW47">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AX47">
         <v>9.4</v>
@@ -12463,13 +12463,13 @@
         <v>4.7</v>
       </c>
       <c r="BE47">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BF47">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="BG47">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="BH47">
         <v>1000</v>
@@ -12555,7 +12555,7 @@
         <v>2.24</v>
       </c>
       <c r="G48">
-        <v>2.26</v>
+        <v>2.28</v>
       </c>
       <c r="H48">
         <v>4.1</v>
@@ -12564,46 +12564,46 @@
         <v>4.3</v>
       </c>
       <c r="J48">
-        <v>3.15</v>
+        <v>3.05</v>
       </c>
       <c r="K48">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="L48">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="M48">
         <v>1.16</v>
       </c>
       <c r="N48">
-        <v>2.36</v>
+        <v>2.32</v>
       </c>
       <c r="O48">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="P48">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="Q48">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="R48">
         <v>1.15</v>
       </c>
       <c r="S48">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="T48">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="U48">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="V48">
         <v>1.3</v>
       </c>
       <c r="W48">
-        <v>1.8</v>
+        <v>1.78</v>
       </c>
       <c r="X48">
         <v>7.2</v>
@@ -12642,7 +12642,7 @@
         <v>150</v>
       </c>
       <c r="AJ48">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK48">
         <v>38</v>
@@ -12681,7 +12681,7 @@
         <v>18.5</v>
       </c>
       <c r="AW48">
-        <v>36</v>
+        <v>75</v>
       </c>
       <c r="AX48">
         <v>10.5</v>
@@ -12690,13 +12690,13 @@
         <v>12</v>
       </c>
       <c r="AZ48">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="BA48">
         <v>42</v>
       </c>
       <c r="BB48">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BC48">
         <v>34</v>
@@ -12708,70 +12708,70 @@
         <v>110</v>
       </c>
       <c r="BF48">
-        <v>36</v>
+        <v>23</v>
       </c>
       <c r="BG48">
         <v>42</v>
       </c>
       <c r="BH48">
-        <v>2.5</v>
+        <v>2.74</v>
       </c>
       <c r="BI48">
-        <v>1.01</v>
+        <v>2.04</v>
       </c>
       <c r="BJ48">
-        <v>36</v>
+        <v>13</v>
       </c>
       <c r="BK48">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL48">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="BM48">
-        <v>42</v>
+        <v>1.01</v>
       </c>
       <c r="BN48">
-        <v>10.5</v>
+        <v>4.8</v>
       </c>
       <c r="BO48">
-        <v>3.75</v>
+        <v>4.2</v>
       </c>
       <c r="BP48">
-        <v>42</v>
+        <v>21</v>
       </c>
       <c r="BQ48">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BR48">
-        <v>90</v>
+        <v>55</v>
       </c>
       <c r="BS48">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT48">
-        <v>17</v>
+        <v>7.6</v>
       </c>
       <c r="BU48">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BV48">
-        <v>75</v>
+        <v>50</v>
       </c>
       <c r="BW48">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX48">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="BY48">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BZ48">
-        <v>90</v>
+        <v>65</v>
       </c>
       <c r="CA48">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB48" t="s">
         <v>270</v>
@@ -12800,13 +12800,13 @@
         <v>3.05</v>
       </c>
       <c r="H49">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="I49">
         <v>2.7</v>
       </c>
       <c r="J49">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="K49">
         <v>3.6</v>
@@ -12815,13 +12815,13 @@
         <v>1.01</v>
       </c>
       <c r="M49">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N49">
-        <v>3.55</v>
+        <v>3.5</v>
       </c>
       <c r="O49">
-        <v>1.33</v>
+        <v>1.36</v>
       </c>
       <c r="P49">
         <v>1.88</v>
@@ -12830,16 +12830,16 @@
         <v>2.04</v>
       </c>
       <c r="R49">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S49">
-        <v>3.35</v>
+        <v>3.75</v>
       </c>
       <c r="T49">
-        <v>1.01</v>
+        <v>1.71</v>
       </c>
       <c r="U49">
-        <v>1.01</v>
+        <v>1.91</v>
       </c>
       <c r="V49">
         <v>1.59</v>
@@ -12848,106 +12848,106 @@
         <v>1.48</v>
       </c>
       <c r="X49">
-        <v>15</v>
+        <v>13.5</v>
       </c>
       <c r="Y49">
+        <v>10.5</v>
+      </c>
+      <c r="Z49">
+        <v>17.5</v>
+      </c>
+      <c r="AA49">
+        <v>40</v>
+      </c>
+      <c r="AB49">
+        <v>11</v>
+      </c>
+      <c r="AC49">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AD49">
+        <v>12.5</v>
+      </c>
+      <c r="AE49">
+        <v>32</v>
+      </c>
+      <c r="AF49">
+        <v>28</v>
+      </c>
+      <c r="AG49">
         <v>13</v>
       </c>
-      <c r="Z49">
-        <v>19.5</v>
-      </c>
-      <c r="AA49">
+      <c r="AH49">
+        <v>19</v>
+      </c>
+      <c r="AI49">
         <v>46</v>
       </c>
-      <c r="AB49">
-        <v>14.5</v>
-      </c>
-      <c r="AC49">
-        <v>9</v>
-      </c>
-      <c r="AD49">
-        <v>14</v>
-      </c>
-      <c r="AE49">
-        <v>34</v>
-      </c>
-      <c r="AF49">
-        <v>23</v>
-      </c>
-      <c r="AG49">
-        <v>15.5</v>
-      </c>
-      <c r="AH49">
-        <v>21</v>
-      </c>
-      <c r="AI49">
-        <v>50</v>
-      </c>
       <c r="AJ49">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="AK49">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AL49">
-        <v>55</v>
+        <v>48</v>
       </c>
       <c r="AM49">
         <v>110</v>
       </c>
       <c r="AN49">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AO49">
-        <v>30</v>
+        <v>27</v>
       </c>
       <c r="AP49">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AQ49">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR49">
-        <v>12.5</v>
+        <v>14.5</v>
       </c>
       <c r="AS49">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="AT49">
         <v>9.199999999999999</v>
       </c>
       <c r="AU49">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="AV49">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AW49">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AX49">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AY49">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AZ49">
-        <v>14.5</v>
+        <v>16.5</v>
       </c>
       <c r="BA49">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="BB49">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="BC49">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="BD49">
-        <v>36</v>
+        <v>11</v>
       </c>
       <c r="BE49">
-        <v>4.8</v>
+        <v>12.5</v>
       </c>
       <c r="BF49">
         <v>23</v>
@@ -13036,22 +13036,22 @@
         <v>252</v>
       </c>
       <c r="F50">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="G50">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="H50">
         <v>4.1</v>
       </c>
       <c r="I50">
-        <v>6.4</v>
+        <v>5.7</v>
       </c>
       <c r="J50">
-        <v>3.95</v>
+        <v>3.4</v>
       </c>
       <c r="K50">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="L50">
         <v>1.01</v>
@@ -13066,13 +13066,13 @@
         <v>1.15</v>
       </c>
       <c r="P50">
-        <v>2.34</v>
+        <v>2.6</v>
       </c>
       <c r="Q50">
-        <v>1.15</v>
+        <v>1.44</v>
       </c>
       <c r="R50">
-        <v>1.59</v>
+        <v>1.68</v>
       </c>
       <c r="S50">
         <v>2.12</v>
@@ -13084,7 +13084,7 @@
         <v>1.01</v>
       </c>
       <c r="V50">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="W50">
         <v>2.14</v>
@@ -13281,20 +13281,20 @@
         <v>1.45</v>
       </c>
       <c r="G51">
-        <v>1.71</v>
+        <v>1.78</v>
       </c>
       <c r="H51">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="I51">
+        <v>7.6</v>
+      </c>
+      <c r="J51">
+        <v>4.2</v>
+      </c>
+      <c r="K51">
         <v>12.5</v>
       </c>
-      <c r="J51">
-        <v>4.4</v>
-      </c>
-      <c r="K51">
-        <v>13</v>
-      </c>
       <c r="L51">
         <v>1.01</v>
       </c>
@@ -13302,19 +13302,19 @@
         <v>1.01</v>
       </c>
       <c r="N51">
-        <v>1.95</v>
+        <v>3.05</v>
       </c>
       <c r="O51">
         <v>1.06</v>
       </c>
       <c r="P51">
-        <v>1.94</v>
+        <v>3.05</v>
       </c>
       <c r="Q51">
-        <v>1.06</v>
+        <v>1.25</v>
       </c>
       <c r="R51">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="S51">
         <v>1.64</v>
@@ -13326,10 +13326,10 @@
         <v>1.01</v>
       </c>
       <c r="V51">
-        <v>1.09</v>
+        <v>1.15</v>
       </c>
       <c r="W51">
-        <v>2.4</v>
+        <v>2.28</v>
       </c>
       <c r="X51">
         <v>1000</v>
@@ -13523,19 +13523,19 @@
         <v>1.53</v>
       </c>
       <c r="G52">
-        <v>1.81</v>
+        <v>1.72</v>
       </c>
       <c r="H52">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I52">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="J52">
         <v>4.6</v>
       </c>
       <c r="K52">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="L52">
         <v>1.01</v>
@@ -13544,22 +13544,22 @@
         <v>1.01</v>
       </c>
       <c r="N52">
-        <v>2.08</v>
+        <v>2.98</v>
       </c>
       <c r="O52">
         <v>1.09</v>
       </c>
       <c r="P52">
-        <v>2.08</v>
+        <v>2.98</v>
       </c>
       <c r="Q52">
-        <v>1.09</v>
+        <v>1.35</v>
       </c>
       <c r="R52">
-        <v>1.87</v>
+        <v>1.79</v>
       </c>
       <c r="S52">
-        <v>1.09</v>
+        <v>1.89</v>
       </c>
       <c r="T52">
         <v>1.01</v>
@@ -13568,10 +13568,10 @@
         <v>1.01</v>
       </c>
       <c r="V52">
-        <v>1.14</v>
+        <v>1.17</v>
       </c>
       <c r="W52">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="X52">
         <v>1000</v>
@@ -13780,7 +13780,7 @@
         <v>4.4</v>
       </c>
       <c r="L53">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M53">
         <v>1.09</v>
@@ -13789,13 +13789,13 @@
         <v>2.58</v>
       </c>
       <c r="O53">
-        <v>1.34</v>
+        <v>1.43</v>
       </c>
       <c r="P53">
         <v>1.65</v>
       </c>
       <c r="Q53">
-        <v>2.22</v>
+        <v>2.26</v>
       </c>
       <c r="R53">
         <v>1.2</v>
@@ -14013,43 +14013,43 @@
         <v>2</v>
       </c>
       <c r="I54">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="J54">
         <v>3.9</v>
       </c>
       <c r="K54">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L54">
         <v>1.01</v>
       </c>
       <c r="M54">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N54">
-        <v>1.97</v>
+        <v>5.1</v>
       </c>
       <c r="O54">
         <v>1.15</v>
       </c>
       <c r="P54">
-        <v>1.97</v>
+        <v>2.52</v>
       </c>
       <c r="Q54">
-        <v>1.15</v>
+        <v>1.51</v>
       </c>
       <c r="R54">
-        <v>1.18</v>
+        <v>1.61</v>
       </c>
       <c r="S54">
-        <v>1.74</v>
+        <v>2.08</v>
       </c>
       <c r="T54">
         <v>1.01</v>
       </c>
       <c r="U54">
-        <v>1.01</v>
+        <v>2.4</v>
       </c>
       <c r="V54">
         <v>1.76</v>
@@ -14058,112 +14058,112 @@
         <v>1.36</v>
       </c>
       <c r="X54">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="Y54">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="Z54">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AA54">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AB54">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AC54">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AD54">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AE54">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AF54">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG54">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AH54">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AI54">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AJ54">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AK54">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AL54">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AM54">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AN54">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO54">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="AP54">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AQ54">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR54">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AS54">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="AT54">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AU54">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AV54">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AW54">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AX54">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="AY54">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AZ54">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BA54">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BB54">
-        <v>1.01</v>
+        <v>48</v>
       </c>
       <c r="BC54">
-        <v>1.01</v>
+        <v>28</v>
       </c>
       <c r="BD54">
-        <v>1.01</v>
+        <v>29</v>
       </c>
       <c r="BE54">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BF54">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="BG54">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH54">
         <v>1000</v>
@@ -14246,7 +14246,7 @@
         <v>257</v>
       </c>
       <c r="F55">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="G55">
         <v>1.49</v>
@@ -14258,7 +14258,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="J55">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="K55">
         <v>5</v>
@@ -14294,7 +14294,7 @@
         <v>1.84</v>
       </c>
       <c r="V55">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="W55">
         <v>3</v>
@@ -14336,7 +14336,7 @@
         <v>150</v>
       </c>
       <c r="AJ55">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AK55">
         <v>19</v>
@@ -14354,7 +14354,7 @@
         <v>220</v>
       </c>
       <c r="AP55">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AQ55">
         <v>23</v>
@@ -14363,7 +14363,7 @@
         <v>60</v>
       </c>
       <c r="AS55">
-        <v>8.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AT55">
         <v>7.2</v>
@@ -14375,7 +14375,7 @@
         <v>27</v>
       </c>
       <c r="AW55">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="AX55">
         <v>7.6</v>
@@ -14387,7 +14387,7 @@
         <v>24</v>
       </c>
       <c r="BA55">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BB55">
         <v>11.5</v>
@@ -14399,13 +14399,13 @@
         <v>34</v>
       </c>
       <c r="BE55">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BF55">
         <v>7</v>
       </c>
       <c r="BG55">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH55">
         <v>1000</v>
@@ -14503,19 +14503,19 @@
         <v>3.85</v>
       </c>
       <c r="K56">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L56">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M56">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N56">
-        <v>2.16</v>
+        <v>4.4</v>
       </c>
       <c r="O56">
-        <v>1.22</v>
+        <v>1.25</v>
       </c>
       <c r="P56">
         <v>2.16</v>
@@ -14524,16 +14524,16 @@
         <v>1.74</v>
       </c>
       <c r="R56">
-        <v>1.38</v>
+        <v>1.47</v>
       </c>
       <c r="S56">
-        <v>2.5</v>
+        <v>2.84</v>
       </c>
       <c r="T56">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="U56">
-        <v>1.89</v>
+        <v>2.32</v>
       </c>
       <c r="V56">
         <v>1.84</v>
@@ -14542,112 +14542,112 @@
         <v>1.36</v>
       </c>
       <c r="X56">
+        <v>18.5</v>
+      </c>
+      <c r="Y56">
+        <v>12</v>
+      </c>
+      <c r="Z56">
+        <v>15</v>
+      </c>
+      <c r="AA56">
+        <v>26</v>
+      </c>
+      <c r="AB56">
+        <v>17</v>
+      </c>
+      <c r="AC56">
+        <v>9</v>
+      </c>
+      <c r="AD56">
+        <v>11</v>
+      </c>
+      <c r="AE56">
         <v>21</v>
       </c>
-      <c r="Y56">
+      <c r="AF56">
+        <v>29</v>
+      </c>
+      <c r="AG56">
+        <v>15.5</v>
+      </c>
+      <c r="AH56">
+        <v>16.5</v>
+      </c>
+      <c r="AI56">
+        <v>32</v>
+      </c>
+      <c r="AJ56">
+        <v>70</v>
+      </c>
+      <c r="AK56">
+        <v>40</v>
+      </c>
+      <c r="AL56">
+        <v>46</v>
+      </c>
+      <c r="AM56">
+        <v>80</v>
+      </c>
+      <c r="AN56">
+        <v>34</v>
+      </c>
+      <c r="AO56">
+        <v>13</v>
+      </c>
+      <c r="AP56">
+        <v>16</v>
+      </c>
+      <c r="AQ56">
+        <v>10</v>
+      </c>
+      <c r="AR56">
+        <v>13</v>
+      </c>
+      <c r="AS56">
+        <v>23</v>
+      </c>
+      <c r="AT56">
+        <v>15</v>
+      </c>
+      <c r="AU56">
+        <v>7.8</v>
+      </c>
+      <c r="AV56">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AW56">
+        <v>18</v>
+      </c>
+      <c r="AX56">
+        <v>24</v>
+      </c>
+      <c r="AY56">
+        <v>13.5</v>
+      </c>
+      <c r="AZ56">
         <v>14.5</v>
       </c>
-      <c r="Z56">
-        <v>17</v>
-      </c>
-      <c r="AA56">
-        <v>30</v>
-      </c>
-      <c r="AB56">
-        <v>21</v>
-      </c>
-      <c r="AC56">
-        <v>10</v>
-      </c>
-      <c r="AD56">
-        <v>12</v>
-      </c>
-      <c r="AE56">
-        <v>24</v>
-      </c>
-      <c r="AF56">
-        <v>32</v>
-      </c>
-      <c r="AG56">
-        <v>17.5</v>
-      </c>
-      <c r="AH56">
-        <v>19</v>
-      </c>
-      <c r="AI56">
-        <v>36</v>
-      </c>
-      <c r="AJ56">
-        <v>80</v>
-      </c>
-      <c r="AK56">
-        <v>46</v>
-      </c>
-      <c r="AL56">
-        <v>50</v>
-      </c>
-      <c r="AM56">
-        <v>90</v>
-      </c>
-      <c r="AN56">
+      <c r="BA56">
+        <v>27</v>
+      </c>
+      <c r="BB56">
+        <v>55</v>
+      </c>
+      <c r="BC56">
+        <v>34</v>
+      </c>
+      <c r="BD56">
         <v>38</v>
       </c>
-      <c r="AO56">
-        <v>16</v>
-      </c>
-      <c r="AP56">
-        <v>4.1</v>
-      </c>
-      <c r="AQ56">
-        <v>9.6</v>
-      </c>
-      <c r="AR56">
-        <v>11</v>
-      </c>
-      <c r="AS56">
-        <v>21</v>
-      </c>
-      <c r="AT56">
-        <v>13.5</v>
-      </c>
-      <c r="AU56">
-        <v>7.6</v>
-      </c>
-      <c r="AV56">
-        <v>9</v>
-      </c>
-      <c r="AW56">
-        <v>16.5</v>
-      </c>
-      <c r="AX56">
-        <v>21</v>
-      </c>
-      <c r="AY56">
-        <v>12</v>
-      </c>
-      <c r="AZ56">
-        <v>13.5</v>
-      </c>
-      <c r="BA56">
-        <v>24</v>
-      </c>
-      <c r="BB56">
-        <v>4.8</v>
-      </c>
-      <c r="BC56">
-        <v>29</v>
-      </c>
-      <c r="BD56">
-        <v>34</v>
-      </c>
       <c r="BE56">
-        <v>4.8</v>
+        <v>60</v>
       </c>
       <c r="BF56">
         <v>22</v>
       </c>
       <c r="BG56">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BH56">
         <v>1000</v>
@@ -14733,16 +14733,16 @@
         <v>1.81</v>
       </c>
       <c r="G57">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="H57">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I57">
         <v>5.7</v>
       </c>
       <c r="J57">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="K57">
         <v>3.65</v>
@@ -14754,7 +14754,7 @@
         <v>1.09</v>
       </c>
       <c r="N57">
-        <v>2.94</v>
+        <v>2.88</v>
       </c>
       <c r="O57">
         <v>1.41</v>
@@ -14772,16 +14772,16 @@
         <v>4.2</v>
       </c>
       <c r="T57">
-        <v>1.85</v>
+        <v>1.99</v>
       </c>
       <c r="U57">
-        <v>1.82</v>
+        <v>1.79</v>
       </c>
       <c r="V57">
         <v>1.21</v>
       </c>
       <c r="W57">
-        <v>1.94</v>
+        <v>1.98</v>
       </c>
       <c r="X57">
         <v>13.5</v>
@@ -14799,7 +14799,7 @@
         <v>7.6</v>
       </c>
       <c r="AC57">
-        <v>9.6</v>
+        <v>8.6</v>
       </c>
       <c r="AD57">
         <v>25</v>
@@ -14808,10 +14808,10 @@
         <v>100</v>
       </c>
       <c r="AF57">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AG57">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH57">
         <v>27</v>
@@ -14820,7 +14820,7 @@
         <v>110</v>
       </c>
       <c r="AJ57">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK57">
         <v>29</v>
@@ -14871,7 +14871,7 @@
         <v>16.5</v>
       </c>
       <c r="BA57">
-        <v>1.01</v>
+        <v>65</v>
       </c>
       <c r="BB57">
         <v>16</v>
@@ -14880,10 +14880,10 @@
         <v>17</v>
       </c>
       <c r="BD57">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="BE57">
-        <v>1.01</v>
+        <v>110</v>
       </c>
       <c r="BF57">
         <v>13.5</v>
@@ -14975,7 +14975,7 @@
         <v>4.5</v>
       </c>
       <c r="G58">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="H58">
         <v>1.86</v>
@@ -14987,19 +14987,19 @@
         <v>3.55</v>
       </c>
       <c r="K58">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="L58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M58">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="N58">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="O58">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="P58">
         <v>1.86</v>
@@ -15008,190 +15008,190 @@
         <v>2</v>
       </c>
       <c r="R58">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="S58">
-        <v>0</v>
+        <v>3.55</v>
       </c>
       <c r="T58">
-        <v>0</v>
+        <v>1.87</v>
       </c>
       <c r="U58">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="V58">
-        <v>0</v>
+        <v>2.06</v>
       </c>
       <c r="W58">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="X58">
-        <v>0</v>
+        <v>16.5</v>
       </c>
       <c r="Y58">
-        <v>0</v>
+        <v>8.6</v>
       </c>
       <c r="Z58">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="AA58">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="AB58">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="AC58">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AD58">
-        <v>0</v>
+        <v>12.5</v>
       </c>
       <c r="AE58">
-        <v>0</v>
+        <v>26</v>
       </c>
       <c r="AF58">
-        <v>0</v>
+        <v>44</v>
       </c>
       <c r="AG58">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="AH58">
-        <v>0</v>
+        <v>24</v>
       </c>
       <c r="AI58">
-        <v>0</v>
+        <v>40</v>
       </c>
       <c r="AJ58">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AK58">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AL58">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AM58">
-        <v>0</v>
+        <v>140</v>
       </c>
       <c r="AN58">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="AO58">
-        <v>0</v>
+        <v>14.5</v>
       </c>
       <c r="AP58">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AQ58">
-        <v>0</v>
+        <v>6.4</v>
       </c>
       <c r="AR58">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="AS58">
-        <v>0</v>
+        <v>15.5</v>
       </c>
       <c r="AT58">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AU58">
-        <v>0</v>
+        <v>7.4</v>
       </c>
       <c r="AV58">
-        <v>0</v>
+        <v>7.6</v>
       </c>
       <c r="AW58">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="AX58">
-        <v>0</v>
+        <v>25</v>
       </c>
       <c r="AY58">
-        <v>0</v>
+        <v>13.5</v>
       </c>
       <c r="AZ58">
-        <v>0</v>
+        <v>14</v>
       </c>
       <c r="BA58">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="BB58">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="BC58">
-        <v>0</v>
+        <v>46</v>
       </c>
       <c r="BD58">
-        <v>0</v>
+        <v>48</v>
       </c>
       <c r="BE58">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="BF58">
-        <v>0</v>
+        <v>50</v>
       </c>
       <c r="BG58">
-        <v>0</v>
+        <v>10.5</v>
       </c>
       <c r="BH58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ58">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA58">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB58" t="s">
         <v>270</v>
@@ -15214,16 +15214,16 @@
         <v>261</v>
       </c>
       <c r="F59">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G59">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="H59">
         <v>4.2</v>
       </c>
       <c r="I59">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="J59">
         <v>3.75</v>
@@ -15232,7 +15232,7 @@
         <v>3.8</v>
       </c>
       <c r="L59">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="M59">
         <v>1.07</v>
@@ -15256,16 +15256,16 @@
         <v>3.55</v>
       </c>
       <c r="T59">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U59">
         <v>2.1</v>
       </c>
       <c r="V59">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="W59">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="X59">
         <v>14.5</v>
@@ -15289,7 +15289,7 @@
         <v>17.5</v>
       </c>
       <c r="AE59">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF59">
         <v>12</v>
@@ -15298,7 +15298,7 @@
         <v>10.5</v>
       </c>
       <c r="AH59">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="AI59">
         <v>65</v>
@@ -15307,7 +15307,7 @@
         <v>23</v>
       </c>
       <c r="AK59">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL59">
         <v>38</v>
@@ -15328,7 +15328,7 @@
         <v>14</v>
       </c>
       <c r="AR59">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS59">
         <v>36</v>
@@ -15343,7 +15343,7 @@
         <v>15.5</v>
       </c>
       <c r="AW59">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AX59">
         <v>10.5</v>
@@ -15355,13 +15355,13 @@
         <v>17</v>
       </c>
       <c r="BA59">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="BB59">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC59">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD59">
         <v>32</v>
@@ -15370,22 +15370,22 @@
         <v>38</v>
       </c>
       <c r="BF59">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG59">
         <v>29</v>
       </c>
       <c r="BH59">
-        <v>1000</v>
+        <v>3.75</v>
       </c>
       <c r="BI59">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BJ59">
         <v>1000</v>
       </c>
       <c r="BK59">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="BL59">
         <v>1000</v>
@@ -15394,16 +15394,16 @@
         <v>1.01</v>
       </c>
       <c r="BN59">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BO59">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BP59">
         <v>1000</v>
       </c>
       <c r="BQ59">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BR59">
         <v>1000</v>
@@ -15415,7 +15415,7 @@
         <v>1000</v>
       </c>
       <c r="BU59">
-        <v>4.7</v>
+        <v>5.7</v>
       </c>
       <c r="BV59">
         <v>1000</v>
@@ -15456,46 +15456,46 @@
         <v>262</v>
       </c>
       <c r="F60">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="G60">
-        <v>110</v>
+        <v>9.6</v>
       </c>
       <c r="H60">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="I60">
-        <v>1.86</v>
+        <v>1.9</v>
       </c>
       <c r="J60">
         <v>3.35</v>
       </c>
       <c r="K60">
-        <v>7.2</v>
+        <v>6.4</v>
       </c>
       <c r="L60">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M60">
         <v>1.05</v>
       </c>
       <c r="N60">
-        <v>1.01</v>
+        <v>3.55</v>
       </c>
       <c r="O60">
         <v>1.3</v>
       </c>
       <c r="P60">
-        <v>1.9</v>
+        <v>1.73</v>
       </c>
       <c r="Q60">
         <v>1.92</v>
       </c>
       <c r="R60">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="S60">
-        <v>2.02</v>
+        <v>2.96</v>
       </c>
       <c r="T60">
         <v>1.01</v>
@@ -15504,10 +15504,10 @@
         <v>1.01</v>
       </c>
       <c r="V60">
-        <v>2.16</v>
+        <v>2.1</v>
       </c>
       <c r="W60">
-        <v>1.06</v>
+        <v>1.11</v>
       </c>
       <c r="X60">
         <v>1000</v>
@@ -15704,10 +15704,10 @@
         <v>7.2</v>
       </c>
       <c r="H61">
+        <v>1.56</v>
+      </c>
+      <c r="I61">
         <v>1.57</v>
-      </c>
-      <c r="I61">
-        <v>1.58</v>
       </c>
       <c r="J61">
         <v>4.4</v>
@@ -15716,7 +15716,7 @@
         <v>4.5</v>
       </c>
       <c r="L61">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="M61">
         <v>1.06</v>
@@ -15725,7 +15725,7 @@
         <v>4.2</v>
       </c>
       <c r="O61">
-        <v>1.3</v>
+        <v>1.29</v>
       </c>
       <c r="P61">
         <v>2.1</v>
@@ -15737,22 +15737,22 @@
         <v>1.41</v>
       </c>
       <c r="S61">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T61">
         <v>1.98</v>
       </c>
       <c r="U61">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="V61">
-        <v>0</v>
+        <v>2.74</v>
       </c>
       <c r="W61">
-        <v>0</v>
+        <v>1.16</v>
       </c>
       <c r="X61">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Y61">
         <v>8.199999999999999</v>
@@ -15770,55 +15770,55 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AD61">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AE61">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AF61">
         <v>60</v>
       </c>
       <c r="AG61">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AH61">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AI61">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AJ61">
-        <v>260</v>
+        <v>210</v>
       </c>
       <c r="AK61">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AL61">
+        <v>100</v>
+      </c>
+      <c r="AM61">
+        <v>130</v>
+      </c>
+      <c r="AN61">
         <v>120</v>
-      </c>
-      <c r="AM61">
-        <v>140</v>
-      </c>
-      <c r="AN61">
-        <v>170</v>
       </c>
       <c r="AO61">
         <v>8.4</v>
       </c>
       <c r="AP61">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AQ61">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="AR61">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AS61">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AT61">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU61">
         <v>9.4</v>
@@ -15830,10 +15830,10 @@
         <v>15</v>
       </c>
       <c r="AX61">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AY61">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ61">
         <v>21</v>
@@ -15848,76 +15848,76 @@
         <v>40</v>
       </c>
       <c r="BD61">
-        <v>60</v>
+        <v>85</v>
       </c>
       <c r="BE61">
         <v>70</v>
       </c>
       <c r="BF61">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="BG61">
+        <v>7.8</v>
+      </c>
+      <c r="BH61">
+        <v>4.3</v>
+      </c>
+      <c r="BI61">
+        <v>2.9</v>
+      </c>
+      <c r="BJ61">
+        <v>13</v>
+      </c>
+      <c r="BK61">
+        <v>8</v>
+      </c>
+      <c r="BL61">
+        <v>180</v>
+      </c>
+      <c r="BM61">
+        <v>26</v>
+      </c>
+      <c r="BN61">
+        <v>12.5</v>
+      </c>
+      <c r="BO61">
         <v>7.6</v>
       </c>
-      <c r="BH61">
-        <v>1000</v>
-      </c>
-      <c r="BI61">
-        <v>1.01</v>
-      </c>
-      <c r="BJ61">
-        <v>1000</v>
-      </c>
-      <c r="BK61">
-        <v>1.01</v>
-      </c>
-      <c r="BL61">
-        <v>1000</v>
-      </c>
-      <c r="BM61">
-        <v>1.01</v>
-      </c>
-      <c r="BN61">
-        <v>1000</v>
-      </c>
-      <c r="BO61">
-        <v>1.01</v>
-      </c>
       <c r="BP61">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BQ61">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BR61">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="BS61">
-        <v>1.01</v>
+        <v>46</v>
       </c>
       <c r="BT61">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BU61">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BV61">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BW61">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BX61">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY61">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BZ61">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA61">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="CB61" t="s">
         <v>270</v>
@@ -15940,58 +15940,58 @@
         <v>264</v>
       </c>
       <c r="F62">
-        <v>1.94</v>
+        <v>1.99</v>
       </c>
       <c r="G62">
         <v>2.14</v>
       </c>
       <c r="H62">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I62">
-        <v>4.1</v>
+        <v>3.6</v>
       </c>
       <c r="J62">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="K62">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L62">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M62">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N62">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="O62">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="P62">
-        <v>2</v>
+        <v>3.95</v>
       </c>
       <c r="Q62">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="R62">
-        <v>0</v>
+        <v>2.16</v>
       </c>
       <c r="S62">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="T62">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="U62">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="V62">
-        <v>0</v>
+        <v>1.38</v>
       </c>
       <c r="W62">
-        <v>0</v>
+        <v>1.88</v>
       </c>
       <c r="X62">
         <v>1000</v>
@@ -16102,64 +16102,64 @@
         <v>1.01</v>
       </c>
       <c r="BH62">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI62">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ62">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK62">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL62">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM62">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN62">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO62">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP62">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ62">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR62">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS62">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT62">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU62">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV62">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW62">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX62">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY62">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ62">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA62">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB62" t="s">
         <v>270</v>
@@ -16182,61 +16182,61 @@
         <v>265</v>
       </c>
       <c r="F63">
-        <v>1.83</v>
+        <v>1.79</v>
       </c>
       <c r="G63">
-        <v>1.89</v>
+        <v>1.82</v>
       </c>
       <c r="H63">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="I63">
-        <v>5.3</v>
+        <v>5.6</v>
       </c>
       <c r="J63">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="K63">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L63">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M63">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="N63">
-        <v>0</v>
+        <v>2.64</v>
       </c>
       <c r="O63">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="P63">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="Q63">
-        <v>2.02</v>
+        <v>1.92</v>
       </c>
       <c r="R63">
-        <v>0</v>
+        <v>1.29</v>
       </c>
       <c r="S63">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="T63">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="U63">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="V63">
-        <v>0</v>
+        <v>1.23</v>
       </c>
       <c r="W63">
-        <v>0</v>
+        <v>2.22</v>
       </c>
       <c r="X63">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="Y63">
         <v>19</v>
@@ -16269,22 +16269,22 @@
         <v>24</v>
       </c>
       <c r="AI63">
-        <v>95</v>
+        <v>85</v>
       </c>
       <c r="AJ63">
         <v>22</v>
       </c>
       <c r="AK63">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AL63">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM63">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AN63">
-        <v>15</v>
+        <v>12.5</v>
       </c>
       <c r="AO63">
         <v>110</v>
@@ -16296,10 +16296,10 @@
         <v>14.5</v>
       </c>
       <c r="AR63">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AS63">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AT63">
         <v>7.2</v>
@@ -16311,7 +16311,7 @@
         <v>18</v>
       </c>
       <c r="AW63">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="AX63">
         <v>9.800000000000001</v>
@@ -16323,85 +16323,85 @@
         <v>17.5</v>
       </c>
       <c r="BA63">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BB63">
-        <v>17.5</v>
+        <v>16.5</v>
       </c>
       <c r="BC63">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="BD63">
-        <v>32</v>
+        <v>5.7</v>
       </c>
       <c r="BE63">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="BF63">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BG63">
-        <v>5.7</v>
+        <v>6.2</v>
       </c>
       <c r="BH63">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI63">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ63">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK63">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL63">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM63">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN63">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO63">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP63">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ63">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR63">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS63">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT63">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU63">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV63">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW63">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX63">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY63">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ63">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA63">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB63" t="s">
         <v>270</v>
@@ -16424,7 +16424,7 @@
         <v>266</v>
       </c>
       <c r="F64">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="G64">
         <v>1.2</v>
@@ -16442,208 +16442,208 @@
         <v>9.4</v>
       </c>
       <c r="L64">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="M64">
-        <v>0</v>
+        <v>1.02</v>
       </c>
       <c r="N64">
-        <v>0</v>
+        <v>6.2</v>
       </c>
       <c r="O64">
-        <v>0</v>
+        <v>1.13</v>
       </c>
       <c r="P64">
         <v>3</v>
       </c>
       <c r="Q64">
-        <v>1.35</v>
+        <v>1.4</v>
       </c>
       <c r="R64">
-        <v>0</v>
+        <v>1.77</v>
       </c>
       <c r="S64">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="T64">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="U64">
-        <v>0</v>
+        <v>1.68</v>
       </c>
       <c r="V64">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W64">
-        <v>0</v>
+        <v>6</v>
       </c>
       <c r="X64">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="Y64">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="Z64">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AA64">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AB64">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AC64">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AD64">
-        <v>0</v>
+        <v>85</v>
       </c>
       <c r="AE64">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AF64">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AG64">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AH64">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AI64">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AJ64">
-        <v>0</v>
+        <v>11.5</v>
       </c>
       <c r="AK64">
-        <v>0</v>
+        <v>18.5</v>
       </c>
       <c r="AL64">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AM64">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AN64">
-        <v>0</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO64">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="AP64">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AQ64">
-        <v>0</v>
+        <v>2.08</v>
       </c>
       <c r="AR64">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AS64">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AT64">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AU64">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="AV64">
-        <v>0</v>
+        <v>1.31</v>
       </c>
       <c r="AW64">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="AX64">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="AY64">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="AZ64">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BA64">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BB64">
-        <v>0</v>
+        <v>1.79</v>
       </c>
       <c r="BC64">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="BD64">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BE64">
-        <v>0</v>
+        <v>2.12</v>
       </c>
       <c r="BF64">
-        <v>0</v>
+        <v>2.5</v>
       </c>
       <c r="BG64">
-        <v>0</v>
+        <v>1.33</v>
       </c>
       <c r="BH64">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI64">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ64">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK64">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL64">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM64">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN64">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO64">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP64">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ64">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR64">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS64">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT64">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU64">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV64">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW64">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX64">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY64">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ64">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA64">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB64" t="s">
         <v>270</v>
@@ -16669,31 +16669,31 @@
         <v>4.2</v>
       </c>
       <c r="G65">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="H65">
         <v>1.82</v>
       </c>
       <c r="I65">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="J65">
         <v>3.85</v>
       </c>
       <c r="K65">
+        <v>4.8</v>
+      </c>
+      <c r="L65">
+        <v>1.01</v>
+      </c>
+      <c r="M65">
+        <v>1.01</v>
+      </c>
+      <c r="N65">
         <v>4.3</v>
       </c>
-      <c r="L65">
-        <v>0</v>
-      </c>
-      <c r="M65">
-        <v>0</v>
-      </c>
-      <c r="N65">
-        <v>0</v>
-      </c>
       <c r="O65">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="P65">
         <v>2.16</v>
@@ -16702,10 +16702,10 @@
         <v>1.66</v>
       </c>
       <c r="R65">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S65">
-        <v>0</v>
+        <v>2.8</v>
       </c>
       <c r="T65">
         <v>1.71</v>
@@ -16714,10 +16714,10 @@
         <v>2.2</v>
       </c>
       <c r="V65">
-        <v>0</v>
+        <v>2.04</v>
       </c>
       <c r="W65">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="X65">
         <v>22</v>
@@ -16828,64 +16828,64 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BH65">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BI65">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BJ65">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BK65">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BL65">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BM65">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BN65">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BO65">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BP65">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BQ65">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BR65">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BS65">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BT65">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BU65">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BV65">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BW65">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BX65">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="BY65">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="BZ65">
-        <v>0</v>
+        <v>1000</v>
       </c>
       <c r="CA65">
-        <v>0</v>
+        <v>1.01</v>
       </c>
       <c r="CB65" t="s">
         <v>270</v>
@@ -16914,7 +16914,7 @@
         <v>1.18</v>
       </c>
       <c r="H66">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="I66">
         <v>21</v>
@@ -16926,46 +16926,46 @@
         <v>10</v>
       </c>
       <c r="L66">
-        <v>0</v>
+        <v>1.17</v>
       </c>
       <c r="M66">
         <v>1.02</v>
       </c>
       <c r="N66">
-        <v>8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="O66">
         <v>1.12</v>
       </c>
       <c r="P66">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="Q66">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="R66">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="S66">
-        <v>1.94</v>
+        <v>1.86</v>
       </c>
       <c r="T66">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="U66">
         <v>1.87</v>
       </c>
       <c r="V66">
-        <v>0</v>
+        <v>1.05</v>
       </c>
       <c r="W66">
-        <v>0</v>
+        <v>6.6</v>
       </c>
       <c r="X66">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="Y66">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Z66">
         <v>1000</v>
@@ -16974,13 +16974,13 @@
         <v>1000</v>
       </c>
       <c r="AB66">
-        <v>13.5</v>
+        <v>14.5</v>
       </c>
       <c r="AC66">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AD66">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AE66">
         <v>360</v>
@@ -17001,7 +17001,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AK66">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AL66">
         <v>36</v>
@@ -17010,43 +17010,43 @@
         <v>1000</v>
       </c>
       <c r="AN66">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="AO66">
         <v>380</v>
       </c>
       <c r="AP66">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="AQ66">
-        <v>34</v>
+        <v>55</v>
       </c>
       <c r="AR66">
         <v>48</v>
       </c>
       <c r="AS66">
+        <v>29</v>
+      </c>
+      <c r="AT66">
+        <v>12.5</v>
+      </c>
+      <c r="AU66">
         <v>22</v>
       </c>
-      <c r="AT66">
+      <c r="AV66">
+        <v>50</v>
+      </c>
+      <c r="AW66">
+        <v>100</v>
+      </c>
+      <c r="AX66">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AY66">
         <v>12</v>
       </c>
-      <c r="AU66">
-        <v>21</v>
-      </c>
-      <c r="AV66">
-        <v>34</v>
-      </c>
-      <c r="AW66">
-        <v>20</v>
-      </c>
-      <c r="AX66">
-        <v>8.6</v>
-      </c>
-      <c r="AY66">
-        <v>11.5</v>
-      </c>
       <c r="AZ66">
-        <v>25</v>
+        <v>38</v>
       </c>
       <c r="BA66">
         <v>46</v>
@@ -17055,19 +17055,19 @@
         <v>8.4</v>
       </c>
       <c r="BC66">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD66">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="BE66">
         <v>46</v>
       </c>
       <c r="BF66">
-        <v>2.76</v>
+        <v>2.68</v>
       </c>
       <c r="BG66">
-        <v>20</v>
+        <v>27</v>
       </c>
       <c r="BH66">
         <v>1000</v>
@@ -17150,22 +17150,22 @@
         <v>269</v>
       </c>
       <c r="F67">
-        <v>2.68</v>
+        <v>2.76</v>
       </c>
       <c r="G67">
-        <v>110</v>
+        <v>3.75</v>
       </c>
       <c r="H67">
-        <v>2.54</v>
+        <v>2.66</v>
       </c>
       <c r="I67">
-        <v>110</v>
+        <v>3.75</v>
       </c>
       <c r="J67">
-        <v>1.12</v>
+        <v>2.52</v>
       </c>
       <c r="K67">
-        <v>110</v>
+        <v>3.35</v>
       </c>
       <c r="L67">
         <v>1.01</v>
@@ -17174,22 +17174,22 @@
         <v>1.1</v>
       </c>
       <c r="N67">
-        <v>1.67</v>
+        <v>2.46</v>
       </c>
       <c r="O67">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="P67">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q67">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="R67">
         <v>1.18</v>
       </c>
       <c r="S67">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="T67">
         <v>1.01</v>
@@ -17198,10 +17198,10 @@
         <v>1.01</v>
       </c>
       <c r="V67">
-        <v>1.05</v>
+        <v>1.36</v>
       </c>
       <c r="W67">
-        <v>1.06</v>
+        <v>1.36</v>
       </c>
       <c r="X67">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-31.xlsx
@@ -826,7 +826,7 @@
     <t>Melgar</t>
   </si>
   <si>
-    <t>2026-08-29 18:16:44</t>
+    <t>2026-08-29 20:38:30</t>
   </si>
 </sst>
 </file>
@@ -1423,7 +1423,7 @@
         <v>1.58</v>
       </c>
       <c r="G2">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="H2">
         <v>5.8</v>
@@ -1432,7 +1432,7 @@
         <v>6.6</v>
       </c>
       <c r="J2">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="K2">
         <v>4.8</v>
@@ -1471,7 +1471,7 @@
         <v>1.18</v>
       </c>
       <c r="W2">
-        <v>2.6</v>
+        <v>2.54</v>
       </c>
       <c r="X2">
         <v>23</v>
@@ -1522,7 +1522,7 @@
         <v>1000</v>
       </c>
       <c r="AN2">
-        <v>8.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AO2">
         <v>1000</v>
@@ -1668,10 +1668,10 @@
         <v>1.33</v>
       </c>
       <c r="H3">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I3">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J3">
         <v>6.4</v>
@@ -1689,7 +1689,7 @@
         <v>7</v>
       </c>
       <c r="O3">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="P3">
         <v>3.05</v>
@@ -1701,7 +1701,7 @@
         <v>1.82</v>
       </c>
       <c r="S3">
-        <v>2.06</v>
+        <v>2.04</v>
       </c>
       <c r="T3">
         <v>1.75</v>
@@ -1716,112 +1716,112 @@
         <v>3.9</v>
       </c>
       <c r="X3">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Y3">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="Z3">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AA3">
-        <v>1000</v>
+        <v>350</v>
       </c>
       <c r="AB3">
-        <v>18.5</v>
+        <v>14</v>
       </c>
       <c r="AC3">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="AD3">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AE3">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AF3">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG3">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AH3">
-        <v>48</v>
+        <v>27</v>
       </c>
       <c r="AI3">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AJ3">
-        <v>15.5</v>
+        <v>12.5</v>
       </c>
       <c r="AK3">
-        <v>17.5</v>
+        <v>14.5</v>
       </c>
       <c r="AL3">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AM3">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN3">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="AO3">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP3">
-        <v>2.58</v>
+        <v>6.8</v>
       </c>
       <c r="AQ3">
-        <v>2.58</v>
+        <v>7</v>
       </c>
       <c r="AR3">
-        <v>2.58</v>
+        <v>7.8</v>
       </c>
       <c r="AS3">
-        <v>2.58</v>
+        <v>8</v>
       </c>
       <c r="AT3">
-        <v>2.26</v>
+        <v>11</v>
       </c>
       <c r="AU3">
-        <v>2.32</v>
+        <v>13</v>
       </c>
       <c r="AV3">
-        <v>2.58</v>
+        <v>6.8</v>
       </c>
       <c r="AW3">
-        <v>2.58</v>
+        <v>7.8</v>
       </c>
       <c r="AX3">
+        <v>9</v>
+      </c>
+      <c r="AY3">
+        <v>9.6</v>
+      </c>
+      <c r="AZ3">
+        <v>21</v>
+      </c>
+      <c r="BA3">
+        <v>7.6</v>
+      </c>
+      <c r="BB3">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="BC3">
+        <v>11.5</v>
+      </c>
+      <c r="BD3">
+        <v>6.6</v>
+      </c>
+      <c r="BE3">
         <v>7.8</v>
       </c>
-      <c r="AY3">
-        <v>2.18</v>
-      </c>
-      <c r="AZ3">
-        <v>2.44</v>
-      </c>
-      <c r="BA3">
-        <v>2.58</v>
-      </c>
-      <c r="BB3">
-        <v>2.2</v>
-      </c>
-      <c r="BC3">
-        <v>2.24</v>
-      </c>
-      <c r="BD3">
-        <v>2.58</v>
-      </c>
-      <c r="BE3">
-        <v>2.58</v>
-      </c>
       <c r="BF3">
-        <v>2.86</v>
+        <v>3.35</v>
       </c>
       <c r="BG3">
-        <v>2.58</v>
+        <v>7.8</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -2149,19 +2149,19 @@
         <v>2.24</v>
       </c>
       <c r="G5">
-        <v>2.44</v>
+        <v>2.4</v>
       </c>
       <c r="H5">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="I5">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="J5">
-        <v>3.1</v>
+        <v>2.82</v>
       </c>
       <c r="K5">
-        <v>3.55</v>
+        <v>3.35</v>
       </c>
       <c r="L5">
         <v>1.01</v>
@@ -2170,16 +2170,16 @@
         <v>1.01</v>
       </c>
       <c r="N5">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="O5">
-        <v>1.02</v>
+        <v>1.48</v>
       </c>
       <c r="P5">
         <v>1.58</v>
       </c>
       <c r="Q5">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="R5">
         <v>1.19</v>
@@ -2188,124 +2188,124 @@
         <v>5</v>
       </c>
       <c r="T5">
-        <v>1.01</v>
+        <v>1.89</v>
       </c>
       <c r="U5">
+        <v>1.66</v>
+      </c>
+      <c r="V5">
+        <v>1.31</v>
+      </c>
+      <c r="W5">
         <v>1.71</v>
       </c>
-      <c r="V5">
-        <v>1.34</v>
-      </c>
-      <c r="W5">
-        <v>1.69</v>
-      </c>
       <c r="X5">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="Y5">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z5">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AA5">
-        <v>1000</v>
+        <v>890</v>
       </c>
       <c r="AB5">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AC5">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="AD5">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE5">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AF5">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG5">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AH5">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI5">
-        <v>1000</v>
+        <v>890</v>
       </c>
       <c r="AJ5">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK5">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AL5">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AM5">
-        <v>1000</v>
+        <v>900</v>
       </c>
       <c r="AN5">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AO5">
-        <v>1000</v>
+        <v>890</v>
       </c>
       <c r="AP5">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AQ5">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AR5">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AS5">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AT5">
-        <v>1.01</v>
+        <v>5.6</v>
       </c>
       <c r="AU5">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV5">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW5">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="AX5">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AY5">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ5">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="BA5">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BB5">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BC5">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BD5">
-        <v>1.01</v>
+        <v>5.8</v>
       </c>
       <c r="BE5">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BF5">
-        <v>1.01</v>
+        <v>5.3</v>
       </c>
       <c r="BG5">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="BH5">
         <v>1000</v>
@@ -2391,19 +2391,19 @@
         <v>2.04</v>
       </c>
       <c r="G6">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="H6">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I6">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="J6">
         <v>3.1</v>
       </c>
       <c r="K6">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="L6">
         <v>1.01</v>
@@ -2412,7 +2412,7 @@
         <v>1.01</v>
       </c>
       <c r="N6">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O6">
         <v>1.48</v>
@@ -2430,13 +2430,13 @@
         <v>4.5</v>
       </c>
       <c r="T6">
-        <v>1.01</v>
+        <v>1.86</v>
       </c>
       <c r="U6">
-        <v>1.01</v>
+        <v>1.6</v>
       </c>
       <c r="V6">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="W6">
         <v>1.83</v>
@@ -2633,16 +2633,16 @@
         <v>1.54</v>
       </c>
       <c r="G7">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="H7">
         <v>6.2</v>
       </c>
       <c r="I7">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="J7">
-        <v>4.6</v>
+        <v>4.8</v>
       </c>
       <c r="K7">
         <v>5.3</v>
@@ -2651,43 +2651,43 @@
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.02</v>
+        <v>1.04</v>
       </c>
       <c r="N7">
         <v>5.3</v>
       </c>
       <c r="O7">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P7">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="Q7">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="R7">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="S7">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="T7">
-        <v>1.66</v>
+        <v>1.71</v>
       </c>
       <c r="U7">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="V7">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W7">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="X7">
         <v>1000</v>
       </c>
       <c r="Y7">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="Z7">
         <v>1000</v>
@@ -2702,7 +2702,7 @@
         <v>14.5</v>
       </c>
       <c r="AD7">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AE7">
         <v>1000</v>
@@ -2726,7 +2726,7 @@
         <v>20</v>
       </c>
       <c r="AL7">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM7">
         <v>1000</v>
@@ -2738,58 +2738,58 @@
         <v>1000</v>
       </c>
       <c r="AP7">
+        <v>2.56</v>
+      </c>
+      <c r="AQ7">
+        <v>2.44</v>
+      </c>
+      <c r="AR7">
+        <v>2.56</v>
+      </c>
+      <c r="AS7">
+        <v>2.56</v>
+      </c>
+      <c r="AT7">
+        <v>2.22</v>
+      </c>
+      <c r="AU7">
+        <v>2.16</v>
+      </c>
+      <c r="AV7">
+        <v>2.4</v>
+      </c>
+      <c r="AW7">
+        <v>2.56</v>
+      </c>
+      <c r="AX7">
+        <v>2.16</v>
+      </c>
+      <c r="AY7">
         <v>2.14</v>
       </c>
-      <c r="AQ7">
-        <v>2.14</v>
-      </c>
-      <c r="AR7">
-        <v>2.14</v>
-      </c>
-      <c r="AS7">
-        <v>2.14</v>
-      </c>
-      <c r="AT7">
-        <v>1.9</v>
-      </c>
-      <c r="AU7">
-        <v>1.87</v>
-      </c>
-      <c r="AV7">
-        <v>2.14</v>
-      </c>
-      <c r="AW7">
-        <v>2.14</v>
-      </c>
-      <c r="AX7">
-        <v>1.87</v>
-      </c>
-      <c r="AY7">
-        <v>1.85</v>
-      </c>
       <c r="AZ7">
-        <v>2</v>
+        <v>2.38</v>
       </c>
       <c r="BA7">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="BB7">
-        <v>1.95</v>
+        <v>2.3</v>
       </c>
       <c r="BC7">
-        <v>1.93</v>
+        <v>2.28</v>
       </c>
       <c r="BD7">
-        <v>2.14</v>
+        <v>2.46</v>
       </c>
       <c r="BE7">
-        <v>2.14</v>
+        <v>2.56</v>
       </c>
       <c r="BF7">
-        <v>4.3</v>
+        <v>1.89</v>
       </c>
       <c r="BG7">
-        <v>18</v>
+        <v>2.56</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -3138,13 +3138,13 @@
         <v>1.01</v>
       </c>
       <c r="N9">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O9">
         <v>1.12</v>
       </c>
       <c r="P9">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="Q9">
         <v>1.12</v>
@@ -3380,13 +3380,13 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="O10">
         <v>1.24</v>
       </c>
       <c r="P10">
-        <v>1.28</v>
+        <v>1.3</v>
       </c>
       <c r="Q10">
         <v>1.25</v>
@@ -3867,19 +3867,19 @@
         <v>1.19</v>
       </c>
       <c r="O12">
-        <v>1.25</v>
+        <v>1.01</v>
       </c>
       <c r="P12">
         <v>1.18</v>
       </c>
       <c r="Q12">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="R12">
         <v>1.18</v>
       </c>
       <c r="S12">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="T12">
         <v>1.01</v>
@@ -4082,7 +4082,7 @@
         <v>215</v>
       </c>
       <c r="F13">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G13">
         <v>1.77</v>
@@ -4097,7 +4097,7 @@
         <v>4.4</v>
       </c>
       <c r="K13">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -4106,13 +4106,13 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="O13">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P13">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="Q13">
         <v>1.5</v>
@@ -4602,7 +4602,7 @@
         <v>1.54</v>
       </c>
       <c r="R15">
-        <v>1.53</v>
+        <v>1.55</v>
       </c>
       <c r="S15">
         <v>2.32</v>
@@ -4808,13 +4808,13 @@
         <v>218</v>
       </c>
       <c r="F16">
-        <v>2.28</v>
+        <v>2.06</v>
       </c>
       <c r="G16">
         <v>2.66</v>
       </c>
       <c r="H16">
-        <v>2.88</v>
+        <v>2.74</v>
       </c>
       <c r="I16">
         <v>3.55</v>
@@ -4823,7 +4823,7 @@
         <v>3.2</v>
       </c>
       <c r="K16">
-        <v>4.1</v>
+        <v>6.4</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4847,7 +4847,7 @@
         <v>1.45</v>
       </c>
       <c r="S16">
-        <v>2.58</v>
+        <v>2.74</v>
       </c>
       <c r="T16">
         <v>1.01</v>
@@ -4859,7 +4859,7 @@
         <v>1.39</v>
       </c>
       <c r="W16">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X16">
         <v>1000</v>
@@ -5053,16 +5053,16 @@
         <v>1.64</v>
       </c>
       <c r="G17">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="H17">
         <v>3.85</v>
       </c>
       <c r="I17">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="J17">
-        <v>3.95</v>
+        <v>1.09</v>
       </c>
       <c r="K17">
         <v>7.8</v>
@@ -5095,13 +5095,13 @@
         <v>1.01</v>
       </c>
       <c r="U17">
-        <v>2.08</v>
+        <v>1.01</v>
       </c>
       <c r="V17">
         <v>1.19</v>
       </c>
       <c r="W17">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -5310,28 +5310,28 @@
         <v>5.1</v>
       </c>
       <c r="L18">
-        <v>1.01</v>
+        <v>1.22</v>
       </c>
       <c r="M18">
         <v>1.01</v>
       </c>
       <c r="N18">
-        <v>4.5</v>
+        <v>2.5</v>
       </c>
       <c r="O18">
         <v>1.17</v>
       </c>
       <c r="P18">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="Q18">
-        <v>1.5</v>
+        <v>1.47</v>
       </c>
       <c r="R18">
-        <v>1.64</v>
+        <v>1.62</v>
       </c>
       <c r="S18">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="T18">
         <v>1.48</v>
@@ -5454,64 +5454,64 @@
         <v>5.6</v>
       </c>
       <c r="BH18">
-        <v>1000</v>
+        <v>5.5</v>
       </c>
       <c r="BI18">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BJ18">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK18">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="BL18">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BM18">
         <v>1.01</v>
       </c>
       <c r="BN18">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="BO18">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="BP18">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BQ18">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="BR18">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BS18">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BT18">
-        <v>1000</v>
+        <v>5.7</v>
       </c>
       <c r="BU18">
-        <v>1.01</v>
+        <v>3.75</v>
       </c>
       <c r="BV18">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BW18">
-        <v>1.01</v>
+        <v>8</v>
       </c>
       <c r="BX18">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY18">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BZ18">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="CA18">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="CB18" t="s">
         <v>270</v>
@@ -5573,7 +5573,7 @@
         <v>1.51</v>
       </c>
       <c r="S19">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="T19">
         <v>1.01</v>
@@ -5791,7 +5791,7 @@
         <v>3.7</v>
       </c>
       <c r="K20">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="L20">
         <v>1.01</v>
@@ -5821,7 +5821,7 @@
         <v>1.01</v>
       </c>
       <c r="U20">
-        <v>2.14</v>
+        <v>1.01</v>
       </c>
       <c r="V20">
         <v>1.44</v>
@@ -6024,7 +6024,7 @@
         <v>3.7</v>
       </c>
       <c r="H21">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="I21">
         <v>2.4</v>
@@ -6260,7 +6260,7 @@
         <v>224</v>
       </c>
       <c r="F22">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="G22">
         <v>2.12</v>
@@ -6275,7 +6275,7 @@
         <v>3.75</v>
       </c>
       <c r="K22">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L22">
         <v>1.01</v>
@@ -6293,7 +6293,7 @@
         <v>2.16</v>
       </c>
       <c r="Q22">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="R22">
         <v>1.46</v>
@@ -6311,7 +6311,7 @@
         <v>1.31</v>
       </c>
       <c r="W22">
-        <v>1.89</v>
+        <v>1.9</v>
       </c>
       <c r="X22">
         <v>19</v>
@@ -6419,7 +6419,7 @@
         <v>10.5</v>
       </c>
       <c r="BG22">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BH22">
         <v>1000</v>
@@ -7010,13 +7010,13 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="O25">
         <v>1.01</v>
       </c>
       <c r="P25">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Q25">
         <v>1.29</v>
@@ -7025,7 +7025,7 @@
         <v>1.18</v>
       </c>
       <c r="S25">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="T25">
         <v>1.01</v>
@@ -7228,40 +7228,40 @@
         <v>228</v>
       </c>
       <c r="F26">
-        <v>2.02</v>
+        <v>2.18</v>
       </c>
       <c r="G26">
-        <v>2.62</v>
+        <v>2.48</v>
       </c>
       <c r="H26">
         <v>3.05</v>
       </c>
       <c r="I26">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J26">
-        <v>3.35</v>
+        <v>3.05</v>
       </c>
       <c r="K26">
-        <v>5.6</v>
+        <v>3.85</v>
       </c>
       <c r="L26">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M26">
         <v>1.01</v>
       </c>
       <c r="N26">
-        <v>2.94</v>
+        <v>2.92</v>
       </c>
       <c r="O26">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="P26">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="Q26">
-        <v>1.96</v>
+        <v>1.86</v>
       </c>
       <c r="R26">
         <v>1.25</v>
@@ -7276,10 +7276,10 @@
         <v>1.01</v>
       </c>
       <c r="V26">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W26">
-        <v>1.61</v>
+        <v>1.67</v>
       </c>
       <c r="X26">
         <v>1000</v>
@@ -7473,7 +7473,7 @@
         <v>2.12</v>
       </c>
       <c r="G27">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="H27">
         <v>3.35</v>
@@ -7488,7 +7488,7 @@
         <v>4</v>
       </c>
       <c r="L27">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="M27">
         <v>1.05</v>
@@ -7512,16 +7512,16 @@
         <v>2.88</v>
       </c>
       <c r="T27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="U27">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="V27">
         <v>1.36</v>
       </c>
       <c r="W27">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="X27">
         <v>1000</v>
@@ -7712,22 +7712,22 @@
         <v>230</v>
       </c>
       <c r="F28">
-        <v>2.3</v>
+        <v>2.26</v>
       </c>
       <c r="G28">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="H28">
-        <v>3</v>
+        <v>2.92</v>
       </c>
       <c r="I28">
         <v>3.35</v>
       </c>
       <c r="J28">
-        <v>3.6</v>
+        <v>1.09</v>
       </c>
       <c r="K28">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="L28">
         <v>1.01</v>
@@ -7742,16 +7742,16 @@
         <v>1.24</v>
       </c>
       <c r="P28">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q28">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="R28">
-        <v>1.46</v>
+        <v>1.42</v>
       </c>
       <c r="S28">
-        <v>2.86</v>
+        <v>2.78</v>
       </c>
       <c r="T28">
         <v>1.01</v>
@@ -7990,16 +7990,16 @@
         <v>1.72</v>
       </c>
       <c r="R29">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S29">
         <v>2.66</v>
       </c>
       <c r="T29">
-        <v>1.6</v>
+        <v>1.01</v>
       </c>
       <c r="U29">
-        <v>2.3</v>
+        <v>1.01</v>
       </c>
       <c r="V29">
         <v>1.35</v>
@@ -8196,7 +8196,7 @@
         <v>232</v>
       </c>
       <c r="F30">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="G30">
         <v>4.1</v>
@@ -8223,10 +8223,10 @@
         <v>5.4</v>
       </c>
       <c r="O30">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="P30">
-        <v>2.44</v>
+        <v>2.48</v>
       </c>
       <c r="Q30">
         <v>1.58</v>
@@ -8235,7 +8235,7 @@
         <v>1.6</v>
       </c>
       <c r="S30">
-        <v>2.46</v>
+        <v>2.44</v>
       </c>
       <c r="T30">
         <v>1.59</v>
@@ -8253,7 +8253,7 @@
         <v>28</v>
       </c>
       <c r="Y30">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="Z30">
         <v>14.5</v>
@@ -8262,7 +8262,7 @@
         <v>23</v>
       </c>
       <c r="AB30">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AC30">
         <v>10.5</v>
@@ -8301,7 +8301,7 @@
         <v>34</v>
       </c>
       <c r="AO30">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AP30">
         <v>18</v>
@@ -8340,7 +8340,7 @@
         <v>19</v>
       </c>
       <c r="BB30">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BC30">
         <v>28</v>
@@ -8349,7 +8349,7 @@
         <v>30</v>
       </c>
       <c r="BE30">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF30">
         <v>21</v>
@@ -8480,10 +8480,10 @@
         <v>3.3</v>
       </c>
       <c r="T31">
-        <v>1.71</v>
+        <v>1.04</v>
       </c>
       <c r="U31">
-        <v>2.1</v>
+        <v>1.05</v>
       </c>
       <c r="V31">
         <v>1.42</v>
@@ -8704,19 +8704,19 @@
         <v>1.01</v>
       </c>
       <c r="N32">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="O32">
         <v>1.02</v>
       </c>
       <c r="P32">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="Q32">
         <v>1.38</v>
       </c>
       <c r="R32">
-        <v>1.09</v>
+        <v>1.16</v>
       </c>
       <c r="S32">
         <v>1.38</v>
@@ -8922,16 +8922,16 @@
         <v>235</v>
       </c>
       <c r="F33">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="G33">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="H33">
         <v>3.9</v>
       </c>
       <c r="I33">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J33">
         <v>4</v>
@@ -8946,7 +8946,7 @@
         <v>1.03</v>
       </c>
       <c r="N33">
-        <v>4.5</v>
+        <v>5.3</v>
       </c>
       <c r="O33">
         <v>1.17</v>
@@ -8958,130 +8958,130 @@
         <v>1.59</v>
       </c>
       <c r="R33">
-        <v>1.5</v>
+        <v>1.57</v>
       </c>
       <c r="S33">
-        <v>2.22</v>
+        <v>2.42</v>
       </c>
       <c r="T33">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="U33">
-        <v>1.01</v>
+        <v>1.98</v>
       </c>
       <c r="V33">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="W33">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="X33">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Y33">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="Z33">
         <v>48</v>
       </c>
       <c r="AA33">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB33">
-        <v>19</v>
+        <v>13</v>
       </c>
       <c r="AC33">
-        <v>14.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD33">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="AE33">
         <v>55</v>
       </c>
       <c r="AF33">
-        <v>21</v>
+        <v>14.5</v>
       </c>
       <c r="AG33">
-        <v>16</v>
+        <v>11</v>
       </c>
       <c r="AH33">
-        <v>23</v>
+        <v>16.5</v>
       </c>
       <c r="AI33">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ33">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="AK33">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="AL33">
         <v>40</v>
       </c>
       <c r="AM33">
-        <v>95</v>
+        <v>80</v>
       </c>
       <c r="AN33">
-        <v>13</v>
+        <v>9</v>
       </c>
       <c r="AO33">
         <v>44</v>
       </c>
       <c r="AP33">
-        <v>2.62</v>
+        <v>17.5</v>
       </c>
       <c r="AQ33">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AR33">
+        <v>8</v>
+      </c>
+      <c r="AS33">
+        <v>9.4</v>
+      </c>
+      <c r="AT33">
+        <v>11</v>
+      </c>
+      <c r="AU33">
+        <v>9</v>
+      </c>
+      <c r="AV33">
+        <v>15</v>
+      </c>
+      <c r="AW33">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX33">
+        <v>12.5</v>
+      </c>
+      <c r="AY33">
+        <v>9.4</v>
+      </c>
+      <c r="AZ33">
+        <v>14</v>
+      </c>
+      <c r="BA33">
+        <v>24</v>
+      </c>
+      <c r="BB33">
         <v>19</v>
       </c>
-      <c r="AS33">
-        <v>2.56</v>
-      </c>
-      <c r="AT33">
-        <v>8</v>
-      </c>
-      <c r="AU33">
-        <v>6.2</v>
-      </c>
-      <c r="AV33">
-        <v>10</v>
-      </c>
-      <c r="AW33">
-        <v>2.5</v>
-      </c>
-      <c r="AX33">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AY33">
-        <v>6.8</v>
-      </c>
-      <c r="AZ33">
-        <v>9.6</v>
-      </c>
-      <c r="BA33">
-        <v>2.52</v>
-      </c>
-      <c r="BB33">
-        <v>14</v>
-      </c>
       <c r="BC33">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="BD33">
         <v>16.5</v>
       </c>
       <c r="BE33">
-        <v>2.56</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF33">
-        <v>5.9</v>
+        <v>7.8</v>
       </c>
       <c r="BG33">
-        <v>17.5</v>
+        <v>7.8</v>
       </c>
       <c r="BH33">
         <v>1000</v>
@@ -9170,7 +9170,7 @@
         <v>4.2</v>
       </c>
       <c r="H34">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="I34">
         <v>2.34</v>
@@ -9179,7 +9179,7 @@
         <v>3.25</v>
       </c>
       <c r="K34">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="L34">
         <v>1.33</v>
@@ -9203,7 +9203,7 @@
         <v>1.3</v>
       </c>
       <c r="S34">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="T34">
         <v>1.73</v>
@@ -9406,55 +9406,55 @@
         <v>237</v>
       </c>
       <c r="F35">
-        <v>1.38</v>
+        <v>1.46</v>
       </c>
       <c r="G35">
         <v>1.54</v>
       </c>
       <c r="H35">
-        <v>3.65</v>
+        <v>6.6</v>
       </c>
       <c r="I35">
-        <v>13.5</v>
+        <v>9.4</v>
       </c>
       <c r="J35">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="K35">
-        <v>950</v>
+        <v>6.2</v>
       </c>
       <c r="L35">
         <v>1.01</v>
       </c>
       <c r="M35">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N35">
-        <v>2.24</v>
+        <v>4.8</v>
       </c>
       <c r="O35">
         <v>1.19</v>
       </c>
       <c r="P35">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q35">
-        <v>1.61</v>
+        <v>1.53</v>
       </c>
       <c r="R35">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="S35">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="T35">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="U35">
-        <v>1.01</v>
+        <v>1.87</v>
       </c>
       <c r="V35">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="W35">
         <v>2.84</v>
@@ -9648,19 +9648,19 @@
         <v>238</v>
       </c>
       <c r="F36">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="G36">
         <v>6.2</v>
       </c>
       <c r="H36">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="I36">
-        <v>1.69</v>
+        <v>1.68</v>
       </c>
       <c r="J36">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K36">
         <v>4.3</v>
@@ -9675,7 +9675,7 @@
         <v>3.75</v>
       </c>
       <c r="O36">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="P36">
         <v>1.95</v>
@@ -9696,13 +9696,13 @@
         <v>1.98</v>
       </c>
       <c r="V36">
-        <v>2.44</v>
+        <v>2.46</v>
       </c>
       <c r="W36">
         <v>1.19</v>
       </c>
       <c r="X36">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="Y36">
         <v>8.800000000000001</v>
@@ -9717,7 +9717,7 @@
         <v>20</v>
       </c>
       <c r="AC36">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="AD36">
         <v>10.5</v>
@@ -9741,7 +9741,7 @@
         <v>190</v>
       </c>
       <c r="AK36">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AL36">
         <v>110</v>
@@ -9750,16 +9750,16 @@
         <v>160</v>
       </c>
       <c r="AN36">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AO36">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AP36">
         <v>13.5</v>
       </c>
       <c r="AQ36">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AR36">
         <v>9</v>
@@ -9792,19 +9792,19 @@
         <v>30</v>
       </c>
       <c r="BB36">
-        <v>9.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="BC36">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BD36">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE36">
         <v>9.199999999999999</v>
       </c>
       <c r="BF36">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BG36">
         <v>9.199999999999999</v>
@@ -9890,7 +9890,7 @@
         <v>239</v>
       </c>
       <c r="F37">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="G37">
         <v>9</v>
@@ -9899,7 +9899,7 @@
         <v>1.51</v>
       </c>
       <c r="I37">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="J37">
         <v>4.3</v>
@@ -9908,13 +9908,13 @@
         <v>4.5</v>
       </c>
       <c r="L37">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="M37">
         <v>1.08</v>
       </c>
       <c r="N37">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="O37">
         <v>1.36</v>
@@ -9938,7 +9938,7 @@
         <v>1.74</v>
       </c>
       <c r="V37">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="W37">
         <v>1.12</v>
@@ -10034,28 +10034,28 @@
         <v>42</v>
       </c>
       <c r="BB37">
-        <v>15</v>
+        <v>16.5</v>
       </c>
       <c r="BC37">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BD37">
         <v>20</v>
       </c>
       <c r="BE37">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="BF37">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BG37">
         <v>8.6</v>
       </c>
       <c r="BH37">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI37">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BJ37">
         <v>1000</v>
@@ -10088,7 +10088,7 @@
         <v>1.01</v>
       </c>
       <c r="BT37">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BU37">
         <v>1.01</v>
@@ -10132,22 +10132,22 @@
         <v>240</v>
       </c>
       <c r="F38">
-        <v>1.14</v>
+        <v>1.15</v>
       </c>
       <c r="G38">
-        <v>1.32</v>
+        <v>1.22</v>
       </c>
       <c r="H38">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I38">
-        <v>660</v>
+        <v>27</v>
       </c>
       <c r="J38">
         <v>6.2</v>
       </c>
       <c r="K38">
-        <v>25</v>
+        <v>14.5</v>
       </c>
       <c r="L38">
         <v>1.01</v>
@@ -10156,22 +10156,22 @@
         <v>1.01</v>
       </c>
       <c r="N38">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="O38">
         <v>1.11</v>
       </c>
       <c r="P38">
-        <v>2.66</v>
+        <v>2.88</v>
       </c>
       <c r="Q38">
-        <v>1.33</v>
+        <v>1.44</v>
       </c>
       <c r="R38">
-        <v>1.58</v>
+        <v>1.62</v>
       </c>
       <c r="S38">
-        <v>1.7</v>
+        <v>1.44</v>
       </c>
       <c r="T38">
         <v>1.01</v>
@@ -10180,10 +10180,10 @@
         <v>1.01</v>
       </c>
       <c r="V38">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="W38">
-        <v>4.1</v>
+        <v>4.9</v>
       </c>
       <c r="X38">
         <v>1000</v>
@@ -10377,10 +10377,10 @@
         <v>3.15</v>
       </c>
       <c r="G39">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="H39">
-        <v>2.32</v>
+        <v>2.24</v>
       </c>
       <c r="I39">
         <v>2.48</v>
@@ -10389,10 +10389,10 @@
         <v>3.45</v>
       </c>
       <c r="K39">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="L39">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="M39">
         <v>1.07</v>
@@ -10425,7 +10425,7 @@
         <v>1.67</v>
       </c>
       <c r="W39">
-        <v>1.41</v>
+        <v>1.39</v>
       </c>
       <c r="X39">
         <v>18</v>
@@ -10455,7 +10455,7 @@
         <v>28</v>
       </c>
       <c r="AG39">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AH39">
         <v>17</v>
@@ -10491,7 +10491,7 @@
         <v>14</v>
       </c>
       <c r="AS39">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="AT39">
         <v>11.5</v>
@@ -10503,7 +10503,7 @@
         <v>10</v>
       </c>
       <c r="AW39">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AX39">
         <v>16.5</v>
@@ -10515,85 +10515,85 @@
         <v>12.5</v>
       </c>
       <c r="BA39">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BB39">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BC39">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BD39">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BE39">
-        <v>60</v>
+        <v>1.01</v>
       </c>
       <c r="BF39">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BG39">
         <v>14</v>
       </c>
       <c r="BH39">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BI39">
-        <v>1.01</v>
+        <v>2.76</v>
       </c>
       <c r="BJ39">
-        <v>13.5</v>
+        <v>1000</v>
       </c>
       <c r="BK39">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="BL39">
         <v>1000</v>
       </c>
       <c r="BM39">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN39">
-        <v>9</v>
+        <v>1000</v>
       </c>
       <c r="BO39">
-        <v>4.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP39">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="BQ39">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BR39">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BS39">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT39">
-        <v>7.6</v>
+        <v>1000</v>
       </c>
       <c r="BU39">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BV39">
-        <v>25</v>
+        <v>1000</v>
       </c>
       <c r="BW39">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BX39">
-        <v>46</v>
+        <v>1000</v>
       </c>
       <c r="BY39">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ39">
-        <v>38</v>
+        <v>1000</v>
       </c>
       <c r="CA39">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB39" t="s">
         <v>270</v>
@@ -10634,16 +10634,16 @@
         <v>4.4</v>
       </c>
       <c r="L40">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M40">
         <v>1.07</v>
       </c>
       <c r="N40">
-        <v>2.62</v>
+        <v>2.4</v>
       </c>
       <c r="O40">
-        <v>1.44</v>
+        <v>1.07</v>
       </c>
       <c r="P40">
         <v>1.51</v>
@@ -10655,7 +10655,7 @@
         <v>1.18</v>
       </c>
       <c r="S40">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="T40">
         <v>1.01</v>
@@ -10867,10 +10867,10 @@
         <v>5.7</v>
       </c>
       <c r="I41">
-        <v>7.4</v>
+        <v>6.6</v>
       </c>
       <c r="J41">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K41">
         <v>3.95</v>
@@ -10882,16 +10882,16 @@
         <v>1.06</v>
       </c>
       <c r="N41">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="O41">
-        <v>1.35</v>
+        <v>1.39</v>
       </c>
       <c r="P41">
-        <v>1.65</v>
+        <v>1.7</v>
       </c>
       <c r="Q41">
-        <v>1.58</v>
+        <v>2.08</v>
       </c>
       <c r="R41">
         <v>1.28</v>
@@ -10900,124 +10900,124 @@
         <v>4.1</v>
       </c>
       <c r="T41">
-        <v>1.01</v>
+        <v>1.82</v>
       </c>
       <c r="U41">
-        <v>1.01</v>
+        <v>1.64</v>
       </c>
       <c r="V41">
-        <v>1.16</v>
+        <v>1.18</v>
       </c>
       <c r="W41">
         <v>2.22</v>
       </c>
       <c r="X41">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="Y41">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z41">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA41">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AB41">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AC41">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD41">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE41">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AF41">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG41">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH41">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI41">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AJ41">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AK41">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AL41">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AM41">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN41">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO41">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AP41">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AQ41">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR41">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="AS41">
-        <v>1.01</v>
+        <v>130</v>
       </c>
       <c r="AT41">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="AU41">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV41">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="AW41">
-        <v>1.01</v>
+        <v>70</v>
       </c>
       <c r="AX41">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AY41">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AZ41">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BA41">
-        <v>1.01</v>
+        <v>70</v>
       </c>
       <c r="BB41">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BC41">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BD41">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BE41">
-        <v>1.01</v>
+        <v>140</v>
       </c>
       <c r="BF41">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BG41">
-        <v>1.01</v>
+        <v>100</v>
       </c>
       <c r="BH41">
         <v>1000</v>
@@ -11100,19 +11100,19 @@
         <v>244</v>
       </c>
       <c r="F42">
-        <v>1.76</v>
+        <v>1.78</v>
       </c>
       <c r="G42">
-        <v>1.79</v>
+        <v>1.85</v>
       </c>
       <c r="H42">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="I42">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="J42">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="K42">
         <v>3.8</v>
@@ -11130,7 +11130,7 @@
         <v>1.4</v>
       </c>
       <c r="P42">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="Q42">
         <v>2.14</v>
@@ -11139,127 +11139,127 @@
         <v>1.28</v>
       </c>
       <c r="S42">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="T42">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="U42">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="V42">
         <v>1.2</v>
       </c>
       <c r="W42">
-        <v>2.26</v>
+        <v>2.18</v>
       </c>
       <c r="X42">
         <v>12</v>
       </c>
       <c r="Y42">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Z42">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AA42">
         <v>170</v>
       </c>
       <c r="AB42">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AC42">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD42">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE42">
-        <v>95</v>
+        <v>110</v>
       </c>
       <c r="AF42">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="AG42">
-        <v>10</v>
+        <v>970</v>
       </c>
       <c r="AH42">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI42">
         <v>130</v>
       </c>
       <c r="AJ42">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AK42">
         <v>21</v>
       </c>
       <c r="AL42">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AM42">
         <v>200</v>
       </c>
       <c r="AN42">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO42">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP42">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AQ42">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="AR42">
-        <v>13</v>
+        <v>36</v>
       </c>
       <c r="AS42">
-        <v>15.5</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AT42">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AU42">
-        <v>7.8</v>
+        <v>5.4</v>
       </c>
       <c r="AV42">
         <v>20</v>
       </c>
       <c r="AW42">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="AX42">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY42">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ42">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA42">
-        <v>15</v>
+        <v>8.6</v>
       </c>
       <c r="BB42">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BC42">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD42">
         <v>40</v>
       </c>
       <c r="BE42">
-        <v>15.5</v>
+        <v>9</v>
       </c>
       <c r="BF42">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BG42">
-        <v>15</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH42">
         <v>1000</v>
@@ -11366,28 +11366,28 @@
         <v>1.02</v>
       </c>
       <c r="N43">
-        <v>4.1</v>
+        <v>4.6</v>
       </c>
       <c r="O43">
-        <v>1.21</v>
+        <v>1.23</v>
       </c>
       <c r="P43">
         <v>2.16</v>
       </c>
       <c r="Q43">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="R43">
-        <v>1.44</v>
+        <v>1.46</v>
       </c>
       <c r="S43">
-        <v>2.68</v>
+        <v>2.58</v>
       </c>
       <c r="T43">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="U43">
-        <v>1.01</v>
+        <v>2.06</v>
       </c>
       <c r="V43">
         <v>1.21</v>
@@ -11396,112 +11396,112 @@
         <v>2.32</v>
       </c>
       <c r="X43">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Y43">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="Z43">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AA43">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AB43">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AC43">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AD43">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AE43">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF43">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AG43">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH43">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AI43">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AJ43">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AK43">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AL43">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM43">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN43">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AO43">
+        <v>90</v>
+      </c>
+      <c r="AP43">
+        <v>17</v>
+      </c>
+      <c r="AQ43">
+        <v>18</v>
+      </c>
+      <c r="AR43">
+        <v>6.6</v>
+      </c>
+      <c r="AS43">
+        <v>7.2</v>
+      </c>
+      <c r="AT43">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AU43">
+        <v>8.4</v>
+      </c>
+      <c r="AV43">
+        <v>17.5</v>
+      </c>
+      <c r="AW43">
+        <v>6.8</v>
+      </c>
+      <c r="AX43">
+        <v>9.6</v>
+      </c>
+      <c r="AY43">
+        <v>8.6</v>
+      </c>
+      <c r="AZ43">
         <v>16</v>
       </c>
-      <c r="AO43">
-        <v>1000</v>
-      </c>
-      <c r="AP43">
-        <v>1.06</v>
-      </c>
-      <c r="AQ43">
-        <v>1.06</v>
-      </c>
-      <c r="AR43">
-        <v>1.06</v>
-      </c>
-      <c r="AS43">
-        <v>1.06</v>
-      </c>
-      <c r="AT43">
-        <v>1.06</v>
-      </c>
-      <c r="AU43">
-        <v>5.8</v>
-      </c>
-      <c r="AV43">
-        <v>1.06</v>
-      </c>
-      <c r="AW43">
-        <v>1.06</v>
-      </c>
-      <c r="AX43">
-        <v>1.06</v>
-      </c>
-      <c r="AY43">
-        <v>1.06</v>
-      </c>
-      <c r="AZ43">
-        <v>1.06</v>
-      </c>
       <c r="BA43">
-        <v>1.06</v>
+        <v>6.8</v>
       </c>
       <c r="BB43">
-        <v>1.06</v>
+        <v>14.5</v>
       </c>
       <c r="BC43">
-        <v>1.06</v>
+        <v>14</v>
       </c>
       <c r="BD43">
-        <v>1.06</v>
+        <v>6.2</v>
       </c>
       <c r="BE43">
-        <v>1.06</v>
+        <v>7.2</v>
       </c>
       <c r="BF43">
-        <v>5.3</v>
+        <v>7.6</v>
       </c>
       <c r="BG43">
-        <v>1.06</v>
+        <v>6.8</v>
       </c>
       <c r="BH43">
         <v>1000</v>
@@ -11584,22 +11584,22 @@
         <v>246</v>
       </c>
       <c r="F44">
-        <v>1.95</v>
+        <v>1.97</v>
       </c>
       <c r="G44">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="H44">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="I44">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="J44">
         <v>4.1</v>
       </c>
       <c r="K44">
-        <v>4.7</v>
+        <v>4.5</v>
       </c>
       <c r="L44">
         <v>1.01</v>
@@ -11614,10 +11614,10 @@
         <v>1.18</v>
       </c>
       <c r="P44">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q44">
-        <v>1.54</v>
+        <v>1.48</v>
       </c>
       <c r="R44">
         <v>1.64</v>
@@ -11629,19 +11629,19 @@
         <v>1.53</v>
       </c>
       <c r="U44">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="V44">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W44">
-        <v>1.96</v>
+        <v>1.91</v>
       </c>
       <c r="X44">
         <v>28</v>
       </c>
       <c r="Y44">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="Z44">
         <v>34</v>
@@ -11659,16 +11659,16 @@
         <v>17</v>
       </c>
       <c r="AE44">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AF44">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AG44">
-        <v>13.5</v>
+        <v>12</v>
       </c>
       <c r="AH44">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AI44">
         <v>46</v>
@@ -11692,16 +11692,16 @@
         <v>27</v>
       </c>
       <c r="AP44">
-        <v>4.8</v>
+        <v>5.6</v>
       </c>
       <c r="AQ44">
         <v>17.5</v>
       </c>
       <c r="AR44">
-        <v>4.9</v>
+        <v>5.8</v>
       </c>
       <c r="AS44">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="AT44">
         <v>12</v>
@@ -11713,7 +11713,7 @@
         <v>13.5</v>
       </c>
       <c r="AW44">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="AX44">
         <v>13</v>
@@ -11725,7 +11725,7 @@
         <v>13</v>
       </c>
       <c r="BA44">
-        <v>5.1</v>
+        <v>6</v>
       </c>
       <c r="BB44">
         <v>20</v>
@@ -11734,10 +11734,10 @@
         <v>15.5</v>
       </c>
       <c r="BD44">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="BE44">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="BF44">
         <v>6.6</v>
@@ -11829,10 +11829,10 @@
         <v>1.57</v>
       </c>
       <c r="G45">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H45">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="I45">
         <v>6.6</v>
@@ -11850,28 +11850,28 @@
         <v>1.01</v>
       </c>
       <c r="N45">
-        <v>5.5</v>
+        <v>1.08</v>
       </c>
       <c r="O45">
-        <v>1.19</v>
+        <v>1.17</v>
       </c>
       <c r="P45">
-        <v>2.54</v>
+        <v>2.44</v>
       </c>
       <c r="Q45">
         <v>1.57</v>
       </c>
       <c r="R45">
-        <v>1.57</v>
+        <v>1.62</v>
       </c>
       <c r="S45">
-        <v>2.36</v>
+        <v>2.34</v>
       </c>
       <c r="T45">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="U45">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V45">
         <v>1.18</v>
@@ -11928,7 +11928,7 @@
         <v>95</v>
       </c>
       <c r="AN45">
-        <v>8.4</v>
+        <v>970</v>
       </c>
       <c r="AO45">
         <v>1000</v>
@@ -12092,7 +12092,7 @@
         <v>1.01</v>
       </c>
       <c r="N46">
-        <v>2.56</v>
+        <v>1.01</v>
       </c>
       <c r="O46">
         <v>1.01</v>
@@ -12310,7 +12310,7 @@
         <v>249</v>
       </c>
       <c r="F47">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="G47">
         <v>1.47</v>
@@ -12319,7 +12319,7 @@
         <v>7.4</v>
       </c>
       <c r="I47">
-        <v>9</v>
+        <v>8.4</v>
       </c>
       <c r="J47">
         <v>5.3</v>
@@ -12340,13 +12340,13 @@
         <v>1.15</v>
       </c>
       <c r="P47">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="Q47">
         <v>1.49</v>
       </c>
       <c r="R47">
-        <v>1.72</v>
+        <v>1.69</v>
       </c>
       <c r="S47">
         <v>2.2</v>
@@ -12355,10 +12355,10 @@
         <v>1.64</v>
       </c>
       <c r="U47">
-        <v>2.18</v>
+        <v>2.14</v>
       </c>
       <c r="V47">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="W47">
         <v>3.1</v>
@@ -12367,7 +12367,7 @@
         <v>36</v>
       </c>
       <c r="Y47">
-        <v>42</v>
+        <v>38</v>
       </c>
       <c r="Z47">
         <v>85</v>
@@ -12382,7 +12382,7 @@
         <v>15.5</v>
       </c>
       <c r="AD47">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AE47">
         <v>110</v>
@@ -12418,16 +12418,16 @@
         <v>100</v>
       </c>
       <c r="AP47">
-        <v>4.8</v>
+        <v>5</v>
       </c>
       <c r="AQ47">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="AR47">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AS47">
-        <v>5.4</v>
+        <v>5.6</v>
       </c>
       <c r="AT47">
         <v>10.5</v>
@@ -12436,10 +12436,10 @@
         <v>11</v>
       </c>
       <c r="AV47">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="AW47">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="AX47">
         <v>9.4</v>
@@ -12451,7 +12451,7 @@
         <v>18</v>
       </c>
       <c r="BA47">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BB47">
         <v>11</v>
@@ -12460,16 +12460,16 @@
         <v>11.5</v>
       </c>
       <c r="BD47">
-        <v>4.7</v>
+        <v>4.9</v>
       </c>
       <c r="BE47">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BF47">
-        <v>3.85</v>
+        <v>4.1</v>
       </c>
       <c r="BG47">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BH47">
         <v>1000</v>
@@ -12552,10 +12552,10 @@
         <v>250</v>
       </c>
       <c r="F48">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G48">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="H48">
         <v>4.1</v>
@@ -12576,19 +12576,19 @@
         <v>1.16</v>
       </c>
       <c r="N48">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="O48">
         <v>1.72</v>
       </c>
       <c r="P48">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="Q48">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="R48">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="S48">
         <v>7.6</v>
@@ -12603,10 +12603,10 @@
         <v>1.3</v>
       </c>
       <c r="W48">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="X48">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="Y48">
         <v>9.6</v>
@@ -12615,10 +12615,10 @@
         <v>28</v>
       </c>
       <c r="AA48">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AB48">
-        <v>6.2</v>
+        <v>6</v>
       </c>
       <c r="AC48">
         <v>7.6</v>
@@ -12627,7 +12627,7 @@
         <v>20</v>
       </c>
       <c r="AE48">
-        <v>100</v>
+        <v>90</v>
       </c>
       <c r="AF48">
         <v>11.5</v>
@@ -12639,7 +12639,7 @@
         <v>32</v>
       </c>
       <c r="AI48">
-        <v>150</v>
+        <v>130</v>
       </c>
       <c r="AJ48">
         <v>34</v>
@@ -12648,7 +12648,7 @@
         <v>38</v>
       </c>
       <c r="AL48">
-        <v>85</v>
+        <v>110</v>
       </c>
       <c r="AM48">
         <v>330</v>
@@ -12660,7 +12660,7 @@
         <v>170</v>
       </c>
       <c r="AP48">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="AQ48">
         <v>9</v>
@@ -12681,7 +12681,7 @@
         <v>18.5</v>
       </c>
       <c r="AW48">
-        <v>75</v>
+        <v>36</v>
       </c>
       <c r="AX48">
         <v>10.5</v>
@@ -12696,7 +12696,7 @@
         <v>42</v>
       </c>
       <c r="BB48">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="BC48">
         <v>34</v>
@@ -12708,70 +12708,70 @@
         <v>110</v>
       </c>
       <c r="BF48">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="BG48">
         <v>42</v>
       </c>
       <c r="BH48">
-        <v>2.74</v>
+        <v>970</v>
       </c>
       <c r="BI48">
-        <v>2.04</v>
+        <v>2.12</v>
       </c>
       <c r="BJ48">
-        <v>13</v>
+        <v>1000</v>
       </c>
       <c r="BK48">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BL48">
-        <v>360</v>
+        <v>1000</v>
       </c>
       <c r="BM48">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BN48">
-        <v>4.8</v>
+        <v>970</v>
       </c>
       <c r="BO48">
-        <v>4.2</v>
+        <v>3.85</v>
       </c>
       <c r="BP48">
-        <v>21</v>
+        <v>1000</v>
       </c>
       <c r="BQ48">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BR48">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BS48">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BT48">
-        <v>7.6</v>
+        <v>970</v>
       </c>
       <c r="BU48">
-        <v>1.01</v>
+        <v>2.32</v>
       </c>
       <c r="BV48">
-        <v>50</v>
+        <v>1000</v>
       </c>
       <c r="BW48">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BX48">
-        <v>80</v>
+        <v>1000</v>
       </c>
       <c r="BY48">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="BZ48">
-        <v>65</v>
+        <v>1000</v>
       </c>
       <c r="CA48">
-        <v>1.01</v>
+        <v>1.11</v>
       </c>
       <c r="CB48" t="s">
         <v>270</v>
@@ -13048,7 +13048,7 @@
         <v>5.7</v>
       </c>
       <c r="J50">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="K50">
         <v>6.2</v>
@@ -13526,7 +13526,7 @@
         <v>1.72</v>
       </c>
       <c r="H52">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="I52">
         <v>7</v>
@@ -13535,7 +13535,7 @@
         <v>4.6</v>
       </c>
       <c r="K52">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="L52">
         <v>1.01</v>
@@ -13783,7 +13783,7 @@
         <v>1.4</v>
       </c>
       <c r="M53">
-        <v>1.09</v>
+        <v>1.06</v>
       </c>
       <c r="N53">
         <v>2.58</v>
@@ -13804,7 +13804,7 @@
         <v>3.75</v>
       </c>
       <c r="T53">
-        <v>1.01</v>
+        <v>1.95</v>
       </c>
       <c r="U53">
         <v>1.01</v>
@@ -13930,58 +13930,58 @@
         <v>1.01</v>
       </c>
       <c r="BJ53">
-        <v>18</v>
+        <v>1000</v>
       </c>
       <c r="BK53">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BL53">
         <v>1000</v>
       </c>
       <c r="BM53">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN53">
-        <v>4.9</v>
+        <v>1000</v>
       </c>
       <c r="BO53">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BP53">
-        <v>15</v>
+        <v>1000</v>
       </c>
       <c r="BQ53">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BR53">
-        <v>48</v>
+        <v>1000</v>
       </c>
       <c r="BS53">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BT53">
-        <v>15.5</v>
+        <v>1000</v>
       </c>
       <c r="BU53">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV53">
         <v>1000</v>
       </c>
       <c r="BW53">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BX53">
         <v>1000</v>
       </c>
       <c r="BY53">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BZ53">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="CA53">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB53" t="s">
         <v>270</v>
@@ -14013,7 +14013,7 @@
         <v>2</v>
       </c>
       <c r="I54">
-        <v>2.32</v>
+        <v>2.26</v>
       </c>
       <c r="J54">
         <v>3.9</v>
@@ -14028,10 +14028,10 @@
         <v>1.02</v>
       </c>
       <c r="N54">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="O54">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="P54">
         <v>2.52</v>
@@ -14046,13 +14046,13 @@
         <v>2.08</v>
       </c>
       <c r="T54">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="U54">
         <v>2.4</v>
       </c>
       <c r="V54">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="W54">
         <v>1.36</v>
@@ -14121,7 +14121,7 @@
         <v>12</v>
       </c>
       <c r="AS54">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="AT54">
         <v>17</v>
@@ -14136,7 +14136,7 @@
         <v>16.5</v>
       </c>
       <c r="AX54">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="AY54">
         <v>11</v>
@@ -14145,19 +14145,19 @@
         <v>11</v>
       </c>
       <c r="BA54">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="BB54">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BC54">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="BD54">
-        <v>29</v>
+        <v>1.01</v>
       </c>
       <c r="BE54">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BF54">
         <v>18</v>
@@ -14255,7 +14255,7 @@
         <v>8</v>
       </c>
       <c r="I55">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="J55">
         <v>4.9</v>
@@ -14267,7 +14267,7 @@
         <v>1.01</v>
       </c>
       <c r="M55">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N55">
         <v>4</v>
@@ -14494,13 +14494,13 @@
         <v>3.8</v>
       </c>
       <c r="H56">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="I56">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="J56">
-        <v>3.85</v>
+        <v>3.95</v>
       </c>
       <c r="K56">
         <v>4</v>
@@ -14536,10 +14536,10 @@
         <v>2.32</v>
       </c>
       <c r="V56">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="W56">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X56">
         <v>18.5</v>
@@ -14587,7 +14587,7 @@
         <v>46</v>
       </c>
       <c r="AM56">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AN56">
         <v>34</v>
@@ -14730,13 +14730,13 @@
         <v>259</v>
       </c>
       <c r="F57">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="G57">
         <v>2.02</v>
       </c>
       <c r="H57">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="I57">
         <v>5.7</v>
@@ -14748,16 +14748,16 @@
         <v>3.65</v>
       </c>
       <c r="L57">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="M57">
         <v>1.09</v>
       </c>
       <c r="N57">
-        <v>2.88</v>
+        <v>2.92</v>
       </c>
       <c r="O57">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P57">
         <v>1.66</v>
@@ -14772,10 +14772,10 @@
         <v>4.2</v>
       </c>
       <c r="T57">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="U57">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="V57">
         <v>1.21</v>
@@ -14796,10 +14796,10 @@
         <v>160</v>
       </c>
       <c r="AB57">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC57">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD57">
         <v>25</v>
@@ -14844,40 +14844,40 @@
         <v>10.5</v>
       </c>
       <c r="AR57">
-        <v>27</v>
+        <v>1.02</v>
       </c>
       <c r="AS57">
         <v>1.01</v>
       </c>
       <c r="AT57">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU57">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AV57">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="AW57">
         <v>1.01</v>
       </c>
       <c r="AX57">
-        <v>8</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY57">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ57">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="BA57">
         <v>65</v>
       </c>
       <c r="BB57">
-        <v>16</v>
+        <v>18.5</v>
       </c>
       <c r="BC57">
-        <v>17</v>
+        <v>19.5</v>
       </c>
       <c r="BD57">
         <v>36</v>
@@ -14886,7 +14886,7 @@
         <v>110</v>
       </c>
       <c r="BF57">
-        <v>13.5</v>
+        <v>1.01</v>
       </c>
       <c r="BG57">
         <v>1.01</v>
@@ -14990,7 +14990,7 @@
         <v>3.9</v>
       </c>
       <c r="L58">
-        <v>1.01</v>
+        <v>1.32</v>
       </c>
       <c r="M58">
         <v>1.07</v>
@@ -15035,7 +15035,7 @@
         <v>12</v>
       </c>
       <c r="AA58">
-        <v>27</v>
+        <v>23</v>
       </c>
       <c r="AB58">
         <v>16</v>
@@ -15083,7 +15083,7 @@
         <v>10</v>
       </c>
       <c r="AQ58">
-        <v>6.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR58">
         <v>10</v>
@@ -15214,13 +15214,13 @@
         <v>261</v>
       </c>
       <c r="F59">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="G59">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H59">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I59">
         <v>4.5</v>
@@ -15229,16 +15229,16 @@
         <v>3.75</v>
       </c>
       <c r="K59">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="L59">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="M59">
         <v>1.07</v>
       </c>
       <c r="N59">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="O59">
         <v>1.33</v>
@@ -15247,13 +15247,13 @@
         <v>1.95</v>
       </c>
       <c r="Q59">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R59">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="S59">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T59">
         <v>1.86</v>
@@ -15262,10 +15262,10 @@
         <v>2.1</v>
       </c>
       <c r="V59">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="W59">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X59">
         <v>14.5</v>
@@ -15334,16 +15334,16 @@
         <v>36</v>
       </c>
       <c r="AT59">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU59">
         <v>7.6</v>
       </c>
       <c r="AV59">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AW59">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AX59">
         <v>10.5</v>
@@ -15373,7 +15373,7 @@
         <v>13</v>
       </c>
       <c r="BG59">
-        <v>29</v>
+        <v>50</v>
       </c>
       <c r="BH59">
         <v>3.75</v>
@@ -15382,7 +15382,7 @@
         <v>2.86</v>
       </c>
       <c r="BJ59">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="BK59">
         <v>7</v>
@@ -15403,7 +15403,7 @@
         <v>1000</v>
       </c>
       <c r="BQ59">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BR59">
         <v>1000</v>
@@ -15412,7 +15412,7 @@
         <v>1.01</v>
       </c>
       <c r="BT59">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BU59">
         <v>5.7</v>
@@ -15456,13 +15456,13 @@
         <v>262</v>
       </c>
       <c r="F60">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="G60">
         <v>9.6</v>
       </c>
       <c r="H60">
-        <v>1.58</v>
+        <v>1.56</v>
       </c>
       <c r="I60">
         <v>1.9</v>
@@ -15474,13 +15474,13 @@
         <v>6.4</v>
       </c>
       <c r="L60">
-        <v>1.32</v>
+        <v>1.01</v>
       </c>
       <c r="M60">
         <v>1.05</v>
       </c>
       <c r="N60">
-        <v>3.55</v>
+        <v>2.7</v>
       </c>
       <c r="O60">
         <v>1.3</v>
@@ -15618,16 +15618,16 @@
         <v>1.01</v>
       </c>
       <c r="BH60">
-        <v>1000</v>
+        <v>3.55</v>
       </c>
       <c r="BI60">
-        <v>1.01</v>
+        <v>2.84</v>
       </c>
       <c r="BJ60">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK60">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL60">
         <v>1000</v>
@@ -15636,46 +15636,46 @@
         <v>1.01</v>
       </c>
       <c r="BN60">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO60">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BP60">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BQ60">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BR60">
         <v>1000</v>
       </c>
       <c r="BS60">
-        <v>1.01</v>
+        <v>44</v>
       </c>
       <c r="BT60">
-        <v>1000</v>
+        <v>4.3</v>
       </c>
       <c r="BU60">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BV60">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BW60">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BX60">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY60">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BZ60">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA60">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="CB60" t="s">
         <v>270</v>
@@ -15698,10 +15698,10 @@
         <v>263</v>
       </c>
       <c r="F61">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="G61">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="H61">
         <v>1.56</v>
@@ -15731,7 +15731,7 @@
         <v>2.1</v>
       </c>
       <c r="Q61">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="R61">
         <v>1.41</v>
@@ -15743,13 +15743,13 @@
         <v>1.98</v>
       </c>
       <c r="U61">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="V61">
         <v>2.74</v>
       </c>
       <c r="W61">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="X61">
         <v>16.5</v>
@@ -15788,7 +15788,7 @@
         <v>36</v>
       </c>
       <c r="AJ61">
-        <v>210</v>
+        <v>220</v>
       </c>
       <c r="AK61">
         <v>95</v>
@@ -15806,7 +15806,7 @@
         <v>8.4</v>
       </c>
       <c r="AP61">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AQ61">
         <v>8</v>
@@ -15854,22 +15854,22 @@
         <v>70</v>
       </c>
       <c r="BF61">
-        <v>100</v>
+        <v>40</v>
       </c>
       <c r="BG61">
         <v>7.8</v>
       </c>
       <c r="BH61">
-        <v>4.3</v>
+        <v>3.65</v>
       </c>
       <c r="BI61">
-        <v>2.9</v>
+        <v>3.35</v>
       </c>
       <c r="BJ61">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BK61">
-        <v>8</v>
+        <v>9.6</v>
       </c>
       <c r="BL61">
         <v>180</v>
@@ -15878,43 +15878,43 @@
         <v>26</v>
       </c>
       <c r="BN61">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BO61">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BP61">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="BQ61">
         <v>44</v>
       </c>
       <c r="BR61">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="BS61">
         <v>46</v>
       </c>
       <c r="BT61">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="BU61">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="BV61">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="BW61">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="BX61">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="BY61">
         <v>18.5</v>
       </c>
       <c r="BZ61">
-        <v>22</v>
+        <v>18.5</v>
       </c>
       <c r="CA61">
         <v>13</v>
@@ -15949,7 +15949,7 @@
         <v>3.15</v>
       </c>
       <c r="I62">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="J62">
         <v>4.5</v>
@@ -15964,7 +15964,7 @@
         <v>1.01</v>
       </c>
       <c r="N62">
-        <v>8.199999999999999</v>
+        <v>3.95</v>
       </c>
       <c r="O62">
         <v>1.07</v>
@@ -15988,10 +15988,10 @@
         <v>3.05</v>
       </c>
       <c r="V62">
-        <v>1.38</v>
+        <v>1.37</v>
       </c>
       <c r="W62">
-        <v>1.88</v>
+        <v>1.87</v>
       </c>
       <c r="X62">
         <v>1000</v>
@@ -16185,16 +16185,16 @@
         <v>1.79</v>
       </c>
       <c r="G63">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="H63">
         <v>5.1</v>
       </c>
       <c r="I63">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J63">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="K63">
         <v>4.1</v>
@@ -16203,37 +16203,37 @@
         <v>1.01</v>
       </c>
       <c r="M63">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N63">
-        <v>2.64</v>
+        <v>3.7</v>
       </c>
       <c r="O63">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="P63">
-        <v>1.8</v>
+        <v>1.93</v>
       </c>
       <c r="Q63">
         <v>1.92</v>
       </c>
       <c r="R63">
-        <v>1.29</v>
+        <v>1.36</v>
       </c>
       <c r="S63">
-        <v>2.08</v>
+        <v>3.3</v>
       </c>
       <c r="T63">
         <v>1.86</v>
       </c>
       <c r="U63">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="V63">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="W63">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="X63">
         <v>15.5</v>
@@ -16242,7 +16242,7 @@
         <v>19</v>
       </c>
       <c r="Z63">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="AA63">
         <v>150</v>
@@ -16260,7 +16260,7 @@
         <v>85</v>
       </c>
       <c r="AF63">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG63">
         <v>12</v>
@@ -16275,34 +16275,34 @@
         <v>22</v>
       </c>
       <c r="AK63">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="AL63">
-        <v>40</v>
+        <v>36</v>
       </c>
       <c r="AM63">
         <v>130</v>
       </c>
       <c r="AN63">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AO63">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AP63">
         <v>12</v>
       </c>
       <c r="AQ63">
-        <v>14.5</v>
+        <v>15.5</v>
       </c>
       <c r="AR63">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="AS63">
-        <v>6.4</v>
+        <v>7.4</v>
       </c>
       <c r="AT63">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AU63">
         <v>7.6</v>
@@ -16311,7 +16311,7 @@
         <v>18</v>
       </c>
       <c r="AW63">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="AX63">
         <v>9.800000000000001</v>
@@ -16323,7 +16323,7 @@
         <v>17.5</v>
       </c>
       <c r="BA63">
-        <v>6.2</v>
+        <v>7</v>
       </c>
       <c r="BB63">
         <v>16.5</v>
@@ -16332,16 +16332,16 @@
         <v>17</v>
       </c>
       <c r="BD63">
-        <v>5.7</v>
+        <v>6.4</v>
       </c>
       <c r="BE63">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="BF63">
         <v>9.199999999999999</v>
       </c>
       <c r="BG63">
-        <v>6.2</v>
+        <v>7.2</v>
       </c>
       <c r="BH63">
         <v>1000</v>
@@ -16430,7 +16430,7 @@
         <v>1.2</v>
       </c>
       <c r="H64">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="I64">
         <v>21</v>
@@ -16442,7 +16442,7 @@
         <v>9.4</v>
       </c>
       <c r="L64">
-        <v>1.01</v>
+        <v>1.21</v>
       </c>
       <c r="M64">
         <v>1.02</v>
@@ -16454,19 +16454,19 @@
         <v>1.13</v>
       </c>
       <c r="P64">
-        <v>3</v>
+        <v>2.78</v>
       </c>
       <c r="Q64">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="R64">
         <v>1.77</v>
       </c>
       <c r="S64">
+        <v>1.74</v>
+      </c>
+      <c r="T64">
         <v>1.98</v>
-      </c>
-      <c r="T64">
-        <v>2.08</v>
       </c>
       <c r="U64">
         <v>1.68</v>
@@ -16601,16 +16601,16 @@
         <v>1000</v>
       </c>
       <c r="BM64">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN64">
         <v>1000</v>
       </c>
       <c r="BO64">
-        <v>1.01</v>
+        <v>2.68</v>
       </c>
       <c r="BP64">
-        <v>1000</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BQ64">
         <v>1.01</v>
@@ -16619,13 +16619,13 @@
         <v>1000</v>
       </c>
       <c r="BS64">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BT64">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BU64">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BV64">
         <v>1000</v>
@@ -16637,13 +16637,13 @@
         <v>1000</v>
       </c>
       <c r="BY64">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BZ64">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="CA64">
-        <v>1.01</v>
+        <v>4.8</v>
       </c>
       <c r="CB64" t="s">
         <v>270</v>
@@ -16669,7 +16669,7 @@
         <v>4.2</v>
       </c>
       <c r="G65">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="H65">
         <v>1.82</v>
@@ -16687,25 +16687,25 @@
         <v>1.01</v>
       </c>
       <c r="M65">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N65">
         <v>4.3</v>
       </c>
       <c r="O65">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P65">
         <v>2.16</v>
       </c>
       <c r="Q65">
-        <v>1.66</v>
+        <v>1.74</v>
       </c>
       <c r="R65">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="S65">
-        <v>2.8</v>
+        <v>2.74</v>
       </c>
       <c r="T65">
         <v>1.71</v>
@@ -16762,16 +16762,16 @@
         <v>60</v>
       </c>
       <c r="AL65">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="AM65">
         <v>85</v>
       </c>
       <c r="AN65">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AO65">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="AP65">
         <v>16</v>
@@ -16798,7 +16798,7 @@
         <v>16</v>
       </c>
       <c r="AX65">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AY65">
         <v>15.5</v>
@@ -16807,22 +16807,22 @@
         <v>15</v>
       </c>
       <c r="BA65">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BB65">
+        <v>6</v>
+      </c>
+      <c r="BC65">
         <v>5.7</v>
       </c>
-      <c r="BC65">
-        <v>5.5</v>
-      </c>
       <c r="BD65">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="BE65">
-        <v>5.7</v>
+        <v>5.9</v>
       </c>
       <c r="BF65">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="BG65">
         <v>8.199999999999999</v>
@@ -16920,19 +16920,19 @@
         <v>21</v>
       </c>
       <c r="J66">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="K66">
         <v>10</v>
       </c>
       <c r="L66">
-        <v>1.17</v>
+        <v>1.21</v>
       </c>
       <c r="M66">
         <v>1.02</v>
       </c>
       <c r="N66">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="O66">
         <v>1.12</v>
@@ -16947,7 +16947,7 @@
         <v>2.06</v>
       </c>
       <c r="S66">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="T66">
         <v>2.06</v>
@@ -16959,13 +16959,13 @@
         <v>1.05</v>
       </c>
       <c r="W66">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="X66">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="Y66">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="Z66">
         <v>1000</v>
@@ -16986,10 +16986,10 @@
         <v>360</v>
       </c>
       <c r="AF66">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG66">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH66">
         <v>44</v>
@@ -17019,13 +17019,13 @@
         <v>40</v>
       </c>
       <c r="AQ66">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AR66">
         <v>48</v>
       </c>
       <c r="AS66">
-        <v>29</v>
+        <v>18.5</v>
       </c>
       <c r="AT66">
         <v>12.5</v>
@@ -17034,13 +17034,13 @@
         <v>22</v>
       </c>
       <c r="AV66">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AW66">
-        <v>100</v>
+        <v>23</v>
       </c>
       <c r="AX66">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY66">
         <v>12</v>
@@ -17064,13 +17064,13 @@
         <v>46</v>
       </c>
       <c r="BF66">
-        <v>2.68</v>
+        <v>2.7</v>
       </c>
       <c r="BG66">
-        <v>27</v>
+        <v>22</v>
       </c>
       <c r="BH66">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BI66">
         <v>1.01</v>
@@ -17088,13 +17088,13 @@
         <v>1.01</v>
       </c>
       <c r="BN66">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BO66">
         <v>1.01</v>
       </c>
       <c r="BP66">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="BQ66">
         <v>1.01</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-31.xlsx
@@ -826,7 +826,7 @@
     <t>Melgar</t>
   </si>
   <si>
-    <t>2026-08-29 20:38:30</t>
+    <t>2026-08-29 23:00:45</t>
   </si>
 </sst>
 </file>
@@ -1423,10 +1423,10 @@
         <v>1.58</v>
       </c>
       <c r="G2">
-        <v>1.65</v>
+        <v>1.64</v>
       </c>
       <c r="H2">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I2">
         <v>6.6</v>
@@ -1435,7 +1435,7 @@
         <v>4.2</v>
       </c>
       <c r="K2">
-        <v>4.8</v>
+        <v>4.7</v>
       </c>
       <c r="L2">
         <v>1.01</v>
@@ -1465,19 +1465,19 @@
         <v>1.82</v>
       </c>
       <c r="U2">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="V2">
         <v>1.18</v>
       </c>
       <c r="W2">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="X2">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="Y2">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="Z2">
         <v>65</v>
@@ -1492,7 +1492,7 @@
         <v>12.5</v>
       </c>
       <c r="AD2">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="AE2">
         <v>1000</v>
@@ -1501,7 +1501,7 @@
         <v>12.5</v>
       </c>
       <c r="AG2">
-        <v>12</v>
+        <v>10.5</v>
       </c>
       <c r="AH2">
         <v>25</v>
@@ -1510,10 +1510,10 @@
         <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AK2">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AL2">
         <v>40</v>
@@ -1531,13 +1531,13 @@
         <v>16.5</v>
       </c>
       <c r="AQ2">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="AR2">
         <v>26</v>
       </c>
       <c r="AS2">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="AT2">
         <v>8.199999999999999</v>
@@ -1564,7 +1564,7 @@
         <v>34</v>
       </c>
       <c r="BB2">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BC2">
         <v>12</v>
@@ -1579,7 +1579,7 @@
         <v>7.2</v>
       </c>
       <c r="BG2">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BH2">
         <v>1000</v>
@@ -1662,22 +1662,22 @@
         <v>205</v>
       </c>
       <c r="F3">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="G3">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="H3">
         <v>9.800000000000001</v>
       </c>
       <c r="I3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="J3">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="K3">
-        <v>7.2</v>
+        <v>6.6</v>
       </c>
       <c r="L3">
         <v>1.01</v>
@@ -1689,28 +1689,28 @@
         <v>7</v>
       </c>
       <c r="O3">
-        <v>1.12</v>
+        <v>1.14</v>
       </c>
       <c r="P3">
         <v>3.05</v>
       </c>
       <c r="Q3">
-        <v>1.4</v>
+        <v>1.43</v>
       </c>
       <c r="R3">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="S3">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="T3">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="U3">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="V3">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="W3">
         <v>3.9</v>
@@ -1728,13 +1728,13 @@
         <v>350</v>
       </c>
       <c r="AB3">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AC3">
         <v>16.5</v>
       </c>
       <c r="AD3">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="AE3">
         <v>150</v>
@@ -1758,7 +1758,7 @@
         <v>14.5</v>
       </c>
       <c r="AL3">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AM3">
         <v>120</v>
@@ -1770,16 +1770,16 @@
         <v>140</v>
       </c>
       <c r="AP3">
-        <v>6.8</v>
+        <v>7.2</v>
       </c>
       <c r="AQ3">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AR3">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS3">
-        <v>8</v>
+        <v>8.6</v>
       </c>
       <c r="AT3">
         <v>11</v>
@@ -1788,10 +1788,10 @@
         <v>13</v>
       </c>
       <c r="AV3">
-        <v>6.8</v>
+        <v>30</v>
       </c>
       <c r="AW3">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AX3">
         <v>9</v>
@@ -1803,7 +1803,7 @@
         <v>21</v>
       </c>
       <c r="BA3">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BB3">
         <v>9.800000000000001</v>
@@ -1812,16 +1812,16 @@
         <v>11.5</v>
       </c>
       <c r="BD3">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BE3">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BF3">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="BG3">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1907,10 +1907,10 @@
         <v>2.06</v>
       </c>
       <c r="G4">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="H4">
-        <v>2.84</v>
+        <v>2.98</v>
       </c>
       <c r="I4">
         <v>4.7</v>
@@ -1919,7 +1919,7 @@
         <v>2.98</v>
       </c>
       <c r="K4">
-        <v>6</v>
+        <v>4.4</v>
       </c>
       <c r="L4">
         <v>1.01</v>
@@ -2146,55 +2146,55 @@
         <v>207</v>
       </c>
       <c r="F5">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G5">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="H5">
         <v>3.75</v>
       </c>
       <c r="I5">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="J5">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="K5">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="L5">
         <v>1.01</v>
       </c>
       <c r="M5">
-        <v>1.01</v>
+        <v>1.12</v>
       </c>
       <c r="N5">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="O5">
-        <v>1.48</v>
+        <v>1.52</v>
       </c>
       <c r="P5">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q5">
         <v>2.58</v>
       </c>
       <c r="R5">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="S5">
-        <v>5</v>
+        <v>5.2</v>
       </c>
       <c r="T5">
-        <v>1.89</v>
+        <v>2.08</v>
       </c>
       <c r="U5">
-        <v>1.66</v>
+        <v>1.81</v>
       </c>
       <c r="V5">
-        <v>1.31</v>
+        <v>1.33</v>
       </c>
       <c r="W5">
         <v>1.71</v>
@@ -2206,10 +2206,10 @@
         <v>11.5</v>
       </c>
       <c r="Z5">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA5">
-        <v>890</v>
+        <v>790</v>
       </c>
       <c r="AB5">
         <v>7.8</v>
@@ -2221,7 +2221,7 @@
         <v>21</v>
       </c>
       <c r="AE5">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="AF5">
         <v>16</v>
@@ -2233,7 +2233,7 @@
         <v>28</v>
       </c>
       <c r="AI5">
-        <v>890</v>
+        <v>790</v>
       </c>
       <c r="AJ5">
         <v>40</v>
@@ -2245,13 +2245,13 @@
         <v>75</v>
       </c>
       <c r="AM5">
-        <v>900</v>
+        <v>800</v>
       </c>
       <c r="AN5">
         <v>40</v>
       </c>
       <c r="AO5">
-        <v>890</v>
+        <v>790</v>
       </c>
       <c r="AP5">
         <v>6.8</v>
@@ -2275,16 +2275,16 @@
         <v>12.5</v>
       </c>
       <c r="AW5">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="AX5">
         <v>11.5</v>
       </c>
       <c r="AY5">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ5">
-        <v>5.1</v>
+        <v>20</v>
       </c>
       <c r="BA5">
         <v>6</v>
@@ -2293,16 +2293,16 @@
         <v>5.4</v>
       </c>
       <c r="BC5">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BD5">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BE5">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="BF5">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="BG5">
         <v>6</v>
@@ -2397,157 +2397,157 @@
         <v>4.2</v>
       </c>
       <c r="I6">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="J6">
         <v>3.1</v>
       </c>
       <c r="K6">
-        <v>3.7</v>
+        <v>3.4</v>
       </c>
       <c r="L6">
         <v>1.01</v>
       </c>
       <c r="M6">
-        <v>1.01</v>
+        <v>1.09</v>
       </c>
       <c r="N6">
-        <v>2.7</v>
+        <v>2.78</v>
       </c>
       <c r="O6">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="P6">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="Q6">
         <v>2.46</v>
       </c>
       <c r="R6">
-        <v>1.13</v>
+        <v>1.21</v>
       </c>
       <c r="S6">
-        <v>4.5</v>
+        <v>5</v>
       </c>
       <c r="T6">
-        <v>1.86</v>
+        <v>2.08</v>
       </c>
       <c r="U6">
-        <v>1.6</v>
+        <v>1.79</v>
       </c>
       <c r="V6">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="W6">
         <v>1.83</v>
       </c>
       <c r="X6">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Y6">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="Z6">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AA6">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AB6">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AC6">
-        <v>9.4</v>
+        <v>7.6</v>
       </c>
       <c r="AD6">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE6">
         <v>100</v>
       </c>
       <c r="AF6">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AG6">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH6">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI6">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ6">
         <v>36</v>
       </c>
       <c r="AK6">
-        <v>38</v>
+        <v>34</v>
       </c>
       <c r="AL6">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AM6">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AN6">
         <v>34</v>
       </c>
       <c r="AO6">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AP6">
-        <v>1.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AQ6">
-        <v>1.5</v>
+        <v>10.5</v>
       </c>
       <c r="AR6">
-        <v>1.45</v>
+        <v>4.5</v>
       </c>
       <c r="AS6">
-        <v>1.5</v>
+        <v>4.9</v>
       </c>
       <c r="AT6">
-        <v>1.28</v>
+        <v>6.2</v>
       </c>
       <c r="AU6">
-        <v>1.3</v>
+        <v>5.6</v>
       </c>
       <c r="AV6">
-        <v>1.5</v>
+        <v>4.1</v>
       </c>
       <c r="AW6">
-        <v>1.48</v>
+        <v>4.8</v>
       </c>
       <c r="AX6">
-        <v>1.5</v>
+        <v>10</v>
       </c>
       <c r="AY6">
-        <v>1.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ6">
-        <v>1.5</v>
+        <v>4.3</v>
       </c>
       <c r="BA6">
-        <v>1.5</v>
+        <v>4.9</v>
       </c>
       <c r="BB6">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC6">
-        <v>1.45</v>
+        <v>20</v>
       </c>
       <c r="BD6">
-        <v>1.5</v>
+        <v>4.7</v>
       </c>
       <c r="BE6">
-        <v>1.5</v>
+        <v>4.9</v>
       </c>
       <c r="BF6">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="BG6">
-        <v>1.5</v>
+        <v>4.9</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2630,166 +2630,166 @@
         <v>209</v>
       </c>
       <c r="F7">
-        <v>1.54</v>
+        <v>1.58</v>
       </c>
       <c r="G7">
-        <v>1.58</v>
+        <v>1.6</v>
       </c>
       <c r="H7">
-        <v>6.2</v>
+        <v>5.7</v>
       </c>
       <c r="I7">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="J7">
         <v>4.8</v>
       </c>
       <c r="K7">
-        <v>5.3</v>
+        <v>5</v>
       </c>
       <c r="L7">
         <v>1.01</v>
       </c>
       <c r="M7">
-        <v>1.04</v>
+        <v>1.03</v>
       </c>
       <c r="N7">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="O7">
         <v>1.2</v>
       </c>
       <c r="P7">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="Q7">
         <v>1.58</v>
       </c>
       <c r="R7">
-        <v>1.61</v>
+        <v>1.63</v>
       </c>
       <c r="S7">
-        <v>2.42</v>
+        <v>2.48</v>
       </c>
       <c r="T7">
-        <v>1.71</v>
+        <v>1.7</v>
       </c>
       <c r="U7">
         <v>2.28</v>
       </c>
       <c r="V7">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="W7">
-        <v>2.72</v>
+        <v>2.66</v>
       </c>
       <c r="X7">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="Y7">
-        <v>50</v>
+        <v>27</v>
       </c>
       <c r="Z7">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA7">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB7">
-        <v>16.5</v>
+        <v>12</v>
       </c>
       <c r="AC7">
-        <v>14.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD7">
-        <v>38</v>
+        <v>24</v>
       </c>
       <c r="AE7">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AF7">
-        <v>14.5</v>
+        <v>12</v>
       </c>
       <c r="AG7">
+        <v>10.5</v>
+      </c>
+      <c r="AH7">
+        <v>19.5</v>
+      </c>
+      <c r="AI7">
+        <v>65</v>
+      </c>
+      <c r="AJ7">
+        <v>17</v>
+      </c>
+      <c r="AK7">
+        <v>16</v>
+      </c>
+      <c r="AL7">
+        <v>29</v>
+      </c>
+      <c r="AM7">
+        <v>80</v>
+      </c>
+      <c r="AN7">
+        <v>6.8</v>
+      </c>
+      <c r="AO7">
+        <v>65</v>
+      </c>
+      <c r="AP7">
+        <v>21</v>
+      </c>
+      <c r="AQ7">
+        <v>21</v>
+      </c>
+      <c r="AR7">
+        <v>8.6</v>
+      </c>
+      <c r="AS7">
+        <v>9.6</v>
+      </c>
+      <c r="AT7">
+        <v>10</v>
+      </c>
+      <c r="AU7">
+        <v>9.6</v>
+      </c>
+      <c r="AV7">
+        <v>18.5</v>
+      </c>
+      <c r="AW7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AX7">
+        <v>10</v>
+      </c>
+      <c r="AY7">
+        <v>9</v>
+      </c>
+      <c r="AZ7">
+        <v>16</v>
+      </c>
+      <c r="BA7">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="BB7">
+        <v>14</v>
+      </c>
+      <c r="BC7">
         <v>13.5</v>
       </c>
-      <c r="AH7">
-        <v>32</v>
-      </c>
-      <c r="AI7">
-        <v>1000</v>
-      </c>
-      <c r="AJ7">
-        <v>22</v>
-      </c>
-      <c r="AK7">
-        <v>20</v>
-      </c>
-      <c r="AL7">
-        <v>55</v>
-      </c>
-      <c r="AM7">
-        <v>1000</v>
-      </c>
-      <c r="AN7">
-        <v>7.4</v>
-      </c>
-      <c r="AO7">
-        <v>1000</v>
-      </c>
-      <c r="AP7">
-        <v>2.56</v>
-      </c>
-      <c r="AQ7">
-        <v>2.44</v>
-      </c>
-      <c r="AR7">
-        <v>2.56</v>
-      </c>
-      <c r="AS7">
-        <v>2.56</v>
-      </c>
-      <c r="AT7">
-        <v>2.22</v>
-      </c>
-      <c r="AU7">
-        <v>2.16</v>
-      </c>
-      <c r="AV7">
-        <v>2.4</v>
-      </c>
-      <c r="AW7">
-        <v>2.56</v>
-      </c>
-      <c r="AX7">
-        <v>2.16</v>
-      </c>
-      <c r="AY7">
-        <v>2.14</v>
-      </c>
-      <c r="AZ7">
-        <v>2.38</v>
-      </c>
-      <c r="BA7">
-        <v>2.56</v>
-      </c>
-      <c r="BB7">
-        <v>2.3</v>
-      </c>
-      <c r="BC7">
-        <v>2.28</v>
-      </c>
       <c r="BD7">
-        <v>2.46</v>
+        <v>7.8</v>
       </c>
       <c r="BE7">
-        <v>2.56</v>
+        <v>9</v>
       </c>
       <c r="BF7">
-        <v>1.89</v>
+        <v>5.8</v>
       </c>
       <c r="BG7">
-        <v>2.56</v>
+        <v>9</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2872,19 +2872,19 @@
         <v>210</v>
       </c>
       <c r="F8">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G8">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H8">
         <v>1.08</v>
       </c>
       <c r="I8">
-        <v>110</v>
+        <v>2.5</v>
       </c>
       <c r="J8">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="K8">
         <v>300</v>
@@ -2896,22 +2896,22 @@
         <v>1.01</v>
       </c>
       <c r="N8">
-        <v>1.25</v>
+        <v>3.6</v>
       </c>
       <c r="O8">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="P8">
         <v>1.25</v>
       </c>
       <c r="Q8">
-        <v>1.28</v>
+        <v>1.75</v>
       </c>
       <c r="R8">
         <v>1.18</v>
       </c>
       <c r="S8">
-        <v>1.28</v>
+        <v>1.01</v>
       </c>
       <c r="T8">
         <v>1.01</v>
@@ -2920,7 +2920,7 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="W8">
         <v>1.02</v>
@@ -3114,19 +3114,19 @@
         <v>211</v>
       </c>
       <c r="F9">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G9">
         <v>1000</v>
       </c>
       <c r="H9">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I9">
         <v>1000</v>
       </c>
       <c r="J9">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K9">
         <v>240</v>
@@ -3144,7 +3144,7 @@
         <v>1.12</v>
       </c>
       <c r="P9">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="Q9">
         <v>1.12</v>
@@ -3356,16 +3356,16 @@
         <v>212</v>
       </c>
       <c r="F10">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="G10">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="H10">
         <v>1.08</v>
       </c>
       <c r="I10">
-        <v>110</v>
+        <v>1.8</v>
       </c>
       <c r="J10">
         <v>1.09</v>
@@ -3380,13 +3380,13 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="O10">
         <v>1.24</v>
       </c>
       <c r="P10">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="Q10">
         <v>1.25</v>
@@ -3404,7 +3404,7 @@
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W10">
         <v>1.02</v>
@@ -3598,7 +3598,7 @@
         <v>213</v>
       </c>
       <c r="F11">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G11">
         <v>1000</v>
@@ -3610,7 +3610,7 @@
         <v>1000</v>
       </c>
       <c r="J11">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="K11">
         <v>230</v>
@@ -3840,19 +3840,19 @@
         <v>214</v>
       </c>
       <c r="F12">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="G12">
         <v>110</v>
       </c>
       <c r="H12">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="I12">
         <v>110</v>
       </c>
       <c r="J12">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K12">
         <v>280</v>
@@ -4106,13 +4106,13 @@
         <v>1.01</v>
       </c>
       <c r="N13">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="O13">
         <v>1.15</v>
       </c>
       <c r="P13">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="Q13">
         <v>1.5</v>
@@ -4327,19 +4327,19 @@
         <v>2.62</v>
       </c>
       <c r="G14">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="H14">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="I14">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J14">
         <v>2.74</v>
       </c>
       <c r="K14">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L14">
         <v>1.01</v>
@@ -4348,7 +4348,7 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>2.32</v>
+        <v>3.4</v>
       </c>
       <c r="O14">
         <v>1.28</v>
@@ -4372,10 +4372,10 @@
         <v>1.01</v>
       </c>
       <c r="V14">
+        <v>1.49</v>
+      </c>
+      <c r="W14">
         <v>1.47</v>
-      </c>
-      <c r="W14">
-        <v>1.46</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4566,22 +4566,22 @@
         <v>217</v>
       </c>
       <c r="F15">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="G15">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="H15">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="I15">
         <v>3.1</v>
       </c>
       <c r="J15">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="K15">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4590,22 +4590,22 @@
         <v>1.01</v>
       </c>
       <c r="N15">
-        <v>2.3</v>
+        <v>4.3</v>
       </c>
       <c r="O15">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P15">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="Q15">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="R15">
-        <v>1.55</v>
+        <v>1.56</v>
       </c>
       <c r="S15">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="T15">
         <v>1.01</v>
@@ -4617,7 +4617,7 @@
         <v>1.48</v>
       </c>
       <c r="W15">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4814,10 +4814,10 @@
         <v>2.66</v>
       </c>
       <c r="H16">
-        <v>2.74</v>
+        <v>2.66</v>
       </c>
       <c r="I16">
-        <v>3.55</v>
+        <v>3.75</v>
       </c>
       <c r="J16">
         <v>3.2</v>
@@ -4832,22 +4832,22 @@
         <v>1.01</v>
       </c>
       <c r="N16">
-        <v>4.4</v>
+        <v>2.28</v>
       </c>
       <c r="O16">
-        <v>1.24</v>
+        <v>1.22</v>
       </c>
       <c r="P16">
-        <v>2.08</v>
+        <v>1.96</v>
       </c>
       <c r="Q16">
         <v>1.66</v>
       </c>
       <c r="R16">
-        <v>1.45</v>
+        <v>1.34</v>
       </c>
       <c r="S16">
-        <v>2.74</v>
+        <v>2.6</v>
       </c>
       <c r="T16">
         <v>1.01</v>
@@ -4856,7 +4856,7 @@
         <v>1.01</v>
       </c>
       <c r="V16">
-        <v>1.39</v>
+        <v>1.36</v>
       </c>
       <c r="W16">
         <v>1.6</v>
@@ -5295,7 +5295,7 @@
         <v>4.1</v>
       </c>
       <c r="G18">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="H18">
         <v>1.67</v>
@@ -5304,13 +5304,13 @@
         <v>1.84</v>
       </c>
       <c r="J18">
-        <v>4.3</v>
+        <v>3.55</v>
       </c>
       <c r="K18">
         <v>5.1</v>
       </c>
       <c r="L18">
-        <v>1.22</v>
+        <v>1.01</v>
       </c>
       <c r="M18">
         <v>1.01</v>
@@ -5319,13 +5319,13 @@
         <v>2.5</v>
       </c>
       <c r="O18">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="P18">
         <v>2.5</v>
       </c>
       <c r="Q18">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="R18">
         <v>1.62</v>
@@ -5558,7 +5558,7 @@
         <v>1.01</v>
       </c>
       <c r="N19">
-        <v>2.26</v>
+        <v>1.01</v>
       </c>
       <c r="O19">
         <v>1.16</v>
@@ -6033,7 +6033,7 @@
         <v>3.4</v>
       </c>
       <c r="K21">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L21">
         <v>1.28</v>
@@ -6260,13 +6260,13 @@
         <v>224</v>
       </c>
       <c r="F22">
-        <v>1.97</v>
+        <v>2</v>
       </c>
       <c r="G22">
         <v>2.12</v>
       </c>
       <c r="H22">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I22">
         <v>4.2</v>
@@ -6308,7 +6308,7 @@
         <v>2.04</v>
       </c>
       <c r="V22">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W22">
         <v>1.9</v>
@@ -6317,7 +6317,7 @@
         <v>19</v>
       </c>
       <c r="Y22">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Z22">
         <v>36</v>
@@ -6362,7 +6362,7 @@
         <v>95</v>
       </c>
       <c r="AN22">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AO22">
         <v>46</v>
@@ -6508,7 +6508,7 @@
         <v>110</v>
       </c>
       <c r="H23">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="I23">
         <v>110</v>
@@ -6532,7 +6532,7 @@
         <v>1.13</v>
       </c>
       <c r="P23">
-        <v>1.18</v>
+        <v>1.2</v>
       </c>
       <c r="Q23">
         <v>1.13</v>
@@ -6744,19 +6744,19 @@
         <v>226</v>
       </c>
       <c r="F24">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="G24">
         <v>110</v>
       </c>
       <c r="H24">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="I24">
         <v>110</v>
       </c>
       <c r="J24">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K24">
         <v>210</v>
@@ -6986,7 +6986,7 @@
         <v>227</v>
       </c>
       <c r="F25">
-        <v>1.04</v>
+        <v>1.06</v>
       </c>
       <c r="G25">
         <v>110</v>
@@ -6998,7 +6998,7 @@
         <v>110</v>
       </c>
       <c r="J25">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K25">
         <v>410</v>
@@ -7010,7 +7010,7 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="O25">
         <v>1.01</v>
@@ -7025,7 +7025,7 @@
         <v>1.18</v>
       </c>
       <c r="S25">
-        <v>1.3</v>
+        <v>1.01</v>
       </c>
       <c r="T25">
         <v>1.01</v>
@@ -7252,19 +7252,19 @@
         <v>1.01</v>
       </c>
       <c r="N26">
-        <v>2.92</v>
+        <v>2.86</v>
       </c>
       <c r="O26">
         <v>1.32</v>
       </c>
       <c r="P26">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="Q26">
-        <v>1.86</v>
+        <v>1.83</v>
       </c>
       <c r="R26">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="S26">
         <v>2.7</v>
@@ -7715,13 +7715,13 @@
         <v>2.26</v>
       </c>
       <c r="G28">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="H28">
         <v>2.92</v>
       </c>
       <c r="I28">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="J28">
         <v>1.09</v>
@@ -7748,7 +7748,7 @@
         <v>1.73</v>
       </c>
       <c r="R28">
-        <v>1.42</v>
+        <v>1.47</v>
       </c>
       <c r="S28">
         <v>2.78</v>
@@ -7763,7 +7763,7 @@
         <v>1.42</v>
       </c>
       <c r="W28">
-        <v>1.67</v>
+        <v>1.65</v>
       </c>
       <c r="X28">
         <v>1000</v>
@@ -8196,7 +8196,7 @@
         <v>232</v>
       </c>
       <c r="F30">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="G30">
         <v>4.1</v>
@@ -8211,7 +8211,7 @@
         <v>4.2</v>
       </c>
       <c r="K30">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L30">
         <v>1.01</v>
@@ -8226,7 +8226,7 @@
         <v>1.2</v>
       </c>
       <c r="P30">
-        <v>2.48</v>
+        <v>2.5</v>
       </c>
       <c r="Q30">
         <v>1.58</v>
@@ -8349,7 +8349,7 @@
         <v>30</v>
       </c>
       <c r="BE30">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BF30">
         <v>21</v>
@@ -8680,19 +8680,19 @@
         <v>234</v>
       </c>
       <c r="F32">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="G32">
         <v>110</v>
       </c>
       <c r="H32">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="I32">
         <v>110</v>
       </c>
       <c r="J32">
-        <v>1.04</v>
+        <v>1.08</v>
       </c>
       <c r="K32">
         <v>300</v>
@@ -8704,7 +8704,7 @@
         <v>1.01</v>
       </c>
       <c r="N32">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="O32">
         <v>1.02</v>
@@ -8728,7 +8728,7 @@
         <v>1.01</v>
       </c>
       <c r="V32">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="W32">
         <v>1.01</v>
@@ -9188,7 +9188,7 @@
         <v>1.08</v>
       </c>
       <c r="N34">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="O34">
         <v>1.35</v>
@@ -9305,22 +9305,22 @@
         <v>14.5</v>
       </c>
       <c r="BA34">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BB34">
-        <v>55</v>
+        <v>1.01</v>
       </c>
       <c r="BC34">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BD34">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BE34">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="BF34">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BG34">
         <v>15</v>
@@ -9436,22 +9436,22 @@
         <v>1.19</v>
       </c>
       <c r="P35">
-        <v>2.28</v>
+        <v>2.32</v>
       </c>
       <c r="Q35">
         <v>1.53</v>
       </c>
       <c r="R35">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="S35">
         <v>2.5</v>
       </c>
       <c r="T35">
-        <v>1.68</v>
+        <v>1.81</v>
       </c>
       <c r="U35">
-        <v>1.87</v>
+        <v>2.04</v>
       </c>
       <c r="V35">
         <v>1.12</v>
@@ -9660,7 +9660,7 @@
         <v>1.68</v>
       </c>
       <c r="J36">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K36">
         <v>4.3</v>
@@ -9672,19 +9672,19 @@
         <v>1.06</v>
       </c>
       <c r="N36">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="O36">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P36">
-        <v>1.95</v>
+        <v>1.99</v>
       </c>
       <c r="Q36">
         <v>1.86</v>
       </c>
       <c r="R36">
-        <v>1.37</v>
+        <v>1.39</v>
       </c>
       <c r="S36">
         <v>3.2</v>
@@ -9759,7 +9759,7 @@
         <v>13.5</v>
       </c>
       <c r="AQ36">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="AR36">
         <v>9</v>
@@ -9798,7 +9798,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="BD36">
-        <v>9.800000000000001</v>
+        <v>65</v>
       </c>
       <c r="BE36">
         <v>9.199999999999999</v>
@@ -9953,7 +9953,7 @@
         <v>7.8</v>
       </c>
       <c r="AA37">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AB37">
         <v>24</v>
@@ -9989,7 +9989,7 @@
         <v>160</v>
       </c>
       <c r="AM37">
-        <v>240</v>
+        <v>260</v>
       </c>
       <c r="AN37">
         <v>280</v>
@@ -10025,7 +10025,7 @@
         <v>32</v>
       </c>
       <c r="AY37">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AZ37">
         <v>27</v>
@@ -10034,7 +10034,7 @@
         <v>42</v>
       </c>
       <c r="BB37">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC37">
         <v>20</v>
@@ -10043,10 +10043,10 @@
         <v>20</v>
       </c>
       <c r="BE37">
-        <v>19.5</v>
+        <v>17.5</v>
       </c>
       <c r="BF37">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BG37">
         <v>8.6</v>
@@ -10156,22 +10156,22 @@
         <v>1.01</v>
       </c>
       <c r="N38">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="O38">
         <v>1.11</v>
       </c>
       <c r="P38">
-        <v>2.88</v>
+        <v>2.9</v>
       </c>
       <c r="Q38">
-        <v>1.44</v>
+        <v>1.38</v>
       </c>
       <c r="R38">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="S38">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="T38">
         <v>1.01</v>
@@ -10377,10 +10377,10 @@
         <v>3.15</v>
       </c>
       <c r="G39">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="H39">
-        <v>2.24</v>
+        <v>2.32</v>
       </c>
       <c r="I39">
         <v>2.48</v>
@@ -10389,10 +10389,10 @@
         <v>3.45</v>
       </c>
       <c r="K39">
-        <v>4.4</v>
+        <v>3.75</v>
       </c>
       <c r="L39">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M39">
         <v>1.07</v>
@@ -10407,7 +10407,7 @@
         <v>1.96</v>
       </c>
       <c r="Q39">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="R39">
         <v>1.37</v>
@@ -10425,7 +10425,7 @@
         <v>1.67</v>
       </c>
       <c r="W39">
-        <v>1.39</v>
+        <v>1.41</v>
       </c>
       <c r="X39">
         <v>18</v>
@@ -10536,61 +10536,61 @@
         <v>14</v>
       </c>
       <c r="BH39">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BI39">
         <v>2.76</v>
       </c>
       <c r="BJ39">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK39">
         <v>1.01</v>
       </c>
       <c r="BL39">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM39">
         <v>1.01</v>
       </c>
       <c r="BN39">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BO39">
-        <v>1.01</v>
+        <v>4.9</v>
       </c>
       <c r="BP39">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BQ39">
         <v>1.01</v>
       </c>
       <c r="BR39">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS39">
         <v>1.01</v>
       </c>
       <c r="BT39">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU39">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="BV39">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BW39">
         <v>1.01</v>
       </c>
       <c r="BX39">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BY39">
         <v>1.01</v>
       </c>
       <c r="BZ39">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="CA39">
         <v>1.01</v>
@@ -10640,7 +10640,7 @@
         <v>1.07</v>
       </c>
       <c r="N40">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="O40">
         <v>1.07</v>
@@ -10649,7 +10649,7 @@
         <v>1.51</v>
       </c>
       <c r="Q40">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="R40">
         <v>1.18</v>
@@ -10858,22 +10858,22 @@
         <v>243</v>
       </c>
       <c r="F41">
-        <v>1.71</v>
+        <v>1.68</v>
       </c>
       <c r="G41">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="H41">
-        <v>5.7</v>
+        <v>4.7</v>
       </c>
       <c r="I41">
         <v>6.6</v>
       </c>
       <c r="J41">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="K41">
-        <v>3.95</v>
+        <v>5.2</v>
       </c>
       <c r="L41">
         <v>1.36</v>
@@ -10882,34 +10882,34 @@
         <v>1.06</v>
       </c>
       <c r="N41">
-        <v>3.15</v>
+        <v>2.98</v>
       </c>
       <c r="O41">
-        <v>1.39</v>
+        <v>1.35</v>
       </c>
       <c r="P41">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="Q41">
         <v>2.08</v>
       </c>
       <c r="R41">
-        <v>1.28</v>
+        <v>1.25</v>
       </c>
       <c r="S41">
-        <v>4.1</v>
+        <v>3.75</v>
       </c>
       <c r="T41">
         <v>1.82</v>
       </c>
       <c r="U41">
-        <v>1.64</v>
+        <v>1.01</v>
       </c>
       <c r="V41">
         <v>1.18</v>
       </c>
       <c r="W41">
-        <v>2.22</v>
+        <v>2.18</v>
       </c>
       <c r="X41">
         <v>14.5</v>
@@ -10963,7 +10963,7 @@
         <v>17</v>
       </c>
       <c r="AO41">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="AP41">
         <v>8.800000000000001</v>
@@ -11100,22 +11100,22 @@
         <v>244</v>
       </c>
       <c r="F42">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="G42">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="H42">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="I42">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J42">
         <v>3.65</v>
       </c>
       <c r="K42">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L42">
         <v>1.01</v>
@@ -11127,28 +11127,28 @@
         <v>3.15</v>
       </c>
       <c r="O42">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P42">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="Q42">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="R42">
         <v>1.28</v>
       </c>
       <c r="S42">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T42">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="U42">
         <v>1.86</v>
       </c>
       <c r="V42">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W42">
         <v>2.18</v>
@@ -11160,91 +11160,91 @@
         <v>16</v>
       </c>
       <c r="Z42">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AA42">
-        <v>170</v>
+        <v>190</v>
       </c>
       <c r="AB42">
         <v>7.4</v>
       </c>
       <c r="AC42">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD42">
-        <v>23</v>
+        <v>27</v>
       </c>
       <c r="AE42">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="AF42">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG42">
-        <v>970</v>
+        <v>10.5</v>
       </c>
       <c r="AH42">
         <v>23</v>
       </c>
       <c r="AI42">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AJ42">
         <v>19.5</v>
       </c>
       <c r="AK42">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="AL42">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM42">
-        <v>200</v>
+        <v>180</v>
       </c>
       <c r="AN42">
         <v>15</v>
       </c>
       <c r="AO42">
-        <v>130</v>
+        <v>160</v>
       </c>
       <c r="AP42">
         <v>10.5</v>
       </c>
       <c r="AQ42">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="AR42">
         <v>36</v>
       </c>
       <c r="AS42">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AT42">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AU42">
-        <v>5.4</v>
+        <v>7.4</v>
       </c>
       <c r="AV42">
         <v>20</v>
       </c>
       <c r="AW42">
-        <v>13.5</v>
+        <v>11</v>
       </c>
       <c r="AX42">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY42">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ42">
         <v>20</v>
       </c>
       <c r="BA42">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BB42">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="BC42">
         <v>19</v>
@@ -11253,13 +11253,13 @@
         <v>40</v>
       </c>
       <c r="BE42">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BF42">
         <v>13</v>
       </c>
       <c r="BG42">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH42">
         <v>1000</v>
@@ -11342,19 +11342,19 @@
         <v>245</v>
       </c>
       <c r="F43">
-        <v>1.67</v>
+        <v>1.69</v>
       </c>
       <c r="G43">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="H43">
         <v>5.2</v>
       </c>
       <c r="I43">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="J43">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K43">
         <v>4.5</v>
@@ -11363,7 +11363,7 @@
         <v>1.01</v>
       </c>
       <c r="M43">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N43">
         <v>4.6</v>
@@ -11372,28 +11372,28 @@
         <v>1.23</v>
       </c>
       <c r="P43">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="Q43">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="R43">
-        <v>1.46</v>
+        <v>1.5</v>
       </c>
       <c r="S43">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="T43">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="U43">
-        <v>2.06</v>
+        <v>2.12</v>
       </c>
       <c r="V43">
         <v>1.21</v>
       </c>
       <c r="W43">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X43">
         <v>21</v>
@@ -11584,7 +11584,7 @@
         <v>246</v>
       </c>
       <c r="F44">
-        <v>1.97</v>
+        <v>1.99</v>
       </c>
       <c r="G44">
         <v>2.08</v>
@@ -11593,13 +11593,13 @@
         <v>3.55</v>
       </c>
       <c r="I44">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="J44">
         <v>4.1</v>
       </c>
       <c r="K44">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="L44">
         <v>1.01</v>
@@ -11617,13 +11617,13 @@
         <v>2.62</v>
       </c>
       <c r="Q44">
-        <v>1.48</v>
+        <v>1.54</v>
       </c>
       <c r="R44">
         <v>1.64</v>
       </c>
       <c r="S44">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="T44">
         <v>1.53</v>
@@ -11632,16 +11632,16 @@
         <v>2.6</v>
       </c>
       <c r="V44">
-        <v>1.34</v>
+        <v>1.36</v>
       </c>
       <c r="W44">
-        <v>1.91</v>
+        <v>1.93</v>
       </c>
       <c r="X44">
         <v>28</v>
       </c>
       <c r="Y44">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="Z44">
         <v>34</v>
@@ -11662,7 +11662,7 @@
         <v>44</v>
       </c>
       <c r="AF44">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AG44">
         <v>12</v>
@@ -11692,16 +11692,16 @@
         <v>27</v>
       </c>
       <c r="AP44">
-        <v>5.6</v>
+        <v>5.3</v>
       </c>
       <c r="AQ44">
         <v>17.5</v>
       </c>
       <c r="AR44">
-        <v>5.8</v>
+        <v>5.4</v>
       </c>
       <c r="AS44">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="AT44">
         <v>12</v>
@@ -11713,7 +11713,7 @@
         <v>13.5</v>
       </c>
       <c r="AW44">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="AX44">
         <v>13</v>
@@ -11725,7 +11725,7 @@
         <v>13</v>
       </c>
       <c r="BA44">
-        <v>6</v>
+        <v>5.7</v>
       </c>
       <c r="BB44">
         <v>20</v>
@@ -11734,10 +11734,10 @@
         <v>15.5</v>
       </c>
       <c r="BD44">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="BE44">
-        <v>6.4</v>
+        <v>5.9</v>
       </c>
       <c r="BF44">
         <v>6.6</v>
@@ -11829,19 +11829,19 @@
         <v>1.57</v>
       </c>
       <c r="G45">
-        <v>1.64</v>
+        <v>1.65</v>
       </c>
       <c r="H45">
-        <v>5.6</v>
+        <v>5</v>
       </c>
       <c r="I45">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="J45">
         <v>4.7</v>
       </c>
       <c r="K45">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L45">
         <v>1.01</v>
@@ -11850,76 +11850,76 @@
         <v>1.01</v>
       </c>
       <c r="N45">
-        <v>1.08</v>
+        <v>4.8</v>
       </c>
       <c r="O45">
         <v>1.17</v>
       </c>
       <c r="P45">
-        <v>2.44</v>
+        <v>2.38</v>
       </c>
       <c r="Q45">
-        <v>1.57</v>
+        <v>1.56</v>
       </c>
       <c r="R45">
-        <v>1.62</v>
+        <v>1.58</v>
       </c>
       <c r="S45">
-        <v>2.34</v>
+        <v>2.36</v>
       </c>
       <c r="T45">
-        <v>1.63</v>
+        <v>1.59</v>
       </c>
       <c r="U45">
         <v>2.16</v>
       </c>
       <c r="V45">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W45">
         <v>2.54</v>
       </c>
       <c r="X45">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y45">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="Z45">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AA45">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AB45">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AC45">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AD45">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AE45">
         <v>85</v>
       </c>
       <c r="AF45">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AG45">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AH45">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI45">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AJ45">
-        <v>19.5</v>
+        <v>16.5</v>
       </c>
       <c r="AK45">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AL45">
         <v>34</v>
@@ -11928,64 +11928,64 @@
         <v>95</v>
       </c>
       <c r="AN45">
-        <v>970</v>
+        <v>7.4</v>
       </c>
       <c r="AO45">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AP45">
-        <v>1.43</v>
+        <v>21</v>
       </c>
       <c r="AQ45">
-        <v>1.37</v>
+        <v>4.8</v>
       </c>
       <c r="AR45">
-        <v>1.43</v>
+        <v>5.2</v>
       </c>
       <c r="AS45">
-        <v>1.43</v>
+        <v>5.6</v>
       </c>
       <c r="AT45">
-        <v>1.43</v>
+        <v>10</v>
       </c>
       <c r="AU45">
-        <v>1.43</v>
+        <v>9.4</v>
       </c>
       <c r="AV45">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AW45">
-        <v>1.41</v>
+        <v>5.4</v>
       </c>
       <c r="AX45">
-        <v>1.43</v>
+        <v>10</v>
       </c>
       <c r="AY45">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ45">
-        <v>1.43</v>
+        <v>15.5</v>
       </c>
       <c r="BA45">
-        <v>1.43</v>
+        <v>5.4</v>
       </c>
       <c r="BB45">
-        <v>1.33</v>
+        <v>13.5</v>
       </c>
       <c r="BC45">
-        <v>1.33</v>
+        <v>13</v>
       </c>
       <c r="BD45">
-        <v>1.37</v>
+        <v>4.9</v>
       </c>
       <c r="BE45">
-        <v>1.41</v>
+        <v>5.4</v>
       </c>
       <c r="BF45">
-        <v>5.4</v>
+        <v>5.7</v>
       </c>
       <c r="BG45">
-        <v>1.43</v>
+        <v>5.3</v>
       </c>
       <c r="BH45">
         <v>1000</v>
@@ -12606,7 +12606,7 @@
         <v>1.77</v>
       </c>
       <c r="X48">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="Y48">
         <v>9.6</v>
@@ -12615,7 +12615,7 @@
         <v>28</v>
       </c>
       <c r="AA48">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AB48">
         <v>6</v>
@@ -12648,7 +12648,7 @@
         <v>38</v>
       </c>
       <c r="AL48">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AM48">
         <v>330</v>
@@ -12696,7 +12696,7 @@
         <v>42</v>
       </c>
       <c r="BB48">
-        <v>21</v>
+        <v>29</v>
       </c>
       <c r="BC48">
         <v>34</v>
@@ -12714,64 +12714,64 @@
         <v>42</v>
       </c>
       <c r="BH48">
-        <v>970</v>
+        <v>2.4</v>
       </c>
       <c r="BI48">
-        <v>2.12</v>
+        <v>2.28</v>
       </c>
       <c r="BJ48">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="BK48">
-        <v>1.11</v>
+        <v>6</v>
       </c>
       <c r="BL48">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="BM48">
-        <v>1.11</v>
+        <v>9.6</v>
       </c>
       <c r="BN48">
-        <v>970</v>
+        <v>4.7</v>
       </c>
       <c r="BO48">
-        <v>3.85</v>
+        <v>4.3</v>
       </c>
       <c r="BP48">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BQ48">
-        <v>3.05</v>
+        <v>7</v>
       </c>
       <c r="BR48">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS48">
-        <v>1.11</v>
+        <v>8.6</v>
       </c>
       <c r="BT48">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="BU48">
-        <v>2.32</v>
+        <v>6.6</v>
       </c>
       <c r="BV48">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BW48">
-        <v>1.11</v>
+        <v>8.6</v>
       </c>
       <c r="BX48">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BY48">
-        <v>1.11</v>
+        <v>9</v>
       </c>
       <c r="BZ48">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="CA48">
-        <v>1.11</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB48" t="s">
         <v>270</v>
@@ -13045,10 +13045,10 @@
         <v>4.1</v>
       </c>
       <c r="I50">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J50">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="K50">
         <v>6.2</v>
@@ -13293,7 +13293,7 @@
         <v>4.2</v>
       </c>
       <c r="K51">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="L51">
         <v>1.01</v>
@@ -13311,7 +13311,7 @@
         <v>3.05</v>
       </c>
       <c r="Q51">
-        <v>1.25</v>
+        <v>1.33</v>
       </c>
       <c r="R51">
         <v>1.93</v>
@@ -13520,22 +13520,22 @@
         <v>254</v>
       </c>
       <c r="F52">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="G52">
-        <v>1.72</v>
+        <v>1.75</v>
       </c>
       <c r="H52">
         <v>4.4</v>
       </c>
       <c r="I52">
-        <v>7</v>
+        <v>6.2</v>
       </c>
       <c r="J52">
         <v>4.6</v>
       </c>
       <c r="K52">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="L52">
         <v>1.01</v>
@@ -13568,10 +13568,10 @@
         <v>1.01</v>
       </c>
       <c r="V52">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="W52">
-        <v>2.38</v>
+        <v>2.32</v>
       </c>
       <c r="X52">
         <v>1000</v>
@@ -13774,7 +13774,7 @@
         <v>9.6</v>
       </c>
       <c r="J53">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K53">
         <v>4.4</v>
@@ -13876,10 +13876,10 @@
         <v>13</v>
       </c>
       <c r="AR53">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="AS53">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="AT53">
         <v>4.2</v>
@@ -13888,10 +13888,10 @@
         <v>6.2</v>
       </c>
       <c r="AV53">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="AW53">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="AX53">
         <v>5.3</v>
@@ -13903,7 +13903,7 @@
         <v>19</v>
       </c>
       <c r="BA53">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="BB53">
         <v>9.199999999999999</v>
@@ -13912,16 +13912,16 @@
         <v>13</v>
       </c>
       <c r="BD53">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BE53">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="BF53">
         <v>8</v>
       </c>
       <c r="BG53">
-        <v>85</v>
+        <v>1.01</v>
       </c>
       <c r="BH53">
         <v>1000</v>
@@ -13945,7 +13945,7 @@
         <v>1000</v>
       </c>
       <c r="BO53">
-        <v>2.7</v>
+        <v>1.01</v>
       </c>
       <c r="BP53">
         <v>1000</v>
@@ -14246,7 +14246,7 @@
         <v>257</v>
       </c>
       <c r="F55">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="G55">
         <v>1.49</v>
@@ -14255,7 +14255,7 @@
         <v>8</v>
       </c>
       <c r="I55">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="J55">
         <v>4.9</v>
@@ -14267,7 +14267,7 @@
         <v>1.01</v>
       </c>
       <c r="M55">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N55">
         <v>4</v>
@@ -14294,7 +14294,7 @@
         <v>1.84</v>
       </c>
       <c r="V55">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="W55">
         <v>3</v>
@@ -14318,13 +14318,13 @@
         <v>11</v>
       </c>
       <c r="AD55">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AE55">
         <v>160</v>
       </c>
       <c r="AF55">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AG55">
         <v>9.800000000000001</v>
@@ -14333,7 +14333,7 @@
         <v>32</v>
       </c>
       <c r="AI55">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AJ55">
         <v>13</v>
@@ -14384,7 +14384,7 @@
         <v>9</v>
       </c>
       <c r="AZ55">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="BA55">
         <v>9</v>
@@ -14491,7 +14491,7 @@
         <v>3.55</v>
       </c>
       <c r="G56">
-        <v>3.8</v>
+        <v>3.7</v>
       </c>
       <c r="H56">
         <v>2.1</v>
@@ -14521,7 +14521,7 @@
         <v>2.16</v>
       </c>
       <c r="Q56">
-        <v>1.74</v>
+        <v>1.61</v>
       </c>
       <c r="R56">
         <v>1.47</v>
@@ -14557,7 +14557,7 @@
         <v>17</v>
       </c>
       <c r="AC56">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AD56">
         <v>11</v>
@@ -14566,7 +14566,7 @@
         <v>21</v>
       </c>
       <c r="AF56">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG56">
         <v>15.5</v>
@@ -14617,7 +14617,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW56">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AX56">
         <v>24</v>
@@ -14730,76 +14730,76 @@
         <v>259</v>
       </c>
       <c r="F57">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="G57">
-        <v>2.02</v>
+        <v>2.06</v>
       </c>
       <c r="H57">
-        <v>4.8</v>
+        <v>4.6</v>
       </c>
       <c r="I57">
         <v>5.7</v>
       </c>
       <c r="J57">
-        <v>3.35</v>
+        <v>2.96</v>
       </c>
       <c r="K57">
         <v>3.65</v>
       </c>
       <c r="L57">
-        <v>1.37</v>
+        <v>1.01</v>
       </c>
       <c r="M57">
         <v>1.09</v>
       </c>
       <c r="N57">
-        <v>2.92</v>
+        <v>2.76</v>
       </c>
       <c r="O57">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P57">
-        <v>1.66</v>
+        <v>1.64</v>
       </c>
       <c r="Q57">
-        <v>2.22</v>
+        <v>2.08</v>
       </c>
       <c r="R57">
         <v>1.24</v>
       </c>
       <c r="S57">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="T57">
-        <v>2</v>
+        <v>1.85</v>
       </c>
       <c r="U57">
-        <v>1.81</v>
+        <v>1.79</v>
       </c>
       <c r="V57">
         <v>1.21</v>
       </c>
       <c r="W57">
-        <v>1.98</v>
+        <v>1.94</v>
       </c>
       <c r="X57">
         <v>13.5</v>
       </c>
       <c r="Y57">
-        <v>15</v>
+        <v>17.5</v>
       </c>
       <c r="Z57">
         <v>46</v>
       </c>
       <c r="AA57">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AB57">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC57">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AD57">
         <v>25</v>
@@ -14811,16 +14811,16 @@
         <v>13</v>
       </c>
       <c r="AG57">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AH57">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AI57">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AJ57">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK57">
         <v>29</v>
@@ -14829,61 +14829,61 @@
         <v>60</v>
       </c>
       <c r="AM57">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="AN57">
         <v>23</v>
       </c>
       <c r="AO57">
-        <v>140</v>
+        <v>150</v>
       </c>
       <c r="AP57">
-        <v>8</v>
+        <v>1.01</v>
       </c>
       <c r="AQ57">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AR57">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AS57">
         <v>1.01</v>
       </c>
       <c r="AT57">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="AU57">
-        <v>6.8</v>
+        <v>1.01</v>
       </c>
       <c r="AV57">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="AW57">
         <v>1.01</v>
       </c>
       <c r="AX57">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY57">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AZ57">
-        <v>19</v>
+        <v>1.01</v>
       </c>
       <c r="BA57">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BB57">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BC57">
-        <v>19.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD57">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BE57">
-        <v>110</v>
+        <v>1.01</v>
       </c>
       <c r="BF57">
         <v>1.01</v>
@@ -15214,7 +15214,7 @@
         <v>261</v>
       </c>
       <c r="F59">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G59">
         <v>1.98</v>
@@ -15229,7 +15229,7 @@
         <v>3.75</v>
       </c>
       <c r="K59">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L59">
         <v>1.42</v>
@@ -15247,7 +15247,7 @@
         <v>1.95</v>
       </c>
       <c r="Q59">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="R59">
         <v>1.36</v>
@@ -15256,13 +15256,13 @@
         <v>3.6</v>
       </c>
       <c r="T59">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="U59">
         <v>2.1</v>
       </c>
       <c r="V59">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W59">
         <v>2.02</v>
@@ -15334,7 +15334,7 @@
         <v>36</v>
       </c>
       <c r="AT59">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AU59">
         <v>7.6</v>
@@ -15474,7 +15474,7 @@
         <v>6.4</v>
       </c>
       <c r="L60">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M60">
         <v>1.05</v>
@@ -15704,16 +15704,16 @@
         <v>7.4</v>
       </c>
       <c r="H61">
+        <v>1.55</v>
+      </c>
+      <c r="I61">
         <v>1.56</v>
       </c>
-      <c r="I61">
-        <v>1.57</v>
-      </c>
       <c r="J61">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="K61">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="L61">
         <v>1.38</v>
@@ -15725,7 +15725,7 @@
         <v>4.2</v>
       </c>
       <c r="O61">
-        <v>1.29</v>
+        <v>1.28</v>
       </c>
       <c r="P61">
         <v>2.1</v>
@@ -15734,7 +15734,7 @@
         <v>1.87</v>
       </c>
       <c r="R61">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="S61">
         <v>3.25</v>
@@ -15743,10 +15743,10 @@
         <v>1.98</v>
       </c>
       <c r="U61">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="V61">
-        <v>2.74</v>
+        <v>2.78</v>
       </c>
       <c r="W61">
         <v>1.15</v>
@@ -15803,7 +15803,7 @@
         <v>120</v>
       </c>
       <c r="AO61">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP61">
         <v>16</v>
@@ -15845,16 +15845,16 @@
         <v>50</v>
       </c>
       <c r="BC61">
-        <v>40</v>
+        <v>85</v>
       </c>
       <c r="BD61">
         <v>85</v>
       </c>
       <c r="BE61">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="BF61">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="BG61">
         <v>7.8</v>
@@ -15949,7 +15949,7 @@
         <v>3.15</v>
       </c>
       <c r="I62">
-        <v>3.65</v>
+        <v>3.4</v>
       </c>
       <c r="J62">
         <v>4.5</v>
@@ -15964,13 +15964,13 @@
         <v>1.01</v>
       </c>
       <c r="N62">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="O62">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="P62">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="Q62">
         <v>1.23</v>
@@ -15988,118 +15988,118 @@
         <v>3.05</v>
       </c>
       <c r="V62">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="W62">
         <v>1.87</v>
       </c>
       <c r="X62">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="Y62">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="Z62">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA62">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB62">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AC62">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AD62">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AE62">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AF62">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AG62">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AH62">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AI62">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AJ62">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AK62">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AL62">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AM62">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AN62">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="AO62">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AP62">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AQ62">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AR62">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="AS62">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="AT62">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="AU62">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AV62">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW62">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AX62">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="AY62">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ62">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BA62">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BB62">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BC62">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BD62">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="BE62">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BF62">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BG62">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BH62">
         <v>1000</v>
@@ -16182,7 +16182,7 @@
         <v>265</v>
       </c>
       <c r="F63">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="G63">
         <v>1.83</v>
@@ -16191,10 +16191,10 @@
         <v>5.1</v>
       </c>
       <c r="I63">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="J63">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="K63">
         <v>4.1</v>
@@ -16215,7 +16215,7 @@
         <v>1.93</v>
       </c>
       <c r="Q63">
-        <v>1.92</v>
+        <v>1.88</v>
       </c>
       <c r="R63">
         <v>1.36</v>
@@ -16230,7 +16230,7 @@
         <v>2.02</v>
       </c>
       <c r="V63">
-        <v>1.22</v>
+        <v>1.23</v>
       </c>
       <c r="W63">
         <v>2.2</v>
@@ -16430,7 +16430,7 @@
         <v>1.2</v>
       </c>
       <c r="H64">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="I64">
         <v>21</v>
@@ -16448,28 +16448,28 @@
         <v>1.02</v>
       </c>
       <c r="N64">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="O64">
         <v>1.13</v>
       </c>
       <c r="P64">
-        <v>2.78</v>
+        <v>2.96</v>
       </c>
       <c r="Q64">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="R64">
-        <v>1.77</v>
+        <v>1.81</v>
       </c>
       <c r="S64">
-        <v>1.74</v>
+        <v>2</v>
       </c>
       <c r="T64">
-        <v>1.98</v>
+        <v>2.16</v>
       </c>
       <c r="U64">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="V64">
         <v>1.05</v>
@@ -16478,112 +16478,112 @@
         <v>6</v>
       </c>
       <c r="X64">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="Y64">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="Z64">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AA64">
         <v>1000</v>
       </c>
       <c r="AB64">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AC64">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AD64">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="AE64">
-        <v>1000</v>
+        <v>300</v>
       </c>
       <c r="AF64">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="AG64">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH64">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AI64">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AJ64">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="AK64">
-        <v>18.5</v>
+        <v>15</v>
       </c>
       <c r="AL64">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM64">
-        <v>1000</v>
+        <v>210</v>
       </c>
       <c r="AN64">
-        <v>8.199999999999999</v>
+        <v>3.35</v>
       </c>
       <c r="AO64">
-        <v>1000</v>
+        <v>460</v>
       </c>
       <c r="AP64">
-        <v>1.33</v>
+        <v>6.4</v>
       </c>
       <c r="AQ64">
-        <v>2.08</v>
+        <v>7.2</v>
       </c>
       <c r="AR64">
-        <v>1.33</v>
+        <v>7.4</v>
       </c>
       <c r="AS64">
-        <v>1.33</v>
+        <v>7.8</v>
       </c>
       <c r="AT64">
-        <v>1.33</v>
+        <v>10</v>
       </c>
       <c r="AU64">
-        <v>1.33</v>
+        <v>15.5</v>
       </c>
       <c r="AV64">
-        <v>1.31</v>
+        <v>7</v>
       </c>
       <c r="AW64">
-        <v>2.12</v>
+        <v>7.6</v>
       </c>
       <c r="AX64">
-        <v>1.79</v>
+        <v>7.6</v>
       </c>
       <c r="AY64">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ64">
-        <v>1.33</v>
+        <v>6.6</v>
       </c>
       <c r="BA64">
-        <v>1.33</v>
+        <v>7.4</v>
       </c>
       <c r="BB64">
-        <v>1.79</v>
+        <v>8</v>
       </c>
       <c r="BC64">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD64">
-        <v>1.33</v>
+        <v>6.8</v>
       </c>
       <c r="BE64">
-        <v>2.12</v>
+        <v>7.4</v>
       </c>
       <c r="BF64">
-        <v>2.5</v>
+        <v>2.86</v>
       </c>
       <c r="BG64">
-        <v>1.33</v>
+        <v>7.6</v>
       </c>
       <c r="BH64">
         <v>1000</v>
@@ -16592,10 +16592,10 @@
         <v>1.01</v>
       </c>
       <c r="BJ64">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="BK64">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BL64">
         <v>1000</v>
@@ -16604,7 +16604,7 @@
         <v>21</v>
       </c>
       <c r="BN64">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BO64">
         <v>2.68</v>
@@ -16613,10 +16613,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BQ64">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="BR64">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BS64">
         <v>13</v>
@@ -16631,7 +16631,7 @@
         <v>1000</v>
       </c>
       <c r="BW64">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BX64">
         <v>1000</v>
@@ -16669,7 +16669,7 @@
         <v>4.2</v>
       </c>
       <c r="G65">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="H65">
         <v>1.82</v>
@@ -16699,13 +16699,13 @@
         <v>2.16</v>
       </c>
       <c r="Q65">
-        <v>1.74</v>
+        <v>1.72</v>
       </c>
       <c r="R65">
         <v>1.47</v>
       </c>
       <c r="S65">
-        <v>2.74</v>
+        <v>2.88</v>
       </c>
       <c r="T65">
         <v>1.71</v>
@@ -16926,7 +16926,7 @@
         <v>10</v>
       </c>
       <c r="L66">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="M66">
         <v>1.02</v>
@@ -16935,7 +16935,7 @@
         <v>9</v>
       </c>
       <c r="O66">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P66">
         <v>3.65</v>
@@ -17025,7 +17025,7 @@
         <v>48</v>
       </c>
       <c r="AS66">
-        <v>18.5</v>
+        <v>25</v>
       </c>
       <c r="AT66">
         <v>12.5</v>
@@ -17034,13 +17034,13 @@
         <v>22</v>
       </c>
       <c r="AV66">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AW66">
-        <v>23</v>
+        <v>50</v>
       </c>
       <c r="AX66">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AY66">
         <v>12</v>
@@ -17052,7 +17052,7 @@
         <v>46</v>
       </c>
       <c r="BB66">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BC66">
         <v>12</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-31.xlsx
@@ -889,7 +889,7 @@
     <t>Academia Anzoategui FC</t>
   </si>
   <si>
-    <t>2026-08-30 01:22:04</t>
+    <t>2026-08-30 03:42:37</t>
   </si>
 </sst>
 </file>
@@ -1489,7 +1489,7 @@
         <v>1.63</v>
       </c>
       <c r="H2">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="I2">
         <v>6.6</v>
@@ -1543,7 +1543,7 @@
         <v>24</v>
       </c>
       <c r="Z2">
-        <v>65</v>
+        <v>70</v>
       </c>
       <c r="AA2">
         <v>1000</v>
@@ -1576,7 +1576,7 @@
         <v>16</v>
       </c>
       <c r="AK2">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AL2">
         <v>40</v>
@@ -1639,7 +1639,7 @@
         <v>40</v>
       </c>
       <c r="BF2">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BG2">
         <v>1.01</v>
@@ -1734,13 +1734,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="I3">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="J3">
         <v>6.2</v>
       </c>
       <c r="K3">
-        <v>7</v>
+        <v>6.6</v>
       </c>
       <c r="L3">
         <v>1.24</v>
@@ -1758,7 +1758,7 @@
         <v>3.1</v>
       </c>
       <c r="Q3">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="R3">
         <v>1.84</v>
@@ -1970,13 +1970,13 @@
         <v>2.2</v>
       </c>
       <c r="G4">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="H4">
         <v>3.25</v>
       </c>
       <c r="I4">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="J4">
         <v>3.45</v>
@@ -2015,10 +2015,10 @@
         <v>1.01</v>
       </c>
       <c r="V4">
-        <v>1.38</v>
+        <v>1.39</v>
       </c>
       <c r="W4">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -2209,7 +2209,7 @@
         <v>221</v>
       </c>
       <c r="F5">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="G5">
         <v>2.38</v>
@@ -2221,7 +2221,7 @@
         <v>3.95</v>
       </c>
       <c r="J5">
-        <v>3.1</v>
+        <v>3.15</v>
       </c>
       <c r="K5">
         <v>3.25</v>
@@ -2233,19 +2233,19 @@
         <v>1.12</v>
       </c>
       <c r="N5">
-        <v>2.76</v>
+        <v>2.78</v>
       </c>
       <c r="O5">
         <v>1.53</v>
       </c>
       <c r="P5">
-        <v>1.56</v>
+        <v>1.58</v>
       </c>
       <c r="Q5">
-        <v>2.68</v>
+        <v>2.64</v>
       </c>
       <c r="R5">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="S5">
         <v>5.5</v>
@@ -2263,7 +2263,7 @@
         <v>1.72</v>
       </c>
       <c r="X5">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="Y5">
         <v>11.5</v>
@@ -2308,13 +2308,13 @@
         <v>75</v>
       </c>
       <c r="AM5">
-        <v>700</v>
+        <v>610</v>
       </c>
       <c r="AN5">
         <v>36</v>
       </c>
       <c r="AO5">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP5">
         <v>6.8</v>
@@ -2326,7 +2326,7 @@
         <v>19</v>
       </c>
       <c r="AS5">
-        <v>55</v>
+        <v>6.2</v>
       </c>
       <c r="AT5">
         <v>5.6</v>
@@ -2338,7 +2338,7 @@
         <v>12.5</v>
       </c>
       <c r="AW5">
-        <v>44</v>
+        <v>5.9</v>
       </c>
       <c r="AX5">
         <v>11.5</v>
@@ -2350,7 +2350,7 @@
         <v>20</v>
       </c>
       <c r="BA5">
-        <v>60</v>
+        <v>6</v>
       </c>
       <c r="BB5">
         <v>23</v>
@@ -2359,16 +2359,16 @@
         <v>23</v>
       </c>
       <c r="BD5">
-        <v>40</v>
+        <v>6.2</v>
       </c>
       <c r="BE5">
-        <v>6</v>
+        <v>6.4</v>
       </c>
       <c r="BF5">
         <v>21</v>
       </c>
       <c r="BG5">
-        <v>55</v>
+        <v>6</v>
       </c>
       <c r="BH5">
         <v>3.15</v>
@@ -2377,22 +2377,22 @@
         <v>2.24</v>
       </c>
       <c r="BJ5">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="BK5">
         <v>8.199999999999999</v>
       </c>
       <c r="BL5">
-        <v>1000</v>
+        <v>910</v>
       </c>
       <c r="BM5">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BN5">
-        <v>5.8</v>
+        <v>4.9</v>
       </c>
       <c r="BO5">
-        <v>3.8</v>
+        <v>4.4</v>
       </c>
       <c r="BP5">
         <v>24</v>
@@ -2407,10 +2407,10 @@
         <v>30</v>
       </c>
       <c r="BT5">
-        <v>8.199999999999999</v>
+        <v>7</v>
       </c>
       <c r="BU5">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BV5">
         <v>46</v>
@@ -2451,7 +2451,7 @@
         <v>222</v>
       </c>
       <c r="F6">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G6">
         <v>2.16</v>
@@ -2493,10 +2493,10 @@
         <v>5.1</v>
       </c>
       <c r="T6">
-        <v>1.89</v>
+        <v>2.08</v>
       </c>
       <c r="U6">
-        <v>1.65</v>
+        <v>1.68</v>
       </c>
       <c r="V6">
         <v>1.27</v>
@@ -2514,10 +2514,10 @@
         <v>40</v>
       </c>
       <c r="AA6">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AB6">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="AC6">
         <v>7.6</v>
@@ -2565,52 +2565,52 @@
         <v>10.5</v>
       </c>
       <c r="AR6">
+        <v>27</v>
+      </c>
+      <c r="AS6">
         <v>5.1</v>
-      </c>
-      <c r="AS6">
-        <v>5.7</v>
       </c>
       <c r="AT6">
         <v>6.2</v>
       </c>
       <c r="AU6">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AV6">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="AW6">
-        <v>5.5</v>
+        <v>5</v>
       </c>
       <c r="AX6">
-        <v>10</v>
+        <v>8.6</v>
       </c>
       <c r="AY6">
-        <v>8.199999999999999</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ6">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BA6">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BB6">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BC6">
         <v>20</v>
       </c>
       <c r="BD6">
-        <v>5.4</v>
+        <v>4.9</v>
       </c>
       <c r="BE6">
-        <v>5.7</v>
+        <v>5.2</v>
       </c>
       <c r="BF6">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BG6">
-        <v>5.6</v>
+        <v>5.1</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2696,13 +2696,13 @@
         <v>1.59</v>
       </c>
       <c r="G7">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="H7">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="I7">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="J7">
         <v>4.7</v>
@@ -2714,7 +2714,7 @@
         <v>1.29</v>
       </c>
       <c r="M7">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N7">
         <v>5.7</v>
@@ -2741,10 +2741,10 @@
         <v>2.32</v>
       </c>
       <c r="V7">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W7">
-        <v>2.66</v>
+        <v>2.62</v>
       </c>
       <c r="X7">
         <v>25</v>
@@ -2756,7 +2756,7 @@
         <v>55</v>
       </c>
       <c r="AA7">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AB7">
         <v>12</v>
@@ -2846,7 +2846,7 @@
         <v>24</v>
       </c>
       <c r="BE7">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BF7">
         <v>6</v>
@@ -2935,13 +2935,13 @@
         <v>224</v>
       </c>
       <c r="F8">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="G8">
         <v>110</v>
       </c>
       <c r="H8">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="I8">
         <v>2.5</v>
@@ -2974,7 +2974,7 @@
         <v>1.18</v>
       </c>
       <c r="S8">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="T8">
         <v>1.01</v>
@@ -2983,10 +2983,10 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="W8">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -3225,10 +3225,10 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W9">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3443,13 +3443,13 @@
         <v>1.01</v>
       </c>
       <c r="N10">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="O10">
         <v>1.24</v>
       </c>
       <c r="P10">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="Q10">
         <v>1.25</v>
@@ -3470,7 +3470,7 @@
         <v>1.02</v>
       </c>
       <c r="W10">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3661,7 +3661,7 @@
         <v>227</v>
       </c>
       <c r="F11">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="G11">
         <v>1000</v>
@@ -3709,10 +3709,10 @@
         <v>1.01</v>
       </c>
       <c r="V11">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W11">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3927,16 +3927,16 @@
         <v>1.01</v>
       </c>
       <c r="N12">
-        <v>2.68</v>
+        <v>2.52</v>
       </c>
       <c r="O12">
         <v>1.15</v>
       </c>
       <c r="P12">
-        <v>2.68</v>
+        <v>2.52</v>
       </c>
       <c r="Q12">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="R12">
         <v>1.63</v>
@@ -4148,43 +4148,43 @@
         <v>2.62</v>
       </c>
       <c r="G13">
-        <v>3.05</v>
+        <v>3.15</v>
       </c>
       <c r="H13">
         <v>2.58</v>
       </c>
       <c r="I13">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="J13">
-        <v>1.96</v>
+        <v>2.76</v>
       </c>
       <c r="K13">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="L13">
         <v>1.29</v>
       </c>
       <c r="M13">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N13">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="O13">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P13">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="Q13">
         <v>1.83</v>
       </c>
       <c r="R13">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="S13">
-        <v>3</v>
+        <v>2.88</v>
       </c>
       <c r="T13">
         <v>1.01</v>
@@ -4193,10 +4193,10 @@
         <v>1.01</v>
       </c>
       <c r="V13">
-        <v>1.51</v>
+        <v>1.49</v>
       </c>
       <c r="W13">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -4396,7 +4396,7 @@
         <v>2.6</v>
       </c>
       <c r="I14">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="J14">
         <v>3.65</v>
@@ -4411,16 +4411,16 @@
         <v>1.01</v>
       </c>
       <c r="N14">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="O14">
         <v>1.18</v>
       </c>
       <c r="P14">
-        <v>2.34</v>
+        <v>2.3</v>
       </c>
       <c r="Q14">
-        <v>1.55</v>
+        <v>1.53</v>
       </c>
       <c r="R14">
         <v>1.58</v>
@@ -4438,7 +4438,7 @@
         <v>1.48</v>
       </c>
       <c r="W14">
-        <v>1.55</v>
+        <v>1.54</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4632,13 +4632,13 @@
         <v>2.06</v>
       </c>
       <c r="G15">
-        <v>2.66</v>
+        <v>2.54</v>
       </c>
       <c r="H15">
         <v>2.66</v>
       </c>
       <c r="I15">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="J15">
         <v>3.2</v>
@@ -4662,13 +4662,13 @@
         <v>1.96</v>
       </c>
       <c r="Q15">
-        <v>1.66</v>
+        <v>1.58</v>
       </c>
       <c r="R15">
         <v>1.37</v>
       </c>
       <c r="S15">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="T15">
         <v>1.01</v>
@@ -4677,10 +4677,10 @@
         <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.36</v>
+        <v>1.38</v>
       </c>
       <c r="W15">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="X15">
         <v>1000</v>
@@ -4871,22 +4871,22 @@
         <v>232</v>
       </c>
       <c r="F16">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="G16">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="H16">
         <v>3.75</v>
       </c>
       <c r="I16">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J16">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="K16">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4895,25 +4895,25 @@
         <v>1.05</v>
       </c>
       <c r="N16">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O16">
-        <v>1.25</v>
+        <v>1.27</v>
       </c>
       <c r="P16">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="Q16">
-        <v>1.74</v>
+        <v>1.78</v>
       </c>
       <c r="R16">
-        <v>1.46</v>
+        <v>1.43</v>
       </c>
       <c r="S16">
-        <v>2.86</v>
+        <v>3</v>
       </c>
       <c r="T16">
-        <v>1.68</v>
+        <v>1.7</v>
       </c>
       <c r="U16">
         <v>2.04</v>
@@ -4922,13 +4922,13 @@
         <v>1.32</v>
       </c>
       <c r="W16">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="X16">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="Y16">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="Z16">
         <v>36</v>
@@ -4937,10 +4937,10 @@
         <v>90</v>
       </c>
       <c r="AB16">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AC16">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AD16">
         <v>16.5</v>
@@ -4964,7 +4964,7 @@
         <v>24</v>
       </c>
       <c r="AK16">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AL16">
         <v>32</v>
@@ -4973,13 +4973,13 @@
         <v>95</v>
       </c>
       <c r="AN16">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AO16">
         <v>46</v>
       </c>
       <c r="AP16">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ16">
         <v>14.5</v>
@@ -4991,7 +4991,7 @@
         <v>1.01</v>
       </c>
       <c r="AT16">
-        <v>9.6</v>
+        <v>7.8</v>
       </c>
       <c r="AU16">
         <v>7.8</v>
@@ -5033,37 +5033,37 @@
         <v>29</v>
       </c>
       <c r="BH16">
-        <v>4.5</v>
+        <v>3.75</v>
       </c>
       <c r="BI16">
-        <v>3</v>
+        <v>3.35</v>
       </c>
       <c r="BJ16">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK16">
         <v>1.01</v>
       </c>
       <c r="BL16">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="BM16">
         <v>1.01</v>
       </c>
       <c r="BN16">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BO16">
         <v>3.8</v>
       </c>
       <c r="BP16">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BQ16">
         <v>1.01</v>
       </c>
       <c r="BR16">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="BS16">
         <v>1.01</v>
@@ -5075,19 +5075,19 @@
         <v>5.5</v>
       </c>
       <c r="BV16">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="BW16">
         <v>1.01</v>
       </c>
       <c r="BX16">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="BY16">
         <v>1.01</v>
       </c>
       <c r="BZ16">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="CA16">
         <v>1.01</v>
@@ -5137,13 +5137,13 @@
         <v>1.01</v>
       </c>
       <c r="N17">
+        <v>1.18</v>
+      </c>
+      <c r="O17">
+        <v>1.01</v>
+      </c>
+      <c r="P17">
         <v>1.19</v>
-      </c>
-      <c r="O17">
-        <v>1.01</v>
-      </c>
-      <c r="P17">
-        <v>1.18</v>
       </c>
       <c r="Q17">
         <v>1.26</v>
@@ -5152,7 +5152,7 @@
         <v>1.18</v>
       </c>
       <c r="S17">
-        <v>1.26</v>
+        <v>2.5</v>
       </c>
       <c r="T17">
         <v>1.01</v>
@@ -5161,10 +5161,10 @@
         <v>1.01</v>
       </c>
       <c r="V17">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W17">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -5358,16 +5358,16 @@
         <v>1.62</v>
       </c>
       <c r="G18">
-        <v>1.95</v>
+        <v>2.04</v>
       </c>
       <c r="H18">
         <v>3.85</v>
       </c>
       <c r="I18">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="J18">
-        <v>3.95</v>
+        <v>1.09</v>
       </c>
       <c r="K18">
         <v>8.199999999999999</v>
@@ -5406,7 +5406,7 @@
         <v>1.19</v>
       </c>
       <c r="W18">
-        <v>2.04</v>
+        <v>1.96</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -5606,10 +5606,10 @@
         <v>4.2</v>
       </c>
       <c r="I19">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="J19">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="K19">
         <v>8.800000000000001</v>
@@ -5645,7 +5645,7 @@
         <v>1.01</v>
       </c>
       <c r="V19">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="W19">
         <v>2.32</v>
@@ -5842,13 +5842,13 @@
         <v>2.3</v>
       </c>
       <c r="G20">
-        <v>2.58</v>
+        <v>2.62</v>
       </c>
       <c r="H20">
         <v>2.8</v>
       </c>
       <c r="I20">
-        <v>3.25</v>
+        <v>3.1</v>
       </c>
       <c r="J20">
         <v>3.7</v>
@@ -5863,7 +5863,7 @@
         <v>1.01</v>
       </c>
       <c r="N20">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="O20">
         <v>1.23</v>
@@ -5887,10 +5887,10 @@
         <v>1.01</v>
       </c>
       <c r="V20">
-        <v>1.44</v>
+        <v>1.47</v>
       </c>
       <c r="W20">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="X20">
         <v>1000</v>
@@ -6123,10 +6123,10 @@
         <v>3</v>
       </c>
       <c r="T21">
-        <v>1.57</v>
+        <v>1.68</v>
       </c>
       <c r="U21">
-        <v>2.02</v>
+        <v>2.2</v>
       </c>
       <c r="V21">
         <v>1.72</v>
@@ -6183,7 +6183,7 @@
         <v>100</v>
       </c>
       <c r="AN21">
-        <v>44</v>
+        <v>34</v>
       </c>
       <c r="AO21">
         <v>19.5</v>
@@ -6323,22 +6323,22 @@
         <v>238</v>
       </c>
       <c r="F22">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="G22">
-        <v>5.5</v>
+        <v>5.2</v>
       </c>
       <c r="H22">
-        <v>1.62</v>
+        <v>1.68</v>
       </c>
       <c r="I22">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="J22">
         <v>4.3</v>
       </c>
       <c r="K22">
-        <v>7.2</v>
+        <v>5.7</v>
       </c>
       <c r="L22">
         <v>1.01</v>
@@ -6347,31 +6347,31 @@
         <v>1.01</v>
       </c>
       <c r="N22">
-        <v>5.3</v>
+        <v>5.7</v>
       </c>
       <c r="O22">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P22">
-        <v>2.5</v>
+        <v>2.62</v>
       </c>
       <c r="Q22">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="R22">
-        <v>1.62</v>
+        <v>1.65</v>
       </c>
       <c r="S22">
         <v>2.2</v>
       </c>
       <c r="T22">
-        <v>1.01</v>
+        <v>1.56</v>
       </c>
       <c r="U22">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="V22">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="W22">
         <v>1.25</v>
@@ -6404,7 +6404,7 @@
         <v>50</v>
       </c>
       <c r="AG22">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AH22">
         <v>17.5</v>
@@ -6419,13 +6419,13 @@
         <v>60</v>
       </c>
       <c r="AL22">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AM22">
         <v>75</v>
       </c>
       <c r="AN22">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AO22">
         <v>7.2</v>
@@ -6446,10 +6446,10 @@
         <v>1.01</v>
       </c>
       <c r="AU22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AV22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="AW22">
         <v>1.01</v>
@@ -6488,7 +6488,7 @@
         <v>5.5</v>
       </c>
       <c r="BI22">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BJ22">
         <v>11</v>
@@ -6497,10 +6497,10 @@
         <v>1.01</v>
       </c>
       <c r="BL22">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="BM22">
-        <v>1.01</v>
+        <v>50</v>
       </c>
       <c r="BN22">
         <v>10.5</v>
@@ -6521,10 +6521,10 @@
         <v>1.01</v>
       </c>
       <c r="BT22">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="BU22">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BV22">
         <v>13</v>
@@ -6539,10 +6539,10 @@
         <v>1.01</v>
       </c>
       <c r="BZ22">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="CA22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="CB22" t="s">
         <v>291</v>
@@ -6571,13 +6571,13 @@
         <v>110</v>
       </c>
       <c r="H23">
-        <v>1.29</v>
+        <v>1.31</v>
       </c>
       <c r="I23">
         <v>110</v>
       </c>
       <c r="J23">
-        <v>1.1</v>
+        <v>1.13</v>
       </c>
       <c r="K23">
         <v>5.9</v>
@@ -6589,7 +6589,7 @@
         <v>1.01</v>
       </c>
       <c r="N23">
-        <v>1.2</v>
+        <v>5.3</v>
       </c>
       <c r="O23">
         <v>1.13</v>
@@ -6613,10 +6613,10 @@
         <v>1.01</v>
       </c>
       <c r="V23">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W23">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X23">
         <v>1000</v>
@@ -6855,10 +6855,10 @@
         <v>1.01</v>
       </c>
       <c r="V24">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W24">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -7097,10 +7097,10 @@
         <v>1.01</v>
       </c>
       <c r="V25">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W25">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X25">
         <v>1000</v>
@@ -7297,10 +7297,10 @@
         <v>2.48</v>
       </c>
       <c r="H26">
-        <v>3.05</v>
+        <v>3.2</v>
       </c>
       <c r="I26">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="J26">
         <v>3.05</v>
@@ -7309,148 +7309,148 @@
         <v>3.85</v>
       </c>
       <c r="L26">
+        <v>1.37</v>
+      </c>
+      <c r="M26">
+        <v>1.07</v>
+      </c>
+      <c r="N26">
+        <v>3.2</v>
+      </c>
+      <c r="O26">
         <v>1.33</v>
       </c>
-      <c r="M26">
-        <v>1.01</v>
-      </c>
-      <c r="N26">
-        <v>2.92</v>
-      </c>
-      <c r="O26">
-        <v>1.32</v>
-      </c>
       <c r="P26">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q26">
         <v>1.86</v>
       </c>
       <c r="R26">
-        <v>1.27</v>
+        <v>1.31</v>
       </c>
       <c r="S26">
-        <v>2.7</v>
+        <v>3.3</v>
       </c>
       <c r="T26">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="U26">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V26">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="W26">
         <v>1.67</v>
       </c>
       <c r="X26">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y26">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="Z26">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AA26">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="AB26">
-        <v>13.5</v>
+        <v>11.5</v>
       </c>
       <c r="AC26">
-        <v>10.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD26">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AE26">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF26">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="AG26">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH26">
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="AI26">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="AJ26">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AK26">
         <v>30</v>
       </c>
       <c r="AL26">
+        <v>46</v>
+      </c>
+      <c r="AM26">
+        <v>120</v>
+      </c>
+      <c r="AN26">
+        <v>23</v>
+      </c>
+      <c r="AO26">
         <v>50</v>
       </c>
-      <c r="AM26">
-        <v>1000</v>
-      </c>
-      <c r="AN26">
-        <v>26</v>
-      </c>
-      <c r="AO26">
-        <v>60</v>
-      </c>
       <c r="AP26">
         <v>1.01</v>
       </c>
       <c r="AQ26">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="AR26">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AS26">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AT26">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AU26">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AV26">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AW26">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AX26">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AY26">
-        <v>7.2</v>
+        <v>1.01</v>
       </c>
       <c r="AZ26">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BA26">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BB26">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BC26">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BD26">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BE26">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BF26">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BG26">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BH26">
         <v>1000</v>
@@ -7554,31 +7554,31 @@
         <v>1.01</v>
       </c>
       <c r="M27">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N27">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="O27">
         <v>1.2</v>
       </c>
       <c r="P27">
-        <v>2.44</v>
+        <v>2.56</v>
       </c>
       <c r="Q27">
         <v>1.6</v>
       </c>
       <c r="R27">
-        <v>1.58</v>
+        <v>1.63</v>
       </c>
       <c r="S27">
-        <v>2.5</v>
+        <v>2.48</v>
       </c>
       <c r="T27">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="U27">
-        <v>2.46</v>
+        <v>2.56</v>
       </c>
       <c r="V27">
         <v>2.06</v>
@@ -7587,19 +7587,19 @@
         <v>1.33</v>
       </c>
       <c r="X27">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="Y27">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="Z27">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AA27">
         <v>23</v>
       </c>
       <c r="AB27">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AC27">
         <v>10.5</v>
@@ -7608,25 +7608,25 @@
         <v>11</v>
       </c>
       <c r="AE27">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AF27">
-        <v>38</v>
+        <v>42</v>
       </c>
       <c r="AG27">
         <v>17</v>
       </c>
       <c r="AH27">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AI27">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="AJ27">
         <v>85</v>
       </c>
       <c r="AK27">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AL27">
         <v>44</v>
@@ -7635,19 +7635,19 @@
         <v>70</v>
       </c>
       <c r="AN27">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO27">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AP27">
         <v>18</v>
       </c>
       <c r="AQ27">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AR27">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AS27">
         <v>19.5</v>
@@ -7656,13 +7656,13 @@
         <v>18</v>
       </c>
       <c r="AU27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AV27">
         <v>9.6</v>
       </c>
       <c r="AW27">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AX27">
         <v>26</v>
@@ -7674,25 +7674,25 @@
         <v>14.5</v>
       </c>
       <c r="BA27">
-        <v>19</v>
+        <v>19.5</v>
       </c>
       <c r="BB27">
-        <v>9.4</v>
+        <v>36</v>
       </c>
       <c r="BC27">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="BD27">
+        <v>34</v>
+      </c>
+      <c r="BE27">
         <v>30</v>
       </c>
-      <c r="BE27">
-        <v>9.4</v>
-      </c>
       <c r="BF27">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BG27">
-        <v>7.8</v>
+        <v>8</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7775,91 +7775,91 @@
         <v>244</v>
       </c>
       <c r="F28">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="G28">
         <v>2.5</v>
       </c>
       <c r="H28">
-        <v>2.92</v>
+        <v>2.94</v>
       </c>
       <c r="I28">
-        <v>3.4</v>
+        <v>3.25</v>
       </c>
       <c r="J28">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K28">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L28">
         <v>1.01</v>
       </c>
       <c r="M28">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N28">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="O28">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P28">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q28">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R28">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="S28">
         <v>2.78</v>
       </c>
       <c r="T28">
-        <v>1.01</v>
+        <v>1.58</v>
       </c>
       <c r="U28">
-        <v>1.01</v>
+        <v>2.24</v>
       </c>
       <c r="V28">
-        <v>1.42</v>
+        <v>1.44</v>
       </c>
       <c r="W28">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="X28">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="Y28">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="Z28">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AA28">
         <v>1000</v>
       </c>
       <c r="AB28">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC28">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD28">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AE28">
         <v>1000</v>
       </c>
       <c r="AF28">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AG28">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH28">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI28">
         <v>1000</v>
@@ -7868,7 +7868,7 @@
         <v>1000</v>
       </c>
       <c r="AK28">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AL28">
         <v>1000</v>
@@ -7883,58 +7883,58 @@
         <v>1000</v>
       </c>
       <c r="AP28">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="AQ28">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="AR28">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AS28">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AT28">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AU28">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AV28">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AW28">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AX28">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="AY28">
-        <v>1.01</v>
+        <v>1.27</v>
       </c>
       <c r="AZ28">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BA28">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BB28">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="BC28">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BD28">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BE28">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BF28">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BG28">
-        <v>1.01</v>
+        <v>1.3</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -8017,61 +8017,61 @@
         <v>245</v>
       </c>
       <c r="F29">
-        <v>2.1</v>
+        <v>2.14</v>
       </c>
       <c r="G29">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="H29">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I29">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="J29">
         <v>3.6</v>
       </c>
       <c r="K29">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="L29">
         <v>1.27</v>
       </c>
       <c r="M29">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N29">
-        <v>2.7</v>
+        <v>4</v>
       </c>
       <c r="O29">
         <v>1.23</v>
       </c>
       <c r="P29">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q29">
         <v>1.76</v>
       </c>
       <c r="R29">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S29">
         <v>2.88</v>
       </c>
       <c r="T29">
-        <v>1.03</v>
+        <v>1.62</v>
       </c>
       <c r="U29">
-        <v>1.05</v>
+        <v>2.22</v>
       </c>
       <c r="V29">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W29">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="X29">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="Y29">
         <v>970</v>
@@ -8086,7 +8086,7 @@
         <v>970</v>
       </c>
       <c r="AC29">
-        <v>44</v>
+        <v>10.5</v>
       </c>
       <c r="AD29">
         <v>970</v>
@@ -8098,7 +8098,7 @@
         <v>970</v>
       </c>
       <c r="AG29">
-        <v>970</v>
+        <v>21</v>
       </c>
       <c r="AH29">
         <v>970</v>
@@ -8110,7 +8110,7 @@
         <v>1000</v>
       </c>
       <c r="AK29">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AL29">
         <v>1000</v>
@@ -8131,52 +8131,52 @@
         <v>4.3</v>
       </c>
       <c r="AR29">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="AS29">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AT29">
-        <v>3.75</v>
+        <v>7.6</v>
       </c>
       <c r="AU29">
-        <v>2.84</v>
+        <v>1.18</v>
       </c>
       <c r="AV29">
-        <v>3.85</v>
+        <v>10</v>
       </c>
       <c r="AW29">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AX29">
-        <v>3.85</v>
+        <v>1.31</v>
       </c>
       <c r="AY29">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="AZ29">
-        <v>4.5</v>
+        <v>1.32</v>
       </c>
       <c r="BA29">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="BB29">
-        <v>7.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BC29">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="BD29">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BE29">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BF29">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="BG29">
-        <v>1.16</v>
+        <v>1.34</v>
       </c>
       <c r="BH29">
         <v>1000</v>
@@ -8262,37 +8262,37 @@
         <v>2.08</v>
       </c>
       <c r="G30">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="H30">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="I30">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J30">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="K30">
-        <v>4.4</v>
+        <v>4.1</v>
       </c>
       <c r="L30">
         <v>1.01</v>
       </c>
       <c r="M30">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N30">
-        <v>2.96</v>
+        <v>4</v>
       </c>
       <c r="O30">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="P30">
         <v>2.12</v>
       </c>
       <c r="Q30">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="R30">
         <v>1.44</v>
@@ -8301,25 +8301,25 @@
         <v>2.66</v>
       </c>
       <c r="T30">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="U30">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="V30">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W30">
-        <v>1.83</v>
+        <v>1.86</v>
       </c>
       <c r="X30">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="Y30">
         <v>970</v>
       </c>
       <c r="Z30">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AA30">
         <v>1000</v>
@@ -8328,7 +8328,7 @@
         <v>970</v>
       </c>
       <c r="AC30">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AD30">
         <v>970</v>
@@ -8352,7 +8352,7 @@
         <v>1000</v>
       </c>
       <c r="AK30">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AL30">
         <v>1000</v>
@@ -8367,58 +8367,58 @@
         <v>1000</v>
       </c>
       <c r="AP30">
-        <v>4.1</v>
+        <v>1.24</v>
       </c>
       <c r="AQ30">
-        <v>4.4</v>
+        <v>1.24</v>
       </c>
       <c r="AR30">
-        <v>5.6</v>
+        <v>5.9</v>
       </c>
       <c r="AS30">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AT30">
-        <v>3.65</v>
+        <v>1.23</v>
       </c>
       <c r="AU30">
-        <v>2.78</v>
+        <v>1.14</v>
       </c>
       <c r="AV30">
-        <v>3.95</v>
+        <v>1.24</v>
       </c>
       <c r="AW30">
+        <v>13</v>
+      </c>
+      <c r="AX30">
+        <v>1.23</v>
+      </c>
+      <c r="AY30">
+        <v>8.4</v>
+      </c>
+      <c r="AZ30">
+        <v>1.24</v>
+      </c>
+      <c r="BA30">
+        <v>14.5</v>
+      </c>
+      <c r="BB30">
+        <v>10.5</v>
+      </c>
+      <c r="BC30">
+        <v>1.24</v>
+      </c>
+      <c r="BD30">
         <v>12</v>
       </c>
-      <c r="AX30">
-        <v>3.65</v>
-      </c>
-      <c r="AY30">
-        <v>3.35</v>
-      </c>
-      <c r="AZ30">
-        <v>4.1</v>
-      </c>
-      <c r="BA30">
-        <v>13.5</v>
-      </c>
-      <c r="BB30">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="BC30">
-        <v>8.6</v>
-      </c>
-      <c r="BD30">
-        <v>11.5</v>
-      </c>
       <c r="BE30">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BF30">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="BG30">
-        <v>1.15</v>
+        <v>1.26</v>
       </c>
       <c r="BH30">
         <v>1000</v>
@@ -8504,73 +8504,73 @@
         <v>1.95</v>
       </c>
       <c r="G31">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="H31">
         <v>3.85</v>
       </c>
       <c r="I31">
-        <v>4.3</v>
+        <v>4.1</v>
       </c>
       <c r="J31">
         <v>3.95</v>
       </c>
       <c r="K31">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="L31">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="M31">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N31">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="O31">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="P31">
         <v>2.46</v>
       </c>
       <c r="Q31">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="R31">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="S31">
-        <v>2.52</v>
+        <v>2.56</v>
       </c>
       <c r="T31">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="U31">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="V31">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="W31">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X31">
         <v>28</v>
       </c>
       <c r="Y31">
-        <v>21</v>
+        <v>19.5</v>
       </c>
       <c r="Z31">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA31">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB31">
         <v>13</v>
       </c>
       <c r="AC31">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="AD31">
         <v>16.5</v>
@@ -8588,13 +8588,13 @@
         <v>16</v>
       </c>
       <c r="AI31">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AJ31">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK31">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AL31">
         <v>28</v>
@@ -8603,34 +8603,34 @@
         <v>75</v>
       </c>
       <c r="AN31">
-        <v>9</v>
+        <v>11.5</v>
       </c>
       <c r="AO31">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="AP31">
         <v>17.5</v>
       </c>
       <c r="AQ31">
-        <v>14</v>
+        <v>17.5</v>
       </c>
       <c r="AR31">
+        <v>21</v>
+      </c>
+      <c r="AS31">
+        <v>34</v>
+      </c>
+      <c r="AT31">
+        <v>11.5</v>
+      </c>
+      <c r="AU31">
         <v>8.800000000000001</v>
       </c>
-      <c r="AS31">
-        <v>10.5</v>
-      </c>
-      <c r="AT31">
-        <v>11</v>
-      </c>
-      <c r="AU31">
-        <v>7.2</v>
-      </c>
       <c r="AV31">
-        <v>12</v>
+        <v>14.5</v>
       </c>
       <c r="AW31">
-        <v>9.6</v>
+        <v>26</v>
       </c>
       <c r="AX31">
         <v>12.5</v>
@@ -8642,7 +8642,7 @@
         <v>14</v>
       </c>
       <c r="BA31">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BB31">
         <v>19</v>
@@ -8651,19 +8651,19 @@
         <v>15.5</v>
       </c>
       <c r="BD31">
-        <v>16.5</v>
+        <v>18.5</v>
       </c>
       <c r="BE31">
-        <v>10</v>
+        <v>38</v>
       </c>
       <c r="BF31">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BG31">
-        <v>8.6</v>
+        <v>21</v>
       </c>
       <c r="BH31">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BI31">
         <v>3.35</v>
@@ -8672,55 +8672,55 @@
         <v>11</v>
       </c>
       <c r="BK31">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BL31">
         <v>100</v>
       </c>
       <c r="BM31">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN31">
-        <v>5.9</v>
+        <v>6</v>
       </c>
       <c r="BO31">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="BP31">
         <v>12.5</v>
       </c>
       <c r="BQ31">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BR31">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="BS31">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT31">
-        <v>9.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BU31">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="BV31">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BW31">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BX31">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BY31">
-        <v>24</v>
+        <v>1.01</v>
       </c>
       <c r="BZ31">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="CA31">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="CB31" t="s">
         <v>291</v>
@@ -8752,10 +8752,10 @@
         <v>2.08</v>
       </c>
       <c r="I32">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="J32">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="K32">
         <v>3.75</v>
@@ -8764,43 +8764,43 @@
         <v>1.33</v>
       </c>
       <c r="M32">
-        <v>1.08</v>
+        <v>1.07</v>
       </c>
       <c r="N32">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O32">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="P32">
         <v>1.83</v>
       </c>
       <c r="Q32">
-        <v>1.96</v>
+        <v>1.99</v>
       </c>
       <c r="R32">
         <v>1.32</v>
       </c>
       <c r="S32">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="T32">
-        <v>1.73</v>
+        <v>1.8</v>
       </c>
       <c r="U32">
-        <v>1.92</v>
+        <v>2.02</v>
       </c>
       <c r="V32">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="W32">
         <v>1.32</v>
       </c>
       <c r="X32">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="Y32">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="Z32">
         <v>14</v>
@@ -8833,10 +8833,10 @@
         <v>42</v>
       </c>
       <c r="AJ32">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AK32">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AL32">
         <v>65</v>
@@ -8985,13 +8985,13 @@
         <v>249</v>
       </c>
       <c r="F33">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="G33">
         <v>110</v>
       </c>
       <c r="H33">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="I33">
         <v>110</v>
@@ -9009,13 +9009,13 @@
         <v>1.01</v>
       </c>
       <c r="N33">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="O33">
         <v>1.02</v>
       </c>
       <c r="P33">
-        <v>1.16</v>
+        <v>1.2</v>
       </c>
       <c r="Q33">
         <v>1.38</v>
@@ -9033,10 +9033,10 @@
         <v>1.01</v>
       </c>
       <c r="V33">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W33">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="X33">
         <v>1000</v>
@@ -9230,7 +9230,7 @@
         <v>2.4</v>
       </c>
       <c r="G34">
-        <v>2.66</v>
+        <v>2.58</v>
       </c>
       <c r="H34">
         <v>3.05</v>
@@ -9239,10 +9239,10 @@
         <v>3.35</v>
       </c>
       <c r="J34">
-        <v>3.25</v>
+        <v>3.35</v>
       </c>
       <c r="K34">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="L34">
         <v>1.32</v>
@@ -9278,7 +9278,7 @@
         <v>1.42</v>
       </c>
       <c r="W34">
-        <v>1.6</v>
+        <v>1.63</v>
       </c>
       <c r="X34">
         <v>970</v>
@@ -9338,34 +9338,34 @@
         <v>3.6</v>
       </c>
       <c r="AQ34">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AR34">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AS34">
         <v>16.5</v>
       </c>
       <c r="AT34">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="AU34">
-        <v>2.62</v>
+        <v>2.7</v>
       </c>
       <c r="AV34">
-        <v>4.1</v>
+        <v>4.3</v>
       </c>
       <c r="AW34">
         <v>13</v>
       </c>
       <c r="AX34">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="AY34">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="AZ34">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="BA34">
         <v>16</v>
@@ -9374,7 +9374,7 @@
         <v>12.5</v>
       </c>
       <c r="BC34">
-        <v>8.6</v>
+        <v>11</v>
       </c>
       <c r="BD34">
         <v>15</v>
@@ -9505,7 +9505,7 @@
         <v>1.27</v>
       </c>
       <c r="R35">
-        <v>1.46</v>
+        <v>1.49</v>
       </c>
       <c r="S35">
         <v>2.5</v>
@@ -9514,7 +9514,7 @@
         <v>1.68</v>
       </c>
       <c r="U35">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="V35">
         <v>1.08</v>
@@ -9559,7 +9559,7 @@
         <v>100</v>
       </c>
       <c r="AJ35">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AK35">
         <v>18.5</v>
@@ -9571,7 +9571,7 @@
         <v>130</v>
       </c>
       <c r="AN35">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AO35">
         <v>130</v>
@@ -9580,7 +9580,7 @@
         <v>16</v>
       </c>
       <c r="AQ35">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="AR35">
         <v>1.01</v>
@@ -9640,13 +9640,13 @@
         <v>12.5</v>
       </c>
       <c r="BK35">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BL35">
         <v>1000</v>
       </c>
       <c r="BM35">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BN35">
         <v>4.9</v>
@@ -9658,37 +9658,37 @@
         <v>11</v>
       </c>
       <c r="BQ35">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BR35">
         <v>27</v>
       </c>
       <c r="BS35">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BT35">
         <v>13</v>
       </c>
       <c r="BU35">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BV35">
         <v>70</v>
       </c>
       <c r="BW35">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BX35">
         <v>70</v>
       </c>
       <c r="BY35">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="BZ35">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="CA35">
-        <v>1.01</v>
+        <v>3.65</v>
       </c>
       <c r="CB35" t="s">
         <v>291</v>
@@ -9711,13 +9711,13 @@
         <v>252</v>
       </c>
       <c r="F36">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="G36">
         <v>6.2</v>
       </c>
       <c r="H36">
-        <v>1.66</v>
+        <v>1.67</v>
       </c>
       <c r="I36">
         <v>1.68</v>
@@ -9738,7 +9738,7 @@
         <v>3.9</v>
       </c>
       <c r="O36">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P36">
         <v>1.99</v>
@@ -9750,7 +9750,7 @@
         <v>1.39</v>
       </c>
       <c r="S36">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="T36">
         <v>1.84</v>
@@ -9765,7 +9765,7 @@
         <v>1.19</v>
       </c>
       <c r="X36">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="Y36">
         <v>8.800000000000001</v>
@@ -9804,7 +9804,7 @@
         <v>170</v>
       </c>
       <c r="AK36">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AL36">
         <v>80</v>
@@ -9813,7 +9813,7 @@
         <v>130</v>
       </c>
       <c r="AN36">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AO36">
         <v>11</v>
@@ -9849,22 +9849,22 @@
         <v>19.5</v>
       </c>
       <c r="AZ36">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BA36">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="BB36">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BC36">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BD36">
         <v>60</v>
       </c>
       <c r="BE36">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BF36">
         <v>7.6</v>
@@ -9962,10 +9962,10 @@
         <v>1.51</v>
       </c>
       <c r="I37">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="J37">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="K37">
         <v>4.5</v>
@@ -10001,7 +10001,7 @@
         <v>1.74</v>
       </c>
       <c r="V37">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="W37">
         <v>1.12</v>
@@ -10085,7 +10085,7 @@
         <v>16</v>
       </c>
       <c r="AX37">
-        <v>32</v>
+        <v>65</v>
       </c>
       <c r="AY37">
         <v>30</v>
@@ -10097,13 +10097,13 @@
         <v>42</v>
       </c>
       <c r="BB37">
-        <v>18</v>
+        <v>19.5</v>
       </c>
       <c r="BC37">
         <v>18.5</v>
       </c>
       <c r="BD37">
-        <v>19</v>
+        <v>44</v>
       </c>
       <c r="BE37">
         <v>19.5</v>
@@ -10115,10 +10115,10 @@
         <v>8.4</v>
       </c>
       <c r="BH37">
-        <v>3.55</v>
+        <v>970</v>
       </c>
       <c r="BI37">
-        <v>2.74</v>
+        <v>1.01</v>
       </c>
       <c r="BJ37">
         <v>1000</v>
@@ -10151,7 +10151,7 @@
         <v>1.01</v>
       </c>
       <c r="BT37">
-        <v>4.3</v>
+        <v>970</v>
       </c>
       <c r="BU37">
         <v>1.01</v>
@@ -10195,58 +10195,58 @@
         <v>254</v>
       </c>
       <c r="F38">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="G38">
-        <v>2</v>
+        <v>2.04</v>
       </c>
       <c r="H38">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="I38">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J38">
         <v>4.1</v>
       </c>
       <c r="K38">
-        <v>4.6</v>
+        <v>4.4</v>
       </c>
       <c r="L38">
         <v>1.01</v>
       </c>
       <c r="M38">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N38">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O38">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P38">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="Q38">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="R38">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="S38">
-        <v>2.3</v>
+        <v>2.4</v>
       </c>
       <c r="T38">
-        <v>1.53</v>
+        <v>1.56</v>
       </c>
       <c r="U38">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="V38">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="W38">
-        <v>2</v>
+        <v>1.96</v>
       </c>
       <c r="X38">
         <v>28</v>
@@ -10255,10 +10255,10 @@
         <v>22</v>
       </c>
       <c r="Z38">
-        <v>34</v>
+        <v>50</v>
       </c>
       <c r="AA38">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB38">
         <v>15</v>
@@ -10270,10 +10270,10 @@
         <v>17</v>
       </c>
       <c r="AE38">
-        <v>44</v>
+        <v>65</v>
       </c>
       <c r="AF38">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="AG38">
         <v>12</v>
@@ -10282,19 +10282,19 @@
         <v>16</v>
       </c>
       <c r="AI38">
-        <v>44</v>
+        <v>75</v>
       </c>
       <c r="AJ38">
         <v>25</v>
       </c>
       <c r="AK38">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AL38">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="AM38">
-        <v>70</v>
+        <v>530</v>
       </c>
       <c r="AN38">
         <v>9.199999999999999</v>
@@ -10303,40 +10303,40 @@
         <v>26</v>
       </c>
       <c r="AP38">
-        <v>5.6</v>
+        <v>19</v>
       </c>
       <c r="AQ38">
         <v>17.5</v>
       </c>
       <c r="AR38">
-        <v>5.8</v>
+        <v>19.5</v>
       </c>
       <c r="AS38">
-        <v>6.4</v>
+        <v>38</v>
       </c>
       <c r="AT38">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AU38">
-        <v>8.800000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AV38">
         <v>13.5</v>
       </c>
       <c r="AW38">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="AX38">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AY38">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ38">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BA38">
-        <v>6</v>
+        <v>22</v>
       </c>
       <c r="BB38">
         <v>20</v>
@@ -10345,16 +10345,16 @@
         <v>15.5</v>
       </c>
       <c r="BD38">
-        <v>5.6</v>
+        <v>17.5</v>
       </c>
       <c r="BE38">
-        <v>6.4</v>
+        <v>32</v>
       </c>
       <c r="BF38">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BG38">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="BH38">
         <v>1000</v>
@@ -10437,40 +10437,40 @@
         <v>255</v>
       </c>
       <c r="F39">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="G39">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="H39">
-        <v>2.26</v>
+        <v>2.32</v>
       </c>
       <c r="I39">
         <v>2.46</v>
       </c>
       <c r="J39">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="K39">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="L39">
         <v>1.34</v>
       </c>
       <c r="M39">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N39">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="O39">
         <v>1.31</v>
       </c>
       <c r="P39">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q39">
-        <v>1.86</v>
+        <v>1.92</v>
       </c>
       <c r="R39">
         <v>1.37</v>
@@ -10482,13 +10482,13 @@
         <v>1.6</v>
       </c>
       <c r="U39">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="V39">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="W39">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="X39">
         <v>18</v>
@@ -10539,7 +10539,7 @@
         <v>110</v>
       </c>
       <c r="AN39">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AO39">
         <v>23</v>
@@ -10599,10 +10599,10 @@
         <v>14</v>
       </c>
       <c r="BH39">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="BI39">
-        <v>2.78</v>
+        <v>3.15</v>
       </c>
       <c r="BJ39">
         <v>11.5</v>
@@ -10635,10 +10635,10 @@
         <v>1.01</v>
       </c>
       <c r="BT39">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BU39">
-        <v>4</v>
+        <v>4.1</v>
       </c>
       <c r="BV39">
         <v>21</v>
@@ -10682,16 +10682,16 @@
         <v>1.44</v>
       </c>
       <c r="G40">
-        <v>1.61</v>
+        <v>1.58</v>
       </c>
       <c r="H40">
-        <v>5.3</v>
+        <v>6.4</v>
       </c>
       <c r="I40">
         <v>8.800000000000001</v>
       </c>
       <c r="J40">
-        <v>3.8</v>
+        <v>4.8</v>
       </c>
       <c r="K40">
         <v>6.4</v>
@@ -10703,7 +10703,7 @@
         <v>1.01</v>
       </c>
       <c r="N40">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="O40">
         <v>1.1</v>
@@ -10730,7 +10730,7 @@
         <v>1.13</v>
       </c>
       <c r="W40">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="X40">
         <v>1000</v>
@@ -10924,88 +10924,88 @@
         <v>1.57</v>
       </c>
       <c r="G41">
-        <v>1.65</v>
+        <v>1.63</v>
       </c>
       <c r="H41">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="I41">
-        <v>7.6</v>
+        <v>6.6</v>
       </c>
       <c r="J41">
         <v>4.7</v>
       </c>
       <c r="K41">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="L41">
         <v>1.01</v>
       </c>
       <c r="M41">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N41">
-        <v>4.8</v>
+        <v>5.5</v>
       </c>
       <c r="O41">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P41">
+        <v>2.5</v>
+      </c>
+      <c r="Q41">
+        <v>1.55</v>
+      </c>
+      <c r="R41">
+        <v>1.61</v>
+      </c>
+      <c r="S41">
         <v>2.38</v>
       </c>
-      <c r="Q41">
-        <v>1.57</v>
-      </c>
-      <c r="R41">
-        <v>1.62</v>
-      </c>
-      <c r="S41">
-        <v>2.36</v>
-      </c>
       <c r="T41">
-        <v>1.59</v>
+        <v>1.66</v>
       </c>
       <c r="U41">
-        <v>2.16</v>
+        <v>2.2</v>
       </c>
       <c r="V41">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W41">
-        <v>2.54</v>
+        <v>2.56</v>
       </c>
       <c r="X41">
         <v>1000</v>
       </c>
       <c r="Y41">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="Z41">
-        <v>1000</v>
+        <v>220</v>
       </c>
       <c r="AA41">
         <v>1000</v>
       </c>
       <c r="AB41">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AC41">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD41">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AE41">
         <v>85</v>
       </c>
       <c r="AF41">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AG41">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH41">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AI41">
         <v>1000</v>
@@ -11023,64 +11023,64 @@
         <v>95</v>
       </c>
       <c r="AN41">
-        <v>970</v>
+        <v>8.6</v>
       </c>
       <c r="AO41">
         <v>1000</v>
       </c>
       <c r="AP41">
-        <v>1.38</v>
+        <v>2.34</v>
       </c>
       <c r="AQ41">
-        <v>1.38</v>
+        <v>4.4</v>
       </c>
       <c r="AR41">
-        <v>1.38</v>
+        <v>2.32</v>
       </c>
       <c r="AS41">
-        <v>1.38</v>
+        <v>2.34</v>
       </c>
       <c r="AT41">
-        <v>1.38</v>
+        <v>8.6</v>
       </c>
       <c r="AU41">
-        <v>1.38</v>
+        <v>8.6</v>
       </c>
       <c r="AV41">
         <v>18</v>
       </c>
       <c r="AW41">
-        <v>1.36</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX41">
-        <v>1.38</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY41">
         <v>8.4</v>
       </c>
       <c r="AZ41">
-        <v>1.38</v>
+        <v>13</v>
       </c>
       <c r="BA41">
-        <v>1.38</v>
+        <v>9</v>
       </c>
       <c r="BB41">
-        <v>1.28</v>
+        <v>2.06</v>
       </c>
       <c r="BC41">
-        <v>1.27</v>
+        <v>2.04</v>
       </c>
       <c r="BD41">
-        <v>1.38</v>
+        <v>2.32</v>
       </c>
       <c r="BE41">
-        <v>1.36</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF41">
-        <v>1.16</v>
+        <v>5.5</v>
       </c>
       <c r="BG41">
-        <v>1.38</v>
+        <v>2.34</v>
       </c>
       <c r="BH41">
         <v>1000</v>
@@ -11166,55 +11166,55 @@
         <v>1.7</v>
       </c>
       <c r="G42">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="H42">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I42">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="J42">
         <v>4.1</v>
       </c>
       <c r="K42">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L42">
         <v>1.01</v>
       </c>
       <c r="M42">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="N42">
-        <v>4.5</v>
+        <v>4.3</v>
       </c>
       <c r="O42">
-        <v>1.23</v>
+        <v>1.22</v>
       </c>
       <c r="P42">
-        <v>2.24</v>
+        <v>2.16</v>
       </c>
       <c r="Q42">
-        <v>1.72</v>
+        <v>1.65</v>
       </c>
       <c r="R42">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S42">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="T42">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="U42">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="V42">
         <v>1.21</v>
       </c>
       <c r="W42">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X42">
         <v>21</v>
@@ -11241,19 +11241,19 @@
         <v>70</v>
       </c>
       <c r="AF42">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG42">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AH42">
         <v>19.5</v>
       </c>
       <c r="AI42">
-        <v>90</v>
+        <v>150</v>
       </c>
       <c r="AJ42">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AK42">
         <v>18</v>
@@ -11265,7 +11265,7 @@
         <v>110</v>
       </c>
       <c r="AN42">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AO42">
         <v>90</v>
@@ -11277,52 +11277,52 @@
         <v>18</v>
       </c>
       <c r="AR42">
-        <v>6.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AS42">
-        <v>7.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT42">
+        <v>9</v>
+      </c>
+      <c r="AU42">
         <v>8.800000000000001</v>
-      </c>
-      <c r="AU42">
-        <v>8.4</v>
       </c>
       <c r="AV42">
         <v>17.5</v>
       </c>
       <c r="AW42">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AX42">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AY42">
-        <v>8.6</v>
+        <v>9</v>
       </c>
       <c r="AZ42">
         <v>16</v>
       </c>
       <c r="BA42">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB42">
         <v>14.5</v>
       </c>
       <c r="BC42">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="BD42">
-        <v>6.2</v>
+        <v>7.6</v>
       </c>
       <c r="BE42">
-        <v>7.2</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF42">
         <v>7.6</v>
       </c>
       <c r="BG42">
-        <v>7</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH42">
         <v>1000</v>
@@ -11411,13 +11411,13 @@
         <v>1.21</v>
       </c>
       <c r="H43">
-        <v>10.5</v>
+        <v>12</v>
       </c>
       <c r="I43">
         <v>27</v>
       </c>
       <c r="J43">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="K43">
         <v>11</v>
@@ -11438,16 +11438,16 @@
         <v>2.9</v>
       </c>
       <c r="Q43">
-        <v>1.38</v>
+        <v>1.43</v>
       </c>
       <c r="R43">
         <v>1.63</v>
       </c>
       <c r="S43">
-        <v>1.51</v>
+        <v>1.71</v>
       </c>
       <c r="T43">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="U43">
         <v>1.61</v>
@@ -11456,7 +11456,7 @@
         <v>1.04</v>
       </c>
       <c r="W43">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="X43">
         <v>42</v>
@@ -11528,7 +11528,7 @@
         <v>1.01</v>
       </c>
       <c r="AU43">
-        <v>1.01</v>
+        <v>15</v>
       </c>
       <c r="AV43">
         <v>1.01</v>
@@ -11537,10 +11537,10 @@
         <v>1.01</v>
       </c>
       <c r="AX43">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AY43">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AZ43">
         <v>1.01</v>
@@ -11549,10 +11549,10 @@
         <v>1.01</v>
       </c>
       <c r="BB43">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="BC43">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BD43">
         <v>1.01</v>
@@ -11561,7 +11561,7 @@
         <v>1.01</v>
       </c>
       <c r="BF43">
-        <v>2.68</v>
+        <v>2.72</v>
       </c>
       <c r="BG43">
         <v>1.01</v>
@@ -11647,22 +11647,22 @@
         <v>260</v>
       </c>
       <c r="F44">
-        <v>1.67</v>
+        <v>1.71</v>
       </c>
       <c r="G44">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="H44">
-        <v>5.3</v>
+        <v>5.5</v>
       </c>
       <c r="I44">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="J44">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K44">
-        <v>4.8</v>
+        <v>3.95</v>
       </c>
       <c r="L44">
         <v>1.36</v>
@@ -11677,10 +11677,10 @@
         <v>1.35</v>
       </c>
       <c r="P44">
-        <v>1.7</v>
+        <v>1.67</v>
       </c>
       <c r="Q44">
-        <v>2.1</v>
+        <v>2.08</v>
       </c>
       <c r="R44">
         <v>1.25</v>
@@ -11695,10 +11695,10 @@
         <v>1.01</v>
       </c>
       <c r="V44">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W44">
-        <v>2.16</v>
+        <v>2.22</v>
       </c>
       <c r="X44">
         <v>14.5</v>
@@ -11740,7 +11740,7 @@
         <v>23</v>
       </c>
       <c r="AK44">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AL44">
         <v>55</v>
@@ -11898,13 +11898,13 @@
         <v>1.98</v>
       </c>
       <c r="I45">
-        <v>2.2</v>
+        <v>2.18</v>
       </c>
       <c r="J45">
         <v>3.1</v>
       </c>
       <c r="K45">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L45">
         <v>1.4</v>
@@ -11913,7 +11913,7 @@
         <v>1.09</v>
       </c>
       <c r="N45">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="O45">
         <v>1.45</v>
@@ -11937,7 +11937,7 @@
         <v>1.01</v>
       </c>
       <c r="V45">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="W45">
         <v>1.25</v>
@@ -11949,7 +11949,7 @@
         <v>10</v>
       </c>
       <c r="Z45">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AA45">
         <v>38</v>
@@ -12131,7 +12131,7 @@
         <v>262</v>
       </c>
       <c r="F46">
-        <v>1.43</v>
+        <v>1.4</v>
       </c>
       <c r="G46">
         <v>1.47</v>
@@ -12140,7 +12140,7 @@
         <v>7.4</v>
       </c>
       <c r="I46">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="J46">
         <v>5.3</v>
@@ -12173,13 +12173,13 @@
         <v>2.22</v>
       </c>
       <c r="T46">
-        <v>1.65</v>
+        <v>1.71</v>
       </c>
       <c r="U46">
         <v>2.14</v>
       </c>
       <c r="V46">
-        <v>1.14</v>
+        <v>1.12</v>
       </c>
       <c r="W46">
         <v>3.1</v>
@@ -12188,7 +12188,7 @@
         <v>34</v>
       </c>
       <c r="Y46">
-        <v>38</v>
+        <v>110</v>
       </c>
       <c r="Z46">
         <v>85</v>
@@ -12239,13 +12239,13 @@
         <v>100</v>
       </c>
       <c r="AP46">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AQ46">
         <v>5.2</v>
       </c>
       <c r="AR46">
-        <v>5.6</v>
+        <v>18.5</v>
       </c>
       <c r="AS46">
         <v>5.8</v>
@@ -12257,10 +12257,10 @@
         <v>11</v>
       </c>
       <c r="AV46">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="AW46">
-        <v>5.7</v>
+        <v>26</v>
       </c>
       <c r="AX46">
         <v>9.4</v>
@@ -12272,7 +12272,7 @@
         <v>18</v>
       </c>
       <c r="BA46">
-        <v>5.6</v>
+        <v>26</v>
       </c>
       <c r="BB46">
         <v>11</v>
@@ -12281,16 +12281,16 @@
         <v>11.5</v>
       </c>
       <c r="BD46">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="BE46">
-        <v>5.6</v>
+        <v>24</v>
       </c>
       <c r="BF46">
         <v>4.1</v>
       </c>
       <c r="BG46">
-        <v>5.6</v>
+        <v>5.8</v>
       </c>
       <c r="BH46">
         <v>1000</v>
@@ -12373,22 +12373,22 @@
         <v>263</v>
       </c>
       <c r="F47">
-        <v>1.73</v>
+        <v>1.77</v>
       </c>
       <c r="G47">
-        <v>1.8</v>
+        <v>1.81</v>
       </c>
       <c r="H47">
         <v>5.6</v>
       </c>
       <c r="I47">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="J47">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K47">
-        <v>3.9</v>
+        <v>3.75</v>
       </c>
       <c r="L47">
         <v>1.01</v>
@@ -12397,67 +12397,67 @@
         <v>1.09</v>
       </c>
       <c r="N47">
-        <v>2.94</v>
+        <v>3.25</v>
       </c>
       <c r="O47">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="P47">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="Q47">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="R47">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="S47">
         <v>4.2</v>
       </c>
       <c r="T47">
-        <v>2.04</v>
+        <v>2.1</v>
       </c>
       <c r="U47">
-        <v>1.76</v>
+        <v>1.85</v>
       </c>
       <c r="V47">
-        <v>1.19</v>
+        <v>1.2</v>
       </c>
       <c r="W47">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="X47">
         <v>12</v>
       </c>
       <c r="Y47">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="Z47">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="AA47">
-        <v>240</v>
+        <v>210</v>
       </c>
       <c r="AB47">
         <v>7.4</v>
       </c>
       <c r="AC47">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AD47">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="AE47">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AF47">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AG47">
         <v>10.5</v>
       </c>
       <c r="AH47">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AI47">
         <v>120</v>
@@ -12469,70 +12469,70 @@
         <v>26</v>
       </c>
       <c r="AL47">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="AM47">
         <v>180</v>
       </c>
       <c r="AN47">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO47">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="AP47">
         <v>10</v>
       </c>
       <c r="AQ47">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR47">
         <v>36</v>
       </c>
       <c r="AS47">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="AT47">
-        <v>6.4</v>
+        <v>6.8</v>
       </c>
       <c r="AU47">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="AV47">
         <v>20</v>
       </c>
       <c r="AW47">
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="AX47">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AY47">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AZ47">
         <v>20</v>
       </c>
       <c r="BA47">
-        <v>11</v>
+        <v>13.5</v>
       </c>
       <c r="BB47">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BC47">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD47">
         <v>40</v>
       </c>
       <c r="BE47">
-        <v>8.6</v>
+        <v>13</v>
       </c>
       <c r="BF47">
+        <v>13</v>
+      </c>
+      <c r="BG47">
         <v>12.5</v>
-      </c>
-      <c r="BG47">
-        <v>8.6</v>
       </c>
       <c r="BH47">
         <v>1000</v>
@@ -12624,10 +12624,10 @@
         <v>4.1</v>
       </c>
       <c r="I48">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="J48">
-        <v>3.4</v>
+        <v>3.55</v>
       </c>
       <c r="K48">
         <v>6.2</v>
@@ -12857,13 +12857,13 @@
         <v>265</v>
       </c>
       <c r="F49">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="G49">
-        <v>3.05</v>
+        <v>2.94</v>
       </c>
       <c r="H49">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="I49">
         <v>2.7</v>
@@ -12887,7 +12887,7 @@
         <v>1.36</v>
       </c>
       <c r="P49">
-        <v>1.88</v>
+        <v>1.89</v>
       </c>
       <c r="Q49">
         <v>2.04</v>
@@ -12902,13 +12902,13 @@
         <v>1.71</v>
       </c>
       <c r="U49">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="V49">
         <v>1.59</v>
       </c>
       <c r="W49">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="X49">
         <v>13.5</v>
@@ -12917,13 +12917,13 @@
         <v>10.5</v>
       </c>
       <c r="Z49">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AA49">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AB49">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC49">
         <v>8.199999999999999</v>
@@ -12935,10 +12935,10 @@
         <v>32</v>
       </c>
       <c r="AF49">
-        <v>28</v>
+        <v>19</v>
       </c>
       <c r="AG49">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH49">
         <v>19</v>
@@ -12950,16 +12950,16 @@
         <v>70</v>
       </c>
       <c r="AK49">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AL49">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="AM49">
         <v>110</v>
       </c>
       <c r="AN49">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AO49">
         <v>27</v>
@@ -12983,7 +12983,7 @@
         <v>7.2</v>
       </c>
       <c r="AV49">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AW49">
         <v>26</v>
@@ -13001,16 +13001,16 @@
         <v>38</v>
       </c>
       <c r="BB49">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BC49">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BD49">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="BE49">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="BF49">
         <v>23</v>
@@ -13099,10 +13099,10 @@
         <v>266</v>
       </c>
       <c r="F50">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="G50">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="H50">
         <v>4.2</v>
@@ -13117,7 +13117,7 @@
         <v>3.1</v>
       </c>
       <c r="L50">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="M50">
         <v>1.16</v>
@@ -13150,7 +13150,7 @@
         <v>1.3</v>
       </c>
       <c r="W50">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="X50">
         <v>7.2</v>
@@ -13189,13 +13189,13 @@
         <v>140</v>
       </c>
       <c r="AJ50">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AK50">
         <v>38</v>
       </c>
       <c r="AL50">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AM50">
         <v>330</v>
@@ -13261,64 +13261,64 @@
         <v>42</v>
       </c>
       <c r="BH50">
-        <v>970</v>
+        <v>2.38</v>
       </c>
       <c r="BI50">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="BJ50">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK50">
-        <v>3</v>
+        <v>6.8</v>
       </c>
       <c r="BL50">
-        <v>1000</v>
+        <v>370</v>
       </c>
       <c r="BM50">
+        <v>13</v>
+      </c>
+      <c r="BN50">
+        <v>4.7</v>
+      </c>
+      <c r="BO50">
+        <v>4.3</v>
+      </c>
+      <c r="BP50">
+        <v>22</v>
+      </c>
+      <c r="BQ50">
+        <v>8.4</v>
+      </c>
+      <c r="BR50">
+        <v>55</v>
+      </c>
+      <c r="BS50">
         <v>11</v>
       </c>
-      <c r="BN50">
-        <v>970</v>
-      </c>
-      <c r="BO50">
-        <v>1.93</v>
-      </c>
-      <c r="BP50">
-        <v>1000</v>
-      </c>
-      <c r="BQ50">
-        <v>3</v>
-      </c>
-      <c r="BR50">
-        <v>1000</v>
-      </c>
-      <c r="BS50">
-        <v>9.199999999999999</v>
-      </c>
       <c r="BT50">
-        <v>970</v>
+        <v>9</v>
       </c>
       <c r="BU50">
-        <v>2.34</v>
+        <v>6.6</v>
       </c>
       <c r="BV50">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="BW50">
-        <v>9.199999999999999</v>
+        <v>11</v>
       </c>
       <c r="BX50">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="BY50">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="BZ50">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="CA50">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="CB50" t="s">
         <v>291</v>
@@ -13347,7 +13347,7 @@
         <v>1.78</v>
       </c>
       <c r="H51">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I51">
         <v>7.6</v>
@@ -13356,7 +13356,7 @@
         <v>4.2</v>
       </c>
       <c r="K51">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="L51">
         <v>1.01</v>
@@ -13380,7 +13380,7 @@
         <v>1.93</v>
       </c>
       <c r="S51">
-        <v>1.64</v>
+        <v>1.33</v>
       </c>
       <c r="T51">
         <v>1.01</v>
@@ -13610,7 +13610,7 @@
         <v>2.98</v>
       </c>
       <c r="O52">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="P52">
         <v>2.98</v>
@@ -13834,10 +13834,10 @@
         <v>7.8</v>
       </c>
       <c r="I53">
-        <v>9.800000000000001</v>
+        <v>9.6</v>
       </c>
       <c r="J53">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K53">
         <v>4.4</v>
@@ -13867,7 +13867,7 @@
         <v>3.75</v>
       </c>
       <c r="T53">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="U53">
         <v>1.46</v>
@@ -14127,7 +14127,7 @@
         <v>18</v>
       </c>
       <c r="Z54">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AA54">
         <v>27</v>
@@ -14142,7 +14142,7 @@
         <v>12</v>
       </c>
       <c r="AE54">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AF54">
         <v>30</v>
@@ -14330,7 +14330,7 @@
         <v>1.01</v>
       </c>
       <c r="M55">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N55">
         <v>4</v>
@@ -14342,10 +14342,10 @@
         <v>2.12</v>
       </c>
       <c r="Q55">
-        <v>1.81</v>
+        <v>1.85</v>
       </c>
       <c r="R55">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S55">
         <v>3.2</v>
@@ -14369,7 +14369,7 @@
         <v>30</v>
       </c>
       <c r="Z55">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="AA55">
         <v>340</v>
@@ -14393,7 +14393,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AH55">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="AI55">
         <v>140</v>
@@ -14414,10 +14414,10 @@
         <v>7.8</v>
       </c>
       <c r="AO55">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="AP55">
-        <v>6.2</v>
+        <v>15</v>
       </c>
       <c r="AQ55">
         <v>23</v>
@@ -14426,7 +14426,7 @@
         <v>60</v>
       </c>
       <c r="AS55">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AT55">
         <v>7.2</v>
@@ -14435,10 +14435,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV55">
-        <v>7.4</v>
+        <v>12.5</v>
       </c>
       <c r="AW55">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AX55">
         <v>7.6</v>
@@ -14450,7 +14450,7 @@
         <v>23</v>
       </c>
       <c r="BA55">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BB55">
         <v>11.5</v>
@@ -14459,16 +14459,16 @@
         <v>14.5</v>
       </c>
       <c r="BD55">
-        <v>7.8</v>
+        <v>17</v>
       </c>
       <c r="BE55">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BF55">
         <v>7</v>
       </c>
       <c r="BG55">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="BH55">
         <v>1000</v>
@@ -14575,16 +14575,16 @@
         <v>1.05</v>
       </c>
       <c r="N56">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O56">
         <v>1.25</v>
       </c>
       <c r="P56">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="Q56">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="R56">
         <v>1.47</v>
@@ -14620,7 +14620,7 @@
         <v>17</v>
       </c>
       <c r="AC56">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AD56">
         <v>11</v>
@@ -14629,7 +14629,7 @@
         <v>21</v>
       </c>
       <c r="AF56">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AG56">
         <v>15.5</v>
@@ -14647,7 +14647,7 @@
         <v>40</v>
       </c>
       <c r="AL56">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AM56">
         <v>75</v>
@@ -14674,7 +14674,7 @@
         <v>15</v>
       </c>
       <c r="AU56">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV56">
         <v>9.800000000000001</v>
@@ -14793,166 +14793,166 @@
         <v>273</v>
       </c>
       <c r="F57">
-        <v>1.42</v>
+        <v>1.81</v>
       </c>
       <c r="G57">
-        <v>110</v>
+        <v>2.1</v>
       </c>
       <c r="H57">
-        <v>1.47</v>
+        <v>4.4</v>
       </c>
       <c r="I57">
-        <v>95</v>
+        <v>5.9</v>
       </c>
       <c r="J57">
-        <v>1.06</v>
+        <v>2.94</v>
       </c>
       <c r="K57">
         <v>3.65</v>
       </c>
       <c r="L57">
-        <v>1.01</v>
+        <v>1.41</v>
       </c>
       <c r="M57">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="N57">
-        <v>1.04</v>
+        <v>2.66</v>
       </c>
       <c r="O57">
         <v>1.41</v>
       </c>
       <c r="P57">
-        <v>1.25</v>
+        <v>1.61</v>
       </c>
       <c r="Q57">
-        <v>1.95</v>
+        <v>2.14</v>
       </c>
       <c r="R57">
-        <v>1.14</v>
+        <v>1.24</v>
       </c>
       <c r="S57">
-        <v>1.95</v>
+        <v>3.25</v>
       </c>
       <c r="T57">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="U57">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="V57">
-        <v>1.02</v>
+        <v>1.2</v>
       </c>
       <c r="W57">
-        <v>1.04</v>
+        <v>1.9</v>
       </c>
       <c r="X57">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y57">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z57">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AA57">
-        <v>1000</v>
+        <v>170</v>
       </c>
       <c r="AB57">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AC57">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD57">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AE57">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AF57">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AG57">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH57">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AI57">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ57">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AK57">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL57">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM57">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AN57">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AO57">
-        <v>1000</v>
+        <v>150</v>
       </c>
       <c r="AP57">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="AQ57">
-        <v>1.01</v>
+        <v>3.7</v>
       </c>
       <c r="AR57">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="AS57">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="AT57">
-        <v>1.01</v>
+        <v>2.96</v>
       </c>
       <c r="AU57">
-        <v>1.01</v>
+        <v>3.15</v>
       </c>
       <c r="AV57">
-        <v>1.01</v>
+        <v>3.95</v>
       </c>
       <c r="AW57">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="AX57">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AY57">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="AZ57">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BA57">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BB57">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BC57">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BD57">
-        <v>1.01</v>
+        <v>4.3</v>
       </c>
       <c r="BE57">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BF57">
-        <v>1.01</v>
+        <v>3.9</v>
       </c>
       <c r="BG57">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BH57">
         <v>1000</v>
@@ -15068,10 +15068,10 @@
         <v>1.96</v>
       </c>
       <c r="Q58">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="R58">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="S58">
         <v>3.55</v>
@@ -15095,22 +15095,22 @@
         <v>15.5</v>
       </c>
       <c r="Z58">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AA58">
         <v>95</v>
       </c>
       <c r="AB58">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AC58">
         <v>8.4</v>
       </c>
       <c r="AD58">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="AE58">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="AF58">
         <v>12</v>
@@ -15119,25 +15119,25 @@
         <v>10.5</v>
       </c>
       <c r="AH58">
-        <v>18.5</v>
+        <v>19.5</v>
       </c>
       <c r="AI58">
         <v>65</v>
       </c>
       <c r="AJ58">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK58">
         <v>21</v>
       </c>
       <c r="AL58">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AM58">
         <v>110</v>
       </c>
       <c r="AN58">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AO58">
         <v>60</v>
@@ -15182,7 +15182,7 @@
         <v>20</v>
       </c>
       <c r="BC58">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD58">
         <v>32</v>
@@ -15191,22 +15191,22 @@
         <v>38</v>
       </c>
       <c r="BF58">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG58">
         <v>50</v>
       </c>
       <c r="BH58">
-        <v>3.75</v>
+        <v>970</v>
       </c>
       <c r="BI58">
-        <v>2.86</v>
+        <v>1.01</v>
       </c>
       <c r="BJ58">
-        <v>19</v>
+        <v>970</v>
       </c>
       <c r="BK58">
-        <v>7</v>
+        <v>1.01</v>
       </c>
       <c r="BL58">
         <v>1000</v>
@@ -15215,16 +15215,16 @@
         <v>1.01</v>
       </c>
       <c r="BN58">
-        <v>5.5</v>
+        <v>970</v>
       </c>
       <c r="BO58">
-        <v>3.8</v>
+        <v>1.01</v>
       </c>
       <c r="BP58">
         <v>1000</v>
       </c>
       <c r="BQ58">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BR58">
         <v>1000</v>
@@ -15233,10 +15233,10 @@
         <v>1.01</v>
       </c>
       <c r="BT58">
-        <v>11</v>
+        <v>970</v>
       </c>
       <c r="BU58">
-        <v>5.7</v>
+        <v>1.01</v>
       </c>
       <c r="BV58">
         <v>1000</v>
@@ -15301,7 +15301,7 @@
         <v>1.07</v>
       </c>
       <c r="N59">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="O59">
         <v>1.34</v>
@@ -15409,7 +15409,7 @@
         <v>15</v>
       </c>
       <c r="AX59">
-        <v>25</v>
+        <v>1.01</v>
       </c>
       <c r="AY59">
         <v>13.5</v>
@@ -15418,22 +15418,22 @@
         <v>14</v>
       </c>
       <c r="BA59">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BB59">
-        <v>75</v>
+        <v>1.01</v>
       </c>
       <c r="BC59">
-        <v>46</v>
+        <v>1.01</v>
       </c>
       <c r="BD59">
-        <v>48</v>
+        <v>1.01</v>
       </c>
       <c r="BE59">
-        <v>80</v>
+        <v>1.01</v>
       </c>
       <c r="BF59">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BG59">
         <v>10.5</v>
@@ -15687,58 +15687,58 @@
         <v>3</v>
       </c>
       <c r="BJ60">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BK60">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BL60">
         <v>1000</v>
       </c>
       <c r="BM60">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BN60">
-        <v>9.4</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BO60">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BP60">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BQ60">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BR60">
         <v>1000</v>
       </c>
       <c r="BS60">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BT60">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="BU60">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="BV60">
         <v>12</v>
       </c>
       <c r="BW60">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BX60">
         <v>29</v>
       </c>
       <c r="BY60">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BZ60">
         <v>23</v>
       </c>
       <c r="CA60">
-        <v>1.01</v>
+        <v>7</v>
       </c>
       <c r="CB60" t="s">
         <v>291</v>
@@ -15932,31 +15932,31 @@
         <v>11.5</v>
       </c>
       <c r="BK61">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BL61">
         <v>180</v>
       </c>
       <c r="BM61">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN61">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BO61">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BP61">
         <v>65</v>
       </c>
       <c r="BQ61">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BR61">
         <v>70</v>
       </c>
       <c r="BS61">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BT61">
         <v>4</v>
@@ -15974,13 +15974,13 @@
         <v>27</v>
       </c>
       <c r="BY61">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="BZ61">
         <v>18.5</v>
       </c>
       <c r="CA61">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="CB61" t="s">
         <v>291</v>
@@ -16018,7 +16018,7 @@
         <v>4.5</v>
       </c>
       <c r="K62">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="L62">
         <v>1.01</v>
@@ -16036,16 +16036,16 @@
         <v>3.8</v>
       </c>
       <c r="Q62">
-        <v>1.29</v>
+        <v>1.19</v>
       </c>
       <c r="R62">
-        <v>2.14</v>
+        <v>2.2</v>
       </c>
       <c r="S62">
-        <v>1.72</v>
+        <v>1.64</v>
       </c>
       <c r="T62">
-        <v>1.35</v>
+        <v>1.34</v>
       </c>
       <c r="U62">
         <v>3.05</v>
@@ -16245,13 +16245,13 @@
         <v>279</v>
       </c>
       <c r="F63">
-        <v>1.79</v>
+        <v>1.77</v>
       </c>
       <c r="G63">
         <v>1.82</v>
       </c>
       <c r="H63">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I63">
         <v>5.5</v>
@@ -16269,22 +16269,22 @@
         <v>1.06</v>
       </c>
       <c r="N63">
-        <v>2.6</v>
+        <v>1.01</v>
       </c>
       <c r="O63">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P63">
         <v>1.74</v>
       </c>
       <c r="Q63">
-        <v>1.57</v>
+        <v>1.87</v>
       </c>
       <c r="R63">
-        <v>1.3</v>
+        <v>1.18</v>
       </c>
       <c r="S63">
-        <v>2.8</v>
+        <v>2.32</v>
       </c>
       <c r="T63">
         <v>1.86</v>
@@ -16296,7 +16296,7 @@
         <v>1.22</v>
       </c>
       <c r="W63">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="X63">
         <v>15.5</v>
@@ -16326,7 +16326,7 @@
         <v>11</v>
       </c>
       <c r="AG63">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH63">
         <v>24</v>
@@ -16359,10 +16359,10 @@
         <v>15.5</v>
       </c>
       <c r="AR63">
-        <v>6.4</v>
+        <v>34</v>
       </c>
       <c r="AS63">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="AT63">
         <v>7.6</v>
@@ -16374,7 +16374,7 @@
         <v>18</v>
       </c>
       <c r="AW63">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AX63">
         <v>9.800000000000001</v>
@@ -16386,7 +16386,7 @@
         <v>17.5</v>
       </c>
       <c r="BA63">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="BB63">
         <v>16.5</v>
@@ -16395,16 +16395,16 @@
         <v>17</v>
       </c>
       <c r="BD63">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="BE63">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="BF63">
         <v>9.199999999999999</v>
       </c>
       <c r="BG63">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH63">
         <v>1000</v>
@@ -16487,19 +16487,19 @@
         <v>280</v>
       </c>
       <c r="F64">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="G64">
         <v>1.2</v>
       </c>
       <c r="H64">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="I64">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="J64">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="K64">
         <v>9.4</v>
@@ -16511,10 +16511,10 @@
         <v>1.02</v>
       </c>
       <c r="N64">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="O64">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="P64">
         <v>2.96</v>
@@ -16526,13 +16526,13 @@
         <v>1.79</v>
       </c>
       <c r="S64">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="T64">
-        <v>1.96</v>
+        <v>2.12</v>
       </c>
       <c r="U64">
-        <v>1.76</v>
+        <v>1.72</v>
       </c>
       <c r="V64">
         <v>1.05</v>
@@ -16541,7 +16541,7 @@
         <v>6</v>
       </c>
       <c r="X64">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="Y64">
         <v>75</v>
@@ -16553,7 +16553,7 @@
         <v>1000</v>
       </c>
       <c r="AB64">
-        <v>14.5</v>
+        <v>13</v>
       </c>
       <c r="AC64">
         <v>24</v>
@@ -16562,10 +16562,10 @@
         <v>70</v>
       </c>
       <c r="AE64">
-        <v>290</v>
+        <v>370</v>
       </c>
       <c r="AF64">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="AG64">
         <v>15.5</v>
@@ -16577,7 +16577,7 @@
         <v>200</v>
       </c>
       <c r="AJ64">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AK64">
         <v>15</v>
@@ -16589,22 +16589,22 @@
         <v>200</v>
       </c>
       <c r="AN64">
-        <v>3.45</v>
+        <v>3.35</v>
       </c>
       <c r="AO64">
-        <v>330</v>
+        <v>470</v>
       </c>
       <c r="AP64">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="AQ64">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AR64">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="AS64">
-        <v>5.9</v>
+        <v>7.2</v>
       </c>
       <c r="AT64">
         <v>10</v>
@@ -16613,10 +16613,10 @@
         <v>15.5</v>
       </c>
       <c r="AV64">
-        <v>5.4</v>
+        <v>6.6</v>
       </c>
       <c r="AW64">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="AX64">
         <v>7.6</v>
@@ -16625,10 +16625,10 @@
         <v>10</v>
       </c>
       <c r="AZ64">
-        <v>5.2</v>
+        <v>6.2</v>
       </c>
       <c r="BA64">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BB64">
         <v>8</v>
@@ -16637,16 +16637,16 @@
         <v>11</v>
       </c>
       <c r="BD64">
-        <v>5.3</v>
+        <v>6.2</v>
       </c>
       <c r="BE64">
-        <v>5.7</v>
+        <v>7</v>
       </c>
       <c r="BF64">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="BG64">
-        <v>5.8</v>
+        <v>7.2</v>
       </c>
       <c r="BH64">
         <v>1000</v>
@@ -16729,7 +16729,7 @@
         <v>281</v>
       </c>
       <c r="F65">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="G65">
         <v>1.19</v>
@@ -16738,13 +16738,13 @@
         <v>19.5</v>
       </c>
       <c r="I65">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="J65">
         <v>9.6</v>
       </c>
       <c r="K65">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="L65">
         <v>1.21</v>
@@ -16756,7 +16756,7 @@
         <v>9</v>
       </c>
       <c r="O65">
-        <v>1.11</v>
+        <v>1.12</v>
       </c>
       <c r="P65">
         <v>3.65</v>
@@ -16765,16 +16765,16 @@
         <v>1.35</v>
       </c>
       <c r="R65">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="S65">
         <v>1.89</v>
       </c>
       <c r="T65">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="U65">
-        <v>1.88</v>
+        <v>1.86</v>
       </c>
       <c r="V65">
         <v>1.05</v>
@@ -16810,22 +16810,22 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AG65">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AH65">
         <v>42</v>
       </c>
       <c r="AI65">
-        <v>1000</v>
+        <v>190</v>
       </c>
       <c r="AJ65">
         <v>9.199999999999999</v>
       </c>
       <c r="AK65">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AL65">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM65">
         <v>1000</v>
@@ -16834,31 +16834,31 @@
         <v>2.74</v>
       </c>
       <c r="AO65">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="AP65">
         <v>38</v>
       </c>
       <c r="AQ65">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="AR65">
         <v>48</v>
       </c>
       <c r="AS65">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AT65">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU65">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AV65">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AW65">
-        <v>55</v>
+        <v>24</v>
       </c>
       <c r="AX65">
         <v>9.199999999999999</v>
@@ -16867,13 +16867,13 @@
         <v>12</v>
       </c>
       <c r="AZ65">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="BA65">
         <v>46</v>
       </c>
       <c r="BB65">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BC65">
         <v>12</v>
@@ -16888,10 +16888,10 @@
         <v>2.7</v>
       </c>
       <c r="BG65">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BH65">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BI65">
         <v>1.01</v>
@@ -16909,13 +16909,13 @@
         <v>1.01</v>
       </c>
       <c r="BN65">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BO65">
         <v>1.01</v>
       </c>
       <c r="BP65">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="BQ65">
         <v>1.01</v>
@@ -16977,7 +16977,7 @@
         <v>4.9</v>
       </c>
       <c r="H66">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="I66">
         <v>1.95</v>
@@ -16986,7 +16986,7 @@
         <v>3.85</v>
       </c>
       <c r="K66">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="L66">
         <v>1.01</v>
@@ -17001,13 +17001,13 @@
         <v>1.25</v>
       </c>
       <c r="P66">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q66">
-        <v>1.67</v>
+        <v>1.74</v>
       </c>
       <c r="R66">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="S66">
         <v>2.78</v>
@@ -17461,7 +17461,7 @@
         <v>1.94</v>
       </c>
       <c r="H68">
-        <v>2.1</v>
+        <v>1.08</v>
       </c>
       <c r="I68">
         <v>110</v>
@@ -17479,22 +17479,22 @@
         <v>1.01</v>
       </c>
       <c r="N68">
-        <v>2.76</v>
+        <v>2.46</v>
       </c>
       <c r="O68">
         <v>1.45</v>
       </c>
       <c r="P68">
-        <v>1.25</v>
+        <v>1.52</v>
       </c>
       <c r="Q68">
-        <v>1.87</v>
+        <v>1.45</v>
       </c>
       <c r="R68">
-        <v>1.12</v>
+        <v>1.2</v>
       </c>
       <c r="S68">
-        <v>1.01</v>
+        <v>2.78</v>
       </c>
       <c r="T68">
         <v>1.01</v>
@@ -17697,22 +17697,22 @@
         <v>285</v>
       </c>
       <c r="F69">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="G69">
-        <v>2.78</v>
+        <v>2.7</v>
       </c>
       <c r="H69">
-        <v>3.45</v>
+        <v>3.5</v>
       </c>
       <c r="I69">
-        <v>4</v>
+        <v>3.95</v>
       </c>
       <c r="J69">
-        <v>2.86</v>
+        <v>2.9</v>
       </c>
       <c r="K69">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L69">
         <v>1.6</v>
@@ -17727,7 +17727,7 @@
         <v>1.59</v>
       </c>
       <c r="P69">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="Q69">
         <v>2.8</v>
@@ -17736,19 +17736,19 @@
         <v>1.17</v>
       </c>
       <c r="S69">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="T69">
-        <v>2.04</v>
+        <v>2.16</v>
       </c>
       <c r="U69">
         <v>1.72</v>
       </c>
       <c r="V69">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="W69">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="X69">
         <v>8</v>
@@ -17805,7 +17805,7 @@
         <v>110</v>
       </c>
       <c r="AP69">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AQ69">
         <v>8.4</v>
@@ -17859,25 +17859,25 @@
         <v>5.9</v>
       </c>
       <c r="BH69">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="BI69">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="BJ69">
         <v>13.5</v>
       </c>
       <c r="BK69">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BL69">
-        <v>280</v>
+        <v>260</v>
       </c>
       <c r="BM69">
         <v>21</v>
       </c>
       <c r="BN69">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="BO69">
         <v>4.1</v>
@@ -17889,7 +17889,7 @@
         <v>17.5</v>
       </c>
       <c r="BR69">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="BS69">
         <v>36</v>
@@ -17907,16 +17907,16 @@
         <v>27</v>
       </c>
       <c r="BX69">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BY69">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BZ69">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="CA69">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="CB69" t="s">
         <v>291</v>
@@ -17939,31 +17939,31 @@
         <v>286</v>
       </c>
       <c r="F70">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="G70">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="H70">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="I70">
-        <v>3.9</v>
+        <v>3.7</v>
       </c>
       <c r="J70">
         <v>3.35</v>
       </c>
       <c r="K70">
-        <v>3.95</v>
+        <v>3.75</v>
       </c>
       <c r="L70">
         <v>1.01</v>
       </c>
       <c r="M70">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="N70">
-        <v>2.98</v>
+        <v>3.55</v>
       </c>
       <c r="O70">
         <v>1.28</v>
@@ -17972,13 +17972,13 @@
         <v>1.96</v>
       </c>
       <c r="Q70">
-        <v>1.85</v>
+        <v>1.81</v>
       </c>
       <c r="R70">
         <v>1.31</v>
       </c>
       <c r="S70">
-        <v>2.8</v>
+        <v>2.82</v>
       </c>
       <c r="T70">
         <v>1.01</v>
@@ -17990,7 +17990,7 @@
         <v>1.34</v>
       </c>
       <c r="W70">
-        <v>1.62</v>
+        <v>1.64</v>
       </c>
       <c r="X70">
         <v>1000</v>
@@ -18426,7 +18426,7 @@
         <v>1.45</v>
       </c>
       <c r="G72">
-        <v>1.48</v>
+        <v>1.47</v>
       </c>
       <c r="H72">
         <v>10</v>
@@ -18450,22 +18450,22 @@
         <v>3.25</v>
       </c>
       <c r="O72">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="P72">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="Q72">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="R72">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="S72">
         <v>3.95</v>
       </c>
       <c r="T72">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="U72">
         <v>1.6</v>
@@ -18474,7 +18474,7 @@
         <v>1.09</v>
       </c>
       <c r="W72">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="X72">
         <v>12.5</v>
@@ -18501,7 +18501,7 @@
         <v>330</v>
       </c>
       <c r="AF72">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="AG72">
         <v>11.5</v>
@@ -18513,7 +18513,7 @@
         <v>270</v>
       </c>
       <c r="AJ72">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AK72">
         <v>23</v>
@@ -18525,7 +18525,7 @@
         <v>350</v>
       </c>
       <c r="AN72">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO72">
         <v>1000</v>
@@ -18534,13 +18534,13 @@
         <v>10.5</v>
       </c>
       <c r="AQ72">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="AR72">
-        <v>9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS72">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="AT72">
         <v>5.8</v>
@@ -18549,10 +18549,10 @@
         <v>9.199999999999999</v>
       </c>
       <c r="AV72">
-        <v>8.199999999999999</v>
+        <v>36</v>
       </c>
       <c r="AW72">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="AX72">
         <v>6.4</v>
@@ -18561,10 +18561,10 @@
         <v>10</v>
       </c>
       <c r="AZ72">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BA72">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BB72">
         <v>10</v>
@@ -18573,16 +18573,16 @@
         <v>16.5</v>
       </c>
       <c r="BD72">
-        <v>8.6</v>
+        <v>9.4</v>
       </c>
       <c r="BE72">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BF72">
         <v>6.6</v>
       </c>
       <c r="BG72">
-        <v>9.6</v>
+        <v>10.5</v>
       </c>
       <c r="BH72">
         <v>1000</v>
@@ -18665,16 +18665,16 @@
         <v>289</v>
       </c>
       <c r="F73">
-        <v>2.18</v>
+        <v>2.22</v>
       </c>
       <c r="G73">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H73">
-        <v>3.85</v>
+        <v>3.75</v>
       </c>
       <c r="I73">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J73">
         <v>3.25</v>
@@ -18686,16 +18686,16 @@
         <v>1.5</v>
       </c>
       <c r="M73">
-        <v>1.11</v>
+        <v>1.1</v>
       </c>
       <c r="N73">
-        <v>2.9</v>
+        <v>2.88</v>
       </c>
       <c r="O73">
         <v>1.46</v>
       </c>
       <c r="P73">
-        <v>1.66</v>
+        <v>1.65</v>
       </c>
       <c r="Q73">
         <v>2.36</v>
@@ -18713,10 +18713,10 @@
         <v>1.88</v>
       </c>
       <c r="V73">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="W73">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="X73">
         <v>10.5</v>
@@ -18725,28 +18725,28 @@
         <v>11.5</v>
       </c>
       <c r="Z73">
-        <v>28</v>
+        <v>32</v>
       </c>
       <c r="AA73">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="AB73">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AC73">
         <v>7.6</v>
       </c>
       <c r="AD73">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AE73">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AF73">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="AG73">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="AH73">
         <v>22</v>
@@ -18755,10 +18755,10 @@
         <v>85</v>
       </c>
       <c r="AJ73">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="AK73">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AL73">
         <v>60</v>
@@ -18767,22 +18767,22 @@
         <v>160</v>
       </c>
       <c r="AN73">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AO73">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="AP73">
         <v>9</v>
       </c>
       <c r="AQ73">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AR73">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AS73">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="AT73">
         <v>6.8</v>
@@ -18791,7 +18791,7 @@
         <v>6.8</v>
       </c>
       <c r="AV73">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AW73">
         <v>42</v>
@@ -18806,7 +18806,7 @@
         <v>18.5</v>
       </c>
       <c r="BA73">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="BB73">
         <v>22</v>
@@ -18818,16 +18818,16 @@
         <v>36</v>
       </c>
       <c r="BE73">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BF73">
         <v>20</v>
       </c>
       <c r="BG73">
-        <v>11.5</v>
+        <v>9.6</v>
       </c>
       <c r="BH73">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="BI73">
         <v>2.52</v>
@@ -18848,10 +18848,10 @@
         <v>5.4</v>
       </c>
       <c r="BO73">
-        <v>3.85</v>
+        <v>4</v>
       </c>
       <c r="BP73">
-        <v>17.5</v>
+        <v>18</v>
       </c>
       <c r="BQ73">
         <v>1.01</v>
@@ -18863,13 +18863,13 @@
         <v>1.01</v>
       </c>
       <c r="BT73">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="BU73">
         <v>5.5</v>
       </c>
       <c r="BV73">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BW73">
         <v>1.01</v>
@@ -18913,13 +18913,13 @@
         <v>970</v>
       </c>
       <c r="H74">
-        <v>1.37</v>
+        <v>1.38</v>
       </c>
       <c r="I74">
         <v>110</v>
       </c>
       <c r="J74">
-        <v>1.39</v>
+        <v>3.4</v>
       </c>
       <c r="K74">
         <v>290</v>
@@ -18931,7 +18931,7 @@
         <v>1.01</v>
       </c>
       <c r="N74">
-        <v>3.7</v>
+        <v>1.25</v>
       </c>
       <c r="O74">
         <v>1.27</v>
@@ -18943,7 +18943,7 @@
         <v>1.27</v>
       </c>
       <c r="R74">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="S74">
         <v>1.29</v>
@@ -18955,10 +18955,10 @@
         <v>1.01</v>
       </c>
       <c r="V74">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W74">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="X74">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-31.xlsx
@@ -889,7 +889,7 @@
     <t>Academia Anzoategui FC</t>
   </si>
   <si>
-    <t>2026-08-30 03:42:37</t>
+    <t>2026-08-30 06:03:59</t>
   </si>
 </sst>
 </file>
@@ -1483,16 +1483,16 @@
         <v>218</v>
       </c>
       <c r="F2">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="G2">
-        <v>1.63</v>
+        <v>1.6</v>
       </c>
       <c r="H2">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="I2">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="J2">
         <v>4.4</v>
@@ -1501,7 +1501,7 @@
         <v>4.7</v>
       </c>
       <c r="L2">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="M2">
         <v>1.05</v>
@@ -1513,10 +1513,10 @@
         <v>1.25</v>
       </c>
       <c r="P2">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="Q2">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="R2">
         <v>1.47</v>
@@ -1525,16 +1525,16 @@
         <v>2.96</v>
       </c>
       <c r="T2">
-        <v>1.82</v>
+        <v>1.85</v>
       </c>
       <c r="U2">
         <v>2.06</v>
       </c>
       <c r="V2">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="W2">
-        <v>2.58</v>
+        <v>2.66</v>
       </c>
       <c r="X2">
         <v>23</v>
@@ -1543,7 +1543,7 @@
         <v>24</v>
       </c>
       <c r="Z2">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AA2">
         <v>1000</v>
@@ -1552,7 +1552,7 @@
         <v>11.5</v>
       </c>
       <c r="AC2">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AD2">
         <v>25</v>
@@ -1561,10 +1561,10 @@
         <v>1000</v>
       </c>
       <c r="AF2">
+        <v>12</v>
+      </c>
+      <c r="AG2">
         <v>12.5</v>
-      </c>
-      <c r="AG2">
-        <v>10.5</v>
       </c>
       <c r="AH2">
         <v>26</v>
@@ -1573,7 +1573,7 @@
         <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="AK2">
         <v>16.5</v>
@@ -1585,7 +1585,7 @@
         <v>1000</v>
       </c>
       <c r="AN2">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AO2">
         <v>1000</v>
@@ -1597,7 +1597,7 @@
         <v>19.5</v>
       </c>
       <c r="AR2">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AS2">
         <v>1.01</v>
@@ -1633,7 +1633,7 @@
         <v>12</v>
       </c>
       <c r="BD2">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BE2">
         <v>40</v>
@@ -1725,7 +1725,7 @@
         <v>219</v>
       </c>
       <c r="F3">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="G3">
         <v>1.35</v>
@@ -1746,28 +1746,28 @@
         <v>1.24</v>
       </c>
       <c r="M3">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N3">
-        <v>7.2</v>
+        <v>7</v>
       </c>
       <c r="O3">
-        <v>1.14</v>
+        <v>1.16</v>
       </c>
       <c r="P3">
-        <v>3.1</v>
+        <v>3</v>
       </c>
       <c r="Q3">
-        <v>1.45</v>
+        <v>1.46</v>
       </c>
       <c r="R3">
-        <v>1.84</v>
+        <v>1.82</v>
       </c>
       <c r="S3">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="T3">
-        <v>1.78</v>
+        <v>1.82</v>
       </c>
       <c r="U3">
         <v>2.14</v>
@@ -1779,37 +1779,37 @@
         <v>3.85</v>
       </c>
       <c r="X3">
-        <v>42</v>
+        <v>36</v>
       </c>
       <c r="Y3">
-        <v>50</v>
+        <v>44</v>
       </c>
       <c r="Z3">
         <v>110</v>
       </c>
       <c r="AA3">
-        <v>350</v>
+        <v>330</v>
       </c>
       <c r="AB3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AC3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AD3">
         <v>38</v>
       </c>
       <c r="AE3">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="AF3">
         <v>11</v>
       </c>
       <c r="AG3">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AH3">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AI3">
         <v>110</v>
@@ -1827,46 +1827,46 @@
         <v>120</v>
       </c>
       <c r="AN3">
-        <v>4</v>
+        <v>4.3</v>
       </c>
       <c r="AO3">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="AP3">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AQ3">
-        <v>36</v>
+        <v>8</v>
       </c>
       <c r="AR3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AS3">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AT3">
         <v>11</v>
       </c>
       <c r="AU3">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AV3">
         <v>30</v>
       </c>
       <c r="AW3">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AX3">
         <v>9.4</v>
       </c>
       <c r="AY3">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AZ3">
         <v>21</v>
       </c>
       <c r="BA3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BB3">
         <v>9.800000000000001</v>
@@ -1875,16 +1875,16 @@
         <v>11.5</v>
       </c>
       <c r="BD3">
-        <v>7.4</v>
+        <v>24</v>
       </c>
       <c r="BE3">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BF3">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="BG3">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1967,22 +1967,22 @@
         <v>220</v>
       </c>
       <c r="F4">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="G4">
-        <v>2.32</v>
+        <v>2.4</v>
       </c>
       <c r="H4">
         <v>3.25</v>
       </c>
       <c r="I4">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="J4">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="K4">
-        <v>3.95</v>
+        <v>3.85</v>
       </c>
       <c r="L4">
         <v>1.35</v>
@@ -1994,13 +1994,13 @@
         <v>4.3</v>
       </c>
       <c r="O4">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P4">
         <v>2.12</v>
       </c>
       <c r="Q4">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R4">
         <v>1.44</v>
@@ -2009,16 +2009,16 @@
         <v>3</v>
       </c>
       <c r="T4">
-        <v>1.01</v>
+        <v>1.57</v>
       </c>
       <c r="U4">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="V4">
-        <v>1.39</v>
+        <v>1.4</v>
       </c>
       <c r="W4">
-        <v>1.75</v>
+        <v>1.71</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -2209,22 +2209,22 @@
         <v>221</v>
       </c>
       <c r="F5">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="G5">
-        <v>2.38</v>
+        <v>2.42</v>
       </c>
       <c r="H5">
-        <v>3.75</v>
+        <v>3.65</v>
       </c>
       <c r="I5">
-        <v>3.95</v>
+        <v>3.8</v>
       </c>
       <c r="J5">
         <v>3.15</v>
       </c>
       <c r="K5">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="L5">
         <v>1.58</v>
@@ -2239,13 +2239,13 @@
         <v>1.53</v>
       </c>
       <c r="P5">
-        <v>1.58</v>
+        <v>1.57</v>
       </c>
       <c r="Q5">
-        <v>2.64</v>
+        <v>2.66</v>
       </c>
       <c r="R5">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="S5">
         <v>5.5</v>
@@ -2257,10 +2257,10 @@
         <v>1.81</v>
       </c>
       <c r="V5">
-        <v>1.33</v>
+        <v>1.35</v>
       </c>
       <c r="W5">
-        <v>1.72</v>
+        <v>1.7</v>
       </c>
       <c r="X5">
         <v>10.5</v>
@@ -2281,10 +2281,10 @@
         <v>7.8</v>
       </c>
       <c r="AD5">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AE5">
-        <v>80</v>
+        <v>75</v>
       </c>
       <c r="AF5">
         <v>16</v>
@@ -2299,28 +2299,28 @@
         <v>110</v>
       </c>
       <c r="AJ5">
+        <v>40</v>
+      </c>
+      <c r="AK5">
         <v>36</v>
-      </c>
-      <c r="AK5">
-        <v>34</v>
       </c>
       <c r="AL5">
         <v>75</v>
       </c>
       <c r="AM5">
-        <v>610</v>
+        <v>520</v>
       </c>
       <c r="AN5">
         <v>36</v>
       </c>
       <c r="AO5">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP5">
         <v>6.8</v>
       </c>
       <c r="AQ5">
-        <v>9.6</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR5">
         <v>19</v>
@@ -2365,13 +2365,13 @@
         <v>6.4</v>
       </c>
       <c r="BF5">
-        <v>21</v>
+        <v>5.8</v>
       </c>
       <c r="BG5">
         <v>6</v>
       </c>
       <c r="BH5">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="BI5">
         <v>2.24</v>
@@ -2383,7 +2383,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BL5">
-        <v>910</v>
+        <v>820</v>
       </c>
       <c r="BM5">
         <v>21</v>
@@ -2407,19 +2407,19 @@
         <v>30</v>
       </c>
       <c r="BT5">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BU5">
         <v>6</v>
       </c>
       <c r="BV5">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="BW5">
         <v>27</v>
       </c>
       <c r="BX5">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="BY5">
         <v>42</v>
@@ -2493,10 +2493,10 @@
         <v>5.1</v>
       </c>
       <c r="T6">
-        <v>2.08</v>
+        <v>1.9</v>
       </c>
       <c r="U6">
-        <v>1.68</v>
+        <v>1.8</v>
       </c>
       <c r="V6">
         <v>1.27</v>
@@ -2508,7 +2508,7 @@
         <v>11.5</v>
       </c>
       <c r="Y6">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="Z6">
         <v>40</v>
@@ -2517,7 +2517,7 @@
         <v>140</v>
       </c>
       <c r="AB6">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="AC6">
         <v>7.6</v>
@@ -2529,7 +2529,7 @@
         <v>100</v>
       </c>
       <c r="AF6">
-        <v>14.5</v>
+        <v>12.5</v>
       </c>
       <c r="AG6">
         <v>13</v>
@@ -2568,7 +2568,7 @@
         <v>27</v>
       </c>
       <c r="AS6">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="AT6">
         <v>6.2</v>
@@ -2577,13 +2577,13 @@
         <v>6.6</v>
       </c>
       <c r="AV6">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="AW6">
-        <v>5</v>
+        <v>6.4</v>
       </c>
       <c r="AX6">
-        <v>8.6</v>
+        <v>10</v>
       </c>
       <c r="AY6">
         <v>9.800000000000001</v>
@@ -2592,7 +2592,7 @@
         <v>19</v>
       </c>
       <c r="BA6">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BB6">
         <v>20</v>
@@ -2601,16 +2601,16 @@
         <v>20</v>
       </c>
       <c r="BD6">
-        <v>4.9</v>
+        <v>6.2</v>
       </c>
       <c r="BE6">
-        <v>5.2</v>
+        <v>6.8</v>
       </c>
       <c r="BF6">
         <v>20</v>
       </c>
       <c r="BG6">
-        <v>5.1</v>
+        <v>6.6</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2693,16 +2693,16 @@
         <v>223</v>
       </c>
       <c r="F7">
-        <v>1.59</v>
+        <v>1.57</v>
       </c>
       <c r="G7">
-        <v>1.61</v>
+        <v>1.6</v>
       </c>
       <c r="H7">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="I7">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="J7">
         <v>4.7</v>
@@ -2723,7 +2723,7 @@
         <v>1.2</v>
       </c>
       <c r="P7">
-        <v>2.58</v>
+        <v>2.6</v>
       </c>
       <c r="Q7">
         <v>1.59</v>
@@ -2735,16 +2735,16 @@
         <v>2.5</v>
       </c>
       <c r="T7">
-        <v>1.7</v>
+        <v>1.72</v>
       </c>
       <c r="U7">
         <v>2.32</v>
       </c>
       <c r="V7">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="W7">
-        <v>2.62</v>
+        <v>2.66</v>
       </c>
       <c r="X7">
         <v>25</v>
@@ -2756,19 +2756,19 @@
         <v>55</v>
       </c>
       <c r="AA7">
-        <v>150</v>
+        <v>160</v>
       </c>
       <c r="AB7">
         <v>12</v>
       </c>
       <c r="AC7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD7">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AE7">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AF7">
         <v>11.5</v>
@@ -2792,10 +2792,10 @@
         <v>28</v>
       </c>
       <c r="AM7">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="AN7">
-        <v>6.8</v>
+        <v>6.4</v>
       </c>
       <c r="AO7">
         <v>60</v>
@@ -2810,7 +2810,7 @@
         <v>44</v>
       </c>
       <c r="AS7">
-        <v>13</v>
+        <v>14.5</v>
       </c>
       <c r="AT7">
         <v>10.5</v>
@@ -2846,10 +2846,10 @@
         <v>24</v>
       </c>
       <c r="BE7">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BF7">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="BG7">
         <v>46</v>
@@ -2935,13 +2935,13 @@
         <v>224</v>
       </c>
       <c r="F8">
-        <v>1.73</v>
+        <v>1.75</v>
       </c>
       <c r="G8">
         <v>110</v>
       </c>
       <c r="H8">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="I8">
         <v>2.5</v>
@@ -2983,10 +2983,10 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="W8">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -3180,13 +3180,13 @@
         <v>1.08</v>
       </c>
       <c r="G9">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="H9">
         <v>1.08</v>
       </c>
       <c r="I9">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="J9">
         <v>1.1</v>
@@ -3225,10 +3225,10 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W9">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3419,19 +3419,19 @@
         <v>226</v>
       </c>
       <c r="F10">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="G10">
         <v>110</v>
       </c>
       <c r="H10">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="I10">
-        <v>1.8</v>
+        <v>1.74</v>
       </c>
       <c r="J10">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="K10">
         <v>410</v>
@@ -3467,10 +3467,10 @@
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>1.02</v>
+        <v>2.34</v>
       </c>
       <c r="W10">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3661,22 +3661,22 @@
         <v>227</v>
       </c>
       <c r="F11">
-        <v>1.08</v>
+        <v>3.15</v>
       </c>
       <c r="G11">
-        <v>1000</v>
+        <v>3.95</v>
       </c>
       <c r="H11">
-        <v>1.08</v>
+        <v>2.18</v>
       </c>
       <c r="I11">
-        <v>110</v>
+        <v>2.2</v>
       </c>
       <c r="J11">
-        <v>1.08</v>
+        <v>3.5</v>
       </c>
       <c r="K11">
-        <v>230</v>
+        <v>4.6</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3685,22 +3685,22 @@
         <v>1.01</v>
       </c>
       <c r="N11">
-        <v>4.1</v>
+        <v>1.01</v>
       </c>
       <c r="O11">
         <v>1.24</v>
       </c>
       <c r="P11">
-        <v>1.18</v>
+        <v>1.64</v>
       </c>
       <c r="Q11">
-        <v>1.25</v>
+        <v>1.31</v>
       </c>
       <c r="R11">
         <v>1.18</v>
       </c>
       <c r="S11">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="T11">
         <v>1.01</v>
@@ -3709,10 +3709,10 @@
         <v>1.01</v>
       </c>
       <c r="V11">
-        <v>1.06</v>
+        <v>1.83</v>
       </c>
       <c r="W11">
-        <v>1.02</v>
+        <v>1.37</v>
       </c>
       <c r="X11">
         <v>1000</v>
@@ -3909,13 +3909,13 @@
         <v>1.77</v>
       </c>
       <c r="H12">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="I12">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J12">
-        <v>4.4</v>
+        <v>4</v>
       </c>
       <c r="K12">
         <v>6.6</v>
@@ -3924,7 +3924,7 @@
         <v>1.01</v>
       </c>
       <c r="M12">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N12">
         <v>2.52</v>
@@ -3954,7 +3954,7 @@
         <v>1.19</v>
       </c>
       <c r="W12">
-        <v>2.3</v>
+        <v>2.28</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -4638,7 +4638,7 @@
         <v>2.66</v>
       </c>
       <c r="I15">
-        <v>3.6</v>
+        <v>3.85</v>
       </c>
       <c r="J15">
         <v>3.2</v>
@@ -4677,7 +4677,7 @@
         <v>1.01</v>
       </c>
       <c r="V15">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="W15">
         <v>1.64</v>
@@ -4874,7 +4874,7 @@
         <v>1.98</v>
       </c>
       <c r="G16">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="H16">
         <v>3.75</v>
@@ -4886,7 +4886,7 @@
         <v>3.8</v>
       </c>
       <c r="K16">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="L16">
         <v>1.01</v>
@@ -4922,7 +4922,7 @@
         <v>1.32</v>
       </c>
       <c r="W16">
-        <v>1.92</v>
+        <v>1.9</v>
       </c>
       <c r="X16">
         <v>17.5</v>
@@ -5116,13 +5116,13 @@
         <v>1.08</v>
       </c>
       <c r="G17">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="H17">
         <v>1.08</v>
       </c>
       <c r="I17">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="J17">
         <v>1.1</v>
@@ -5137,7 +5137,7 @@
         <v>1.01</v>
       </c>
       <c r="N17">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="O17">
         <v>1.01</v>
@@ -5161,10 +5161,10 @@
         <v>1.01</v>
       </c>
       <c r="V17">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W17">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -5618,7 +5618,7 @@
         <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N19">
         <v>1.01</v>
@@ -5842,7 +5842,7 @@
         <v>2.3</v>
       </c>
       <c r="G20">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="H20">
         <v>2.8</v>
@@ -5890,7 +5890,7 @@
         <v>1.47</v>
       </c>
       <c r="W20">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="X20">
         <v>1000</v>
@@ -6081,16 +6081,16 @@
         <v>237</v>
       </c>
       <c r="F21">
-        <v>3.25</v>
+        <v>3.4</v>
       </c>
       <c r="G21">
-        <v>3.7</v>
+        <v>3.75</v>
       </c>
       <c r="H21">
         <v>2.16</v>
       </c>
       <c r="I21">
-        <v>2.4</v>
+        <v>2.26</v>
       </c>
       <c r="J21">
         <v>3.5</v>
@@ -6120,7 +6120,7 @@
         <v>1.39</v>
       </c>
       <c r="S21">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="T21">
         <v>1.68</v>
@@ -6129,7 +6129,7 @@
         <v>2.2</v>
       </c>
       <c r="V21">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="W21">
         <v>1.37</v>
@@ -6144,7 +6144,7 @@
         <v>18.5</v>
       </c>
       <c r="AA21">
-        <v>32</v>
+        <v>38</v>
       </c>
       <c r="AB21">
         <v>17.5</v>
@@ -6156,7 +6156,7 @@
         <v>13.5</v>
       </c>
       <c r="AE21">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AF21">
         <v>34</v>
@@ -6183,7 +6183,7 @@
         <v>100</v>
       </c>
       <c r="AN21">
-        <v>34</v>
+        <v>38</v>
       </c>
       <c r="AO21">
         <v>19.5</v>
@@ -6344,19 +6344,19 @@
         <v>1.01</v>
       </c>
       <c r="M22">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N22">
         <v>5.7</v>
       </c>
       <c r="O22">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="P22">
-        <v>2.62</v>
+        <v>2.6</v>
       </c>
       <c r="Q22">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="R22">
         <v>1.65</v>
@@ -6377,10 +6377,10 @@
         <v>1.25</v>
       </c>
       <c r="X22">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="Y22">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="Z22">
         <v>16.5</v>
@@ -6389,10 +6389,10 @@
         <v>20</v>
       </c>
       <c r="AB22">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AC22">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="AD22">
         <v>13</v>
@@ -6401,7 +6401,7 @@
         <v>17</v>
       </c>
       <c r="AF22">
-        <v>50</v>
+        <v>42</v>
       </c>
       <c r="AG22">
         <v>20</v>
@@ -6428,61 +6428,61 @@
         <v>42</v>
       </c>
       <c r="AO22">
-        <v>7.2</v>
+        <v>8.4</v>
       </c>
       <c r="AP22">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="AQ22">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR22">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AS22">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AT22">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AU22">
+        <v>9.4</v>
+      </c>
+      <c r="AV22">
+        <v>9</v>
+      </c>
+      <c r="AW22">
+        <v>11.5</v>
+      </c>
+      <c r="AX22">
         <v>1.02</v>
       </c>
-      <c r="AV22">
+      <c r="AY22">
+        <v>14</v>
+      </c>
+      <c r="AZ22">
+        <v>12</v>
+      </c>
+      <c r="BA22">
+        <v>18.5</v>
+      </c>
+      <c r="BB22">
         <v>1.02</v>
       </c>
-      <c r="AW22">
-        <v>1.01</v>
-      </c>
-      <c r="AX22">
-        <v>1.01</v>
-      </c>
-      <c r="AY22">
-        <v>1.01</v>
-      </c>
-      <c r="AZ22">
-        <v>1.01</v>
-      </c>
-      <c r="BA22">
-        <v>1.01</v>
-      </c>
-      <c r="BB22">
-        <v>1.01</v>
-      </c>
       <c r="BC22">
         <v>1.01</v>
       </c>
       <c r="BD22">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BE22">
         <v>1.01</v>
       </c>
       <c r="BF22">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="BG22">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="BH22">
         <v>5.5</v>
@@ -6500,7 +6500,7 @@
         <v>90</v>
       </c>
       <c r="BM22">
-        <v>50</v>
+        <v>1.01</v>
       </c>
       <c r="BN22">
         <v>10.5</v>
@@ -6539,10 +6539,10 @@
         <v>1.01</v>
       </c>
       <c r="BZ22">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="CA22">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="CB22" t="s">
         <v>291</v>
@@ -6571,13 +6571,13 @@
         <v>110</v>
       </c>
       <c r="H23">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="I23">
         <v>110</v>
       </c>
       <c r="J23">
-        <v>1.13</v>
+        <v>1.17</v>
       </c>
       <c r="K23">
         <v>5.9</v>
@@ -6586,7 +6586,7 @@
         <v>1.01</v>
       </c>
       <c r="M23">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N23">
         <v>5.3</v>
@@ -6613,10 +6613,10 @@
         <v>1.01</v>
       </c>
       <c r="V23">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W23">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X23">
         <v>1000</v>
@@ -6810,13 +6810,13 @@
         <v>1.08</v>
       </c>
       <c r="G24">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="H24">
         <v>1.08</v>
       </c>
       <c r="I24">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="J24">
         <v>1.1</v>
@@ -6855,10 +6855,10 @@
         <v>1.01</v>
       </c>
       <c r="V24">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W24">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -7052,7 +7052,7 @@
         <v>1.08</v>
       </c>
       <c r="G25">
-        <v>110</v>
+        <v>970</v>
       </c>
       <c r="H25">
         <v>1.4</v>
@@ -7097,10 +7097,10 @@
         <v>1.01</v>
       </c>
       <c r="V25">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W25">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X25">
         <v>1000</v>
@@ -7300,7 +7300,7 @@
         <v>3.2</v>
       </c>
       <c r="I26">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="J26">
         <v>3.05</v>
@@ -7315,19 +7315,19 @@
         <v>1.07</v>
       </c>
       <c r="N26">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O26">
         <v>1.33</v>
       </c>
       <c r="P26">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q26">
         <v>1.86</v>
       </c>
       <c r="R26">
-        <v>1.31</v>
+        <v>1.29</v>
       </c>
       <c r="S26">
         <v>3.3</v>
@@ -7336,7 +7336,7 @@
         <v>1.76</v>
       </c>
       <c r="U26">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="V26">
         <v>1.32</v>
@@ -7360,7 +7360,7 @@
         <v>11.5</v>
       </c>
       <c r="AC26">
-        <v>9.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD26">
         <v>17</v>
@@ -7375,7 +7375,7 @@
         <v>13</v>
       </c>
       <c r="AH26">
-        <v>18.5</v>
+        <v>21</v>
       </c>
       <c r="AI26">
         <v>60</v>
@@ -7539,7 +7539,7 @@
         <v>4.1</v>
       </c>
       <c r="H27">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="I27">
         <v>1.93</v>
@@ -7548,7 +7548,7 @@
         <v>4.2</v>
       </c>
       <c r="K27">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L27">
         <v>1.01</v>
@@ -7563,31 +7563,31 @@
         <v>1.2</v>
       </c>
       <c r="P27">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="Q27">
-        <v>1.6</v>
+        <v>1.58</v>
       </c>
       <c r="R27">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="S27">
-        <v>2.48</v>
+        <v>2.44</v>
       </c>
       <c r="T27">
         <v>1.59</v>
       </c>
       <c r="U27">
-        <v>2.56</v>
+        <v>2.6</v>
       </c>
       <c r="V27">
         <v>2.06</v>
       </c>
       <c r="W27">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="X27">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="Y27">
         <v>13.5</v>
@@ -7611,7 +7611,7 @@
         <v>17.5</v>
       </c>
       <c r="AF27">
-        <v>42</v>
+        <v>34</v>
       </c>
       <c r="AG27">
         <v>17</v>
@@ -7656,7 +7656,7 @@
         <v>18</v>
       </c>
       <c r="AU27">
-        <v>9</v>
+        <v>9.4</v>
       </c>
       <c r="AV27">
         <v>9.6</v>
@@ -7665,7 +7665,7 @@
         <v>15.5</v>
       </c>
       <c r="AX27">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY27">
         <v>14.5</v>
@@ -7692,7 +7692,7 @@
         <v>22</v>
       </c>
       <c r="BG27">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7775,37 +7775,37 @@
         <v>244</v>
       </c>
       <c r="F28">
+        <v>2.26</v>
+      </c>
+      <c r="G28">
         <v>2.3</v>
       </c>
-      <c r="G28">
-        <v>2.5</v>
-      </c>
       <c r="H28">
-        <v>2.94</v>
+        <v>3.1</v>
       </c>
       <c r="I28">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="J28">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="K28">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="L28">
         <v>1.01</v>
       </c>
       <c r="M28">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N28">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O28">
         <v>1.25</v>
       </c>
       <c r="P28">
-        <v>2.12</v>
+        <v>2.18</v>
       </c>
       <c r="Q28">
         <v>1.74</v>
@@ -7814,7 +7814,7 @@
         <v>1.43</v>
       </c>
       <c r="S28">
-        <v>2.78</v>
+        <v>2.8</v>
       </c>
       <c r="T28">
         <v>1.58</v>
@@ -7826,10 +7826,10 @@
         <v>1.44</v>
       </c>
       <c r="W28">
-        <v>1.67</v>
+        <v>1.76</v>
       </c>
       <c r="X28">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Y28">
         <v>970</v>
@@ -7844,7 +7844,7 @@
         <v>970</v>
       </c>
       <c r="AC28">
-        <v>970</v>
+        <v>12.5</v>
       </c>
       <c r="AD28">
         <v>970</v>
@@ -7853,7 +7853,7 @@
         <v>1000</v>
       </c>
       <c r="AF28">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AG28">
         <v>970</v>
@@ -7868,7 +7868,7 @@
         <v>1000</v>
       </c>
       <c r="AK28">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AL28">
         <v>1000</v>
@@ -7883,58 +7883,58 @@
         <v>1000</v>
       </c>
       <c r="AP28">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AQ28">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AR28">
-        <v>5.1</v>
+        <v>4.9</v>
       </c>
       <c r="AS28">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AT28">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AU28">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AV28">
-        <v>1.27</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AW28">
+        <v>9.6</v>
+      </c>
+      <c r="AX28">
+        <v>1.23</v>
+      </c>
+      <c r="AY28">
+        <v>8</v>
+      </c>
+      <c r="AZ28">
+        <v>1.23</v>
+      </c>
+      <c r="BA28">
+        <v>11</v>
+      </c>
+      <c r="BB28">
         <v>10</v>
       </c>
-      <c r="AX28">
-        <v>1.28</v>
-      </c>
-      <c r="AY28">
-        <v>1.27</v>
-      </c>
-      <c r="AZ28">
-        <v>11</v>
-      </c>
-      <c r="BA28">
-        <v>12</v>
-      </c>
-      <c r="BB28">
-        <v>10.5</v>
-      </c>
       <c r="BC28">
-        <v>6.8</v>
+        <v>5.8</v>
       </c>
       <c r="BD28">
-        <v>11.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BE28">
-        <v>16</v>
+        <v>14.5</v>
       </c>
       <c r="BF28">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BG28">
-        <v>1.3</v>
+        <v>1.25</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -8017,19 +8017,19 @@
         <v>245</v>
       </c>
       <c r="F29">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="G29">
-        <v>2.26</v>
+        <v>2.34</v>
       </c>
       <c r="H29">
         <v>3.35</v>
       </c>
       <c r="I29">
-        <v>3.75</v>
+        <v>3.9</v>
       </c>
       <c r="J29">
-        <v>3.6</v>
+        <v>3.55</v>
       </c>
       <c r="K29">
         <v>3.8</v>
@@ -8059,19 +8059,19 @@
         <v>2.88</v>
       </c>
       <c r="T29">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="U29">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="V29">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="W29">
-        <v>1.79</v>
+        <v>1.75</v>
       </c>
       <c r="X29">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="Y29">
         <v>970</v>
@@ -8086,7 +8086,7 @@
         <v>970</v>
       </c>
       <c r="AC29">
-        <v>10.5</v>
+        <v>970</v>
       </c>
       <c r="AD29">
         <v>970</v>
@@ -8125,52 +8125,52 @@
         <v>1000</v>
       </c>
       <c r="AP29">
-        <v>3.85</v>
+        <v>1.31</v>
       </c>
       <c r="AQ29">
-        <v>4.3</v>
+        <v>1.32</v>
       </c>
       <c r="AR29">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AS29">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT29">
         <v>7.6</v>
       </c>
       <c r="AU29">
-        <v>1.18</v>
+        <v>1.17</v>
       </c>
       <c r="AV29">
-        <v>10</v>
+        <v>1.32</v>
       </c>
       <c r="AW29">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AX29">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="AY29">
-        <v>3.35</v>
+        <v>1.26</v>
       </c>
       <c r="AZ29">
         <v>1.32</v>
       </c>
       <c r="BA29">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BB29">
-        <v>9.800000000000001</v>
+        <v>9.4</v>
       </c>
       <c r="BC29">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="BD29">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="BE29">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BF29">
         <v>1.34</v>
@@ -8262,7 +8262,7 @@
         <v>2.08</v>
       </c>
       <c r="G30">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="H30">
         <v>3.6</v>
@@ -8271,16 +8271,16 @@
         <v>3.8</v>
       </c>
       <c r="J30">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K30">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="L30">
         <v>1.01</v>
       </c>
       <c r="M30">
-        <v>1.02</v>
+        <v>1.05</v>
       </c>
       <c r="N30">
         <v>4</v>
@@ -8292,7 +8292,7 @@
         <v>2.12</v>
       </c>
       <c r="Q30">
-        <v>1.66</v>
+        <v>1.72</v>
       </c>
       <c r="R30">
         <v>1.44</v>
@@ -8310,10 +8310,10 @@
         <v>1.36</v>
       </c>
       <c r="W30">
-        <v>1.86</v>
+        <v>1.84</v>
       </c>
       <c r="X30">
-        <v>80</v>
+        <v>21</v>
       </c>
       <c r="Y30">
         <v>970</v>
@@ -8328,7 +8328,7 @@
         <v>970</v>
       </c>
       <c r="AC30">
-        <v>12.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AD30">
         <v>970</v>
@@ -8367,58 +8367,58 @@
         <v>1000</v>
       </c>
       <c r="AP30">
-        <v>1.24</v>
+        <v>1.27</v>
       </c>
       <c r="AQ30">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AR30">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="AS30">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AT30">
-        <v>1.23</v>
+        <v>1.32</v>
       </c>
       <c r="AU30">
-        <v>1.14</v>
+        <v>1.18</v>
       </c>
       <c r="AV30">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="AW30">
         <v>13</v>
       </c>
       <c r="AX30">
-        <v>1.23</v>
+        <v>1.33</v>
       </c>
       <c r="AY30">
-        <v>8.4</v>
+        <v>1.32</v>
       </c>
       <c r="AZ30">
-        <v>1.24</v>
+        <v>1.33</v>
       </c>
       <c r="BA30">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="BB30">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BC30">
-        <v>1.24</v>
+        <v>1.34</v>
       </c>
       <c r="BD30">
         <v>12</v>
       </c>
       <c r="BE30">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="BF30">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="BG30">
-        <v>1.26</v>
+        <v>1.35</v>
       </c>
       <c r="BH30">
         <v>1000</v>
@@ -8546,7 +8546,7 @@
         <v>1.61</v>
       </c>
       <c r="U31">
-        <v>2.5</v>
+        <v>2.54</v>
       </c>
       <c r="V31">
         <v>1.32</v>
@@ -8603,7 +8603,7 @@
         <v>75</v>
       </c>
       <c r="AN31">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="AO31">
         <v>42</v>
@@ -8642,7 +8642,7 @@
         <v>14</v>
       </c>
       <c r="BA31">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BB31">
         <v>19</v>
@@ -8669,7 +8669,7 @@
         <v>3.35</v>
       </c>
       <c r="BJ31">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="BK31">
         <v>1.01</v>
@@ -8687,7 +8687,7 @@
         <v>3.9</v>
       </c>
       <c r="BP31">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BQ31">
         <v>1.01</v>
@@ -8788,7 +8788,7 @@
         <v>1.8</v>
       </c>
       <c r="U32">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V32">
         <v>1.75</v>
@@ -8833,10 +8833,10 @@
         <v>42</v>
       </c>
       <c r="AJ32">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AK32">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AL32">
         <v>65</v>
@@ -8848,7 +8848,7 @@
         <v>60</v>
       </c>
       <c r="AO32">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AP32">
         <v>9.800000000000001</v>
@@ -9009,13 +9009,13 @@
         <v>1.01</v>
       </c>
       <c r="N33">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="O33">
         <v>1.02</v>
       </c>
       <c r="P33">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="Q33">
         <v>1.38</v>
@@ -9033,10 +9033,10 @@
         <v>1.01</v>
       </c>
       <c r="V33">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W33">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="X33">
         <v>1000</v>
@@ -9227,58 +9227,58 @@
         <v>250</v>
       </c>
       <c r="F34">
-        <v>2.4</v>
+        <v>2.42</v>
       </c>
       <c r="G34">
-        <v>2.58</v>
+        <v>2.56</v>
       </c>
       <c r="H34">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="I34">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="J34">
-        <v>3.35</v>
+        <v>3.4</v>
       </c>
       <c r="K34">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="L34">
         <v>1.32</v>
       </c>
       <c r="M34">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="N34">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="O34">
-        <v>1.31</v>
+        <v>1.32</v>
       </c>
       <c r="P34">
-        <v>1.86</v>
+        <v>1.91</v>
       </c>
       <c r="Q34">
-        <v>1.96</v>
+        <v>1.98</v>
       </c>
       <c r="R34">
-        <v>1.37</v>
+        <v>1.33</v>
       </c>
       <c r="S34">
         <v>3.3</v>
       </c>
       <c r="T34">
-        <v>1.04</v>
+        <v>1.68</v>
       </c>
       <c r="U34">
-        <v>1.05</v>
+        <v>2.18</v>
       </c>
       <c r="V34">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W34">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="X34">
         <v>970</v>
@@ -9296,7 +9296,7 @@
         <v>970</v>
       </c>
       <c r="AC34">
-        <v>34</v>
+        <v>9.6</v>
       </c>
       <c r="AD34">
         <v>970</v>
@@ -9335,37 +9335,37 @@
         <v>1000</v>
       </c>
       <c r="AP34">
-        <v>3.6</v>
+        <v>1.28</v>
       </c>
       <c r="AQ34">
-        <v>4.5</v>
+        <v>10</v>
       </c>
       <c r="AR34">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="AS34">
         <v>16.5</v>
       </c>
       <c r="AT34">
-        <v>3.7</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU34">
-        <v>2.7</v>
+        <v>2.72</v>
       </c>
       <c r="AV34">
-        <v>4.3</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AW34">
         <v>13</v>
       </c>
       <c r="AX34">
-        <v>4.5</v>
+        <v>1.29</v>
       </c>
       <c r="AY34">
-        <v>3.8</v>
+        <v>1.29</v>
       </c>
       <c r="AZ34">
-        <v>5.4</v>
+        <v>13</v>
       </c>
       <c r="BA34">
         <v>16</v>
@@ -9374,7 +9374,7 @@
         <v>12.5</v>
       </c>
       <c r="BC34">
-        <v>11</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BD34">
         <v>15</v>
@@ -9383,10 +9383,10 @@
         <v>12</v>
       </c>
       <c r="BF34">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="BG34">
-        <v>1.19</v>
+        <v>1.32</v>
       </c>
       <c r="BH34">
         <v>1000</v>
@@ -9711,13 +9711,13 @@
         <v>252</v>
       </c>
       <c r="F36">
-        <v>5.6</v>
+        <v>6</v>
       </c>
       <c r="G36">
         <v>6.2</v>
       </c>
       <c r="H36">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="I36">
         <v>1.68</v>
@@ -9738,7 +9738,7 @@
         <v>3.9</v>
       </c>
       <c r="O36">
-        <v>1.29</v>
+        <v>1.27</v>
       </c>
       <c r="P36">
         <v>1.99</v>
@@ -9804,7 +9804,7 @@
         <v>170</v>
       </c>
       <c r="AK36">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="AL36">
         <v>80</v>
@@ -9813,7 +9813,7 @@
         <v>130</v>
       </c>
       <c r="AN36">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AO36">
         <v>11</v>
@@ -9956,13 +9956,13 @@
         <v>8.6</v>
       </c>
       <c r="G37">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="H37">
         <v>1.51</v>
       </c>
       <c r="I37">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="J37">
         <v>4.4</v>
@@ -10001,7 +10001,7 @@
         <v>1.74</v>
       </c>
       <c r="V37">
-        <v>2.92</v>
+        <v>2.9</v>
       </c>
       <c r="W37">
         <v>1.12</v>
@@ -10043,7 +10043,7 @@
         <v>55</v>
       </c>
       <c r="AJ37">
-        <v>380</v>
+        <v>340</v>
       </c>
       <c r="AK37">
         <v>180</v>
@@ -10085,7 +10085,7 @@
         <v>16</v>
       </c>
       <c r="AX37">
-        <v>65</v>
+        <v>38</v>
       </c>
       <c r="AY37">
         <v>30</v>
@@ -10100,7 +10100,7 @@
         <v>19.5</v>
       </c>
       <c r="BC37">
-        <v>18.5</v>
+        <v>44</v>
       </c>
       <c r="BD37">
         <v>44</v>
@@ -10109,7 +10109,7 @@
         <v>19.5</v>
       </c>
       <c r="BF37">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BG37">
         <v>8.4</v>
@@ -10130,7 +10130,7 @@
         <v>1000</v>
       </c>
       <c r="BM37">
-        <v>1.01</v>
+        <v>34</v>
       </c>
       <c r="BN37">
         <v>1000</v>
@@ -10142,13 +10142,13 @@
         <v>1000</v>
       </c>
       <c r="BQ37">
-        <v>1.01</v>
+        <v>19</v>
       </c>
       <c r="BR37">
         <v>1000</v>
       </c>
       <c r="BS37">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BT37">
         <v>970</v>
@@ -10166,13 +10166,13 @@
         <v>1000</v>
       </c>
       <c r="BY37">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="BZ37">
         <v>1000</v>
       </c>
       <c r="CA37">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="CB37" t="s">
         <v>291</v>
@@ -10195,7 +10195,7 @@
         <v>254</v>
       </c>
       <c r="F38">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G38">
         <v>2.04</v>
@@ -10207,10 +10207,10 @@
         <v>3.8</v>
       </c>
       <c r="J38">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K38">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="L38">
         <v>1.01</v>
@@ -10222,10 +10222,10 @@
         <v>5.8</v>
       </c>
       <c r="O38">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P38">
-        <v>2.64</v>
+        <v>2.62</v>
       </c>
       <c r="Q38">
         <v>1.56</v>
@@ -10246,7 +10246,7 @@
         <v>1.36</v>
       </c>
       <c r="W38">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="X38">
         <v>28</v>
@@ -10264,7 +10264,7 @@
         <v>15</v>
       </c>
       <c r="AC38">
-        <v>12.5</v>
+        <v>10.5</v>
       </c>
       <c r="AD38">
         <v>17</v>
@@ -10297,7 +10297,7 @@
         <v>530</v>
       </c>
       <c r="AN38">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AO38">
         <v>26</v>
@@ -10348,7 +10348,7 @@
         <v>17.5</v>
       </c>
       <c r="BE38">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="BF38">
         <v>8.199999999999999</v>
@@ -10452,13 +10452,13 @@
         <v>3.45</v>
       </c>
       <c r="K39">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L39">
         <v>1.34</v>
       </c>
       <c r="M39">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N39">
         <v>3.8</v>
@@ -10602,7 +10602,7 @@
         <v>4</v>
       </c>
       <c r="BI39">
-        <v>3.15</v>
+        <v>2.76</v>
       </c>
       <c r="BJ39">
         <v>11.5</v>
@@ -10930,7 +10930,7 @@
         <v>5.7</v>
       </c>
       <c r="I41">
-        <v>6.6</v>
+        <v>6.2</v>
       </c>
       <c r="J41">
         <v>4.7</v>
@@ -10945,16 +10945,16 @@
         <v>1.02</v>
       </c>
       <c r="N41">
-        <v>5.5</v>
+        <v>5.1</v>
       </c>
       <c r="O41">
-        <v>1.17</v>
+        <v>1.2</v>
       </c>
       <c r="P41">
-        <v>2.5</v>
+        <v>2.56</v>
       </c>
       <c r="Q41">
-        <v>1.55</v>
+        <v>1.51</v>
       </c>
       <c r="R41">
         <v>1.61</v>
@@ -10963,13 +10963,13 @@
         <v>2.38</v>
       </c>
       <c r="T41">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="U41">
-        <v>2.2</v>
+        <v>2.28</v>
       </c>
       <c r="V41">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="W41">
         <v>2.56</v>
@@ -10978,10 +10978,10 @@
         <v>1000</v>
       </c>
       <c r="Y41">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="Z41">
-        <v>220</v>
+        <v>190</v>
       </c>
       <c r="AA41">
         <v>1000</v>
@@ -10993,7 +10993,7 @@
         <v>970</v>
       </c>
       <c r="AD41">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="AE41">
         <v>85</v>
@@ -11005,7 +11005,7 @@
         <v>11</v>
       </c>
       <c r="AH41">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AI41">
         <v>1000</v>
@@ -11029,58 +11029,58 @@
         <v>1000</v>
       </c>
       <c r="AP41">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="AQ41">
-        <v>4.4</v>
+        <v>5.2</v>
       </c>
       <c r="AR41">
-        <v>2.32</v>
+        <v>2.14</v>
       </c>
       <c r="AS41">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="AT41">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AU41">
-        <v>8.6</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AV41">
         <v>18</v>
       </c>
       <c r="AW41">
+        <v>12.5</v>
+      </c>
+      <c r="AX41">
         <v>8.800000000000001</v>
-      </c>
-      <c r="AX41">
-        <v>8.199999999999999</v>
       </c>
       <c r="AY41">
         <v>8.4</v>
       </c>
       <c r="AZ41">
-        <v>13</v>
+        <v>4.6</v>
       </c>
       <c r="BA41">
-        <v>9</v>
+        <v>10.5</v>
       </c>
       <c r="BB41">
-        <v>2.06</v>
+        <v>1.92</v>
       </c>
       <c r="BC41">
-        <v>2.04</v>
+        <v>1.91</v>
       </c>
       <c r="BD41">
-        <v>2.32</v>
+        <v>2.16</v>
       </c>
       <c r="BE41">
-        <v>8.800000000000001</v>
+        <v>12.5</v>
       </c>
       <c r="BF41">
         <v>5.5</v>
       </c>
       <c r="BG41">
-        <v>2.34</v>
+        <v>2.16</v>
       </c>
       <c r="BH41">
         <v>1000</v>
@@ -11163,7 +11163,7 @@
         <v>258</v>
       </c>
       <c r="F42">
-        <v>1.7</v>
+        <v>1.69</v>
       </c>
       <c r="G42">
         <v>1.74</v>
@@ -11196,7 +11196,7 @@
         <v>2.16</v>
       </c>
       <c r="Q42">
-        <v>1.65</v>
+        <v>1.67</v>
       </c>
       <c r="R42">
         <v>1.48</v>
@@ -11205,7 +11205,7 @@
         <v>2.72</v>
       </c>
       <c r="T42">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="U42">
         <v>2.2</v>
@@ -11668,7 +11668,7 @@
         <v>1.36</v>
       </c>
       <c r="M44">
-        <v>1.03</v>
+        <v>1.06</v>
       </c>
       <c r="N44">
         <v>3</v>
@@ -11677,7 +11677,7 @@
         <v>1.35</v>
       </c>
       <c r="P44">
-        <v>1.67</v>
+        <v>1.72</v>
       </c>
       <c r="Q44">
         <v>2.08</v>
@@ -11803,7 +11803,7 @@
         <v>1.01</v>
       </c>
       <c r="BF44">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BG44">
         <v>1.01</v>
@@ -11898,7 +11898,7 @@
         <v>1.98</v>
       </c>
       <c r="I45">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="J45">
         <v>3.1</v>
@@ -11919,10 +11919,10 @@
         <v>1.45</v>
       </c>
       <c r="P45">
-        <v>1.63</v>
+        <v>1.61</v>
       </c>
       <c r="Q45">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="R45">
         <v>1.2</v>
@@ -11937,7 +11937,7 @@
         <v>1.01</v>
       </c>
       <c r="V45">
-        <v>1.84</v>
+        <v>1.86</v>
       </c>
       <c r="W45">
         <v>1.25</v>
@@ -11949,7 +11949,7 @@
         <v>10</v>
       </c>
       <c r="Z45">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AA45">
         <v>38</v>
@@ -12057,7 +12057,7 @@
         <v>1.01</v>
       </c>
       <c r="BJ45">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK45">
         <v>1.01</v>
@@ -12069,43 +12069,43 @@
         <v>1.01</v>
       </c>
       <c r="BN45">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BO45">
-        <v>1.01</v>
+        <v>5</v>
       </c>
       <c r="BP45">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BQ45">
         <v>1.01</v>
       </c>
       <c r="BR45">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BS45">
         <v>1.01</v>
       </c>
       <c r="BT45">
-        <v>1000</v>
+        <v>6</v>
       </c>
       <c r="BU45">
-        <v>1.01</v>
+        <v>3.2</v>
       </c>
       <c r="BV45">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="BW45">
         <v>1.01</v>
       </c>
       <c r="BX45">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="BY45">
         <v>1.01</v>
       </c>
       <c r="BZ45">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="CA45">
         <v>1.01</v>
@@ -12134,7 +12134,7 @@
         <v>1.4</v>
       </c>
       <c r="G46">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="H46">
         <v>7.4</v>
@@ -12146,13 +12146,13 @@
         <v>5.3</v>
       </c>
       <c r="K46">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="L46">
         <v>1.01</v>
       </c>
       <c r="M46">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N46">
         <v>6</v>
@@ -12182,7 +12182,7 @@
         <v>1.12</v>
       </c>
       <c r="W46">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="X46">
         <v>34</v>
@@ -12373,10 +12373,10 @@
         <v>263</v>
       </c>
       <c r="F47">
-        <v>1.77</v>
+        <v>1.78</v>
       </c>
       <c r="G47">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="H47">
         <v>5.6</v>
@@ -12403,7 +12403,7 @@
         <v>1.41</v>
       </c>
       <c r="P47">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q47">
         <v>2.24</v>
@@ -12415,7 +12415,7 @@
         <v>4.2</v>
       </c>
       <c r="T47">
-        <v>2.1</v>
+        <v>2.06</v>
       </c>
       <c r="U47">
         <v>1.85</v>
@@ -12424,13 +12424,13 @@
         <v>1.2</v>
       </c>
       <c r="W47">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="X47">
         <v>12</v>
       </c>
       <c r="Y47">
-        <v>970</v>
+        <v>16.5</v>
       </c>
       <c r="Z47">
         <v>44</v>
@@ -12442,7 +12442,7 @@
         <v>7.4</v>
       </c>
       <c r="AC47">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD47">
         <v>28</v>
@@ -12460,7 +12460,7 @@
         <v>23</v>
       </c>
       <c r="AI47">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ47">
         <v>18.5</v>
@@ -12490,7 +12490,7 @@
         <v>36</v>
       </c>
       <c r="AS47">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AT47">
         <v>6.8</v>
@@ -12502,10 +12502,10 @@
         <v>20</v>
       </c>
       <c r="AW47">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AX47">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AY47">
         <v>9.6</v>
@@ -12514,10 +12514,10 @@
         <v>20</v>
       </c>
       <c r="BA47">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="BB47">
-        <v>16.5</v>
+        <v>17</v>
       </c>
       <c r="BC47">
         <v>19</v>
@@ -12526,13 +12526,13 @@
         <v>40</v>
       </c>
       <c r="BE47">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BF47">
         <v>13</v>
       </c>
       <c r="BG47">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BH47">
         <v>1000</v>
@@ -12627,7 +12627,7 @@
         <v>5.7</v>
       </c>
       <c r="J48">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K48">
         <v>6.2</v>
@@ -12947,7 +12947,7 @@
         <v>46</v>
       </c>
       <c r="AJ49">
-        <v>70</v>
+        <v>48</v>
       </c>
       <c r="AK49">
         <v>34</v>
@@ -13117,7 +13117,7 @@
         <v>3.1</v>
       </c>
       <c r="L50">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="M50">
         <v>1.16</v>
@@ -13195,7 +13195,7 @@
         <v>38</v>
       </c>
       <c r="AL50">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AM50">
         <v>330</v>
@@ -13270,13 +13270,13 @@
         <v>13</v>
       </c>
       <c r="BK50">
-        <v>6.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BL50">
         <v>370</v>
       </c>
       <c r="BM50">
-        <v>13</v>
+        <v>40</v>
       </c>
       <c r="BN50">
         <v>4.7</v>
@@ -13288,16 +13288,16 @@
         <v>22</v>
       </c>
       <c r="BQ50">
-        <v>8.4</v>
+        <v>10.5</v>
       </c>
       <c r="BR50">
         <v>55</v>
       </c>
       <c r="BS50">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BT50">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="BU50">
         <v>6.6</v>
@@ -13306,19 +13306,19 @@
         <v>55</v>
       </c>
       <c r="BW50">
-        <v>11</v>
+        <v>15</v>
       </c>
       <c r="BX50">
         <v>100</v>
       </c>
       <c r="BY50">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="BZ50">
-        <v>80</v>
+        <v>65</v>
       </c>
       <c r="CA50">
-        <v>11.5</v>
+        <v>15.5</v>
       </c>
       <c r="CB50" t="s">
         <v>291</v>
@@ -13362,7 +13362,7 @@
         <v>1.01</v>
       </c>
       <c r="M51">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N51">
         <v>3.05</v>
@@ -13380,7 +13380,7 @@
         <v>1.93</v>
       </c>
       <c r="S51">
-        <v>1.33</v>
+        <v>1.5</v>
       </c>
       <c r="T51">
         <v>1.01</v>
@@ -13604,7 +13604,7 @@
         <v>1.01</v>
       </c>
       <c r="M52">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="N52">
         <v>2.98</v>
@@ -14076,7 +14076,7 @@
         <v>2</v>
       </c>
       <c r="I54">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="J54">
         <v>3.9</v>
@@ -14091,7 +14091,7 @@
         <v>1.02</v>
       </c>
       <c r="N54">
-        <v>2.28</v>
+        <v>5.1</v>
       </c>
       <c r="O54">
         <v>1.15</v>
@@ -14115,10 +14115,10 @@
         <v>2.4</v>
       </c>
       <c r="V54">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="W54">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="X54">
         <v>32</v>
@@ -14318,7 +14318,7 @@
         <v>8</v>
       </c>
       <c r="I55">
-        <v>9.4</v>
+        <v>9</v>
       </c>
       <c r="J55">
         <v>4.9</v>
@@ -14336,31 +14336,31 @@
         <v>4</v>
       </c>
       <c r="O55">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P55">
         <v>2.12</v>
       </c>
       <c r="Q55">
+        <v>1.86</v>
+      </c>
+      <c r="R55">
+        <v>1.41</v>
+      </c>
+      <c r="S55">
+        <v>3.25</v>
+      </c>
+      <c r="T55">
+        <v>2.06</v>
+      </c>
+      <c r="U55">
         <v>1.85</v>
-      </c>
-      <c r="R55">
-        <v>1.4</v>
-      </c>
-      <c r="S55">
-        <v>3.2</v>
-      </c>
-      <c r="T55">
-        <v>1.87</v>
-      </c>
-      <c r="U55">
-        <v>1.84</v>
       </c>
       <c r="V55">
         <v>1.13</v>
       </c>
       <c r="W55">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="X55">
         <v>17.5</v>
@@ -14369,13 +14369,13 @@
         <v>30</v>
       </c>
       <c r="Z55">
-        <v>150</v>
+        <v>75</v>
       </c>
       <c r="AA55">
         <v>340</v>
       </c>
       <c r="AB55">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="AC55">
         <v>11</v>
@@ -14384,7 +14384,7 @@
         <v>32</v>
       </c>
       <c r="AE55">
-        <v>160</v>
+        <v>150</v>
       </c>
       <c r="AF55">
         <v>8.4</v>
@@ -14402,19 +14402,19 @@
         <v>13</v>
       </c>
       <c r="AK55">
-        <v>18.5</v>
+        <v>17.5</v>
       </c>
       <c r="AL55">
         <v>44</v>
       </c>
       <c r="AM55">
+        <v>180</v>
+      </c>
+      <c r="AN55">
+        <v>8</v>
+      </c>
+      <c r="AO55">
         <v>190</v>
-      </c>
-      <c r="AN55">
-        <v>7.8</v>
-      </c>
-      <c r="AO55">
-        <v>200</v>
       </c>
       <c r="AP55">
         <v>15</v>
@@ -14426,7 +14426,7 @@
         <v>60</v>
       </c>
       <c r="AS55">
-        <v>9.6</v>
+        <v>11.5</v>
       </c>
       <c r="AT55">
         <v>7.2</v>
@@ -14435,10 +14435,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AV55">
-        <v>12.5</v>
+        <v>15.5</v>
       </c>
       <c r="AW55">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="AX55">
         <v>7.6</v>
@@ -14450,7 +14450,7 @@
         <v>23</v>
       </c>
       <c r="BA55">
-        <v>9.199999999999999</v>
+        <v>11.5</v>
       </c>
       <c r="BB55">
         <v>11.5</v>
@@ -14459,16 +14459,16 @@
         <v>14.5</v>
       </c>
       <c r="BD55">
-        <v>17</v>
+        <v>20</v>
       </c>
       <c r="BE55">
-        <v>9.4</v>
+        <v>11</v>
       </c>
       <c r="BF55">
         <v>7</v>
       </c>
       <c r="BG55">
-        <v>9.4</v>
+        <v>11.5</v>
       </c>
       <c r="BH55">
         <v>1000</v>
@@ -14551,7 +14551,7 @@
         <v>272</v>
       </c>
       <c r="F56">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="G56">
         <v>3.7</v>
@@ -14560,7 +14560,7 @@
         <v>2.1</v>
       </c>
       <c r="I56">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="J56">
         <v>3.95</v>
@@ -14575,31 +14575,31 @@
         <v>1.05</v>
       </c>
       <c r="N56">
-        <v>4.4</v>
+        <v>3.85</v>
       </c>
       <c r="O56">
         <v>1.25</v>
       </c>
       <c r="P56">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="Q56">
-        <v>1.74</v>
+        <v>1.68</v>
       </c>
       <c r="R56">
-        <v>1.47</v>
+        <v>1.44</v>
       </c>
       <c r="S56">
-        <v>2.84</v>
+        <v>2.72</v>
       </c>
       <c r="T56">
-        <v>1.64</v>
+        <v>1.66</v>
       </c>
       <c r="U56">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="V56">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="W56">
         <v>1.37</v>
@@ -14647,7 +14647,7 @@
         <v>40</v>
       </c>
       <c r="AL56">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="AM56">
         <v>75</v>
@@ -14662,7 +14662,7 @@
         <v>16</v>
       </c>
       <c r="AQ56">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AR56">
         <v>13</v>
@@ -14680,7 +14680,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW56">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AX56">
         <v>24</v>
@@ -14793,64 +14793,64 @@
         <v>273</v>
       </c>
       <c r="F57">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="G57">
-        <v>2.1</v>
+        <v>1.99</v>
       </c>
       <c r="H57">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="I57">
-        <v>5.9</v>
+        <v>5.7</v>
       </c>
       <c r="J57">
-        <v>2.94</v>
+        <v>3.4</v>
       </c>
       <c r="K57">
-        <v>3.65</v>
+        <v>3.8</v>
       </c>
       <c r="L57">
-        <v>1.41</v>
+        <v>1.48</v>
       </c>
       <c r="M57">
         <v>1.09</v>
       </c>
       <c r="N57">
-        <v>2.66</v>
+        <v>2.94</v>
       </c>
       <c r="O57">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P57">
-        <v>1.61</v>
+        <v>1.65</v>
       </c>
       <c r="Q57">
-        <v>2.14</v>
+        <v>2.24</v>
       </c>
       <c r="R57">
         <v>1.24</v>
       </c>
       <c r="S57">
-        <v>3.25</v>
+        <v>4.2</v>
       </c>
       <c r="T57">
-        <v>1.94</v>
+        <v>2</v>
       </c>
       <c r="U57">
-        <v>1.76</v>
+        <v>1.8</v>
       </c>
       <c r="V57">
-        <v>1.2</v>
+        <v>1.21</v>
       </c>
       <c r="W57">
-        <v>1.9</v>
+        <v>2</v>
       </c>
       <c r="X57">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y57">
-        <v>17.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z57">
         <v>46</v>
@@ -14859,10 +14859,10 @@
         <v>170</v>
       </c>
       <c r="AB57">
-        <v>8</v>
+        <v>7.4</v>
       </c>
       <c r="AC57">
-        <v>9.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD57">
         <v>25</v>
@@ -14871,10 +14871,10 @@
         <v>100</v>
       </c>
       <c r="AF57">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="AG57">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AH57">
         <v>28</v>
@@ -14883,7 +14883,7 @@
         <v>120</v>
       </c>
       <c r="AJ57">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK57">
         <v>29</v>
@@ -14895,124 +14895,124 @@
         <v>200</v>
       </c>
       <c r="AN57">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO57">
         <v>150</v>
       </c>
       <c r="AP57">
-        <v>3.35</v>
+        <v>8</v>
       </c>
       <c r="AQ57">
-        <v>3.7</v>
+        <v>10.5</v>
       </c>
       <c r="AR57">
-        <v>4.2</v>
+        <v>5.5</v>
       </c>
       <c r="AS57">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="AT57">
-        <v>2.96</v>
+        <v>5.4</v>
       </c>
       <c r="AU57">
-        <v>3.15</v>
+        <v>6</v>
       </c>
       <c r="AV57">
-        <v>3.95</v>
+        <v>5</v>
       </c>
       <c r="AW57">
-        <v>4.4</v>
+        <v>5.9</v>
       </c>
       <c r="AX57">
-        <v>3.45</v>
+        <v>4</v>
       </c>
       <c r="AY57">
-        <v>3.45</v>
+        <v>7.8</v>
       </c>
       <c r="AZ57">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="BA57">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BB57">
-        <v>4</v>
+        <v>5.1</v>
       </c>
       <c r="BC57">
-        <v>4</v>
+        <v>5.2</v>
       </c>
       <c r="BD57">
-        <v>4.3</v>
+        <v>5.7</v>
       </c>
       <c r="BE57">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BF57">
-        <v>3.9</v>
+        <v>4.9</v>
       </c>
       <c r="BG57">
-        <v>4.5</v>
+        <v>6</v>
       </c>
       <c r="BH57">
-        <v>1000</v>
+        <v>3.1</v>
       </c>
       <c r="BI57">
-        <v>1.01</v>
+        <v>2.42</v>
       </c>
       <c r="BJ57">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK57">
-        <v>1.01</v>
+        <v>5.5</v>
       </c>
       <c r="BL57">
         <v>1000</v>
       </c>
       <c r="BM57">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BN57">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BO57">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BP57">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BQ57">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BR57">
         <v>1000</v>
       </c>
       <c r="BS57">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BT57">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="BU57">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BV57">
         <v>1000</v>
       </c>
       <c r="BW57">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BX57">
         <v>1000</v>
       </c>
       <c r="BY57">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BZ57">
         <v>1000</v>
       </c>
       <c r="CA57">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="CB57" t="s">
         <v>291</v>
@@ -15035,10 +15035,10 @@
         <v>274</v>
       </c>
       <c r="F58">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="G58">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="H58">
         <v>4.3</v>
@@ -15050,7 +15050,7 @@
         <v>3.75</v>
       </c>
       <c r="K58">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L58">
         <v>1.42</v>
@@ -15083,10 +15083,10 @@
         <v>2.1</v>
       </c>
       <c r="V58">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="W58">
-        <v>2.02</v>
+        <v>2</v>
       </c>
       <c r="X58">
         <v>14.5</v>
@@ -15095,7 +15095,7 @@
         <v>15.5</v>
       </c>
       <c r="Z58">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="AA58">
         <v>95</v>
@@ -15119,7 +15119,7 @@
         <v>10.5</v>
       </c>
       <c r="AH58">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AI58">
         <v>65</v>
@@ -15161,10 +15161,10 @@
         <v>7.6</v>
       </c>
       <c r="AV58">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AW58">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AX58">
         <v>10.5</v>
@@ -15212,7 +15212,7 @@
         <v>1000</v>
       </c>
       <c r="BM58">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BN58">
         <v>970</v>
@@ -15230,7 +15230,7 @@
         <v>1000</v>
       </c>
       <c r="BS58">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="BT58">
         <v>970</v>
@@ -15242,19 +15242,19 @@
         <v>1000</v>
       </c>
       <c r="BW58">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BX58">
         <v>1000</v>
       </c>
       <c r="BY58">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BZ58">
         <v>1000</v>
       </c>
       <c r="CA58">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="CB58" t="s">
         <v>291</v>
@@ -15280,7 +15280,7 @@
         <v>4.5</v>
       </c>
       <c r="G59">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="H59">
         <v>1.86</v>
@@ -15292,7 +15292,7 @@
         <v>3.55</v>
       </c>
       <c r="K59">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="L59">
         <v>1.32</v>
@@ -15307,13 +15307,13 @@
         <v>1.34</v>
       </c>
       <c r="P59">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q59">
         <v>2</v>
       </c>
       <c r="R59">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="S59">
         <v>3.6</v>
@@ -15522,19 +15522,19 @@
         <v>4.9</v>
       </c>
       <c r="G60">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="H60">
-        <v>1.56</v>
+        <v>1.53</v>
       </c>
       <c r="I60">
         <v>1.9</v>
       </c>
       <c r="J60">
-        <v>3.35</v>
+        <v>3.2</v>
       </c>
       <c r="K60">
-        <v>6.4</v>
+        <v>7</v>
       </c>
       <c r="L60">
         <v>1.01</v>
@@ -15761,16 +15761,16 @@
         <v>277</v>
       </c>
       <c r="F61">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="G61">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="H61">
+        <v>1.54</v>
+      </c>
+      <c r="I61">
         <v>1.55</v>
-      </c>
-      <c r="I61">
-        <v>1.56</v>
       </c>
       <c r="J61">
         <v>4.5</v>
@@ -15791,7 +15791,7 @@
         <v>1.28</v>
       </c>
       <c r="P61">
-        <v>2.1</v>
+        <v>2.12</v>
       </c>
       <c r="Q61">
         <v>1.87</v>
@@ -15803,13 +15803,13 @@
         <v>3.25</v>
       </c>
       <c r="T61">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="U61">
         <v>1.95</v>
       </c>
       <c r="V61">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="W61">
         <v>1.15</v>
@@ -15851,22 +15851,22 @@
         <v>36</v>
       </c>
       <c r="AJ61">
-        <v>220</v>
+        <v>290</v>
       </c>
       <c r="AK61">
         <v>95</v>
       </c>
       <c r="AL61">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="AM61">
         <v>130</v>
       </c>
       <c r="AN61">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AO61">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AP61">
         <v>16</v>
@@ -15902,25 +15902,25 @@
         <v>21</v>
       </c>
       <c r="BA61">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="BB61">
-        <v>60</v>
+        <v>160</v>
       </c>
       <c r="BC61">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BD61">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BE61">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="BF61">
         <v>100</v>
       </c>
       <c r="BG61">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH61">
         <v>3.65</v>
@@ -15938,10 +15938,10 @@
         <v>180</v>
       </c>
       <c r="BM61">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="BN61">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="BO61">
         <v>9.199999999999999</v>
@@ -15950,19 +15950,19 @@
         <v>65</v>
       </c>
       <c r="BQ61">
-        <v>9.4</v>
+        <v>10</v>
       </c>
       <c r="BR61">
         <v>70</v>
       </c>
       <c r="BS61">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="BT61">
         <v>4</v>
       </c>
       <c r="BU61">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="BV61">
         <v>10.5</v>
@@ -15974,13 +15974,13 @@
         <v>27</v>
       </c>
       <c r="BY61">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BZ61">
         <v>18.5</v>
       </c>
       <c r="CA61">
-        <v>6.8</v>
+        <v>7.4</v>
       </c>
       <c r="CB61" t="s">
         <v>291</v>
@@ -16003,13 +16003,13 @@
         <v>278</v>
       </c>
       <c r="F62">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="G62">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="H62">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="I62">
         <v>3.4</v>
@@ -16027,37 +16027,37 @@
         <v>1.01</v>
       </c>
       <c r="N62">
-        <v>3.8</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="O62">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="P62">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="Q62">
-        <v>1.19</v>
+        <v>1.29</v>
       </c>
       <c r="R62">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="S62">
-        <v>1.64</v>
+        <v>1.72</v>
       </c>
       <c r="T62">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="U62">
-        <v>3.05</v>
+        <v>3.55</v>
       </c>
       <c r="V62">
         <v>1.41</v>
       </c>
       <c r="W62">
-        <v>1.87</v>
+        <v>1.9</v>
       </c>
       <c r="X62">
-        <v>65</v>
+        <v>450</v>
       </c>
       <c r="Y62">
         <v>40</v>
@@ -16066,7 +16066,7 @@
         <v>46</v>
       </c>
       <c r="AA62">
-        <v>70</v>
+        <v>1000</v>
       </c>
       <c r="AB62">
         <v>32</v>
@@ -16111,58 +16111,58 @@
         <v>14</v>
       </c>
       <c r="AP62">
-        <v>4.1</v>
+        <v>29</v>
       </c>
       <c r="AQ62">
-        <v>4</v>
+        <v>21</v>
       </c>
       <c r="AR62">
-        <v>4</v>
+        <v>23</v>
       </c>
       <c r="AS62">
-        <v>4.2</v>
+        <v>32</v>
       </c>
       <c r="AT62">
-        <v>19</v>
+        <v>17.5</v>
       </c>
       <c r="AU62">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AV62">
         <v>12.5</v>
       </c>
       <c r="AW62">
+        <v>19</v>
+      </c>
+      <c r="AX62">
+        <v>16</v>
+      </c>
+      <c r="AY62">
+        <v>11.5</v>
+      </c>
+      <c r="AZ62">
+        <v>12.5</v>
+      </c>
+      <c r="BA62">
+        <v>17.5</v>
+      </c>
+      <c r="BB62">
         <v>20</v>
       </c>
-      <c r="AX62">
+      <c r="BC62">
+        <v>16</v>
+      </c>
+      <c r="BD62">
         <v>17.5</v>
       </c>
-      <c r="AY62">
-        <v>10</v>
-      </c>
-      <c r="AZ62">
+      <c r="BE62">
+        <v>21</v>
+      </c>
+      <c r="BF62">
+        <v>5.5</v>
+      </c>
+      <c r="BG62">
         <v>10.5</v>
-      </c>
-      <c r="BA62">
-        <v>18.5</v>
-      </c>
-      <c r="BB62">
-        <v>21</v>
-      </c>
-      <c r="BC62">
-        <v>13.5</v>
-      </c>
-      <c r="BD62">
-        <v>15</v>
-      </c>
-      <c r="BE62">
-        <v>4</v>
-      </c>
-      <c r="BF62">
-        <v>4.7</v>
-      </c>
-      <c r="BG62">
-        <v>9</v>
       </c>
       <c r="BH62">
         <v>1000</v>
@@ -16254,10 +16254,10 @@
         <v>5.2</v>
       </c>
       <c r="I63">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="J63">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="K63">
         <v>4.1</v>
@@ -16269,31 +16269,31 @@
         <v>1.06</v>
       </c>
       <c r="N63">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="O63">
         <v>1.3</v>
       </c>
       <c r="P63">
-        <v>1.74</v>
+        <v>1.85</v>
       </c>
       <c r="Q63">
-        <v>1.87</v>
+        <v>1.89</v>
       </c>
       <c r="R63">
-        <v>1.18</v>
+        <v>1.33</v>
       </c>
       <c r="S63">
-        <v>2.32</v>
+        <v>3.05</v>
       </c>
       <c r="T63">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="U63">
-        <v>2.02</v>
+        <v>2.04</v>
       </c>
       <c r="V63">
-        <v>1.22</v>
+        <v>1.21</v>
       </c>
       <c r="W63">
         <v>2.22</v>
@@ -16326,7 +16326,7 @@
         <v>11</v>
       </c>
       <c r="AG63">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AH63">
         <v>24</v>
@@ -16362,19 +16362,19 @@
         <v>34</v>
       </c>
       <c r="AS63">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="AT63">
         <v>7.6</v>
       </c>
       <c r="AU63">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="AV63">
         <v>18</v>
       </c>
       <c r="AW63">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="AX63">
         <v>9.800000000000001</v>
@@ -16386,7 +16386,7 @@
         <v>17.5</v>
       </c>
       <c r="BA63">
-        <v>7.4</v>
+        <v>9</v>
       </c>
       <c r="BB63">
         <v>16.5</v>
@@ -16395,16 +16395,16 @@
         <v>17</v>
       </c>
       <c r="BD63">
-        <v>6.6</v>
+        <v>7.8</v>
       </c>
       <c r="BE63">
-        <v>7.8</v>
+        <v>8.4</v>
       </c>
       <c r="BF63">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="BG63">
-        <v>7.6</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BH63">
         <v>1000</v>
@@ -16493,7 +16493,7 @@
         <v>1.2</v>
       </c>
       <c r="H64">
-        <v>17</v>
+        <v>17.5</v>
       </c>
       <c r="I64">
         <v>21</v>
@@ -16511,28 +16511,28 @@
         <v>1.02</v>
       </c>
       <c r="N64">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="O64">
-        <v>1.13</v>
+        <v>1.14</v>
       </c>
       <c r="P64">
-        <v>2.96</v>
+        <v>3.05</v>
       </c>
       <c r="Q64">
         <v>1.43</v>
       </c>
       <c r="R64">
-        <v>1.79</v>
+        <v>1.81</v>
       </c>
       <c r="S64">
-        <v>1.89</v>
+        <v>2</v>
       </c>
       <c r="T64">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="U64">
-        <v>1.72</v>
+        <v>1.73</v>
       </c>
       <c r="V64">
         <v>1.05</v>
@@ -16541,7 +16541,7 @@
         <v>6</v>
       </c>
       <c r="X64">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="Y64">
         <v>75</v>
@@ -16553,7 +16553,7 @@
         <v>1000</v>
       </c>
       <c r="AB64">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AC64">
         <v>24</v>
@@ -16562,10 +16562,10 @@
         <v>70</v>
       </c>
       <c r="AE64">
-        <v>370</v>
+        <v>380</v>
       </c>
       <c r="AF64">
-        <v>9.4</v>
+        <v>10.5</v>
       </c>
       <c r="AG64">
         <v>15.5</v>
@@ -16574,10 +16574,10 @@
         <v>44</v>
       </c>
       <c r="AI64">
-        <v>200</v>
+        <v>260</v>
       </c>
       <c r="AJ64">
-        <v>11</v>
+        <v>9.4</v>
       </c>
       <c r="AK64">
         <v>15</v>
@@ -16586,25 +16586,25 @@
         <v>42</v>
       </c>
       <c r="AM64">
-        <v>200</v>
+        <v>250</v>
       </c>
       <c r="AN64">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="AO64">
-        <v>470</v>
+        <v>480</v>
       </c>
       <c r="AP64">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="AQ64">
-        <v>6.6</v>
+        <v>7.2</v>
       </c>
       <c r="AR64">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AS64">
-        <v>7.2</v>
+        <v>7.8</v>
       </c>
       <c r="AT64">
         <v>10</v>
@@ -16613,10 +16613,10 @@
         <v>15.5</v>
       </c>
       <c r="AV64">
-        <v>6.6</v>
+        <v>7</v>
       </c>
       <c r="AW64">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="AX64">
         <v>7.6</v>
@@ -16625,28 +16625,28 @@
         <v>10</v>
       </c>
       <c r="AZ64">
-        <v>6.2</v>
+        <v>6.6</v>
       </c>
       <c r="BA64">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BB64">
         <v>8</v>
       </c>
       <c r="BC64">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BD64">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="BE64">
-        <v>7</v>
+        <v>7.6</v>
       </c>
       <c r="BF64">
-        <v>2.86</v>
+        <v>2.84</v>
       </c>
       <c r="BG64">
-        <v>7.2</v>
+        <v>7.6</v>
       </c>
       <c r="BH64">
         <v>1000</v>
@@ -16658,13 +16658,13 @@
         <v>20</v>
       </c>
       <c r="BK64">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL64">
         <v>1000</v>
       </c>
       <c r="BM64">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN64">
         <v>5.3</v>
@@ -16682,25 +16682,25 @@
         <v>30</v>
       </c>
       <c r="BS64">
-        <v>13</v>
+        <v>1.01</v>
       </c>
       <c r="BT64">
         <v>28</v>
       </c>
       <c r="BU64">
-        <v>11.5</v>
+        <v>1.01</v>
       </c>
       <c r="BV64">
         <v>1000</v>
       </c>
       <c r="BW64">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BX64">
         <v>1000</v>
       </c>
       <c r="BY64">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BZ64">
         <v>10.5</v>
@@ -16732,16 +16732,16 @@
         <v>1.17</v>
       </c>
       <c r="G65">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="H65">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="I65">
         <v>22</v>
       </c>
       <c r="J65">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K65">
         <v>10</v>
@@ -16756,7 +16756,7 @@
         <v>9</v>
       </c>
       <c r="O65">
-        <v>1.12</v>
+        <v>1.11</v>
       </c>
       <c r="P65">
         <v>3.65</v>
@@ -16765,7 +16765,7 @@
         <v>1.35</v>
       </c>
       <c r="R65">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="S65">
         <v>1.89</v>
@@ -16774,13 +16774,13 @@
         <v>2.06</v>
       </c>
       <c r="U65">
-        <v>1.86</v>
+        <v>1.88</v>
       </c>
       <c r="V65">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W65">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="X65">
         <v>46</v>
@@ -16801,7 +16801,7 @@
         <v>24</v>
       </c>
       <c r="AD65">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="AE65">
         <v>350</v>
@@ -16810,13 +16810,13 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AG65">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AH65">
         <v>42</v>
       </c>
       <c r="AI65">
-        <v>190</v>
+        <v>1000</v>
       </c>
       <c r="AJ65">
         <v>9.199999999999999</v>
@@ -16837,28 +16837,28 @@
         <v>360</v>
       </c>
       <c r="AP65">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AQ65">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="AR65">
         <v>48</v>
       </c>
       <c r="AS65">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AT65">
         <v>12.5</v>
       </c>
       <c r="AU65">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV65">
         <v>55</v>
       </c>
       <c r="AW65">
-        <v>24</v>
+        <v>50</v>
       </c>
       <c r="AX65">
         <v>9.199999999999999</v>
@@ -16885,70 +16885,70 @@
         <v>46</v>
       </c>
       <c r="BF65">
-        <v>2.7</v>
+        <v>2.68</v>
       </c>
       <c r="BG65">
+        <v>24</v>
+      </c>
+      <c r="BH65">
+        <v>1000</v>
+      </c>
+      <c r="BI65">
+        <v>1.47</v>
+      </c>
+      <c r="BJ65">
+        <v>36</v>
+      </c>
+      <c r="BK65">
+        <v>7.4</v>
+      </c>
+      <c r="BL65">
+        <v>1000</v>
+      </c>
+      <c r="BM65">
+        <v>32</v>
+      </c>
+      <c r="BN65">
+        <v>9.4</v>
+      </c>
+      <c r="BO65">
+        <v>2.84</v>
+      </c>
+      <c r="BP65">
+        <v>970</v>
+      </c>
+      <c r="BQ65">
+        <v>3.65</v>
+      </c>
+      <c r="BR65">
+        <v>48</v>
+      </c>
+      <c r="BS65">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BT65">
+        <v>48</v>
+      </c>
+      <c r="BU65">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="BV65">
+        <v>1000</v>
+      </c>
+      <c r="BW65">
+        <v>34</v>
+      </c>
+      <c r="BX65">
+        <v>1000</v>
+      </c>
+      <c r="BY65">
         <v>25</v>
       </c>
-      <c r="BH65">
-        <v>1000</v>
-      </c>
-      <c r="BI65">
-        <v>1.01</v>
-      </c>
-      <c r="BJ65">
-        <v>1000</v>
-      </c>
-      <c r="BK65">
-        <v>1.01</v>
-      </c>
-      <c r="BL65">
-        <v>1000</v>
-      </c>
-      <c r="BM65">
-        <v>1.01</v>
-      </c>
-      <c r="BN65">
-        <v>1000</v>
-      </c>
-      <c r="BO65">
-        <v>1.01</v>
-      </c>
-      <c r="BP65">
-        <v>1000</v>
-      </c>
-      <c r="BQ65">
-        <v>1.01</v>
-      </c>
-      <c r="BR65">
-        <v>1000</v>
-      </c>
-      <c r="BS65">
-        <v>1.01</v>
-      </c>
-      <c r="BT65">
-        <v>1000</v>
-      </c>
-      <c r="BU65">
-        <v>1.01</v>
-      </c>
-      <c r="BV65">
-        <v>1000</v>
-      </c>
-      <c r="BW65">
-        <v>1.01</v>
-      </c>
-      <c r="BX65">
-        <v>1000</v>
-      </c>
-      <c r="BY65">
-        <v>1.01</v>
-      </c>
       <c r="BZ65">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="CA65">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="CB65" t="s">
         <v>291</v>
@@ -16974,52 +16974,52 @@
         <v>4.2</v>
       </c>
       <c r="G66">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="H66">
-        <v>1.82</v>
+        <v>1.83</v>
       </c>
       <c r="I66">
-        <v>1.95</v>
+        <v>1.94</v>
       </c>
       <c r="J66">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="K66">
-        <v>4.8</v>
+        <v>4.3</v>
       </c>
       <c r="L66">
-        <v>1.01</v>
+        <v>1.33</v>
       </c>
       <c r="M66">
-        <v>1.06</v>
+        <v>1.05</v>
       </c>
       <c r="N66">
         <v>4.3</v>
       </c>
       <c r="O66">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P66">
-        <v>2.16</v>
+        <v>2.18</v>
       </c>
       <c r="Q66">
-        <v>1.74</v>
+        <v>1.75</v>
       </c>
       <c r="R66">
         <v>1.47</v>
       </c>
       <c r="S66">
-        <v>2.78</v>
+        <v>2.9</v>
       </c>
       <c r="T66">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="U66">
-        <v>2.2</v>
+        <v>2.24</v>
       </c>
       <c r="V66">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="W66">
         <v>1.26</v>
@@ -17028,7 +17028,7 @@
         <v>22</v>
       </c>
       <c r="Y66">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="Z66">
         <v>14.5</v>
@@ -17103,94 +17103,94 @@
         <v>16</v>
       </c>
       <c r="AX66">
-        <v>5.3</v>
+        <v>5.8</v>
       </c>
       <c r="AY66">
         <v>15.5</v>
       </c>
       <c r="AZ66">
-        <v>15</v>
+        <v>15.5</v>
       </c>
       <c r="BA66">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="BB66">
+        <v>6.4</v>
+      </c>
+      <c r="BC66">
         <v>6</v>
       </c>
-      <c r="BC66">
-        <v>5.7</v>
-      </c>
       <c r="BD66">
-        <v>5.7</v>
+        <v>6</v>
       </c>
       <c r="BE66">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="BF66">
-        <v>5.6</v>
+        <v>6.2</v>
       </c>
       <c r="BG66">
-        <v>8.199999999999999</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH66">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI66">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ66">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK66">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="BL66">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BM66">
         <v>1.01</v>
       </c>
       <c r="BN66">
-        <v>1000</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BO66">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="BP66">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BQ66">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BR66">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BS66">
-        <v>1.01</v>
+        <v>30</v>
       </c>
       <c r="BT66">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BU66">
-        <v>1.01</v>
+        <v>3.8</v>
       </c>
       <c r="BV66">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BW66">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="BX66">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="BY66">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BZ66">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="CA66">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="CB66" t="s">
         <v>291</v>
@@ -17219,7 +17219,7 @@
         <v>3.75</v>
       </c>
       <c r="H67">
-        <v>2.66</v>
+        <v>2.52</v>
       </c>
       <c r="I67">
         <v>3.75</v>
@@ -17455,22 +17455,22 @@
         <v>284</v>
       </c>
       <c r="F68">
-        <v>1.66</v>
+        <v>1.7</v>
       </c>
       <c r="G68">
-        <v>1.94</v>
+        <v>1.91</v>
       </c>
       <c r="H68">
-        <v>1.08</v>
+        <v>5.3</v>
       </c>
       <c r="I68">
-        <v>110</v>
+        <v>7.6</v>
       </c>
       <c r="J68">
-        <v>1.09</v>
+        <v>2.92</v>
       </c>
       <c r="K68">
-        <v>950</v>
+        <v>1000</v>
       </c>
       <c r="L68">
         <v>1.01</v>
@@ -17479,22 +17479,22 @@
         <v>1.01</v>
       </c>
       <c r="N68">
-        <v>2.46</v>
+        <v>2.72</v>
       </c>
       <c r="O68">
         <v>1.45</v>
       </c>
       <c r="P68">
-        <v>1.52</v>
+        <v>1.25</v>
       </c>
       <c r="Q68">
-        <v>1.45</v>
+        <v>2.24</v>
       </c>
       <c r="R68">
         <v>1.2</v>
       </c>
       <c r="S68">
-        <v>2.78</v>
+        <v>1.01</v>
       </c>
       <c r="T68">
         <v>1.01</v>
@@ -17503,10 +17503,10 @@
         <v>1.01</v>
       </c>
       <c r="V68">
-        <v>1.08</v>
+        <v>1.15</v>
       </c>
       <c r="W68">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="X68">
         <v>1000</v>
@@ -17697,7 +17697,7 @@
         <v>285</v>
       </c>
       <c r="F69">
-        <v>2.38</v>
+        <v>2.46</v>
       </c>
       <c r="G69">
         <v>2.7</v>
@@ -17712,7 +17712,7 @@
         <v>2.9</v>
       </c>
       <c r="K69">
-        <v>3.25</v>
+        <v>3.15</v>
       </c>
       <c r="L69">
         <v>1.6</v>
@@ -17730,7 +17730,7 @@
         <v>1.49</v>
       </c>
       <c r="Q69">
-        <v>2.8</v>
+        <v>2.84</v>
       </c>
       <c r="R69">
         <v>1.17</v>
@@ -17748,7 +17748,7 @@
         <v>1.34</v>
       </c>
       <c r="W69">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="X69">
         <v>8</v>
@@ -17942,19 +17942,19 @@
         <v>2.26</v>
       </c>
       <c r="G70">
-        <v>2.54</v>
+        <v>2.42</v>
       </c>
       <c r="H70">
         <v>3.25</v>
       </c>
       <c r="I70">
-        <v>3.7</v>
+        <v>3.55</v>
       </c>
       <c r="J70">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="K70">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L70">
         <v>1.01</v>
@@ -17963,7 +17963,7 @@
         <v>1.06</v>
       </c>
       <c r="N70">
-        <v>3.55</v>
+        <v>3.7</v>
       </c>
       <c r="O70">
         <v>1.28</v>
@@ -17972,112 +17972,112 @@
         <v>1.96</v>
       </c>
       <c r="Q70">
-        <v>1.81</v>
+        <v>1.87</v>
       </c>
       <c r="R70">
-        <v>1.31</v>
+        <v>1.36</v>
       </c>
       <c r="S70">
-        <v>2.82</v>
+        <v>3.2</v>
       </c>
       <c r="T70">
-        <v>1.01</v>
+        <v>1.63</v>
       </c>
       <c r="U70">
-        <v>1.01</v>
+        <v>2.02</v>
       </c>
       <c r="V70">
-        <v>1.34</v>
+        <v>1.39</v>
       </c>
       <c r="W70">
-        <v>1.64</v>
+        <v>1.7</v>
       </c>
       <c r="X70">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Y70">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z70">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="AA70">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB70">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC70">
-        <v>1000</v>
+        <v>9.4</v>
       </c>
       <c r="AD70">
-        <v>1000</v>
+        <v>16.5</v>
       </c>
       <c r="AE70">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF70">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AG70">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="AH70">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AI70">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AJ70">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AK70">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL70">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AM70">
-        <v>1000</v>
+        <v>100</v>
       </c>
       <c r="AN70">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AO70">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AP70">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AQ70">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AR70">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AS70">
         <v>1.01</v>
       </c>
       <c r="AT70">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU70">
-        <v>1.01</v>
+        <v>6.4</v>
       </c>
       <c r="AV70">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW70">
         <v>1.01</v>
       </c>
       <c r="AX70">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AY70">
-        <v>1.01</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="AZ70">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA70">
         <v>1.01</v>
@@ -18086,7 +18086,7 @@
         <v>1.01</v>
       </c>
       <c r="BC70">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BD70">
         <v>1.01</v>
@@ -18095,7 +18095,7 @@
         <v>1.01</v>
       </c>
       <c r="BF70">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="BG70">
         <v>1.01</v>
@@ -18444,7 +18444,7 @@
         <v>1.01</v>
       </c>
       <c r="M72">
-        <v>1.07</v>
+        <v>1.06</v>
       </c>
       <c r="N72">
         <v>3.25</v>
@@ -18665,19 +18665,19 @@
         <v>289</v>
       </c>
       <c r="F73">
-        <v>2.22</v>
+        <v>2.24</v>
       </c>
       <c r="G73">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="H73">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="I73">
         <v>4.1</v>
       </c>
       <c r="J73">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="K73">
         <v>3.35</v>
@@ -18713,10 +18713,10 @@
         <v>1.88</v>
       </c>
       <c r="V73">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W73">
-        <v>1.76</v>
+        <v>1.74</v>
       </c>
       <c r="X73">
         <v>10.5</v>
@@ -18782,7 +18782,7 @@
         <v>20</v>
       </c>
       <c r="AS73">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AT73">
         <v>6.8</v>
@@ -18806,7 +18806,7 @@
         <v>18.5</v>
       </c>
       <c r="BA73">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB73">
         <v>22</v>
@@ -18907,19 +18907,19 @@
         <v>290</v>
       </c>
       <c r="F74">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="G74">
-        <v>970</v>
+        <v>3.75</v>
       </c>
       <c r="H74">
-        <v>1.38</v>
+        <v>1.54</v>
       </c>
       <c r="I74">
         <v>110</v>
       </c>
       <c r="J74">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="K74">
         <v>290</v>
@@ -18931,16 +18931,16 @@
         <v>1.01</v>
       </c>
       <c r="N74">
-        <v>1.25</v>
+        <v>1.7</v>
       </c>
       <c r="O74">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="P74">
         <v>1.25</v>
       </c>
       <c r="Q74">
-        <v>1.27</v>
+        <v>1.26</v>
       </c>
       <c r="R74">
         <v>1.18</v>
@@ -18955,10 +18955,10 @@
         <v>1.01</v>
       </c>
       <c r="V74">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="W74">
-        <v>1.37</v>
+        <v>1.52</v>
       </c>
       <c r="X74">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-31.xlsx
@@ -889,7 +889,7 @@
     <t>Academia Anzoategui FC</t>
   </si>
   <si>
-    <t>2026-08-30 06:03:59</t>
+    <t>2026-08-30 08:25:00</t>
   </si>
 </sst>
 </file>
@@ -1483,22 +1483,22 @@
         <v>218</v>
       </c>
       <c r="F2">
-        <v>1.57</v>
+        <v>1.52</v>
       </c>
       <c r="G2">
-        <v>1.6</v>
+        <v>1.55</v>
       </c>
       <c r="H2">
-        <v>6.2</v>
+        <v>6.8</v>
       </c>
       <c r="I2">
-        <v>6.8</v>
+        <v>7.6</v>
       </c>
       <c r="J2">
-        <v>4.4</v>
+        <v>4.6</v>
       </c>
       <c r="K2">
-        <v>4.7</v>
+        <v>5</v>
       </c>
       <c r="L2">
         <v>1.35</v>
@@ -1513,34 +1513,34 @@
         <v>1.25</v>
       </c>
       <c r="P2">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="Q2">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="R2">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S2">
-        <v>2.96</v>
+        <v>2.92</v>
       </c>
       <c r="T2">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U2">
-        <v>2.06</v>
+        <v>2.02</v>
       </c>
       <c r="V2">
-        <v>1.17</v>
+        <v>1.15</v>
       </c>
       <c r="W2">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="X2">
         <v>23</v>
       </c>
       <c r="Y2">
-        <v>24</v>
+        <v>30</v>
       </c>
       <c r="Z2">
         <v>65</v>
@@ -1549,19 +1549,19 @@
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>11.5</v>
+        <v>9.4</v>
       </c>
       <c r="AC2">
         <v>13</v>
       </c>
       <c r="AD2">
-        <v>25</v>
+        <v>32</v>
       </c>
       <c r="AE2">
         <v>1000</v>
       </c>
       <c r="AF2">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="AG2">
         <v>12.5</v>
@@ -1573,19 +1573,19 @@
         <v>1000</v>
       </c>
       <c r="AJ2">
-        <v>18</v>
+        <v>14.5</v>
       </c>
       <c r="AK2">
         <v>16.5</v>
       </c>
       <c r="AL2">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="AM2">
         <v>1000</v>
       </c>
       <c r="AN2">
-        <v>9.199999999999999</v>
+        <v>8.6</v>
       </c>
       <c r="AO2">
         <v>1000</v>
@@ -1594,10 +1594,10 @@
         <v>16.5</v>
       </c>
       <c r="AQ2">
-        <v>19.5</v>
+        <v>21</v>
       </c>
       <c r="AR2">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AS2">
         <v>1.01</v>
@@ -1609,25 +1609,25 @@
         <v>9</v>
       </c>
       <c r="AV2">
-        <v>20</v>
+        <v>17.5</v>
       </c>
       <c r="AW2">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="AX2">
-        <v>8.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AY2">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ2">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BA2">
-        <v>34</v>
+        <v>1.01</v>
       </c>
       <c r="BB2">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BC2">
         <v>12</v>
@@ -1639,7 +1639,7 @@
         <v>40</v>
       </c>
       <c r="BF2">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="BG2">
         <v>1.01</v>
@@ -1749,7 +1749,7 @@
         <v>1.03</v>
       </c>
       <c r="N3">
-        <v>7</v>
+        <v>6.8</v>
       </c>
       <c r="O3">
         <v>1.16</v>
@@ -1758,13 +1758,13 @@
         <v>3</v>
       </c>
       <c r="Q3">
-        <v>1.46</v>
+        <v>1.47</v>
       </c>
       <c r="R3">
-        <v>1.82</v>
+        <v>1.8</v>
       </c>
       <c r="S3">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="T3">
         <v>1.82</v>
@@ -1806,10 +1806,10 @@
         <v>11</v>
       </c>
       <c r="AG3">
-        <v>11</v>
+        <v>12.5</v>
       </c>
       <c r="AH3">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AI3">
         <v>110</v>
@@ -1818,7 +1818,7 @@
         <v>12.5</v>
       </c>
       <c r="AK3">
-        <v>14.5</v>
+        <v>16</v>
       </c>
       <c r="AL3">
         <v>30</v>
@@ -1833,19 +1833,19 @@
         <v>130</v>
       </c>
       <c r="AP3">
-        <v>7.6</v>
+        <v>7</v>
       </c>
       <c r="AQ3">
+        <v>8.6</v>
+      </c>
+      <c r="AR3">
         <v>8</v>
       </c>
-      <c r="AR3">
-        <v>8.800000000000001</v>
-      </c>
       <c r="AS3">
-        <v>9.4</v>
+        <v>8</v>
       </c>
       <c r="AT3">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AU3">
         <v>13</v>
@@ -1854,37 +1854,37 @@
         <v>30</v>
       </c>
       <c r="AW3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AX3">
         <v>9.4</v>
       </c>
       <c r="AY3">
-        <v>9.800000000000001</v>
+        <v>7.2</v>
       </c>
       <c r="AZ3">
         <v>21</v>
       </c>
       <c r="BA3">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="BB3">
-        <v>9.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="BC3">
-        <v>11.5</v>
+        <v>12</v>
       </c>
       <c r="BD3">
         <v>24</v>
       </c>
       <c r="BE3">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BF3">
-        <v>3.65</v>
+        <v>3.75</v>
       </c>
       <c r="BG3">
-        <v>9</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BH3">
         <v>1000</v>
@@ -1967,10 +1967,10 @@
         <v>220</v>
       </c>
       <c r="F4">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G4">
-        <v>2.4</v>
+        <v>2.38</v>
       </c>
       <c r="H4">
         <v>3.25</v>
@@ -1982,7 +1982,7 @@
         <v>3.55</v>
       </c>
       <c r="K4">
-        <v>3.85</v>
+        <v>3.9</v>
       </c>
       <c r="L4">
         <v>1.35</v>
@@ -1997,7 +1997,7 @@
         <v>1.26</v>
       </c>
       <c r="P4">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="Q4">
         <v>1.8</v>
@@ -2009,16 +2009,16 @@
         <v>3</v>
       </c>
       <c r="T4">
-        <v>1.57</v>
+        <v>1.64</v>
       </c>
       <c r="U4">
-        <v>2.12</v>
+        <v>2.26</v>
       </c>
       <c r="V4">
         <v>1.4</v>
       </c>
       <c r="W4">
-        <v>1.71</v>
+        <v>1.72</v>
       </c>
       <c r="X4">
         <v>1000</v>
@@ -2209,34 +2209,34 @@
         <v>221</v>
       </c>
       <c r="F5">
-        <v>2.34</v>
+        <v>2.28</v>
       </c>
       <c r="G5">
-        <v>2.42</v>
+        <v>2.3</v>
       </c>
       <c r="H5">
-        <v>3.65</v>
+        <v>3.9</v>
       </c>
       <c r="I5">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="J5">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="K5">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="L5">
         <v>1.58</v>
       </c>
       <c r="M5">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="N5">
         <v>2.78</v>
       </c>
       <c r="O5">
-        <v>1.53</v>
+        <v>1.54</v>
       </c>
       <c r="P5">
         <v>1.57</v>
@@ -2257,10 +2257,10 @@
         <v>1.81</v>
       </c>
       <c r="V5">
-        <v>1.35</v>
+        <v>1.32</v>
       </c>
       <c r="W5">
-        <v>1.7</v>
+        <v>1.77</v>
       </c>
       <c r="X5">
         <v>10.5</v>
@@ -2269,10 +2269,10 @@
         <v>11.5</v>
       </c>
       <c r="Z5">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="AA5">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AB5">
         <v>7.8</v>
@@ -2284,10 +2284,10 @@
         <v>18</v>
       </c>
       <c r="AE5">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AF5">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AG5">
         <v>14.5</v>
@@ -2308,16 +2308,16 @@
         <v>75</v>
       </c>
       <c r="AM5">
-        <v>520</v>
+        <v>420</v>
       </c>
       <c r="AN5">
-        <v>36</v>
+        <v>40</v>
       </c>
       <c r="AO5">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AP5">
-        <v>6.8</v>
+        <v>7.8</v>
       </c>
       <c r="AQ5">
         <v>9.199999999999999</v>
@@ -2326,49 +2326,49 @@
         <v>19</v>
       </c>
       <c r="AS5">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AT5">
-        <v>5.6</v>
+        <v>6.6</v>
       </c>
       <c r="AU5">
         <v>6.4</v>
       </c>
       <c r="AV5">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="AW5">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="AX5">
         <v>11.5</v>
       </c>
       <c r="AY5">
-        <v>8.800000000000001</v>
+        <v>10.5</v>
       </c>
       <c r="AZ5">
         <v>20</v>
       </c>
       <c r="BA5">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BB5">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BC5">
         <v>23</v>
       </c>
       <c r="BD5">
-        <v>6.2</v>
+        <v>20</v>
       </c>
       <c r="BE5">
+        <v>6.8</v>
+      </c>
+      <c r="BF5">
+        <v>11</v>
+      </c>
+      <c r="BG5">
         <v>6.4</v>
-      </c>
-      <c r="BF5">
-        <v>5.8</v>
-      </c>
-      <c r="BG5">
-        <v>6</v>
       </c>
       <c r="BH5">
         <v>3.1</v>
@@ -2383,13 +2383,13 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BL5">
-        <v>820</v>
+        <v>720</v>
       </c>
       <c r="BM5">
         <v>21</v>
       </c>
       <c r="BN5">
-        <v>4.9</v>
+        <v>5.7</v>
       </c>
       <c r="BO5">
         <v>4.4</v>
@@ -2407,19 +2407,19 @@
         <v>30</v>
       </c>
       <c r="BT5">
-        <v>6.8</v>
+        <v>8.4</v>
       </c>
       <c r="BU5">
         <v>6</v>
       </c>
       <c r="BV5">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="BW5">
         <v>27</v>
       </c>
       <c r="BX5">
-        <v>70</v>
+        <v>75</v>
       </c>
       <c r="BY5">
         <v>42</v>
@@ -2457,7 +2457,7 @@
         <v>2.16</v>
       </c>
       <c r="H6">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="I6">
         <v>4.8</v>
@@ -2493,7 +2493,7 @@
         <v>5.1</v>
       </c>
       <c r="T6">
-        <v>1.9</v>
+        <v>2.08</v>
       </c>
       <c r="U6">
         <v>1.8</v>
@@ -2693,16 +2693,16 @@
         <v>223</v>
       </c>
       <c r="F7">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G7">
         <v>1.6</v>
       </c>
       <c r="H7">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="I7">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="J7">
         <v>4.7</v>
@@ -2717,7 +2717,7 @@
         <v>1.04</v>
       </c>
       <c r="N7">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O7">
         <v>1.2</v>
@@ -2726,16 +2726,16 @@
         <v>2.6</v>
       </c>
       <c r="Q7">
-        <v>1.59</v>
+        <v>1.6</v>
       </c>
       <c r="R7">
         <v>1.63</v>
       </c>
       <c r="S7">
-        <v>2.5</v>
+        <v>2.52</v>
       </c>
       <c r="T7">
-        <v>1.72</v>
+        <v>1.71</v>
       </c>
       <c r="U7">
         <v>2.32</v>
@@ -2744,7 +2744,7 @@
         <v>1.19</v>
       </c>
       <c r="W7">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="X7">
         <v>25</v>
@@ -2762,10 +2762,10 @@
         <v>12</v>
       </c>
       <c r="AC7">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="AD7">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AE7">
         <v>75</v>
@@ -2810,7 +2810,7 @@
         <v>44</v>
       </c>
       <c r="AS7">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AT7">
         <v>10.5</v>
@@ -2837,22 +2837,22 @@
         <v>50</v>
       </c>
       <c r="BB7">
-        <v>14.5</v>
+        <v>13.5</v>
       </c>
       <c r="BC7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BD7">
         <v>24</v>
       </c>
       <c r="BE7">
-        <v>13.5</v>
+        <v>13</v>
       </c>
       <c r="BF7">
         <v>5.8</v>
       </c>
       <c r="BG7">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BH7">
         <v>1000</v>
@@ -2935,7 +2935,7 @@
         <v>224</v>
       </c>
       <c r="F8">
-        <v>1.75</v>
+        <v>1.77</v>
       </c>
       <c r="G8">
         <v>110</v>
@@ -2962,19 +2962,19 @@
         <v>3.6</v>
       </c>
       <c r="O8">
-        <v>1.26</v>
+        <v>1.01</v>
       </c>
       <c r="P8">
         <v>1.25</v>
       </c>
       <c r="Q8">
-        <v>1.75</v>
+        <v>1.28</v>
       </c>
       <c r="R8">
         <v>1.18</v>
       </c>
       <c r="S8">
-        <v>2.28</v>
+        <v>1.28</v>
       </c>
       <c r="T8">
         <v>1.01</v>
@@ -2983,10 +2983,10 @@
         <v>1.01</v>
       </c>
       <c r="V8">
-        <v>1.72</v>
+        <v>1.74</v>
       </c>
       <c r="W8">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X8">
         <v>1000</v>
@@ -3177,13 +3177,13 @@
         <v>225</v>
       </c>
       <c r="F9">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="G9">
         <v>970</v>
       </c>
       <c r="H9">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="I9">
         <v>970</v>
@@ -3216,7 +3216,7 @@
         <v>1.18</v>
       </c>
       <c r="S9">
-        <v>1.13</v>
+        <v>1.12</v>
       </c>
       <c r="T9">
         <v>1.01</v>
@@ -3225,10 +3225,10 @@
         <v>1.01</v>
       </c>
       <c r="V9">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="W9">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3419,19 +3419,19 @@
         <v>226</v>
       </c>
       <c r="F10">
-        <v>2.4</v>
+        <v>2.46</v>
       </c>
       <c r="G10">
         <v>110</v>
       </c>
       <c r="H10">
-        <v>1.1</v>
+        <v>1.11</v>
       </c>
       <c r="I10">
-        <v>1.74</v>
+        <v>1.71</v>
       </c>
       <c r="J10">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="K10">
         <v>410</v>
@@ -3467,10 +3467,10 @@
         <v>1.01</v>
       </c>
       <c r="V10">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="W10">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3664,7 +3664,7 @@
         <v>3.15</v>
       </c>
       <c r="G11">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="H11">
         <v>2.18</v>
@@ -3673,10 +3673,10 @@
         <v>2.2</v>
       </c>
       <c r="J11">
-        <v>3.5</v>
+        <v>3.55</v>
       </c>
       <c r="K11">
-        <v>4.6</v>
+        <v>4.3</v>
       </c>
       <c r="L11">
         <v>1.01</v>
@@ -3691,16 +3691,16 @@
         <v>1.24</v>
       </c>
       <c r="P11">
-        <v>1.64</v>
+        <v>2.1</v>
       </c>
       <c r="Q11">
         <v>1.31</v>
       </c>
       <c r="R11">
-        <v>1.18</v>
+        <v>1.31</v>
       </c>
       <c r="S11">
-        <v>1.26</v>
+        <v>1.03</v>
       </c>
       <c r="T11">
         <v>1.01</v>
@@ -3906,16 +3906,16 @@
         <v>1.58</v>
       </c>
       <c r="G12">
-        <v>1.77</v>
+        <v>1.74</v>
       </c>
       <c r="H12">
         <v>4.7</v>
       </c>
       <c r="I12">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="J12">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="K12">
         <v>6.6</v>
@@ -3927,16 +3927,16 @@
         <v>1.03</v>
       </c>
       <c r="N12">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="O12">
         <v>1.15</v>
       </c>
       <c r="P12">
-        <v>2.52</v>
+        <v>2.66</v>
       </c>
       <c r="Q12">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="R12">
         <v>1.63</v>
@@ -3954,7 +3954,7 @@
         <v>1.19</v>
       </c>
       <c r="W12">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="X12">
         <v>1000</v>
@@ -4145,58 +4145,58 @@
         <v>229</v>
       </c>
       <c r="F13">
-        <v>2.62</v>
+        <v>2.54</v>
       </c>
       <c r="G13">
-        <v>3.15</v>
+        <v>2.7</v>
       </c>
       <c r="H13">
-        <v>2.58</v>
+        <v>2.72</v>
       </c>
       <c r="I13">
         <v>3.05</v>
       </c>
       <c r="J13">
-        <v>2.76</v>
+        <v>3.35</v>
       </c>
       <c r="K13">
-        <v>3.8</v>
+        <v>4.2</v>
       </c>
       <c r="L13">
         <v>1.29</v>
       </c>
       <c r="M13">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="N13">
-        <v>3.5</v>
+        <v>3.35</v>
       </c>
       <c r="O13">
-        <v>1.29</v>
+        <v>1.22</v>
       </c>
       <c r="P13">
-        <v>1.91</v>
+        <v>1.92</v>
       </c>
       <c r="Q13">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="R13">
-        <v>1.33</v>
+        <v>1.28</v>
       </c>
       <c r="S13">
-        <v>2.88</v>
+        <v>3.1</v>
       </c>
       <c r="T13">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="U13">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="V13">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="W13">
-        <v>1.47</v>
+        <v>1.58</v>
       </c>
       <c r="X13">
         <v>1000</v>
@@ -4387,28 +4387,28 @@
         <v>230</v>
       </c>
       <c r="F14">
-        <v>2.42</v>
+        <v>2.44</v>
       </c>
       <c r="G14">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="H14">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="I14">
-        <v>3.05</v>
+        <v>2.98</v>
       </c>
       <c r="J14">
-        <v>3.65</v>
+        <v>1.1</v>
       </c>
       <c r="K14">
-        <v>5.2</v>
+        <v>110</v>
       </c>
       <c r="L14">
         <v>1.01</v>
       </c>
       <c r="M14">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N14">
         <v>2.3</v>
@@ -4420,13 +4420,13 @@
         <v>2.3</v>
       </c>
       <c r="Q14">
-        <v>1.53</v>
+        <v>1.01</v>
       </c>
       <c r="R14">
         <v>1.58</v>
       </c>
       <c r="S14">
-        <v>2.28</v>
+        <v>1.01</v>
       </c>
       <c r="T14">
         <v>1.01</v>
@@ -4435,10 +4435,10 @@
         <v>1.01</v>
       </c>
       <c r="V14">
-        <v>1.48</v>
+        <v>1.53</v>
       </c>
       <c r="W14">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="X14">
         <v>1000</v>
@@ -4629,22 +4629,22 @@
         <v>231</v>
       </c>
       <c r="F15">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="G15">
         <v>2.54</v>
       </c>
       <c r="H15">
-        <v>2.66</v>
+        <v>2.72</v>
       </c>
       <c r="I15">
-        <v>3.85</v>
+        <v>3.8</v>
       </c>
       <c r="J15">
         <v>3.2</v>
       </c>
       <c r="K15">
-        <v>7</v>
+        <v>4.2</v>
       </c>
       <c r="L15">
         <v>1.01</v>
@@ -4671,7 +4671,7 @@
         <v>2.64</v>
       </c>
       <c r="T15">
-        <v>1.01</v>
+        <v>1.52</v>
       </c>
       <c r="U15">
         <v>1.01</v>
@@ -4874,13 +4874,13 @@
         <v>1.98</v>
       </c>
       <c r="G16">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="H16">
         <v>3.75</v>
       </c>
       <c r="I16">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="J16">
         <v>3.8</v>
@@ -4895,7 +4895,7 @@
         <v>1.05</v>
       </c>
       <c r="N16">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="O16">
         <v>1.27</v>
@@ -4904,10 +4904,10 @@
         <v>2.08</v>
       </c>
       <c r="Q16">
-        <v>1.78</v>
+        <v>1.66</v>
       </c>
       <c r="R16">
-        <v>1.43</v>
+        <v>1.42</v>
       </c>
       <c r="S16">
         <v>3</v>
@@ -5113,13 +5113,13 @@
         <v>233</v>
       </c>
       <c r="F17">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="G17">
         <v>970</v>
       </c>
       <c r="H17">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="I17">
         <v>970</v>
@@ -5143,7 +5143,7 @@
         <v>1.01</v>
       </c>
       <c r="P17">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="Q17">
         <v>1.26</v>
@@ -5152,7 +5152,7 @@
         <v>1.18</v>
       </c>
       <c r="S17">
-        <v>2.5</v>
+        <v>1.25</v>
       </c>
       <c r="T17">
         <v>1.01</v>
@@ -5161,10 +5161,10 @@
         <v>1.01</v>
       </c>
       <c r="V17">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="W17">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X17">
         <v>1000</v>
@@ -5397,10 +5397,10 @@
         <v>2.42</v>
       </c>
       <c r="T18">
-        <v>1.01</v>
+        <v>1.51</v>
       </c>
       <c r="U18">
-        <v>1.01</v>
+        <v>2.1</v>
       </c>
       <c r="V18">
         <v>1.19</v>
@@ -5597,7 +5597,7 @@
         <v>235</v>
       </c>
       <c r="F19">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="G19">
         <v>1.75</v>
@@ -5609,10 +5609,10 @@
         <v>7.4</v>
       </c>
       <c r="J19">
-        <v>4</v>
+        <v>4.2</v>
       </c>
       <c r="K19">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="L19">
         <v>1.01</v>
@@ -5621,7 +5621,7 @@
         <v>1.03</v>
       </c>
       <c r="N19">
-        <v>1.01</v>
+        <v>2.26</v>
       </c>
       <c r="O19">
         <v>1.16</v>
@@ -5636,7 +5636,7 @@
         <v>1.51</v>
       </c>
       <c r="S19">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="T19">
         <v>1.01</v>
@@ -5648,7 +5648,7 @@
         <v>1.16</v>
       </c>
       <c r="W19">
-        <v>2.32</v>
+        <v>2.34</v>
       </c>
       <c r="X19">
         <v>1000</v>
@@ -5839,7 +5839,7 @@
         <v>236</v>
       </c>
       <c r="F20">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="G20">
         <v>2.6</v>
@@ -5863,7 +5863,7 @@
         <v>1.01</v>
       </c>
       <c r="N20">
-        <v>3.8</v>
+        <v>4.1</v>
       </c>
       <c r="O20">
         <v>1.23</v>
@@ -5884,7 +5884,7 @@
         <v>1.01</v>
       </c>
       <c r="U20">
-        <v>1.01</v>
+        <v>2.16</v>
       </c>
       <c r="V20">
         <v>1.47</v>
@@ -6132,7 +6132,7 @@
         <v>1.79</v>
       </c>
       <c r="W21">
-        <v>1.37</v>
+        <v>1.36</v>
       </c>
       <c r="X21">
         <v>20</v>
@@ -6168,7 +6168,7 @@
         <v>20</v>
       </c>
       <c r="AI21">
-        <v>44</v>
+        <v>36</v>
       </c>
       <c r="AJ21">
         <v>80</v>
@@ -6186,7 +6186,7 @@
         <v>38</v>
       </c>
       <c r="AO21">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="AP21">
         <v>12</v>
@@ -6204,7 +6204,7 @@
         <v>10.5</v>
       </c>
       <c r="AU21">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="AV21">
         <v>8.199999999999999</v>
@@ -6323,22 +6323,22 @@
         <v>238</v>
       </c>
       <c r="F22">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="G22">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="H22">
-        <v>1.68</v>
+        <v>1.66</v>
       </c>
       <c r="I22">
-        <v>1.83</v>
+        <v>1.78</v>
       </c>
       <c r="J22">
         <v>4.3</v>
       </c>
       <c r="K22">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="L22">
         <v>1.01</v>
@@ -6347,34 +6347,34 @@
         <v>1.03</v>
       </c>
       <c r="N22">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="O22">
         <v>1.17</v>
       </c>
       <c r="P22">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="Q22">
-        <v>1.48</v>
+        <v>1.51</v>
       </c>
       <c r="R22">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="S22">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="T22">
-        <v>1.56</v>
+        <v>1.59</v>
       </c>
       <c r="U22">
         <v>2.42</v>
       </c>
       <c r="V22">
-        <v>2.2</v>
+        <v>2.26</v>
       </c>
       <c r="W22">
-        <v>1.25</v>
+        <v>1.23</v>
       </c>
       <c r="X22">
         <v>32</v>
@@ -6383,10 +6383,10 @@
         <v>16</v>
       </c>
       <c r="Z22">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AA22">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AB22">
         <v>29</v>
@@ -6401,7 +6401,7 @@
         <v>17</v>
       </c>
       <c r="AF22">
-        <v>42</v>
+        <v>55</v>
       </c>
       <c r="AG22">
         <v>20</v>
@@ -6428,7 +6428,7 @@
         <v>42</v>
       </c>
       <c r="AO22">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AP22">
         <v>20</v>
@@ -6455,7 +6455,7 @@
         <v>11.5</v>
       </c>
       <c r="AX22">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="AY22">
         <v>14</v>
@@ -6467,7 +6467,7 @@
         <v>18.5</v>
       </c>
       <c r="BB22">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BC22">
         <v>1.01</v>
@@ -6479,7 +6479,7 @@
         <v>1.01</v>
       </c>
       <c r="BF22">
-        <v>1.02</v>
+        <v>1.01</v>
       </c>
       <c r="BG22">
         <v>5.9</v>
@@ -6497,7 +6497,7 @@
         <v>1.01</v>
       </c>
       <c r="BL22">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BM22">
         <v>1.01</v>
@@ -6521,10 +6521,10 @@
         <v>1.01</v>
       </c>
       <c r="BT22">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BU22">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BV22">
         <v>13</v>
@@ -6539,7 +6539,7 @@
         <v>1.01</v>
       </c>
       <c r="BZ22">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="CA22">
         <v>1.01</v>
@@ -6565,22 +6565,22 @@
         <v>239</v>
       </c>
       <c r="F23">
-        <v>1.23</v>
+        <v>1.08</v>
       </c>
       <c r="G23">
         <v>110</v>
       </c>
       <c r="H23">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="I23">
         <v>110</v>
       </c>
       <c r="J23">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="K23">
-        <v>5.9</v>
+        <v>310</v>
       </c>
       <c r="L23">
         <v>1.01</v>
@@ -6589,7 +6589,7 @@
         <v>1.02</v>
       </c>
       <c r="N23">
-        <v>5.3</v>
+        <v>1.2</v>
       </c>
       <c r="O23">
         <v>1.13</v>
@@ -6613,10 +6613,10 @@
         <v>1.01</v>
       </c>
       <c r="V23">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="W23">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X23">
         <v>1000</v>
@@ -6807,13 +6807,13 @@
         <v>240</v>
       </c>
       <c r="F24">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="G24">
         <v>970</v>
       </c>
       <c r="H24">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="I24">
         <v>970</v>
@@ -6855,10 +6855,10 @@
         <v>1.01</v>
       </c>
       <c r="V24">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="W24">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X24">
         <v>1000</v>
@@ -7049,19 +7049,19 @@
         <v>241</v>
       </c>
       <c r="F25">
-        <v>1.08</v>
+        <v>1.28</v>
       </c>
       <c r="G25">
         <v>970</v>
       </c>
       <c r="H25">
-        <v>1.4</v>
+        <v>1.41</v>
       </c>
       <c r="I25">
         <v>110</v>
       </c>
       <c r="J25">
-        <v>1.1</v>
+        <v>3.35</v>
       </c>
       <c r="K25">
         <v>410</v>
@@ -7073,7 +7073,7 @@
         <v>1.01</v>
       </c>
       <c r="N25">
-        <v>1.23</v>
+        <v>3.3</v>
       </c>
       <c r="O25">
         <v>1.01</v>
@@ -7085,10 +7085,10 @@
         <v>1.29</v>
       </c>
       <c r="R25">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="S25">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="T25">
         <v>1.01</v>
@@ -7097,10 +7097,10 @@
         <v>1.01</v>
       </c>
       <c r="V25">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="W25">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X25">
         <v>1000</v>
@@ -7294,7 +7294,7 @@
         <v>2.18</v>
       </c>
       <c r="G26">
-        <v>2.48</v>
+        <v>2.52</v>
       </c>
       <c r="H26">
         <v>3.2</v>
@@ -7315,13 +7315,13 @@
         <v>1.07</v>
       </c>
       <c r="N26">
-        <v>3.15</v>
+        <v>3.45</v>
       </c>
       <c r="O26">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="P26">
-        <v>1.75</v>
+        <v>1.76</v>
       </c>
       <c r="Q26">
         <v>1.86</v>
@@ -7330,7 +7330,7 @@
         <v>1.29</v>
       </c>
       <c r="S26">
-        <v>3.3</v>
+        <v>3.25</v>
       </c>
       <c r="T26">
         <v>1.76</v>
@@ -7342,7 +7342,7 @@
         <v>1.32</v>
       </c>
       <c r="W26">
-        <v>1.67</v>
+        <v>1.66</v>
       </c>
       <c r="X26">
         <v>16</v>
@@ -7536,16 +7536,16 @@
         <v>3.9</v>
       </c>
       <c r="G27">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="H27">
-        <v>1.91</v>
+        <v>1.88</v>
       </c>
       <c r="I27">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="J27">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="K27">
         <v>4.5</v>
@@ -7557,31 +7557,31 @@
         <v>1.03</v>
       </c>
       <c r="N27">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="O27">
-        <v>1.2</v>
+        <v>1.18</v>
       </c>
       <c r="P27">
-        <v>2.6</v>
+        <v>2.66</v>
       </c>
       <c r="Q27">
+        <v>1.55</v>
+      </c>
+      <c r="R27">
+        <v>1.66</v>
+      </c>
+      <c r="S27">
+        <v>2.38</v>
+      </c>
+      <c r="T27">
         <v>1.58</v>
       </c>
-      <c r="R27">
-        <v>1.64</v>
-      </c>
-      <c r="S27">
-        <v>2.44</v>
-      </c>
-      <c r="T27">
-        <v>1.59</v>
-      </c>
       <c r="U27">
-        <v>2.6</v>
+        <v>2.64</v>
       </c>
       <c r="V27">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="W27">
         <v>1.32</v>
@@ -7596,16 +7596,16 @@
         <v>15</v>
       </c>
       <c r="AA27">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AB27">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AC27">
+        <v>11</v>
+      </c>
+      <c r="AD27">
         <v>10.5</v>
-      </c>
-      <c r="AD27">
-        <v>11</v>
       </c>
       <c r="AE27">
         <v>17.5</v>
@@ -7614,7 +7614,7 @@
         <v>34</v>
       </c>
       <c r="AG27">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="AH27">
         <v>16</v>
@@ -7626,37 +7626,37 @@
         <v>85</v>
       </c>
       <c r="AK27">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AL27">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="AM27">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="AN27">
-        <v>32</v>
+        <v>29</v>
       </c>
       <c r="AO27">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AP27">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AQ27">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AR27">
         <v>13</v>
       </c>
       <c r="AS27">
+        <v>20</v>
+      </c>
+      <c r="AT27">
         <v>19.5</v>
       </c>
-      <c r="AT27">
-        <v>18</v>
-      </c>
       <c r="AU27">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="AV27">
         <v>9.6</v>
@@ -7665,34 +7665,34 @@
         <v>15.5</v>
       </c>
       <c r="AX27">
-        <v>27</v>
+        <v>32</v>
       </c>
       <c r="AY27">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AZ27">
         <v>14.5</v>
       </c>
       <c r="BA27">
-        <v>19.5</v>
+        <v>22</v>
       </c>
       <c r="BB27">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="BC27">
-        <v>29</v>
+        <v>34</v>
       </c>
       <c r="BD27">
         <v>34</v>
       </c>
       <c r="BE27">
-        <v>30</v>
+        <v>50</v>
       </c>
       <c r="BF27">
-        <v>22</v>
+        <v>19.5</v>
       </c>
       <c r="BG27">
-        <v>7.8</v>
+        <v>7.4</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7775,22 +7775,22 @@
         <v>244</v>
       </c>
       <c r="F28">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G28">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H28">
-        <v>3.1</v>
+        <v>3.25</v>
       </c>
       <c r="I28">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="J28">
         <v>3.8</v>
       </c>
       <c r="K28">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="L28">
         <v>1.01</v>
@@ -7799,142 +7799,142 @@
         <v>1.05</v>
       </c>
       <c r="N28">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="O28">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P28">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q28">
-        <v>1.74</v>
+        <v>1.81</v>
       </c>
       <c r="R28">
-        <v>1.43</v>
+        <v>1.45</v>
       </c>
       <c r="S28">
-        <v>2.8</v>
+        <v>2.86</v>
       </c>
       <c r="T28">
-        <v>1.58</v>
+        <v>1.67</v>
       </c>
       <c r="U28">
-        <v>2.24</v>
+        <v>2.38</v>
       </c>
       <c r="V28">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="W28">
         <v>1.76</v>
       </c>
       <c r="X28">
-        <v>85</v>
+        <v>19</v>
       </c>
       <c r="Y28">
         <v>970</v>
       </c>
       <c r="Z28">
-        <v>110</v>
+        <v>29</v>
       </c>
       <c r="AA28">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB28">
         <v>970</v>
       </c>
       <c r="AC28">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="AD28">
+        <v>14.5</v>
+      </c>
+      <c r="AE28">
+        <v>42</v>
+      </c>
+      <c r="AF28">
+        <v>50</v>
+      </c>
+      <c r="AG28">
+        <v>11.5</v>
+      </c>
+      <c r="AH28">
+        <v>17</v>
+      </c>
+      <c r="AI28">
+        <v>50</v>
+      </c>
+      <c r="AJ28">
+        <v>34</v>
+      </c>
+      <c r="AK28">
+        <v>26</v>
+      </c>
+      <c r="AL28">
+        <v>38</v>
+      </c>
+      <c r="AM28">
+        <v>90</v>
+      </c>
+      <c r="AN28">
+        <v>970</v>
+      </c>
+      <c r="AO28">
+        <v>36</v>
+      </c>
+      <c r="AP28">
+        <v>5.6</v>
+      </c>
+      <c r="AQ28">
+        <v>13</v>
+      </c>
+      <c r="AR28">
+        <v>19.5</v>
+      </c>
+      <c r="AS28">
+        <v>7.6</v>
+      </c>
+      <c r="AT28">
+        <v>10.5</v>
+      </c>
+      <c r="AU28">
+        <v>5.9</v>
+      </c>
+      <c r="AV28">
         <v>12.5</v>
       </c>
-      <c r="AD28">
-        <v>970</v>
-      </c>
-      <c r="AE28">
-        <v>1000</v>
-      </c>
-      <c r="AF28">
-        <v>80</v>
-      </c>
-      <c r="AG28">
-        <v>970</v>
-      </c>
-      <c r="AH28">
-        <v>970</v>
-      </c>
-      <c r="AI28">
-        <v>1000</v>
-      </c>
-      <c r="AJ28">
-        <v>1000</v>
-      </c>
-      <c r="AK28">
-        <v>150</v>
-      </c>
-      <c r="AL28">
-        <v>1000</v>
-      </c>
-      <c r="AM28">
-        <v>1000</v>
-      </c>
-      <c r="AN28">
-        <v>1000</v>
-      </c>
-      <c r="AO28">
-        <v>1000</v>
-      </c>
-      <c r="AP28">
-        <v>1.23</v>
-      </c>
-      <c r="AQ28">
-        <v>1.23</v>
-      </c>
-      <c r="AR28">
-        <v>4.9</v>
-      </c>
-      <c r="AS28">
-        <v>11.5</v>
-      </c>
-      <c r="AT28">
-        <v>9.199999999999999</v>
-      </c>
-      <c r="AU28">
-        <v>6.2</v>
-      </c>
-      <c r="AV28">
-        <v>9.199999999999999</v>
-      </c>
       <c r="AW28">
-        <v>9.6</v>
+        <v>28</v>
       </c>
       <c r="AX28">
-        <v>1.23</v>
+        <v>13</v>
       </c>
       <c r="AY28">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AZ28">
-        <v>1.23</v>
+        <v>14.5</v>
       </c>
       <c r="BA28">
-        <v>11</v>
+        <v>34</v>
       </c>
       <c r="BB28">
-        <v>10</v>
+        <v>23</v>
       </c>
       <c r="BC28">
-        <v>5.8</v>
+        <v>17</v>
       </c>
       <c r="BD28">
-        <v>9.800000000000001</v>
+        <v>25</v>
       </c>
       <c r="BE28">
-        <v>14.5</v>
+        <v>5</v>
       </c>
       <c r="BF28">
-        <v>1.25</v>
+        <v>12.5</v>
       </c>
       <c r="BG28">
-        <v>1.25</v>
+        <v>23</v>
       </c>
       <c r="BH28">
         <v>1000</v>
@@ -8020,19 +8020,19 @@
         <v>2.12</v>
       </c>
       <c r="G29">
-        <v>2.34</v>
+        <v>2.26</v>
       </c>
       <c r="H29">
-        <v>3.35</v>
+        <v>3.3</v>
       </c>
       <c r="I29">
+        <v>3.7</v>
+      </c>
+      <c r="J29">
+        <v>3.6</v>
+      </c>
+      <c r="K29">
         <v>3.9</v>
-      </c>
-      <c r="J29">
-        <v>3.55</v>
-      </c>
-      <c r="K29">
-        <v>3.8</v>
       </c>
       <c r="L29">
         <v>1.27</v>
@@ -8053,31 +8053,31 @@
         <v>1.76</v>
       </c>
       <c r="R29">
-        <v>1.45</v>
+        <v>1.43</v>
       </c>
       <c r="S29">
         <v>2.88</v>
       </c>
       <c r="T29">
-        <v>1.6</v>
+        <v>1.64</v>
       </c>
       <c r="U29">
-        <v>2.16</v>
+        <v>2.4</v>
       </c>
       <c r="V29">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="W29">
-        <v>1.75</v>
+        <v>1.79</v>
       </c>
       <c r="X29">
-        <v>75</v>
+        <v>150</v>
       </c>
       <c r="Y29">
         <v>970</v>
       </c>
       <c r="Z29">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="AA29">
         <v>1000</v>
@@ -8098,10 +8098,10 @@
         <v>970</v>
       </c>
       <c r="AG29">
-        <v>21</v>
+        <v>970</v>
       </c>
       <c r="AH29">
-        <v>970</v>
+        <v>1000</v>
       </c>
       <c r="AI29">
         <v>1000</v>
@@ -8110,7 +8110,7 @@
         <v>1000</v>
       </c>
       <c r="AK29">
-        <v>160</v>
+        <v>230</v>
       </c>
       <c r="AL29">
         <v>1000</v>
@@ -8125,58 +8125,58 @@
         <v>1000</v>
       </c>
       <c r="AP29">
-        <v>1.31</v>
+        <v>1.24</v>
       </c>
       <c r="AQ29">
-        <v>1.32</v>
+        <v>1.24</v>
       </c>
       <c r="AR29">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="AS29">
-        <v>14</v>
+        <v>7.2</v>
       </c>
       <c r="AT29">
+        <v>1.24</v>
+      </c>
+      <c r="AU29">
+        <v>1.1</v>
+      </c>
+      <c r="AV29">
+        <v>1.24</v>
+      </c>
+      <c r="AW29">
+        <v>6.6</v>
+      </c>
+      <c r="AX29">
+        <v>1.24</v>
+      </c>
+      <c r="AY29">
+        <v>1.18</v>
+      </c>
+      <c r="AZ29">
+        <v>1.25</v>
+      </c>
+      <c r="BA29">
+        <v>6.8</v>
+      </c>
+      <c r="BB29">
+        <v>6</v>
+      </c>
+      <c r="BC29">
+        <v>12.5</v>
+      </c>
+      <c r="BD29">
+        <v>6.4</v>
+      </c>
+      <c r="BE29">
         <v>7.6</v>
       </c>
-      <c r="AU29">
-        <v>1.17</v>
-      </c>
-      <c r="AV29">
-        <v>1.32</v>
-      </c>
-      <c r="AW29">
-        <v>11</v>
-      </c>
-      <c r="AX29">
-        <v>1.32</v>
-      </c>
-      <c r="AY29">
-        <v>1.26</v>
-      </c>
-      <c r="AZ29">
-        <v>1.32</v>
-      </c>
-      <c r="BA29">
-        <v>12.5</v>
-      </c>
-      <c r="BB29">
-        <v>9.4</v>
-      </c>
-      <c r="BC29">
-        <v>6.2</v>
-      </c>
-      <c r="BD29">
-        <v>11</v>
-      </c>
-      <c r="BE29">
-        <v>16</v>
-      </c>
       <c r="BF29">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="BG29">
-        <v>1.34</v>
+        <v>1.25</v>
       </c>
       <c r="BH29">
         <v>1000</v>
@@ -8262,7 +8262,7 @@
         <v>2.08</v>
       </c>
       <c r="G30">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="H30">
         <v>3.6</v>
@@ -8271,10 +8271,10 @@
         <v>3.8</v>
       </c>
       <c r="J30">
-        <v>3.6</v>
+        <v>3.75</v>
       </c>
       <c r="K30">
-        <v>4.2</v>
+        <v>4</v>
       </c>
       <c r="L30">
         <v>1.01</v>
@@ -8292,7 +8292,7 @@
         <v>2.12</v>
       </c>
       <c r="Q30">
-        <v>1.72</v>
+        <v>1.66</v>
       </c>
       <c r="R30">
         <v>1.44</v>
@@ -8301,7 +8301,7 @@
         <v>2.66</v>
       </c>
       <c r="T30">
-        <v>1.57</v>
+        <v>1.6</v>
       </c>
       <c r="U30">
         <v>2.26</v>
@@ -8319,7 +8319,7 @@
         <v>970</v>
       </c>
       <c r="Z30">
-        <v>120</v>
+        <v>130</v>
       </c>
       <c r="AA30">
         <v>1000</v>
@@ -8328,7 +8328,7 @@
         <v>970</v>
       </c>
       <c r="AC30">
-        <v>9.800000000000001</v>
+        <v>13</v>
       </c>
       <c r="AD30">
         <v>970</v>
@@ -8352,7 +8352,7 @@
         <v>1000</v>
       </c>
       <c r="AK30">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AL30">
         <v>1000</v>
@@ -8367,58 +8367,58 @@
         <v>1000</v>
       </c>
       <c r="AP30">
-        <v>1.27</v>
+        <v>1.23</v>
       </c>
       <c r="AQ30">
-        <v>1.33</v>
+        <v>12</v>
       </c>
       <c r="AR30">
-        <v>5.8</v>
+        <v>6.2</v>
       </c>
       <c r="AS30">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="AT30">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AU30">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="AV30">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AW30">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AX30">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="AY30">
-        <v>1.32</v>
+        <v>1.28</v>
       </c>
       <c r="AZ30">
-        <v>1.33</v>
+        <v>1.29</v>
       </c>
       <c r="BA30">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BB30">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="BC30">
-        <v>1.34</v>
+        <v>1.3</v>
       </c>
       <c r="BD30">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="BE30">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BF30">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="BG30">
-        <v>1.35</v>
+        <v>1.31</v>
       </c>
       <c r="BH30">
         <v>1000</v>
@@ -8501,19 +8501,19 @@
         <v>247</v>
       </c>
       <c r="F31">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="G31">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="H31">
         <v>3.85</v>
       </c>
       <c r="I31">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J31">
-        <v>3.95</v>
+        <v>4</v>
       </c>
       <c r="K31">
         <v>4.3</v>
@@ -8549,10 +8549,10 @@
         <v>2.54</v>
       </c>
       <c r="V31">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W31">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="X31">
         <v>28</v>
@@ -8642,7 +8642,7 @@
         <v>14</v>
       </c>
       <c r="BA31">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BB31">
         <v>19</v>
@@ -8654,7 +8654,7 @@
         <v>18.5</v>
       </c>
       <c r="BE31">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="BF31">
         <v>8.4</v>
@@ -8687,7 +8687,7 @@
         <v>3.9</v>
       </c>
       <c r="BP31">
-        <v>13</v>
+        <v>15.5</v>
       </c>
       <c r="BQ31">
         <v>1.01</v>
@@ -8749,7 +8749,7 @@
         <v>4.1</v>
       </c>
       <c r="H32">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="I32">
         <v>2.32</v>
@@ -8758,31 +8758,31 @@
         <v>3.3</v>
       </c>
       <c r="K32">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="L32">
         <v>1.33</v>
       </c>
       <c r="M32">
-        <v>1.07</v>
+        <v>1.01</v>
       </c>
       <c r="N32">
-        <v>3.35</v>
+        <v>1.01</v>
       </c>
       <c r="O32">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="P32">
-        <v>1.83</v>
+        <v>1.81</v>
       </c>
       <c r="Q32">
         <v>1.99</v>
       </c>
       <c r="R32">
-        <v>1.32</v>
+        <v>1.27</v>
       </c>
       <c r="S32">
-        <v>3.55</v>
+        <v>3.25</v>
       </c>
       <c r="T32">
         <v>1.8</v>
@@ -8985,13 +8985,13 @@
         <v>249</v>
       </c>
       <c r="F33">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="G33">
         <v>110</v>
       </c>
       <c r="H33">
-        <v>1.08</v>
+        <v>1.1</v>
       </c>
       <c r="I33">
         <v>110</v>
@@ -9009,13 +9009,13 @@
         <v>1.01</v>
       </c>
       <c r="N33">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="O33">
         <v>1.02</v>
       </c>
       <c r="P33">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="Q33">
         <v>1.38</v>
@@ -9033,10 +9033,10 @@
         <v>1.01</v>
       </c>
       <c r="V33">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="W33">
-        <v>1.07</v>
+        <v>1.09</v>
       </c>
       <c r="X33">
         <v>1000</v>
@@ -9236,7 +9236,7 @@
         <v>3.1</v>
       </c>
       <c r="I34">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="J34">
         <v>3.4</v>
@@ -9269,7 +9269,7 @@
         <v>3.3</v>
       </c>
       <c r="T34">
-        <v>1.68</v>
+        <v>1.72</v>
       </c>
       <c r="U34">
         <v>2.18</v>
@@ -9287,7 +9287,7 @@
         <v>970</v>
       </c>
       <c r="Z34">
-        <v>95</v>
+        <v>210</v>
       </c>
       <c r="AA34">
         <v>1000</v>
@@ -9296,7 +9296,7 @@
         <v>970</v>
       </c>
       <c r="AC34">
-        <v>9.6</v>
+        <v>970</v>
       </c>
       <c r="AD34">
         <v>970</v>
@@ -9311,7 +9311,7 @@
         <v>970</v>
       </c>
       <c r="AH34">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="AI34">
         <v>1000</v>
@@ -9335,58 +9335,58 @@
         <v>1000</v>
       </c>
       <c r="AP34">
-        <v>1.28</v>
+        <v>1.23</v>
       </c>
       <c r="AQ34">
+        <v>1.24</v>
+      </c>
+      <c r="AR34">
+        <v>5.8</v>
+      </c>
+      <c r="AS34">
+        <v>11.5</v>
+      </c>
+      <c r="AT34">
+        <v>1.23</v>
+      </c>
+      <c r="AU34">
+        <v>1.09</v>
+      </c>
+      <c r="AV34">
+        <v>1.24</v>
+      </c>
+      <c r="AW34">
         <v>10</v>
       </c>
-      <c r="AR34">
-        <v>5.3</v>
-      </c>
-      <c r="AS34">
-        <v>16.5</v>
-      </c>
-      <c r="AT34">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="AU34">
-        <v>2.72</v>
-      </c>
-      <c r="AV34">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="AW34">
-        <v>13</v>
-      </c>
       <c r="AX34">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AY34">
-        <v>1.29</v>
+        <v>1.24</v>
       </c>
       <c r="AZ34">
-        <v>13</v>
+        <v>1.24</v>
       </c>
       <c r="BA34">
-        <v>16</v>
+        <v>11.5</v>
       </c>
       <c r="BB34">
-        <v>12.5</v>
+        <v>11</v>
       </c>
       <c r="BC34">
-        <v>9.199999999999999</v>
+        <v>6.2</v>
       </c>
       <c r="BD34">
-        <v>15</v>
+        <v>10.5</v>
       </c>
       <c r="BE34">
-        <v>12</v>
+        <v>9.6</v>
       </c>
       <c r="BF34">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="BG34">
-        <v>1.32</v>
+        <v>1.25</v>
       </c>
       <c r="BH34">
         <v>1000</v>
@@ -9469,43 +9469,43 @@
         <v>251</v>
       </c>
       <c r="F35">
-        <v>1.4</v>
+        <v>1.45</v>
       </c>
       <c r="G35">
         <v>1.54</v>
       </c>
       <c r="H35">
-        <v>3.75</v>
+        <v>6.6</v>
       </c>
       <c r="I35">
-        <v>13</v>
+        <v>9.4</v>
       </c>
       <c r="J35">
         <v>4.6</v>
       </c>
       <c r="K35">
-        <v>950</v>
+        <v>6.2</v>
       </c>
       <c r="L35">
         <v>1.01</v>
       </c>
       <c r="M35">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N35">
-        <v>2.24</v>
+        <v>4</v>
       </c>
       <c r="O35">
         <v>1.19</v>
       </c>
       <c r="P35">
-        <v>2.24</v>
+        <v>2.28</v>
       </c>
       <c r="Q35">
-        <v>1.27</v>
+        <v>1.62</v>
       </c>
       <c r="R35">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="S35">
         <v>2.5</v>
@@ -9517,7 +9517,7 @@
         <v>2.04</v>
       </c>
       <c r="V35">
-        <v>1.08</v>
+        <v>1.11</v>
       </c>
       <c r="W35">
         <v>2.84</v>
@@ -9729,13 +9729,13 @@
         <v>4.4</v>
       </c>
       <c r="L36">
-        <v>1.01</v>
+        <v>1.02</v>
       </c>
       <c r="M36">
         <v>1.06</v>
       </c>
       <c r="N36">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="O36">
         <v>1.27</v>
@@ -9744,7 +9744,7 @@
         <v>1.99</v>
       </c>
       <c r="Q36">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R36">
         <v>1.39</v>
@@ -9852,7 +9852,7 @@
         <v>18</v>
       </c>
       <c r="BA36">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="BB36">
         <v>9</v>
@@ -9861,76 +9861,76 @@
         <v>8.6</v>
       </c>
       <c r="BD36">
-        <v>60</v>
+        <v>8.4</v>
       </c>
       <c r="BE36">
-        <v>7.8</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BF36">
-        <v>7.6</v>
+        <v>8.6</v>
       </c>
       <c r="BG36">
         <v>9.199999999999999</v>
       </c>
       <c r="BH36">
-        <v>1000</v>
+        <v>4.1</v>
       </c>
       <c r="BI36">
-        <v>1.01</v>
+        <v>2.82</v>
       </c>
       <c r="BJ36">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BK36">
-        <v>1.01</v>
+        <v>3.5</v>
       </c>
       <c r="BL36">
         <v>1000</v>
       </c>
       <c r="BM36">
-        <v>1.01</v>
+        <v>4.7</v>
       </c>
       <c r="BN36">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BO36">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BP36">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="BQ36">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BR36">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BS36">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BT36">
-        <v>1000</v>
+        <v>5</v>
       </c>
       <c r="BU36">
-        <v>1.01</v>
+        <v>3.35</v>
       </c>
       <c r="BV36">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BW36">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BX36">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BY36">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BZ36">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="CA36">
-        <v>1.01</v>
+        <v>4.1</v>
       </c>
       <c r="CB36" t="s">
         <v>291</v>
@@ -9959,10 +9959,10 @@
         <v>8.800000000000001</v>
       </c>
       <c r="H37">
-        <v>1.51</v>
+        <v>1.5</v>
       </c>
       <c r="I37">
-        <v>1.53</v>
+        <v>1.52</v>
       </c>
       <c r="J37">
         <v>4.4</v>
@@ -9980,7 +9980,7 @@
         <v>3.6</v>
       </c>
       <c r="O37">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="P37">
         <v>1.87</v>
@@ -9989,19 +9989,19 @@
         <v>2.08</v>
       </c>
       <c r="R37">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S37">
         <v>3.9</v>
       </c>
       <c r="T37">
-        <v>2.28</v>
+        <v>2.3</v>
       </c>
       <c r="U37">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V37">
-        <v>2.9</v>
+        <v>2.92</v>
       </c>
       <c r="W37">
         <v>1.12</v>
@@ -10013,16 +10013,16 @@
         <v>7</v>
       </c>
       <c r="Z37">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="AA37">
         <v>12.5</v>
       </c>
       <c r="AB37">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AC37">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD37">
         <v>10.5</v>
@@ -10052,10 +10052,10 @@
         <v>160</v>
       </c>
       <c r="AM37">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="AN37">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="AO37">
         <v>9.4</v>
@@ -10064,7 +10064,7 @@
         <v>12</v>
       </c>
       <c r="AQ37">
-        <v>6.6</v>
+        <v>6.4</v>
       </c>
       <c r="AR37">
         <v>7</v>
@@ -10073,7 +10073,7 @@
         <v>11.5</v>
       </c>
       <c r="AT37">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU37">
         <v>9.199999999999999</v>
@@ -10091,13 +10091,13 @@
         <v>30</v>
       </c>
       <c r="AZ37">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="BA37">
         <v>42</v>
       </c>
       <c r="BB37">
-        <v>19.5</v>
+        <v>18.5</v>
       </c>
       <c r="BC37">
         <v>44</v>
@@ -10106,13 +10106,13 @@
         <v>44</v>
       </c>
       <c r="BE37">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="BF37">
-        <v>16.5</v>
+        <v>18</v>
       </c>
       <c r="BG37">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="BH37">
         <v>970</v>
@@ -10195,7 +10195,7 @@
         <v>254</v>
       </c>
       <c r="F38">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="G38">
         <v>2.04</v>
@@ -10207,7 +10207,7 @@
         <v>3.8</v>
       </c>
       <c r="J38">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="K38">
         <v>4.5</v>
@@ -10222,10 +10222,10 @@
         <v>5.8</v>
       </c>
       <c r="O38">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P38">
-        <v>2.62</v>
+        <v>2.64</v>
       </c>
       <c r="Q38">
         <v>1.56</v>
@@ -10246,7 +10246,7 @@
         <v>1.36</v>
       </c>
       <c r="W38">
-        <v>1.97</v>
+        <v>1.96</v>
       </c>
       <c r="X38">
         <v>28</v>
@@ -10294,7 +10294,7 @@
         <v>40</v>
       </c>
       <c r="AM38">
-        <v>530</v>
+        <v>440</v>
       </c>
       <c r="AN38">
         <v>8.800000000000001</v>
@@ -10312,10 +10312,10 @@
         <v>19.5</v>
       </c>
       <c r="AS38">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="AT38">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU38">
         <v>9.199999999999999</v>
@@ -10333,7 +10333,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ38">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BA38">
         <v>22</v>
@@ -10348,7 +10348,7 @@
         <v>17.5</v>
       </c>
       <c r="BE38">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BF38">
         <v>8.199999999999999</v>
@@ -10467,10 +10467,10 @@
         <v>1.31</v>
       </c>
       <c r="P39">
-        <v>1.96</v>
+        <v>1.95</v>
       </c>
       <c r="Q39">
-        <v>1.92</v>
+        <v>1.84</v>
       </c>
       <c r="R39">
         <v>1.37</v>
@@ -10700,7 +10700,7 @@
         <v>1.01</v>
       </c>
       <c r="M40">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N40">
         <v>2.6</v>
@@ -10921,13 +10921,13 @@
         <v>257</v>
       </c>
       <c r="F41">
-        <v>1.57</v>
+        <v>1.58</v>
       </c>
       <c r="G41">
         <v>1.63</v>
       </c>
       <c r="H41">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="I41">
         <v>6.2</v>
@@ -10942,37 +10942,37 @@
         <v>1.01</v>
       </c>
       <c r="M41">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N41">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="O41">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="P41">
-        <v>2.56</v>
+        <v>2.52</v>
       </c>
       <c r="Q41">
-        <v>1.51</v>
+        <v>1.52</v>
       </c>
       <c r="R41">
         <v>1.61</v>
       </c>
       <c r="S41">
-        <v>2.38</v>
+        <v>2.4</v>
       </c>
       <c r="T41">
-        <v>1.7</v>
+        <v>1.64</v>
       </c>
       <c r="U41">
-        <v>2.28</v>
+        <v>2.16</v>
       </c>
       <c r="V41">
         <v>1.19</v>
       </c>
       <c r="W41">
-        <v>2.56</v>
+        <v>2.58</v>
       </c>
       <c r="X41">
         <v>1000</v>
@@ -10981,7 +10981,7 @@
         <v>120</v>
       </c>
       <c r="Z41">
-        <v>190</v>
+        <v>160</v>
       </c>
       <c r="AA41">
         <v>1000</v>
@@ -10993,7 +10993,7 @@
         <v>970</v>
       </c>
       <c r="AD41">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="AE41">
         <v>85</v>
@@ -11005,7 +11005,7 @@
         <v>11</v>
       </c>
       <c r="AH41">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AI41">
         <v>1000</v>
@@ -11029,58 +11029,58 @@
         <v>1000</v>
       </c>
       <c r="AP41">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="AQ41">
-        <v>5.2</v>
+        <v>4.4</v>
       </c>
       <c r="AR41">
+        <v>2.12</v>
+      </c>
+      <c r="AS41">
         <v>2.14</v>
       </c>
-      <c r="AS41">
-        <v>2.16</v>
-      </c>
       <c r="AT41">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AU41">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AV41">
         <v>18</v>
       </c>
       <c r="AW41">
-        <v>12.5</v>
+        <v>6.4</v>
       </c>
       <c r="AX41">
-        <v>8.800000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="AY41">
         <v>8.4</v>
       </c>
       <c r="AZ41">
-        <v>4.6</v>
+        <v>13</v>
       </c>
       <c r="BA41">
-        <v>10.5</v>
+        <v>6.6</v>
       </c>
       <c r="BB41">
-        <v>1.92</v>
+        <v>1.91</v>
       </c>
       <c r="BC41">
-        <v>1.91</v>
+        <v>1.9</v>
       </c>
       <c r="BD41">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="BE41">
-        <v>12.5</v>
+        <v>7.6</v>
       </c>
       <c r="BF41">
         <v>5.5</v>
       </c>
       <c r="BG41">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="BH41">
         <v>1000</v>
@@ -11163,7 +11163,7 @@
         <v>258</v>
       </c>
       <c r="F42">
-        <v>1.69</v>
+        <v>1.7</v>
       </c>
       <c r="G42">
         <v>1.74</v>
@@ -11175,7 +11175,7 @@
         <v>5.7</v>
       </c>
       <c r="J42">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="K42">
         <v>4.5</v>
@@ -11411,13 +11411,13 @@
         <v>1.21</v>
       </c>
       <c r="H43">
-        <v>12</v>
+        <v>17</v>
       </c>
       <c r="I43">
         <v>27</v>
       </c>
       <c r="J43">
-        <v>7.2</v>
+        <v>7.4</v>
       </c>
       <c r="K43">
         <v>11</v>
@@ -11429,10 +11429,10 @@
         <v>1.01</v>
       </c>
       <c r="N43">
-        <v>2.9</v>
+        <v>6.6</v>
       </c>
       <c r="O43">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="P43">
         <v>2.9</v>
@@ -11441,10 +11441,10 @@
         <v>1.43</v>
       </c>
       <c r="R43">
-        <v>1.63</v>
+        <v>1.76</v>
       </c>
       <c r="S43">
-        <v>1.71</v>
+        <v>2.1</v>
       </c>
       <c r="T43">
         <v>2.24</v>
@@ -11647,55 +11647,55 @@
         <v>260</v>
       </c>
       <c r="F44">
-        <v>1.71</v>
+        <v>1.76</v>
       </c>
       <c r="G44">
         <v>1.81</v>
       </c>
       <c r="H44">
-        <v>5.5</v>
+        <v>5.7</v>
       </c>
       <c r="I44">
-        <v>6.8</v>
+        <v>6.6</v>
       </c>
       <c r="J44">
         <v>3.55</v>
       </c>
       <c r="K44">
-        <v>3.95</v>
+        <v>3.7</v>
       </c>
       <c r="L44">
         <v>1.36</v>
       </c>
       <c r="M44">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N44">
-        <v>3</v>
+        <v>3.05</v>
       </c>
       <c r="O44">
-        <v>1.35</v>
+        <v>1.37</v>
       </c>
       <c r="P44">
+        <v>1.77</v>
+      </c>
+      <c r="Q44">
+        <v>2.02</v>
+      </c>
+      <c r="R44">
+        <v>1.28</v>
+      </c>
+      <c r="S44">
+        <v>4.1</v>
+      </c>
+      <c r="T44">
+        <v>1.01</v>
+      </c>
+      <c r="U44">
         <v>1.72</v>
       </c>
-      <c r="Q44">
-        <v>2.08</v>
-      </c>
-      <c r="R44">
-        <v>1.25</v>
-      </c>
-      <c r="S44">
-        <v>3.75</v>
-      </c>
-      <c r="T44">
-        <v>1.01</v>
-      </c>
-      <c r="U44">
-        <v>1.01</v>
-      </c>
       <c r="V44">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="W44">
         <v>2.22</v>
@@ -11904,13 +11904,13 @@
         <v>3.1</v>
       </c>
       <c r="K45">
-        <v>3.6</v>
+        <v>3.5</v>
       </c>
       <c r="L45">
         <v>1.4</v>
       </c>
       <c r="M45">
-        <v>1.09</v>
+        <v>1.1</v>
       </c>
       <c r="N45">
         <v>2.9</v>
@@ -11925,10 +11925,10 @@
         <v>2.32</v>
       </c>
       <c r="R45">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="S45">
-        <v>4.1</v>
+        <v>3.85</v>
       </c>
       <c r="T45">
         <v>1.01</v>
@@ -12131,22 +12131,22 @@
         <v>262</v>
       </c>
       <c r="F46">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="G46">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="H46">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="I46">
         <v>9</v>
       </c>
       <c r="J46">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="K46">
-        <v>5.9</v>
+        <v>6.2</v>
       </c>
       <c r="L46">
         <v>1.01</v>
@@ -12155,28 +12155,28 @@
         <v>1.02</v>
       </c>
       <c r="N46">
-        <v>6</v>
+        <v>5.3</v>
       </c>
       <c r="O46">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P46">
         <v>2.72</v>
       </c>
       <c r="Q46">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="R46">
-        <v>1.69</v>
+        <v>1.71</v>
       </c>
       <c r="S46">
-        <v>2.22</v>
+        <v>2.16</v>
       </c>
       <c r="T46">
-        <v>1.71</v>
+        <v>1.74</v>
       </c>
       <c r="U46">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="V46">
         <v>1.12</v>
@@ -12188,7 +12188,7 @@
         <v>34</v>
       </c>
       <c r="Y46">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="Z46">
         <v>85</v>
@@ -12209,7 +12209,7 @@
         <v>110</v>
       </c>
       <c r="AF46">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="AG46">
         <v>12.5</v>
@@ -12239,16 +12239,16 @@
         <v>100</v>
       </c>
       <c r="AP46">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="AQ46">
-        <v>5.2</v>
+        <v>5.4</v>
       </c>
       <c r="AR46">
         <v>18.5</v>
       </c>
       <c r="AS46">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="AT46">
         <v>10.5</v>
@@ -12257,7 +12257,7 @@
         <v>11</v>
       </c>
       <c r="AV46">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="AW46">
         <v>26</v>
@@ -12281,16 +12281,16 @@
         <v>11.5</v>
       </c>
       <c r="BD46">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="BE46">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="BF46">
         <v>4.1</v>
       </c>
       <c r="BG46">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="BH46">
         <v>1000</v>
@@ -12373,22 +12373,22 @@
         <v>263</v>
       </c>
       <c r="F47">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="G47">
-        <v>1.83</v>
+        <v>1.85</v>
       </c>
       <c r="H47">
-        <v>5.6</v>
+        <v>5.4</v>
       </c>
       <c r="I47">
-        <v>6</v>
+        <v>5.8</v>
       </c>
       <c r="J47">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="K47">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="L47">
         <v>1.01</v>
@@ -12397,16 +12397,16 @@
         <v>1.09</v>
       </c>
       <c r="N47">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="O47">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="P47">
-        <v>1.76</v>
+        <v>1.75</v>
       </c>
       <c r="Q47">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="R47">
         <v>1.28</v>
@@ -12418,37 +12418,37 @@
         <v>2.06</v>
       </c>
       <c r="U47">
-        <v>1.85</v>
+        <v>1.87</v>
       </c>
       <c r="V47">
         <v>1.2</v>
       </c>
       <c r="W47">
-        <v>2.2</v>
+        <v>2.16</v>
       </c>
       <c r="X47">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="Y47">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="Z47">
         <v>44</v>
       </c>
       <c r="AA47">
-        <v>210</v>
+        <v>170</v>
       </c>
       <c r="AB47">
-        <v>7.4</v>
+        <v>8</v>
       </c>
       <c r="AC47">
         <v>8.199999999999999</v>
       </c>
       <c r="AD47">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="AE47">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AF47">
         <v>9.800000000000001</v>
@@ -12457,7 +12457,7 @@
         <v>10.5</v>
       </c>
       <c r="AH47">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AI47">
         <v>110</v>
@@ -12466,19 +12466,19 @@
         <v>18.5</v>
       </c>
       <c r="AK47">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AL47">
-        <v>46</v>
+        <v>50</v>
       </c>
       <c r="AM47">
         <v>180</v>
       </c>
       <c r="AN47">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AO47">
-        <v>170</v>
+        <v>130</v>
       </c>
       <c r="AP47">
         <v>10</v>
@@ -12490,49 +12490,49 @@
         <v>36</v>
       </c>
       <c r="AS47">
-        <v>13.5</v>
+        <v>14</v>
       </c>
       <c r="AT47">
-        <v>6.8</v>
+        <v>7</v>
       </c>
       <c r="AU47">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="AV47">
-        <v>20</v>
+        <v>18.5</v>
       </c>
       <c r="AW47">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX47">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AY47">
-        <v>9.6</v>
+        <v>10</v>
       </c>
       <c r="AZ47">
         <v>20</v>
       </c>
       <c r="BA47">
+        <v>15</v>
+      </c>
+      <c r="BB47">
+        <v>18</v>
+      </c>
+      <c r="BC47">
+        <v>20</v>
+      </c>
+      <c r="BD47">
+        <v>42</v>
+      </c>
+      <c r="BE47">
         <v>14</v>
-      </c>
-      <c r="BB47">
-        <v>17</v>
-      </c>
-      <c r="BC47">
-        <v>19</v>
-      </c>
-      <c r="BD47">
-        <v>40</v>
-      </c>
-      <c r="BE47">
-        <v>13.5</v>
       </c>
       <c r="BF47">
         <v>13</v>
       </c>
       <c r="BG47">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BH47">
         <v>1000</v>
@@ -12627,7 +12627,7 @@
         <v>5.7</v>
       </c>
       <c r="J48">
-        <v>3.4</v>
+        <v>3.65</v>
       </c>
       <c r="K48">
         <v>6.2</v>
@@ -12881,13 +12881,13 @@
         <v>1.07</v>
       </c>
       <c r="N49">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="O49">
         <v>1.36</v>
       </c>
       <c r="P49">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="Q49">
         <v>2.04</v>
@@ -12932,7 +12932,7 @@
         <v>12.5</v>
       </c>
       <c r="AE49">
-        <v>32</v>
+        <v>44</v>
       </c>
       <c r="AF49">
         <v>19</v>
@@ -12953,16 +12953,16 @@
         <v>34</v>
       </c>
       <c r="AL49">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="AM49">
         <v>110</v>
       </c>
       <c r="AN49">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="AO49">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="AP49">
         <v>11.5</v>
@@ -13007,10 +13007,10 @@
         <v>29</v>
       </c>
       <c r="BD49">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BE49">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="BF49">
         <v>23</v>
@@ -13228,7 +13228,7 @@
         <v>18.5</v>
       </c>
       <c r="AW50">
-        <v>36</v>
+        <v>50</v>
       </c>
       <c r="AX50">
         <v>10.5</v>
@@ -13270,7 +13270,7 @@
         <v>13</v>
       </c>
       <c r="BK50">
-        <v>8.199999999999999</v>
+        <v>6.8</v>
       </c>
       <c r="BL50">
         <v>370</v>
@@ -13288,16 +13288,16 @@
         <v>22</v>
       </c>
       <c r="BQ50">
-        <v>10.5</v>
+        <v>8.6</v>
       </c>
       <c r="BR50">
         <v>55</v>
       </c>
       <c r="BS50">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BT50">
-        <v>7.6</v>
+        <v>9</v>
       </c>
       <c r="BU50">
         <v>6.6</v>
@@ -13306,19 +13306,19 @@
         <v>55</v>
       </c>
       <c r="BW50">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="BX50">
         <v>100</v>
       </c>
       <c r="BY50">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="BZ50">
         <v>65</v>
       </c>
       <c r="CA50">
-        <v>15.5</v>
+        <v>11.5</v>
       </c>
       <c r="CB50" t="s">
         <v>291</v>
@@ -13344,7 +13344,7 @@
         <v>1.45</v>
       </c>
       <c r="G51">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="H51">
         <v>4.3</v>
@@ -13380,7 +13380,7 @@
         <v>1.93</v>
       </c>
       <c r="S51">
-        <v>1.5</v>
+        <v>1.33</v>
       </c>
       <c r="T51">
         <v>1.01</v>
@@ -13392,7 +13392,7 @@
         <v>1.15</v>
       </c>
       <c r="W51">
-        <v>2.28</v>
+        <v>2.24</v>
       </c>
       <c r="X51">
         <v>1000</v>
@@ -13586,7 +13586,7 @@
         <v>1.54</v>
       </c>
       <c r="G52">
-        <v>1.75</v>
+        <v>1.73</v>
       </c>
       <c r="H52">
         <v>4.4</v>
@@ -13610,7 +13610,7 @@
         <v>2.98</v>
       </c>
       <c r="O52">
-        <v>1.1</v>
+        <v>1.09</v>
       </c>
       <c r="P52">
         <v>2.98</v>
@@ -13619,7 +13619,7 @@
         <v>1.35</v>
       </c>
       <c r="R52">
-        <v>1.79</v>
+        <v>1.88</v>
       </c>
       <c r="S52">
         <v>1.89</v>
@@ -13843,10 +13843,10 @@
         <v>4.4</v>
       </c>
       <c r="L53">
-        <v>1.4</v>
+        <v>1.46</v>
       </c>
       <c r="M53">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="N53">
         <v>2.58</v>
@@ -13987,61 +13987,61 @@
         <v>1.01</v>
       </c>
       <c r="BH53">
-        <v>1000</v>
+        <v>3.35</v>
       </c>
       <c r="BI53">
-        <v>1.01</v>
+        <v>2.52</v>
       </c>
       <c r="BJ53">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BK53">
         <v>1.01</v>
       </c>
       <c r="BL53">
-        <v>1000</v>
+        <v>290</v>
       </c>
       <c r="BM53">
         <v>1.01</v>
       </c>
       <c r="BN53">
-        <v>1000</v>
+        <v>3.85</v>
       </c>
       <c r="BO53">
-        <v>1.01</v>
+        <v>3.3</v>
       </c>
       <c r="BP53">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="BQ53">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="BR53">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="BS53">
         <v>1.01</v>
       </c>
       <c r="BT53">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BU53">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="BV53">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BW53">
         <v>1.01</v>
       </c>
       <c r="BX53">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="BY53">
         <v>1.01</v>
       </c>
       <c r="BZ53">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA53">
         <v>1.01</v>
@@ -14103,7 +14103,7 @@
         <v>1.43</v>
       </c>
       <c r="R54">
-        <v>1.61</v>
+        <v>1.55</v>
       </c>
       <c r="S54">
         <v>2.08</v>
@@ -14309,10 +14309,10 @@
         <v>271</v>
       </c>
       <c r="F55">
-        <v>1.47</v>
+        <v>1.46</v>
       </c>
       <c r="G55">
-        <v>1.49</v>
+        <v>1.48</v>
       </c>
       <c r="H55">
         <v>8</v>
@@ -14324,7 +14324,7 @@
         <v>4.9</v>
       </c>
       <c r="K55">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="L55">
         <v>1.01</v>
@@ -14348,7 +14348,7 @@
         <v>1.41</v>
       </c>
       <c r="S55">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T55">
         <v>2.06</v>
@@ -14569,28 +14569,28 @@
         <v>4</v>
       </c>
       <c r="L56">
-        <v>1.01</v>
+        <v>1.18</v>
       </c>
       <c r="M56">
         <v>1.05</v>
       </c>
       <c r="N56">
-        <v>3.85</v>
+        <v>4.5</v>
       </c>
       <c r="O56">
         <v>1.25</v>
       </c>
       <c r="P56">
-        <v>2.08</v>
+        <v>2.2</v>
       </c>
       <c r="Q56">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="R56">
-        <v>1.44</v>
+        <v>1.48</v>
       </c>
       <c r="S56">
-        <v>2.72</v>
+        <v>2.86</v>
       </c>
       <c r="T56">
         <v>1.66</v>
@@ -14680,7 +14680,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW56">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AX56">
         <v>24</v>
@@ -14793,22 +14793,22 @@
         <v>273</v>
       </c>
       <c r="F57">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="G57">
-        <v>1.99</v>
+        <v>1.98</v>
       </c>
       <c r="H57">
         <v>4.8</v>
       </c>
       <c r="I57">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J57">
         <v>3.4</v>
       </c>
       <c r="K57">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="L57">
         <v>1.48</v>
@@ -14835,16 +14835,16 @@
         <v>4.2</v>
       </c>
       <c r="T57">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="U57">
-        <v>1.8</v>
+        <v>1.82</v>
       </c>
       <c r="V57">
         <v>1.21</v>
       </c>
       <c r="W57">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X57">
         <v>11.5</v>
@@ -14913,10 +14913,10 @@
         <v>6</v>
       </c>
       <c r="AT57">
-        <v>5.4</v>
+        <v>6.2</v>
       </c>
       <c r="AU57">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="AV57">
         <v>5</v>
@@ -14928,7 +14928,7 @@
         <v>4</v>
       </c>
       <c r="AY57">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="AZ57">
         <v>5.1</v>
@@ -15035,16 +15035,16 @@
         <v>274</v>
       </c>
       <c r="F58">
-        <v>1.97</v>
+        <v>1.98</v>
       </c>
       <c r="G58">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="H58">
         <v>4.3</v>
       </c>
       <c r="I58">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="J58">
         <v>3.75</v>
@@ -15068,13 +15068,13 @@
         <v>1.96</v>
       </c>
       <c r="Q58">
-        <v>1.99</v>
+        <v>2</v>
       </c>
       <c r="R58">
         <v>1.37</v>
       </c>
       <c r="S58">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="T58">
         <v>1.85</v>
@@ -15107,10 +15107,10 @@
         <v>8.4</v>
       </c>
       <c r="AD58">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE58">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AF58">
         <v>12</v>
@@ -15152,7 +15152,7 @@
         <v>29</v>
       </c>
       <c r="AS58">
-        <v>36</v>
+        <v>80</v>
       </c>
       <c r="AT58">
         <v>8.6</v>
@@ -15167,7 +15167,7 @@
         <v>48</v>
       </c>
       <c r="AX58">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AY58">
         <v>9.6</v>
@@ -15182,7 +15182,7 @@
         <v>20</v>
       </c>
       <c r="BC58">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="BD58">
         <v>32</v>
@@ -15280,7 +15280,7 @@
         <v>4.5</v>
       </c>
       <c r="G59">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="H59">
         <v>1.86</v>
@@ -15289,16 +15289,16 @@
         <v>1.93</v>
       </c>
       <c r="J59">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="K59">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="L59">
         <v>1.32</v>
       </c>
       <c r="M59">
-        <v>1.07</v>
+        <v>1.05</v>
       </c>
       <c r="N59">
         <v>3.55</v>
@@ -15322,7 +15322,7 @@
         <v>1.87</v>
       </c>
       <c r="U59">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="V59">
         <v>2.06</v>
@@ -15528,7 +15528,7 @@
         <v>1.53</v>
       </c>
       <c r="I60">
-        <v>1.9</v>
+        <v>1.86</v>
       </c>
       <c r="J60">
         <v>3.2</v>
@@ -15567,10 +15567,10 @@
         <v>1.01</v>
       </c>
       <c r="V60">
-        <v>2.1</v>
+        <v>2.28</v>
       </c>
       <c r="W60">
-        <v>1.11</v>
+        <v>1.15</v>
       </c>
       <c r="X60">
         <v>1000</v>
@@ -15761,16 +15761,16 @@
         <v>277</v>
       </c>
       <c r="F61">
+        <v>7.2</v>
+      </c>
+      <c r="G61">
         <v>7.4</v>
       </c>
-      <c r="G61">
-        <v>7.6</v>
-      </c>
       <c r="H61">
-        <v>1.54</v>
+        <v>1.56</v>
       </c>
       <c r="I61">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="J61">
         <v>4.5</v>
@@ -15785,31 +15785,31 @@
         <v>1.06</v>
       </c>
       <c r="N61">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="O61">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P61">
         <v>2.12</v>
       </c>
       <c r="Q61">
-        <v>1.87</v>
+        <v>1.86</v>
       </c>
       <c r="R61">
         <v>1.42</v>
       </c>
       <c r="S61">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="T61">
-        <v>2</v>
+        <v>1.98</v>
       </c>
       <c r="U61">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="V61">
-        <v>2.82</v>
+        <v>2.76</v>
       </c>
       <c r="W61">
         <v>1.15</v>
@@ -15851,7 +15851,7 @@
         <v>36</v>
       </c>
       <c r="AJ61">
-        <v>290</v>
+        <v>270</v>
       </c>
       <c r="AK61">
         <v>95</v>
@@ -15866,7 +15866,7 @@
         <v>110</v>
       </c>
       <c r="AO61">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AP61">
         <v>16</v>
@@ -15911,7 +15911,7 @@
         <v>90</v>
       </c>
       <c r="BD61">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="BE61">
         <v>100</v>
@@ -15938,10 +15938,10 @@
         <v>180</v>
       </c>
       <c r="BM61">
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="BN61">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="BO61">
         <v>9.199999999999999</v>
@@ -15950,19 +15950,19 @@
         <v>65</v>
       </c>
       <c r="BQ61">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BR61">
         <v>70</v>
       </c>
       <c r="BS61">
-        <v>10.5</v>
+        <v>9.4</v>
       </c>
       <c r="BT61">
         <v>4</v>
       </c>
       <c r="BU61">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="BV61">
         <v>10.5</v>
@@ -15974,13 +15974,13 @@
         <v>27</v>
       </c>
       <c r="BY61">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="BZ61">
         <v>18.5</v>
       </c>
       <c r="CA61">
-        <v>7.4</v>
+        <v>6.8</v>
       </c>
       <c r="CB61" t="s">
         <v>291</v>
@@ -16003,22 +16003,22 @@
         <v>278</v>
       </c>
       <c r="F62">
-        <v>2</v>
+        <v>1.99</v>
       </c>
       <c r="G62">
         <v>2.12</v>
       </c>
       <c r="H62">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="I62">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="J62">
         <v>4.5</v>
       </c>
       <c r="K62">
-        <v>5.2</v>
+        <v>5</v>
       </c>
       <c r="L62">
         <v>1.01</v>
@@ -16027,10 +16027,10 @@
         <v>1.01</v>
       </c>
       <c r="N62">
-        <v>9.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="O62">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="P62">
         <v>3.85</v>
@@ -16054,10 +16054,10 @@
         <v>1.41</v>
       </c>
       <c r="W62">
-        <v>1.9</v>
+        <v>1.92</v>
       </c>
       <c r="X62">
-        <v>450</v>
+        <v>530</v>
       </c>
       <c r="Y62">
         <v>40</v>
@@ -16147,7 +16147,7 @@
         <v>17.5</v>
       </c>
       <c r="BB62">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="BC62">
         <v>16</v>
@@ -16159,7 +16159,7 @@
         <v>21</v>
       </c>
       <c r="BF62">
-        <v>5.5</v>
+        <v>5.4</v>
       </c>
       <c r="BG62">
         <v>10.5</v>
@@ -16245,16 +16245,16 @@
         <v>279</v>
       </c>
       <c r="F63">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="G63">
-        <v>1.82</v>
+        <v>1.81</v>
       </c>
       <c r="H63">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="I63">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="J63">
         <v>3.8</v>
@@ -16272,25 +16272,25 @@
         <v>3.8</v>
       </c>
       <c r="O63">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="P63">
         <v>1.85</v>
       </c>
       <c r="Q63">
-        <v>1.89</v>
+        <v>1.91</v>
       </c>
       <c r="R63">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S63">
-        <v>3.05</v>
+        <v>3.1</v>
       </c>
       <c r="T63">
-        <v>1.89</v>
+        <v>1.84</v>
       </c>
       <c r="U63">
-        <v>2.04</v>
+        <v>1.94</v>
       </c>
       <c r="V63">
         <v>1.21</v>
@@ -16359,7 +16359,7 @@
         <v>15.5</v>
       </c>
       <c r="AR63">
-        <v>34</v>
+        <v>8</v>
       </c>
       <c r="AS63">
         <v>8.4</v>
@@ -16404,7 +16404,7 @@
         <v>10.5</v>
       </c>
       <c r="BG63">
-        <v>8.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="BH63">
         <v>1000</v>
@@ -16490,19 +16490,19 @@
         <v>1.18</v>
       </c>
       <c r="G64">
-        <v>1.2</v>
+        <v>1.19</v>
       </c>
       <c r="H64">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="I64">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="J64">
-        <v>8.4</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="K64">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="L64">
         <v>1.21</v>
@@ -16514,7 +16514,7 @@
         <v>7</v>
       </c>
       <c r="O64">
-        <v>1.14</v>
+        <v>1.13</v>
       </c>
       <c r="P64">
         <v>3.05</v>
@@ -16523,10 +16523,10 @@
         <v>1.43</v>
       </c>
       <c r="R64">
-        <v>1.81</v>
+        <v>1.8</v>
       </c>
       <c r="S64">
-        <v>2</v>
+        <v>1.86</v>
       </c>
       <c r="T64">
         <v>2.16</v>
@@ -16535,10 +16535,10 @@
         <v>1.73</v>
       </c>
       <c r="V64">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="W64">
-        <v>6</v>
+        <v>6.2</v>
       </c>
       <c r="X64">
         <v>42</v>
@@ -16735,16 +16735,16 @@
         <v>1.18</v>
       </c>
       <c r="H65">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="I65">
         <v>22</v>
       </c>
       <c r="J65">
-        <v>9.800000000000001</v>
+        <v>10</v>
       </c>
       <c r="K65">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="L65">
         <v>1.21</v>
@@ -16759,7 +16759,7 @@
         <v>1.11</v>
       </c>
       <c r="P65">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="Q65">
         <v>1.35</v>
@@ -16768,7 +16768,7 @@
         <v>2.08</v>
       </c>
       <c r="S65">
-        <v>1.89</v>
+        <v>1.88</v>
       </c>
       <c r="T65">
         <v>2.06</v>
@@ -16786,7 +16786,7 @@
         <v>46</v>
       </c>
       <c r="Y65">
-        <v>80</v>
+        <v>85</v>
       </c>
       <c r="Z65">
         <v>1000</v>
@@ -16831,7 +16831,7 @@
         <v>1000</v>
       </c>
       <c r="AN65">
-        <v>2.74</v>
+        <v>2.72</v>
       </c>
       <c r="AO65">
         <v>360</v>
@@ -16846,10 +16846,10 @@
         <v>48</v>
       </c>
       <c r="AS65">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT65">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="AU65">
         <v>21</v>
@@ -16885,10 +16885,10 @@
         <v>46</v>
       </c>
       <c r="BF65">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="BG65">
-        <v>24</v>
+        <v>27</v>
       </c>
       <c r="BH65">
         <v>1000</v>
@@ -16971,7 +16971,7 @@
         <v>282</v>
       </c>
       <c r="F66">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="G66">
         <v>4.8</v>
@@ -16980,16 +16980,16 @@
         <v>1.83</v>
       </c>
       <c r="I66">
-        <v>1.94</v>
+        <v>1.93</v>
       </c>
       <c r="J66">
         <v>3.9</v>
       </c>
       <c r="K66">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="L66">
-        <v>1.33</v>
+        <v>1.31</v>
       </c>
       <c r="M66">
         <v>1.05</v>
@@ -17007,7 +17007,7 @@
         <v>1.75</v>
       </c>
       <c r="R66">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="S66">
         <v>2.9</v>
@@ -17142,7 +17142,7 @@
         <v>11</v>
       </c>
       <c r="BK66">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL66">
         <v>120</v>
@@ -17154,19 +17154,19 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BO66">
-        <v>6.2</v>
+        <v>1.01</v>
       </c>
       <c r="BP66">
         <v>40</v>
       </c>
       <c r="BQ66">
-        <v>26</v>
+        <v>1.01</v>
       </c>
       <c r="BR66">
         <v>48</v>
       </c>
       <c r="BS66">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BT66">
         <v>5.3</v>
@@ -17178,19 +17178,19 @@
         <v>14.5</v>
       </c>
       <c r="BW66">
-        <v>9.6</v>
+        <v>1.01</v>
       </c>
       <c r="BX66">
         <v>29</v>
       </c>
       <c r="BY66">
-        <v>18.5</v>
+        <v>1.01</v>
       </c>
       <c r="BZ66">
         <v>22</v>
       </c>
       <c r="CA66">
-        <v>14.5</v>
+        <v>1.01</v>
       </c>
       <c r="CB66" t="s">
         <v>291</v>
@@ -17222,7 +17222,7 @@
         <v>2.52</v>
       </c>
       <c r="I67">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="J67">
         <v>2.52</v>
@@ -17261,7 +17261,7 @@
         <v>1.01</v>
       </c>
       <c r="V67">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="W67">
         <v>1.36</v>
@@ -17455,22 +17455,22 @@
         <v>284</v>
       </c>
       <c r="F68">
-        <v>1.7</v>
+        <v>1.71</v>
       </c>
       <c r="G68">
-        <v>1.91</v>
+        <v>2.22</v>
       </c>
       <c r="H68">
         <v>5.3</v>
       </c>
       <c r="I68">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="J68">
-        <v>2.92</v>
+        <v>1.08</v>
       </c>
       <c r="K68">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="L68">
         <v>1.01</v>
@@ -17479,13 +17479,13 @@
         <v>1.01</v>
       </c>
       <c r="N68">
-        <v>2.72</v>
+        <v>2.8</v>
       </c>
       <c r="O68">
-        <v>1.45</v>
+        <v>1.01</v>
       </c>
       <c r="P68">
-        <v>1.25</v>
+        <v>1.54</v>
       </c>
       <c r="Q68">
         <v>2.24</v>
@@ -17494,7 +17494,7 @@
         <v>1.2</v>
       </c>
       <c r="S68">
-        <v>1.01</v>
+        <v>4.4</v>
       </c>
       <c r="T68">
         <v>1.01</v>
@@ -17503,10 +17503,10 @@
         <v>1.01</v>
       </c>
       <c r="V68">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="W68">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="X68">
         <v>1000</v>
@@ -17697,16 +17697,16 @@
         <v>285</v>
       </c>
       <c r="F69">
-        <v>2.46</v>
+        <v>2.48</v>
       </c>
       <c r="G69">
-        <v>2.7</v>
+        <v>2.64</v>
       </c>
       <c r="H69">
-        <v>3.5</v>
+        <v>3.45</v>
       </c>
       <c r="I69">
-        <v>3.95</v>
+        <v>3.9</v>
       </c>
       <c r="J69">
         <v>2.9</v>
@@ -17727,7 +17727,7 @@
         <v>1.59</v>
       </c>
       <c r="P69">
-        <v>1.49</v>
+        <v>1.5</v>
       </c>
       <c r="Q69">
         <v>2.84</v>
@@ -17862,7 +17862,7 @@
         <v>2.86</v>
       </c>
       <c r="BI69">
-        <v>2.22</v>
+        <v>2.2</v>
       </c>
       <c r="BJ69">
         <v>13.5</v>
@@ -17871,7 +17871,7 @@
         <v>8.800000000000001</v>
       </c>
       <c r="BL69">
-        <v>260</v>
+        <v>270</v>
       </c>
       <c r="BM69">
         <v>21</v>
@@ -17889,7 +17889,7 @@
         <v>17.5</v>
       </c>
       <c r="BR69">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="BS69">
         <v>36</v>
@@ -17957,16 +17957,16 @@
         <v>3.8</v>
       </c>
       <c r="L70">
-        <v>1.01</v>
+        <v>1.38</v>
       </c>
       <c r="M70">
         <v>1.06</v>
       </c>
       <c r="N70">
-        <v>3.7</v>
+        <v>3.85</v>
       </c>
       <c r="O70">
-        <v>1.28</v>
+        <v>1.29</v>
       </c>
       <c r="P70">
         <v>1.96</v>
@@ -17981,10 +17981,10 @@
         <v>3.2</v>
       </c>
       <c r="T70">
-        <v>1.63</v>
+        <v>1.72</v>
       </c>
       <c r="U70">
-        <v>2.02</v>
+        <v>2.14</v>
       </c>
       <c r="V70">
         <v>1.39</v>
@@ -18101,61 +18101,61 @@
         <v>1.01</v>
       </c>
       <c r="BH70">
-        <v>4.4</v>
+        <v>3.9</v>
       </c>
       <c r="BI70">
-        <v>2.8</v>
+        <v>3.1</v>
       </c>
       <c r="BJ70">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK70">
         <v>1.01</v>
       </c>
       <c r="BL70">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM70">
         <v>1.01</v>
       </c>
       <c r="BN70">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="BO70">
-        <v>1.01</v>
+        <v>4.2</v>
       </c>
       <c r="BP70">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BQ70">
         <v>1.01</v>
       </c>
       <c r="BR70">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BS70">
         <v>1.01</v>
       </c>
       <c r="BT70">
-        <v>1000</v>
+        <v>7.6</v>
       </c>
       <c r="BU70">
-        <v>1.01</v>
+        <v>5.2</v>
       </c>
       <c r="BV70">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW70">
         <v>1.01</v>
       </c>
       <c r="BX70">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="BY70">
         <v>1.01</v>
       </c>
       <c r="BZ70">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="CA70">
         <v>1.01</v>
@@ -18426,19 +18426,19 @@
         <v>1.45</v>
       </c>
       <c r="G72">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="H72">
         <v>10</v>
       </c>
       <c r="I72">
-        <v>12</v>
+        <v>11.5</v>
       </c>
       <c r="J72">
         <v>4.3</v>
       </c>
       <c r="K72">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="L72">
         <v>1.01</v>
@@ -18447,142 +18447,142 @@
         <v>1.06</v>
       </c>
       <c r="N72">
-        <v>3.25</v>
+        <v>3.05</v>
       </c>
       <c r="O72">
-        <v>1.38</v>
+        <v>1.34</v>
       </c>
       <c r="P72">
-        <v>1.77</v>
+        <v>1.72</v>
       </c>
       <c r="Q72">
-        <v>2.14</v>
+        <v>1.8</v>
       </c>
       <c r="R72">
-        <v>1.29</v>
+        <v>1.23</v>
       </c>
       <c r="S72">
-        <v>3.95</v>
+        <v>3.2</v>
       </c>
       <c r="T72">
-        <v>2.2</v>
+        <v>1.02</v>
       </c>
       <c r="U72">
-        <v>1.6</v>
+        <v>1.02</v>
       </c>
       <c r="V72">
         <v>1.09</v>
       </c>
       <c r="W72">
-        <v>3.1</v>
+        <v>3.05</v>
       </c>
       <c r="X72">
-        <v>12.5</v>
+        <v>1000</v>
       </c>
       <c r="Y72">
-        <v>26</v>
+        <v>1000</v>
       </c>
       <c r="Z72">
-        <v>130</v>
+        <v>1000</v>
       </c>
       <c r="AA72">
         <v>1000</v>
       </c>
       <c r="AB72">
-        <v>6.6</v>
+        <v>1000</v>
       </c>
       <c r="AC72">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="AD72">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="AE72">
-        <v>330</v>
+        <v>1000</v>
       </c>
       <c r="AF72">
-        <v>7.2</v>
+        <v>1000</v>
       </c>
       <c r="AG72">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AH72">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="AI72">
-        <v>270</v>
+        <v>1000</v>
       </c>
       <c r="AJ72">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="AK72">
-        <v>23</v>
+        <v>1000</v>
       </c>
       <c r="AL72">
-        <v>75</v>
+        <v>1000</v>
       </c>
       <c r="AM72">
-        <v>350</v>
+        <v>1000</v>
       </c>
       <c r="AN72">
-        <v>8.800000000000001</v>
+        <v>1000</v>
       </c>
       <c r="AO72">
         <v>1000</v>
       </c>
       <c r="AP72">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AQ72">
-        <v>7.6</v>
+        <v>1.01</v>
       </c>
       <c r="AR72">
-        <v>9.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="AS72">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="AT72">
-        <v>5.8</v>
+        <v>1.01</v>
       </c>
       <c r="AU72">
-        <v>9.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="AV72">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="AW72">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AX72">
-        <v>6.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY72">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="AZ72">
-        <v>8.199999999999999</v>
+        <v>1.01</v>
       </c>
       <c r="BA72">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BB72">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BC72">
-        <v>16.5</v>
+        <v>1.01</v>
       </c>
       <c r="BD72">
-        <v>9.4</v>
+        <v>1.01</v>
       </c>
       <c r="BE72">
-        <v>10</v>
+        <v>1.01</v>
       </c>
       <c r="BF72">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="BG72">
-        <v>10.5</v>
+        <v>1.01</v>
       </c>
       <c r="BH72">
         <v>1000</v>
@@ -18680,7 +18680,7 @@
         <v>3.2</v>
       </c>
       <c r="K73">
-        <v>3.35</v>
+        <v>3.45</v>
       </c>
       <c r="L73">
         <v>1.5</v>
@@ -18907,46 +18907,46 @@
         <v>290</v>
       </c>
       <c r="F74">
-        <v>1.09</v>
+        <v>1.35</v>
       </c>
       <c r="G74">
-        <v>3.75</v>
+        <v>1.5</v>
       </c>
       <c r="H74">
-        <v>1.54</v>
+        <v>7</v>
       </c>
       <c r="I74">
         <v>110</v>
       </c>
       <c r="J74">
-        <v>3.5</v>
+        <v>4.4</v>
       </c>
       <c r="K74">
-        <v>290</v>
+        <v>8.6</v>
       </c>
       <c r="L74">
-        <v>1.01</v>
+        <v>1.29</v>
       </c>
       <c r="M74">
         <v>1.01</v>
       </c>
       <c r="N74">
-        <v>1.7</v>
+        <v>3.45</v>
       </c>
       <c r="O74">
         <v>1.26</v>
       </c>
       <c r="P74">
-        <v>1.25</v>
+        <v>1.98</v>
       </c>
       <c r="Q74">
-        <v>1.26</v>
+        <v>1.79</v>
       </c>
       <c r="R74">
-        <v>1.18</v>
+        <v>1.3</v>
       </c>
       <c r="S74">
-        <v>1.29</v>
+        <v>2.76</v>
       </c>
       <c r="T74">
         <v>1.01</v>
@@ -18958,7 +18958,7 @@
         <v>1.06</v>
       </c>
       <c r="W74">
-        <v>1.52</v>
+        <v>3</v>
       </c>
       <c r="X74">
         <v>1000</v>

--- a/Jogos_do_Dia_Betfair_Back_Lay_2026-08-31.xlsx
+++ b/Jogos_do_Dia_Betfair_Back_Lay_2026-08-31.xlsx
@@ -910,7 +910,7 @@
     <t>Academia Anzoategui FC</t>
   </si>
   <si>
-    <t>2026-08-30 10:46:03</t>
+    <t>2026-08-30 13:03:54</t>
   </si>
 </sst>
 </file>
@@ -1504,85 +1504,85 @@
         <v>223</v>
       </c>
       <c r="F2">
+        <v>1.49</v>
+      </c>
+      <c r="G2">
         <v>1.52</v>
       </c>
-      <c r="G2">
-        <v>1.55</v>
-      </c>
       <c r="H2">
-        <v>7</v>
+        <v>7.2</v>
       </c>
       <c r="I2">
-        <v>7.6</v>
+        <v>8</v>
       </c>
       <c r="J2">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="K2">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="L2">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M2">
         <v>1.05</v>
       </c>
       <c r="N2">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="O2">
-        <v>1.25</v>
+        <v>1.26</v>
       </c>
       <c r="P2">
-        <v>2.24</v>
+        <v>2.2</v>
       </c>
       <c r="Q2">
-        <v>1.75</v>
+        <v>1.78</v>
       </c>
       <c r="R2">
-        <v>1.49</v>
+        <v>1.47</v>
       </c>
       <c r="S2">
-        <v>2.96</v>
+        <v>3</v>
       </c>
       <c r="T2">
-        <v>1.89</v>
+        <v>1.93</v>
       </c>
       <c r="U2">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="V2">
-        <v>1.15</v>
+        <v>1.14</v>
       </c>
       <c r="W2">
-        <v>2.8</v>
+        <v>2.92</v>
       </c>
       <c r="X2">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="Y2">
         <v>26</v>
       </c>
       <c r="Z2">
-        <v>65</v>
+        <v>85</v>
       </c>
       <c r="AA2">
         <v>1000</v>
       </c>
       <c r="AB2">
-        <v>9.6</v>
+        <v>9</v>
       </c>
       <c r="AC2">
         <v>13</v>
       </c>
       <c r="AD2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE2">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AF2">
-        <v>11.5</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AG2">
         <v>12.5</v>
@@ -1591,64 +1591,64 @@
         <v>24</v>
       </c>
       <c r="AI2">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AJ2">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AK2">
-        <v>16.5</v>
+        <v>19</v>
       </c>
       <c r="AL2">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="AM2">
         <v>1000</v>
       </c>
       <c r="AN2">
-        <v>8.800000000000001</v>
+        <v>7.4</v>
       </c>
       <c r="AO2">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="AP2">
         <v>16.5</v>
       </c>
       <c r="AQ2">
-        <v>21</v>
+        <v>17.5</v>
       </c>
       <c r="AR2">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AS2">
         <v>1.01</v>
       </c>
       <c r="AT2">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="AU2">
         <v>9</v>
       </c>
       <c r="AV2">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="AW2">
-        <v>1.01</v>
+        <v>36</v>
       </c>
       <c r="AX2">
-        <v>8.4</v>
+        <v>8</v>
       </c>
       <c r="AY2">
         <v>8.800000000000001</v>
       </c>
       <c r="AZ2">
-        <v>19.5</v>
+        <v>20</v>
       </c>
       <c r="BA2">
         <v>1.01</v>
       </c>
       <c r="BB2">
-        <v>12.5</v>
+        <v>12</v>
       </c>
       <c r="BC2">
         <v>12</v>
@@ -1773,7 +1773,7 @@
         <v>6.8</v>
       </c>
       <c r="O3">
-        <v>1.16</v>
+        <v>1.15</v>
       </c>
       <c r="P3">
         <v>3</v>
@@ -1803,10 +1803,10 @@
         <v>36</v>
       </c>
       <c r="Y3">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="Z3">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="AA3">
         <v>360</v>
@@ -1839,7 +1839,7 @@
         <v>12.5</v>
       </c>
       <c r="AK3">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="AL3">
         <v>30</v>
@@ -1854,7 +1854,7 @@
         <v>150</v>
       </c>
       <c r="AP3">
-        <v>8.199999999999999</v>
+        <v>7.4</v>
       </c>
       <c r="AQ3">
         <v>34</v>
@@ -1866,7 +1866,7 @@
         <v>8</v>
       </c>
       <c r="AT3">
-        <v>5.5</v>
+        <v>11</v>
       </c>
       <c r="AU3">
         <v>13</v>
@@ -1875,16 +1875,16 @@
         <v>30</v>
       </c>
       <c r="AW3">
-        <v>7.8</v>
+        <v>8.6</v>
       </c>
       <c r="AX3">
         <v>9.4</v>
       </c>
       <c r="AY3">
-        <v>9.199999999999999</v>
+        <v>9</v>
       </c>
       <c r="AZ3">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BA3">
         <v>8.800000000000001</v>
@@ -1902,7 +1902,7 @@
         <v>7.6</v>
       </c>
       <c r="BF3">
-        <v>3.8</v>
+        <v>3.75</v>
       </c>
       <c r="BG3">
         <v>8.800000000000001</v>
@@ -1988,25 +1988,25 @@
         <v>225</v>
       </c>
       <c r="F4">
-        <v>2.28</v>
+        <v>2.26</v>
       </c>
       <c r="G4">
         <v>2.36</v>
       </c>
       <c r="H4">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="I4">
         <v>3.5</v>
       </c>
       <c r="J4">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="K4">
         <v>3.85</v>
       </c>
       <c r="L4">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="M4">
         <v>1.06</v>
@@ -2018,13 +2018,13 @@
         <v>1.26</v>
       </c>
       <c r="P4">
-        <v>2.12</v>
+        <v>2.16</v>
       </c>
       <c r="Q4">
         <v>1.8</v>
       </c>
       <c r="R4">
-        <v>1.44</v>
+        <v>1.45</v>
       </c>
       <c r="S4">
         <v>3</v>
@@ -2039,7 +2039,7 @@
         <v>1.4</v>
       </c>
       <c r="W4">
-        <v>1.73</v>
+        <v>1.74</v>
       </c>
       <c r="X4">
         <v>18</v>
@@ -2162,7 +2162,7 @@
         <v>1.01</v>
       </c>
       <c r="BL4">
-        <v>110</v>
+        <v>120</v>
       </c>
       <c r="BM4">
         <v>1.01</v>
@@ -2186,7 +2186,7 @@
         <v>1.01</v>
       </c>
       <c r="BT4">
-        <v>7.6</v>
+        <v>7.8</v>
       </c>
       <c r="BU4">
         <v>5.3</v>
@@ -2230,25 +2230,25 @@
         <v>226</v>
       </c>
       <c r="F5">
-        <v>2.26</v>
+        <v>2.3</v>
       </c>
       <c r="G5">
-        <v>2.3</v>
+        <v>2.36</v>
       </c>
       <c r="H5">
-        <v>3.9</v>
+        <v>3.85</v>
       </c>
       <c r="I5">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="J5">
         <v>3.1</v>
       </c>
       <c r="K5">
-        <v>3.3</v>
+        <v>3.2</v>
       </c>
       <c r="L5">
-        <v>1.58</v>
+        <v>1.59</v>
       </c>
       <c r="M5">
         <v>1.12</v>
@@ -2278,10 +2278,10 @@
         <v>1.82</v>
       </c>
       <c r="V5">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="W5">
-        <v>1.77</v>
+        <v>1.75</v>
       </c>
       <c r="X5">
         <v>9</v>
@@ -2296,10 +2296,10 @@
         <v>1000</v>
       </c>
       <c r="AB5">
+        <v>7.2</v>
+      </c>
+      <c r="AC5">
         <v>7.4</v>
-      </c>
-      <c r="AC5">
-        <v>7.2</v>
       </c>
       <c r="AD5">
         <v>17</v>
@@ -2326,7 +2326,7 @@
         <v>34</v>
       </c>
       <c r="AL5">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="AM5">
         <v>1000</v>
@@ -2335,7 +2335,7 @@
         <v>32</v>
       </c>
       <c r="AO5">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AP5">
         <v>8.199999999999999</v>
@@ -2344,10 +2344,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AR5">
-        <v>24</v>
+        <v>21</v>
       </c>
       <c r="AS5">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="AT5">
         <v>6.6</v>
@@ -2368,13 +2368,13 @@
         <v>10.5</v>
       </c>
       <c r="AZ5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BA5">
-        <v>50</v>
+        <v>38</v>
       </c>
       <c r="BB5">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BC5">
         <v>25</v>
@@ -2383,16 +2383,16 @@
         <v>44</v>
       </c>
       <c r="BE5">
-        <v>15.5</v>
+        <v>17</v>
       </c>
       <c r="BF5">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="BG5">
         <v>36</v>
       </c>
       <c r="BH5">
-        <v>2.98</v>
+        <v>3.15</v>
       </c>
       <c r="BI5">
         <v>2.24</v>
@@ -2404,7 +2404,7 @@
         <v>3.7</v>
       </c>
       <c r="BL5">
-        <v>620</v>
+        <v>520</v>
       </c>
       <c r="BM5">
         <v>5</v>
@@ -2413,7 +2413,7 @@
         <v>5.8</v>
       </c>
       <c r="BO5">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="BP5">
         <v>24</v>
@@ -2431,10 +2431,10 @@
         <v>8.199999999999999</v>
       </c>
       <c r="BU5">
-        <v>3.5</v>
+        <v>5.3</v>
       </c>
       <c r="BV5">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="BW5">
         <v>4.6</v>
@@ -2472,13 +2472,13 @@
         <v>227</v>
       </c>
       <c r="F6">
-        <v>2.08</v>
+        <v>2.04</v>
       </c>
       <c r="G6">
-        <v>2.14</v>
+        <v>2.18</v>
       </c>
       <c r="H6">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I6">
         <v>4.8</v>
@@ -2487,31 +2487,31 @@
         <v>3.15</v>
       </c>
       <c r="K6">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="L6">
-        <v>1.54</v>
+        <v>1.55</v>
       </c>
       <c r="M6">
-        <v>1.12</v>
+        <v>1.1</v>
       </c>
       <c r="N6">
-        <v>2.84</v>
+        <v>2.8</v>
       </c>
       <c r="O6">
         <v>1.5</v>
       </c>
       <c r="P6">
-        <v>1.59</v>
+        <v>1.58</v>
       </c>
       <c r="Q6">
-        <v>2.58</v>
+        <v>2.46</v>
       </c>
       <c r="R6">
         <v>1.21</v>
       </c>
       <c r="S6">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="T6">
         <v>2.1</v>
@@ -2523,10 +2523,10 @@
         <v>1.27</v>
       </c>
       <c r="W6">
-        <v>1.87</v>
+        <v>1.84</v>
       </c>
       <c r="X6">
-        <v>11.5</v>
+        <v>11</v>
       </c>
       <c r="Y6">
         <v>13</v>
@@ -2556,10 +2556,10 @@
         <v>13</v>
       </c>
       <c r="AH6">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AI6">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="AJ6">
         <v>36</v>
@@ -2580,7 +2580,7 @@
         <v>140</v>
       </c>
       <c r="AP6">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AQ6">
         <v>10.5</v>
@@ -2589,7 +2589,7 @@
         <v>27</v>
       </c>
       <c r="AS6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="AT6">
         <v>6.2</v>
@@ -2598,10 +2598,10 @@
         <v>6.6</v>
       </c>
       <c r="AV6">
-        <v>16</v>
+        <v>5.4</v>
       </c>
       <c r="AW6">
-        <v>6.4</v>
+        <v>6.6</v>
       </c>
       <c r="AX6">
         <v>10</v>
@@ -2622,7 +2622,7 @@
         <v>20</v>
       </c>
       <c r="BD6">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="BE6">
         <v>6.8</v>
@@ -2631,7 +2631,7 @@
         <v>20</v>
       </c>
       <c r="BG6">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="BH6">
         <v>1000</v>
@@ -2717,10 +2717,10 @@
         <v>1.58</v>
       </c>
       <c r="G7">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="H7">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="I7">
         <v>6.2</v>
@@ -2747,13 +2747,13 @@
         <v>2.6</v>
       </c>
       <c r="Q7">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="R7">
         <v>1.63</v>
       </c>
       <c r="S7">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="T7">
         <v>1.71</v>
@@ -2765,7 +2765,7 @@
         <v>1.19</v>
       </c>
       <c r="W7">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="X7">
         <v>25</v>
@@ -2783,7 +2783,7 @@
         <v>12</v>
       </c>
       <c r="AC7">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="AD7">
         <v>23</v>
@@ -2873,61 +2873,61 @@
         <v>6</v>
       </c>
       <c r="BG7">
-        <v>48</v>
+        <v>12.5</v>
       </c>
       <c r="BH7">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BI7">
-        <v>3.55</v>
+        <v>1.01</v>
       </c>
       <c r="BJ7">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BK7">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BL7">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BM7">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="BN7">
-        <v>5</v>
+        <v>1000</v>
       </c>
       <c r="BO7">
-        <v>3.6</v>
+        <v>1.01</v>
       </c>
       <c r="BP7">
-        <v>11</v>
+        <v>1000</v>
       </c>
       <c r="BQ7">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR7">
-        <v>24</v>
+        <v>1000</v>
       </c>
       <c r="BS7">
-        <v>15.5</v>
+        <v>1.01</v>
       </c>
       <c r="BT7">
-        <v>11.5</v>
+        <v>1000</v>
       </c>
       <c r="BU7">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="BV7">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BW7">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BX7">
-        <v>55</v>
+        <v>1000</v>
       </c>
       <c r="BY7">
-        <v>32</v>
+        <v>1.01</v>
       </c>
       <c r="BZ7">
         <v>0</v>
@@ -2956,145 +2956,145 @@
         <v>229</v>
       </c>
       <c r="F8">
-        <v>2.62</v>
+        <v>4.9</v>
       </c>
       <c r="G8">
-        <v>10.5</v>
+        <v>5.9</v>
       </c>
       <c r="H8">
-        <v>1.62</v>
+        <v>1.66</v>
       </c>
       <c r="I8">
-        <v>1.91</v>
+        <v>1.8</v>
       </c>
       <c r="J8">
-        <v>3.5</v>
+        <v>3.95</v>
       </c>
       <c r="K8">
-        <v>410</v>
+        <v>4.5</v>
       </c>
       <c r="L8">
         <v>1.01</v>
       </c>
       <c r="M8">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N8">
-        <v>3.6</v>
+        <v>4.3</v>
       </c>
       <c r="O8">
-        <v>1.24</v>
+        <v>1.25</v>
       </c>
       <c r="P8">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q8">
         <v>1.71</v>
       </c>
       <c r="R8">
-        <v>1.4</v>
+        <v>1.44</v>
       </c>
       <c r="S8">
-        <v>2.58</v>
+        <v>2.84</v>
       </c>
       <c r="T8">
-        <v>1.01</v>
+        <v>1.73</v>
       </c>
       <c r="U8">
-        <v>1.01</v>
+        <v>2.12</v>
       </c>
       <c r="V8">
-        <v>1.94</v>
+        <v>2.24</v>
       </c>
       <c r="W8">
-        <v>1.1</v>
+        <v>1.2</v>
       </c>
       <c r="X8">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="Y8">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Z8">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AA8">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AB8">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AC8">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AD8">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AE8">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AF8">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AG8">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="AH8">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI8">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AJ8">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AK8">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AL8">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AM8">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AN8">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AO8">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AP8">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AQ8">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AR8">
-        <v>1.01</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AS8">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="AT8">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AU8">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AV8">
-        <v>1.01</v>
+        <v>7.6</v>
       </c>
       <c r="AW8">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AX8">
         <v>1.01</v>
       </c>
       <c r="AY8">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AZ8">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA8">
         <v>1.01</v>
@@ -3115,7 +3115,7 @@
         <v>1.01</v>
       </c>
       <c r="BG8">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BH8">
         <v>1000</v>
@@ -3198,28 +3198,28 @@
         <v>230</v>
       </c>
       <c r="F9">
-        <v>3.3</v>
+        <v>1.1</v>
       </c>
       <c r="G9">
-        <v>3.9</v>
+        <v>140</v>
       </c>
       <c r="H9">
-        <v>2.18</v>
+        <v>1.09</v>
       </c>
       <c r="I9">
         <v>2.2</v>
       </c>
       <c r="J9">
-        <v>3.55</v>
+        <v>1.92</v>
       </c>
       <c r="K9">
-        <v>4.1</v>
+        <v>230</v>
       </c>
       <c r="L9">
         <v>1.01</v>
       </c>
       <c r="M9">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="N9">
         <v>2.16</v>
@@ -3231,25 +3231,25 @@
         <v>1.21</v>
       </c>
       <c r="Q9">
-        <v>1.31</v>
+        <v>1.25</v>
       </c>
       <c r="R9">
         <v>1.18</v>
       </c>
       <c r="S9">
-        <v>1.03</v>
+        <v>1.24</v>
       </c>
       <c r="T9">
         <v>1.01</v>
       </c>
       <c r="U9">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="V9">
         <v>1.83</v>
       </c>
       <c r="W9">
-        <v>1.37</v>
+        <v>1.02</v>
       </c>
       <c r="X9">
         <v>1000</v>
@@ -3443,13 +3443,13 @@
         <v>1.58</v>
       </c>
       <c r="G10">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="H10">
         <v>4.7</v>
       </c>
       <c r="I10">
-        <v>6.4</v>
+        <v>7.2</v>
       </c>
       <c r="J10">
         <v>4.4</v>
@@ -3461,16 +3461,16 @@
         <v>1.01</v>
       </c>
       <c r="M10">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N10">
-        <v>2.52</v>
+        <v>5.3</v>
       </c>
       <c r="O10">
         <v>1.15</v>
       </c>
       <c r="P10">
-        <v>2.52</v>
+        <v>2.68</v>
       </c>
       <c r="Q10">
         <v>1.48</v>
@@ -3479,19 +3479,19 @@
         <v>1.63</v>
       </c>
       <c r="S10">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="T10">
         <v>1.01</v>
       </c>
       <c r="U10">
-        <v>1.01</v>
+        <v>2.28</v>
       </c>
       <c r="V10">
-        <v>1.19</v>
+        <v>1.22</v>
       </c>
       <c r="W10">
-        <v>2.28</v>
+        <v>2.36</v>
       </c>
       <c r="X10">
         <v>1000</v>
@@ -3521,10 +3521,10 @@
         <v>1000</v>
       </c>
       <c r="AG10">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH10">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AI10">
         <v>1000</v>
@@ -3551,7 +3551,7 @@
         <v>1.01</v>
       </c>
       <c r="AQ10">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AR10">
         <v>1.01</v>
@@ -3581,7 +3581,7 @@
         <v>1.01</v>
       </c>
       <c r="BA10">
-        <v>1.01</v>
+        <v>24</v>
       </c>
       <c r="BB10">
         <v>1.01</v>
@@ -3682,172 +3682,172 @@
         <v>232</v>
       </c>
       <c r="F11">
-        <v>2.04</v>
+        <v>2.08</v>
       </c>
       <c r="G11">
         <v>2.3</v>
       </c>
       <c r="H11">
-        <v>3.5</v>
+        <v>3.65</v>
       </c>
       <c r="I11">
-        <v>4.4</v>
+        <v>4.2</v>
       </c>
       <c r="J11">
         <v>3.35</v>
       </c>
       <c r="K11">
-        <v>4.5</v>
+        <v>4.1</v>
       </c>
       <c r="L11">
         <v>1.36</v>
       </c>
       <c r="M11">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N11">
-        <v>3.55</v>
+        <v>3.6</v>
       </c>
       <c r="O11">
-        <v>1.29</v>
+        <v>1.32</v>
       </c>
       <c r="P11">
-        <v>1.84</v>
+        <v>1.88</v>
       </c>
       <c r="Q11">
-        <v>1.94</v>
+        <v>1.97</v>
       </c>
       <c r="R11">
-        <v>1.28</v>
+        <v>1.33</v>
       </c>
       <c r="S11">
-        <v>3.25</v>
+        <v>3.5</v>
       </c>
       <c r="T11">
-        <v>1.01</v>
+        <v>1.78</v>
       </c>
       <c r="U11">
-        <v>1.01</v>
+        <v>2.08</v>
       </c>
       <c r="V11">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="W11">
-        <v>1.76</v>
+        <v>1.77</v>
       </c>
       <c r="X11">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Y11">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="Z11">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA11">
-        <v>1000</v>
+        <v>90</v>
       </c>
       <c r="AB11">
-        <v>1000</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AC11">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="AD11">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AE11">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AF11">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AG11">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AH11">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI11">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AJ11">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AK11">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AL11">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AM11">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN11">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AO11">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AP11">
-        <v>1.01</v>
+        <v>10.5</v>
       </c>
       <c r="AQ11">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AR11">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AS11">
         <v>1.01</v>
       </c>
       <c r="AT11">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AU11">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV11">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AW11">
         <v>1.01</v>
       </c>
       <c r="AX11">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AY11">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AZ11">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA11">
         <v>1.01</v>
       </c>
       <c r="BB11">
-        <v>1.01</v>
+        <v>20</v>
       </c>
       <c r="BC11">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BD11">
-        <v>1.01</v>
+        <v>32</v>
       </c>
       <c r="BE11">
         <v>1.01</v>
       </c>
       <c r="BF11">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BG11">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="BH11">
         <v>3.75</v>
       </c>
       <c r="BI11">
-        <v>2.78</v>
+        <v>2.76</v>
       </c>
       <c r="BJ11">
         <v>11</v>
@@ -3859,25 +3859,25 @@
         <v>150</v>
       </c>
       <c r="BM11">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN11">
         <v>5.1</v>
       </c>
       <c r="BO11">
-        <v>4.3</v>
+        <v>4</v>
       </c>
       <c r="BP11">
         <v>16.5</v>
       </c>
       <c r="BQ11">
-        <v>12</v>
+        <v>1.01</v>
       </c>
       <c r="BR11">
         <v>36</v>
       </c>
       <c r="BS11">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BT11">
         <v>8</v>
@@ -3889,19 +3889,19 @@
         <v>36</v>
       </c>
       <c r="BW11">
-        <v>23</v>
+        <v>1.01</v>
       </c>
       <c r="BX11">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="BY11">
-        <v>30</v>
+        <v>1.01</v>
       </c>
       <c r="BZ11">
         <v>32</v>
       </c>
       <c r="CA11">
-        <v>22</v>
+        <v>1.01</v>
       </c>
       <c r="CB11" t="s">
         <v>298</v>
@@ -3924,22 +3924,22 @@
         <v>233</v>
       </c>
       <c r="F12">
-        <v>2.46</v>
+        <v>2.52</v>
       </c>
       <c r="G12">
         <v>2.68</v>
       </c>
       <c r="H12">
-        <v>2.82</v>
+        <v>2.86</v>
       </c>
       <c r="I12">
-        <v>3.15</v>
+        <v>3.1</v>
       </c>
       <c r="J12">
         <v>3.5</v>
       </c>
       <c r="K12">
-        <v>3.75</v>
+        <v>3.6</v>
       </c>
       <c r="L12">
         <v>1.29</v>
@@ -3948,22 +3948,22 @@
         <v>1.07</v>
       </c>
       <c r="N12">
-        <v>3.45</v>
+        <v>3.7</v>
       </c>
       <c r="O12">
-        <v>1.29</v>
+        <v>1.3</v>
       </c>
       <c r="P12">
-        <v>1.12</v>
+        <v>2</v>
       </c>
       <c r="Q12">
-        <v>1.88</v>
+        <v>1.85</v>
       </c>
       <c r="R12">
-        <v>1.37</v>
+        <v>1.35</v>
       </c>
       <c r="S12">
-        <v>1.89</v>
+        <v>3.25</v>
       </c>
       <c r="T12">
         <v>1.71</v>
@@ -3972,13 +3972,13 @@
         <v>2.14</v>
       </c>
       <c r="V12">
-        <v>1.46</v>
+        <v>1.48</v>
       </c>
       <c r="W12">
         <v>1.6</v>
       </c>
       <c r="X12">
-        <v>15.5</v>
+        <v>16.5</v>
       </c>
       <c r="Y12">
         <v>13</v>
@@ -3987,34 +3987,34 @@
         <v>22</v>
       </c>
       <c r="AA12">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AB12">
         <v>11.5</v>
       </c>
       <c r="AC12">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AD12">
         <v>13.5</v>
       </c>
       <c r="AE12">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="AF12">
         <v>17.5</v>
       </c>
       <c r="AG12">
-        <v>12</v>
+        <v>12.5</v>
       </c>
       <c r="AH12">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AI12">
         <v>46</v>
       </c>
       <c r="AJ12">
-        <v>38</v>
+        <v>44</v>
       </c>
       <c r="AK12">
         <v>28</v>
@@ -4026,7 +4026,7 @@
         <v>90</v>
       </c>
       <c r="AN12">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AO12">
         <v>30</v>
@@ -4038,7 +4038,7 @@
         <v>11</v>
       </c>
       <c r="AR12">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AS12">
         <v>40</v>
@@ -4053,7 +4053,7 @@
         <v>11.5</v>
       </c>
       <c r="AW12">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AX12">
         <v>14.5</v>
@@ -4062,7 +4062,7 @@
         <v>10.5</v>
       </c>
       <c r="AZ12">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="BA12">
         <v>36</v>
@@ -4077,13 +4077,13 @@
         <v>32</v>
       </c>
       <c r="BE12">
-        <v>10</v>
+        <v>9.4</v>
       </c>
       <c r="BF12">
         <v>19</v>
       </c>
       <c r="BG12">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="BH12">
         <v>1000</v>
@@ -4166,22 +4166,22 @@
         <v>234</v>
       </c>
       <c r="F13">
-        <v>2.34</v>
+        <v>2.62</v>
       </c>
       <c r="G13">
-        <v>2.78</v>
+        <v>2.82</v>
       </c>
       <c r="H13">
-        <v>2.56</v>
+        <v>2.5</v>
       </c>
       <c r="I13">
-        <v>2.86</v>
+        <v>2.7</v>
       </c>
       <c r="J13">
-        <v>3.75</v>
+        <v>3.85</v>
       </c>
       <c r="K13">
-        <v>5.5</v>
+        <v>4.3</v>
       </c>
       <c r="L13">
         <v>1.01</v>
@@ -4190,109 +4190,109 @@
         <v>1.02</v>
       </c>
       <c r="N13">
-        <v>3.8</v>
+        <v>5.4</v>
       </c>
       <c r="O13">
-        <v>1.18</v>
+        <v>1.19</v>
       </c>
       <c r="P13">
+        <v>2.5</v>
+      </c>
+      <c r="Q13">
+        <v>1.48</v>
+      </c>
+      <c r="R13">
+        <v>1.64</v>
+      </c>
+      <c r="S13">
         <v>2.42</v>
       </c>
-      <c r="Q13">
-        <v>1.53</v>
-      </c>
-      <c r="R13">
-        <v>1.58</v>
-      </c>
-      <c r="S13">
-        <v>2.3</v>
-      </c>
       <c r="T13">
-        <v>1.01</v>
+        <v>1.54</v>
       </c>
       <c r="U13">
-        <v>1.01</v>
+        <v>2.64</v>
       </c>
       <c r="V13">
-        <v>1.54</v>
+        <v>1.59</v>
       </c>
       <c r="W13">
-        <v>1.56</v>
+        <v>1.57</v>
       </c>
       <c r="X13">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="Y13">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="Z13">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AA13">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AB13">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AC13">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AD13">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AE13">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AF13">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AG13">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH13">
-        <v>1000</v>
+        <v>18</v>
       </c>
       <c r="AI13">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AJ13">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AK13">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AL13">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AM13">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AN13">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AO13">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AP13">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AQ13">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="AR13">
-        <v>1.01</v>
+        <v>18</v>
       </c>
       <c r="AS13">
         <v>1.01</v>
       </c>
       <c r="AT13">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AU13">
-        <v>1.01</v>
+        <v>7.4</v>
       </c>
       <c r="AV13">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW13">
         <v>1.01</v>
@@ -4301,10 +4301,10 @@
         <v>1.01</v>
       </c>
       <c r="AY13">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AZ13">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BA13">
         <v>1.01</v>
@@ -4313,19 +4313,19 @@
         <v>1.01</v>
       </c>
       <c r="BC13">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BD13">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BE13">
         <v>1.01</v>
       </c>
       <c r="BF13">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BG13">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BH13">
         <v>1000</v>
@@ -4408,49 +4408,49 @@
         <v>235</v>
       </c>
       <c r="F14">
-        <v>2.06</v>
+        <v>2.2</v>
       </c>
       <c r="G14">
-        <v>2.52</v>
+        <v>2.5</v>
       </c>
       <c r="H14">
-        <v>2.66</v>
+        <v>2.8</v>
       </c>
       <c r="I14">
-        <v>3.8</v>
+        <v>3.85</v>
       </c>
       <c r="J14">
         <v>3.2</v>
       </c>
       <c r="K14">
-        <v>7</v>
+        <v>4.1</v>
       </c>
       <c r="L14">
         <v>1.01</v>
       </c>
       <c r="M14">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N14">
-        <v>2.28</v>
+        <v>4.5</v>
       </c>
       <c r="O14">
-        <v>1.22</v>
+        <v>1.24</v>
       </c>
       <c r="P14">
-        <v>1.96</v>
+        <v>2.06</v>
       </c>
       <c r="Q14">
-        <v>1.58</v>
+        <v>1.68</v>
       </c>
       <c r="R14">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="S14">
-        <v>2.64</v>
+        <v>2.74</v>
       </c>
       <c r="T14">
-        <v>1.52</v>
+        <v>1.53</v>
       </c>
       <c r="U14">
         <v>1.01</v>
@@ -4459,82 +4459,82 @@
         <v>1.35</v>
       </c>
       <c r="W14">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="X14">
         <v>1000</v>
       </c>
       <c r="Y14">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="Z14">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="AA14">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="AB14">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AC14">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD14">
-        <v>1000</v>
+        <v>19</v>
       </c>
       <c r="AE14">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AF14">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG14">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH14">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI14">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AJ14">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AK14">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL14">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AM14">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="AN14">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AO14">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AP14">
         <v>1.01</v>
       </c>
       <c r="AQ14">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AR14">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="AS14">
         <v>1.01</v>
       </c>
       <c r="AT14">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AU14">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV14">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AW14">
         <v>1.01</v>
@@ -4543,7 +4543,7 @@
         <v>1.01</v>
       </c>
       <c r="AY14">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AZ14">
         <v>1.01</v>
@@ -4555,7 +4555,7 @@
         <v>1.01</v>
       </c>
       <c r="BC14">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BD14">
         <v>1.01</v>
@@ -4564,10 +4564,10 @@
         <v>1.01</v>
       </c>
       <c r="BF14">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BG14">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BH14">
         <v>1000</v>
@@ -4653,28 +4653,28 @@
         <v>1.55</v>
       </c>
       <c r="G15">
-        <v>1.78</v>
+        <v>1.75</v>
       </c>
       <c r="H15">
-        <v>4.2</v>
+        <v>4.4</v>
       </c>
       <c r="I15">
-        <v>7.4</v>
+        <v>7.6</v>
       </c>
       <c r="J15">
-        <v>4.2</v>
+        <v>3.95</v>
       </c>
       <c r="K15">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="L15">
         <v>1.01</v>
       </c>
       <c r="M15">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N15">
-        <v>2.28</v>
+        <v>4.8</v>
       </c>
       <c r="O15">
         <v>1.16</v>
@@ -4686,7 +4686,7 @@
         <v>1.44</v>
       </c>
       <c r="R15">
-        <v>1.51</v>
+        <v>1.63</v>
       </c>
       <c r="S15">
         <v>2.12</v>
@@ -4695,22 +4695,22 @@
         <v>1.01</v>
       </c>
       <c r="U15">
-        <v>1.01</v>
+        <v>2.14</v>
       </c>
       <c r="V15">
-        <v>1.16</v>
+        <v>1.17</v>
       </c>
       <c r="W15">
-        <v>2.28</v>
+        <v>2.34</v>
       </c>
       <c r="X15">
         <v>1000</v>
       </c>
       <c r="Y15">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="Z15">
-        <v>1000</v>
+        <v>75</v>
       </c>
       <c r="AA15">
         <v>1000</v>
@@ -4719,22 +4719,22 @@
         <v>1000</v>
       </c>
       <c r="AC15">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD15">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AE15">
         <v>1000</v>
       </c>
       <c r="AF15">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AG15">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AH15">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AI15">
         <v>1000</v>
@@ -4764,46 +4764,46 @@
         <v>1.01</v>
       </c>
       <c r="AR15">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AS15">
         <v>1.01</v>
       </c>
       <c r="AT15">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AU15">
         <v>1.01</v>
       </c>
       <c r="AV15">
-        <v>1.01</v>
+        <v>12.5</v>
       </c>
       <c r="AW15">
-        <v>1.01</v>
+        <v>23</v>
       </c>
       <c r="AX15">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AY15">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AZ15">
         <v>1.01</v>
       </c>
       <c r="BA15">
-        <v>1.01</v>
+        <v>22</v>
       </c>
       <c r="BB15">
         <v>1.01</v>
       </c>
       <c r="BC15">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BD15">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="BE15">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="BF15">
         <v>1.01</v>
@@ -4895,13 +4895,13 @@
         <v>4.5</v>
       </c>
       <c r="G16">
-        <v>5.3</v>
+        <v>5.4</v>
       </c>
       <c r="H16">
-        <v>1.66</v>
+        <v>1.68</v>
       </c>
       <c r="I16">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="J16">
         <v>4.4</v>
@@ -4916,7 +4916,7 @@
         <v>1.03</v>
       </c>
       <c r="N16">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="O16">
         <v>1.16</v>
@@ -4937,13 +4937,13 @@
         <v>1.59</v>
       </c>
       <c r="U16">
-        <v>2.44</v>
+        <v>2.42</v>
       </c>
       <c r="V16">
         <v>2.28</v>
       </c>
       <c r="W16">
-        <v>1.23</v>
+        <v>1.25</v>
       </c>
       <c r="X16">
         <v>32</v>
@@ -4985,7 +4985,7 @@
         <v>120</v>
       </c>
       <c r="AK16">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AL16">
         <v>55</v>
@@ -5021,13 +5021,13 @@
         <v>9</v>
       </c>
       <c r="AW16">
-        <v>11.5</v>
+        <v>13</v>
       </c>
       <c r="AX16">
         <v>1.01</v>
       </c>
       <c r="AY16">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="AZ16">
         <v>12</v>
@@ -5066,7 +5066,7 @@
         <v>1.01</v>
       </c>
       <c r="BL16">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="BM16">
         <v>1.01</v>
@@ -5090,7 +5090,7 @@
         <v>1.01</v>
       </c>
       <c r="BT16">
-        <v>5.8</v>
+        <v>5.7</v>
       </c>
       <c r="BU16">
         <v>3.75</v>
@@ -5134,7 +5134,7 @@
         <v>238</v>
       </c>
       <c r="F17">
-        <v>1.64</v>
+        <v>1.71</v>
       </c>
       <c r="G17">
         <v>2.04</v>
@@ -5149,34 +5149,34 @@
         <v>1.09</v>
       </c>
       <c r="K17">
-        <v>7.8</v>
+        <v>7.6</v>
       </c>
       <c r="L17">
         <v>1.01</v>
       </c>
       <c r="M17">
-        <v>1.03</v>
+        <v>1.04</v>
       </c>
       <c r="N17">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="O17">
         <v>1.21</v>
       </c>
       <c r="P17">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q17">
         <v>1.59</v>
       </c>
       <c r="R17">
-        <v>1.4</v>
+        <v>1.38</v>
       </c>
       <c r="S17">
         <v>2.42</v>
       </c>
       <c r="T17">
-        <v>1.51</v>
+        <v>1.53</v>
       </c>
       <c r="U17">
         <v>2.1</v>
@@ -5191,10 +5191,10 @@
         <v>1000</v>
       </c>
       <c r="Y17">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="Z17">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AA17">
         <v>1000</v>
@@ -5203,10 +5203,10 @@
         <v>1000</v>
       </c>
       <c r="AC17">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD17">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AE17">
         <v>1000</v>
@@ -5215,10 +5215,10 @@
         <v>1000</v>
       </c>
       <c r="AG17">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH17">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="AI17">
         <v>1000</v>
@@ -5254,22 +5254,22 @@
         <v>1.01</v>
       </c>
       <c r="AT17">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AU17">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV17">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AW17">
         <v>1.01</v>
       </c>
       <c r="AX17">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AY17">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AZ17">
         <v>1.01</v>
@@ -5284,7 +5284,7 @@
         <v>1.01</v>
       </c>
       <c r="BD17">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="BE17">
         <v>1.01</v>
@@ -5376,19 +5376,19 @@
         <v>239</v>
       </c>
       <c r="F18">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="G18">
         <v>970</v>
       </c>
       <c r="H18">
-        <v>1.11</v>
+        <v>1.13</v>
       </c>
       <c r="I18">
         <v>970</v>
       </c>
       <c r="J18">
-        <v>1.1</v>
+        <v>3.35</v>
       </c>
       <c r="K18">
         <v>280</v>
@@ -5400,13 +5400,13 @@
         <v>1.01</v>
       </c>
       <c r="N18">
+        <v>3.1</v>
+      </c>
+      <c r="O18">
+        <v>1.01</v>
+      </c>
+      <c r="P18">
         <v>1.19</v>
-      </c>
-      <c r="O18">
-        <v>1.01</v>
-      </c>
-      <c r="P18">
-        <v>1.18</v>
       </c>
       <c r="Q18">
         <v>1.79</v>
@@ -5424,10 +5424,10 @@
         <v>1.01</v>
       </c>
       <c r="V18">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="W18">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X18">
         <v>1000</v>
@@ -5487,22 +5487,22 @@
         <v>1.01</v>
       </c>
       <c r="AQ18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AR18">
         <v>1.01</v>
       </c>
       <c r="AS18">
-        <v>1.01</v>
+        <v>1.14</v>
       </c>
       <c r="AT18">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="AU18">
         <v>1.01</v>
       </c>
       <c r="AV18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AW18">
         <v>1.01</v>
@@ -5511,7 +5511,7 @@
         <v>1.01</v>
       </c>
       <c r="AY18">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="AZ18">
         <v>1.01</v>
@@ -5520,7 +5520,7 @@
         <v>1.01</v>
       </c>
       <c r="BB18">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BC18">
         <v>1.01</v>
@@ -5529,7 +5529,7 @@
         <v>1.01</v>
       </c>
       <c r="BE18">
-        <v>1.01</v>
+        <v>1.06</v>
       </c>
       <c r="BF18">
         <v>1.01</v>
@@ -5621,7 +5621,7 @@
         <v>2.32</v>
       </c>
       <c r="G19">
-        <v>2.6</v>
+        <v>2.58</v>
       </c>
       <c r="H19">
         <v>2.8</v>
@@ -5639,7 +5639,7 @@
         <v>1.01</v>
       </c>
       <c r="M19">
-        <v>1.01</v>
+        <v>1.04</v>
       </c>
       <c r="N19">
         <v>4.3</v>
@@ -5648,7 +5648,7 @@
         <v>1.23</v>
       </c>
       <c r="P19">
-        <v>2.04</v>
+        <v>2.06</v>
       </c>
       <c r="Q19">
         <v>1.56</v>
@@ -5660,7 +5660,7 @@
         <v>2.36</v>
       </c>
       <c r="T19">
-        <v>1.01</v>
+        <v>1.47</v>
       </c>
       <c r="U19">
         <v>2.16</v>
@@ -5669,7 +5669,7 @@
         <v>1.47</v>
       </c>
       <c r="W19">
-        <v>1.62</v>
+        <v>1.63</v>
       </c>
       <c r="X19">
         <v>1000</v>
@@ -5678,7 +5678,7 @@
         <v>1000</v>
       </c>
       <c r="Z19">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AA19">
         <v>1000</v>
@@ -5687,22 +5687,22 @@
         <v>1000</v>
       </c>
       <c r="AC19">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AD19">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AE19">
         <v>1000</v>
       </c>
       <c r="AF19">
-        <v>1000</v>
+        <v>29</v>
       </c>
       <c r="AG19">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="AH19">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI19">
         <v>1000</v>
@@ -5729,46 +5729,46 @@
         <v>1.01</v>
       </c>
       <c r="AQ19">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AR19">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AS19">
-        <v>1.01</v>
+        <v>21</v>
       </c>
       <c r="AT19">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="AU19">
-        <v>1.01</v>
+        <v>6.2</v>
       </c>
       <c r="AV19">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AW19">
-        <v>1.01</v>
+        <v>14.5</v>
       </c>
       <c r="AX19">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AY19">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AZ19">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BA19">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="BB19">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BC19">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BD19">
-        <v>1.01</v>
+        <v>17.5</v>
       </c>
       <c r="BE19">
         <v>1.01</v>
@@ -5866,7 +5866,7 @@
         <v>3.75</v>
       </c>
       <c r="H20">
-        <v>2.14</v>
+        <v>2.16</v>
       </c>
       <c r="I20">
         <v>2.26</v>
@@ -5875,10 +5875,10 @@
         <v>3.5</v>
       </c>
       <c r="K20">
-        <v>4.1</v>
+        <v>3.95</v>
       </c>
       <c r="L20">
-        <v>1.36</v>
+        <v>1.37</v>
       </c>
       <c r="M20">
         <v>1.06</v>
@@ -5887,13 +5887,13 @@
         <v>3.9</v>
       </c>
       <c r="O20">
-        <v>1.27</v>
+        <v>1.28</v>
       </c>
       <c r="P20">
         <v>2</v>
       </c>
       <c r="Q20">
-        <v>1.8</v>
+        <v>1.83</v>
       </c>
       <c r="R20">
         <v>1.39</v>
@@ -5902,7 +5902,7 @@
         <v>3.05</v>
       </c>
       <c r="T20">
-        <v>1.68</v>
+        <v>1.69</v>
       </c>
       <c r="U20">
         <v>2.2</v>
@@ -5914,13 +5914,13 @@
         <v>1.36</v>
       </c>
       <c r="X20">
-        <v>20</v>
+        <v>19.5</v>
       </c>
       <c r="Y20">
         <v>13</v>
       </c>
       <c r="Z20">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AA20">
         <v>38</v>
@@ -5971,7 +5971,7 @@
         <v>12</v>
       </c>
       <c r="AQ20">
-        <v>8.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AR20">
         <v>11</v>
@@ -5980,13 +5980,13 @@
         <v>21</v>
       </c>
       <c r="AT20">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AU20">
         <v>6.4</v>
       </c>
       <c r="AV20">
-        <v>8.199999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="AW20">
         <v>17</v>
@@ -5995,7 +5995,7 @@
         <v>18</v>
       </c>
       <c r="AY20">
-        <v>10.5</v>
+        <v>12.5</v>
       </c>
       <c r="AZ20">
         <v>12</v>
@@ -6022,61 +6022,61 @@
         <v>11.5</v>
       </c>
       <c r="BH20">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI20">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BJ20">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK20">
         <v>1.01</v>
       </c>
       <c r="BL20">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM20">
         <v>1.01</v>
       </c>
       <c r="BN20">
-        <v>1000</v>
+        <v>7.8</v>
       </c>
       <c r="BO20">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BP20">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BQ20">
         <v>1.01</v>
       </c>
       <c r="BR20">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BS20">
         <v>1.01</v>
       </c>
       <c r="BT20">
-        <v>1000</v>
+        <v>5.3</v>
       </c>
       <c r="BU20">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV20">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="BW20">
         <v>1.01</v>
       </c>
       <c r="BX20">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="BY20">
-        <v>1.01</v>
+        <v>16.5</v>
       </c>
       <c r="BZ20">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA20">
         <v>1.01</v>
@@ -6108,16 +6108,16 @@
         <v>2.08</v>
       </c>
       <c r="H21">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="I21">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="J21">
-        <v>3.7</v>
+        <v>3.65</v>
       </c>
       <c r="K21">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="L21">
         <v>1.01</v>
@@ -6135,7 +6135,7 @@
         <v>2.08</v>
       </c>
       <c r="Q21">
-        <v>1.78</v>
+        <v>1.8</v>
       </c>
       <c r="R21">
         <v>1.43</v>
@@ -6156,19 +6156,19 @@
         <v>1.92</v>
       </c>
       <c r="X21">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="Y21">
         <v>16.5</v>
       </c>
       <c r="Z21">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="AA21">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="AB21">
-        <v>11</v>
+        <v>10.5</v>
       </c>
       <c r="AC21">
         <v>9</v>
@@ -6177,10 +6177,10 @@
         <v>16.5</v>
       </c>
       <c r="AE21">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AF21">
-        <v>14</v>
+        <v>13.5</v>
       </c>
       <c r="AG21">
         <v>11</v>
@@ -6189,7 +6189,7 @@
         <v>17</v>
       </c>
       <c r="AI21">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="AJ21">
         <v>24</v>
@@ -6201,13 +6201,13 @@
         <v>32</v>
       </c>
       <c r="AM21">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="AN21">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AO21">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="AP21">
         <v>15</v>
@@ -6216,13 +6216,13 @@
         <v>14.5</v>
       </c>
       <c r="AR21">
-        <v>19</v>
+        <v>26</v>
       </c>
       <c r="AS21">
-        <v>1.01</v>
+        <v>42</v>
       </c>
       <c r="AT21">
-        <v>7.8</v>
+        <v>9.4</v>
       </c>
       <c r="AU21">
         <v>7.8</v>
@@ -6231,37 +6231,37 @@
         <v>14</v>
       </c>
       <c r="AW21">
-        <v>30</v>
+        <v>36</v>
       </c>
       <c r="AX21">
         <v>12</v>
       </c>
       <c r="AY21">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AZ21">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="BA21">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="BB21">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="BC21">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BD21">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BE21">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="BF21">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BG21">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="BH21">
         <v>3.75</v>
@@ -6344,112 +6344,112 @@
         <v>243</v>
       </c>
       <c r="F22">
-        <v>1.11</v>
+        <v>2.7</v>
       </c>
       <c r="G22">
-        <v>970</v>
+        <v>3.45</v>
       </c>
       <c r="H22">
-        <v>1.11</v>
+        <v>2.54</v>
       </c>
       <c r="I22">
-        <v>970</v>
+        <v>3.2</v>
       </c>
       <c r="J22">
-        <v>1.1</v>
+        <v>2.88</v>
       </c>
       <c r="K22">
-        <v>210</v>
+        <v>3.7</v>
       </c>
       <c r="L22">
-        <v>1.01</v>
+        <v>1.4</v>
       </c>
       <c r="M22">
-        <v>1.01</v>
+        <v>1.08</v>
       </c>
       <c r="N22">
-        <v>1.26</v>
+        <v>2.78</v>
       </c>
       <c r="O22">
-        <v>1.41</v>
+        <v>1.38</v>
       </c>
       <c r="P22">
-        <v>1.25</v>
+        <v>1.71</v>
       </c>
       <c r="Q22">
-        <v>1.41</v>
+        <v>2.06</v>
       </c>
       <c r="R22">
-        <v>1.15</v>
+        <v>1.27</v>
       </c>
       <c r="S22">
-        <v>1.41</v>
+        <v>3.55</v>
       </c>
       <c r="T22">
-        <v>1.01</v>
+        <v>1.79</v>
       </c>
       <c r="U22">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V22">
-        <v>1.09</v>
+        <v>1.45</v>
       </c>
       <c r="W22">
-        <v>1.09</v>
+        <v>1.4</v>
       </c>
       <c r="X22">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Y22">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="Z22">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AA22">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="AB22">
-        <v>1000</v>
+        <v>12.5</v>
       </c>
       <c r="AC22">
-        <v>1000</v>
+        <v>8.6</v>
       </c>
       <c r="AD22">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="AE22">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AF22">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AG22">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="AH22">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="AI22">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ22">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AK22">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AL22">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM22">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="AN22">
-        <v>1000</v>
+        <v>42</v>
       </c>
       <c r="AO22">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AP22">
         <v>1.01</v>
@@ -6506,61 +6506,61 @@
         <v>1.01</v>
       </c>
       <c r="BH22">
-        <v>1000</v>
+        <v>3.5</v>
       </c>
       <c r="BI22">
-        <v>1.01</v>
+        <v>2.6</v>
       </c>
       <c r="BJ22">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BK22">
         <v>1.01</v>
       </c>
       <c r="BL22">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="BM22">
         <v>1.01</v>
       </c>
       <c r="BN22">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="BO22">
-        <v>1.01</v>
+        <v>4.6</v>
       </c>
       <c r="BP22">
-        <v>1000</v>
+        <v>28</v>
       </c>
       <c r="BQ22">
         <v>1.01</v>
       </c>
       <c r="BR22">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="BS22">
         <v>1.01</v>
       </c>
       <c r="BT22">
-        <v>1000</v>
+        <v>6.4</v>
       </c>
       <c r="BU22">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV22">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="BW22">
         <v>1.01</v>
       </c>
       <c r="BX22">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY22">
         <v>1.01</v>
       </c>
       <c r="BZ22">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="CA22">
         <v>1.01</v>
@@ -6586,223 +6586,223 @@
         <v>244</v>
       </c>
       <c r="F23">
-        <v>4.5</v>
+        <v>7.2</v>
       </c>
       <c r="G23">
-        <v>34</v>
+        <v>9</v>
       </c>
       <c r="H23">
-        <v>1.53</v>
+        <v>1.43</v>
       </c>
       <c r="I23">
-        <v>1.6</v>
+        <v>1.51</v>
       </c>
       <c r="J23">
-        <v>2.8</v>
+        <v>4.8</v>
       </c>
       <c r="K23">
-        <v>34</v>
+        <v>5.5</v>
       </c>
       <c r="L23">
-        <v>1.01</v>
+        <v>1.24</v>
       </c>
       <c r="M23">
-        <v>1.02</v>
+        <v>1.03</v>
       </c>
       <c r="N23">
+        <v>5.3</v>
+      </c>
+      <c r="O23">
+        <v>1.18</v>
+      </c>
+      <c r="P23">
+        <v>2.48</v>
+      </c>
+      <c r="Q23">
+        <v>1.54</v>
+      </c>
+      <c r="R23">
+        <v>1.63</v>
+      </c>
+      <c r="S23">
+        <v>2.34</v>
+      </c>
+      <c r="T23">
+        <v>1.78</v>
+      </c>
+      <c r="U23">
+        <v>2.06</v>
+      </c>
+      <c r="V23">
+        <v>2.94</v>
+      </c>
+      <c r="W23">
+        <v>1.12</v>
+      </c>
+      <c r="X23">
+        <v>27</v>
+      </c>
+      <c r="Y23">
+        <v>11.5</v>
+      </c>
+      <c r="Z23">
+        <v>11</v>
+      </c>
+      <c r="AA23">
+        <v>13.5</v>
+      </c>
+      <c r="AB23">
+        <v>32</v>
+      </c>
+      <c r="AC23">
+        <v>12.5</v>
+      </c>
+      <c r="AD23">
+        <v>11</v>
+      </c>
+      <c r="AE23">
+        <v>16</v>
+      </c>
+      <c r="AF23">
+        <v>80</v>
+      </c>
+      <c r="AG23">
+        <v>30</v>
+      </c>
+      <c r="AH23">
+        <v>23</v>
+      </c>
+      <c r="AI23">
+        <v>32</v>
+      </c>
+      <c r="AJ23">
+        <v>250</v>
+      </c>
+      <c r="AK23">
+        <v>120</v>
+      </c>
+      <c r="AL23">
+        <v>95</v>
+      </c>
+      <c r="AM23">
+        <v>110</v>
+      </c>
+      <c r="AN23">
+        <v>120</v>
+      </c>
+      <c r="AO23">
+        <v>5.6</v>
+      </c>
+      <c r="AP23">
+        <v>20</v>
+      </c>
+      <c r="AQ23">
+        <v>8.6</v>
+      </c>
+      <c r="AR23">
+        <v>8</v>
+      </c>
+      <c r="AS23">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="AT23">
+        <v>1.01</v>
+      </c>
+      <c r="AU23">
+        <v>10</v>
+      </c>
+      <c r="AV23">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="AW23">
+        <v>11</v>
+      </c>
+      <c r="AX23">
+        <v>1.01</v>
+      </c>
+      <c r="AY23">
+        <v>1.01</v>
+      </c>
+      <c r="AZ23">
+        <v>17</v>
+      </c>
+      <c r="BA23">
+        <v>22</v>
+      </c>
+      <c r="BB23">
+        <v>1.01</v>
+      </c>
+      <c r="BC23">
+        <v>1.01</v>
+      </c>
+      <c r="BD23">
+        <v>1.01</v>
+      </c>
+      <c r="BE23">
+        <v>1.01</v>
+      </c>
+      <c r="BF23">
+        <v>1.01</v>
+      </c>
+      <c r="BG23">
+        <v>4.3</v>
+      </c>
+      <c r="BH23">
         <v>5.1</v>
       </c>
-      <c r="O23">
-        <v>1.13</v>
-      </c>
-      <c r="P23">
-        <v>1.26</v>
-      </c>
-      <c r="Q23">
-        <v>1.13</v>
-      </c>
-      <c r="R23">
-        <v>1.18</v>
-      </c>
-      <c r="S23">
-        <v>1.13</v>
-      </c>
-      <c r="T23">
-        <v>1.01</v>
-      </c>
-      <c r="U23">
-        <v>1.01</v>
-      </c>
-      <c r="V23">
-        <v>2.66</v>
-      </c>
-      <c r="W23">
-        <v>1.1</v>
-      </c>
-      <c r="X23">
-        <v>1000</v>
-      </c>
-      <c r="Y23">
-        <v>1000</v>
-      </c>
-      <c r="Z23">
-        <v>1000</v>
-      </c>
-      <c r="AA23">
-        <v>1000</v>
-      </c>
-      <c r="AB23">
-        <v>1000</v>
-      </c>
-      <c r="AC23">
-        <v>1000</v>
-      </c>
-      <c r="AD23">
-        <v>1000</v>
-      </c>
-      <c r="AE23">
-        <v>1000</v>
-      </c>
-      <c r="AF23">
-        <v>1000</v>
-      </c>
-      <c r="AG23">
-        <v>1000</v>
-      </c>
-      <c r="AH23">
-        <v>1000</v>
-      </c>
-      <c r="AI23">
-        <v>1000</v>
-      </c>
-      <c r="AJ23">
-        <v>1000</v>
-      </c>
-      <c r="AK23">
-        <v>1000</v>
-      </c>
-      <c r="AL23">
-        <v>1000</v>
-      </c>
-      <c r="AM23">
-        <v>1000</v>
-      </c>
-      <c r="AN23">
-        <v>1000</v>
-      </c>
-      <c r="AO23">
-        <v>1000</v>
-      </c>
-      <c r="AP23">
-        <v>1.01</v>
-      </c>
-      <c r="AQ23">
-        <v>1.01</v>
-      </c>
-      <c r="AR23">
-        <v>1.01</v>
-      </c>
-      <c r="AS23">
-        <v>1.01</v>
-      </c>
-      <c r="AT23">
-        <v>1.01</v>
-      </c>
-      <c r="AU23">
-        <v>1.01</v>
-      </c>
-      <c r="AV23">
-        <v>1.01</v>
-      </c>
-      <c r="AW23">
-        <v>1.01</v>
-      </c>
-      <c r="AX23">
-        <v>1.01</v>
-      </c>
-      <c r="AY23">
-        <v>1.01</v>
-      </c>
-      <c r="AZ23">
-        <v>1.01</v>
-      </c>
-      <c r="BA23">
-        <v>1.01</v>
-      </c>
-      <c r="BB23">
-        <v>1.01</v>
-      </c>
-      <c r="BC23">
-        <v>1.01</v>
-      </c>
-      <c r="BD23">
-        <v>1.01</v>
-      </c>
-      <c r="BE23">
-        <v>1.01</v>
-      </c>
-      <c r="BF23">
-        <v>1.01</v>
-      </c>
-      <c r="BG23">
-        <v>1.01</v>
-      </c>
-      <c r="BH23">
-        <v>1000</v>
-      </c>
       <c r="BI23">
-        <v>1.01</v>
+        <v>3.6</v>
       </c>
       <c r="BJ23">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="BK23">
         <v>1.01</v>
       </c>
       <c r="BL23">
-        <v>1000</v>
+        <v>130</v>
       </c>
       <c r="BM23">
         <v>1.01</v>
       </c>
       <c r="BN23">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="BO23">
         <v>1.01</v>
       </c>
       <c r="BP23">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BQ23">
         <v>1.01</v>
       </c>
       <c r="BR23">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="BS23">
         <v>1.01</v>
       </c>
       <c r="BT23">
-        <v>1000</v>
+        <v>4.7</v>
       </c>
       <c r="BU23">
-        <v>1.01</v>
+        <v>3.4</v>
       </c>
       <c r="BV23">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="BW23">
         <v>1.01</v>
       </c>
       <c r="BX23">
-        <v>1000</v>
+        <v>24</v>
       </c>
       <c r="BY23">
         <v>1.01</v>
       </c>
       <c r="BZ23">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="CA23">
         <v>1.01</v>
@@ -6831,76 +6831,76 @@
         <v>6.2</v>
       </c>
       <c r="G24">
-        <v>10.5</v>
+        <v>19.5</v>
       </c>
       <c r="H24">
         <v>1.47</v>
       </c>
       <c r="I24">
-        <v>1.77</v>
+        <v>1.73</v>
       </c>
       <c r="J24">
-        <v>3.5</v>
+        <v>3.7</v>
       </c>
       <c r="K24">
-        <v>6.4</v>
+        <v>6</v>
       </c>
       <c r="L24">
         <v>1.33</v>
       </c>
       <c r="M24">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="N24">
         <v>3.55</v>
       </c>
       <c r="O24">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="P24">
-        <v>1.69</v>
+        <v>1.73</v>
       </c>
       <c r="Q24">
-        <v>1.89</v>
+        <v>1.83</v>
       </c>
       <c r="R24">
-        <v>1.2</v>
+        <v>1.22</v>
       </c>
       <c r="S24">
-        <v>1.89</v>
+        <v>2.72</v>
       </c>
       <c r="T24">
-        <v>1.01</v>
+        <v>1.94</v>
       </c>
       <c r="U24">
         <v>1.01</v>
       </c>
       <c r="V24">
-        <v>2.3</v>
+        <v>2.38</v>
       </c>
       <c r="W24">
-        <v>1.11</v>
+        <v>1.05</v>
       </c>
       <c r="X24">
         <v>1000</v>
       </c>
       <c r="Y24">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="Z24">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AA24">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AB24">
         <v>1000</v>
       </c>
       <c r="AC24">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AD24">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AE24">
         <v>1000</v>
@@ -6939,22 +6939,22 @@
         <v>1.01</v>
       </c>
       <c r="AQ24">
-        <v>1.01</v>
+        <v>5.1</v>
       </c>
       <c r="AR24">
-        <v>1.01</v>
+        <v>5.7</v>
       </c>
       <c r="AS24">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="AT24">
         <v>1.01</v>
       </c>
       <c r="AU24">
-        <v>1.01</v>
+        <v>6.6</v>
       </c>
       <c r="AV24">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AW24">
         <v>1.01</v>
@@ -6966,22 +6966,22 @@
         <v>1.01</v>
       </c>
       <c r="AZ24">
-        <v>1.01</v>
+        <v>13.5</v>
       </c>
       <c r="BA24">
         <v>1.01</v>
       </c>
       <c r="BB24">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BC24">
-        <v>1.01</v>
+        <v>1.03</v>
       </c>
       <c r="BD24">
-        <v>1.01</v>
+        <v>1.07</v>
       </c>
       <c r="BE24">
-        <v>1.01</v>
+        <v>1.13</v>
       </c>
       <c r="BF24">
         <v>1.01</v>
@@ -7094,7 +7094,7 @@
         <v>1.07</v>
       </c>
       <c r="N25">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="O25">
         <v>1.31</v>
@@ -7103,7 +7103,7 @@
         <v>1.76</v>
       </c>
       <c r="Q25">
-        <v>1.86</v>
+        <v>1.89</v>
       </c>
       <c r="R25">
         <v>1.29</v>
@@ -7139,13 +7139,13 @@
         <v>11.5</v>
       </c>
       <c r="AC25">
-        <v>8.4</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD25">
         <v>17</v>
       </c>
       <c r="AE25">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AF25">
         <v>17</v>
@@ -7175,7 +7175,7 @@
         <v>23</v>
       </c>
       <c r="AO25">
-        <v>44</v>
+        <v>50</v>
       </c>
       <c r="AP25">
         <v>1.01</v>
@@ -7312,16 +7312,16 @@
         <v>247</v>
       </c>
       <c r="F26">
-        <v>2.24</v>
+        <v>2.3</v>
       </c>
       <c r="G26">
-        <v>2.3</v>
+        <v>2.32</v>
       </c>
       <c r="H26">
-        <v>3.25</v>
+        <v>3.2</v>
       </c>
       <c r="I26">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="J26">
         <v>3.85</v>
@@ -7336,13 +7336,13 @@
         <v>1.05</v>
       </c>
       <c r="N26">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="O26">
         <v>1.26</v>
       </c>
       <c r="P26">
-        <v>2.18</v>
+        <v>2.16</v>
       </c>
       <c r="Q26">
         <v>1.81</v>
@@ -7354,16 +7354,16 @@
         <v>2.94</v>
       </c>
       <c r="T26">
-        <v>1.68</v>
+        <v>1.67</v>
       </c>
       <c r="U26">
         <v>2.36</v>
       </c>
       <c r="V26">
-        <v>1.42</v>
+        <v>1.43</v>
       </c>
       <c r="W26">
-        <v>1.77</v>
+        <v>1.76</v>
       </c>
       <c r="X26">
         <v>18</v>
@@ -7375,7 +7375,7 @@
         <v>25</v>
       </c>
       <c r="AA26">
-        <v>60</v>
+        <v>350</v>
       </c>
       <c r="AB26">
         <v>12</v>
@@ -7384,13 +7384,13 @@
         <v>8.6</v>
       </c>
       <c r="AD26">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AE26">
         <v>60</v>
       </c>
       <c r="AF26">
-        <v>15.5</v>
+        <v>16</v>
       </c>
       <c r="AG26">
         <v>11.5</v>
@@ -7435,7 +7435,7 @@
         <v>10.5</v>
       </c>
       <c r="AU26">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AV26">
         <v>12.5</v>
@@ -7453,7 +7453,7 @@
         <v>15</v>
       </c>
       <c r="BA26">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BB26">
         <v>26</v>
@@ -7557,16 +7557,16 @@
         <v>2.12</v>
       </c>
       <c r="G27">
-        <v>2.24</v>
+        <v>2.26</v>
       </c>
       <c r="H27">
-        <v>3.4</v>
+        <v>3.35</v>
       </c>
       <c r="I27">
         <v>3.85</v>
       </c>
       <c r="J27">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K27">
         <v>3.9</v>
@@ -7581,10 +7581,10 @@
         <v>4.1</v>
       </c>
       <c r="O27">
-        <v>1.23</v>
+        <v>1.26</v>
       </c>
       <c r="P27">
-        <v>2.08</v>
+        <v>2.12</v>
       </c>
       <c r="Q27">
         <v>1.76</v>
@@ -7605,7 +7605,7 @@
         <v>1.35</v>
       </c>
       <c r="W27">
-        <v>1.8</v>
+        <v>1.79</v>
       </c>
       <c r="X27">
         <v>70</v>
@@ -7638,7 +7638,7 @@
         <v>21</v>
       </c>
       <c r="AH27">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI27">
         <v>1000</v>
@@ -7647,7 +7647,7 @@
         <v>1000</v>
       </c>
       <c r="AK27">
-        <v>160</v>
+        <v>120</v>
       </c>
       <c r="AL27">
         <v>1000</v>
@@ -7662,58 +7662,58 @@
         <v>1000</v>
       </c>
       <c r="AP27">
-        <v>1.31</v>
+        <v>1.35</v>
       </c>
       <c r="AQ27">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AR27">
-        <v>5.2</v>
+        <v>5.5</v>
       </c>
       <c r="AS27">
-        <v>14</v>
+        <v>14.5</v>
       </c>
       <c r="AT27">
-        <v>8</v>
+        <v>8.4</v>
       </c>
       <c r="AU27">
-        <v>1.16</v>
+        <v>1.19</v>
       </c>
       <c r="AV27">
-        <v>1.32</v>
+        <v>1.35</v>
       </c>
       <c r="AW27">
         <v>11</v>
       </c>
       <c r="AX27">
-        <v>1.34</v>
+        <v>10</v>
       </c>
       <c r="AY27">
-        <v>1.26</v>
+        <v>1.29</v>
       </c>
       <c r="AZ27">
-        <v>1.34</v>
+        <v>11.5</v>
       </c>
       <c r="BA27">
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="BB27">
-        <v>9.4</v>
+        <v>9.6</v>
       </c>
       <c r="BC27">
-        <v>12.5</v>
+        <v>5.6</v>
       </c>
       <c r="BD27">
         <v>11</v>
       </c>
       <c r="BE27">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="BF27">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="BG27">
-        <v>1.34</v>
+        <v>1.37</v>
       </c>
       <c r="BH27">
         <v>1000</v>
@@ -7796,13 +7796,13 @@
         <v>249</v>
       </c>
       <c r="F28">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="G28">
         <v>2.16</v>
       </c>
       <c r="H28">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="I28">
         <v>3.8</v>
@@ -7814,7 +7814,7 @@
         <v>4</v>
       </c>
       <c r="L28">
-        <v>1.01</v>
+        <v>1.28</v>
       </c>
       <c r="M28">
         <v>1.05</v>
@@ -7826,10 +7826,10 @@
         <v>1.22</v>
       </c>
       <c r="P28">
-        <v>2.12</v>
+        <v>2.1</v>
       </c>
       <c r="Q28">
-        <v>1.65</v>
+        <v>1.66</v>
       </c>
       <c r="R28">
         <v>1.44</v>
@@ -7838,10 +7838,10 @@
         <v>2.66</v>
       </c>
       <c r="T28">
-        <v>1.6</v>
+        <v>1.57</v>
       </c>
       <c r="U28">
-        <v>2.42</v>
+        <v>2.4</v>
       </c>
       <c r="V28">
         <v>1.36</v>
@@ -7865,7 +7865,7 @@
         <v>970</v>
       </c>
       <c r="AC28">
-        <v>10.5</v>
+        <v>11.5</v>
       </c>
       <c r="AD28">
         <v>970</v>
@@ -7880,7 +7880,7 @@
         <v>970</v>
       </c>
       <c r="AH28">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="AI28">
         <v>1000</v>
@@ -7904,100 +7904,100 @@
         <v>1000</v>
       </c>
       <c r="AP28">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="AQ28">
+        <v>1.33</v>
+      </c>
+      <c r="AR28">
+        <v>6.2</v>
+      </c>
+      <c r="AS28">
+        <v>20</v>
+      </c>
+      <c r="AT28">
+        <v>1.33</v>
+      </c>
+      <c r="AU28">
+        <v>1.21</v>
+      </c>
+      <c r="AV28">
+        <v>1.33</v>
+      </c>
+      <c r="AW28">
+        <v>14.5</v>
+      </c>
+      <c r="AX28">
+        <v>1.33</v>
+      </c>
+      <c r="AY28">
         <v>1.32</v>
       </c>
-      <c r="AR28">
-        <v>6.4</v>
-      </c>
-      <c r="AS28">
-        <v>19.5</v>
-      </c>
-      <c r="AT28">
-        <v>1.32</v>
-      </c>
-      <c r="AU28">
-        <v>1.18</v>
-      </c>
-      <c r="AV28">
-        <v>1.32</v>
-      </c>
-      <c r="AW28">
-        <v>14</v>
-      </c>
-      <c r="AX28">
-        <v>1.32</v>
-      </c>
-      <c r="AY28">
-        <v>1.31</v>
-      </c>
       <c r="AZ28">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="BA28">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB28">
         <v>11</v>
       </c>
       <c r="BC28">
-        <v>1.33</v>
+        <v>1.34</v>
       </c>
       <c r="BD28">
-        <v>11</v>
+        <v>11.5</v>
       </c>
       <c r="BE28">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BF28">
-        <v>1.34</v>
+        <v>1.35</v>
       </c>
       <c r="BG28">
-        <v>1.35</v>
+        <v>1.36</v>
       </c>
       <c r="BH28">
-        <v>1000</v>
+        <v>4.6</v>
       </c>
       <c r="BI28">
-        <v>1.01</v>
+        <v>3.1</v>
       </c>
       <c r="BJ28">
-        <v>1000</v>
+        <v>13</v>
       </c>
       <c r="BK28">
         <v>1.01</v>
       </c>
       <c r="BL28">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BM28">
         <v>1.01</v>
       </c>
       <c r="BN28">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="BO28">
-        <v>1.01</v>
+        <v>4</v>
       </c>
       <c r="BP28">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="BQ28">
         <v>1.01</v>
       </c>
       <c r="BR28">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BS28">
         <v>1.01</v>
       </c>
       <c r="BT28">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="BU28">
-        <v>1.01</v>
+        <v>4.5</v>
       </c>
       <c r="BV28">
         <v>1000</v>
@@ -8006,13 +8006,13 @@
         <v>1.01</v>
       </c>
       <c r="BX28">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="BY28">
         <v>1.01</v>
       </c>
       <c r="BZ28">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="CA28">
         <v>1.01</v>
@@ -8038,16 +8038,16 @@
         <v>250</v>
       </c>
       <c r="F29">
-        <v>3.9</v>
+        <v>3.95</v>
       </c>
       <c r="G29">
         <v>4.2</v>
       </c>
       <c r="H29">
+        <v>1.88</v>
+      </c>
+      <c r="I29">
         <v>1.9</v>
-      </c>
-      <c r="I29">
-        <v>1.91</v>
       </c>
       <c r="J29">
         <v>4.3</v>
@@ -8068,10 +8068,10 @@
         <v>1.18</v>
       </c>
       <c r="P29">
-        <v>2.66</v>
+        <v>2.68</v>
       </c>
       <c r="Q29">
-        <v>1.56</v>
+        <v>1.55</v>
       </c>
       <c r="R29">
         <v>1.66</v>
@@ -8086,7 +8086,7 @@
         <v>2.62</v>
       </c>
       <c r="V29">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="W29">
         <v>1.32</v>
@@ -8125,7 +8125,7 @@
         <v>16</v>
       </c>
       <c r="AI29">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AJ29">
         <v>85</v>
@@ -8140,7 +8140,7 @@
         <v>65</v>
       </c>
       <c r="AN29">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AO29">
         <v>8.4</v>
@@ -8194,10 +8194,10 @@
         <v>50</v>
       </c>
       <c r="BF29">
-        <v>24</v>
+        <v>19.5</v>
       </c>
       <c r="BG29">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="BH29">
         <v>1000</v>
@@ -8304,7 +8304,7 @@
         <v>1.07</v>
       </c>
       <c r="N30">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="O30">
         <v>1.32</v>
@@ -8319,7 +8319,7 @@
         <v>1.33</v>
       </c>
       <c r="S30">
-        <v>3.3</v>
+        <v>3.35</v>
       </c>
       <c r="T30">
         <v>1.72</v>
@@ -8340,7 +8340,7 @@
         <v>970</v>
       </c>
       <c r="Z30">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AA30">
         <v>1000</v>
@@ -8364,7 +8364,7 @@
         <v>970</v>
       </c>
       <c r="AH30">
-        <v>85</v>
+        <v>80</v>
       </c>
       <c r="AI30">
         <v>1000</v>
@@ -8388,58 +8388,58 @@
         <v>1000</v>
       </c>
       <c r="AP30">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AQ30">
-        <v>1.35</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AR30">
         <v>5.6</v>
       </c>
       <c r="AS30">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="AT30">
+        <v>1.33</v>
+      </c>
+      <c r="AU30">
+        <v>1.19</v>
+      </c>
+      <c r="AV30">
+        <v>1.33</v>
+      </c>
+      <c r="AW30">
+        <v>17.5</v>
+      </c>
+      <c r="AX30">
         <v>1.34</v>
       </c>
-      <c r="AU30">
-        <v>1.18</v>
-      </c>
-      <c r="AV30">
-        <v>1.35</v>
-      </c>
-      <c r="AW30">
-        <v>14.5</v>
-      </c>
-      <c r="AX30">
-        <v>1.35</v>
-      </c>
       <c r="AY30">
-        <v>1.35</v>
+        <v>1.33</v>
       </c>
       <c r="AZ30">
-        <v>1.36</v>
+        <v>13</v>
       </c>
       <c r="BA30">
-        <v>18.5</v>
+        <v>17</v>
       </c>
       <c r="BB30">
-        <v>14</v>
+        <v>16.5</v>
       </c>
       <c r="BC30">
-        <v>9.199999999999999</v>
+        <v>8.800000000000001</v>
       </c>
       <c r="BD30">
-        <v>16.5</v>
+        <v>15.5</v>
       </c>
       <c r="BE30">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BF30">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="BG30">
-        <v>1.39</v>
+        <v>1.37</v>
       </c>
       <c r="BH30">
         <v>1000</v>
@@ -8546,16 +8546,16 @@
         <v>1.01</v>
       </c>
       <c r="N31">
-        <v>2.8</v>
+        <v>1.01</v>
       </c>
       <c r="O31">
         <v>1.33</v>
       </c>
       <c r="P31">
-        <v>1.81</v>
+        <v>1.83</v>
       </c>
       <c r="Q31">
-        <v>1.99</v>
+        <v>1.01</v>
       </c>
       <c r="R31">
         <v>1.27</v>
@@ -8764,19 +8764,19 @@
         <v>253</v>
       </c>
       <c r="F32">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="G32">
         <v>110</v>
       </c>
       <c r="H32">
-        <v>1.12</v>
+        <v>1.13</v>
       </c>
       <c r="I32">
         <v>110</v>
       </c>
       <c r="J32">
-        <v>1.1</v>
+        <v>1.24</v>
       </c>
       <c r="K32">
         <v>300</v>
@@ -8788,22 +8788,22 @@
         <v>1.01</v>
       </c>
       <c r="N32">
-        <v>1.17</v>
+        <v>2.64</v>
       </c>
       <c r="O32">
         <v>1.02</v>
       </c>
       <c r="P32">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="Q32">
         <v>1.38</v>
       </c>
       <c r="R32">
-        <v>1.16</v>
+        <v>1.08</v>
       </c>
       <c r="S32">
-        <v>1.38</v>
+        <v>1.4</v>
       </c>
       <c r="T32">
         <v>1.01</v>
@@ -8812,10 +8812,10 @@
         <v>1.01</v>
       </c>
       <c r="V32">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="W32">
-        <v>1.09</v>
+        <v>1.11</v>
       </c>
       <c r="X32">
         <v>1000</v>
@@ -9042,7 +9042,7 @@
         <v>1.63</v>
       </c>
       <c r="R33">
-        <v>1.6</v>
+        <v>1.59</v>
       </c>
       <c r="S33">
         <v>2.56</v>
@@ -9078,13 +9078,13 @@
         <v>9.6</v>
       </c>
       <c r="AD33">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AE33">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="AF33">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AG33">
         <v>11</v>
@@ -9108,7 +9108,7 @@
         <v>75</v>
       </c>
       <c r="AN33">
-        <v>10</v>
+        <v>11.5</v>
       </c>
       <c r="AO33">
         <v>42</v>
@@ -9117,7 +9117,7 @@
         <v>17.5</v>
       </c>
       <c r="AQ33">
-        <v>17.5</v>
+        <v>17</v>
       </c>
       <c r="AR33">
         <v>21</v>
@@ -9204,7 +9204,7 @@
         <v>1.01</v>
       </c>
       <c r="BT33">
-        <v>9</v>
+        <v>7.6</v>
       </c>
       <c r="BU33">
         <v>5.7</v>
@@ -9248,112 +9248,112 @@
         <v>255</v>
       </c>
       <c r="F34">
-        <v>2.32</v>
+        <v>2.36</v>
       </c>
       <c r="G34">
-        <v>2.7</v>
+        <v>2.6</v>
       </c>
       <c r="H34">
         <v>2.96</v>
       </c>
       <c r="I34">
-        <v>3.65</v>
+        <v>3.7</v>
       </c>
       <c r="J34">
+        <v>3.1</v>
+      </c>
+      <c r="K34">
+        <v>3.7</v>
+      </c>
+      <c r="L34">
+        <v>1.37</v>
+      </c>
+      <c r="M34">
+        <v>1.07</v>
+      </c>
+      <c r="N34">
         <v>3.15</v>
       </c>
-      <c r="K34">
-        <v>4.4</v>
-      </c>
-      <c r="L34">
-        <v>1.01</v>
-      </c>
-      <c r="M34">
-        <v>1.01</v>
-      </c>
-      <c r="N34">
-        <v>1.01</v>
-      </c>
       <c r="O34">
-        <v>1.01</v>
+        <v>1.34</v>
       </c>
       <c r="P34">
-        <v>1.1</v>
+        <v>1.85</v>
       </c>
       <c r="Q34">
-        <v>1.98</v>
+        <v>2</v>
       </c>
       <c r="R34">
-        <v>1.28</v>
+        <v>1.32</v>
       </c>
       <c r="S34">
-        <v>3.1</v>
+        <v>3.5</v>
       </c>
       <c r="T34">
-        <v>1.01</v>
+        <v>1.68</v>
       </c>
       <c r="U34">
-        <v>1.01</v>
+        <v>1.96</v>
       </c>
       <c r="V34">
-        <v>1.01</v>
+        <v>1.37</v>
       </c>
       <c r="W34">
-        <v>1.52</v>
+        <v>1.63</v>
       </c>
       <c r="X34">
-        <v>1000</v>
+        <v>15.5</v>
       </c>
       <c r="Y34">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="Z34">
-        <v>1000</v>
+        <v>26</v>
       </c>
       <c r="AA34">
-        <v>1000</v>
+        <v>65</v>
       </c>
       <c r="AB34">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="AC34">
-        <v>1000</v>
+        <v>9</v>
       </c>
       <c r="AD34">
-        <v>1000</v>
+        <v>16</v>
       </c>
       <c r="AE34">
-        <v>1000</v>
+        <v>46</v>
       </c>
       <c r="AF34">
-        <v>1000</v>
+        <v>18.5</v>
       </c>
       <c r="AG34">
-        <v>1000</v>
+        <v>13.5</v>
       </c>
       <c r="AH34">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="AI34">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AJ34">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AK34">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="AL34">
-        <v>1000</v>
+        <v>48</v>
       </c>
       <c r="AM34">
-        <v>1000</v>
+        <v>120</v>
       </c>
       <c r="AN34">
-        <v>1000</v>
+        <v>27</v>
       </c>
       <c r="AO34">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="AP34">
         <v>1.01</v>
@@ -9410,61 +9410,61 @@
         <v>1.01</v>
       </c>
       <c r="BH34">
-        <v>1000</v>
+        <v>3.7</v>
       </c>
       <c r="BI34">
-        <v>1.01</v>
+        <v>2.74</v>
       </c>
       <c r="BJ34">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BK34">
         <v>1.01</v>
       </c>
       <c r="BL34">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="BM34">
         <v>1.01</v>
       </c>
       <c r="BN34">
-        <v>1000</v>
+        <v>6.2</v>
       </c>
       <c r="BO34">
         <v>1.01</v>
       </c>
       <c r="BP34">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="BQ34">
         <v>1.01</v>
       </c>
       <c r="BR34">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="BS34">
         <v>1.01</v>
       </c>
       <c r="BT34">
-        <v>1000</v>
+        <v>7.2</v>
       </c>
       <c r="BU34">
         <v>1.01</v>
       </c>
       <c r="BV34">
-        <v>1000</v>
+        <v>30</v>
       </c>
       <c r="BW34">
         <v>1.01</v>
       </c>
       <c r="BX34">
-        <v>1000</v>
+        <v>44</v>
       </c>
       <c r="BY34">
         <v>1.01</v>
       </c>
       <c r="BZ34">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="CA34">
         <v>1.01</v>
@@ -9490,22 +9490,22 @@
         <v>256</v>
       </c>
       <c r="F35">
-        <v>1.08</v>
+        <v>3.25</v>
       </c>
       <c r="G35">
-        <v>1000</v>
+        <v>5.6</v>
       </c>
       <c r="H35">
-        <v>1.08</v>
+        <v>1.91</v>
       </c>
       <c r="I35">
-        <v>1000</v>
+        <v>2.28</v>
       </c>
       <c r="J35">
-        <v>1.08</v>
+        <v>2.78</v>
       </c>
       <c r="K35">
-        <v>1000</v>
+        <v>5.9</v>
       </c>
       <c r="L35">
         <v>1.01</v>
@@ -9514,13 +9514,13 @@
         <v>1.01</v>
       </c>
       <c r="N35">
-        <v>2.64</v>
+        <v>2.68</v>
       </c>
       <c r="O35">
         <v>1.01</v>
       </c>
       <c r="P35">
-        <v>1.61</v>
+        <v>1.62</v>
       </c>
       <c r="Q35">
         <v>1.92</v>
@@ -9529,7 +9529,7 @@
         <v>1.18</v>
       </c>
       <c r="S35">
-        <v>1.02</v>
+        <v>2.66</v>
       </c>
       <c r="T35">
         <v>1.01</v>
@@ -9538,10 +9538,10 @@
         <v>1.01</v>
       </c>
       <c r="V35">
-        <v>1.53</v>
+        <v>1.78</v>
       </c>
       <c r="W35">
-        <v>1.32</v>
+        <v>1.21</v>
       </c>
       <c r="X35">
         <v>1000</v>
@@ -9750,7 +9750,7 @@
         <v>6.2</v>
       </c>
       <c r="L36">
-        <v>1.01</v>
+        <v>1.26</v>
       </c>
       <c r="M36">
         <v>1.04</v>
@@ -9980,10 +9980,10 @@
         <v>6.4</v>
       </c>
       <c r="H37">
+        <v>1.65</v>
+      </c>
+      <c r="I37">
         <v>1.66</v>
-      </c>
-      <c r="I37">
-        <v>1.68</v>
       </c>
       <c r="J37">
         <v>4.2</v>
@@ -9992,7 +9992,7 @@
         <v>4.3</v>
       </c>
       <c r="L37">
-        <v>1.38</v>
+        <v>1.35</v>
       </c>
       <c r="M37">
         <v>1.06</v>
@@ -10001,7 +10001,7 @@
         <v>3.8</v>
       </c>
       <c r="O37">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="P37">
         <v>1.97</v>
@@ -10016,19 +10016,19 @@
         <v>3.2</v>
       </c>
       <c r="T37">
-        <v>1.85</v>
+        <v>1.86</v>
       </c>
       <c r="U37">
         <v>1.98</v>
       </c>
       <c r="V37">
-        <v>2.46</v>
+        <v>2.5</v>
       </c>
       <c r="W37">
         <v>1.18</v>
       </c>
       <c r="X37">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="Y37">
         <v>8.800000000000001</v>
@@ -10055,7 +10055,7 @@
         <v>55</v>
       </c>
       <c r="AG37">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AH37">
         <v>23</v>
@@ -10064,7 +10064,7 @@
         <v>38</v>
       </c>
       <c r="AJ37">
-        <v>170</v>
+        <v>160</v>
       </c>
       <c r="AK37">
         <v>90</v>
@@ -10073,7 +10073,7 @@
         <v>80</v>
       </c>
       <c r="AM37">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="AN37">
         <v>110</v>
@@ -10118,16 +10118,16 @@
         <v>30</v>
       </c>
       <c r="BB37">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC37">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="BD37">
         <v>8.800000000000001</v>
       </c>
       <c r="BE37">
-        <v>9</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BF37">
         <v>9</v>
@@ -10216,10 +10216,10 @@
         <v>259</v>
       </c>
       <c r="F38">
+        <v>8.6</v>
+      </c>
+      <c r="G38">
         <v>8.800000000000001</v>
-      </c>
-      <c r="G38">
-        <v>9</v>
       </c>
       <c r="H38">
         <v>1.5</v>
@@ -10237,7 +10237,7 @@
         <v>1.45</v>
       </c>
       <c r="M38">
-        <v>1.07</v>
+        <v>1.08</v>
       </c>
       <c r="N38">
         <v>3.6</v>
@@ -10252,7 +10252,7 @@
         <v>2.1</v>
       </c>
       <c r="R38">
-        <v>1.33</v>
+        <v>1.32</v>
       </c>
       <c r="S38">
         <v>3.9</v>
@@ -10288,7 +10288,7 @@
         <v>10</v>
       </c>
       <c r="AD38">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AE38">
         <v>18</v>
@@ -10348,7 +10348,7 @@
         <v>16</v>
       </c>
       <c r="AX38">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AY38">
         <v>30</v>
@@ -10360,7 +10360,7 @@
         <v>44</v>
       </c>
       <c r="BB38">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BC38">
         <v>44</v>
@@ -10369,70 +10369,70 @@
         <v>44</v>
       </c>
       <c r="BE38">
-        <v>17</v>
+        <v>48</v>
       </c>
       <c r="BF38">
-        <v>16.5</v>
+        <v>17.5</v>
       </c>
       <c r="BG38">
         <v>8.6</v>
       </c>
       <c r="BH38">
-        <v>970</v>
+        <v>3.35</v>
       </c>
       <c r="BI38">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BJ38">
-        <v>1000</v>
+        <v>15</v>
       </c>
       <c r="BK38">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="BL38">
-        <v>1000</v>
+        <v>250</v>
       </c>
       <c r="BM38">
         <v>34</v>
       </c>
       <c r="BN38">
-        <v>1000</v>
+        <v>14.5</v>
       </c>
       <c r="BO38">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="BP38">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BQ38">
-        <v>19</v>
+        <v>7.4</v>
       </c>
       <c r="BR38">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="BS38">
         <v>20</v>
       </c>
       <c r="BT38">
-        <v>970</v>
+        <v>3.8</v>
       </c>
       <c r="BU38">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="BV38">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="BW38">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BX38">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="BY38">
         <v>12.5</v>
       </c>
       <c r="BZ38">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="CA38">
         <v>8.800000000000001</v>
@@ -10458,13 +10458,13 @@
         <v>260</v>
       </c>
       <c r="F39">
-        <v>1.98</v>
+        <v>1.97</v>
       </c>
       <c r="G39">
         <v>2.04</v>
       </c>
       <c r="H39">
-        <v>3.6</v>
+        <v>3.65</v>
       </c>
       <c r="I39">
         <v>3.85</v>
@@ -10482,13 +10482,13 @@
         <v>1.03</v>
       </c>
       <c r="N39">
-        <v>5.8</v>
+        <v>6</v>
       </c>
       <c r="O39">
-        <v>1.19</v>
+        <v>1.18</v>
       </c>
       <c r="P39">
-        <v>2.66</v>
+        <v>2.64</v>
       </c>
       <c r="Q39">
         <v>1.56</v>
@@ -10500,7 +10500,7 @@
         <v>2.38</v>
       </c>
       <c r="T39">
-        <v>1.52</v>
+        <v>1.54</v>
       </c>
       <c r="U39">
         <v>2.68</v>
@@ -10509,13 +10509,13 @@
         <v>1.35</v>
       </c>
       <c r="W39">
-        <v>1.96</v>
+        <v>1.97</v>
       </c>
       <c r="X39">
-        <v>28</v>
+        <v>46</v>
       </c>
       <c r="Y39">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="Z39">
         <v>55</v>
@@ -10527,58 +10527,58 @@
         <v>15</v>
       </c>
       <c r="AC39">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="AD39">
         <v>16.5</v>
       </c>
       <c r="AE39">
-        <v>70</v>
+        <v>55</v>
       </c>
       <c r="AF39">
-        <v>16.5</v>
+        <v>16</v>
       </c>
       <c r="AG39">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH39">
         <v>16</v>
       </c>
       <c r="AI39">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AJ39">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK39">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AL39">
+        <v>38</v>
+      </c>
+      <c r="AM39">
+        <v>380</v>
+      </c>
+      <c r="AN39">
+        <v>9.199999999999999</v>
+      </c>
+      <c r="AO39">
         <v>40</v>
-      </c>
-      <c r="AM39">
-        <v>400</v>
-      </c>
-      <c r="AN39">
-        <v>8.800000000000001</v>
-      </c>
-      <c r="AO39">
-        <v>26</v>
       </c>
       <c r="AP39">
         <v>19</v>
       </c>
       <c r="AQ39">
-        <v>18</v>
+        <v>18.5</v>
       </c>
       <c r="AR39">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AS39">
-        <v>32</v>
+        <v>40</v>
       </c>
       <c r="AT39">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AU39">
         <v>9.199999999999999</v>
@@ -10596,10 +10596,10 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AZ39">
-        <v>12</v>
+        <v>13.5</v>
       </c>
       <c r="BA39">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB39">
         <v>20</v>
@@ -10611,7 +10611,7 @@
         <v>17.5</v>
       </c>
       <c r="BE39">
-        <v>29</v>
+        <v>36</v>
       </c>
       <c r="BF39">
         <v>8.199999999999999</v>
@@ -10700,13 +10700,13 @@
         <v>261</v>
       </c>
       <c r="F40">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="G40">
-        <v>3.4</v>
+        <v>3.45</v>
       </c>
       <c r="H40">
-        <v>2.32</v>
+        <v>2.3</v>
       </c>
       <c r="I40">
         <v>2.46</v>
@@ -10730,10 +10730,10 @@
         <v>1.31</v>
       </c>
       <c r="P40">
-        <v>1.95</v>
+        <v>1.96</v>
       </c>
       <c r="Q40">
-        <v>1.84</v>
+        <v>1.92</v>
       </c>
       <c r="R40">
         <v>1.37</v>
@@ -10751,7 +10751,7 @@
         <v>1.69</v>
       </c>
       <c r="W40">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="X40">
         <v>18</v>
@@ -10945,19 +10945,19 @@
         <v>1.44</v>
       </c>
       <c r="G41">
-        <v>1.58</v>
+        <v>1.61</v>
       </c>
       <c r="H41">
-        <v>6.4</v>
+        <v>2.7</v>
       </c>
       <c r="I41">
-        <v>8.800000000000001</v>
+        <v>110</v>
       </c>
       <c r="J41">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="K41">
-        <v>6.4</v>
+        <v>110</v>
       </c>
       <c r="L41">
         <v>1.01</v>
@@ -10966,16 +10966,16 @@
         <v>1.03</v>
       </c>
       <c r="N41">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="O41">
         <v>1.1</v>
       </c>
       <c r="P41">
-        <v>2.6</v>
+        <v>2.56</v>
       </c>
       <c r="Q41">
-        <v>1.49</v>
+        <v>1.11</v>
       </c>
       <c r="R41">
         <v>1.63</v>
@@ -10990,10 +10990,10 @@
         <v>1.01</v>
       </c>
       <c r="V41">
-        <v>1.13</v>
+        <v>1.02</v>
       </c>
       <c r="W41">
-        <v>2.74</v>
+        <v>2.64</v>
       </c>
       <c r="X41">
         <v>1000</v>
@@ -11214,7 +11214,7 @@
         <v>1.19</v>
       </c>
       <c r="P42">
-        <v>2.56</v>
+        <v>2.62</v>
       </c>
       <c r="Q42">
         <v>1.57</v>
@@ -11313,7 +11313,7 @@
         <v>19</v>
       </c>
       <c r="AW42">
-        <v>8.800000000000001</v>
+        <v>8.6</v>
       </c>
       <c r="AX42">
         <v>10</v>
@@ -11331,7 +11331,7 @@
         <v>13.5</v>
       </c>
       <c r="BC42">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="BD42">
         <v>7.4</v>
@@ -11429,7 +11429,7 @@
         <v>1.67</v>
       </c>
       <c r="G43">
-        <v>1.72</v>
+        <v>1.79</v>
       </c>
       <c r="H43">
         <v>4.8</v>
@@ -11438,10 +11438,10 @@
         <v>5.9</v>
       </c>
       <c r="J43">
-        <v>4.1</v>
+        <v>3.8</v>
       </c>
       <c r="K43">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="L43">
         <v>1.01</v>
@@ -11456,7 +11456,7 @@
         <v>1.22</v>
       </c>
       <c r="P43">
-        <v>2.24</v>
+        <v>2.22</v>
       </c>
       <c r="Q43">
         <v>1.67</v>
@@ -11468,7 +11468,7 @@
         <v>2.68</v>
       </c>
       <c r="T43">
-        <v>1.78</v>
+        <v>1.77</v>
       </c>
       <c r="U43">
         <v>2.18</v>
@@ -11477,7 +11477,7 @@
         <v>1.22</v>
       </c>
       <c r="W43">
-        <v>2.38</v>
+        <v>2.26</v>
       </c>
       <c r="X43">
         <v>21</v>
@@ -11513,7 +11513,7 @@
         <v>19.5</v>
       </c>
       <c r="AI43">
-        <v>150</v>
+        <v>90</v>
       </c>
       <c r="AJ43">
         <v>18</v>
@@ -11680,7 +11680,7 @@
         <v>27</v>
       </c>
       <c r="J44">
-        <v>7.4</v>
+        <v>7</v>
       </c>
       <c r="K44">
         <v>11</v>
@@ -11707,7 +11707,7 @@
         <v>1.76</v>
       </c>
       <c r="S44">
-        <v>2.1</v>
+        <v>2.18</v>
       </c>
       <c r="T44">
         <v>2.24</v>
@@ -11719,7 +11719,7 @@
         <v>1.04</v>
       </c>
       <c r="W44">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="X44">
         <v>42</v>
@@ -11910,7 +11910,7 @@
         <v>266</v>
       </c>
       <c r="F45">
-        <v>1.76</v>
+        <v>1.67</v>
       </c>
       <c r="G45">
         <v>1.81</v>
@@ -11919,13 +11919,13 @@
         <v>5.7</v>
       </c>
       <c r="I45">
-        <v>6.6</v>
+        <v>7.4</v>
       </c>
       <c r="J45">
         <v>3.55</v>
       </c>
       <c r="K45">
-        <v>3.85</v>
+        <v>4.7</v>
       </c>
       <c r="L45">
         <v>1.36</v>
@@ -11934,22 +11934,22 @@
         <v>1.09</v>
       </c>
       <c r="N45">
-        <v>3.2</v>
+        <v>3.15</v>
       </c>
       <c r="O45">
-        <v>1.4</v>
+        <v>1.39</v>
       </c>
       <c r="P45">
-        <v>1.75</v>
+        <v>1.74</v>
       </c>
       <c r="Q45">
-        <v>2.16</v>
+        <v>2.08</v>
       </c>
       <c r="R45">
         <v>1.28</v>
       </c>
       <c r="S45">
-        <v>4.1</v>
+        <v>4</v>
       </c>
       <c r="T45">
         <v>2.04</v>
@@ -11958,7 +11958,7 @@
         <v>1.83</v>
       </c>
       <c r="V45">
-        <v>1.18</v>
+        <v>1.15</v>
       </c>
       <c r="W45">
         <v>2.22</v>
@@ -12272,7 +12272,7 @@
         <v>20</v>
       </c>
       <c r="AT46">
-        <v>10.5</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AU46">
         <v>6.4</v>
@@ -12281,19 +12281,19 @@
         <v>8.4</v>
       </c>
       <c r="AW46">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX46">
         <v>1.01</v>
       </c>
       <c r="AY46">
-        <v>14.5</v>
+        <v>14</v>
       </c>
       <c r="AZ46">
         <v>18.5</v>
       </c>
       <c r="BA46">
-        <v>38</v>
+        <v>1.01</v>
       </c>
       <c r="BB46">
         <v>1.01</v>
@@ -12397,7 +12397,7 @@
         <v>1.39</v>
       </c>
       <c r="G47">
-        <v>1.41</v>
+        <v>1.43</v>
       </c>
       <c r="H47">
         <v>7.8</v>
@@ -12421,7 +12421,7 @@
         <v>6</v>
       </c>
       <c r="O47">
-        <v>1.15</v>
+        <v>1.16</v>
       </c>
       <c r="P47">
         <v>2.8</v>
@@ -12430,7 +12430,7 @@
         <v>1.48</v>
       </c>
       <c r="R47">
-        <v>1.71</v>
+        <v>1.69</v>
       </c>
       <c r="S47">
         <v>2.16</v>
@@ -12439,7 +12439,7 @@
         <v>1.74</v>
       </c>
       <c r="U47">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="V47">
         <v>1.13</v>
@@ -12451,7 +12451,7 @@
         <v>34</v>
       </c>
       <c r="Y47">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="Z47">
         <v>85</v>
@@ -12547,7 +12547,7 @@
         <v>5.7</v>
       </c>
       <c r="BE47">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="BF47">
         <v>4.1</v>
@@ -12639,22 +12639,22 @@
         <v>1.8</v>
       </c>
       <c r="G48">
-        <v>1.84</v>
+        <v>1.83</v>
       </c>
       <c r="H48">
-        <v>5.4</v>
+        <v>5.5</v>
       </c>
       <c r="I48">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="J48">
-        <v>3.65</v>
+        <v>3.6</v>
       </c>
       <c r="K48">
         <v>3.7</v>
       </c>
       <c r="L48">
-        <v>1.01</v>
+        <v>1.39</v>
       </c>
       <c r="M48">
         <v>1.09</v>
@@ -12663,13 +12663,13 @@
         <v>3.2</v>
       </c>
       <c r="O48">
-        <v>1.42</v>
+        <v>1.41</v>
       </c>
       <c r="P48">
         <v>1.73</v>
       </c>
       <c r="Q48">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="R48">
         <v>1.28</v>
@@ -12681,13 +12681,13 @@
         <v>2.06</v>
       </c>
       <c r="U48">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="V48">
         <v>1.2</v>
       </c>
       <c r="W48">
-        <v>2.18</v>
+        <v>2.2</v>
       </c>
       <c r="X48">
         <v>11.5</v>
@@ -12702,13 +12702,13 @@
         <v>170</v>
       </c>
       <c r="AB48">
-        <v>9.6</v>
+        <v>9.4</v>
       </c>
       <c r="AC48">
         <v>8</v>
       </c>
       <c r="AD48">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AE48">
         <v>90</v>
@@ -12720,16 +12720,16 @@
         <v>10.5</v>
       </c>
       <c r="AH48">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AI48">
         <v>110</v>
       </c>
       <c r="AJ48">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AK48">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AL48">
         <v>50</v>
@@ -12738,7 +12738,7 @@
         <v>180</v>
       </c>
       <c r="AN48">
-        <v>15</v>
+        <v>14.5</v>
       </c>
       <c r="AO48">
         <v>130</v>
@@ -12750,7 +12750,7 @@
         <v>15</v>
       </c>
       <c r="AR48">
-        <v>36</v>
+        <v>10</v>
       </c>
       <c r="AS48">
         <v>11</v>
@@ -12759,16 +12759,16 @@
         <v>7</v>
       </c>
       <c r="AU48">
-        <v>7</v>
+        <v>7.4</v>
       </c>
       <c r="AV48">
-        <v>18.5</v>
+        <v>19</v>
       </c>
       <c r="AW48">
-        <v>75</v>
+        <v>11</v>
       </c>
       <c r="AX48">
-        <v>9</v>
+        <v>8.6</v>
       </c>
       <c r="AY48">
         <v>10</v>
@@ -12777,82 +12777,82 @@
         <v>20</v>
       </c>
       <c r="BA48">
-        <v>14.5</v>
+        <v>11</v>
       </c>
       <c r="BB48">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="BC48">
         <v>20</v>
       </c>
       <c r="BD48">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="BE48">
         <v>11</v>
       </c>
       <c r="BF48">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="BG48">
+        <v>11.5</v>
+      </c>
+      <c r="BH48">
+        <v>3.55</v>
+      </c>
+      <c r="BI48">
+        <v>2.48</v>
+      </c>
+      <c r="BJ48">
+        <v>13.5</v>
+      </c>
+      <c r="BK48">
+        <v>1.01</v>
+      </c>
+      <c r="BL48">
+        <v>220</v>
+      </c>
+      <c r="BM48">
+        <v>1.01</v>
+      </c>
+      <c r="BN48">
+        <v>4.9</v>
+      </c>
+      <c r="BO48">
+        <v>3.25</v>
+      </c>
+      <c r="BP48">
+        <v>15.5</v>
+      </c>
+      <c r="BQ48">
+        <v>1.01</v>
+      </c>
+      <c r="BR48">
+        <v>40</v>
+      </c>
+      <c r="BS48">
+        <v>1.01</v>
+      </c>
+      <c r="BT48">
         <v>11</v>
       </c>
-      <c r="BH48">
-        <v>1000</v>
-      </c>
-      <c r="BI48">
-        <v>1.01</v>
-      </c>
-      <c r="BJ48">
-        <v>1000</v>
-      </c>
-      <c r="BK48">
-        <v>1.01</v>
-      </c>
-      <c r="BL48">
-        <v>1000</v>
-      </c>
-      <c r="BM48">
-        <v>1.01</v>
-      </c>
-      <c r="BN48">
-        <v>1000</v>
-      </c>
-      <c r="BO48">
-        <v>1.01</v>
-      </c>
-      <c r="BP48">
-        <v>1000</v>
-      </c>
-      <c r="BQ48">
-        <v>1.01</v>
-      </c>
-      <c r="BR48">
-        <v>1000</v>
-      </c>
-      <c r="BS48">
-        <v>1.01</v>
-      </c>
-      <c r="BT48">
-        <v>1000</v>
-      </c>
       <c r="BU48">
         <v>1.01</v>
       </c>
       <c r="BV48">
-        <v>1000</v>
+        <v>70</v>
       </c>
       <c r="BW48">
         <v>1.01</v>
       </c>
       <c r="BX48">
-        <v>1000</v>
+        <v>85</v>
       </c>
       <c r="BY48">
         <v>1.01</v>
       </c>
       <c r="BZ48">
-        <v>1000</v>
+        <v>36</v>
       </c>
       <c r="CA48">
         <v>1.01</v>
@@ -12881,19 +12881,19 @@
         <v>1.68</v>
       </c>
       <c r="G49">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="H49">
         <v>4.1</v>
       </c>
       <c r="I49">
-        <v>5.7</v>
+        <v>5.8</v>
       </c>
       <c r="J49">
-        <v>3.55</v>
+        <v>3.4</v>
       </c>
       <c r="K49">
-        <v>6.2</v>
+        <v>6.4</v>
       </c>
       <c r="L49">
         <v>1.01</v>
@@ -12902,16 +12902,16 @@
         <v>1.02</v>
       </c>
       <c r="N49">
-        <v>2.62</v>
+        <v>1.01</v>
       </c>
       <c r="O49">
         <v>1.15</v>
       </c>
       <c r="P49">
-        <v>2.62</v>
+        <v>2.74</v>
       </c>
       <c r="Q49">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="R49">
         <v>1.68</v>
@@ -12929,7 +12929,7 @@
         <v>1.21</v>
       </c>
       <c r="W49">
-        <v>2.14</v>
+        <v>2.12</v>
       </c>
       <c r="X49">
         <v>1000</v>
@@ -13362,13 +13362,13 @@
         <v>272</v>
       </c>
       <c r="F51">
-        <v>2.26</v>
+        <v>2.24</v>
       </c>
       <c r="G51">
         <v>2.28</v>
       </c>
       <c r="H51">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="I51">
         <v>4.4</v>
@@ -13386,7 +13386,7 @@
         <v>1.16</v>
       </c>
       <c r="N51">
-        <v>2.34</v>
+        <v>2.32</v>
       </c>
       <c r="O51">
         <v>1.72</v>
@@ -13434,10 +13434,10 @@
         <v>7.4</v>
       </c>
       <c r="AD51">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AE51">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="AF51">
         <v>11.5</v>
@@ -13455,7 +13455,7 @@
         <v>32</v>
       </c>
       <c r="AK51">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="AL51">
         <v>110</v>
@@ -13518,10 +13518,10 @@
         <v>110</v>
       </c>
       <c r="BF51">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="BG51">
-        <v>42</v>
+        <v>18.5</v>
       </c>
       <c r="BH51">
         <v>2.38</v>
@@ -13533,7 +13533,7 @@
         <v>13</v>
       </c>
       <c r="BK51">
-        <v>7.4</v>
+        <v>7.2</v>
       </c>
       <c r="BL51">
         <v>370</v>
@@ -13551,16 +13551,16 @@
         <v>22</v>
       </c>
       <c r="BQ51">
-        <v>9.4</v>
+        <v>8.6</v>
       </c>
       <c r="BR51">
         <v>55</v>
       </c>
       <c r="BS51">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BT51">
-        <v>8.4</v>
+        <v>9</v>
       </c>
       <c r="BU51">
         <v>6.6</v>
@@ -13569,19 +13569,19 @@
         <v>55</v>
       </c>
       <c r="BW51">
-        <v>12.5</v>
+        <v>11.5</v>
       </c>
       <c r="BX51">
         <v>100</v>
       </c>
       <c r="BY51">
-        <v>22</v>
+        <v>12.5</v>
       </c>
       <c r="BZ51">
         <v>65</v>
       </c>
       <c r="CA51">
-        <v>13</v>
+        <v>11.5</v>
       </c>
       <c r="CB51" t="s">
         <v>298</v>
@@ -13622,22 +13622,22 @@
         <v>4.4</v>
       </c>
       <c r="L52">
-        <v>1.29</v>
+        <v>1.01</v>
       </c>
       <c r="M52">
         <v>1.01</v>
       </c>
       <c r="N52">
-        <v>1.01</v>
+        <v>3.45</v>
       </c>
       <c r="O52">
         <v>1.01</v>
       </c>
       <c r="P52">
-        <v>1.24</v>
+        <v>1.99</v>
       </c>
       <c r="Q52">
-        <v>1.01</v>
+        <v>1.76</v>
       </c>
       <c r="R52">
         <v>1.38</v>
@@ -13846,7 +13846,7 @@
         <v>274</v>
       </c>
       <c r="F53">
-        <v>1.5</v>
+        <v>1.56</v>
       </c>
       <c r="G53">
         <v>1.74</v>
@@ -13861,7 +13861,7 @@
         <v>4.2</v>
       </c>
       <c r="K53">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="L53">
         <v>1.01</v>
@@ -13870,10 +13870,10 @@
         <v>1.02</v>
       </c>
       <c r="N53">
-        <v>3.1</v>
+        <v>7.6</v>
       </c>
       <c r="O53">
-        <v>1.06</v>
+        <v>1.08</v>
       </c>
       <c r="P53">
         <v>3.1</v>
@@ -13882,13 +13882,13 @@
         <v>1.33</v>
       </c>
       <c r="R53">
-        <v>1.91</v>
+        <v>2.06</v>
       </c>
       <c r="S53">
         <v>1.65</v>
       </c>
       <c r="T53">
-        <v>1.33</v>
+        <v>1.01</v>
       </c>
       <c r="U53">
         <v>1.01</v>
@@ -14088,13 +14088,13 @@
         <v>275</v>
       </c>
       <c r="F54">
-        <v>1.55</v>
+        <v>1.58</v>
       </c>
       <c r="G54">
         <v>1.73</v>
       </c>
       <c r="H54">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="I54">
         <v>6.2</v>
@@ -14103,7 +14103,7 @@
         <v>4.6</v>
       </c>
       <c r="K54">
-        <v>7.8</v>
+        <v>7</v>
       </c>
       <c r="L54">
         <v>1.01</v>
@@ -14112,13 +14112,13 @@
         <v>1.02</v>
       </c>
       <c r="N54">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="O54">
         <v>1.09</v>
       </c>
       <c r="P54">
-        <v>2.72</v>
+        <v>2.76</v>
       </c>
       <c r="Q54">
         <v>1.35</v>
@@ -14127,7 +14127,7 @@
         <v>1.88</v>
       </c>
       <c r="S54">
-        <v>1.89</v>
+        <v>1.92</v>
       </c>
       <c r="T54">
         <v>1.01</v>
@@ -14348,7 +14348,7 @@
         <v>4.4</v>
       </c>
       <c r="L55">
-        <v>1.46</v>
+        <v>1.4</v>
       </c>
       <c r="M55">
         <v>1.09</v>
@@ -14396,7 +14396,7 @@
         <v>440</v>
       </c>
       <c r="AB55">
-        <v>6.4</v>
+        <v>6.2</v>
       </c>
       <c r="AC55">
         <v>9.800000000000001</v>
@@ -14492,61 +14492,61 @@
         <v>1.01</v>
       </c>
       <c r="BH55">
-        <v>3.35</v>
+        <v>1000</v>
       </c>
       <c r="BI55">
-        <v>2.52</v>
+        <v>1.01</v>
       </c>
       <c r="BJ55">
-        <v>13.5</v>
+        <v>18</v>
       </c>
       <c r="BK55">
         <v>1.01</v>
       </c>
       <c r="BL55">
-        <v>290</v>
+        <v>1000</v>
       </c>
       <c r="BM55">
         <v>1.01</v>
       </c>
       <c r="BN55">
-        <v>3.85</v>
+        <v>4.9</v>
       </c>
       <c r="BO55">
-        <v>3.3</v>
+        <v>2.68</v>
       </c>
       <c r="BP55">
-        <v>12.5</v>
+        <v>15</v>
       </c>
       <c r="BQ55">
-        <v>8.4</v>
+        <v>1.01</v>
       </c>
       <c r="BR55">
-        <v>40</v>
+        <v>48</v>
       </c>
       <c r="BS55">
         <v>1.01</v>
       </c>
       <c r="BT55">
-        <v>12</v>
+        <v>16</v>
       </c>
       <c r="BU55">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="BV55">
-        <v>110</v>
+        <v>1000</v>
       </c>
       <c r="BW55">
         <v>1.01</v>
       </c>
       <c r="BX55">
-        <v>120</v>
+        <v>1000</v>
       </c>
       <c r="BY55">
         <v>1.01</v>
       </c>
       <c r="BZ55">
-        <v>29</v>
+        <v>1000</v>
       </c>
       <c r="CA55">
         <v>1.01</v>
@@ -14596,10 +14596,10 @@
         <v>1.02</v>
       </c>
       <c r="N56">
-        <v>5.1</v>
+        <v>5.5</v>
       </c>
       <c r="O56">
-        <v>1.15</v>
+        <v>1.17</v>
       </c>
       <c r="P56">
         <v>2.28</v>
@@ -14608,10 +14608,10 @@
         <v>1.43</v>
       </c>
       <c r="R56">
-        <v>1.55</v>
+        <v>1.62</v>
       </c>
       <c r="S56">
-        <v>2.08</v>
+        <v>2.3</v>
       </c>
       <c r="T56">
         <v>1.4</v>
@@ -14817,7 +14817,7 @@
         <v>1.47</v>
       </c>
       <c r="G57">
-        <v>1.48</v>
+        <v>1.49</v>
       </c>
       <c r="H57">
         <v>8</v>
@@ -14832,10 +14832,10 @@
         <v>5</v>
       </c>
       <c r="L57">
-        <v>1.01</v>
+        <v>1.31</v>
       </c>
       <c r="M57">
-        <v>1.05</v>
+        <v>1.06</v>
       </c>
       <c r="N57">
         <v>4</v>
@@ -14844,22 +14844,22 @@
         <v>1.3</v>
       </c>
       <c r="P57">
-        <v>2.08</v>
+        <v>2.06</v>
       </c>
       <c r="Q57">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="R57">
-        <v>1.41</v>
+        <v>1.4</v>
       </c>
       <c r="S57">
-        <v>3.25</v>
+        <v>3.3</v>
       </c>
       <c r="T57">
-        <v>2.06</v>
+        <v>2.1</v>
       </c>
       <c r="U57">
-        <v>1.85</v>
+        <v>1.84</v>
       </c>
       <c r="V57">
         <v>1.12</v>
@@ -14874,13 +14874,13 @@
         <v>30</v>
       </c>
       <c r="Z57">
-        <v>75</v>
+        <v>190</v>
       </c>
       <c r="AA57">
         <v>330</v>
       </c>
       <c r="AB57">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AC57">
         <v>11</v>
@@ -14916,7 +14916,7 @@
         <v>180</v>
       </c>
       <c r="AN57">
-        <v>8</v>
+        <v>7.8</v>
       </c>
       <c r="AO57">
         <v>190</v>
@@ -14931,7 +14931,7 @@
         <v>60</v>
       </c>
       <c r="AS57">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="AT57">
         <v>7.2</v>
@@ -14964,73 +14964,73 @@
         <v>14.5</v>
       </c>
       <c r="BD57">
-        <v>19</v>
+        <v>16.5</v>
       </c>
       <c r="BE57">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BF57">
         <v>7</v>
       </c>
       <c r="BG57">
-        <v>10.5</v>
+        <v>11</v>
       </c>
       <c r="BH57">
-        <v>1000</v>
+        <v>4.2</v>
       </c>
       <c r="BI57">
-        <v>1.01</v>
+        <v>2.86</v>
       </c>
       <c r="BJ57">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BK57">
         <v>1.01</v>
       </c>
       <c r="BL57">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="BM57">
         <v>1.01</v>
       </c>
       <c r="BN57">
-        <v>1000</v>
+        <v>4.5</v>
       </c>
       <c r="BO57">
-        <v>1.01</v>
+        <v>3.05</v>
       </c>
       <c r="BP57">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="BQ57">
         <v>1.01</v>
       </c>
       <c r="BR57">
-        <v>1000</v>
+        <v>32</v>
       </c>
       <c r="BS57">
         <v>1.01</v>
       </c>
       <c r="BT57">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="BU57">
         <v>1.01</v>
       </c>
       <c r="BV57">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BW57">
         <v>1.01</v>
       </c>
       <c r="BX57">
-        <v>1000</v>
+        <v>95</v>
       </c>
       <c r="BY57">
         <v>1.01</v>
       </c>
       <c r="BZ57">
-        <v>1000</v>
+        <v>21</v>
       </c>
       <c r="CA57">
         <v>1.01</v>
@@ -15152,7 +15152,7 @@
         <v>40</v>
       </c>
       <c r="AL58">
-        <v>95</v>
+        <v>46</v>
       </c>
       <c r="AM58">
         <v>75</v>
@@ -15185,7 +15185,7 @@
         <v>9.800000000000001</v>
       </c>
       <c r="AW58">
-        <v>18.5</v>
+        <v>18</v>
       </c>
       <c r="AX58">
         <v>24</v>
@@ -15540,10 +15540,10 @@
         <v>281</v>
       </c>
       <c r="F60">
+        <v>1.97</v>
+      </c>
+      <c r="G60">
         <v>1.98</v>
-      </c>
-      <c r="G60">
-        <v>1.99</v>
       </c>
       <c r="H60">
         <v>4.4</v>
@@ -15591,7 +15591,7 @@
         <v>1.28</v>
       </c>
       <c r="W60">
-        <v>2</v>
+        <v>2.02</v>
       </c>
       <c r="X60">
         <v>14.5</v>
@@ -15603,7 +15603,7 @@
         <v>32</v>
       </c>
       <c r="AA60">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="AB60">
         <v>9</v>
@@ -15612,7 +15612,7 @@
         <v>8.4</v>
       </c>
       <c r="AD60">
-        <v>18</v>
+        <v>17.5</v>
       </c>
       <c r="AE60">
         <v>60</v>
@@ -15630,7 +15630,7 @@
         <v>65</v>
       </c>
       <c r="AJ60">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="AK60">
         <v>21</v>
@@ -15645,7 +15645,7 @@
         <v>14.5</v>
       </c>
       <c r="AO60">
-        <v>60</v>
+        <v>65</v>
       </c>
       <c r="AP60">
         <v>13</v>
@@ -15687,7 +15687,7 @@
         <v>20</v>
       </c>
       <c r="BC60">
-        <v>19</v>
+        <v>18.5</v>
       </c>
       <c r="BD60">
         <v>32</v>
@@ -15845,7 +15845,7 @@
         <v>12</v>
       </c>
       <c r="AA61">
-        <v>23</v>
+        <v>26</v>
       </c>
       <c r="AB61">
         <v>16</v>
@@ -16042,22 +16042,22 @@
         <v>4.3</v>
       </c>
       <c r="L62">
-        <v>1.01</v>
+        <v>1.35</v>
       </c>
       <c r="M62">
         <v>1.07</v>
       </c>
       <c r="N62">
-        <v>3.15</v>
+        <v>3.6</v>
       </c>
       <c r="O62">
-        <v>1.3</v>
+        <v>1.31</v>
       </c>
       <c r="P62">
-        <v>1.81</v>
+        <v>1.89</v>
       </c>
       <c r="Q62">
-        <v>1.91</v>
+        <v>1.95</v>
       </c>
       <c r="R62">
         <v>1.33</v>
@@ -16066,10 +16066,10 @@
         <v>3.4</v>
       </c>
       <c r="T62">
-        <v>1.81</v>
+        <v>1.93</v>
       </c>
       <c r="U62">
-        <v>1.8</v>
+        <v>1.9</v>
       </c>
       <c r="V62">
         <v>2.32</v>
@@ -16078,94 +16078,94 @@
         <v>1.17</v>
       </c>
       <c r="X62">
-        <v>1000</v>
+        <v>17</v>
       </c>
       <c r="Y62">
-        <v>1000</v>
+        <v>8.4</v>
       </c>
       <c r="Z62">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AA62">
-        <v>1000</v>
+        <v>17.5</v>
       </c>
       <c r="AB62">
-        <v>1000</v>
+        <v>20</v>
       </c>
       <c r="AC62">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD62">
-        <v>1000</v>
+        <v>10.5</v>
       </c>
       <c r="AE62">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AF62">
-        <v>1000</v>
+        <v>55</v>
       </c>
       <c r="AG62">
-        <v>1000</v>
+        <v>25</v>
       </c>
       <c r="AH62">
-        <v>1000</v>
+        <v>23</v>
       </c>
       <c r="AI62">
-        <v>1000</v>
+        <v>40</v>
       </c>
       <c r="AJ62">
-        <v>1000</v>
+        <v>200</v>
       </c>
       <c r="AK62">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AL62">
-        <v>1000</v>
+        <v>110</v>
       </c>
       <c r="AM62">
-        <v>1000</v>
+        <v>160</v>
       </c>
       <c r="AN62">
-        <v>1000</v>
+        <v>140</v>
       </c>
       <c r="AO62">
-        <v>1000</v>
+        <v>11.5</v>
       </c>
       <c r="AP62">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AQ62">
-        <v>1.01</v>
+        <v>6.8</v>
       </c>
       <c r="AR62">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AS62">
-        <v>1.01</v>
+        <v>14</v>
       </c>
       <c r="AT62">
-        <v>1.01</v>
+        <v>16</v>
       </c>
       <c r="AU62">
-        <v>1.01</v>
+        <v>7.8</v>
       </c>
       <c r="AV62">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="AW62">
-        <v>1.01</v>
+        <v>15.5</v>
       </c>
       <c r="AX62">
-        <v>1.01</v>
+        <v>38</v>
       </c>
       <c r="AY62">
-        <v>1.01</v>
+        <v>19.5</v>
       </c>
       <c r="AZ62">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="BA62">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="BB62">
         <v>1.01</v>
@@ -16183,7 +16183,7 @@
         <v>1.01</v>
       </c>
       <c r="BG62">
-        <v>1.01</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="BH62">
         <v>3.55</v>
@@ -16281,7 +16281,7 @@
         <v>4.5</v>
       </c>
       <c r="K63">
-        <v>4.6</v>
+        <v>4.7</v>
       </c>
       <c r="L63">
         <v>1.38</v>
@@ -16290,7 +16290,7 @@
         <v>1.06</v>
       </c>
       <c r="N63">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="O63">
         <v>1.29</v>
@@ -16299,7 +16299,7 @@
         <v>2.12</v>
       </c>
       <c r="Q63">
-        <v>1.86</v>
+        <v>1.87</v>
       </c>
       <c r="R63">
         <v>1.42</v>
@@ -16308,10 +16308,10 @@
         <v>3.2</v>
       </c>
       <c r="T63">
-        <v>1.98</v>
+        <v>1.99</v>
       </c>
       <c r="U63">
-        <v>2</v>
+        <v>1.97</v>
       </c>
       <c r="V63">
         <v>2.78</v>
@@ -16326,7 +16326,7 @@
         <v>8.199999999999999</v>
       </c>
       <c r="Z63">
-        <v>8.800000000000001</v>
+        <v>9</v>
       </c>
       <c r="AA63">
         <v>13.5</v>
@@ -16362,7 +16362,7 @@
         <v>95</v>
       </c>
       <c r="AL63">
-        <v>110</v>
+        <v>100</v>
       </c>
       <c r="AM63">
         <v>130</v>
@@ -16371,16 +16371,16 @@
         <v>110</v>
       </c>
       <c r="AO63">
-        <v>8.199999999999999</v>
+        <v>8.4</v>
       </c>
       <c r="AP63">
-        <v>16</v>
+        <v>16.5</v>
       </c>
       <c r="AQ63">
         <v>8</v>
       </c>
       <c r="AR63">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="AS63">
         <v>13</v>
@@ -16389,7 +16389,7 @@
         <v>22</v>
       </c>
       <c r="AU63">
-        <v>9.6</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="AV63">
         <v>9.4</v>
@@ -16398,7 +16398,7 @@
         <v>15.5</v>
       </c>
       <c r="AX63">
-        <v>50</v>
+        <v>55</v>
       </c>
       <c r="AY63">
         <v>24</v>
@@ -16416,7 +16416,7 @@
         <v>90</v>
       </c>
       <c r="BD63">
-        <v>85</v>
+        <v>90</v>
       </c>
       <c r="BE63">
         <v>100</v>
@@ -16511,16 +16511,16 @@
         <v>2.06</v>
       </c>
       <c r="G64">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="H64">
         <v>3.1</v>
       </c>
       <c r="I64">
-        <v>3.45</v>
+        <v>3.4</v>
       </c>
       <c r="J64">
-        <v>4.2</v>
+        <v>4.5</v>
       </c>
       <c r="K64">
         <v>5</v>
@@ -16535,10 +16535,10 @@
         <v>8.6</v>
       </c>
       <c r="O64">
-        <v>1.08</v>
+        <v>1.09</v>
       </c>
       <c r="P64">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Q64">
         <v>1.29</v>
@@ -16556,13 +16556,13 @@
         <v>3.55</v>
       </c>
       <c r="V64">
-        <v>1.41</v>
+        <v>1.42</v>
       </c>
       <c r="W64">
-        <v>1.9</v>
+        <v>1.89</v>
       </c>
       <c r="X64">
-        <v>470</v>
+        <v>460</v>
       </c>
       <c r="Y64">
         <v>40</v>
@@ -16616,7 +16616,7 @@
         <v>14</v>
       </c>
       <c r="AP64">
-        <v>29</v>
+        <v>5.2</v>
       </c>
       <c r="AQ64">
         <v>21</v>
@@ -16756,10 +16756,10 @@
         <v>1.82</v>
       </c>
       <c r="H65">
-        <v>5.1</v>
+        <v>5.2</v>
       </c>
       <c r="I65">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="J65">
         <v>3.8</v>
@@ -16771,37 +16771,37 @@
         <v>1.01</v>
       </c>
       <c r="M65">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="N65">
-        <v>3.75</v>
+        <v>3.7</v>
       </c>
       <c r="O65">
-        <v>1.32</v>
+        <v>1.33</v>
       </c>
       <c r="P65">
-        <v>1.87</v>
+        <v>1.88</v>
       </c>
       <c r="Q65">
-        <v>1.93</v>
+        <v>1.98</v>
       </c>
       <c r="R65">
-        <v>1.32</v>
+        <v>1.34</v>
       </c>
       <c r="S65">
-        <v>3.15</v>
+        <v>3.35</v>
       </c>
       <c r="T65">
         <v>1.89</v>
       </c>
       <c r="U65">
-        <v>2.04</v>
+        <v>2.02</v>
       </c>
       <c r="V65">
-        <v>1.21</v>
+        <v>1.22</v>
       </c>
       <c r="W65">
-        <v>2.2</v>
+        <v>2.22</v>
       </c>
       <c r="X65">
         <v>17</v>
@@ -16816,7 +16816,7 @@
         <v>160</v>
       </c>
       <c r="AB65">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AC65">
         <v>8.800000000000001</v>
@@ -16834,7 +16834,7 @@
         <v>10</v>
       </c>
       <c r="AH65">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AI65">
         <v>85</v>
@@ -16846,31 +16846,31 @@
         <v>19.5</v>
       </c>
       <c r="AL65">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="AM65">
         <v>130</v>
       </c>
       <c r="AN65">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AO65">
         <v>110</v>
       </c>
       <c r="AP65">
-        <v>13</v>
+        <v>12.5</v>
       </c>
       <c r="AQ65">
         <v>15.5</v>
       </c>
       <c r="AR65">
-        <v>8.4</v>
+        <v>7.8</v>
       </c>
       <c r="AS65">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AT65">
-        <v>7.6</v>
+        <v>7.4</v>
       </c>
       <c r="AU65">
         <v>7.8</v>
@@ -16879,7 +16879,7 @@
         <v>18</v>
       </c>
       <c r="AW65">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="AX65">
         <v>9.6</v>
@@ -16891,25 +16891,25 @@
         <v>17.5</v>
       </c>
       <c r="BA65">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="BB65">
-        <v>17</v>
+        <v>16.5</v>
       </c>
       <c r="BC65">
         <v>17</v>
       </c>
       <c r="BD65">
+        <v>7.4</v>
+      </c>
+      <c r="BE65">
         <v>8</v>
-      </c>
-      <c r="BE65">
-        <v>8.800000000000001</v>
       </c>
       <c r="BF65">
         <v>10.5</v>
       </c>
       <c r="BG65">
-        <v>8.800000000000001</v>
+        <v>7.8</v>
       </c>
       <c r="BH65">
         <v>1000</v>
@@ -16992,16 +16992,16 @@
         <v>287</v>
       </c>
       <c r="F66">
-        <v>1.17</v>
+        <v>1.18</v>
       </c>
       <c r="G66">
         <v>1.19</v>
       </c>
       <c r="H66">
-        <v>19.5</v>
+        <v>19</v>
       </c>
       <c r="I66">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="J66">
         <v>9</v>
@@ -17028,25 +17028,25 @@
         <v>1.43</v>
       </c>
       <c r="R66">
-        <v>1.81</v>
+        <v>1.84</v>
       </c>
       <c r="S66">
-        <v>1.92</v>
+        <v>1.96</v>
       </c>
       <c r="T66">
-        <v>2.16</v>
+        <v>2.14</v>
       </c>
       <c r="U66">
-        <v>1.78</v>
+        <v>1.79</v>
       </c>
       <c r="V66">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W66">
         <v>6.2</v>
       </c>
       <c r="X66">
-        <v>42</v>
+        <v>1000</v>
       </c>
       <c r="Y66">
         <v>75</v>
@@ -17064,31 +17064,31 @@
         <v>24</v>
       </c>
       <c r="AD66">
-        <v>70</v>
+        <v>85</v>
       </c>
       <c r="AE66">
         <v>380</v>
       </c>
       <c r="AF66">
-        <v>9.199999999999999</v>
+        <v>10.5</v>
       </c>
       <c r="AG66">
         <v>15.5</v>
       </c>
       <c r="AH66">
-        <v>44</v>
+        <v>48</v>
       </c>
       <c r="AI66">
         <v>260</v>
       </c>
       <c r="AJ66">
-        <v>9.4</v>
+        <v>970</v>
       </c>
       <c r="AK66">
         <v>14.5</v>
       </c>
       <c r="AL66">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="AM66">
         <v>250</v>
@@ -17100,58 +17100,58 @@
         <v>480</v>
       </c>
       <c r="AP66">
-        <v>7.8</v>
+        <v>4.2</v>
       </c>
       <c r="AQ66">
-        <v>8.4</v>
+        <v>6.6</v>
       </c>
       <c r="AR66">
-        <v>8.800000000000001</v>
+        <v>3.85</v>
       </c>
       <c r="AS66">
-        <v>9.199999999999999</v>
+        <v>3.9</v>
       </c>
       <c r="AT66">
         <v>10</v>
       </c>
       <c r="AU66">
-        <v>15.5</v>
+        <v>18.5</v>
       </c>
       <c r="AV66">
-        <v>8</v>
+        <v>3.9</v>
       </c>
       <c r="AW66">
-        <v>9</v>
+        <v>3.9</v>
       </c>
       <c r="AX66">
-        <v>7.6</v>
+        <v>7.2</v>
       </c>
       <c r="AY66">
         <v>10</v>
       </c>
       <c r="AZ66">
-        <v>7.6</v>
+        <v>30</v>
       </c>
       <c r="BA66">
-        <v>8.800000000000001</v>
+        <v>3.85</v>
       </c>
       <c r="BB66">
-        <v>8</v>
+        <v>7.2</v>
       </c>
       <c r="BC66">
         <v>12</v>
       </c>
       <c r="BD66">
-        <v>7.8</v>
+        <v>6.2</v>
       </c>
       <c r="BE66">
-        <v>8.800000000000001</v>
+        <v>4</v>
       </c>
       <c r="BF66">
         <v>2.88</v>
       </c>
       <c r="BG66">
-        <v>9</v>
+        <v>3.9</v>
       </c>
       <c r="BH66">
         <v>1000</v>
@@ -17234,58 +17234,58 @@
         <v>288</v>
       </c>
       <c r="F67">
+        <v>1.16</v>
+      </c>
+      <c r="G67">
         <v>1.17</v>
       </c>
-      <c r="G67">
-        <v>1.18</v>
-      </c>
       <c r="H67">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="I67">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="J67">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K67">
         <v>10.5</v>
       </c>
       <c r="L67">
-        <v>1.21</v>
+        <v>1.2</v>
       </c>
       <c r="M67">
         <v>1.02</v>
       </c>
       <c r="N67">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="O67">
         <v>1.11</v>
       </c>
       <c r="P67">
-        <v>3.75</v>
+        <v>3.8</v>
       </c>
       <c r="Q67">
-        <v>1.34</v>
+        <v>1.33</v>
       </c>
       <c r="R67">
-        <v>2.12</v>
+        <v>2.14</v>
       </c>
       <c r="S67">
-        <v>1.86</v>
+        <v>1.85</v>
       </c>
       <c r="T67">
-        <v>2.08</v>
+        <v>2.1</v>
       </c>
       <c r="U67">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="V67">
         <v>1.04</v>
       </c>
       <c r="W67">
-        <v>6.6</v>
+        <v>6.8</v>
       </c>
       <c r="X67">
         <v>46</v>
@@ -17300,19 +17300,19 @@
         <v>1000</v>
       </c>
       <c r="AB67">
-        <v>14.5</v>
+        <v>15</v>
       </c>
       <c r="AC67">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AD67">
-        <v>75</v>
+        <v>80</v>
       </c>
       <c r="AE67">
-        <v>350</v>
+        <v>390</v>
       </c>
       <c r="AF67">
-        <v>10</v>
+        <v>10.5</v>
       </c>
       <c r="AG67">
         <v>14</v>
@@ -17336,7 +17336,7 @@
         <v>1000</v>
       </c>
       <c r="AN67">
-        <v>2.68</v>
+        <v>2.6</v>
       </c>
       <c r="AO67">
         <v>360</v>
@@ -17345,28 +17345,28 @@
         <v>40</v>
       </c>
       <c r="AQ67">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="AR67">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="AS67">
-        <v>19.5</v>
+        <v>18</v>
       </c>
       <c r="AT67">
-        <v>13</v>
+        <v>13.5</v>
       </c>
       <c r="AU67">
         <v>21</v>
       </c>
       <c r="AV67">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="AW67">
-        <v>50</v>
+        <v>30</v>
       </c>
       <c r="AX67">
-        <v>9.199999999999999</v>
+        <v>9.4</v>
       </c>
       <c r="AY67">
         <v>12.5</v>
@@ -17375,10 +17375,10 @@
         <v>36</v>
       </c>
       <c r="BA67">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="BB67">
-        <v>8.4</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="BC67">
         <v>12</v>
@@ -17390,19 +17390,19 @@
         <v>46</v>
       </c>
       <c r="BF67">
-        <v>2.54</v>
+        <v>2.48</v>
       </c>
       <c r="BG67">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BH67">
         <v>1000</v>
       </c>
       <c r="BI67">
-        <v>1.47</v>
+        <v>1.23</v>
       </c>
       <c r="BJ67">
-        <v>36</v>
+        <v>1000</v>
       </c>
       <c r="BK67">
         <v>7.4</v>
@@ -17414,7 +17414,7 @@
         <v>32</v>
       </c>
       <c r="BN67">
-        <v>9.4</v>
+        <v>1000</v>
       </c>
       <c r="BO67">
         <v>2.84</v>
@@ -17432,7 +17432,7 @@
         <v>9.199999999999999</v>
       </c>
       <c r="BT67">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="BU67">
         <v>9.199999999999999</v>
@@ -17450,7 +17450,7 @@
         <v>25</v>
       </c>
       <c r="BZ67">
-        <v>15.5</v>
+        <v>15</v>
       </c>
       <c r="CA67">
         <v>4.2</v>
@@ -17482,10 +17482,10 @@
         <v>4.8</v>
       </c>
       <c r="H68">
-        <v>1.83</v>
+        <v>1.84</v>
       </c>
       <c r="I68">
-        <v>1.93</v>
+        <v>1.92</v>
       </c>
       <c r="J68">
         <v>3.9</v>
@@ -17524,7 +17524,7 @@
         <v>2.24</v>
       </c>
       <c r="V68">
-        <v>2.06</v>
+        <v>2.08</v>
       </c>
       <c r="W68">
         <v>1.26</v>
@@ -17960,40 +17960,40 @@
         <v>291</v>
       </c>
       <c r="F70">
-        <v>1.1</v>
+        <v>1.75</v>
       </c>
       <c r="G70">
-        <v>1.94</v>
+        <v>1.83</v>
       </c>
       <c r="H70">
-        <v>5.3</v>
+        <v>5.9</v>
       </c>
       <c r="I70">
-        <v>1000</v>
+        <v>7.4</v>
       </c>
       <c r="J70">
-        <v>1.09</v>
+        <v>3.45</v>
       </c>
       <c r="K70">
-        <v>1000</v>
+        <v>3.8</v>
       </c>
       <c r="L70">
         <v>1.01</v>
       </c>
       <c r="M70">
-        <v>1.05</v>
+        <v>1.04</v>
       </c>
       <c r="N70">
-        <v>2.74</v>
+        <v>2.8</v>
       </c>
       <c r="O70">
         <v>1.45</v>
       </c>
       <c r="P70">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="Q70">
-        <v>2.28</v>
+        <v>2.2</v>
       </c>
       <c r="R70">
         <v>1.2</v>
@@ -18011,7 +18011,7 @@
         <v>1.17</v>
       </c>
       <c r="W70">
-        <v>1.01</v>
+        <v>2.2</v>
       </c>
       <c r="X70">
         <v>1000</v>
@@ -18068,52 +18068,52 @@
         <v>1000</v>
       </c>
       <c r="AP70">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AQ70">
-        <v>11</v>
+        <v>1.01</v>
       </c>
       <c r="AR70">
-        <v>28</v>
+        <v>1.01</v>
       </c>
       <c r="AS70">
-        <v>100</v>
+        <v>1.01</v>
       </c>
       <c r="AT70">
-        <v>5.5</v>
+        <v>1.01</v>
       </c>
       <c r="AU70">
-        <v>6.6</v>
+        <v>1.01</v>
       </c>
       <c r="AV70">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="AW70">
-        <v>65</v>
+        <v>1.01</v>
       </c>
       <c r="AX70">
-        <v>7.4</v>
+        <v>1.01</v>
       </c>
       <c r="AY70">
-        <v>9</v>
+        <v>1.01</v>
       </c>
       <c r="AZ70">
-        <v>20</v>
+        <v>1.01</v>
       </c>
       <c r="BA70">
-        <v>80</v>
+        <v>1.01</v>
       </c>
       <c r="BB70">
-        <v>15</v>
+        <v>1.01</v>
       </c>
       <c r="BC70">
-        <v>18</v>
+        <v>1.01</v>
       </c>
       <c r="BD70">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="BE70">
-        <v>100</v>
+        <v>1.01</v>
       </c>
       <c r="BF70">
         <v>1.01</v>
@@ -18232,7 +18232,7 @@
         <v>1.61</v>
       </c>
       <c r="P71">
-        <v>1.49</v>
+        <v>1.46</v>
       </c>
       <c r="Q71">
         <v>2.84</v>
@@ -18247,13 +18247,13 @@
         <v>2.22</v>
       </c>
       <c r="U71">
-        <v>1.74</v>
+        <v>1.73</v>
       </c>
       <c r="V71">
         <v>1.35</v>
       </c>
       <c r="W71">
-        <v>1.6</v>
+        <v>1.61</v>
       </c>
       <c r="X71">
         <v>8</v>
@@ -18373,13 +18373,13 @@
         <v>13.5</v>
       </c>
       <c r="BK71">
-        <v>8.800000000000001</v>
+        <v>1.01</v>
       </c>
       <c r="BL71">
         <v>270</v>
       </c>
       <c r="BM71">
-        <v>21</v>
+        <v>1.01</v>
       </c>
       <c r="BN71">
         <v>5.8</v>
@@ -18391,13 +18391,13 @@
         <v>27</v>
       </c>
       <c r="BQ71">
-        <v>17.5</v>
+        <v>1.01</v>
       </c>
       <c r="BR71">
         <v>60</v>
       </c>
       <c r="BS71">
-        <v>36</v>
+        <v>1.01</v>
       </c>
       <c r="BT71">
         <v>7.4</v>
@@ -18409,19 +18409,19 @@
         <v>42</v>
       </c>
       <c r="BW71">
-        <v>27</v>
+        <v>1.01</v>
       </c>
       <c r="BX71">
         <v>70</v>
       </c>
       <c r="BY71">
-        <v>44</v>
+        <v>1.01</v>
       </c>
       <c r="BZ71">
         <v>65</v>
       </c>
       <c r="CA71">
-        <v>40</v>
+        <v>1.01</v>
       </c>
       <c r="CB71" t="s">
         <v>298</v>
@@ -18474,7 +18474,7 @@
         <v>1.29</v>
       </c>
       <c r="P72">
-        <v>1.96</v>
+        <v>2</v>
       </c>
       <c r="Q72">
         <v>1.87</v>
@@ -19030,7 +19030,7 @@
         <v>160</v>
       </c>
       <c r="AN74">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AO74">
         <v>80</v>
@@ -19069,7 +19069,7 @@
         <v>18.5</v>
       </c>
       <c r="BA74">
-        <v>10</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="BB74">
         <v>22</v>
@@ -19081,7 +19081,7 @@
         <v>36</v>
       </c>
       <c r="BE74">
-        <v>10.5</v>
+        <v>10</v>
       </c>
       <c r="BF74">
         <v>20</v>
@@ -19170,166 +19170,166 @@
         <v>296</v>
       </c>
       <c r="F75">
-        <v>1.45</v>
+        <v>1.52</v>
       </c>
       <c r="G75">
-        <v>1.48</v>
+        <v>1.58</v>
       </c>
       <c r="H75">
-        <v>10</v>
+        <v>7.8</v>
       </c>
       <c r="I75">
-        <v>12.5</v>
+        <v>9.4</v>
       </c>
       <c r="J75">
-        <v>4.3</v>
+        <v>4.2</v>
       </c>
       <c r="K75">
-        <v>4.7</v>
+        <v>4.4</v>
       </c>
       <c r="L75">
         <v>1.01</v>
       </c>
       <c r="M75">
-        <v>1.06</v>
+        <v>1.09</v>
       </c>
       <c r="N75">
         <v>3.3</v>
       </c>
       <c r="O75">
-        <v>1.34</v>
+        <v>1.4</v>
       </c>
       <c r="P75">
         <v>1.78</v>
       </c>
       <c r="Q75">
-        <v>1.8</v>
+        <v>2.18</v>
       </c>
       <c r="R75">
         <v>1.29</v>
       </c>
       <c r="S75">
-        <v>3.2</v>
+        <v>4</v>
       </c>
       <c r="T75">
-        <v>1.02</v>
+        <v>2.3</v>
       </c>
       <c r="U75">
-        <v>1.02</v>
+        <v>1.64</v>
       </c>
       <c r="V75">
-        <v>1.08</v>
+        <v>1.12</v>
       </c>
       <c r="W75">
-        <v>3.05</v>
+        <v>2.74</v>
       </c>
       <c r="X75">
-        <v>1000</v>
+        <v>12</v>
       </c>
       <c r="Y75">
-        <v>1000</v>
+        <v>22</v>
       </c>
       <c r="Z75">
-        <v>1000</v>
+        <v>80</v>
       </c>
       <c r="AA75">
-        <v>1000</v>
+        <v>360</v>
       </c>
       <c r="AB75">
-        <v>1000</v>
+        <v>6.8</v>
       </c>
       <c r="AC75">
-        <v>1000</v>
+        <v>9.6</v>
       </c>
       <c r="AD75">
-        <v>1000</v>
+        <v>34</v>
       </c>
       <c r="AE75">
-        <v>1000</v>
+        <v>180</v>
       </c>
       <c r="AF75">
-        <v>1000</v>
+        <v>8</v>
       </c>
       <c r="AG75">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AH75">
-        <v>1000</v>
+        <v>38</v>
       </c>
       <c r="AI75">
-        <v>1000</v>
+        <v>230</v>
       </c>
       <c r="AJ75">
-        <v>1000</v>
+        <v>14</v>
       </c>
       <c r="AK75">
-        <v>1000</v>
+        <v>19.5</v>
       </c>
       <c r="AL75">
-        <v>1000</v>
+        <v>60</v>
       </c>
       <c r="AM75">
-        <v>1000</v>
+        <v>280</v>
       </c>
       <c r="AN75">
-        <v>1000</v>
+        <v>11</v>
       </c>
       <c r="AO75">
-        <v>1000</v>
+        <v>320</v>
       </c>
       <c r="AP75">
-        <v>1.01</v>
+        <v>10</v>
       </c>
       <c r="AQ75">
-        <v>1.01</v>
+        <v>18.5</v>
       </c>
       <c r="AR75">
-        <v>1.01</v>
+        <v>11.5</v>
       </c>
       <c r="AS75">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AT75">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AU75">
-        <v>1.01</v>
+        <v>8.4</v>
       </c>
       <c r="AV75">
-        <v>1.01</v>
+        <v>27</v>
       </c>
       <c r="AW75">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="AX75">
-        <v>1.01</v>
+        <v>7.2</v>
       </c>
       <c r="AY75">
-        <v>1.01</v>
+        <v>9.6</v>
       </c>
       <c r="AZ75">
-        <v>1.01</v>
+        <v>26</v>
       </c>
       <c r="BA75">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BB75">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BC75">
-        <v>1.01</v>
+        <v>17</v>
       </c>
       <c r="BD75">
-        <v>1.01</v>
+        <v>40</v>
       </c>
       <c r="BE75">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BF75">
-        <v>1.01</v>
+        <v>9.4</v>
       </c>
       <c r="BG75">
-        <v>1.01</v>
+        <v>11</v>
       </c>
       <c r="BH75">
         <v>1000</v>
@@ -19415,19 +19415,19 @@
         <v>1.35</v>
       </c>
       <c r="G76">
-        <v>1.5</v>
+        <v>1.44</v>
       </c>
       <c r="H76">
-        <v>7.8</v>
+        <v>10</v>
       </c>
       <c r="I76">
-        <v>110</v>
+        <v>14</v>
       </c>
       <c r="J76">
         <v>4.4</v>
       </c>
       <c r="K76">
-        <v>7.8</v>
+        <v>5.8</v>
       </c>
       <c r="L76">
         <v>1.29</v>
@@ -19436,22 +19436,22 @@
         <v>1.01</v>
       </c>
       <c r="N76">
-        <v>3.45</v>
+        <v>3.55</v>
       </c>
       <c r="O76">
-        <v>1.26</v>
+        <v>1.27</v>
       </c>
       <c r="P76">
         <v>1.98</v>
       </c>
       <c r="Q76">
-        <v>1.79</v>
+        <v>1.8</v>
       </c>
       <c r="R76">
         <v>1.38</v>
       </c>
       <c r="S76">
-        <v>2.76</v>
+        <v>2.88</v>
       </c>
       <c r="T76">
         <v>1.01</v>
@@ -19460,10 +19460,10 @@
         <v>1.01</v>
       </c>
       <c r="V76">
-        <v>1.06</v>
+        <v>1.07</v>
       </c>
       <c r="W76">
-        <v>3</v>
+        <v>3.25</v>
       </c>
       <c r="X76">
         <v>1000</v>
@@ -19520,7 +19520,7 @@
         <v>1000</v>
       </c>
       <c r="AP76">
-        <v>1.01</v>
+        <v>13</v>
       </c>
       <c r="AQ76">
         <v>1.01</v>
@@ -19532,10 +19532,10 @@
         <v>1.01</v>
       </c>
       <c r="AT76">
-        <v>1.01</v>
+        <v>5.9</v>
       </c>
       <c r="AU76">
-        <v>1.01</v>
+        <v>9</v>
       </c>
       <c r="AV76">
         <v>1.01</v>
@@ -19544,10 +19544,10 @@
         <v>1.01</v>
       </c>
       <c r="AX76">
-        <v>1.01</v>
+        <v>6</v>
       </c>
       <c r="AY76">
-        <v>1.01</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AZ76">
         <v>1.01</v>
@@ -19556,10 +19556,10 @@
         <v>1.01</v>
       </c>
       <c r="BB76">
-        <v>1.01</v>
+        <v>8.6</v>
       </c>
       <c r="BC76">
-        <v>1.01</v>
+        <v>12</v>
       </c>
       <c r="BD76">
         <v>1.01</v>
@@ -19568,7 +19568,7 @@
         <v>1.01</v>
       </c>
       <c r="BF76">
-        <v>1.01</v>
+        <v>5.4</v>
       </c>
       <c r="BG76">
         <v>1.01</v>
